--- a/wwwroot/ExcelModel/Kik_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Kik_PHY_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6073EE-45BF-408A-A979-AEF6FF54DAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6858BC92-7C90-4706-8409-DCAF60DA23A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="216">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -1656,6 +1656,14 @@
   </si>
   <si>
     <t>Sample：</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clockwise</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Anticlockwise</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2308,6 +2316,66 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2317,65 +2385,50 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2407,149 +2460,122 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2561,27 +2587,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2598,6 +2603,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2946,25 +2954,25 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="97"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="98"/>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="98"/>
-      <c r="S3" s="98"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -3195,185 +3203,185 @@
       </c>
       <c r="F11" s="82"/>
       <c r="G11" s="82"/>
-      <c r="H11" s="95"/>
+      <c r="H11" s="79"/>
       <c r="I11" s="81" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="82"/>
       <c r="K11" s="82"/>
-      <c r="L11" s="95"/>
+      <c r="L11" s="79"/>
       <c r="M11" s="81" t="s">
         <v>11</v>
       </c>
       <c r="N11" s="82"/>
       <c r="O11" s="82"/>
-      <c r="P11" s="95"/>
+      <c r="P11" s="79"/>
       <c r="Q11" s="81" t="s">
         <v>12</v>
       </c>
       <c r="R11" s="82"/>
       <c r="S11" s="82"/>
-      <c r="T11" s="95"/>
+      <c r="T11" s="79"/>
       <c r="U11" s="81" t="s">
         <v>13</v>
       </c>
       <c r="V11" s="82"/>
       <c r="W11" s="82"/>
-      <c r="X11" s="96"/>
+      <c r="X11" s="78"/>
       <c r="Y11" s="86"/>
       <c r="Z11" s="87"/>
       <c r="AA11" s="87"/>
       <c r="AB11" s="88"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="77"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="95"/>
-      <c r="M12" s="99"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="96"/>
-      <c r="P12" s="95"/>
-      <c r="Q12" s="99"/>
-      <c r="R12" s="96"/>
-      <c r="S12" s="96"/>
-      <c r="T12" s="95"/>
-      <c r="U12" s="99"/>
-      <c r="V12" s="96"/>
-      <c r="W12" s="96"/>
-      <c r="X12" s="95"/>
-      <c r="Y12" s="99"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="96"/>
-      <c r="AB12" s="95"/>
+      <c r="A12" s="97"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="77"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="79"/>
+      <c r="Q12" s="77"/>
+      <c r="R12" s="78"/>
+      <c r="S12" s="78"/>
+      <c r="T12" s="79"/>
+      <c r="U12" s="77"/>
+      <c r="V12" s="78"/>
+      <c r="W12" s="78"/>
+      <c r="X12" s="79"/>
+      <c r="Y12" s="77"/>
+      <c r="Z12" s="78"/>
+      <c r="AA12" s="78"/>
+      <c r="AB12" s="79"/>
     </row>
     <row r="13" spans="1:28">
-      <c r="A13" s="77"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="95"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="95"/>
-      <c r="Q13" s="99"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="95"/>
-      <c r="U13" s="99"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="96"/>
-      <c r="X13" s="95"/>
-      <c r="Y13" s="99"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="96"/>
-      <c r="AB13" s="95"/>
+      <c r="A13" s="97"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="79"/>
+      <c r="Q13" s="77"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="78"/>
+      <c r="T13" s="79"/>
+      <c r="U13" s="77"/>
+      <c r="V13" s="78"/>
+      <c r="W13" s="78"/>
+      <c r="X13" s="79"/>
+      <c r="Y13" s="77"/>
+      <c r="Z13" s="78"/>
+      <c r="AA13" s="78"/>
+      <c r="AB13" s="79"/>
     </row>
     <row r="14" spans="1:28">
-      <c r="A14" s="77"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="99"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="99"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="95"/>
-      <c r="U14" s="99"/>
-      <c r="V14" s="96"/>
-      <c r="W14" s="96"/>
-      <c r="X14" s="95"/>
-      <c r="Y14" s="99"/>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="96"/>
-      <c r="AB14" s="95"/>
+      <c r="A14" s="97"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="79"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="79"/>
+      <c r="U14" s="77"/>
+      <c r="V14" s="78"/>
+      <c r="W14" s="78"/>
+      <c r="X14" s="79"/>
+      <c r="Y14" s="77"/>
+      <c r="Z14" s="78"/>
+      <c r="AA14" s="78"/>
+      <c r="AB14" s="79"/>
     </row>
     <row r="15" spans="1:28">
-      <c r="A15" s="77"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="99"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="95"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="96"/>
-      <c r="S15" s="96"/>
-      <c r="T15" s="95"/>
-      <c r="U15" s="99"/>
-      <c r="V15" s="96"/>
-      <c r="W15" s="96"/>
-      <c r="X15" s="95"/>
-      <c r="Y15" s="99"/>
-      <c r="Z15" s="96"/>
-      <c r="AA15" s="96"/>
-      <c r="AB15" s="95"/>
+      <c r="A15" s="97"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="79"/>
+      <c r="Q15" s="77"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="79"/>
+      <c r="U15" s="77"/>
+      <c r="V15" s="78"/>
+      <c r="W15" s="78"/>
+      <c r="X15" s="79"/>
+      <c r="Y15" s="77"/>
+      <c r="Z15" s="78"/>
+      <c r="AA15" s="78"/>
+      <c r="AB15" s="79"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="99"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="99"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="95"/>
-      <c r="Q16" s="99"/>
-      <c r="R16" s="96"/>
-      <c r="S16" s="96"/>
-      <c r="T16" s="95"/>
-      <c r="U16" s="99"/>
-      <c r="V16" s="96"/>
-      <c r="W16" s="96"/>
-      <c r="X16" s="95"/>
-      <c r="Y16" s="99"/>
-      <c r="Z16" s="96"/>
-      <c r="AA16" s="96"/>
-      <c r="AB16" s="95"/>
+      <c r="A16" s="97"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="79"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="78"/>
+      <c r="S16" s="78"/>
+      <c r="T16" s="79"/>
+      <c r="U16" s="77"/>
+      <c r="V16" s="78"/>
+      <c r="W16" s="78"/>
+      <c r="X16" s="79"/>
+      <c r="Y16" s="77"/>
+      <c r="Z16" s="78"/>
+      <c r="AA16" s="78"/>
+      <c r="AB16" s="79"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="3" t="s">
@@ -3516,14 +3524,32 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="Y15:AB15"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="Y12:AB12"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="Y13:AB13"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="Y14:AB14"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="J1:AB1"/>
+    <mergeCell ref="E10:X10"/>
+    <mergeCell ref="Y10:AB11"/>
+    <mergeCell ref="A10:D11"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
     <mergeCell ref="M15:P15"/>
     <mergeCell ref="Q15:T15"/>
     <mergeCell ref="M16:P16"/>
@@ -3536,32 +3562,14 @@
     <mergeCell ref="Q13:T13"/>
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="J1:AB1"/>
-    <mergeCell ref="E10:X10"/>
-    <mergeCell ref="Y10:AB11"/>
-    <mergeCell ref="A10:D11"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:P11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="Y12:AB12"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="Y13:AB13"/>
+    <mergeCell ref="U14:X14"/>
+    <mergeCell ref="Y14:AB14"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3602,32 +3610,32 @@
       <c r="J1" s="41"/>
       <c r="K1" s="41"/>
       <c r="L1" s="41"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
-      <c r="AC1" s="106"/>
-      <c r="AD1" s="106"/>
-      <c r="AE1" s="106"/>
-      <c r="AF1" s="106"/>
-      <c r="AG1" s="106"/>
-      <c r="AH1" s="106"/>
-      <c r="AI1" s="106"/>
-      <c r="AJ1" s="106"/>
-      <c r="AK1" s="106"/>
-      <c r="AL1" s="106"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="121"/>
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="121"/>
+      <c r="AL1" s="121"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="42" t="s">
@@ -3663,17 +3671,17 @@
       <c r="AF2" s="39"/>
     </row>
     <row r="3" spans="1:38" ht="15.75" customHeight="1">
-      <c r="A3" s="107"/>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
+      <c r="A3" s="122"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
       <c r="L3" s="39"/>
       <c r="M3" s="39"/>
       <c r="N3" s="39"/>
@@ -3890,45 +3898,45 @@
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="109"/>
-      <c r="F10" s="100" t="s">
+      <c r="D10" s="123"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="115" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="101"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="101"/>
-      <c r="J10" s="101"/>
-      <c r="K10" s="101"/>
-      <c r="L10" s="101"/>
-      <c r="M10" s="101"/>
-      <c r="N10" s="101"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="100" t="s">
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="116"/>
+      <c r="L10" s="116"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="116"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="Q10" s="101"/>
-      <c r="R10" s="101"/>
-      <c r="S10" s="101"/>
-      <c r="T10" s="101"/>
-      <c r="U10" s="101"/>
-      <c r="V10" s="101"/>
-      <c r="W10" s="101"/>
-      <c r="X10" s="101"/>
-      <c r="Y10" s="101"/>
-      <c r="Z10" s="101"/>
-      <c r="AA10" s="101"/>
-      <c r="AB10" s="101"/>
-      <c r="AC10" s="101"/>
-      <c r="AD10" s="101"/>
-      <c r="AE10" s="101"/>
-      <c r="AF10" s="101"/>
-      <c r="AG10" s="101"/>
-      <c r="AH10" s="101"/>
-      <c r="AI10" s="101"/>
-      <c r="AJ10" s="101"/>
-      <c r="AK10" s="101"/>
-      <c r="AL10" s="102"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
+      <c r="S10" s="116"/>
+      <c r="T10" s="116"/>
+      <c r="U10" s="116"/>
+      <c r="V10" s="116"/>
+      <c r="W10" s="116"/>
+      <c r="X10" s="116"/>
+      <c r="Y10" s="116"/>
+      <c r="Z10" s="116"/>
+      <c r="AA10" s="116"/>
+      <c r="AB10" s="116"/>
+      <c r="AC10" s="116"/>
+      <c r="AD10" s="116"/>
+      <c r="AE10" s="116"/>
+      <c r="AF10" s="116"/>
+      <c r="AG10" s="116"/>
+      <c r="AH10" s="116"/>
+      <c r="AI10" s="116"/>
+      <c r="AJ10" s="116"/>
+      <c r="AK10" s="116"/>
+      <c r="AL10" s="117"/>
     </row>
     <row r="11" spans="1:38">
       <c r="A11" s="43" t="s">
@@ -3938,62 +3946,62 @@
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
       <c r="E11" s="46"/>
-      <c r="F11" s="100" t="s">
+      <c r="F11" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="101"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="102"/>
-      <c r="K11" s="100" t="s">
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="101"/>
-      <c r="M11" s="101"/>
-      <c r="N11" s="101"/>
-      <c r="O11" s="102"/>
-      <c r="P11" s="100" t="s">
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="117"/>
+      <c r="P11" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" s="101"/>
-      <c r="R11" s="101"/>
-      <c r="S11" s="101"/>
-      <c r="T11" s="102"/>
-      <c r="U11" s="100" t="s">
+      <c r="Q11" s="116"/>
+      <c r="R11" s="116"/>
+      <c r="S11" s="116"/>
+      <c r="T11" s="117"/>
+      <c r="U11" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="V11" s="101"/>
-      <c r="W11" s="101"/>
-      <c r="X11" s="101"/>
-      <c r="Y11" s="102"/>
-      <c r="Z11" s="100" t="s">
+      <c r="V11" s="116"/>
+      <c r="W11" s="116"/>
+      <c r="X11" s="116"/>
+      <c r="Y11" s="117"/>
+      <c r="Z11" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="101"/>
-      <c r="AB11" s="101"/>
-      <c r="AC11" s="101"/>
-      <c r="AD11" s="102"/>
-      <c r="AE11" s="100" t="s">
+      <c r="AA11" s="116"/>
+      <c r="AB11" s="116"/>
+      <c r="AC11" s="116"/>
+      <c r="AD11" s="117"/>
+      <c r="AE11" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="AF11" s="101"/>
-      <c r="AG11" s="101"/>
-      <c r="AH11" s="101"/>
-      <c r="AI11" s="102"/>
-      <c r="AJ11" s="103" t="s">
+      <c r="AF11" s="116"/>
+      <c r="AG11" s="116"/>
+      <c r="AH11" s="116"/>
+      <c r="AI11" s="117"/>
+      <c r="AJ11" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="104"/>
-      <c r="AL11" s="105"/>
+      <c r="AK11" s="119"/>
+      <c r="AL11" s="120"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="112"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="102"/>
       <c r="F12" s="47"/>
       <c r="G12" s="48"/>
       <c r="H12" s="48"/>
@@ -4029,11 +4037,11 @@
       <c r="AL12" s="52"/>
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A13" s="113"/>
-      <c r="B13" s="114"/>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="115"/>
+      <c r="A13" s="103"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="105"/>
       <c r="F13" s="53"/>
       <c r="G13" s="54"/>
       <c r="H13" s="54"/>
@@ -4069,13 +4077,13 @@
       <c r="AL13" s="58"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A14" s="110" t="s">
+      <c r="A14" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="112"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="102"/>
       <c r="F14" s="47"/>
       <c r="G14" s="48"/>
       <c r="H14" s="48"/>
@@ -4111,11 +4119,11 @@
       <c r="AL14" s="52"/>
     </row>
     <row r="15" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A15" s="113"/>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="115"/>
+      <c r="A15" s="103"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="105"/>
       <c r="F15" s="53"/>
       <c r="G15" s="54"/>
       <c r="H15" s="54"/>
@@ -4151,13 +4159,13 @@
       <c r="AL15" s="58"/>
     </row>
     <row r="16" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A16" s="110" t="s">
+      <c r="A16" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="112"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="102"/>
       <c r="F16" s="47"/>
       <c r="G16" s="48"/>
       <c r="H16" s="48"/>
@@ -4193,11 +4201,11 @@
       <c r="AL16" s="52"/>
     </row>
     <row r="17" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A17" s="113"/>
-      <c r="B17" s="114"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="115"/>
+      <c r="A17" s="103"/>
+      <c r="B17" s="104"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="105"/>
       <c r="F17" s="53"/>
       <c r="G17" s="54"/>
       <c r="H17" s="54"/>
@@ -4233,13 +4241,13 @@
       <c r="AL17" s="58"/>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A18" s="110" t="s">
+      <c r="A18" s="100" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="111"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="112"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="102"/>
       <c r="F18" s="47"/>
       <c r="G18" s="48"/>
       <c r="H18" s="48"/>
@@ -4275,11 +4283,11 @@
       <c r="AL18" s="52"/>
     </row>
     <row r="19" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A19" s="113"/>
-      <c r="B19" s="114"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="115"/>
+      <c r="A19" s="103"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="105"/>
       <c r="F19" s="53"/>
       <c r="G19" s="54"/>
       <c r="H19" s="54"/>
@@ -4315,13 +4323,13 @@
       <c r="AL19" s="58"/>
     </row>
     <row r="20" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="111"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="112"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="102"/>
       <c r="F20" s="47"/>
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
@@ -4357,11 +4365,11 @@
       <c r="AL20" s="52"/>
     </row>
     <row r="21" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A21" s="113"/>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="115"/>
+      <c r="A21" s="103"/>
+      <c r="B21" s="104"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="105"/>
       <c r="F21" s="53"/>
       <c r="G21" s="54"/>
       <c r="H21" s="54"/>
@@ -4397,13 +4405,13 @@
       <c r="AL21" s="58"/>
     </row>
     <row r="22" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A22" s="110" t="s">
+      <c r="A22" s="100" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="112"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="102"/>
       <c r="F22" s="47"/>
       <c r="G22" s="48"/>
       <c r="H22" s="48"/>
@@ -4439,11 +4447,11 @@
       <c r="AL22" s="52"/>
     </row>
     <row r="23" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A23" s="113"/>
-      <c r="B23" s="114"/>
-      <c r="C23" s="114"/>
-      <c r="D23" s="114"/>
-      <c r="E23" s="115"/>
+      <c r="A23" s="103"/>
+      <c r="B23" s="104"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="105"/>
       <c r="F23" s="53"/>
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
@@ -4479,13 +4487,13 @@
       <c r="AL23" s="58"/>
     </row>
     <row r="24" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A24" s="110" t="s">
+      <c r="A24" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="111"/>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="112"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="102"/>
       <c r="F24" s="47"/>
       <c r="G24" s="48"/>
       <c r="H24" s="48"/>
@@ -4521,11 +4529,11 @@
       <c r="AL24" s="52"/>
     </row>
     <row r="25" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A25" s="113"/>
-      <c r="B25" s="114"/>
-      <c r="C25" s="114"/>
-      <c r="D25" s="114"/>
-      <c r="E25" s="115"/>
+      <c r="A25" s="103"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="105"/>
       <c r="F25" s="53"/>
       <c r="G25" s="54"/>
       <c r="H25" s="54"/>
@@ -4561,13 +4569,13 @@
       <c r="AL25" s="58"/>
     </row>
     <row r="26" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A26" s="110" t="s">
+      <c r="A26" s="100" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="111"/>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="112"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="102"/>
       <c r="F26" s="47"/>
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
@@ -4603,11 +4611,11 @@
       <c r="AL26" s="52"/>
     </row>
     <row r="27" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A27" s="113"/>
-      <c r="B27" s="114"/>
-      <c r="C27" s="114"/>
-      <c r="D27" s="114"/>
-      <c r="E27" s="115"/>
+      <c r="A27" s="103"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="105"/>
       <c r="F27" s="53"/>
       <c r="G27" s="54"/>
       <c r="H27" s="54"/>
@@ -4643,13 +4651,13 @@
       <c r="AL27" s="58"/>
     </row>
     <row r="28" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A28" s="110" t="s">
+      <c r="A28" s="100" t="s">
         <v>100</v>
       </c>
-      <c r="B28" s="111"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="112"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="102"/>
       <c r="F28" s="47"/>
       <c r="G28" s="48"/>
       <c r="H28" s="48"/>
@@ -4685,11 +4693,11 @@
       <c r="AL28" s="52"/>
     </row>
     <row r="29" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A29" s="113"/>
-      <c r="B29" s="114"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="114"/>
-      <c r="E29" s="115"/>
+      <c r="A29" s="103"/>
+      <c r="B29" s="104"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="105"/>
       <c r="F29" s="53"/>
       <c r="G29" s="54"/>
       <c r="H29" s="54"/>
@@ -4725,13 +4733,13 @@
       <c r="AL29" s="58"/>
     </row>
     <row r="30" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A30" s="110" t="s">
+      <c r="A30" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="111"/>
-      <c r="C30" s="111"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="112"/>
+      <c r="B30" s="101"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="102"/>
       <c r="F30" s="47"/>
       <c r="G30" s="48"/>
       <c r="H30" s="48"/>
@@ -4767,11 +4775,11 @@
       <c r="AL30" s="52"/>
     </row>
     <row r="31" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A31" s="113"/>
-      <c r="B31" s="114"/>
-      <c r="C31" s="114"/>
-      <c r="D31" s="114"/>
-      <c r="E31" s="115"/>
+      <c r="A31" s="103"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="105"/>
       <c r="F31" s="53"/>
       <c r="G31" s="54"/>
       <c r="H31" s="54"/>
@@ -4807,13 +4815,13 @@
       <c r="AL31" s="58"/>
     </row>
     <row r="32" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A32" s="110" t="s">
+      <c r="A32" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="111"/>
-      <c r="C32" s="111"/>
-      <c r="D32" s="111"/>
-      <c r="E32" s="111"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="101"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="101"/>
       <c r="F32" s="47"/>
       <c r="G32" s="48"/>
       <c r="H32" s="48"/>
@@ -4849,11 +4857,11 @@
       <c r="AL32" s="52"/>
     </row>
     <row r="33" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A33" s="113"/>
-      <c r="B33" s="114"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="114"/>
-      <c r="E33" s="114"/>
+      <c r="A33" s="103"/>
+      <c r="B33" s="104"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
       <c r="F33" s="53"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
@@ -4889,13 +4897,13 @@
       <c r="AL33" s="58"/>
     </row>
     <row r="34" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A34" s="110" t="s">
+      <c r="A34" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="111"/>
-      <c r="C34" s="111"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="101"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
       <c r="F34" s="47"/>
       <c r="G34" s="48"/>
       <c r="H34" s="48"/>
@@ -4931,11 +4939,11 @@
       <c r="AL34" s="52"/>
     </row>
     <row r="35" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A35" s="113"/>
-      <c r="B35" s="114"/>
-      <c r="C35" s="114"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="115"/>
+      <c r="A35" s="103"/>
+      <c r="B35" s="104"/>
+      <c r="C35" s="104"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="105"/>
       <c r="F35" s="53"/>
       <c r="G35" s="54"/>
       <c r="H35" s="54"/>
@@ -4971,13 +4979,13 @@
       <c r="AL35" s="58"/>
     </row>
     <row r="36" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A36" s="116" t="s">
+      <c r="A36" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="117"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="118"/>
+      <c r="B36" s="107"/>
+      <c r="C36" s="107"/>
+      <c r="D36" s="107"/>
+      <c r="E36" s="108"/>
       <c r="F36" s="47"/>
       <c r="G36" s="48"/>
       <c r="H36" s="48"/>
@@ -5013,11 +5021,11 @@
       <c r="AL36" s="52"/>
     </row>
     <row r="37" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A37" s="119"/>
-      <c r="B37" s="120"/>
-      <c r="C37" s="120"/>
-      <c r="D37" s="120"/>
-      <c r="E37" s="121"/>
+      <c r="A37" s="109"/>
+      <c r="B37" s="110"/>
+      <c r="C37" s="110"/>
+      <c r="D37" s="110"/>
+      <c r="E37" s="111"/>
       <c r="F37" s="53"/>
       <c r="G37" s="54"/>
       <c r="H37" s="54"/>
@@ -5086,21 +5094,21 @@
       <c r="AF38" s="39"/>
     </row>
     <row r="39" spans="1:38">
-      <c r="A39" s="122" t="s">
+      <c r="A39" s="112" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="122"/>
-      <c r="C39" s="122"/>
-      <c r="D39" s="123" t="s">
+      <c r="B39" s="112"/>
+      <c r="C39" s="112"/>
+      <c r="D39" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="123"/>
-      <c r="F39" s="123"/>
-      <c r="G39" s="123"/>
-      <c r="H39" s="123"/>
-      <c r="I39" s="123"/>
-      <c r="J39" s="123"/>
-      <c r="K39" s="123"/>
+      <c r="E39" s="113"/>
+      <c r="F39" s="113"/>
+      <c r="G39" s="113"/>
+      <c r="H39" s="113"/>
+      <c r="I39" s="113"/>
+      <c r="J39" s="113"/>
+      <c r="K39" s="113"/>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
       <c r="N39" s="39"/>
@@ -5124,19 +5132,19 @@
       <c r="AF39" s="39"/>
     </row>
     <row r="40" spans="1:38">
-      <c r="A40" s="122"/>
-      <c r="B40" s="122"/>
-      <c r="C40" s="122"/>
-      <c r="D40" s="124" t="s">
+      <c r="A40" s="112"/>
+      <c r="B40" s="112"/>
+      <c r="C40" s="112"/>
+      <c r="D40" s="114" t="s">
         <v>108</v>
       </c>
-      <c r="E40" s="124"/>
-      <c r="F40" s="124"/>
-      <c r="G40" s="124"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="124"/>
-      <c r="J40" s="124"/>
-      <c r="K40" s="124"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="114"/>
+      <c r="G40" s="114"/>
+      <c r="H40" s="114"/>
+      <c r="I40" s="114"/>
+      <c r="J40" s="114"/>
+      <c r="K40" s="114"/>
       <c r="L40" s="39"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
@@ -5355,13 +5363,13 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="A32:E33"/>
-    <mergeCell ref="A34:E35"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="AE11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="P10:AL10"/>
     <mergeCell ref="A12:E13"/>
     <mergeCell ref="A14:E15"/>
     <mergeCell ref="A16:E17"/>
@@ -5376,13 +5384,13 @@
     <mergeCell ref="K11:O11"/>
     <mergeCell ref="P11:T11"/>
     <mergeCell ref="U11:Y11"/>
-    <mergeCell ref="AE11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="P10:AL10"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="A32:E33"/>
+    <mergeCell ref="A34:E35"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:K39"/>
+    <mergeCell ref="D40:K40"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5589,238 +5597,238 @@
       <c r="AL5" s="1"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="128" t="s">
+      <c r="A6" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="128"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="128"/>
-      <c r="G6" s="128"/>
-      <c r="H6" s="132" t="s">
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="132"/>
-      <c r="L6" s="133" t="s">
+      <c r="I6" s="127"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="133"/>
-      <c r="N6" s="133"/>
-      <c r="O6" s="133"/>
-      <c r="P6" s="133"/>
-      <c r="Q6" s="133"/>
-      <c r="R6" s="133"/>
-      <c r="S6" s="133"/>
-      <c r="T6" s="133"/>
-      <c r="U6" s="133"/>
-      <c r="V6" s="133"/>
-      <c r="W6" s="133"/>
-      <c r="X6" s="132" t="s">
+      <c r="M6" s="128"/>
+      <c r="N6" s="128"/>
+      <c r="O6" s="128"/>
+      <c r="P6" s="128"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="128"/>
+      <c r="S6" s="128"/>
+      <c r="T6" s="128"/>
+      <c r="U6" s="128"/>
+      <c r="V6" s="128"/>
+      <c r="W6" s="128"/>
+      <c r="X6" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="Y6" s="132"/>
-      <c r="Z6" s="132"/>
-      <c r="AA6" s="132"/>
-      <c r="AB6" s="133" t="s">
+      <c r="Y6" s="127"/>
+      <c r="Z6" s="127"/>
+      <c r="AA6" s="127"/>
+      <c r="AB6" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="AC6" s="133"/>
-      <c r="AD6" s="133"/>
-      <c r="AE6" s="133"/>
-      <c r="AF6" s="133"/>
-      <c r="AG6" s="133"/>
-      <c r="AH6" s="133"/>
-      <c r="AI6" s="133"/>
-      <c r="AJ6" s="133"/>
-      <c r="AK6" s="133"/>
-      <c r="AL6" s="133"/>
+      <c r="AC6" s="128"/>
+      <c r="AD6" s="128"/>
+      <c r="AE6" s="128"/>
+      <c r="AF6" s="128"/>
+      <c r="AG6" s="128"/>
+      <c r="AH6" s="128"/>
+      <c r="AI6" s="128"/>
+      <c r="AJ6" s="128"/>
+      <c r="AK6" s="128"/>
+      <c r="AL6" s="128"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
-      <c r="A7" s="128"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="133" t="s">
+      <c r="A7" s="132"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="133"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="133"/>
-      <c r="P7" s="133" t="s">
+      <c r="M7" s="128"/>
+      <c r="N7" s="128"/>
+      <c r="O7" s="128"/>
+      <c r="P7" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="Q7" s="133"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="133"/>
-      <c r="T7" s="133" t="s">
+      <c r="Q7" s="128"/>
+      <c r="R7" s="128"/>
+      <c r="S7" s="128"/>
+      <c r="T7" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="U7" s="133"/>
-      <c r="V7" s="133"/>
-      <c r="W7" s="133"/>
-      <c r="X7" s="132"/>
-      <c r="Y7" s="132"/>
-      <c r="Z7" s="132"/>
-      <c r="AA7" s="132"/>
-      <c r="AB7" s="133" t="s">
+      <c r="U7" s="128"/>
+      <c r="V7" s="128"/>
+      <c r="W7" s="128"/>
+      <c r="X7" s="127"/>
+      <c r="Y7" s="127"/>
+      <c r="Z7" s="127"/>
+      <c r="AA7" s="127"/>
+      <c r="AB7" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="AC7" s="133"/>
-      <c r="AD7" s="133"/>
-      <c r="AE7" s="133"/>
-      <c r="AF7" s="133" t="s">
+      <c r="AC7" s="128"/>
+      <c r="AD7" s="128"/>
+      <c r="AE7" s="128"/>
+      <c r="AF7" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="AG7" s="133"/>
-      <c r="AH7" s="133"/>
-      <c r="AI7" s="133"/>
-      <c r="AJ7" s="133" t="s">
+      <c r="AG7" s="128"/>
+      <c r="AH7" s="128"/>
+      <c r="AI7" s="128"/>
+      <c r="AJ7" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="AK7" s="133"/>
-      <c r="AL7" s="133"/>
+      <c r="AK7" s="128"/>
+      <c r="AL7" s="128"/>
     </row>
     <row r="8" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A8" s="125"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
       <c r="H8" s="126">
         <v>125</v>
       </c>
       <c r="I8" s="126"/>
       <c r="J8" s="126"/>
       <c r="K8" s="126"/>
-      <c r="L8" s="127"/>
-      <c r="M8" s="127"/>
-      <c r="N8" s="127"/>
-      <c r="O8" s="127"/>
-      <c r="P8" s="127"/>
-      <c r="Q8" s="127"/>
-      <c r="R8" s="127"/>
-      <c r="S8" s="127"/>
-      <c r="T8" s="127"/>
-      <c r="U8" s="127"/>
-      <c r="V8" s="127"/>
-      <c r="W8" s="127"/>
+      <c r="L8" s="125"/>
+      <c r="M8" s="125"/>
+      <c r="N8" s="125"/>
+      <c r="O8" s="125"/>
+      <c r="P8" s="125"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="125"/>
+      <c r="T8" s="125"/>
+      <c r="U8" s="125"/>
+      <c r="V8" s="125"/>
+      <c r="W8" s="125"/>
       <c r="X8" s="126">
         <v>2000</v>
       </c>
       <c r="Y8" s="126"/>
       <c r="Z8" s="126"/>
       <c r="AA8" s="126"/>
-      <c r="AB8" s="127"/>
-      <c r="AC8" s="127"/>
-      <c r="AD8" s="127"/>
-      <c r="AE8" s="127"/>
-      <c r="AF8" s="127"/>
-      <c r="AG8" s="127"/>
-      <c r="AH8" s="127"/>
-      <c r="AI8" s="127"/>
-      <c r="AJ8" s="127"/>
-      <c r="AK8" s="127"/>
-      <c r="AL8" s="127"/>
+      <c r="AB8" s="125"/>
+      <c r="AC8" s="125"/>
+      <c r="AD8" s="125"/>
+      <c r="AE8" s="125"/>
+      <c r="AF8" s="125"/>
+      <c r="AG8" s="125"/>
+      <c r="AH8" s="125"/>
+      <c r="AI8" s="125"/>
+      <c r="AJ8" s="125"/>
+      <c r="AK8" s="125"/>
+      <c r="AL8" s="125"/>
     </row>
     <row r="9" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A9" s="125"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
       <c r="H9" s="126">
         <v>500</v>
       </c>
       <c r="I9" s="126"/>
       <c r="J9" s="126"/>
       <c r="K9" s="126"/>
-      <c r="L9" s="127"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="127"/>
-      <c r="O9" s="127"/>
-      <c r="P9" s="127"/>
-      <c r="Q9" s="127"/>
-      <c r="R9" s="127"/>
-      <c r="S9" s="127"/>
-      <c r="T9" s="127"/>
-      <c r="U9" s="127"/>
-      <c r="V9" s="127"/>
-      <c r="W9" s="127"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="125"/>
+      <c r="O9" s="125"/>
+      <c r="P9" s="125"/>
+      <c r="Q9" s="125"/>
+      <c r="R9" s="125"/>
+      <c r="S9" s="125"/>
+      <c r="T9" s="125"/>
+      <c r="U9" s="125"/>
+      <c r="V9" s="125"/>
+      <c r="W9" s="125"/>
       <c r="X9" s="126">
         <v>5000</v>
       </c>
       <c r="Y9" s="126"/>
       <c r="Z9" s="126"/>
       <c r="AA9" s="126"/>
-      <c r="AB9" s="127"/>
-      <c r="AC9" s="127"/>
-      <c r="AD9" s="127"/>
-      <c r="AE9" s="127"/>
-      <c r="AF9" s="127"/>
-      <c r="AG9" s="127"/>
-      <c r="AH9" s="127"/>
-      <c r="AI9" s="127"/>
-      <c r="AJ9" s="127"/>
-      <c r="AK9" s="127"/>
-      <c r="AL9" s="127"/>
+      <c r="AB9" s="125"/>
+      <c r="AC9" s="125"/>
+      <c r="AD9" s="125"/>
+      <c r="AE9" s="125"/>
+      <c r="AF9" s="125"/>
+      <c r="AG9" s="125"/>
+      <c r="AH9" s="125"/>
+      <c r="AI9" s="125"/>
+      <c r="AJ9" s="125"/>
+      <c r="AK9" s="125"/>
+      <c r="AL9" s="125"/>
     </row>
     <row r="10" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A10" s="125"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
       <c r="H10" s="126">
         <v>1000</v>
       </c>
       <c r="I10" s="126"/>
       <c r="J10" s="126"/>
       <c r="K10" s="126"/>
-      <c r="L10" s="127"/>
-      <c r="M10" s="127"/>
-      <c r="N10" s="127"/>
-      <c r="O10" s="127"/>
-      <c r="P10" s="127"/>
-      <c r="Q10" s="127"/>
-      <c r="R10" s="127"/>
-      <c r="S10" s="127"/>
-      <c r="T10" s="127"/>
-      <c r="U10" s="127"/>
-      <c r="V10" s="127"/>
-      <c r="W10" s="127"/>
+      <c r="L10" s="125"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="125"/>
+      <c r="O10" s="125"/>
+      <c r="P10" s="125"/>
+      <c r="Q10" s="125"/>
+      <c r="R10" s="125"/>
+      <c r="S10" s="125"/>
+      <c r="T10" s="125"/>
+      <c r="U10" s="125"/>
+      <c r="V10" s="125"/>
+      <c r="W10" s="125"/>
       <c r="X10" s="126">
         <v>7000</v>
       </c>
       <c r="Y10" s="126"/>
       <c r="Z10" s="126"/>
       <c r="AA10" s="126"/>
-      <c r="AB10" s="127"/>
-      <c r="AC10" s="127"/>
-      <c r="AD10" s="127"/>
-      <c r="AE10" s="127"/>
-      <c r="AF10" s="127"/>
-      <c r="AG10" s="127"/>
-      <c r="AH10" s="127"/>
-      <c r="AI10" s="127"/>
-      <c r="AJ10" s="127"/>
-      <c r="AK10" s="127"/>
-      <c r="AL10" s="127"/>
+      <c r="AB10" s="125"/>
+      <c r="AC10" s="125"/>
+      <c r="AD10" s="125"/>
+      <c r="AE10" s="125"/>
+      <c r="AF10" s="125"/>
+      <c r="AG10" s="125"/>
+      <c r="AH10" s="125"/>
+      <c r="AI10" s="125"/>
+      <c r="AJ10" s="125"/>
+      <c r="AK10" s="125"/>
+      <c r="AL10" s="125"/>
     </row>
     <row r="11" spans="1:38" ht="21.15" customHeight="1">
       <c r="A11" s="28"/>
@@ -5899,238 +5907,238 @@
       <c r="AL12" s="1"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1">
-      <c r="A13" s="128" t="s">
+      <c r="A13" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="128"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="128"/>
-      <c r="H13" s="132" t="s">
+      <c r="B13" s="132"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="133" t="s">
+      <c r="I13" s="127"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="127"/>
+      <c r="L13" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="133"/>
-      <c r="N13" s="133"/>
-      <c r="O13" s="133"/>
-      <c r="P13" s="133"/>
-      <c r="Q13" s="133"/>
-      <c r="R13" s="133"/>
-      <c r="S13" s="133"/>
-      <c r="T13" s="133"/>
-      <c r="U13" s="133"/>
-      <c r="V13" s="133"/>
-      <c r="W13" s="133"/>
-      <c r="X13" s="132" t="s">
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="128"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="128"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="128"/>
+      <c r="U13" s="128"/>
+      <c r="V13" s="128"/>
+      <c r="W13" s="128"/>
+      <c r="X13" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="Y13" s="132"/>
-      <c r="Z13" s="132"/>
-      <c r="AA13" s="132"/>
-      <c r="AB13" s="133" t="s">
+      <c r="Y13" s="127"/>
+      <c r="Z13" s="127"/>
+      <c r="AA13" s="127"/>
+      <c r="AB13" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="AC13" s="133"/>
-      <c r="AD13" s="133"/>
-      <c r="AE13" s="133"/>
-      <c r="AF13" s="133"/>
-      <c r="AG13" s="133"/>
-      <c r="AH13" s="133"/>
-      <c r="AI13" s="133"/>
-      <c r="AJ13" s="133"/>
-      <c r="AK13" s="133"/>
-      <c r="AL13" s="133"/>
+      <c r="AC13" s="128"/>
+      <c r="AD13" s="128"/>
+      <c r="AE13" s="128"/>
+      <c r="AF13" s="128"/>
+      <c r="AG13" s="128"/>
+      <c r="AH13" s="128"/>
+      <c r="AI13" s="128"/>
+      <c r="AJ13" s="128"/>
+      <c r="AK13" s="128"/>
+      <c r="AL13" s="128"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1">
-      <c r="A14" s="128"/>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="132"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="133" t="s">
+      <c r="A14" s="132"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="127"/>
+      <c r="L14" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="M14" s="133"/>
-      <c r="N14" s="133"/>
-      <c r="O14" s="133"/>
-      <c r="P14" s="133" t="s">
+      <c r="M14" s="128"/>
+      <c r="N14" s="128"/>
+      <c r="O14" s="128"/>
+      <c r="P14" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="Q14" s="133"/>
-      <c r="R14" s="133"/>
-      <c r="S14" s="133"/>
-      <c r="T14" s="133" t="s">
+      <c r="Q14" s="128"/>
+      <c r="R14" s="128"/>
+      <c r="S14" s="128"/>
+      <c r="T14" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="U14" s="133"/>
-      <c r="V14" s="133"/>
-      <c r="W14" s="133"/>
-      <c r="X14" s="132"/>
-      <c r="Y14" s="132"/>
-      <c r="Z14" s="132"/>
-      <c r="AA14" s="132"/>
-      <c r="AB14" s="133" t="s">
+      <c r="U14" s="128"/>
+      <c r="V14" s="128"/>
+      <c r="W14" s="128"/>
+      <c r="X14" s="127"/>
+      <c r="Y14" s="127"/>
+      <c r="Z14" s="127"/>
+      <c r="AA14" s="127"/>
+      <c r="AB14" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="AC14" s="133"/>
-      <c r="AD14" s="133"/>
-      <c r="AE14" s="133"/>
-      <c r="AF14" s="133" t="s">
+      <c r="AC14" s="128"/>
+      <c r="AD14" s="128"/>
+      <c r="AE14" s="128"/>
+      <c r="AF14" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="AG14" s="133"/>
-      <c r="AH14" s="133"/>
-      <c r="AI14" s="133"/>
-      <c r="AJ14" s="133" t="s">
+      <c r="AG14" s="128"/>
+      <c r="AH14" s="128"/>
+      <c r="AI14" s="128"/>
+      <c r="AJ14" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="AK14" s="133"/>
-      <c r="AL14" s="133"/>
+      <c r="AK14" s="128"/>
+      <c r="AL14" s="128"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1">
-      <c r="A15" s="125"/>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
+      <c r="A15" s="133"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
       <c r="H15" s="126">
         <v>125</v>
       </c>
       <c r="I15" s="126"/>
       <c r="J15" s="126"/>
       <c r="K15" s="126"/>
-      <c r="L15" s="127"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="127"/>
-      <c r="O15" s="127"/>
-      <c r="P15" s="127"/>
-      <c r="Q15" s="127"/>
-      <c r="R15" s="127"/>
-      <c r="S15" s="127"/>
-      <c r="T15" s="127"/>
-      <c r="U15" s="127"/>
-      <c r="V15" s="127"/>
-      <c r="W15" s="127"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
+      <c r="U15" s="125"/>
+      <c r="V15" s="125"/>
+      <c r="W15" s="125"/>
       <c r="X15" s="126">
         <v>2000</v>
       </c>
       <c r="Y15" s="126"/>
       <c r="Z15" s="126"/>
       <c r="AA15" s="126"/>
-      <c r="AB15" s="127"/>
-      <c r="AC15" s="127"/>
-      <c r="AD15" s="127"/>
-      <c r="AE15" s="127"/>
-      <c r="AF15" s="127"/>
-      <c r="AG15" s="127"/>
-      <c r="AH15" s="127"/>
-      <c r="AI15" s="127"/>
-      <c r="AJ15" s="127"/>
-      <c r="AK15" s="127"/>
-      <c r="AL15" s="127"/>
+      <c r="AB15" s="125"/>
+      <c r="AC15" s="125"/>
+      <c r="AD15" s="125"/>
+      <c r="AE15" s="125"/>
+      <c r="AF15" s="125"/>
+      <c r="AG15" s="125"/>
+      <c r="AH15" s="125"/>
+      <c r="AI15" s="125"/>
+      <c r="AJ15" s="125"/>
+      <c r="AK15" s="125"/>
+      <c r="AL15" s="125"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1">
-      <c r="A16" s="125"/>
-      <c r="B16" s="125"/>
-      <c r="C16" s="125"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="125"/>
-      <c r="G16" s="125"/>
+      <c r="A16" s="133"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
       <c r="H16" s="126">
         <v>500</v>
       </c>
       <c r="I16" s="126"/>
       <c r="J16" s="126"/>
       <c r="K16" s="126"/>
-      <c r="L16" s="127"/>
-      <c r="M16" s="127"/>
-      <c r="N16" s="127"/>
-      <c r="O16" s="127"/>
-      <c r="P16" s="127"/>
-      <c r="Q16" s="127"/>
-      <c r="R16" s="127"/>
-      <c r="S16" s="127"/>
-      <c r="T16" s="127"/>
-      <c r="U16" s="127"/>
-      <c r="V16" s="127"/>
-      <c r="W16" s="127"/>
+      <c r="L16" s="125"/>
+      <c r="M16" s="125"/>
+      <c r="N16" s="125"/>
+      <c r="O16" s="125"/>
+      <c r="P16" s="125"/>
+      <c r="Q16" s="125"/>
+      <c r="R16" s="125"/>
+      <c r="S16" s="125"/>
+      <c r="T16" s="125"/>
+      <c r="U16" s="125"/>
+      <c r="V16" s="125"/>
+      <c r="W16" s="125"/>
       <c r="X16" s="126">
         <v>5000</v>
       </c>
       <c r="Y16" s="126"/>
       <c r="Z16" s="126"/>
       <c r="AA16" s="126"/>
-      <c r="AB16" s="127"/>
-      <c r="AC16" s="127"/>
-      <c r="AD16" s="127"/>
-      <c r="AE16" s="127"/>
-      <c r="AF16" s="127"/>
-      <c r="AG16" s="127"/>
-      <c r="AH16" s="127"/>
-      <c r="AI16" s="127"/>
-      <c r="AJ16" s="127"/>
-      <c r="AK16" s="127"/>
-      <c r="AL16" s="127"/>
+      <c r="AB16" s="125"/>
+      <c r="AC16" s="125"/>
+      <c r="AD16" s="125"/>
+      <c r="AE16" s="125"/>
+      <c r="AF16" s="125"/>
+      <c r="AG16" s="125"/>
+      <c r="AH16" s="125"/>
+      <c r="AI16" s="125"/>
+      <c r="AJ16" s="125"/>
+      <c r="AK16" s="125"/>
+      <c r="AL16" s="125"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
-      <c r="A17" s="125"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="125"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="125"/>
-      <c r="G17" s="125"/>
+      <c r="A17" s="133"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="133"/>
       <c r="H17" s="126">
         <v>1000</v>
       </c>
       <c r="I17" s="126"/>
       <c r="J17" s="126"/>
       <c r="K17" s="126"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="127"/>
-      <c r="P17" s="127"/>
-      <c r="Q17" s="127"/>
-      <c r="R17" s="127"/>
-      <c r="S17" s="127"/>
-      <c r="T17" s="127"/>
-      <c r="U17" s="127"/>
-      <c r="V17" s="127"/>
-      <c r="W17" s="127"/>
+      <c r="L17" s="125"/>
+      <c r="M17" s="125"/>
+      <c r="N17" s="125"/>
+      <c r="O17" s="125"/>
+      <c r="P17" s="125"/>
+      <c r="Q17" s="125"/>
+      <c r="R17" s="125"/>
+      <c r="S17" s="125"/>
+      <c r="T17" s="125"/>
+      <c r="U17" s="125"/>
+      <c r="V17" s="125"/>
+      <c r="W17" s="125"/>
       <c r="X17" s="126">
         <v>7000</v>
       </c>
       <c r="Y17" s="126"/>
       <c r="Z17" s="126"/>
       <c r="AA17" s="126"/>
-      <c r="AB17" s="127"/>
-      <c r="AC17" s="127"/>
-      <c r="AD17" s="127"/>
-      <c r="AE17" s="127"/>
-      <c r="AF17" s="127"/>
-      <c r="AG17" s="127"/>
-      <c r="AH17" s="127"/>
-      <c r="AI17" s="127"/>
-      <c r="AJ17" s="127"/>
-      <c r="AK17" s="127"/>
-      <c r="AL17" s="127"/>
+      <c r="AB17" s="125"/>
+      <c r="AC17" s="125"/>
+      <c r="AD17" s="125"/>
+      <c r="AE17" s="125"/>
+      <c r="AF17" s="125"/>
+      <c r="AG17" s="125"/>
+      <c r="AH17" s="125"/>
+      <c r="AI17" s="125"/>
+      <c r="AJ17" s="125"/>
+      <c r="AK17" s="125"/>
+      <c r="AL17" s="125"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1">
       <c r="A18" s="28"/>
@@ -7580,65 +7588,6 @@
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AB15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="AJ15:AL15"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="X16:AA16"/>
-    <mergeCell ref="AB16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L10:O10"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X10:AA10"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="X15:AA15"/>
-    <mergeCell ref="H13:K14"/>
-    <mergeCell ref="L13:W13"/>
-    <mergeCell ref="X13:AA14"/>
-    <mergeCell ref="AB13:AL13"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="AB14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AB10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="L9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="F3:S3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A6:G7"/>
-    <mergeCell ref="H6:K7"/>
-    <mergeCell ref="L6:W6"/>
-    <mergeCell ref="X6:AA7"/>
-    <mergeCell ref="AB6:AL6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="P7:S7"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="AB7:AE7"/>
-    <mergeCell ref="AF7:AI7"/>
-    <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="A8:G10"/>
     <mergeCell ref="A15:G17"/>
     <mergeCell ref="H15:K15"/>
@@ -7655,6 +7604,65 @@
     <mergeCell ref="L8:O8"/>
     <mergeCell ref="P8:S8"/>
     <mergeCell ref="A13:G14"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="F3:S3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A6:G7"/>
+    <mergeCell ref="H6:K7"/>
+    <mergeCell ref="L6:W6"/>
+    <mergeCell ref="X6:AA7"/>
+    <mergeCell ref="AB6:AL6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="P7:S7"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="AB7:AE7"/>
+    <mergeCell ref="AF7:AI7"/>
+    <mergeCell ref="AJ7:AL7"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="L9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="AB8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="AB10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AB13:AL13"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="AB14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="L10:O10"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="X15:AA15"/>
+    <mergeCell ref="H13:K14"/>
+    <mergeCell ref="L13:W13"/>
+    <mergeCell ref="X13:AA14"/>
+    <mergeCell ref="AB15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="X16:AA16"/>
+    <mergeCell ref="AB16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="AJ16:AL16"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7755,17 +7763,17 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="97"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
       <c r="L3" s="16"/>
       <c r="M3" s="16"/>
       <c r="N3" s="12" t="s">
@@ -9723,7 +9731,9 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
+      <c r="M54" s="9" t="s">
+        <v>214</v>
+      </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
@@ -9731,7 +9741,9 @@
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
+      <c r="U54" s="9" t="s">
+        <v>215</v>
+      </c>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
@@ -10200,32 +10212,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="135"/>
-      <c r="Z1" s="135"/>
-      <c r="AA1" s="135"/>
-      <c r="AB1" s="135"/>
-      <c r="AC1" s="135"/>
-      <c r="AD1" s="135"/>
-      <c r="AE1" s="135"/>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="135"/>
-      <c r="AI1" s="135"/>
-      <c r="AJ1" s="135"/>
-      <c r="AK1" s="135"/>
-      <c r="AL1" s="135"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="144"/>
+      <c r="Z1" s="144"/>
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="144"/>
+      <c r="AF1" s="144"/>
+      <c r="AG1" s="144"/>
+      <c r="AH1" s="144"/>
+      <c r="AI1" s="144"/>
+      <c r="AJ1" s="144"/>
+      <c r="AK1" s="144"/>
+      <c r="AL1" s="144"/>
       <c r="AM1" s="67"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -10269,17 +10281,17 @@
       <c r="AM2" s="67"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="136"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -10299,11 +10311,11 @@
       <c r="Z3" s="38"/>
       <c r="AA3" s="76"/>
       <c r="AB3" s="34"/>
-      <c r="AC3" s="135"/>
-      <c r="AD3" s="135"/>
-      <c r="AE3" s="135"/>
-      <c r="AF3" s="135"/>
-      <c r="AG3" s="135"/>
+      <c r="AC3" s="144"/>
+      <c r="AD3" s="144"/>
+      <c r="AE3" s="144"/>
+      <c r="AF3" s="144"/>
+      <c r="AG3" s="144"/>
       <c r="AH3" s="34"/>
       <c r="AI3" s="34"/>
       <c r="AJ3" s="34"/>
@@ -10323,12 +10335,12 @@
       <c r="G4" s="69"/>
       <c r="H4" s="69"/>
       <c r="I4" s="69"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
+      <c r="O4" s="145"/>
       <c r="P4" s="34"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="34"/>
@@ -10361,51 +10373,51 @@
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
       <c r="D5" s="138"/>
-      <c r="E5" s="140" t="s">
+      <c r="E5" s="143" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140" t="s">
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="143" t="s">
         <v>165</v>
       </c>
-      <c r="M5" s="140"/>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="140"/>
-      <c r="R5" s="140"/>
-      <c r="S5" s="140" t="s">
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="143"/>
+      <c r="Q5" s="143"/>
+      <c r="R5" s="143"/>
+      <c r="S5" s="143" t="s">
         <v>164</v>
       </c>
-      <c r="T5" s="140"/>
-      <c r="U5" s="140"/>
-      <c r="V5" s="140"/>
-      <c r="W5" s="140"/>
-      <c r="X5" s="140"/>
-      <c r="Y5" s="140"/>
-      <c r="Z5" s="140" t="s">
+      <c r="T5" s="143"/>
+      <c r="U5" s="143"/>
+      <c r="V5" s="143"/>
+      <c r="W5" s="143"/>
+      <c r="X5" s="143"/>
+      <c r="Y5" s="143"/>
+      <c r="Z5" s="143" t="s">
         <v>163</v>
       </c>
-      <c r="AA5" s="140"/>
-      <c r="AB5" s="140"/>
-      <c r="AC5" s="140"/>
-      <c r="AD5" s="140"/>
-      <c r="AE5" s="140"/>
-      <c r="AF5" s="140"/>
-      <c r="AG5" s="140" t="s">
+      <c r="AA5" s="143"/>
+      <c r="AB5" s="143"/>
+      <c r="AC5" s="143"/>
+      <c r="AD5" s="143"/>
+      <c r="AE5" s="143"/>
+      <c r="AF5" s="143"/>
+      <c r="AG5" s="143" t="s">
         <v>162</v>
       </c>
-      <c r="AH5" s="140"/>
-      <c r="AI5" s="140"/>
-      <c r="AJ5" s="140"/>
-      <c r="AK5" s="140"/>
-      <c r="AL5" s="140"/>
-      <c r="AM5" s="140"/>
+      <c r="AH5" s="143"/>
+      <c r="AI5" s="143"/>
+      <c r="AJ5" s="143"/>
+      <c r="AK5" s="143"/>
+      <c r="AL5" s="143"/>
+      <c r="AM5" s="143"/>
     </row>
     <row r="6" spans="1:39" ht="15" customHeight="1">
       <c r="A6" s="138" t="s">
@@ -10414,41 +10426,41 @@
       <c r="B6" s="138"/>
       <c r="C6" s="138"/>
       <c r="D6" s="138"/>
-      <c r="E6" s="139"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="139"/>
-      <c r="I6" s="139"/>
-      <c r="J6" s="139"/>
-      <c r="K6" s="139"/>
-      <c r="L6" s="139"/>
-      <c r="M6" s="139"/>
-      <c r="N6" s="139"/>
-      <c r="O6" s="139"/>
-      <c r="P6" s="139"/>
-      <c r="Q6" s="139"/>
-      <c r="R6" s="139"/>
-      <c r="S6" s="139"/>
-      <c r="T6" s="139"/>
-      <c r="U6" s="139"/>
-      <c r="V6" s="139"/>
-      <c r="W6" s="139"/>
-      <c r="X6" s="139"/>
-      <c r="Y6" s="139"/>
-      <c r="Z6" s="139"/>
-      <c r="AA6" s="139"/>
-      <c r="AB6" s="139"/>
-      <c r="AC6" s="139"/>
-      <c r="AD6" s="139"/>
-      <c r="AE6" s="139"/>
-      <c r="AF6" s="139"/>
-      <c r="AG6" s="139"/>
-      <c r="AH6" s="139"/>
-      <c r="AI6" s="139"/>
-      <c r="AJ6" s="139"/>
-      <c r="AK6" s="139"/>
-      <c r="AL6" s="139"/>
-      <c r="AM6" s="139"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="142"/>
+      <c r="I6" s="142"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="142"/>
+      <c r="M6" s="142"/>
+      <c r="N6" s="142"/>
+      <c r="O6" s="142"/>
+      <c r="P6" s="142"/>
+      <c r="Q6" s="142"/>
+      <c r="R6" s="142"/>
+      <c r="S6" s="142"/>
+      <c r="T6" s="142"/>
+      <c r="U6" s="142"/>
+      <c r="V6" s="142"/>
+      <c r="W6" s="142"/>
+      <c r="X6" s="142"/>
+      <c r="Y6" s="142"/>
+      <c r="Z6" s="142"/>
+      <c r="AA6" s="142"/>
+      <c r="AB6" s="142"/>
+      <c r="AC6" s="142"/>
+      <c r="AD6" s="142"/>
+      <c r="AE6" s="142"/>
+      <c r="AF6" s="142"/>
+      <c r="AG6" s="142"/>
+      <c r="AH6" s="142"/>
+      <c r="AI6" s="142"/>
+      <c r="AJ6" s="142"/>
+      <c r="AK6" s="142"/>
+      <c r="AL6" s="142"/>
+      <c r="AM6" s="142"/>
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
       <c r="A7" s="138" t="s">
@@ -10457,41 +10469,41 @@
       <c r="B7" s="138"/>
       <c r="C7" s="138"/>
       <c r="D7" s="138"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="139"/>
-      <c r="I7" s="139"/>
-      <c r="J7" s="139"/>
-      <c r="K7" s="139"/>
-      <c r="L7" s="139"/>
-      <c r="M7" s="139"/>
-      <c r="N7" s="139"/>
-      <c r="O7" s="139"/>
-      <c r="P7" s="139"/>
-      <c r="Q7" s="139"/>
-      <c r="R7" s="139"/>
-      <c r="S7" s="139"/>
-      <c r="T7" s="139"/>
-      <c r="U7" s="139"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="139"/>
-      <c r="X7" s="139"/>
-      <c r="Y7" s="139"/>
-      <c r="Z7" s="139"/>
-      <c r="AA7" s="139"/>
-      <c r="AB7" s="139"/>
-      <c r="AC7" s="139"/>
-      <c r="AD7" s="139"/>
-      <c r="AE7" s="139"/>
-      <c r="AF7" s="139"/>
-      <c r="AG7" s="139"/>
-      <c r="AH7" s="139"/>
-      <c r="AI7" s="139"/>
-      <c r="AJ7" s="139"/>
-      <c r="AK7" s="139"/>
-      <c r="AL7" s="139"/>
-      <c r="AM7" s="139"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="142"/>
+      <c r="H7" s="142"/>
+      <c r="I7" s="142"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="142"/>
+      <c r="M7" s="142"/>
+      <c r="N7" s="142"/>
+      <c r="O7" s="142"/>
+      <c r="P7" s="142"/>
+      <c r="Q7" s="142"/>
+      <c r="R7" s="142"/>
+      <c r="S7" s="142"/>
+      <c r="T7" s="142"/>
+      <c r="U7" s="142"/>
+      <c r="V7" s="142"/>
+      <c r="W7" s="142"/>
+      <c r="X7" s="142"/>
+      <c r="Y7" s="142"/>
+      <c r="Z7" s="142"/>
+      <c r="AA7" s="142"/>
+      <c r="AB7" s="142"/>
+      <c r="AC7" s="142"/>
+      <c r="AD7" s="142"/>
+      <c r="AE7" s="142"/>
+      <c r="AF7" s="142"/>
+      <c r="AG7" s="142"/>
+      <c r="AH7" s="142"/>
+      <c r="AI7" s="142"/>
+      <c r="AJ7" s="142"/>
+      <c r="AK7" s="142"/>
+      <c r="AL7" s="142"/>
+      <c r="AM7" s="142"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
       <c r="A8" s="138" t="s">
@@ -10500,51 +10512,51 @@
       <c r="B8" s="138"/>
       <c r="C8" s="138"/>
       <c r="D8" s="138"/>
-      <c r="E8" s="140" t="s">
+      <c r="E8" s="143" t="s">
         <v>166</v>
       </c>
-      <c r="F8" s="140"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140" t="s">
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="143"/>
+      <c r="L8" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="140"/>
-      <c r="S8" s="140" t="s">
+      <c r="M8" s="143"/>
+      <c r="N8" s="143"/>
+      <c r="O8" s="143"/>
+      <c r="P8" s="143"/>
+      <c r="Q8" s="143"/>
+      <c r="R8" s="143"/>
+      <c r="S8" s="143" t="s">
         <v>168</v>
       </c>
-      <c r="T8" s="140"/>
-      <c r="U8" s="140"/>
-      <c r="V8" s="140"/>
-      <c r="W8" s="140"/>
-      <c r="X8" s="140"/>
-      <c r="Y8" s="140"/>
-      <c r="Z8" s="140" t="s">
+      <c r="T8" s="143"/>
+      <c r="U8" s="143"/>
+      <c r="V8" s="143"/>
+      <c r="W8" s="143"/>
+      <c r="X8" s="143"/>
+      <c r="Y8" s="143"/>
+      <c r="Z8" s="143" t="s">
         <v>169</v>
       </c>
-      <c r="AA8" s="140"/>
-      <c r="AB8" s="140"/>
-      <c r="AC8" s="140"/>
-      <c r="AD8" s="140"/>
-      <c r="AE8" s="140"/>
-      <c r="AF8" s="140"/>
-      <c r="AG8" s="140" t="s">
+      <c r="AA8" s="143"/>
+      <c r="AB8" s="143"/>
+      <c r="AC8" s="143"/>
+      <c r="AD8" s="143"/>
+      <c r="AE8" s="143"/>
+      <c r="AF8" s="143"/>
+      <c r="AG8" s="143" t="s">
         <v>170</v>
       </c>
-      <c r="AH8" s="140"/>
-      <c r="AI8" s="140"/>
-      <c r="AJ8" s="140"/>
-      <c r="AK8" s="140"/>
-      <c r="AL8" s="140"/>
-      <c r="AM8" s="140"/>
+      <c r="AH8" s="143"/>
+      <c r="AI8" s="143"/>
+      <c r="AJ8" s="143"/>
+      <c r="AK8" s="143"/>
+      <c r="AL8" s="143"/>
+      <c r="AM8" s="143"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
       <c r="A9" s="138" t="s">
@@ -10553,41 +10565,41 @@
       <c r="B9" s="138"/>
       <c r="C9" s="138"/>
       <c r="D9" s="138"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="139"/>
-      <c r="G9" s="139"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="139"/>
-      <c r="L9" s="139"/>
-      <c r="M9" s="139"/>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
-      <c r="R9" s="139"/>
-      <c r="S9" s="139"/>
-      <c r="T9" s="139"/>
-      <c r="U9" s="139"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="139"/>
-      <c r="X9" s="139"/>
-      <c r="Y9" s="139"/>
-      <c r="Z9" s="139"/>
-      <c r="AA9" s="139"/>
-      <c r="AB9" s="139"/>
-      <c r="AC9" s="139"/>
-      <c r="AD9" s="139"/>
-      <c r="AE9" s="139"/>
-      <c r="AF9" s="139"/>
-      <c r="AG9" s="139"/>
-      <c r="AH9" s="139"/>
-      <c r="AI9" s="139"/>
-      <c r="AJ9" s="139"/>
-      <c r="AK9" s="139"/>
-      <c r="AL9" s="139"/>
-      <c r="AM9" s="139"/>
+      <c r="E9" s="142"/>
+      <c r="F9" s="142"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="142"/>
+      <c r="I9" s="142"/>
+      <c r="J9" s="142"/>
+      <c r="K9" s="142"/>
+      <c r="L9" s="142"/>
+      <c r="M9" s="142"/>
+      <c r="N9" s="142"/>
+      <c r="O9" s="142"/>
+      <c r="P9" s="142"/>
+      <c r="Q9" s="142"/>
+      <c r="R9" s="142"/>
+      <c r="S9" s="142"/>
+      <c r="T9" s="142"/>
+      <c r="U9" s="142"/>
+      <c r="V9" s="142"/>
+      <c r="W9" s="142"/>
+      <c r="X9" s="142"/>
+      <c r="Y9" s="142"/>
+      <c r="Z9" s="142"/>
+      <c r="AA9" s="142"/>
+      <c r="AB9" s="142"/>
+      <c r="AC9" s="142"/>
+      <c r="AD9" s="142"/>
+      <c r="AE9" s="142"/>
+      <c r="AF9" s="142"/>
+      <c r="AG9" s="142"/>
+      <c r="AH9" s="142"/>
+      <c r="AI9" s="142"/>
+      <c r="AJ9" s="142"/>
+      <c r="AK9" s="142"/>
+      <c r="AL9" s="142"/>
+      <c r="AM9" s="142"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
       <c r="A10" s="138" t="s">
@@ -10596,41 +10608,41 @@
       <c r="B10" s="138"/>
       <c r="C10" s="138"/>
       <c r="D10" s="138"/>
-      <c r="E10" s="139"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="139"/>
-      <c r="K10" s="139"/>
-      <c r="L10" s="139"/>
-      <c r="M10" s="139"/>
-      <c r="N10" s="139"/>
-      <c r="O10" s="139"/>
-      <c r="P10" s="139"/>
-      <c r="Q10" s="139"/>
-      <c r="R10" s="139"/>
-      <c r="S10" s="139"/>
-      <c r="T10" s="139"/>
-      <c r="U10" s="139"/>
-      <c r="V10" s="139"/>
-      <c r="W10" s="139"/>
-      <c r="X10" s="139"/>
-      <c r="Y10" s="139"/>
-      <c r="Z10" s="139"/>
-      <c r="AA10" s="139"/>
-      <c r="AB10" s="139"/>
-      <c r="AC10" s="139"/>
-      <c r="AD10" s="139"/>
-      <c r="AE10" s="139"/>
-      <c r="AF10" s="139"/>
-      <c r="AG10" s="139"/>
-      <c r="AH10" s="139"/>
-      <c r="AI10" s="139"/>
-      <c r="AJ10" s="139"/>
-      <c r="AK10" s="139"/>
-      <c r="AL10" s="139"/>
-      <c r="AM10" s="139"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="142"/>
+      <c r="L10" s="142"/>
+      <c r="M10" s="142"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="142"/>
+      <c r="P10" s="142"/>
+      <c r="Q10" s="142"/>
+      <c r="R10" s="142"/>
+      <c r="S10" s="142"/>
+      <c r="T10" s="142"/>
+      <c r="U10" s="142"/>
+      <c r="V10" s="142"/>
+      <c r="W10" s="142"/>
+      <c r="X10" s="142"/>
+      <c r="Y10" s="142"/>
+      <c r="Z10" s="142"/>
+      <c r="AA10" s="142"/>
+      <c r="AB10" s="142"/>
+      <c r="AC10" s="142"/>
+      <c r="AD10" s="142"/>
+      <c r="AE10" s="142"/>
+      <c r="AF10" s="142"/>
+      <c r="AG10" s="142"/>
+      <c r="AH10" s="142"/>
+      <c r="AI10" s="142"/>
+      <c r="AJ10" s="142"/>
+      <c r="AK10" s="142"/>
+      <c r="AL10" s="142"/>
+      <c r="AM10" s="142"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
       <c r="A11" s="138" t="s">
@@ -10639,51 +10651,51 @@
       <c r="B11" s="138"/>
       <c r="C11" s="138"/>
       <c r="D11" s="138"/>
-      <c r="E11" s="140" t="s">
+      <c r="E11" s="143" t="s">
         <v>171</v>
       </c>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140" t="s">
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143" t="s">
         <v>172</v>
       </c>
-      <c r="M11" s="140"/>
-      <c r="N11" s="140"/>
-      <c r="O11" s="140"/>
-      <c r="P11" s="140"/>
-      <c r="Q11" s="140"/>
-      <c r="R11" s="140"/>
-      <c r="S11" s="140" t="s">
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="143"/>
+      <c r="S11" s="143" t="s">
         <v>173</v>
       </c>
-      <c r="T11" s="140"/>
-      <c r="U11" s="140"/>
-      <c r="V11" s="140"/>
-      <c r="W11" s="140"/>
-      <c r="X11" s="140"/>
-      <c r="Y11" s="140"/>
-      <c r="Z11" s="140" t="s">
+      <c r="T11" s="143"/>
+      <c r="U11" s="143"/>
+      <c r="V11" s="143"/>
+      <c r="W11" s="143"/>
+      <c r="X11" s="143"/>
+      <c r="Y11" s="143"/>
+      <c r="Z11" s="143" t="s">
         <v>174</v>
       </c>
-      <c r="AA11" s="140"/>
-      <c r="AB11" s="140"/>
-      <c r="AC11" s="140"/>
-      <c r="AD11" s="140"/>
-      <c r="AE11" s="140"/>
-      <c r="AF11" s="140"/>
-      <c r="AG11" s="140" t="s">
+      <c r="AA11" s="143"/>
+      <c r="AB11" s="143"/>
+      <c r="AC11" s="143"/>
+      <c r="AD11" s="143"/>
+      <c r="AE11" s="143"/>
+      <c r="AF11" s="143"/>
+      <c r="AG11" s="143" t="s">
         <v>175</v>
       </c>
-      <c r="AH11" s="140"/>
-      <c r="AI11" s="140"/>
-      <c r="AJ11" s="140"/>
-      <c r="AK11" s="140"/>
-      <c r="AL11" s="140"/>
-      <c r="AM11" s="140"/>
+      <c r="AH11" s="143"/>
+      <c r="AI11" s="143"/>
+      <c r="AJ11" s="143"/>
+      <c r="AK11" s="143"/>
+      <c r="AL11" s="143"/>
+      <c r="AM11" s="143"/>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1">
       <c r="A12" s="138" t="s">
@@ -10692,41 +10704,41 @@
       <c r="B12" s="138"/>
       <c r="C12" s="138"/>
       <c r="D12" s="138"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="139"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="139"/>
-      <c r="K12" s="139"/>
-      <c r="L12" s="139"/>
-      <c r="M12" s="139"/>
-      <c r="N12" s="139"/>
-      <c r="O12" s="139"/>
-      <c r="P12" s="139"/>
-      <c r="Q12" s="139"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="139"/>
-      <c r="T12" s="139"/>
-      <c r="U12" s="139"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="139"/>
-      <c r="X12" s="139"/>
-      <c r="Y12" s="139"/>
-      <c r="Z12" s="139"/>
-      <c r="AA12" s="139"/>
-      <c r="AB12" s="139"/>
-      <c r="AC12" s="139"/>
-      <c r="AD12" s="139"/>
-      <c r="AE12" s="139"/>
-      <c r="AF12" s="139"/>
-      <c r="AG12" s="139"/>
-      <c r="AH12" s="139"/>
-      <c r="AI12" s="139"/>
-      <c r="AJ12" s="139"/>
-      <c r="AK12" s="139"/>
-      <c r="AL12" s="139"/>
-      <c r="AM12" s="139"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="142"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="142"/>
+      <c r="P12" s="142"/>
+      <c r="Q12" s="142"/>
+      <c r="R12" s="142"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="142"/>
+      <c r="U12" s="142"/>
+      <c r="V12" s="142"/>
+      <c r="W12" s="142"/>
+      <c r="X12" s="142"/>
+      <c r="Y12" s="142"/>
+      <c r="Z12" s="142"/>
+      <c r="AA12" s="142"/>
+      <c r="AB12" s="142"/>
+      <c r="AC12" s="142"/>
+      <c r="AD12" s="142"/>
+      <c r="AE12" s="142"/>
+      <c r="AF12" s="142"/>
+      <c r="AG12" s="142"/>
+      <c r="AH12" s="142"/>
+      <c r="AI12" s="142"/>
+      <c r="AJ12" s="142"/>
+      <c r="AK12" s="142"/>
+      <c r="AL12" s="142"/>
+      <c r="AM12" s="142"/>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1">
       <c r="A13" s="138" t="s">
@@ -10735,41 +10747,41 @@
       <c r="B13" s="138"/>
       <c r="C13" s="138"/>
       <c r="D13" s="138"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="139"/>
-      <c r="G13" s="139"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="139"/>
-      <c r="J13" s="139"/>
-      <c r="K13" s="139"/>
-      <c r="L13" s="139"/>
-      <c r="M13" s="139"/>
-      <c r="N13" s="139"/>
-      <c r="O13" s="139"/>
-      <c r="P13" s="139"/>
-      <c r="Q13" s="139"/>
-      <c r="R13" s="139"/>
-      <c r="S13" s="139"/>
-      <c r="T13" s="139"/>
-      <c r="U13" s="139"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="139"/>
-      <c r="X13" s="139"/>
-      <c r="Y13" s="139"/>
-      <c r="Z13" s="139"/>
-      <c r="AA13" s="139"/>
-      <c r="AB13" s="139"/>
-      <c r="AC13" s="139"/>
-      <c r="AD13" s="139"/>
-      <c r="AE13" s="139"/>
-      <c r="AF13" s="139"/>
-      <c r="AG13" s="139"/>
-      <c r="AH13" s="139"/>
-      <c r="AI13" s="139"/>
-      <c r="AJ13" s="139"/>
-      <c r="AK13" s="139"/>
-      <c r="AL13" s="139"/>
-      <c r="AM13" s="139"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="142"/>
+      <c r="N13" s="142"/>
+      <c r="O13" s="142"/>
+      <c r="P13" s="142"/>
+      <c r="Q13" s="142"/>
+      <c r="R13" s="142"/>
+      <c r="S13" s="142"/>
+      <c r="T13" s="142"/>
+      <c r="U13" s="142"/>
+      <c r="V13" s="142"/>
+      <c r="W13" s="142"/>
+      <c r="X13" s="142"/>
+      <c r="Y13" s="142"/>
+      <c r="Z13" s="142"/>
+      <c r="AA13" s="142"/>
+      <c r="AB13" s="142"/>
+      <c r="AC13" s="142"/>
+      <c r="AD13" s="142"/>
+      <c r="AE13" s="142"/>
+      <c r="AF13" s="142"/>
+      <c r="AG13" s="142"/>
+      <c r="AH13" s="142"/>
+      <c r="AI13" s="142"/>
+      <c r="AJ13" s="142"/>
+      <c r="AK13" s="142"/>
+      <c r="AL13" s="142"/>
+      <c r="AM13" s="142"/>
     </row>
     <row r="14" spans="1:39">
       <c r="A14" s="68" t="s">
@@ -10896,17 +10908,17 @@
       <c r="AM16" s="34"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
+      <c r="A17" s="141"/>
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="141"/>
+      <c r="H17" s="141"/>
+      <c r="I17" s="141"/>
+      <c r="J17" s="141"/>
+      <c r="K17" s="141"/>
       <c r="L17" s="34"/>
       <c r="M17" s="34"/>
       <c r="N17" s="34"/>
@@ -10978,118 +10990,118 @@
       <c r="AM18" s="34"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="145" t="s">
+      <c r="A19" s="140" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="145"/>
-      <c r="C19" s="145"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="144" t="s">
+      <c r="B19" s="140"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="139" t="s">
         <v>184</v>
       </c>
-      <c r="F19" s="144"/>
-      <c r="G19" s="144"/>
-      <c r="H19" s="144"/>
-      <c r="I19" s="144"/>
-      <c r="J19" s="144"/>
-      <c r="K19" s="144"/>
-      <c r="L19" s="144" t="s">
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="139"/>
+      <c r="I19" s="139"/>
+      <c r="J19" s="139"/>
+      <c r="K19" s="139"/>
+      <c r="L19" s="139" t="s">
         <v>185</v>
       </c>
-      <c r="M19" s="144"/>
-      <c r="N19" s="144"/>
-      <c r="O19" s="144"/>
-      <c r="P19" s="144"/>
-      <c r="Q19" s="144"/>
-      <c r="R19" s="144"/>
-      <c r="S19" s="144" t="s">
+      <c r="M19" s="139"/>
+      <c r="N19" s="139"/>
+      <c r="O19" s="139"/>
+      <c r="P19" s="139"/>
+      <c r="Q19" s="139"/>
+      <c r="R19" s="139"/>
+      <c r="S19" s="139" t="s">
         <v>186</v>
       </c>
-      <c r="T19" s="144"/>
-      <c r="U19" s="144"/>
-      <c r="V19" s="144"/>
-      <c r="W19" s="144"/>
-      <c r="X19" s="144"/>
-      <c r="Y19" s="144"/>
-      <c r="Z19" s="144" t="s">
+      <c r="T19" s="139"/>
+      <c r="U19" s="139"/>
+      <c r="V19" s="139"/>
+      <c r="W19" s="139"/>
+      <c r="X19" s="139"/>
+      <c r="Y19" s="139"/>
+      <c r="Z19" s="139" t="s">
         <v>187</v>
       </c>
-      <c r="AA19" s="144"/>
-      <c r="AB19" s="144"/>
-      <c r="AC19" s="144"/>
-      <c r="AD19" s="144"/>
-      <c r="AE19" s="144"/>
-      <c r="AF19" s="144"/>
-      <c r="AG19" s="144" t="s">
+      <c r="AA19" s="139"/>
+      <c r="AB19" s="139"/>
+      <c r="AC19" s="139"/>
+      <c r="AD19" s="139"/>
+      <c r="AE19" s="139"/>
+      <c r="AF19" s="139"/>
+      <c r="AG19" s="139" t="s">
         <v>188</v>
       </c>
-      <c r="AH19" s="144"/>
-      <c r="AI19" s="144"/>
-      <c r="AJ19" s="144"/>
-      <c r="AK19" s="144"/>
-      <c r="AL19" s="144"/>
-      <c r="AM19" s="144"/>
+      <c r="AH19" s="139"/>
+      <c r="AI19" s="139"/>
+      <c r="AJ19" s="139"/>
+      <c r="AK19" s="139"/>
+      <c r="AL19" s="139"/>
+      <c r="AM19" s="139"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="145"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="144" t="s">
+      <c r="A20" s="140"/>
+      <c r="B20" s="140"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="F20" s="144"/>
-      <c r="G20" s="144"/>
-      <c r="H20" s="144" t="s">
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="I20" s="144"/>
-      <c r="J20" s="144"/>
-      <c r="K20" s="144"/>
-      <c r="L20" s="144" t="s">
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="M20" s="144"/>
-      <c r="N20" s="144"/>
-      <c r="O20" s="144" t="s">
+      <c r="M20" s="139"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="P20" s="144"/>
-      <c r="Q20" s="144"/>
-      <c r="R20" s="144"/>
-      <c r="S20" s="144" t="s">
+      <c r="P20" s="139"/>
+      <c r="Q20" s="139"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="T20" s="144"/>
-      <c r="U20" s="144"/>
-      <c r="V20" s="144" t="s">
+      <c r="T20" s="139"/>
+      <c r="U20" s="139"/>
+      <c r="V20" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="W20" s="144"/>
-      <c r="X20" s="144"/>
-      <c r="Y20" s="144"/>
-      <c r="Z20" s="144" t="s">
+      <c r="W20" s="139"/>
+      <c r="X20" s="139"/>
+      <c r="Y20" s="139"/>
+      <c r="Z20" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="AA20" s="144"/>
-      <c r="AB20" s="144"/>
-      <c r="AC20" s="144" t="s">
+      <c r="AA20" s="139"/>
+      <c r="AB20" s="139"/>
+      <c r="AC20" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="AD20" s="144"/>
-      <c r="AE20" s="144"/>
-      <c r="AF20" s="144"/>
-      <c r="AG20" s="144" t="s">
+      <c r="AD20" s="139"/>
+      <c r="AE20" s="139"/>
+      <c r="AF20" s="139"/>
+      <c r="AG20" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="AH20" s="144"/>
-      <c r="AI20" s="144"/>
-      <c r="AJ20" s="144" t="s">
+      <c r="AH20" s="139"/>
+      <c r="AI20" s="139"/>
+      <c r="AJ20" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="AK20" s="144"/>
-      <c r="AL20" s="144"/>
-      <c r="AM20" s="144"/>
+      <c r="AK20" s="139"/>
+      <c r="AL20" s="139"/>
+      <c r="AM20" s="139"/>
     </row>
     <row r="21" spans="1:39">
       <c r="A21" s="138" t="s">
@@ -11098,41 +11110,41 @@
       <c r="B21" s="138"/>
       <c r="C21" s="138"/>
       <c r="D21" s="138"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="142"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="141"/>
-      <c r="I21" s="142"/>
-      <c r="J21" s="142"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="141"/>
-      <c r="M21" s="142"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="141"/>
-      <c r="P21" s="142"/>
-      <c r="Q21" s="142"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="141"/>
-      <c r="T21" s="142"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="141"/>
-      <c r="W21" s="142"/>
-      <c r="X21" s="142"/>
-      <c r="Y21" s="143"/>
-      <c r="Z21" s="141"/>
-      <c r="AA21" s="142"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="141"/>
-      <c r="AD21" s="142"/>
-      <c r="AE21" s="142"/>
-      <c r="AF21" s="143"/>
-      <c r="AG21" s="141"/>
-      <c r="AH21" s="142"/>
-      <c r="AI21" s="143"/>
-      <c r="AJ21" s="141"/>
-      <c r="AK21" s="142"/>
-      <c r="AL21" s="142"/>
-      <c r="AM21" s="143"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="136"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="137"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="136"/>
+      <c r="N21" s="137"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="136"/>
+      <c r="Q21" s="136"/>
+      <c r="R21" s="137"/>
+      <c r="S21" s="135"/>
+      <c r="T21" s="136"/>
+      <c r="U21" s="137"/>
+      <c r="V21" s="135"/>
+      <c r="W21" s="136"/>
+      <c r="X21" s="136"/>
+      <c r="Y21" s="137"/>
+      <c r="Z21" s="135"/>
+      <c r="AA21" s="136"/>
+      <c r="AB21" s="137"/>
+      <c r="AC21" s="135"/>
+      <c r="AD21" s="136"/>
+      <c r="AE21" s="136"/>
+      <c r="AF21" s="137"/>
+      <c r="AG21" s="135"/>
+      <c r="AH21" s="136"/>
+      <c r="AI21" s="137"/>
+      <c r="AJ21" s="135"/>
+      <c r="AK21" s="136"/>
+      <c r="AL21" s="136"/>
+      <c r="AM21" s="137"/>
     </row>
     <row r="22" spans="1:39">
       <c r="A22" s="138" t="s">
@@ -11141,155 +11153,155 @@
       <c r="B22" s="138"/>
       <c r="C22" s="138"/>
       <c r="D22" s="138"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="142"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="141"/>
-      <c r="I22" s="142"/>
-      <c r="J22" s="142"/>
-      <c r="K22" s="143"/>
-      <c r="L22" s="141"/>
-      <c r="M22" s="142"/>
-      <c r="N22" s="143"/>
-      <c r="O22" s="141"/>
-      <c r="P22" s="142"/>
-      <c r="Q22" s="142"/>
-      <c r="R22" s="143"/>
-      <c r="S22" s="141"/>
-      <c r="T22" s="142"/>
-      <c r="U22" s="143"/>
-      <c r="V22" s="141"/>
-      <c r="W22" s="142"/>
-      <c r="X22" s="142"/>
-      <c r="Y22" s="143"/>
-      <c r="Z22" s="141"/>
-      <c r="AA22" s="142"/>
-      <c r="AB22" s="143"/>
-      <c r="AC22" s="141"/>
-      <c r="AD22" s="142"/>
-      <c r="AE22" s="142"/>
-      <c r="AF22" s="143"/>
-      <c r="AG22" s="141"/>
-      <c r="AH22" s="142"/>
-      <c r="AI22" s="143"/>
-      <c r="AJ22" s="141"/>
-      <c r="AK22" s="142"/>
-      <c r="AL22" s="142"/>
-      <c r="AM22" s="143"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="137"/>
+      <c r="O22" s="135"/>
+      <c r="P22" s="136"/>
+      <c r="Q22" s="136"/>
+      <c r="R22" s="137"/>
+      <c r="S22" s="135"/>
+      <c r="T22" s="136"/>
+      <c r="U22" s="137"/>
+      <c r="V22" s="135"/>
+      <c r="W22" s="136"/>
+      <c r="X22" s="136"/>
+      <c r="Y22" s="137"/>
+      <c r="Z22" s="135"/>
+      <c r="AA22" s="136"/>
+      <c r="AB22" s="137"/>
+      <c r="AC22" s="135"/>
+      <c r="AD22" s="136"/>
+      <c r="AE22" s="136"/>
+      <c r="AF22" s="137"/>
+      <c r="AG22" s="135"/>
+      <c r="AH22" s="136"/>
+      <c r="AI22" s="137"/>
+      <c r="AJ22" s="135"/>
+      <c r="AK22" s="136"/>
+      <c r="AL22" s="136"/>
+      <c r="AM22" s="137"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="145" t="s">
+      <c r="A23" s="140" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="145"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="144" t="s">
+      <c r="B23" s="140"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="139" t="s">
         <v>189</v>
       </c>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
-      <c r="K23" s="144"/>
-      <c r="L23" s="144" t="s">
+      <c r="F23" s="139"/>
+      <c r="G23" s="139"/>
+      <c r="H23" s="139"/>
+      <c r="I23" s="139"/>
+      <c r="J23" s="139"/>
+      <c r="K23" s="139"/>
+      <c r="L23" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="M23" s="144"/>
-      <c r="N23" s="144"/>
-      <c r="O23" s="144"/>
-      <c r="P23" s="144"/>
-      <c r="Q23" s="144"/>
-      <c r="R23" s="144"/>
-      <c r="S23" s="144" t="s">
+      <c r="M23" s="139"/>
+      <c r="N23" s="139"/>
+      <c r="O23" s="139"/>
+      <c r="P23" s="139"/>
+      <c r="Q23" s="139"/>
+      <c r="R23" s="139"/>
+      <c r="S23" s="139" t="s">
         <v>191</v>
       </c>
-      <c r="T23" s="144"/>
-      <c r="U23" s="144"/>
-      <c r="V23" s="144"/>
-      <c r="W23" s="144"/>
-      <c r="X23" s="144"/>
-      <c r="Y23" s="144"/>
-      <c r="Z23" s="144" t="s">
+      <c r="T23" s="139"/>
+      <c r="U23" s="139"/>
+      <c r="V23" s="139"/>
+      <c r="W23" s="139"/>
+      <c r="X23" s="139"/>
+      <c r="Y23" s="139"/>
+      <c r="Z23" s="139" t="s">
         <v>192</v>
       </c>
-      <c r="AA23" s="144"/>
-      <c r="AB23" s="144"/>
-      <c r="AC23" s="144"/>
-      <c r="AD23" s="144"/>
-      <c r="AE23" s="144"/>
-      <c r="AF23" s="144"/>
-      <c r="AG23" s="144" t="s">
+      <c r="AA23" s="139"/>
+      <c r="AB23" s="139"/>
+      <c r="AC23" s="139"/>
+      <c r="AD23" s="139"/>
+      <c r="AE23" s="139"/>
+      <c r="AF23" s="139"/>
+      <c r="AG23" s="139" t="s">
         <v>193</v>
       </c>
-      <c r="AH23" s="144"/>
-      <c r="AI23" s="144"/>
-      <c r="AJ23" s="144"/>
-      <c r="AK23" s="144"/>
-      <c r="AL23" s="144"/>
-      <c r="AM23" s="144"/>
+      <c r="AH23" s="139"/>
+      <c r="AI23" s="139"/>
+      <c r="AJ23" s="139"/>
+      <c r="AK23" s="139"/>
+      <c r="AL23" s="139"/>
+      <c r="AM23" s="139"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="145"/>
-      <c r="B24" s="145"/>
-      <c r="C24" s="145"/>
-      <c r="D24" s="145"/>
-      <c r="E24" s="144" t="s">
+      <c r="A24" s="140"/>
+      <c r="B24" s="140"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144" t="s">
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="I24" s="144"/>
-      <c r="J24" s="144"/>
-      <c r="K24" s="144"/>
-      <c r="L24" s="144" t="s">
+      <c r="I24" s="139"/>
+      <c r="J24" s="139"/>
+      <c r="K24" s="139"/>
+      <c r="L24" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="M24" s="144"/>
-      <c r="N24" s="144"/>
-      <c r="O24" s="144" t="s">
+      <c r="M24" s="139"/>
+      <c r="N24" s="139"/>
+      <c r="O24" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="P24" s="144"/>
-      <c r="Q24" s="144"/>
-      <c r="R24" s="144"/>
-      <c r="S24" s="144" t="s">
+      <c r="P24" s="139"/>
+      <c r="Q24" s="139"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="T24" s="144"/>
-      <c r="U24" s="144"/>
-      <c r="V24" s="144" t="s">
+      <c r="T24" s="139"/>
+      <c r="U24" s="139"/>
+      <c r="V24" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="W24" s="144"/>
-      <c r="X24" s="144"/>
-      <c r="Y24" s="144"/>
-      <c r="Z24" s="144" t="s">
+      <c r="W24" s="139"/>
+      <c r="X24" s="139"/>
+      <c r="Y24" s="139"/>
+      <c r="Z24" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="AA24" s="144"/>
-      <c r="AB24" s="144"/>
-      <c r="AC24" s="144" t="s">
+      <c r="AA24" s="139"/>
+      <c r="AB24" s="139"/>
+      <c r="AC24" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="AD24" s="144"/>
-      <c r="AE24" s="144"/>
-      <c r="AF24" s="144"/>
-      <c r="AG24" s="144" t="s">
+      <c r="AD24" s="139"/>
+      <c r="AE24" s="139"/>
+      <c r="AF24" s="139"/>
+      <c r="AG24" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="AH24" s="144"/>
-      <c r="AI24" s="144"/>
-      <c r="AJ24" s="144" t="s">
+      <c r="AH24" s="139"/>
+      <c r="AI24" s="139"/>
+      <c r="AJ24" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="AK24" s="144"/>
-      <c r="AL24" s="144"/>
-      <c r="AM24" s="144"/>
+      <c r="AK24" s="139"/>
+      <c r="AL24" s="139"/>
+      <c r="AM24" s="139"/>
     </row>
     <row r="25" spans="1:39">
       <c r="A25" s="138" t="s">
@@ -11298,41 +11310,41 @@
       <c r="B25" s="138"/>
       <c r="C25" s="138"/>
       <c r="D25" s="138"/>
-      <c r="E25" s="141"/>
-      <c r="F25" s="142"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="141"/>
-      <c r="I25" s="142"/>
-      <c r="J25" s="142"/>
-      <c r="K25" s="143"/>
-      <c r="L25" s="141"/>
-      <c r="M25" s="142"/>
-      <c r="N25" s="143"/>
-      <c r="O25" s="141"/>
-      <c r="P25" s="142"/>
-      <c r="Q25" s="142"/>
-      <c r="R25" s="143"/>
-      <c r="S25" s="141"/>
-      <c r="T25" s="142"/>
-      <c r="U25" s="143"/>
-      <c r="V25" s="141"/>
-      <c r="W25" s="142"/>
-      <c r="X25" s="142"/>
-      <c r="Y25" s="143"/>
-      <c r="Z25" s="141"/>
-      <c r="AA25" s="142"/>
-      <c r="AB25" s="143"/>
-      <c r="AC25" s="141"/>
-      <c r="AD25" s="142"/>
-      <c r="AE25" s="142"/>
-      <c r="AF25" s="143"/>
-      <c r="AG25" s="141"/>
-      <c r="AH25" s="142"/>
-      <c r="AI25" s="143"/>
-      <c r="AJ25" s="141"/>
-      <c r="AK25" s="142"/>
-      <c r="AL25" s="142"/>
-      <c r="AM25" s="143"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="135"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="137"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="136"/>
+      <c r="N25" s="137"/>
+      <c r="O25" s="135"/>
+      <c r="P25" s="136"/>
+      <c r="Q25" s="136"/>
+      <c r="R25" s="137"/>
+      <c r="S25" s="135"/>
+      <c r="T25" s="136"/>
+      <c r="U25" s="137"/>
+      <c r="V25" s="135"/>
+      <c r="W25" s="136"/>
+      <c r="X25" s="136"/>
+      <c r="Y25" s="137"/>
+      <c r="Z25" s="135"/>
+      <c r="AA25" s="136"/>
+      <c r="AB25" s="137"/>
+      <c r="AC25" s="135"/>
+      <c r="AD25" s="136"/>
+      <c r="AE25" s="136"/>
+      <c r="AF25" s="137"/>
+      <c r="AG25" s="135"/>
+      <c r="AH25" s="136"/>
+      <c r="AI25" s="137"/>
+      <c r="AJ25" s="135"/>
+      <c r="AK25" s="136"/>
+      <c r="AL25" s="136"/>
+      <c r="AM25" s="137"/>
     </row>
     <row r="26" spans="1:39">
       <c r="A26" s="138" t="s">
@@ -11341,155 +11353,155 @@
       <c r="B26" s="138"/>
       <c r="C26" s="138"/>
       <c r="D26" s="138"/>
-      <c r="E26" s="141"/>
-      <c r="F26" s="142"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="141"/>
-      <c r="I26" s="142"/>
-      <c r="J26" s="142"/>
-      <c r="K26" s="143"/>
-      <c r="L26" s="141"/>
-      <c r="M26" s="142"/>
-      <c r="N26" s="143"/>
-      <c r="O26" s="141"/>
-      <c r="P26" s="142"/>
-      <c r="Q26" s="142"/>
-      <c r="R26" s="143"/>
-      <c r="S26" s="141"/>
-      <c r="T26" s="142"/>
-      <c r="U26" s="143"/>
-      <c r="V26" s="141"/>
-      <c r="W26" s="142"/>
-      <c r="X26" s="142"/>
-      <c r="Y26" s="143"/>
-      <c r="Z26" s="141"/>
-      <c r="AA26" s="142"/>
-      <c r="AB26" s="143"/>
-      <c r="AC26" s="141"/>
-      <c r="AD26" s="142"/>
-      <c r="AE26" s="142"/>
-      <c r="AF26" s="143"/>
-      <c r="AG26" s="141"/>
-      <c r="AH26" s="142"/>
-      <c r="AI26" s="143"/>
-      <c r="AJ26" s="141"/>
-      <c r="AK26" s="142"/>
-      <c r="AL26" s="142"/>
-      <c r="AM26" s="143"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="135"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="137"/>
+      <c r="L26" s="135"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="137"/>
+      <c r="O26" s="135"/>
+      <c r="P26" s="136"/>
+      <c r="Q26" s="136"/>
+      <c r="R26" s="137"/>
+      <c r="S26" s="135"/>
+      <c r="T26" s="136"/>
+      <c r="U26" s="137"/>
+      <c r="V26" s="135"/>
+      <c r="W26" s="136"/>
+      <c r="X26" s="136"/>
+      <c r="Y26" s="137"/>
+      <c r="Z26" s="135"/>
+      <c r="AA26" s="136"/>
+      <c r="AB26" s="137"/>
+      <c r="AC26" s="135"/>
+      <c r="AD26" s="136"/>
+      <c r="AE26" s="136"/>
+      <c r="AF26" s="137"/>
+      <c r="AG26" s="135"/>
+      <c r="AH26" s="136"/>
+      <c r="AI26" s="137"/>
+      <c r="AJ26" s="135"/>
+      <c r="AK26" s="136"/>
+      <c r="AL26" s="136"/>
+      <c r="AM26" s="137"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="145" t="s">
+      <c r="A27" s="140" t="s">
         <v>160</v>
       </c>
-      <c r="B27" s="145"/>
-      <c r="C27" s="145"/>
-      <c r="D27" s="145"/>
-      <c r="E27" s="144" t="s">
+      <c r="B27" s="140"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="140"/>
+      <c r="E27" s="139" t="s">
         <v>198</v>
       </c>
-      <c r="F27" s="144"/>
-      <c r="G27" s="144"/>
-      <c r="H27" s="144"/>
-      <c r="I27" s="144"/>
-      <c r="J27" s="144"/>
-      <c r="K27" s="144"/>
-      <c r="L27" s="144" t="s">
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
+      <c r="H27" s="139"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="139"/>
+      <c r="K27" s="139"/>
+      <c r="L27" s="139" t="s">
         <v>197</v>
       </c>
-      <c r="M27" s="144"/>
-      <c r="N27" s="144"/>
-      <c r="O27" s="144"/>
-      <c r="P27" s="144"/>
-      <c r="Q27" s="144"/>
-      <c r="R27" s="144"/>
-      <c r="S27" s="144" t="s">
+      <c r="M27" s="139"/>
+      <c r="N27" s="139"/>
+      <c r="O27" s="139"/>
+      <c r="P27" s="139"/>
+      <c r="Q27" s="139"/>
+      <c r="R27" s="139"/>
+      <c r="S27" s="139" t="s">
         <v>196</v>
       </c>
-      <c r="T27" s="144"/>
-      <c r="U27" s="144"/>
-      <c r="V27" s="144"/>
-      <c r="W27" s="144"/>
-      <c r="X27" s="144"/>
-      <c r="Y27" s="144"/>
-      <c r="Z27" s="144" t="s">
+      <c r="T27" s="139"/>
+      <c r="U27" s="139"/>
+      <c r="V27" s="139"/>
+      <c r="W27" s="139"/>
+      <c r="X27" s="139"/>
+      <c r="Y27" s="139"/>
+      <c r="Z27" s="139" t="s">
         <v>195</v>
       </c>
-      <c r="AA27" s="144"/>
-      <c r="AB27" s="144"/>
-      <c r="AC27" s="144"/>
-      <c r="AD27" s="144"/>
-      <c r="AE27" s="144"/>
-      <c r="AF27" s="144"/>
-      <c r="AG27" s="144" t="s">
+      <c r="AA27" s="139"/>
+      <c r="AB27" s="139"/>
+      <c r="AC27" s="139"/>
+      <c r="AD27" s="139"/>
+      <c r="AE27" s="139"/>
+      <c r="AF27" s="139"/>
+      <c r="AG27" s="139" t="s">
         <v>194</v>
       </c>
-      <c r="AH27" s="144"/>
-      <c r="AI27" s="144"/>
-      <c r="AJ27" s="144"/>
-      <c r="AK27" s="144"/>
-      <c r="AL27" s="144"/>
-      <c r="AM27" s="144"/>
+      <c r="AH27" s="139"/>
+      <c r="AI27" s="139"/>
+      <c r="AJ27" s="139"/>
+      <c r="AK27" s="139"/>
+      <c r="AL27" s="139"/>
+      <c r="AM27" s="139"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="145"/>
-      <c r="B28" s="145"/>
-      <c r="C28" s="145"/>
-      <c r="D28" s="145"/>
-      <c r="E28" s="144" t="s">
+      <c r="A28" s="140"/>
+      <c r="B28" s="140"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="140"/>
+      <c r="E28" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="F28" s="144"/>
-      <c r="G28" s="144"/>
-      <c r="H28" s="144" t="s">
+      <c r="F28" s="139"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="I28" s="144"/>
-      <c r="J28" s="144"/>
-      <c r="K28" s="144"/>
-      <c r="L28" s="144" t="s">
+      <c r="I28" s="139"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="139"/>
+      <c r="L28" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="M28" s="144"/>
-      <c r="N28" s="144"/>
-      <c r="O28" s="144" t="s">
+      <c r="M28" s="139"/>
+      <c r="N28" s="139"/>
+      <c r="O28" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="P28" s="144"/>
-      <c r="Q28" s="144"/>
-      <c r="R28" s="144"/>
-      <c r="S28" s="144" t="s">
+      <c r="P28" s="139"/>
+      <c r="Q28" s="139"/>
+      <c r="R28" s="139"/>
+      <c r="S28" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="T28" s="144"/>
-      <c r="U28" s="144"/>
-      <c r="V28" s="144" t="s">
+      <c r="T28" s="139"/>
+      <c r="U28" s="139"/>
+      <c r="V28" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="W28" s="144"/>
-      <c r="X28" s="144"/>
-      <c r="Y28" s="144"/>
-      <c r="Z28" s="144" t="s">
+      <c r="W28" s="139"/>
+      <c r="X28" s="139"/>
+      <c r="Y28" s="139"/>
+      <c r="Z28" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="AA28" s="144"/>
-      <c r="AB28" s="144"/>
-      <c r="AC28" s="144" t="s">
+      <c r="AA28" s="139"/>
+      <c r="AB28" s="139"/>
+      <c r="AC28" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="AD28" s="144"/>
-      <c r="AE28" s="144"/>
-      <c r="AF28" s="144"/>
-      <c r="AG28" s="144" t="s">
+      <c r="AD28" s="139"/>
+      <c r="AE28" s="139"/>
+      <c r="AF28" s="139"/>
+      <c r="AG28" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="AH28" s="144"/>
-      <c r="AI28" s="144"/>
-      <c r="AJ28" s="144" t="s">
+      <c r="AH28" s="139"/>
+      <c r="AI28" s="139"/>
+      <c r="AJ28" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="AK28" s="144"/>
-      <c r="AL28" s="144"/>
-      <c r="AM28" s="144"/>
+      <c r="AK28" s="139"/>
+      <c r="AL28" s="139"/>
+      <c r="AM28" s="139"/>
     </row>
     <row r="29" spans="1:39">
       <c r="A29" s="138" t="s">
@@ -11498,41 +11510,41 @@
       <c r="B29" s="138"/>
       <c r="C29" s="138"/>
       <c r="D29" s="138"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="141"/>
-      <c r="I29" s="142"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="143"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="142"/>
-      <c r="N29" s="143"/>
-      <c r="O29" s="141"/>
-      <c r="P29" s="142"/>
-      <c r="Q29" s="142"/>
-      <c r="R29" s="143"/>
-      <c r="S29" s="141"/>
-      <c r="T29" s="142"/>
-      <c r="U29" s="143"/>
-      <c r="V29" s="141"/>
-      <c r="W29" s="142"/>
-      <c r="X29" s="142"/>
-      <c r="Y29" s="143"/>
-      <c r="Z29" s="141"/>
-      <c r="AA29" s="142"/>
-      <c r="AB29" s="143"/>
-      <c r="AC29" s="141"/>
-      <c r="AD29" s="142"/>
-      <c r="AE29" s="142"/>
-      <c r="AF29" s="143"/>
-      <c r="AG29" s="141"/>
-      <c r="AH29" s="142"/>
-      <c r="AI29" s="143"/>
-      <c r="AJ29" s="141"/>
-      <c r="AK29" s="142"/>
-      <c r="AL29" s="142"/>
-      <c r="AM29" s="143"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="136"/>
+      <c r="G29" s="137"/>
+      <c r="H29" s="135"/>
+      <c r="I29" s="136"/>
+      <c r="J29" s="136"/>
+      <c r="K29" s="137"/>
+      <c r="L29" s="135"/>
+      <c r="M29" s="136"/>
+      <c r="N29" s="137"/>
+      <c r="O29" s="135"/>
+      <c r="P29" s="136"/>
+      <c r="Q29" s="136"/>
+      <c r="R29" s="137"/>
+      <c r="S29" s="135"/>
+      <c r="T29" s="136"/>
+      <c r="U29" s="137"/>
+      <c r="V29" s="135"/>
+      <c r="W29" s="136"/>
+      <c r="X29" s="136"/>
+      <c r="Y29" s="137"/>
+      <c r="Z29" s="135"/>
+      <c r="AA29" s="136"/>
+      <c r="AB29" s="137"/>
+      <c r="AC29" s="135"/>
+      <c r="AD29" s="136"/>
+      <c r="AE29" s="136"/>
+      <c r="AF29" s="137"/>
+      <c r="AG29" s="135"/>
+      <c r="AH29" s="136"/>
+      <c r="AI29" s="137"/>
+      <c r="AJ29" s="135"/>
+      <c r="AK29" s="136"/>
+      <c r="AL29" s="136"/>
+      <c r="AM29" s="137"/>
     </row>
     <row r="30" spans="1:39">
       <c r="A30" s="138" t="s">
@@ -11541,41 +11553,41 @@
       <c r="B30" s="138"/>
       <c r="C30" s="138"/>
       <c r="D30" s="138"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="141"/>
-      <c r="I30" s="142"/>
-      <c r="J30" s="142"/>
-      <c r="K30" s="143"/>
-      <c r="L30" s="141"/>
-      <c r="M30" s="142"/>
-      <c r="N30" s="143"/>
-      <c r="O30" s="141"/>
-      <c r="P30" s="142"/>
-      <c r="Q30" s="142"/>
-      <c r="R30" s="143"/>
-      <c r="S30" s="141"/>
-      <c r="T30" s="142"/>
-      <c r="U30" s="143"/>
-      <c r="V30" s="141"/>
-      <c r="W30" s="142"/>
-      <c r="X30" s="142"/>
-      <c r="Y30" s="143"/>
-      <c r="Z30" s="141"/>
-      <c r="AA30" s="142"/>
-      <c r="AB30" s="143"/>
-      <c r="AC30" s="141"/>
-      <c r="AD30" s="142"/>
-      <c r="AE30" s="142"/>
-      <c r="AF30" s="143"/>
-      <c r="AG30" s="141"/>
-      <c r="AH30" s="142"/>
-      <c r="AI30" s="143"/>
-      <c r="AJ30" s="141"/>
-      <c r="AK30" s="142"/>
-      <c r="AL30" s="142"/>
-      <c r="AM30" s="143"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="136"/>
+      <c r="G30" s="137"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="137"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="136"/>
+      <c r="N30" s="137"/>
+      <c r="O30" s="135"/>
+      <c r="P30" s="136"/>
+      <c r="Q30" s="136"/>
+      <c r="R30" s="137"/>
+      <c r="S30" s="135"/>
+      <c r="T30" s="136"/>
+      <c r="U30" s="137"/>
+      <c r="V30" s="135"/>
+      <c r="W30" s="136"/>
+      <c r="X30" s="136"/>
+      <c r="Y30" s="137"/>
+      <c r="Z30" s="135"/>
+      <c r="AA30" s="136"/>
+      <c r="AB30" s="137"/>
+      <c r="AC30" s="135"/>
+      <c r="AD30" s="136"/>
+      <c r="AE30" s="136"/>
+      <c r="AF30" s="137"/>
+      <c r="AG30" s="135"/>
+      <c r="AH30" s="136"/>
+      <c r="AI30" s="137"/>
+      <c r="AJ30" s="135"/>
+      <c r="AK30" s="136"/>
+      <c r="AL30" s="136"/>
+      <c r="AM30" s="137"/>
     </row>
     <row r="31" spans="1:39">
       <c r="A31" s="68" t="s">
@@ -11696,155 +11708,6 @@
     </row>
   </sheetData>
   <mergeCells count="173">
-    <mergeCell ref="S30:U30"/>
-    <mergeCell ref="V30:Y30"/>
-    <mergeCell ref="Z30:AB30"/>
-    <mergeCell ref="AC30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AM30"/>
-    <mergeCell ref="V29:Y29"/>
-    <mergeCell ref="Z29:AB29"/>
-    <mergeCell ref="AC29:AF29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AM29"/>
-    <mergeCell ref="S29:U29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="S28:U28"/>
-    <mergeCell ref="V28:Y28"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="AC28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ28:AM28"/>
-    <mergeCell ref="A27:D28"/>
-    <mergeCell ref="E27:K27"/>
-    <mergeCell ref="L27:R27"/>
-    <mergeCell ref="S27:Y27"/>
-    <mergeCell ref="Z27:AF27"/>
-    <mergeCell ref="AG27:AM27"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="S26:U26"/>
-    <mergeCell ref="V26:Y26"/>
-    <mergeCell ref="Z26:AB26"/>
-    <mergeCell ref="AC26:AF26"/>
-    <mergeCell ref="AG26:AI26"/>
-    <mergeCell ref="AJ26:AM26"/>
-    <mergeCell ref="V25:Y25"/>
-    <mergeCell ref="Z25:AB25"/>
-    <mergeCell ref="AC25:AF25"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AM25"/>
-    <mergeCell ref="S25:U25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="AC20:AF20"/>
-    <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="AJ20:AM20"/>
-    <mergeCell ref="A23:D24"/>
-    <mergeCell ref="E23:K23"/>
-    <mergeCell ref="L23:R23"/>
-    <mergeCell ref="S23:Y23"/>
-    <mergeCell ref="Z23:AF23"/>
-    <mergeCell ref="AG23:AM23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="V24:Y24"/>
-    <mergeCell ref="Z24:AB24"/>
-    <mergeCell ref="AC24:AF24"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="AJ24:AM24"/>
-    <mergeCell ref="AG19:AM19"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="S20:U20"/>
-    <mergeCell ref="V20:Y20"/>
-    <mergeCell ref="Z20:AB20"/>
-    <mergeCell ref="AG21:AI21"/>
-    <mergeCell ref="AJ21:AM21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="S22:U22"/>
-    <mergeCell ref="V22:Y22"/>
-    <mergeCell ref="Z22:AB22"/>
-    <mergeCell ref="AC22:AF22"/>
-    <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AJ22:AM22"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="V21:Y21"/>
-    <mergeCell ref="Z21:AB21"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E12:K12"/>
-    <mergeCell ref="L12:R12"/>
-    <mergeCell ref="S12:Y12"/>
-    <mergeCell ref="Z12:AF12"/>
-    <mergeCell ref="L19:R19"/>
-    <mergeCell ref="S19:Y19"/>
-    <mergeCell ref="Z19:AF19"/>
-    <mergeCell ref="A19:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="E19:K19"/>
-    <mergeCell ref="AC21:AF21"/>
-    <mergeCell ref="AG12:AM12"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E10:K10"/>
-    <mergeCell ref="L10:R10"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="Z10:AF10"/>
-    <mergeCell ref="AG10:AM10"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:K9"/>
-    <mergeCell ref="L9:R9"/>
-    <mergeCell ref="S9:Y9"/>
-    <mergeCell ref="Z9:AF9"/>
-    <mergeCell ref="AG9:AM9"/>
-    <mergeCell ref="AG6:AM6"/>
-    <mergeCell ref="E5:K5"/>
-    <mergeCell ref="L5:R5"/>
-    <mergeCell ref="S5:Y5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:K8"/>
-    <mergeCell ref="L8:R8"/>
-    <mergeCell ref="S8:Y8"/>
-    <mergeCell ref="Z8:AF8"/>
-    <mergeCell ref="AG8:AM8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:K7"/>
-    <mergeCell ref="L7:R7"/>
-    <mergeCell ref="S7:Y7"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AM7"/>
     <mergeCell ref="AC3:AG3"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A3:K3"/>
@@ -11869,6 +11732,155 @@
     <mergeCell ref="L6:R6"/>
     <mergeCell ref="S6:Y6"/>
     <mergeCell ref="Z6:AF6"/>
+    <mergeCell ref="AG6:AM6"/>
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="L5:R5"/>
+    <mergeCell ref="S5:Y5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:K8"/>
+    <mergeCell ref="L8:R8"/>
+    <mergeCell ref="S8:Y8"/>
+    <mergeCell ref="Z8:AF8"/>
+    <mergeCell ref="AG8:AM8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:K7"/>
+    <mergeCell ref="L7:R7"/>
+    <mergeCell ref="S7:Y7"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AM7"/>
+    <mergeCell ref="AG12:AM12"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:K10"/>
+    <mergeCell ref="L10:R10"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="Z10:AF10"/>
+    <mergeCell ref="AG10:AM10"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:K9"/>
+    <mergeCell ref="L9:R9"/>
+    <mergeCell ref="S9:Y9"/>
+    <mergeCell ref="Z9:AF9"/>
+    <mergeCell ref="AG9:AM9"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="S21:U21"/>
+    <mergeCell ref="V21:Y21"/>
+    <mergeCell ref="Z21:AB21"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:K12"/>
+    <mergeCell ref="L12:R12"/>
+    <mergeCell ref="S12:Y12"/>
+    <mergeCell ref="Z12:AF12"/>
+    <mergeCell ref="L19:R19"/>
+    <mergeCell ref="S19:Y19"/>
+    <mergeCell ref="Z19:AF19"/>
+    <mergeCell ref="A19:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="AC21:AF21"/>
+    <mergeCell ref="AG19:AM19"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="Z20:AB20"/>
+    <mergeCell ref="AG21:AI21"/>
+    <mergeCell ref="AJ21:AM21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="S22:U22"/>
+    <mergeCell ref="V22:Y22"/>
+    <mergeCell ref="Z22:AB22"/>
+    <mergeCell ref="AC22:AF22"/>
+    <mergeCell ref="AG22:AI22"/>
+    <mergeCell ref="AJ22:AM22"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="AC20:AF20"/>
+    <mergeCell ref="AG20:AI20"/>
+    <mergeCell ref="AJ20:AM20"/>
+    <mergeCell ref="A23:D24"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="L23:R23"/>
+    <mergeCell ref="S23:Y23"/>
+    <mergeCell ref="Z23:AF23"/>
+    <mergeCell ref="AG23:AM23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="V24:Y24"/>
+    <mergeCell ref="Z24:AB24"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AJ24:AM24"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="S26:U26"/>
+    <mergeCell ref="V26:Y26"/>
+    <mergeCell ref="Z26:AB26"/>
+    <mergeCell ref="AC26:AF26"/>
+    <mergeCell ref="AG26:AI26"/>
+    <mergeCell ref="AJ26:AM26"/>
+    <mergeCell ref="V25:Y25"/>
+    <mergeCell ref="Z25:AB25"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AM25"/>
+    <mergeCell ref="S25:U25"/>
+    <mergeCell ref="S28:U28"/>
+    <mergeCell ref="V28:Y28"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="AC28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AJ28:AM28"/>
+    <mergeCell ref="A27:D28"/>
+    <mergeCell ref="E27:K27"/>
+    <mergeCell ref="L27:R27"/>
+    <mergeCell ref="S27:Y27"/>
+    <mergeCell ref="Z27:AF27"/>
+    <mergeCell ref="AG27:AM27"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="S30:U30"/>
+    <mergeCell ref="V30:Y30"/>
+    <mergeCell ref="Z30:AB30"/>
+    <mergeCell ref="AC30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AM30"/>
+    <mergeCell ref="V29:Y29"/>
+    <mergeCell ref="Z29:AB29"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AM29"/>
+    <mergeCell ref="S29:U29"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11909,32 +11921,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="135"/>
-      <c r="Z1" s="135"/>
-      <c r="AA1" s="135"/>
-      <c r="AB1" s="135"/>
-      <c r="AC1" s="135"/>
-      <c r="AD1" s="135"/>
-      <c r="AE1" s="135"/>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="135"/>
-      <c r="AI1" s="135"/>
-      <c r="AJ1" s="135"/>
-      <c r="AK1" s="135"/>
-      <c r="AL1" s="135"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="144"/>
+      <c r="Z1" s="144"/>
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="144"/>
+      <c r="AF1" s="144"/>
+      <c r="AG1" s="144"/>
+      <c r="AH1" s="144"/>
+      <c r="AI1" s="144"/>
+      <c r="AJ1" s="144"/>
+      <c r="AK1" s="144"/>
+      <c r="AL1" s="144"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="33" t="s">
@@ -11976,17 +11988,17 @@
       <c r="AL2" s="34"/>
     </row>
     <row r="3" spans="1:38">
-      <c r="A3" s="136"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -12063,12 +12075,12 @@
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="35"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
       <c r="L5" s="6" t="s">
         <v>129</v>
       </c>
@@ -12106,13 +12118,13 @@
       <c r="B6" s="6"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
-      <c r="E6" s="147"/>
-      <c r="F6" s="147"/>
-      <c r="G6" s="147"/>
-      <c r="H6" s="147"/>
-      <c r="I6" s="147"/>
-      <c r="J6" s="147"/>
-      <c r="K6" s="147"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="157"/>
+      <c r="J6" s="157"/>
+      <c r="K6" s="157"/>
       <c r="L6" s="6" t="s">
         <v>131</v>
       </c>
@@ -12154,13 +12166,13 @@
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="37"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="148"/>
-      <c r="L7" s="148"/>
-      <c r="M7" s="148"/>
-      <c r="N7" s="148"/>
-      <c r="O7" s="148"/>
+      <c r="I7" s="158"/>
+      <c r="J7" s="158"/>
+      <c r="K7" s="158"/>
+      <c r="L7" s="158"/>
+      <c r="M7" s="158"/>
+      <c r="N7" s="158"/>
+      <c r="O7" s="158"/>
       <c r="P7" s="37"/>
       <c r="Q7" s="37"/>
       <c r="R7" s="37"/>
@@ -12273,547 +12285,547 @@
       </c>
       <c r="B10" s="65"/>
       <c r="C10" s="66"/>
-      <c r="D10" s="150"/>
-      <c r="E10" s="150"/>
-      <c r="F10" s="150"/>
-      <c r="G10" s="153" t="s">
+      <c r="D10" s="151"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="151"/>
+      <c r="G10" s="155" t="s">
         <v>134</v>
       </c>
-      <c r="H10" s="154"/>
-      <c r="I10" s="152"/>
-      <c r="J10" s="146"/>
-      <c r="K10" s="146"/>
-      <c r="L10" s="146"/>
-      <c r="M10" s="146"/>
-      <c r="N10" s="146"/>
-      <c r="O10" s="146"/>
-      <c r="P10" s="146"/>
-      <c r="Q10" s="146"/>
-      <c r="R10" s="146"/>
-      <c r="S10" s="146"/>
-      <c r="T10" s="146"/>
-      <c r="U10" s="146"/>
-      <c r="V10" s="146"/>
-      <c r="W10" s="146"/>
-      <c r="X10" s="146"/>
-      <c r="Y10" s="146"/>
-      <c r="Z10" s="146"/>
-      <c r="AA10" s="146"/>
-      <c r="AB10" s="146"/>
-      <c r="AC10" s="146"/>
-      <c r="AD10" s="146"/>
-      <c r="AE10" s="146"/>
-      <c r="AF10" s="146"/>
-      <c r="AG10" s="146"/>
-      <c r="AH10" s="146"/>
-      <c r="AI10" s="146"/>
-      <c r="AJ10" s="146"/>
-      <c r="AK10" s="146"/>
-      <c r="AL10" s="146"/>
+      <c r="H10" s="156"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="154"/>
+      <c r="L10" s="154"/>
+      <c r="M10" s="154"/>
+      <c r="N10" s="154"/>
+      <c r="O10" s="154"/>
+      <c r="P10" s="154"/>
+      <c r="Q10" s="154"/>
+      <c r="R10" s="154"/>
+      <c r="S10" s="154"/>
+      <c r="T10" s="154"/>
+      <c r="U10" s="154"/>
+      <c r="V10" s="154"/>
+      <c r="W10" s="154"/>
+      <c r="X10" s="154"/>
+      <c r="Y10" s="154"/>
+      <c r="Z10" s="154"/>
+      <c r="AA10" s="154"/>
+      <c r="AB10" s="154"/>
+      <c r="AC10" s="154"/>
+      <c r="AD10" s="154"/>
+      <c r="AE10" s="154"/>
+      <c r="AF10" s="154"/>
+      <c r="AG10" s="154"/>
+      <c r="AH10" s="154"/>
+      <c r="AI10" s="154"/>
+      <c r="AJ10" s="154"/>
+      <c r="AK10" s="154"/>
+      <c r="AL10" s="154"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1">
-      <c r="A11" s="149" t="s">
+      <c r="A11" s="150" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="149"/>
-      <c r="C11" s="151"/>
-      <c r="D11" s="151"/>
-      <c r="E11" s="151"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="151"/>
-      <c r="H11" s="151"/>
-      <c r="I11" s="149"/>
-      <c r="J11" s="149"/>
-      <c r="K11" s="149"/>
-      <c r="L11" s="149"/>
-      <c r="M11" s="149"/>
-      <c r="N11" s="149"/>
-      <c r="O11" s="149"/>
-      <c r="P11" s="149"/>
-      <c r="Q11" s="149"/>
-      <c r="R11" s="149"/>
-      <c r="S11" s="149"/>
-      <c r="T11" s="149"/>
-      <c r="U11" s="149"/>
-      <c r="V11" s="149"/>
-      <c r="W11" s="149"/>
-      <c r="X11" s="149"/>
-      <c r="Y11" s="149"/>
-      <c r="Z11" s="149"/>
-      <c r="AA11" s="149"/>
-      <c r="AB11" s="149"/>
-      <c r="AC11" s="149"/>
-      <c r="AD11" s="149"/>
-      <c r="AE11" s="149"/>
-      <c r="AF11" s="149"/>
-      <c r="AG11" s="149"/>
-      <c r="AH11" s="149"/>
-      <c r="AI11" s="149"/>
-      <c r="AJ11" s="149"/>
-      <c r="AK11" s="149"/>
-      <c r="AL11" s="149"/>
+      <c r="B11" s="150"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="152"/>
+      <c r="E11" s="152"/>
+      <c r="F11" s="152"/>
+      <c r="G11" s="152"/>
+      <c r="H11" s="152"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="150"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="150"/>
+      <c r="N11" s="150"/>
+      <c r="O11" s="150"/>
+      <c r="P11" s="150"/>
+      <c r="Q11" s="150"/>
+      <c r="R11" s="150"/>
+      <c r="S11" s="150"/>
+      <c r="T11" s="150"/>
+      <c r="U11" s="150"/>
+      <c r="V11" s="150"/>
+      <c r="W11" s="150"/>
+      <c r="X11" s="150"/>
+      <c r="Y11" s="150"/>
+      <c r="Z11" s="150"/>
+      <c r="AA11" s="150"/>
+      <c r="AB11" s="150"/>
+      <c r="AC11" s="150"/>
+      <c r="AD11" s="150"/>
+      <c r="AE11" s="150"/>
+      <c r="AF11" s="150"/>
+      <c r="AG11" s="150"/>
+      <c r="AH11" s="150"/>
+      <c r="AI11" s="150"/>
+      <c r="AJ11" s="150"/>
+      <c r="AK11" s="150"/>
+      <c r="AL11" s="150"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="149" t="s">
+      <c r="A12" s="150" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="149"/>
-      <c r="C12" s="149"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="149"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="149"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="149"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="149"/>
-      <c r="L12" s="149"/>
-      <c r="M12" s="149"/>
-      <c r="N12" s="149"/>
-      <c r="O12" s="149"/>
-      <c r="P12" s="149"/>
-      <c r="Q12" s="149"/>
-      <c r="R12" s="149"/>
-      <c r="S12" s="149"/>
-      <c r="T12" s="149"/>
-      <c r="U12" s="149"/>
-      <c r="V12" s="149"/>
-      <c r="W12" s="149"/>
-      <c r="X12" s="149"/>
-      <c r="Y12" s="149"/>
-      <c r="Z12" s="149"/>
-      <c r="AA12" s="149"/>
-      <c r="AB12" s="149"/>
-      <c r="AC12" s="149"/>
-      <c r="AD12" s="149"/>
-      <c r="AE12" s="149"/>
-      <c r="AF12" s="149"/>
-      <c r="AG12" s="149"/>
-      <c r="AH12" s="149"/>
-      <c r="AI12" s="149"/>
-      <c r="AJ12" s="149"/>
-      <c r="AK12" s="149"/>
-      <c r="AL12" s="149"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="150"/>
+      <c r="E12" s="150"/>
+      <c r="F12" s="150"/>
+      <c r="G12" s="150"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="150"/>
+      <c r="J12" s="150"/>
+      <c r="K12" s="150"/>
+      <c r="L12" s="150"/>
+      <c r="M12" s="150"/>
+      <c r="N12" s="150"/>
+      <c r="O12" s="150"/>
+      <c r="P12" s="150"/>
+      <c r="Q12" s="150"/>
+      <c r="R12" s="150"/>
+      <c r="S12" s="150"/>
+      <c r="T12" s="150"/>
+      <c r="U12" s="150"/>
+      <c r="V12" s="150"/>
+      <c r="W12" s="150"/>
+      <c r="X12" s="150"/>
+      <c r="Y12" s="150"/>
+      <c r="Z12" s="150"/>
+      <c r="AA12" s="150"/>
+      <c r="AB12" s="150"/>
+      <c r="AC12" s="150"/>
+      <c r="AD12" s="150"/>
+      <c r="AE12" s="150"/>
+      <c r="AF12" s="150"/>
+      <c r="AG12" s="150"/>
+      <c r="AH12" s="150"/>
+      <c r="AI12" s="150"/>
+      <c r="AJ12" s="150"/>
+      <c r="AK12" s="150"/>
+      <c r="AL12" s="150"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="149" t="s">
+      <c r="A13" s="150" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="149"/>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="149"/>
-      <c r="I13" s="149"/>
-      <c r="J13" s="149"/>
-      <c r="K13" s="149"/>
-      <c r="L13" s="149"/>
-      <c r="M13" s="149"/>
-      <c r="N13" s="149"/>
-      <c r="O13" s="149"/>
-      <c r="P13" s="149"/>
-      <c r="Q13" s="149"/>
-      <c r="R13" s="149"/>
-      <c r="S13" s="149"/>
-      <c r="T13" s="149"/>
-      <c r="U13" s="149"/>
-      <c r="V13" s="149"/>
-      <c r="W13" s="149"/>
-      <c r="X13" s="149"/>
-      <c r="Y13" s="149"/>
-      <c r="Z13" s="149"/>
-      <c r="AA13" s="149"/>
-      <c r="AB13" s="149"/>
-      <c r="AC13" s="149"/>
-      <c r="AD13" s="149"/>
-      <c r="AE13" s="149"/>
-      <c r="AF13" s="149"/>
-      <c r="AG13" s="149"/>
-      <c r="AH13" s="149"/>
-      <c r="AI13" s="149"/>
-      <c r="AJ13" s="149"/>
-      <c r="AK13" s="149"/>
-      <c r="AL13" s="149"/>
+      <c r="B13" s="150"/>
+      <c r="C13" s="150"/>
+      <c r="D13" s="150"/>
+      <c r="E13" s="150"/>
+      <c r="F13" s="150"/>
+      <c r="G13" s="150"/>
+      <c r="H13" s="150"/>
+      <c r="I13" s="150"/>
+      <c r="J13" s="150"/>
+      <c r="K13" s="150"/>
+      <c r="L13" s="150"/>
+      <c r="M13" s="150"/>
+      <c r="N13" s="150"/>
+      <c r="O13" s="150"/>
+      <c r="P13" s="150"/>
+      <c r="Q13" s="150"/>
+      <c r="R13" s="150"/>
+      <c r="S13" s="150"/>
+      <c r="T13" s="150"/>
+      <c r="U13" s="150"/>
+      <c r="V13" s="150"/>
+      <c r="W13" s="150"/>
+      <c r="X13" s="150"/>
+      <c r="Y13" s="150"/>
+      <c r="Z13" s="150"/>
+      <c r="AA13" s="150"/>
+      <c r="AB13" s="150"/>
+      <c r="AC13" s="150"/>
+      <c r="AD13" s="150"/>
+      <c r="AE13" s="150"/>
+      <c r="AF13" s="150"/>
+      <c r="AG13" s="150"/>
+      <c r="AH13" s="150"/>
+      <c r="AI13" s="150"/>
+      <c r="AJ13" s="150"/>
+      <c r="AK13" s="150"/>
+      <c r="AL13" s="150"/>
     </row>
     <row r="14" spans="1:38" ht="18" customHeight="1">
-      <c r="A14" s="149" t="s">
+      <c r="A14" s="150" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="149"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="149"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="149"/>
-      <c r="I14" s="149"/>
-      <c r="J14" s="149"/>
-      <c r="K14" s="149"/>
-      <c r="L14" s="149"/>
-      <c r="M14" s="149"/>
-      <c r="N14" s="149"/>
-      <c r="O14" s="149"/>
-      <c r="P14" s="149"/>
-      <c r="Q14" s="149"/>
-      <c r="R14" s="149"/>
-      <c r="S14" s="149"/>
-      <c r="T14" s="149"/>
-      <c r="U14" s="149"/>
-      <c r="V14" s="149"/>
-      <c r="W14" s="149"/>
-      <c r="X14" s="149"/>
-      <c r="Y14" s="149"/>
-      <c r="Z14" s="149"/>
-      <c r="AA14" s="149"/>
-      <c r="AB14" s="149"/>
-      <c r="AC14" s="149"/>
-      <c r="AD14" s="149"/>
-      <c r="AE14" s="149"/>
-      <c r="AF14" s="149"/>
-      <c r="AG14" s="149"/>
-      <c r="AH14" s="149"/>
-      <c r="AI14" s="149"/>
-      <c r="AJ14" s="149"/>
-      <c r="AK14" s="149"/>
-      <c r="AL14" s="149"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="150"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="150"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="150"/>
+      <c r="M14" s="150"/>
+      <c r="N14" s="150"/>
+      <c r="O14" s="150"/>
+      <c r="P14" s="150"/>
+      <c r="Q14" s="150"/>
+      <c r="R14" s="150"/>
+      <c r="S14" s="150"/>
+      <c r="T14" s="150"/>
+      <c r="U14" s="150"/>
+      <c r="V14" s="150"/>
+      <c r="W14" s="150"/>
+      <c r="X14" s="150"/>
+      <c r="Y14" s="150"/>
+      <c r="Z14" s="150"/>
+      <c r="AA14" s="150"/>
+      <c r="AB14" s="150"/>
+      <c r="AC14" s="150"/>
+      <c r="AD14" s="150"/>
+      <c r="AE14" s="150"/>
+      <c r="AF14" s="150"/>
+      <c r="AG14" s="150"/>
+      <c r="AH14" s="150"/>
+      <c r="AI14" s="150"/>
+      <c r="AJ14" s="150"/>
+      <c r="AK14" s="150"/>
+      <c r="AL14" s="150"/>
     </row>
     <row r="15" spans="1:38" ht="18" customHeight="1">
-      <c r="A15" s="149" t="s">
+      <c r="A15" s="150" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="149"/>
-      <c r="C15" s="149"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="149"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="149"/>
-      <c r="L15" s="149"/>
-      <c r="M15" s="149"/>
-      <c r="N15" s="149"/>
-      <c r="O15" s="149"/>
-      <c r="P15" s="149"/>
-      <c r="Q15" s="149"/>
-      <c r="R15" s="149"/>
-      <c r="S15" s="149"/>
-      <c r="T15" s="149"/>
-      <c r="U15" s="149"/>
-      <c r="V15" s="149"/>
-      <c r="W15" s="149"/>
-      <c r="X15" s="149"/>
-      <c r="Y15" s="149"/>
-      <c r="Z15" s="149"/>
-      <c r="AA15" s="149"/>
-      <c r="AB15" s="149"/>
-      <c r="AC15" s="149"/>
-      <c r="AD15" s="149"/>
-      <c r="AE15" s="149"/>
-      <c r="AF15" s="149"/>
-      <c r="AG15" s="149"/>
-      <c r="AH15" s="149"/>
-      <c r="AI15" s="149"/>
-      <c r="AJ15" s="149"/>
-      <c r="AK15" s="149"/>
-      <c r="AL15" s="149"/>
+      <c r="B15" s="150"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="150"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="150"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="150"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="150"/>
+      <c r="M15" s="150"/>
+      <c r="N15" s="150"/>
+      <c r="O15" s="150"/>
+      <c r="P15" s="150"/>
+      <c r="Q15" s="150"/>
+      <c r="R15" s="150"/>
+      <c r="S15" s="150"/>
+      <c r="T15" s="150"/>
+      <c r="U15" s="150"/>
+      <c r="V15" s="150"/>
+      <c r="W15" s="150"/>
+      <c r="X15" s="150"/>
+      <c r="Y15" s="150"/>
+      <c r="Z15" s="150"/>
+      <c r="AA15" s="150"/>
+      <c r="AB15" s="150"/>
+      <c r="AC15" s="150"/>
+      <c r="AD15" s="150"/>
+      <c r="AE15" s="150"/>
+      <c r="AF15" s="150"/>
+      <c r="AG15" s="150"/>
+      <c r="AH15" s="150"/>
+      <c r="AI15" s="150"/>
+      <c r="AJ15" s="150"/>
+      <c r="AK15" s="150"/>
+      <c r="AL15" s="150"/>
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
-      <c r="A16" s="149" t="s">
+      <c r="A16" s="150" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="149"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="149"/>
-      <c r="H16" s="149"/>
-      <c r="I16" s="149"/>
-      <c r="J16" s="149"/>
-      <c r="K16" s="149"/>
-      <c r="L16" s="149"/>
-      <c r="M16" s="149"/>
-      <c r="N16" s="149"/>
-      <c r="O16" s="149"/>
-      <c r="P16" s="149"/>
-      <c r="Q16" s="149"/>
-      <c r="R16" s="149"/>
-      <c r="S16" s="149"/>
-      <c r="T16" s="149"/>
-      <c r="U16" s="149"/>
-      <c r="V16" s="149"/>
-      <c r="W16" s="149"/>
-      <c r="X16" s="149"/>
-      <c r="Y16" s="149"/>
-      <c r="Z16" s="149"/>
-      <c r="AA16" s="149"/>
-      <c r="AB16" s="149"/>
-      <c r="AC16" s="149"/>
-      <c r="AD16" s="149"/>
-      <c r="AE16" s="149"/>
-      <c r="AF16" s="149"/>
-      <c r="AG16" s="149"/>
-      <c r="AH16" s="149"/>
-      <c r="AI16" s="149"/>
-      <c r="AJ16" s="149"/>
-      <c r="AK16" s="149"/>
-      <c r="AL16" s="149"/>
+      <c r="B16" s="150"/>
+      <c r="C16" s="150"/>
+      <c r="D16" s="150"/>
+      <c r="E16" s="150"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="150"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="150"/>
+      <c r="M16" s="150"/>
+      <c r="N16" s="150"/>
+      <c r="O16" s="150"/>
+      <c r="P16" s="150"/>
+      <c r="Q16" s="150"/>
+      <c r="R16" s="150"/>
+      <c r="S16" s="150"/>
+      <c r="T16" s="150"/>
+      <c r="U16" s="150"/>
+      <c r="V16" s="150"/>
+      <c r="W16" s="150"/>
+      <c r="X16" s="150"/>
+      <c r="Y16" s="150"/>
+      <c r="Z16" s="150"/>
+      <c r="AA16" s="150"/>
+      <c r="AB16" s="150"/>
+      <c r="AC16" s="150"/>
+      <c r="AD16" s="150"/>
+      <c r="AE16" s="150"/>
+      <c r="AF16" s="150"/>
+      <c r="AG16" s="150"/>
+      <c r="AH16" s="150"/>
+      <c r="AI16" s="150"/>
+      <c r="AJ16" s="150"/>
+      <c r="AK16" s="150"/>
+      <c r="AL16" s="150"/>
     </row>
     <row r="17" spans="1:38" ht="18" customHeight="1">
-      <c r="A17" s="149" t="s">
+      <c r="A17" s="150" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="149"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="149"/>
-      <c r="I17" s="149"/>
-      <c r="J17" s="149"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="149"/>
-      <c r="M17" s="149"/>
-      <c r="N17" s="149"/>
-      <c r="O17" s="149"/>
-      <c r="P17" s="149"/>
-      <c r="Q17" s="149"/>
-      <c r="R17" s="149"/>
-      <c r="S17" s="149"/>
-      <c r="T17" s="149"/>
-      <c r="U17" s="149"/>
-      <c r="V17" s="149"/>
-      <c r="W17" s="149"/>
-      <c r="X17" s="149"/>
-      <c r="Y17" s="149"/>
-      <c r="Z17" s="149"/>
-      <c r="AA17" s="149"/>
-      <c r="AB17" s="149"/>
-      <c r="AC17" s="149"/>
-      <c r="AD17" s="149"/>
-      <c r="AE17" s="149"/>
-      <c r="AF17" s="149"/>
-      <c r="AG17" s="149"/>
-      <c r="AH17" s="149"/>
-      <c r="AI17" s="149"/>
-      <c r="AJ17" s="149"/>
-      <c r="AK17" s="149"/>
-      <c r="AL17" s="149"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="150"/>
+      <c r="E17" s="150"/>
+      <c r="F17" s="150"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="150"/>
+      <c r="J17" s="150"/>
+      <c r="K17" s="150"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="150"/>
+      <c r="N17" s="150"/>
+      <c r="O17" s="150"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="150"/>
+      <c r="R17" s="150"/>
+      <c r="S17" s="150"/>
+      <c r="T17" s="150"/>
+      <c r="U17" s="150"/>
+      <c r="V17" s="150"/>
+      <c r="W17" s="150"/>
+      <c r="X17" s="150"/>
+      <c r="Y17" s="150"/>
+      <c r="Z17" s="150"/>
+      <c r="AA17" s="150"/>
+      <c r="AB17" s="150"/>
+      <c r="AC17" s="150"/>
+      <c r="AD17" s="150"/>
+      <c r="AE17" s="150"/>
+      <c r="AF17" s="150"/>
+      <c r="AG17" s="150"/>
+      <c r="AH17" s="150"/>
+      <c r="AI17" s="150"/>
+      <c r="AJ17" s="150"/>
+      <c r="AK17" s="150"/>
+      <c r="AL17" s="150"/>
     </row>
     <row r="18" spans="1:38" ht="18" customHeight="1">
-      <c r="A18" s="149" t="s">
+      <c r="A18" s="150" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="149"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="149"/>
-      <c r="I18" s="149"/>
-      <c r="J18" s="149"/>
-      <c r="K18" s="149"/>
-      <c r="L18" s="149"/>
-      <c r="M18" s="149"/>
-      <c r="N18" s="149"/>
-      <c r="O18" s="149"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-      <c r="R18" s="149"/>
-      <c r="S18" s="149"/>
-      <c r="T18" s="149"/>
-      <c r="U18" s="149"/>
-      <c r="V18" s="149"/>
-      <c r="W18" s="149"/>
-      <c r="X18" s="149"/>
-      <c r="Y18" s="149"/>
-      <c r="Z18" s="149"/>
-      <c r="AA18" s="149"/>
-      <c r="AB18" s="149"/>
-      <c r="AC18" s="149"/>
-      <c r="AD18" s="149"/>
-      <c r="AE18" s="149"/>
-      <c r="AF18" s="149"/>
-      <c r="AG18" s="149"/>
-      <c r="AH18" s="149"/>
-      <c r="AI18" s="149"/>
-      <c r="AJ18" s="149"/>
-      <c r="AK18" s="149"/>
-      <c r="AL18" s="149"/>
+      <c r="B18" s="150"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="150"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="150"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="150"/>
+      <c r="K18" s="150"/>
+      <c r="L18" s="150"/>
+      <c r="M18" s="150"/>
+      <c r="N18" s="150"/>
+      <c r="O18" s="150"/>
+      <c r="P18" s="150"/>
+      <c r="Q18" s="150"/>
+      <c r="R18" s="150"/>
+      <c r="S18" s="150"/>
+      <c r="T18" s="150"/>
+      <c r="U18" s="150"/>
+      <c r="V18" s="150"/>
+      <c r="W18" s="150"/>
+      <c r="X18" s="150"/>
+      <c r="Y18" s="150"/>
+      <c r="Z18" s="150"/>
+      <c r="AA18" s="150"/>
+      <c r="AB18" s="150"/>
+      <c r="AC18" s="150"/>
+      <c r="AD18" s="150"/>
+      <c r="AE18" s="150"/>
+      <c r="AF18" s="150"/>
+      <c r="AG18" s="150"/>
+      <c r="AH18" s="150"/>
+      <c r="AI18" s="150"/>
+      <c r="AJ18" s="150"/>
+      <c r="AK18" s="150"/>
+      <c r="AL18" s="150"/>
     </row>
     <row r="19" spans="1:38" ht="18" customHeight="1">
-      <c r="A19" s="149" t="s">
+      <c r="A19" s="150" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="149"/>
-      <c r="C19" s="149"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
-      <c r="I19" s="149"/>
-      <c r="J19" s="149"/>
-      <c r="K19" s="149"/>
-      <c r="L19" s="149"/>
-      <c r="M19" s="149"/>
-      <c r="N19" s="149"/>
-      <c r="O19" s="149"/>
-      <c r="P19" s="149"/>
-      <c r="Q19" s="149"/>
-      <c r="R19" s="149"/>
-      <c r="S19" s="149"/>
-      <c r="T19" s="149"/>
-      <c r="U19" s="149"/>
-      <c r="V19" s="149"/>
-      <c r="W19" s="149"/>
-      <c r="X19" s="149"/>
-      <c r="Y19" s="149"/>
-      <c r="Z19" s="149"/>
-      <c r="AA19" s="149"/>
-      <c r="AB19" s="149"/>
-      <c r="AC19" s="149"/>
-      <c r="AD19" s="149"/>
-      <c r="AE19" s="149"/>
-      <c r="AF19" s="149"/>
-      <c r="AG19" s="149"/>
-      <c r="AH19" s="149"/>
-      <c r="AI19" s="149"/>
-      <c r="AJ19" s="149"/>
-      <c r="AK19" s="149"/>
-      <c r="AL19" s="149"/>
+      <c r="B19" s="150"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="150"/>
+      <c r="I19" s="150"/>
+      <c r="J19" s="150"/>
+      <c r="K19" s="150"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="150"/>
+      <c r="N19" s="150"/>
+      <c r="O19" s="150"/>
+      <c r="P19" s="150"/>
+      <c r="Q19" s="150"/>
+      <c r="R19" s="150"/>
+      <c r="S19" s="150"/>
+      <c r="T19" s="150"/>
+      <c r="U19" s="150"/>
+      <c r="V19" s="150"/>
+      <c r="W19" s="150"/>
+      <c r="X19" s="150"/>
+      <c r="Y19" s="150"/>
+      <c r="Z19" s="150"/>
+      <c r="AA19" s="150"/>
+      <c r="AB19" s="150"/>
+      <c r="AC19" s="150"/>
+      <c r="AD19" s="150"/>
+      <c r="AE19" s="150"/>
+      <c r="AF19" s="150"/>
+      <c r="AG19" s="150"/>
+      <c r="AH19" s="150"/>
+      <c r="AI19" s="150"/>
+      <c r="AJ19" s="150"/>
+      <c r="AK19" s="150"/>
+      <c r="AL19" s="150"/>
     </row>
     <row r="20" spans="1:38" ht="18" customHeight="1">
-      <c r="A20" s="149" t="s">
+      <c r="A20" s="150" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="149"/>
-      <c r="C20" s="149"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="149"/>
-      <c r="I20" s="149"/>
-      <c r="J20" s="149"/>
-      <c r="K20" s="149"/>
-      <c r="L20" s="149"/>
-      <c r="M20" s="149"/>
-      <c r="N20" s="149"/>
-      <c r="O20" s="149"/>
-      <c r="P20" s="149"/>
-      <c r="Q20" s="149"/>
-      <c r="R20" s="149"/>
-      <c r="S20" s="149"/>
-      <c r="T20" s="149"/>
-      <c r="U20" s="149"/>
-      <c r="V20" s="149"/>
-      <c r="W20" s="149"/>
-      <c r="X20" s="149"/>
-      <c r="Y20" s="149"/>
-      <c r="Z20" s="149"/>
-      <c r="AA20" s="149"/>
-      <c r="AB20" s="149"/>
-      <c r="AC20" s="149"/>
-      <c r="AD20" s="149"/>
-      <c r="AE20" s="149"/>
-      <c r="AF20" s="149"/>
-      <c r="AG20" s="149"/>
-      <c r="AH20" s="149"/>
-      <c r="AI20" s="149"/>
-      <c r="AJ20" s="149"/>
-      <c r="AK20" s="149"/>
-      <c r="AL20" s="149"/>
+      <c r="B20" s="150"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="150"/>
+      <c r="J20" s="150"/>
+      <c r="K20" s="150"/>
+      <c r="L20" s="150"/>
+      <c r="M20" s="150"/>
+      <c r="N20" s="150"/>
+      <c r="O20" s="150"/>
+      <c r="P20" s="150"/>
+      <c r="Q20" s="150"/>
+      <c r="R20" s="150"/>
+      <c r="S20" s="150"/>
+      <c r="T20" s="150"/>
+      <c r="U20" s="150"/>
+      <c r="V20" s="150"/>
+      <c r="W20" s="150"/>
+      <c r="X20" s="150"/>
+      <c r="Y20" s="150"/>
+      <c r="Z20" s="150"/>
+      <c r="AA20" s="150"/>
+      <c r="AB20" s="150"/>
+      <c r="AC20" s="150"/>
+      <c r="AD20" s="150"/>
+      <c r="AE20" s="150"/>
+      <c r="AF20" s="150"/>
+      <c r="AG20" s="150"/>
+      <c r="AH20" s="150"/>
+      <c r="AI20" s="150"/>
+      <c r="AJ20" s="150"/>
+      <c r="AK20" s="150"/>
+      <c r="AL20" s="150"/>
     </row>
     <row r="21" spans="1:38" ht="18" customHeight="1">
-      <c r="A21" s="149" t="s">
+      <c r="A21" s="150" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="149"/>
-      <c r="C21" s="149"/>
-      <c r="D21" s="149"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="149"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="149"/>
-      <c r="I21" s="149"/>
-      <c r="J21" s="149"/>
-      <c r="K21" s="149"/>
-      <c r="L21" s="149"/>
-      <c r="M21" s="149"/>
-      <c r="N21" s="149"/>
-      <c r="O21" s="149"/>
-      <c r="P21" s="149"/>
-      <c r="Q21" s="149"/>
-      <c r="R21" s="149"/>
-      <c r="S21" s="149"/>
-      <c r="T21" s="149"/>
-      <c r="U21" s="149"/>
-      <c r="V21" s="149"/>
-      <c r="W21" s="149"/>
-      <c r="X21" s="149"/>
-      <c r="Y21" s="149"/>
-      <c r="Z21" s="149"/>
-      <c r="AA21" s="149"/>
-      <c r="AB21" s="149"/>
-      <c r="AC21" s="149"/>
-      <c r="AD21" s="149"/>
-      <c r="AE21" s="149"/>
-      <c r="AF21" s="149"/>
-      <c r="AG21" s="149"/>
-      <c r="AH21" s="149"/>
-      <c r="AI21" s="149"/>
-      <c r="AJ21" s="149"/>
-      <c r="AK21" s="149"/>
-      <c r="AL21" s="149"/>
+      <c r="B21" s="150"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="150"/>
+      <c r="G21" s="150"/>
+      <c r="H21" s="150"/>
+      <c r="I21" s="150"/>
+      <c r="J21" s="150"/>
+      <c r="K21" s="150"/>
+      <c r="L21" s="150"/>
+      <c r="M21" s="150"/>
+      <c r="N21" s="150"/>
+      <c r="O21" s="150"/>
+      <c r="P21" s="150"/>
+      <c r="Q21" s="150"/>
+      <c r="R21" s="150"/>
+      <c r="S21" s="150"/>
+      <c r="T21" s="150"/>
+      <c r="U21" s="150"/>
+      <c r="V21" s="150"/>
+      <c r="W21" s="150"/>
+      <c r="X21" s="150"/>
+      <c r="Y21" s="150"/>
+      <c r="Z21" s="150"/>
+      <c r="AA21" s="150"/>
+      <c r="AB21" s="150"/>
+      <c r="AC21" s="150"/>
+      <c r="AD21" s="150"/>
+      <c r="AE21" s="150"/>
+      <c r="AF21" s="150"/>
+      <c r="AG21" s="150"/>
+      <c r="AH21" s="150"/>
+      <c r="AI21" s="150"/>
+      <c r="AJ21" s="150"/>
+      <c r="AK21" s="150"/>
+      <c r="AL21" s="150"/>
     </row>
     <row r="22" spans="1:38" ht="18" customHeight="1">
-      <c r="A22" s="149" t="s">
+      <c r="A22" s="150" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="149"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="149"/>
-      <c r="I22" s="149"/>
-      <c r="J22" s="149"/>
-      <c r="K22" s="149"/>
-      <c r="L22" s="149"/>
-      <c r="M22" s="149"/>
-      <c r="N22" s="149"/>
-      <c r="O22" s="149"/>
-      <c r="P22" s="149"/>
-      <c r="Q22" s="149"/>
-      <c r="R22" s="149"/>
-      <c r="S22" s="149"/>
-      <c r="T22" s="149"/>
-      <c r="U22" s="149"/>
-      <c r="V22" s="149"/>
-      <c r="W22" s="149"/>
-      <c r="X22" s="149"/>
-      <c r="Y22" s="149"/>
-      <c r="Z22" s="149"/>
-      <c r="AA22" s="149"/>
-      <c r="AB22" s="149"/>
-      <c r="AC22" s="149"/>
-      <c r="AD22" s="149"/>
-      <c r="AE22" s="149"/>
-      <c r="AF22" s="149"/>
-      <c r="AG22" s="149"/>
-      <c r="AH22" s="149"/>
-      <c r="AI22" s="149"/>
-      <c r="AJ22" s="149"/>
-      <c r="AK22" s="149"/>
-      <c r="AL22" s="149"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="150"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="150"/>
+      <c r="G22" s="150"/>
+      <c r="H22" s="150"/>
+      <c r="I22" s="150"/>
+      <c r="J22" s="150"/>
+      <c r="K22" s="150"/>
+      <c r="L22" s="150"/>
+      <c r="M22" s="150"/>
+      <c r="N22" s="150"/>
+      <c r="O22" s="150"/>
+      <c r="P22" s="150"/>
+      <c r="Q22" s="150"/>
+      <c r="R22" s="150"/>
+      <c r="S22" s="150"/>
+      <c r="T22" s="150"/>
+      <c r="U22" s="150"/>
+      <c r="V22" s="150"/>
+      <c r="W22" s="150"/>
+      <c r="X22" s="150"/>
+      <c r="Y22" s="150"/>
+      <c r="Z22" s="150"/>
+      <c r="AA22" s="150"/>
+      <c r="AB22" s="150"/>
+      <c r="AC22" s="150"/>
+      <c r="AD22" s="150"/>
+      <c r="AE22" s="150"/>
+      <c r="AF22" s="150"/>
+      <c r="AG22" s="150"/>
+      <c r="AH22" s="150"/>
+      <c r="AI22" s="150"/>
+      <c r="AJ22" s="150"/>
+      <c r="AK22" s="150"/>
+      <c r="AL22" s="150"/>
     </row>
     <row r="23" spans="1:38" ht="14.4">
       <c r="A23" s="6" t="s">
@@ -12821,146 +12833,146 @@
       </c>
     </row>
     <row r="24" spans="1:38">
-      <c r="A24" s="144" t="s">
+      <c r="A24" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="144"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="158" t="s">
+      <c r="B24" s="139"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="139"/>
+      <c r="I24" s="149" t="s">
         <v>149</v>
       </c>
-      <c r="J24" s="158"/>
-      <c r="K24" s="158"/>
-      <c r="L24" s="158"/>
-      <c r="M24" s="158"/>
-      <c r="N24" s="158"/>
-      <c r="O24" s="144" t="s">
+      <c r="J24" s="149"/>
+      <c r="K24" s="149"/>
+      <c r="L24" s="149"/>
+      <c r="M24" s="149"/>
+      <c r="N24" s="149"/>
+      <c r="O24" s="139" t="s">
         <v>150</v>
       </c>
-      <c r="P24" s="144"/>
-      <c r="Q24" s="144"/>
-      <c r="R24" s="144"/>
-      <c r="S24" s="144"/>
-      <c r="T24" s="144"/>
-      <c r="U24" s="144"/>
-      <c r="V24" s="144"/>
-      <c r="W24" s="144"/>
-      <c r="X24" s="144"/>
-      <c r="Y24" s="144"/>
-      <c r="Z24" s="144"/>
-      <c r="AA24" s="144"/>
-      <c r="AB24" s="144"/>
-      <c r="AC24" s="144" t="s">
+      <c r="P24" s="139"/>
+      <c r="Q24" s="139"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139"/>
+      <c r="T24" s="139"/>
+      <c r="U24" s="139"/>
+      <c r="V24" s="139"/>
+      <c r="W24" s="139"/>
+      <c r="X24" s="139"/>
+      <c r="Y24" s="139"/>
+      <c r="Z24" s="139"/>
+      <c r="AA24" s="139"/>
+      <c r="AB24" s="139"/>
+      <c r="AC24" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="AD24" s="144"/>
-      <c r="AE24" s="144"/>
-      <c r="AF24" s="144"/>
-      <c r="AG24" s="144"/>
-      <c r="AH24" s="144"/>
-      <c r="AI24" s="144"/>
-      <c r="AJ24" s="144"/>
-      <c r="AK24" s="144"/>
-      <c r="AL24" s="144"/>
+      <c r="AD24" s="139"/>
+      <c r="AE24" s="139"/>
+      <c r="AF24" s="139"/>
+      <c r="AG24" s="139"/>
+      <c r="AH24" s="139"/>
+      <c r="AI24" s="139"/>
+      <c r="AJ24" s="139"/>
+      <c r="AK24" s="139"/>
+      <c r="AL24" s="139"/>
     </row>
     <row r="25" spans="1:38">
-      <c r="A25" s="144" t="s">
+      <c r="A25" s="139" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="144"/>
-      <c r="C25" s="144"/>
-      <c r="D25" s="144"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="144"/>
-      <c r="I25" s="144">
+      <c r="B25" s="139"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139">
         <v>20</v>
       </c>
-      <c r="J25" s="144"/>
-      <c r="K25" s="144"/>
-      <c r="L25" s="144"/>
-      <c r="M25" s="144"/>
-      <c r="N25" s="144"/>
-      <c r="O25" s="155" t="s">
+      <c r="J25" s="139"/>
+      <c r="K25" s="139"/>
+      <c r="L25" s="139"/>
+      <c r="M25" s="139"/>
+      <c r="N25" s="139"/>
+      <c r="O25" s="146" t="s">
         <v>152</v>
       </c>
-      <c r="P25" s="156"/>
-      <c r="Q25" s="156"/>
-      <c r="R25" s="156"/>
-      <c r="S25" s="156"/>
-      <c r="T25" s="156"/>
-      <c r="U25" s="156"/>
-      <c r="V25" s="156"/>
-      <c r="W25" s="156"/>
-      <c r="X25" s="156"/>
-      <c r="Y25" s="157"/>
-      <c r="Z25" s="155">
+      <c r="P25" s="147"/>
+      <c r="Q25" s="147"/>
+      <c r="R25" s="147"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="147"/>
+      <c r="U25" s="147"/>
+      <c r="V25" s="147"/>
+      <c r="W25" s="147"/>
+      <c r="X25" s="147"/>
+      <c r="Y25" s="148"/>
+      <c r="Z25" s="146">
         <v>100</v>
       </c>
-      <c r="AA25" s="156"/>
-      <c r="AB25" s="157"/>
-      <c r="AC25" s="144" t="s">
+      <c r="AA25" s="147"/>
+      <c r="AB25" s="148"/>
+      <c r="AC25" s="139" t="s">
         <v>154</v>
       </c>
-      <c r="AD25" s="144"/>
-      <c r="AE25" s="144"/>
-      <c r="AF25" s="144"/>
-      <c r="AG25" s="144"/>
-      <c r="AH25" s="144"/>
-      <c r="AI25" s="144"/>
-      <c r="AJ25" s="144"/>
-      <c r="AK25" s="144"/>
-      <c r="AL25" s="144"/>
+      <c r="AD25" s="139"/>
+      <c r="AE25" s="139"/>
+      <c r="AF25" s="139"/>
+      <c r="AG25" s="139"/>
+      <c r="AH25" s="139"/>
+      <c r="AI25" s="139"/>
+      <c r="AJ25" s="139"/>
+      <c r="AK25" s="139"/>
+      <c r="AL25" s="139"/>
     </row>
     <row r="26" spans="1:38">
-      <c r="A26" s="144"/>
-      <c r="B26" s="144"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="144"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="144"/>
-      <c r="L26" s="144"/>
-      <c r="M26" s="144"/>
-      <c r="N26" s="144"/>
-      <c r="O26" s="155" t="s">
+      <c r="A26" s="139"/>
+      <c r="B26" s="139"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
+      <c r="L26" s="139"/>
+      <c r="M26" s="139"/>
+      <c r="N26" s="139"/>
+      <c r="O26" s="146" t="s">
         <v>153</v>
       </c>
-      <c r="P26" s="156"/>
-      <c r="Q26" s="156"/>
-      <c r="R26" s="156"/>
-      <c r="S26" s="156"/>
-      <c r="T26" s="156"/>
-      <c r="U26" s="156"/>
-      <c r="V26" s="156"/>
-      <c r="W26" s="156"/>
-      <c r="X26" s="156"/>
-      <c r="Y26" s="157"/>
-      <c r="Z26" s="155">
+      <c r="P26" s="147"/>
+      <c r="Q26" s="147"/>
+      <c r="R26" s="147"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="147"/>
+      <c r="U26" s="147"/>
+      <c r="V26" s="147"/>
+      <c r="W26" s="147"/>
+      <c r="X26" s="147"/>
+      <c r="Y26" s="148"/>
+      <c r="Z26" s="146">
         <v>200</v>
       </c>
-      <c r="AA26" s="156"/>
-      <c r="AB26" s="157"/>
-      <c r="AC26" s="144"/>
-      <c r="AD26" s="144"/>
-      <c r="AE26" s="144"/>
-      <c r="AF26" s="144"/>
-      <c r="AG26" s="144"/>
-      <c r="AH26" s="144"/>
-      <c r="AI26" s="144"/>
-      <c r="AJ26" s="144"/>
-      <c r="AK26" s="144"/>
-      <c r="AL26" s="144"/>
+      <c r="AA26" s="147"/>
+      <c r="AB26" s="148"/>
+      <c r="AC26" s="139"/>
+      <c r="AD26" s="139"/>
+      <c r="AE26" s="139"/>
+      <c r="AF26" s="139"/>
+      <c r="AG26" s="139"/>
+      <c r="AH26" s="139"/>
+      <c r="AI26" s="139"/>
+      <c r="AJ26" s="139"/>
+      <c r="AK26" s="139"/>
+      <c r="AL26" s="139"/>
     </row>
     <row r="27" spans="1:38">
       <c r="A27" s="6" t="s">
@@ -12969,77 +12981,14 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="AC24:AL24"/>
-    <mergeCell ref="A25:H26"/>
-    <mergeCell ref="I25:N26"/>
-    <mergeCell ref="AC25:AL26"/>
-    <mergeCell ref="Z25:AB25"/>
-    <mergeCell ref="Z26:AB26"/>
-    <mergeCell ref="O25:Y25"/>
-    <mergeCell ref="O26:Y26"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="O24:AB24"/>
-    <mergeCell ref="AG22:AL22"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="I21:N21"/>
-    <mergeCell ref="O21:T21"/>
-    <mergeCell ref="U21:Z21"/>
-    <mergeCell ref="AA21:AF21"/>
-    <mergeCell ref="AG21:AL21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="I22:N22"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="U22:Z22"/>
-    <mergeCell ref="AA22:AF22"/>
-    <mergeCell ref="AG20:AL20"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="U19:Z19"/>
-    <mergeCell ref="AA19:AF19"/>
-    <mergeCell ref="AG19:AL19"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="I20:N20"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="U20:Z20"/>
-    <mergeCell ref="AA20:AF20"/>
-    <mergeCell ref="AG18:AL18"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="U17:Z17"/>
-    <mergeCell ref="AA17:AF17"/>
-    <mergeCell ref="AG17:AL17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="U18:Z18"/>
-    <mergeCell ref="AA18:AF18"/>
-    <mergeCell ref="AG16:AL16"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:T15"/>
-    <mergeCell ref="U15:Z15"/>
-    <mergeCell ref="AA15:AF15"/>
-    <mergeCell ref="AG15:AL15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="AA16:AF16"/>
-    <mergeCell ref="AG13:AL13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="U14:Z14"/>
-    <mergeCell ref="AA14:AF14"/>
-    <mergeCell ref="AG14:AL14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="U13:Z13"/>
-    <mergeCell ref="AA13:AF13"/>
+    <mergeCell ref="U10:Z10"/>
+    <mergeCell ref="AA10:AF10"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="F5:K5"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="AG10:AL10"/>
     <mergeCell ref="AG12:AL12"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="I11:N11"/>
@@ -13056,14 +13005,77 @@
     <mergeCell ref="U12:Z12"/>
     <mergeCell ref="AA12:AF12"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="U10:Z10"/>
-    <mergeCell ref="AA10:AF10"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="I7:O7"/>
-    <mergeCell ref="AG10:AL10"/>
+    <mergeCell ref="AG13:AL13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="U14:Z14"/>
+    <mergeCell ref="AA14:AF14"/>
+    <mergeCell ref="AG14:AL14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="U13:Z13"/>
+    <mergeCell ref="AA13:AF13"/>
+    <mergeCell ref="AG16:AL16"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:T15"/>
+    <mergeCell ref="U15:Z15"/>
+    <mergeCell ref="AA15:AF15"/>
+    <mergeCell ref="AG15:AL15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="AA16:AF16"/>
+    <mergeCell ref="AG18:AL18"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="U17:Z17"/>
+    <mergeCell ref="AA17:AF17"/>
+    <mergeCell ref="AG17:AL17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="AA18:AF18"/>
+    <mergeCell ref="AG20:AL20"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="U19:Z19"/>
+    <mergeCell ref="AA19:AF19"/>
+    <mergeCell ref="AG19:AL19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="I20:N20"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="U20:Z20"/>
+    <mergeCell ref="AA20:AF20"/>
+    <mergeCell ref="AG22:AL22"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="I21:N21"/>
+    <mergeCell ref="O21:T21"/>
+    <mergeCell ref="U21:Z21"/>
+    <mergeCell ref="AA21:AF21"/>
+    <mergeCell ref="AG21:AL21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="I22:N22"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="U22:Z22"/>
+    <mergeCell ref="AA22:AF22"/>
+    <mergeCell ref="AC24:AL24"/>
+    <mergeCell ref="A25:H26"/>
+    <mergeCell ref="I25:N26"/>
+    <mergeCell ref="AC25:AL26"/>
+    <mergeCell ref="Z25:AB25"/>
+    <mergeCell ref="Z26:AB26"/>
+    <mergeCell ref="O25:Y25"/>
+    <mergeCell ref="O26:Y26"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="O24:AB24"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13104,32 +13116,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="135"/>
-      <c r="Z1" s="135"/>
-      <c r="AA1" s="135"/>
-      <c r="AB1" s="135"/>
-      <c r="AC1" s="135"/>
-      <c r="AD1" s="135"/>
-      <c r="AE1" s="135"/>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="135"/>
-      <c r="AI1" s="135"/>
-      <c r="AJ1" s="135"/>
-      <c r="AK1" s="135"/>
-      <c r="AL1" s="135"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="144"/>
+      <c r="Z1" s="144"/>
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="144"/>
+      <c r="AF1" s="144"/>
+      <c r="AG1" s="144"/>
+      <c r="AH1" s="144"/>
+      <c r="AI1" s="144"/>
+      <c r="AJ1" s="144"/>
+      <c r="AK1" s="144"/>
+      <c r="AL1" s="144"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="33" t="s">
@@ -13171,17 +13183,17 @@
       <c r="AL2" s="34"/>
     </row>
     <row r="3" spans="1:38">
-      <c r="A3" s="136"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -13338,9 +13350,9 @@
       <c r="A7" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="135"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="135"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
       <c r="H7" s="63" t="s">
         <v>113</v>
       </c>
@@ -13371,270 +13383,270 @@
       <c r="AL7" s="34"/>
     </row>
     <row r="8" spans="1:38">
-      <c r="A8" s="168" t="s">
+      <c r="A8" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="168"/>
-      <c r="C8" s="168"/>
-      <c r="D8" s="168"/>
-      <c r="E8" s="168"/>
-      <c r="F8" s="168" t="s">
+      <c r="B8" s="174"/>
+      <c r="C8" s="174"/>
+      <c r="D8" s="174"/>
+      <c r="E8" s="174"/>
+      <c r="F8" s="174" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="168"/>
-      <c r="H8" s="168"/>
-      <c r="I8" s="168"/>
-      <c r="J8" s="168" t="s">
+      <c r="G8" s="174"/>
+      <c r="H8" s="174"/>
+      <c r="I8" s="174"/>
+      <c r="J8" s="174" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="168"/>
-      <c r="L8" s="168"/>
-      <c r="M8" s="168"/>
-      <c r="N8" s="168"/>
-      <c r="O8" s="168"/>
-      <c r="P8" s="168"/>
-      <c r="Q8" s="168"/>
-      <c r="R8" s="168"/>
-      <c r="S8" s="168"/>
-      <c r="T8" s="168"/>
-      <c r="U8" s="168"/>
-      <c r="V8" s="168"/>
-      <c r="W8" s="168"/>
-      <c r="X8" s="168"/>
-      <c r="Y8" s="168"/>
-      <c r="Z8" s="168"/>
-      <c r="AA8" s="168"/>
-      <c r="AB8" s="168"/>
-      <c r="AC8" s="168"/>
-      <c r="AD8" s="168"/>
-      <c r="AE8" s="168"/>
-      <c r="AF8" s="168"/>
-      <c r="AG8" s="168"/>
-      <c r="AH8" s="168"/>
-      <c r="AI8" s="169" t="s">
+      <c r="K8" s="174"/>
+      <c r="L8" s="174"/>
+      <c r="M8" s="174"/>
+      <c r="N8" s="174"/>
+      <c r="O8" s="174"/>
+      <c r="P8" s="174"/>
+      <c r="Q8" s="174"/>
+      <c r="R8" s="174"/>
+      <c r="S8" s="174"/>
+      <c r="T8" s="174"/>
+      <c r="U8" s="174"/>
+      <c r="V8" s="174"/>
+      <c r="W8" s="174"/>
+      <c r="X8" s="174"/>
+      <c r="Y8" s="174"/>
+      <c r="Z8" s="174"/>
+      <c r="AA8" s="174"/>
+      <c r="AB8" s="174"/>
+      <c r="AC8" s="174"/>
+      <c r="AD8" s="174"/>
+      <c r="AE8" s="174"/>
+      <c r="AF8" s="174"/>
+      <c r="AG8" s="174"/>
+      <c r="AH8" s="174"/>
+      <c r="AI8" s="168" t="s">
         <v>116</v>
       </c>
-      <c r="AJ8" s="170"/>
-      <c r="AK8" s="170"/>
-      <c r="AL8" s="171"/>
+      <c r="AJ8" s="169"/>
+      <c r="AK8" s="169"/>
+      <c r="AL8" s="170"/>
     </row>
     <row r="9" spans="1:38">
-      <c r="A9" s="168"/>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="168"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="168"/>
-      <c r="H9" s="168"/>
-      <c r="I9" s="168"/>
-      <c r="J9" s="168" t="s">
+      <c r="A9" s="174"/>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="174"/>
+      <c r="E9" s="174"/>
+      <c r="F9" s="174"/>
+      <c r="G9" s="174"/>
+      <c r="H9" s="174"/>
+      <c r="I9" s="174"/>
+      <c r="J9" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="168"/>
-      <c r="L9" s="168"/>
-      <c r="M9" s="168"/>
-      <c r="N9" s="168"/>
-      <c r="O9" s="168" t="s">
+      <c r="K9" s="174"/>
+      <c r="L9" s="174"/>
+      <c r="M9" s="174"/>
+      <c r="N9" s="174"/>
+      <c r="O9" s="174" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="168"/>
-      <c r="Q9" s="168"/>
-      <c r="R9" s="168"/>
-      <c r="S9" s="168"/>
-      <c r="T9" s="168" t="s">
+      <c r="P9" s="174"/>
+      <c r="Q9" s="174"/>
+      <c r="R9" s="174"/>
+      <c r="S9" s="174"/>
+      <c r="T9" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="168"/>
-      <c r="V9" s="168"/>
-      <c r="W9" s="168"/>
-      <c r="X9" s="168"/>
-      <c r="Y9" s="168" t="s">
+      <c r="U9" s="174"/>
+      <c r="V9" s="174"/>
+      <c r="W9" s="174"/>
+      <c r="X9" s="174"/>
+      <c r="Y9" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="Z9" s="168"/>
-      <c r="AA9" s="168"/>
-      <c r="AB9" s="168"/>
-      <c r="AC9" s="168"/>
-      <c r="AD9" s="168" t="s">
+      <c r="Z9" s="174"/>
+      <c r="AA9" s="174"/>
+      <c r="AB9" s="174"/>
+      <c r="AC9" s="174"/>
+      <c r="AD9" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="AE9" s="168"/>
-      <c r="AF9" s="168"/>
-      <c r="AG9" s="168"/>
-      <c r="AH9" s="168"/>
-      <c r="AI9" s="172"/>
-      <c r="AJ9" s="173"/>
-      <c r="AK9" s="173"/>
-      <c r="AL9" s="174"/>
+      <c r="AE9" s="174"/>
+      <c r="AF9" s="174"/>
+      <c r="AG9" s="174"/>
+      <c r="AH9" s="174"/>
+      <c r="AI9" s="171"/>
+      <c r="AJ9" s="172"/>
+      <c r="AK9" s="172"/>
+      <c r="AL9" s="173"/>
     </row>
     <row r="10" spans="1:38">
-      <c r="A10" s="162"/>
-      <c r="B10" s="163"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="163"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="160" t="s">
+      <c r="A10" s="159"/>
+      <c r="B10" s="160"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="161"/>
+      <c r="F10" s="166" t="s">
         <v>117</v>
       </c>
-      <c r="G10" s="160"/>
-      <c r="H10" s="160"/>
-      <c r="I10" s="160"/>
-      <c r="J10" s="159"/>
-      <c r="K10" s="160"/>
-      <c r="L10" s="160"/>
-      <c r="M10" s="160"/>
-      <c r="N10" s="160"/>
-      <c r="O10" s="159"/>
-      <c r="P10" s="160"/>
-      <c r="Q10" s="160"/>
-      <c r="R10" s="160"/>
-      <c r="S10" s="160"/>
-      <c r="T10" s="159"/>
-      <c r="U10" s="160"/>
-      <c r="V10" s="160"/>
-      <c r="W10" s="160"/>
-      <c r="X10" s="160"/>
-      <c r="Y10" s="159"/>
-      <c r="Z10" s="160"/>
-      <c r="AA10" s="160"/>
-      <c r="AB10" s="160"/>
-      <c r="AC10" s="160"/>
-      <c r="AD10" s="159"/>
-      <c r="AE10" s="160"/>
-      <c r="AF10" s="160"/>
-      <c r="AG10" s="160"/>
-      <c r="AH10" s="160"/>
-      <c r="AI10" s="159"/>
-      <c r="AJ10" s="160"/>
-      <c r="AK10" s="160"/>
-      <c r="AL10" s="161"/>
+      <c r="G10" s="166"/>
+      <c r="H10" s="166"/>
+      <c r="I10" s="166"/>
+      <c r="J10" s="165"/>
+      <c r="K10" s="166"/>
+      <c r="L10" s="166"/>
+      <c r="M10" s="166"/>
+      <c r="N10" s="166"/>
+      <c r="O10" s="165"/>
+      <c r="P10" s="166"/>
+      <c r="Q10" s="166"/>
+      <c r="R10" s="166"/>
+      <c r="S10" s="166"/>
+      <c r="T10" s="165"/>
+      <c r="U10" s="166"/>
+      <c r="V10" s="166"/>
+      <c r="W10" s="166"/>
+      <c r="X10" s="166"/>
+      <c r="Y10" s="165"/>
+      <c r="Z10" s="166"/>
+      <c r="AA10" s="166"/>
+      <c r="AB10" s="166"/>
+      <c r="AC10" s="166"/>
+      <c r="AD10" s="165"/>
+      <c r="AE10" s="166"/>
+      <c r="AF10" s="166"/>
+      <c r="AG10" s="166"/>
+      <c r="AH10" s="166"/>
+      <c r="AI10" s="165"/>
+      <c r="AJ10" s="166"/>
+      <c r="AK10" s="166"/>
+      <c r="AL10" s="167"/>
     </row>
     <row r="11" spans="1:38" ht="16.2">
-      <c r="A11" s="165"/>
-      <c r="B11" s="166"/>
-      <c r="C11" s="166"/>
-      <c r="D11" s="166"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="160" t="s">
+      <c r="A11" s="162"/>
+      <c r="B11" s="163"/>
+      <c r="C11" s="163"/>
+      <c r="D11" s="163"/>
+      <c r="E11" s="164"/>
+      <c r="F11" s="166" t="s">
         <v>118</v>
       </c>
-      <c r="G11" s="160"/>
-      <c r="H11" s="160"/>
-      <c r="I11" s="160"/>
-      <c r="J11" s="159"/>
-      <c r="K11" s="160"/>
-      <c r="L11" s="160"/>
-      <c r="M11" s="160"/>
-      <c r="N11" s="160"/>
-      <c r="O11" s="159"/>
-      <c r="P11" s="160"/>
-      <c r="Q11" s="160"/>
-      <c r="R11" s="160"/>
-      <c r="S11" s="160"/>
-      <c r="T11" s="159"/>
-      <c r="U11" s="160"/>
-      <c r="V11" s="160"/>
-      <c r="W11" s="160"/>
-      <c r="X11" s="160"/>
-      <c r="Y11" s="159"/>
-      <c r="Z11" s="160"/>
-      <c r="AA11" s="160"/>
-      <c r="AB11" s="160"/>
-      <c r="AC11" s="160"/>
-      <c r="AD11" s="159"/>
-      <c r="AE11" s="160"/>
-      <c r="AF11" s="160"/>
-      <c r="AG11" s="160"/>
-      <c r="AH11" s="160"/>
-      <c r="AI11" s="159"/>
-      <c r="AJ11" s="160"/>
-      <c r="AK11" s="160"/>
-      <c r="AL11" s="161"/>
+      <c r="G11" s="166"/>
+      <c r="H11" s="166"/>
+      <c r="I11" s="166"/>
+      <c r="J11" s="165"/>
+      <c r="K11" s="166"/>
+      <c r="L11" s="166"/>
+      <c r="M11" s="166"/>
+      <c r="N11" s="166"/>
+      <c r="O11" s="165"/>
+      <c r="P11" s="166"/>
+      <c r="Q11" s="166"/>
+      <c r="R11" s="166"/>
+      <c r="S11" s="166"/>
+      <c r="T11" s="165"/>
+      <c r="U11" s="166"/>
+      <c r="V11" s="166"/>
+      <c r="W11" s="166"/>
+      <c r="X11" s="166"/>
+      <c r="Y11" s="165"/>
+      <c r="Z11" s="166"/>
+      <c r="AA11" s="166"/>
+      <c r="AB11" s="166"/>
+      <c r="AC11" s="166"/>
+      <c r="AD11" s="165"/>
+      <c r="AE11" s="166"/>
+      <c r="AF11" s="166"/>
+      <c r="AG11" s="166"/>
+      <c r="AH11" s="166"/>
+      <c r="AI11" s="165"/>
+      <c r="AJ11" s="166"/>
+      <c r="AK11" s="166"/>
+      <c r="AL11" s="167"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="162"/>
-      <c r="B12" s="163"/>
-      <c r="C12" s="163"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="160" t="s">
+      <c r="A12" s="159"/>
+      <c r="B12" s="160"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="161"/>
+      <c r="F12" s="166" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="160"/>
-      <c r="H12" s="160"/>
-      <c r="I12" s="160"/>
-      <c r="J12" s="159"/>
-      <c r="K12" s="160"/>
-      <c r="L12" s="160"/>
-      <c r="M12" s="160"/>
-      <c r="N12" s="160"/>
-      <c r="O12" s="159"/>
-      <c r="P12" s="160"/>
-      <c r="Q12" s="160"/>
-      <c r="R12" s="160"/>
-      <c r="S12" s="160"/>
-      <c r="T12" s="159"/>
-      <c r="U12" s="160"/>
-      <c r="V12" s="160"/>
-      <c r="W12" s="160"/>
-      <c r="X12" s="160"/>
-      <c r="Y12" s="159"/>
-      <c r="Z12" s="160"/>
-      <c r="AA12" s="160"/>
-      <c r="AB12" s="160"/>
-      <c r="AC12" s="160"/>
-      <c r="AD12" s="159"/>
-      <c r="AE12" s="160"/>
-      <c r="AF12" s="160"/>
-      <c r="AG12" s="160"/>
-      <c r="AH12" s="160"/>
-      <c r="AI12" s="159"/>
-      <c r="AJ12" s="160"/>
-      <c r="AK12" s="160"/>
-      <c r="AL12" s="161"/>
+      <c r="G12" s="166"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="166"/>
+      <c r="J12" s="165"/>
+      <c r="K12" s="166"/>
+      <c r="L12" s="166"/>
+      <c r="M12" s="166"/>
+      <c r="N12" s="166"/>
+      <c r="O12" s="165"/>
+      <c r="P12" s="166"/>
+      <c r="Q12" s="166"/>
+      <c r="R12" s="166"/>
+      <c r="S12" s="166"/>
+      <c r="T12" s="165"/>
+      <c r="U12" s="166"/>
+      <c r="V12" s="166"/>
+      <c r="W12" s="166"/>
+      <c r="X12" s="166"/>
+      <c r="Y12" s="165"/>
+      <c r="Z12" s="166"/>
+      <c r="AA12" s="166"/>
+      <c r="AB12" s="166"/>
+      <c r="AC12" s="166"/>
+      <c r="AD12" s="165"/>
+      <c r="AE12" s="166"/>
+      <c r="AF12" s="166"/>
+      <c r="AG12" s="166"/>
+      <c r="AH12" s="166"/>
+      <c r="AI12" s="165"/>
+      <c r="AJ12" s="166"/>
+      <c r="AK12" s="166"/>
+      <c r="AL12" s="167"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="165"/>
-      <c r="B13" s="166"/>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="167"/>
-      <c r="F13" s="160" t="s">
+      <c r="A13" s="162"/>
+      <c r="B13" s="163"/>
+      <c r="C13" s="163"/>
+      <c r="D13" s="163"/>
+      <c r="E13" s="164"/>
+      <c r="F13" s="166" t="s">
         <v>118</v>
       </c>
-      <c r="G13" s="160"/>
-      <c r="H13" s="160"/>
-      <c r="I13" s="160"/>
-      <c r="J13" s="159"/>
-      <c r="K13" s="160"/>
-      <c r="L13" s="160"/>
-      <c r="M13" s="160"/>
-      <c r="N13" s="160"/>
-      <c r="O13" s="159"/>
-      <c r="P13" s="160"/>
-      <c r="Q13" s="160"/>
-      <c r="R13" s="160"/>
-      <c r="S13" s="160"/>
-      <c r="T13" s="159"/>
-      <c r="U13" s="160"/>
-      <c r="V13" s="160"/>
-      <c r="W13" s="160"/>
-      <c r="X13" s="160"/>
-      <c r="Y13" s="159"/>
-      <c r="Z13" s="160"/>
-      <c r="AA13" s="160"/>
-      <c r="AB13" s="160"/>
-      <c r="AC13" s="160"/>
-      <c r="AD13" s="159"/>
-      <c r="AE13" s="160"/>
-      <c r="AF13" s="160"/>
-      <c r="AG13" s="160"/>
-      <c r="AH13" s="160"/>
-      <c r="AI13" s="159"/>
-      <c r="AJ13" s="160"/>
-      <c r="AK13" s="160"/>
-      <c r="AL13" s="161"/>
+      <c r="G13" s="166"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="166"/>
+      <c r="J13" s="165"/>
+      <c r="K13" s="166"/>
+      <c r="L13" s="166"/>
+      <c r="M13" s="166"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="165"/>
+      <c r="P13" s="166"/>
+      <c r="Q13" s="166"/>
+      <c r="R13" s="166"/>
+      <c r="S13" s="166"/>
+      <c r="T13" s="165"/>
+      <c r="U13" s="166"/>
+      <c r="V13" s="166"/>
+      <c r="W13" s="166"/>
+      <c r="X13" s="166"/>
+      <c r="Y13" s="165"/>
+      <c r="Z13" s="166"/>
+      <c r="AA13" s="166"/>
+      <c r="AB13" s="166"/>
+      <c r="AC13" s="166"/>
+      <c r="AD13" s="165"/>
+      <c r="AE13" s="166"/>
+      <c r="AF13" s="166"/>
+      <c r="AG13" s="166"/>
+      <c r="AH13" s="166"/>
+      <c r="AI13" s="165"/>
+      <c r="AJ13" s="166"/>
+      <c r="AK13" s="166"/>
+      <c r="AL13" s="167"/>
     </row>
     <row r="14" spans="1:38" ht="10.8" customHeight="1">
       <c r="A14" s="35"/>
@@ -13680,9 +13692,9 @@
       <c r="A15" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
       <c r="H15" s="63" t="s">
         <v>113</v>
       </c>
@@ -13713,270 +13725,270 @@
       <c r="AL15" s="34"/>
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
-      <c r="A16" s="168" t="s">
+      <c r="A16" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="168"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="168"/>
-      <c r="F16" s="168" t="s">
+      <c r="B16" s="174"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="174"/>
+      <c r="F16" s="174" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="168"/>
-      <c r="H16" s="168"/>
-      <c r="I16" s="168"/>
-      <c r="J16" s="168" t="s">
+      <c r="G16" s="174"/>
+      <c r="H16" s="174"/>
+      <c r="I16" s="174"/>
+      <c r="J16" s="174" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="168"/>
-      <c r="L16" s="168"/>
-      <c r="M16" s="168"/>
-      <c r="N16" s="168"/>
-      <c r="O16" s="168"/>
-      <c r="P16" s="168"/>
-      <c r="Q16" s="168"/>
-      <c r="R16" s="168"/>
-      <c r="S16" s="168"/>
-      <c r="T16" s="168"/>
-      <c r="U16" s="168"/>
-      <c r="V16" s="168"/>
-      <c r="W16" s="168"/>
-      <c r="X16" s="168"/>
-      <c r="Y16" s="168"/>
-      <c r="Z16" s="168"/>
-      <c r="AA16" s="168"/>
-      <c r="AB16" s="168"/>
-      <c r="AC16" s="168"/>
-      <c r="AD16" s="168"/>
-      <c r="AE16" s="168"/>
-      <c r="AF16" s="168"/>
-      <c r="AG16" s="168"/>
-      <c r="AH16" s="168"/>
-      <c r="AI16" s="169" t="s">
+      <c r="K16" s="174"/>
+      <c r="L16" s="174"/>
+      <c r="M16" s="174"/>
+      <c r="N16" s="174"/>
+      <c r="O16" s="174"/>
+      <c r="P16" s="174"/>
+      <c r="Q16" s="174"/>
+      <c r="R16" s="174"/>
+      <c r="S16" s="174"/>
+      <c r="T16" s="174"/>
+      <c r="U16" s="174"/>
+      <c r="V16" s="174"/>
+      <c r="W16" s="174"/>
+      <c r="X16" s="174"/>
+      <c r="Y16" s="174"/>
+      <c r="Z16" s="174"/>
+      <c r="AA16" s="174"/>
+      <c r="AB16" s="174"/>
+      <c r="AC16" s="174"/>
+      <c r="AD16" s="174"/>
+      <c r="AE16" s="174"/>
+      <c r="AF16" s="174"/>
+      <c r="AG16" s="174"/>
+      <c r="AH16" s="174"/>
+      <c r="AI16" s="168" t="s">
         <v>116</v>
       </c>
-      <c r="AJ16" s="170"/>
-      <c r="AK16" s="170"/>
-      <c r="AL16" s="171"/>
+      <c r="AJ16" s="169"/>
+      <c r="AK16" s="169"/>
+      <c r="AL16" s="170"/>
     </row>
     <row r="17" spans="1:38">
-      <c r="A17" s="168"/>
-      <c r="B17" s="168"/>
-      <c r="C17" s="168"/>
-      <c r="D17" s="168"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="168"/>
-      <c r="H17" s="168"/>
-      <c r="I17" s="168"/>
-      <c r="J17" s="168" t="s">
+      <c r="A17" s="174"/>
+      <c r="B17" s="174"/>
+      <c r="C17" s="174"/>
+      <c r="D17" s="174"/>
+      <c r="E17" s="174"/>
+      <c r="F17" s="174"/>
+      <c r="G17" s="174"/>
+      <c r="H17" s="174"/>
+      <c r="I17" s="174"/>
+      <c r="J17" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="K17" s="168"/>
-      <c r="L17" s="168"/>
-      <c r="M17" s="168"/>
-      <c r="N17" s="168"/>
-      <c r="O17" s="168" t="s">
+      <c r="K17" s="174"/>
+      <c r="L17" s="174"/>
+      <c r="M17" s="174"/>
+      <c r="N17" s="174"/>
+      <c r="O17" s="174" t="s">
         <v>10</v>
       </c>
-      <c r="P17" s="168"/>
-      <c r="Q17" s="168"/>
-      <c r="R17" s="168"/>
-      <c r="S17" s="168"/>
-      <c r="T17" s="168" t="s">
+      <c r="P17" s="174"/>
+      <c r="Q17" s="174"/>
+      <c r="R17" s="174"/>
+      <c r="S17" s="174"/>
+      <c r="T17" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="U17" s="168"/>
-      <c r="V17" s="168"/>
-      <c r="W17" s="168"/>
-      <c r="X17" s="168"/>
-      <c r="Y17" s="168" t="s">
+      <c r="U17" s="174"/>
+      <c r="V17" s="174"/>
+      <c r="W17" s="174"/>
+      <c r="X17" s="174"/>
+      <c r="Y17" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="Z17" s="168"/>
-      <c r="AA17" s="168"/>
-      <c r="AB17" s="168"/>
-      <c r="AC17" s="168"/>
-      <c r="AD17" s="168" t="s">
+      <c r="Z17" s="174"/>
+      <c r="AA17" s="174"/>
+      <c r="AB17" s="174"/>
+      <c r="AC17" s="174"/>
+      <c r="AD17" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="AE17" s="168"/>
-      <c r="AF17" s="168"/>
-      <c r="AG17" s="168"/>
-      <c r="AH17" s="168"/>
-      <c r="AI17" s="172"/>
-      <c r="AJ17" s="173"/>
-      <c r="AK17" s="173"/>
-      <c r="AL17" s="174"/>
+      <c r="AE17" s="174"/>
+      <c r="AF17" s="174"/>
+      <c r="AG17" s="174"/>
+      <c r="AH17" s="174"/>
+      <c r="AI17" s="171"/>
+      <c r="AJ17" s="172"/>
+      <c r="AK17" s="172"/>
+      <c r="AL17" s="173"/>
     </row>
     <row r="18" spans="1:38">
-      <c r="A18" s="162"/>
-      <c r="B18" s="163"/>
-      <c r="C18" s="163"/>
-      <c r="D18" s="163"/>
-      <c r="E18" s="164"/>
-      <c r="F18" s="160" t="s">
+      <c r="A18" s="159"/>
+      <c r="B18" s="160"/>
+      <c r="C18" s="160"/>
+      <c r="D18" s="160"/>
+      <c r="E18" s="161"/>
+      <c r="F18" s="166" t="s">
         <v>117</v>
       </c>
-      <c r="G18" s="160"/>
-      <c r="H18" s="160"/>
-      <c r="I18" s="160"/>
-      <c r="J18" s="159"/>
-      <c r="K18" s="160"/>
-      <c r="L18" s="160"/>
-      <c r="M18" s="160"/>
-      <c r="N18" s="160"/>
-      <c r="O18" s="159"/>
-      <c r="P18" s="160"/>
-      <c r="Q18" s="160"/>
-      <c r="R18" s="160"/>
-      <c r="S18" s="160"/>
-      <c r="T18" s="159"/>
-      <c r="U18" s="160"/>
-      <c r="V18" s="160"/>
-      <c r="W18" s="160"/>
-      <c r="X18" s="160"/>
-      <c r="Y18" s="159"/>
-      <c r="Z18" s="160"/>
-      <c r="AA18" s="160"/>
-      <c r="AB18" s="160"/>
-      <c r="AC18" s="160"/>
-      <c r="AD18" s="159"/>
-      <c r="AE18" s="160"/>
-      <c r="AF18" s="160"/>
-      <c r="AG18" s="160"/>
-      <c r="AH18" s="160"/>
-      <c r="AI18" s="159"/>
-      <c r="AJ18" s="160"/>
-      <c r="AK18" s="160"/>
-      <c r="AL18" s="161"/>
+      <c r="G18" s="166"/>
+      <c r="H18" s="166"/>
+      <c r="I18" s="166"/>
+      <c r="J18" s="165"/>
+      <c r="K18" s="166"/>
+      <c r="L18" s="166"/>
+      <c r="M18" s="166"/>
+      <c r="N18" s="166"/>
+      <c r="O18" s="165"/>
+      <c r="P18" s="166"/>
+      <c r="Q18" s="166"/>
+      <c r="R18" s="166"/>
+      <c r="S18" s="166"/>
+      <c r="T18" s="165"/>
+      <c r="U18" s="166"/>
+      <c r="V18" s="166"/>
+      <c r="W18" s="166"/>
+      <c r="X18" s="166"/>
+      <c r="Y18" s="165"/>
+      <c r="Z18" s="166"/>
+      <c r="AA18" s="166"/>
+      <c r="AB18" s="166"/>
+      <c r="AC18" s="166"/>
+      <c r="AD18" s="165"/>
+      <c r="AE18" s="166"/>
+      <c r="AF18" s="166"/>
+      <c r="AG18" s="166"/>
+      <c r="AH18" s="166"/>
+      <c r="AI18" s="165"/>
+      <c r="AJ18" s="166"/>
+      <c r="AK18" s="166"/>
+      <c r="AL18" s="167"/>
     </row>
     <row r="19" spans="1:38" ht="16.2">
-      <c r="A19" s="165"/>
-      <c r="B19" s="166"/>
-      <c r="C19" s="166"/>
-      <c r="D19" s="166"/>
-      <c r="E19" s="167"/>
-      <c r="F19" s="160" t="s">
+      <c r="A19" s="162"/>
+      <c r="B19" s="163"/>
+      <c r="C19" s="163"/>
+      <c r="D19" s="163"/>
+      <c r="E19" s="164"/>
+      <c r="F19" s="166" t="s">
         <v>118</v>
       </c>
-      <c r="G19" s="160"/>
-      <c r="H19" s="160"/>
-      <c r="I19" s="160"/>
-      <c r="J19" s="159"/>
-      <c r="K19" s="160"/>
-      <c r="L19" s="160"/>
-      <c r="M19" s="160"/>
-      <c r="N19" s="160"/>
-      <c r="O19" s="159"/>
-      <c r="P19" s="160"/>
-      <c r="Q19" s="160"/>
-      <c r="R19" s="160"/>
-      <c r="S19" s="160"/>
-      <c r="T19" s="159"/>
-      <c r="U19" s="160"/>
-      <c r="V19" s="160"/>
-      <c r="W19" s="160"/>
-      <c r="X19" s="160"/>
-      <c r="Y19" s="159"/>
-      <c r="Z19" s="160"/>
-      <c r="AA19" s="160"/>
-      <c r="AB19" s="160"/>
-      <c r="AC19" s="160"/>
-      <c r="AD19" s="159"/>
-      <c r="AE19" s="160"/>
-      <c r="AF19" s="160"/>
-      <c r="AG19" s="160"/>
-      <c r="AH19" s="160"/>
-      <c r="AI19" s="159"/>
-      <c r="AJ19" s="160"/>
-      <c r="AK19" s="160"/>
-      <c r="AL19" s="161"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="166"/>
+      <c r="I19" s="166"/>
+      <c r="J19" s="165"/>
+      <c r="K19" s="166"/>
+      <c r="L19" s="166"/>
+      <c r="M19" s="166"/>
+      <c r="N19" s="166"/>
+      <c r="O19" s="165"/>
+      <c r="P19" s="166"/>
+      <c r="Q19" s="166"/>
+      <c r="R19" s="166"/>
+      <c r="S19" s="166"/>
+      <c r="T19" s="165"/>
+      <c r="U19" s="166"/>
+      <c r="V19" s="166"/>
+      <c r="W19" s="166"/>
+      <c r="X19" s="166"/>
+      <c r="Y19" s="165"/>
+      <c r="Z19" s="166"/>
+      <c r="AA19" s="166"/>
+      <c r="AB19" s="166"/>
+      <c r="AC19" s="166"/>
+      <c r="AD19" s="165"/>
+      <c r="AE19" s="166"/>
+      <c r="AF19" s="166"/>
+      <c r="AG19" s="166"/>
+      <c r="AH19" s="166"/>
+      <c r="AI19" s="165"/>
+      <c r="AJ19" s="166"/>
+      <c r="AK19" s="166"/>
+      <c r="AL19" s="167"/>
     </row>
     <row r="20" spans="1:38">
-      <c r="A20" s="162"/>
-      <c r="B20" s="163"/>
-      <c r="C20" s="163"/>
-      <c r="D20" s="163"/>
-      <c r="E20" s="164"/>
-      <c r="F20" s="160" t="s">
+      <c r="A20" s="159"/>
+      <c r="B20" s="160"/>
+      <c r="C20" s="160"/>
+      <c r="D20" s="160"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="166" t="s">
         <v>117</v>
       </c>
-      <c r="G20" s="160"/>
-      <c r="H20" s="160"/>
-      <c r="I20" s="160"/>
-      <c r="J20" s="159"/>
-      <c r="K20" s="160"/>
-      <c r="L20" s="160"/>
-      <c r="M20" s="160"/>
-      <c r="N20" s="160"/>
-      <c r="O20" s="159"/>
-      <c r="P20" s="160"/>
-      <c r="Q20" s="160"/>
-      <c r="R20" s="160"/>
-      <c r="S20" s="160"/>
-      <c r="T20" s="159"/>
-      <c r="U20" s="160"/>
-      <c r="V20" s="160"/>
-      <c r="W20" s="160"/>
-      <c r="X20" s="160"/>
-      <c r="Y20" s="159"/>
-      <c r="Z20" s="160"/>
-      <c r="AA20" s="160"/>
-      <c r="AB20" s="160"/>
-      <c r="AC20" s="160"/>
-      <c r="AD20" s="159"/>
-      <c r="AE20" s="160"/>
-      <c r="AF20" s="160"/>
-      <c r="AG20" s="160"/>
-      <c r="AH20" s="160"/>
-      <c r="AI20" s="159"/>
-      <c r="AJ20" s="160"/>
-      <c r="AK20" s="160"/>
-      <c r="AL20" s="161"/>
+      <c r="G20" s="166"/>
+      <c r="H20" s="166"/>
+      <c r="I20" s="166"/>
+      <c r="J20" s="165"/>
+      <c r="K20" s="166"/>
+      <c r="L20" s="166"/>
+      <c r="M20" s="166"/>
+      <c r="N20" s="166"/>
+      <c r="O20" s="165"/>
+      <c r="P20" s="166"/>
+      <c r="Q20" s="166"/>
+      <c r="R20" s="166"/>
+      <c r="S20" s="166"/>
+      <c r="T20" s="165"/>
+      <c r="U20" s="166"/>
+      <c r="V20" s="166"/>
+      <c r="W20" s="166"/>
+      <c r="X20" s="166"/>
+      <c r="Y20" s="165"/>
+      <c r="Z20" s="166"/>
+      <c r="AA20" s="166"/>
+      <c r="AB20" s="166"/>
+      <c r="AC20" s="166"/>
+      <c r="AD20" s="165"/>
+      <c r="AE20" s="166"/>
+      <c r="AF20" s="166"/>
+      <c r="AG20" s="166"/>
+      <c r="AH20" s="166"/>
+      <c r="AI20" s="165"/>
+      <c r="AJ20" s="166"/>
+      <c r="AK20" s="166"/>
+      <c r="AL20" s="167"/>
     </row>
     <row r="21" spans="1:38" ht="16.2">
-      <c r="A21" s="165"/>
-      <c r="B21" s="166"/>
-      <c r="C21" s="166"/>
-      <c r="D21" s="166"/>
-      <c r="E21" s="167"/>
-      <c r="F21" s="160" t="s">
+      <c r="A21" s="162"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="163"/>
+      <c r="D21" s="163"/>
+      <c r="E21" s="164"/>
+      <c r="F21" s="166" t="s">
         <v>118</v>
       </c>
-      <c r="G21" s="160"/>
-      <c r="H21" s="160"/>
-      <c r="I21" s="160"/>
-      <c r="J21" s="159"/>
-      <c r="K21" s="160"/>
-      <c r="L21" s="160"/>
-      <c r="M21" s="160"/>
-      <c r="N21" s="160"/>
-      <c r="O21" s="159"/>
-      <c r="P21" s="160"/>
-      <c r="Q21" s="160"/>
-      <c r="R21" s="160"/>
-      <c r="S21" s="160"/>
-      <c r="T21" s="159"/>
-      <c r="U21" s="160"/>
-      <c r="V21" s="160"/>
-      <c r="W21" s="160"/>
-      <c r="X21" s="160"/>
-      <c r="Y21" s="159"/>
-      <c r="Z21" s="160"/>
-      <c r="AA21" s="160"/>
-      <c r="AB21" s="160"/>
-      <c r="AC21" s="160"/>
-      <c r="AD21" s="159"/>
-      <c r="AE21" s="160"/>
-      <c r="AF21" s="160"/>
-      <c r="AG21" s="160"/>
-      <c r="AH21" s="160"/>
-      <c r="AI21" s="159"/>
-      <c r="AJ21" s="160"/>
-      <c r="AK21" s="160"/>
-      <c r="AL21" s="161"/>
+      <c r="G21" s="166"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="166"/>
+      <c r="J21" s="165"/>
+      <c r="K21" s="166"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="166"/>
+      <c r="N21" s="166"/>
+      <c r="O21" s="165"/>
+      <c r="P21" s="166"/>
+      <c r="Q21" s="166"/>
+      <c r="R21" s="166"/>
+      <c r="S21" s="166"/>
+      <c r="T21" s="165"/>
+      <c r="U21" s="166"/>
+      <c r="V21" s="166"/>
+      <c r="W21" s="166"/>
+      <c r="X21" s="166"/>
+      <c r="Y21" s="165"/>
+      <c r="Z21" s="166"/>
+      <c r="AA21" s="166"/>
+      <c r="AB21" s="166"/>
+      <c r="AC21" s="166"/>
+      <c r="AD21" s="165"/>
+      <c r="AE21" s="166"/>
+      <c r="AF21" s="166"/>
+      <c r="AG21" s="166"/>
+      <c r="AH21" s="166"/>
+      <c r="AI21" s="165"/>
+      <c r="AJ21" s="166"/>
+      <c r="AK21" s="166"/>
+      <c r="AL21" s="167"/>
     </row>
     <row r="22" spans="1:38">
       <c r="A22" s="74"/>
@@ -14301,6 +14313,72 @@
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="AI12:AL12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="Y13:AC13"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="AI13:AL13"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="AI11:AL11"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AI10:AL10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="J11:N11"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="A12:E13"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="F8:I9"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="AI8:AL9"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:N20"/>
+    <mergeCell ref="O20:S20"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="AI21:AL21"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="Y21:AC21"/>
+    <mergeCell ref="AD21:AH21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A16:E17"/>
+    <mergeCell ref="F16:I17"/>
+    <mergeCell ref="J16:AH16"/>
+    <mergeCell ref="J17:N17"/>
+    <mergeCell ref="O17:S17"/>
+    <mergeCell ref="T17:X17"/>
+    <mergeCell ref="Y17:AC17"/>
+    <mergeCell ref="AD17:AH17"/>
+    <mergeCell ref="AI19:AL19"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="J18:N18"/>
+    <mergeCell ref="O18:S18"/>
+    <mergeCell ref="T18:X18"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="Y18:AC18"/>
     <mergeCell ref="M1:AL1"/>
@@ -14317,72 +14395,6 @@
     <mergeCell ref="T19:X19"/>
     <mergeCell ref="Y19:AC19"/>
     <mergeCell ref="AD19:AH19"/>
-    <mergeCell ref="AI19:AL19"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="J18:N18"/>
-    <mergeCell ref="O18:S18"/>
-    <mergeCell ref="T18:X18"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A16:E17"/>
-    <mergeCell ref="F16:I17"/>
-    <mergeCell ref="J16:AH16"/>
-    <mergeCell ref="J17:N17"/>
-    <mergeCell ref="O17:S17"/>
-    <mergeCell ref="T17:X17"/>
-    <mergeCell ref="Y17:AC17"/>
-    <mergeCell ref="AD17:AH17"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:N20"/>
-    <mergeCell ref="O20:S20"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="AI21:AL21"/>
-    <mergeCell ref="J21:N21"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="Y21:AC21"/>
-    <mergeCell ref="AD21:AH21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:I9"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="AI8:AL9"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="A12:E13"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="AI11:AL11"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="AI10:AL10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="Y13:AC13"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="AI13:AL13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -14423,32 +14435,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="135"/>
-      <c r="Z1" s="135"/>
-      <c r="AA1" s="135"/>
-      <c r="AB1" s="135"/>
-      <c r="AC1" s="135"/>
-      <c r="AD1" s="135"/>
-      <c r="AE1" s="135"/>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="135"/>
-      <c r="AI1" s="135"/>
-      <c r="AJ1" s="135"/>
-      <c r="AK1" s="135"/>
-      <c r="AL1" s="135"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="144"/>
+      <c r="Z1" s="144"/>
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="144"/>
+      <c r="AF1" s="144"/>
+      <c r="AG1" s="144"/>
+      <c r="AH1" s="144"/>
+      <c r="AI1" s="144"/>
+      <c r="AJ1" s="144"/>
+      <c r="AK1" s="144"/>
+      <c r="AL1" s="144"/>
       <c r="AM1" s="67"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -14492,25 +14504,25 @@
       <c r="AM2" s="67"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="136"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="136"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
-      <c r="S3" s="136"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="141"/>
+      <c r="S3" s="141"/>
       <c r="T3" s="34"/>
       <c r="U3" s="34"/>
       <c r="V3" s="34"/>
@@ -14549,442 +14561,442 @@
       <c r="A7" s="6"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="144" t="s">
+      <c r="A8" s="139" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="144"/>
-      <c r="J8" s="144" t="s">
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="139" t="s">
         <v>160</v>
       </c>
-      <c r="K8" s="144"/>
-      <c r="L8" s="144"/>
-      <c r="M8" s="144"/>
-      <c r="N8" s="144"/>
-      <c r="O8" s="144"/>
-      <c r="P8" s="144"/>
-      <c r="Q8" s="144"/>
-      <c r="R8" s="144"/>
-      <c r="S8" s="144"/>
-      <c r="T8" s="144"/>
-      <c r="U8" s="144"/>
-      <c r="V8" s="144"/>
-      <c r="W8" s="144"/>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="144"/>
-      <c r="Z8" s="144"/>
-      <c r="AA8" s="144"/>
-      <c r="AB8" s="144"/>
-      <c r="AC8" s="144"/>
-      <c r="AD8" s="144"/>
-      <c r="AE8" s="144"/>
-      <c r="AF8" s="144"/>
-      <c r="AG8" s="144"/>
-      <c r="AH8" s="144"/>
-      <c r="AI8" s="144" t="s">
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="139"/>
+      <c r="Q8" s="139"/>
+      <c r="R8" s="139"/>
+      <c r="S8" s="139"/>
+      <c r="T8" s="139"/>
+      <c r="U8" s="139"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="139"/>
+      <c r="X8" s="139"/>
+      <c r="Y8" s="139"/>
+      <c r="Z8" s="139"/>
+      <c r="AA8" s="139"/>
+      <c r="AB8" s="139"/>
+      <c r="AC8" s="139"/>
+      <c r="AD8" s="139"/>
+      <c r="AE8" s="139"/>
+      <c r="AF8" s="139"/>
+      <c r="AG8" s="139"/>
+      <c r="AH8" s="139"/>
+      <c r="AI8" s="139" t="s">
         <v>203</v>
       </c>
-      <c r="AJ8" s="144"/>
-      <c r="AK8" s="144"/>
-      <c r="AL8" s="144"/>
-      <c r="AM8" s="144"/>
+      <c r="AJ8" s="139"/>
+      <c r="AK8" s="139"/>
+      <c r="AL8" s="139"/>
+      <c r="AM8" s="139"/>
     </row>
     <row r="9" spans="1:39">
-      <c r="A9" s="144"/>
-      <c r="B9" s="144"/>
-      <c r="C9" s="144"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="144"/>
-      <c r="I9" s="144"/>
-      <c r="J9" s="144" t="s">
+      <c r="A9" s="139"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="139"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="139"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="139" t="s">
         <v>205</v>
       </c>
-      <c r="K9" s="144"/>
-      <c r="L9" s="144"/>
-      <c r="M9" s="144" t="s">
+      <c r="K9" s="139"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="139" t="s">
         <v>206</v>
       </c>
-      <c r="N9" s="144"/>
-      <c r="O9" s="144"/>
-      <c r="P9" s="144" t="s">
+      <c r="N9" s="139"/>
+      <c r="O9" s="139"/>
+      <c r="P9" s="139" t="s">
         <v>207</v>
       </c>
-      <c r="Q9" s="144"/>
-      <c r="R9" s="144"/>
-      <c r="S9" s="144" t="s">
+      <c r="Q9" s="139"/>
+      <c r="R9" s="139"/>
+      <c r="S9" s="139" t="s">
         <v>208</v>
       </c>
-      <c r="T9" s="144"/>
-      <c r="U9" s="144"/>
-      <c r="V9" s="144" t="s">
+      <c r="T9" s="139"/>
+      <c r="U9" s="139"/>
+      <c r="V9" s="139" t="s">
         <v>209</v>
       </c>
-      <c r="W9" s="144"/>
-      <c r="X9" s="144"/>
-      <c r="Y9" s="144" t="s">
+      <c r="W9" s="139"/>
+      <c r="X9" s="139"/>
+      <c r="Y9" s="139" t="s">
         <v>204</v>
       </c>
-      <c r="Z9" s="144"/>
-      <c r="AA9" s="144"/>
-      <c r="AB9" s="144"/>
-      <c r="AC9" s="144" t="s">
+      <c r="Z9" s="139"/>
+      <c r="AA9" s="139"/>
+      <c r="AB9" s="139"/>
+      <c r="AC9" s="139" t="s">
         <v>202</v>
       </c>
-      <c r="AD9" s="144"/>
-      <c r="AE9" s="144"/>
-      <c r="AF9" s="144"/>
-      <c r="AG9" s="144"/>
-      <c r="AH9" s="144"/>
-      <c r="AI9" s="144"/>
-      <c r="AJ9" s="144"/>
-      <c r="AK9" s="144"/>
-      <c r="AL9" s="144"/>
-      <c r="AM9" s="144"/>
+      <c r="AD9" s="139"/>
+      <c r="AE9" s="139"/>
+      <c r="AF9" s="139"/>
+      <c r="AG9" s="139"/>
+      <c r="AH9" s="139"/>
+      <c r="AI9" s="139"/>
+      <c r="AJ9" s="139"/>
+      <c r="AK9" s="139"/>
+      <c r="AL9" s="139"/>
+      <c r="AM9" s="139"/>
     </row>
     <row r="10" spans="1:39">
       <c r="A10" s="175"/>
       <c r="B10" s="175"/>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="139" t="s">
         <v>211</v>
       </c>
-      <c r="D10" s="144"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="144"/>
-      <c r="L10" s="144"/>
-      <c r="M10" s="144"/>
-      <c r="N10" s="144"/>
-      <c r="O10" s="144"/>
-      <c r="P10" s="144"/>
-      <c r="Q10" s="144"/>
-      <c r="R10" s="144"/>
-      <c r="S10" s="144"/>
-      <c r="T10" s="144"/>
-      <c r="U10" s="144"/>
-      <c r="V10" s="144"/>
-      <c r="W10" s="144"/>
-      <c r="X10" s="144"/>
-      <c r="Y10" s="144"/>
-      <c r="Z10" s="144"/>
-      <c r="AA10" s="144"/>
-      <c r="AB10" s="144"/>
-      <c r="AC10" s="144"/>
-      <c r="AD10" s="144"/>
-      <c r="AE10" s="144"/>
-      <c r="AF10" s="144"/>
-      <c r="AG10" s="144"/>
-      <c r="AH10" s="144"/>
-      <c r="AI10" s="144"/>
-      <c r="AJ10" s="144"/>
-      <c r="AK10" s="144"/>
-      <c r="AL10" s="144"/>
-      <c r="AM10" s="144"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="139"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="139"/>
+      <c r="N10" s="139"/>
+      <c r="O10" s="139"/>
+      <c r="P10" s="139"/>
+      <c r="Q10" s="139"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="139"/>
+      <c r="T10" s="139"/>
+      <c r="U10" s="139"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="139"/>
+      <c r="X10" s="139"/>
+      <c r="Y10" s="139"/>
+      <c r="Z10" s="139"/>
+      <c r="AA10" s="139"/>
+      <c r="AB10" s="139"/>
+      <c r="AC10" s="139"/>
+      <c r="AD10" s="139"/>
+      <c r="AE10" s="139"/>
+      <c r="AF10" s="139"/>
+      <c r="AG10" s="139"/>
+      <c r="AH10" s="139"/>
+      <c r="AI10" s="139"/>
+      <c r="AJ10" s="139"/>
+      <c r="AK10" s="139"/>
+      <c r="AL10" s="139"/>
+      <c r="AM10" s="139"/>
     </row>
     <row r="11" spans="1:39">
       <c r="A11" s="175"/>
       <c r="B11" s="175"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="144"/>
-      <c r="N11" s="144"/>
-      <c r="O11" s="144"/>
-      <c r="P11" s="144"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="144"/>
-      <c r="S11" s="144"/>
-      <c r="T11" s="144"/>
-      <c r="U11" s="144"/>
-      <c r="V11" s="144"/>
-      <c r="W11" s="144"/>
-      <c r="X11" s="144"/>
-      <c r="Y11" s="144"/>
-      <c r="Z11" s="144"/>
-      <c r="AA11" s="144"/>
-      <c r="AB11" s="144"/>
-      <c r="AC11" s="144"/>
-      <c r="AD11" s="144"/>
-      <c r="AE11" s="144"/>
-      <c r="AF11" s="144"/>
-      <c r="AG11" s="144"/>
-      <c r="AH11" s="144"/>
-      <c r="AI11" s="144"/>
-      <c r="AJ11" s="144"/>
-      <c r="AK11" s="144"/>
-      <c r="AL11" s="144"/>
-      <c r="AM11" s="144"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="139"/>
+      <c r="L11" s="139"/>
+      <c r="M11" s="139"/>
+      <c r="N11" s="139"/>
+      <c r="O11" s="139"/>
+      <c r="P11" s="139"/>
+      <c r="Q11" s="139"/>
+      <c r="R11" s="139"/>
+      <c r="S11" s="139"/>
+      <c r="T11" s="139"/>
+      <c r="U11" s="139"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="139"/>
+      <c r="X11" s="139"/>
+      <c r="Y11" s="139"/>
+      <c r="Z11" s="139"/>
+      <c r="AA11" s="139"/>
+      <c r="AB11" s="139"/>
+      <c r="AC11" s="139"/>
+      <c r="AD11" s="139"/>
+      <c r="AE11" s="139"/>
+      <c r="AF11" s="139"/>
+      <c r="AG11" s="139"/>
+      <c r="AH11" s="139"/>
+      <c r="AI11" s="139"/>
+      <c r="AJ11" s="139"/>
+      <c r="AK11" s="139"/>
+      <c r="AL11" s="139"/>
+      <c r="AM11" s="139"/>
     </row>
     <row r="12" spans="1:39">
       <c r="A12" s="175"/>
       <c r="B12" s="175"/>
-      <c r="C12" s="144" t="s">
+      <c r="C12" s="139" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="144"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="144"/>
-      <c r="L12" s="144"/>
-      <c r="M12" s="144"/>
-      <c r="N12" s="144"/>
-      <c r="O12" s="144"/>
-      <c r="P12" s="144"/>
-      <c r="Q12" s="144"/>
-      <c r="R12" s="144"/>
-      <c r="S12" s="144"/>
-      <c r="T12" s="144"/>
-      <c r="U12" s="144"/>
-      <c r="V12" s="144"/>
-      <c r="W12" s="144"/>
-      <c r="X12" s="144"/>
-      <c r="Y12" s="144"/>
-      <c r="Z12" s="144"/>
-      <c r="AA12" s="144"/>
-      <c r="AB12" s="144"/>
-      <c r="AC12" s="144"/>
-      <c r="AD12" s="144"/>
-      <c r="AE12" s="144"/>
-      <c r="AF12" s="144"/>
-      <c r="AG12" s="144"/>
-      <c r="AH12" s="144"/>
-      <c r="AI12" s="144"/>
-      <c r="AJ12" s="144"/>
-      <c r="AK12" s="144"/>
-      <c r="AL12" s="144"/>
-      <c r="AM12" s="144"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="139"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="139"/>
+      <c r="K12" s="139"/>
+      <c r="L12" s="139"/>
+      <c r="M12" s="139"/>
+      <c r="N12" s="139"/>
+      <c r="O12" s="139"/>
+      <c r="P12" s="139"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="139"/>
+      <c r="T12" s="139"/>
+      <c r="U12" s="139"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="139"/>
+      <c r="X12" s="139"/>
+      <c r="Y12" s="139"/>
+      <c r="Z12" s="139"/>
+      <c r="AA12" s="139"/>
+      <c r="AB12" s="139"/>
+      <c r="AC12" s="139"/>
+      <c r="AD12" s="139"/>
+      <c r="AE12" s="139"/>
+      <c r="AF12" s="139"/>
+      <c r="AG12" s="139"/>
+      <c r="AH12" s="139"/>
+      <c r="AI12" s="139"/>
+      <c r="AJ12" s="139"/>
+      <c r="AK12" s="139"/>
+      <c r="AL12" s="139"/>
+      <c r="AM12" s="139"/>
     </row>
     <row r="13" spans="1:39">
       <c r="A13" s="175"/>
       <c r="B13" s="175"/>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
-      <c r="O13" s="144"/>
-      <c r="P13" s="144"/>
-      <c r="Q13" s="144"/>
-      <c r="R13" s="144"/>
-      <c r="S13" s="144"/>
-      <c r="T13" s="144"/>
-      <c r="U13" s="144"/>
-      <c r="V13" s="144"/>
-      <c r="W13" s="144"/>
-      <c r="X13" s="144"/>
-      <c r="Y13" s="144"/>
-      <c r="Z13" s="144"/>
-      <c r="AA13" s="144"/>
-      <c r="AB13" s="144"/>
-      <c r="AC13" s="144"/>
-      <c r="AD13" s="144"/>
-      <c r="AE13" s="144"/>
-      <c r="AF13" s="144"/>
-      <c r="AG13" s="144"/>
-      <c r="AH13" s="144"/>
-      <c r="AI13" s="144"/>
-      <c r="AJ13" s="144"/>
-      <c r="AK13" s="144"/>
-      <c r="AL13" s="144"/>
-      <c r="AM13" s="144"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="139"/>
+      <c r="K13" s="139"/>
+      <c r="L13" s="139"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="139"/>
+      <c r="O13" s="139"/>
+      <c r="P13" s="139"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139"/>
+      <c r="T13" s="139"/>
+      <c r="U13" s="139"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="139"/>
+      <c r="X13" s="139"/>
+      <c r="Y13" s="139"/>
+      <c r="Z13" s="139"/>
+      <c r="AA13" s="139"/>
+      <c r="AB13" s="139"/>
+      <c r="AC13" s="139"/>
+      <c r="AD13" s="139"/>
+      <c r="AE13" s="139"/>
+      <c r="AF13" s="139"/>
+      <c r="AG13" s="139"/>
+      <c r="AH13" s="139"/>
+      <c r="AI13" s="139"/>
+      <c r="AJ13" s="139"/>
+      <c r="AK13" s="139"/>
+      <c r="AL13" s="139"/>
+      <c r="AM13" s="139"/>
     </row>
     <row r="14" spans="1:39">
       <c r="A14" s="175"/>
       <c r="B14" s="175"/>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="139" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144"/>
-      <c r="Q14" s="144"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="144"/>
-      <c r="T14" s="144"/>
-      <c r="U14" s="144"/>
-      <c r="V14" s="144"/>
-      <c r="W14" s="144"/>
-      <c r="X14" s="144"/>
-      <c r="Y14" s="144"/>
-      <c r="Z14" s="144"/>
-      <c r="AA14" s="144"/>
-      <c r="AB14" s="144"/>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="144"/>
-      <c r="AG14" s="144"/>
-      <c r="AH14" s="144"/>
-      <c r="AI14" s="144"/>
-      <c r="AJ14" s="144"/>
-      <c r="AK14" s="144"/>
-      <c r="AL14" s="144"/>
-      <c r="AM14" s="144"/>
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="139"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="139"/>
+      <c r="N14" s="139"/>
+      <c r="O14" s="139"/>
+      <c r="P14" s="139"/>
+      <c r="Q14" s="139"/>
+      <c r="R14" s="139"/>
+      <c r="S14" s="139"/>
+      <c r="T14" s="139"/>
+      <c r="U14" s="139"/>
+      <c r="V14" s="139"/>
+      <c r="W14" s="139"/>
+      <c r="X14" s="139"/>
+      <c r="Y14" s="139"/>
+      <c r="Z14" s="139"/>
+      <c r="AA14" s="139"/>
+      <c r="AB14" s="139"/>
+      <c r="AC14" s="139"/>
+      <c r="AD14" s="139"/>
+      <c r="AE14" s="139"/>
+      <c r="AF14" s="139"/>
+      <c r="AG14" s="139"/>
+      <c r="AH14" s="139"/>
+      <c r="AI14" s="139"/>
+      <c r="AJ14" s="139"/>
+      <c r="AK14" s="139"/>
+      <c r="AL14" s="139"/>
+      <c r="AM14" s="139"/>
     </row>
     <row r="15" spans="1:39">
       <c r="A15" s="175"/>
       <c r="B15" s="175"/>
-      <c r="C15" s="144"/>
-      <c r="D15" s="144"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="144"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="144"/>
-      <c r="L15" s="144"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="144"/>
-      <c r="Q15" s="144"/>
-      <c r="R15" s="144"/>
-      <c r="S15" s="144"/>
-      <c r="T15" s="144"/>
-      <c r="U15" s="144"/>
-      <c r="V15" s="144"/>
-      <c r="W15" s="144"/>
-      <c r="X15" s="144"/>
-      <c r="Y15" s="144"/>
-      <c r="Z15" s="144"/>
-      <c r="AA15" s="144"/>
-      <c r="AB15" s="144"/>
-      <c r="AC15" s="144"/>
-      <c r="AD15" s="144"/>
-      <c r="AE15" s="144"/>
-      <c r="AF15" s="144"/>
-      <c r="AG15" s="144"/>
-      <c r="AH15" s="144"/>
-      <c r="AI15" s="144"/>
-      <c r="AJ15" s="144"/>
-      <c r="AK15" s="144"/>
-      <c r="AL15" s="144"/>
-      <c r="AM15" s="144"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
+      <c r="U15" s="139"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="139"/>
+      <c r="X15" s="139"/>
+      <c r="Y15" s="139"/>
+      <c r="Z15" s="139"/>
+      <c r="AA15" s="139"/>
+      <c r="AB15" s="139"/>
+      <c r="AC15" s="139"/>
+      <c r="AD15" s="139"/>
+      <c r="AE15" s="139"/>
+      <c r="AF15" s="139"/>
+      <c r="AG15" s="139"/>
+      <c r="AH15" s="139"/>
+      <c r="AI15" s="139"/>
+      <c r="AJ15" s="139"/>
+      <c r="AK15" s="139"/>
+      <c r="AL15" s="139"/>
+      <c r="AM15" s="139"/>
     </row>
     <row r="16" spans="1:39">
       <c r="A16" s="175"/>
       <c r="B16" s="175"/>
-      <c r="C16" s="144" t="s">
+      <c r="C16" s="139" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="144"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="144"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="144"/>
-      <c r="P16" s="144"/>
-      <c r="Q16" s="144"/>
-      <c r="R16" s="144"/>
-      <c r="S16" s="144"/>
-      <c r="T16" s="144"/>
-      <c r="U16" s="144"/>
-      <c r="V16" s="144"/>
-      <c r="W16" s="144"/>
-      <c r="X16" s="144"/>
-      <c r="Y16" s="144"/>
-      <c r="Z16" s="144"/>
-      <c r="AA16" s="144"/>
-      <c r="AB16" s="144"/>
-      <c r="AC16" s="144"/>
-      <c r="AD16" s="144"/>
-      <c r="AE16" s="144"/>
-      <c r="AF16" s="144"/>
-      <c r="AG16" s="144"/>
-      <c r="AH16" s="144"/>
-      <c r="AI16" s="144"/>
-      <c r="AJ16" s="144"/>
-      <c r="AK16" s="144"/>
-      <c r="AL16" s="144"/>
-      <c r="AM16" s="144"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="139"/>
+      <c r="M16" s="139"/>
+      <c r="N16" s="139"/>
+      <c r="O16" s="139"/>
+      <c r="P16" s="139"/>
+      <c r="Q16" s="139"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="139"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="139"/>
+      <c r="V16" s="139"/>
+      <c r="W16" s="139"/>
+      <c r="X16" s="139"/>
+      <c r="Y16" s="139"/>
+      <c r="Z16" s="139"/>
+      <c r="AA16" s="139"/>
+      <c r="AB16" s="139"/>
+      <c r="AC16" s="139"/>
+      <c r="AD16" s="139"/>
+      <c r="AE16" s="139"/>
+      <c r="AF16" s="139"/>
+      <c r="AG16" s="139"/>
+      <c r="AH16" s="139"/>
+      <c r="AI16" s="139"/>
+      <c r="AJ16" s="139"/>
+      <c r="AK16" s="139"/>
+      <c r="AL16" s="139"/>
+      <c r="AM16" s="139"/>
     </row>
     <row r="17" spans="1:39">
       <c r="A17" s="175"/>
       <c r="B17" s="175"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="144"/>
-      <c r="J17" s="144"/>
-      <c r="K17" s="144"/>
-      <c r="L17" s="144"/>
-      <c r="M17" s="144"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="144"/>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144"/>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
-      <c r="U17" s="144"/>
-      <c r="V17" s="144"/>
-      <c r="W17" s="144"/>
-      <c r="X17" s="144"/>
-      <c r="Y17" s="144"/>
-      <c r="Z17" s="144"/>
-      <c r="AA17" s="144"/>
-      <c r="AB17" s="144"/>
-      <c r="AC17" s="144"/>
-      <c r="AD17" s="144"/>
-      <c r="AE17" s="144"/>
-      <c r="AF17" s="144"/>
-      <c r="AG17" s="144"/>
-      <c r="AH17" s="144"/>
-      <c r="AI17" s="144"/>
-      <c r="AJ17" s="144"/>
-      <c r="AK17" s="144"/>
-      <c r="AL17" s="144"/>
-      <c r="AM17" s="144"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="139"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="139"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="139"/>
+      <c r="K17" s="139"/>
+      <c r="L17" s="139"/>
+      <c r="M17" s="139"/>
+      <c r="N17" s="139"/>
+      <c r="O17" s="139"/>
+      <c r="P17" s="139"/>
+      <c r="Q17" s="139"/>
+      <c r="R17" s="139"/>
+      <c r="S17" s="139"/>
+      <c r="T17" s="139"/>
+      <c r="U17" s="139"/>
+      <c r="V17" s="139"/>
+      <c r="W17" s="139"/>
+      <c r="X17" s="139"/>
+      <c r="Y17" s="139"/>
+      <c r="Z17" s="139"/>
+      <c r="AA17" s="139"/>
+      <c r="AB17" s="139"/>
+      <c r="AC17" s="139"/>
+      <c r="AD17" s="139"/>
+      <c r="AE17" s="139"/>
+      <c r="AF17" s="139"/>
+      <c r="AG17" s="139"/>
+      <c r="AH17" s="139"/>
+      <c r="AI17" s="139"/>
+      <c r="AJ17" s="139"/>
+      <c r="AK17" s="139"/>
+      <c r="AL17" s="139"/>
+      <c r="AM17" s="139"/>
     </row>
     <row r="19" spans="1:39">
       <c r="A19" s="68" t="s">
@@ -14993,40 +15005,6 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="Y16:AB17"/>
-    <mergeCell ref="AC16:AH17"/>
-    <mergeCell ref="AI16:AM17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="J16:L17"/>
-    <mergeCell ref="M16:O17"/>
-    <mergeCell ref="P16:R17"/>
-    <mergeCell ref="S16:U17"/>
-    <mergeCell ref="V16:X17"/>
-    <mergeCell ref="AI14:AM15"/>
-    <mergeCell ref="J10:L11"/>
-    <mergeCell ref="P10:R11"/>
-    <mergeCell ref="M10:O11"/>
-    <mergeCell ref="S10:U11"/>
-    <mergeCell ref="V10:X11"/>
-    <mergeCell ref="Y10:AB11"/>
-    <mergeCell ref="AC10:AH11"/>
-    <mergeCell ref="AI12:AM13"/>
-    <mergeCell ref="AI10:AM11"/>
-    <mergeCell ref="P14:R15"/>
-    <mergeCell ref="S14:U15"/>
-    <mergeCell ref="V14:X15"/>
-    <mergeCell ref="Y14:AB15"/>
-    <mergeCell ref="AC14:AH15"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="AC9:AH9"/>
-    <mergeCell ref="P12:R13"/>
-    <mergeCell ref="S12:U13"/>
-    <mergeCell ref="V12:X13"/>
-    <mergeCell ref="Y12:AB13"/>
-    <mergeCell ref="AC12:AH13"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="S9:U9"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="AI8:AM9"/>
     <mergeCell ref="M1:AL1"/>
@@ -15043,6 +15021,40 @@
     <mergeCell ref="C10:I11"/>
     <mergeCell ref="C12:I13"/>
     <mergeCell ref="A8:I9"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="Y9:AB9"/>
+    <mergeCell ref="AC9:AH9"/>
+    <mergeCell ref="P12:R13"/>
+    <mergeCell ref="S12:U13"/>
+    <mergeCell ref="V12:X13"/>
+    <mergeCell ref="Y12:AB13"/>
+    <mergeCell ref="AC12:AH13"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="AI14:AM15"/>
+    <mergeCell ref="J10:L11"/>
+    <mergeCell ref="P10:R11"/>
+    <mergeCell ref="M10:O11"/>
+    <mergeCell ref="S10:U11"/>
+    <mergeCell ref="V10:X11"/>
+    <mergeCell ref="Y10:AB11"/>
+    <mergeCell ref="AC10:AH11"/>
+    <mergeCell ref="AI12:AM13"/>
+    <mergeCell ref="AI10:AM11"/>
+    <mergeCell ref="P14:R15"/>
+    <mergeCell ref="S14:U15"/>
+    <mergeCell ref="V14:X15"/>
+    <mergeCell ref="Y14:AB15"/>
+    <mergeCell ref="AC14:AH15"/>
+    <mergeCell ref="Y16:AB17"/>
+    <mergeCell ref="AC16:AH17"/>
+    <mergeCell ref="AI16:AM17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="J16:L17"/>
+    <mergeCell ref="M16:O17"/>
+    <mergeCell ref="P16:R17"/>
+    <mergeCell ref="S16:U17"/>
+    <mergeCell ref="V16:X17"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/wwwroot/ExcelModel/Kik_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Kik_PHY_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6858BC92-7C90-4706-8409-DCAF60DA23A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11C42FE-670E-456F-9B6B-0C4CF422D5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2316,74 +2316,104 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2430,41 +2460,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2472,22 +2487,25 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2497,28 +2515,37 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
@@ -2533,31 +2560,13 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2578,13 +2587,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2603,9 +2606,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2954,25 +2954,25 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="98"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -3203,185 +3203,185 @@
       </c>
       <c r="F11" s="82"/>
       <c r="G11" s="82"/>
-      <c r="H11" s="79"/>
+      <c r="H11" s="95"/>
       <c r="I11" s="81" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="82"/>
       <c r="K11" s="82"/>
-      <c r="L11" s="79"/>
+      <c r="L11" s="95"/>
       <c r="M11" s="81" t="s">
         <v>11</v>
       </c>
       <c r="N11" s="82"/>
       <c r="O11" s="82"/>
-      <c r="P11" s="79"/>
+      <c r="P11" s="95"/>
       <c r="Q11" s="81" t="s">
         <v>12</v>
       </c>
       <c r="R11" s="82"/>
       <c r="S11" s="82"/>
-      <c r="T11" s="79"/>
+      <c r="T11" s="95"/>
       <c r="U11" s="81" t="s">
         <v>13</v>
       </c>
       <c r="V11" s="82"/>
       <c r="W11" s="82"/>
-      <c r="X11" s="78"/>
+      <c r="X11" s="96"/>
       <c r="Y11" s="86"/>
       <c r="Z11" s="87"/>
       <c r="AA11" s="87"/>
       <c r="AB11" s="88"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="97"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="78"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="77"/>
-      <c r="R12" s="78"/>
-      <c r="S12" s="78"/>
-      <c r="T12" s="79"/>
-      <c r="U12" s="77"/>
-      <c r="V12" s="78"/>
-      <c r="W12" s="78"/>
-      <c r="X12" s="79"/>
-      <c r="Y12" s="77"/>
-      <c r="Z12" s="78"/>
-      <c r="AA12" s="78"/>
-      <c r="AB12" s="79"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="95"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="96"/>
+      <c r="O12" s="96"/>
+      <c r="P12" s="95"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="96"/>
+      <c r="T12" s="95"/>
+      <c r="U12" s="99"/>
+      <c r="V12" s="96"/>
+      <c r="W12" s="96"/>
+      <c r="X12" s="95"/>
+      <c r="Y12" s="99"/>
+      <c r="Z12" s="96"/>
+      <c r="AA12" s="96"/>
+      <c r="AB12" s="95"/>
     </row>
     <row r="13" spans="1:28">
-      <c r="A13" s="97"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="77"/>
-      <c r="N13" s="78"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="79"/>
-      <c r="Q13" s="77"/>
-      <c r="R13" s="78"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="79"/>
-      <c r="U13" s="77"/>
-      <c r="V13" s="78"/>
-      <c r="W13" s="78"/>
-      <c r="X13" s="79"/>
-      <c r="Y13" s="77"/>
-      <c r="Z13" s="78"/>
-      <c r="AA13" s="78"/>
-      <c r="AB13" s="79"/>
+      <c r="A13" s="77"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="95"/>
+      <c r="Q13" s="99"/>
+      <c r="R13" s="96"/>
+      <c r="S13" s="96"/>
+      <c r="T13" s="95"/>
+      <c r="U13" s="99"/>
+      <c r="V13" s="96"/>
+      <c r="W13" s="96"/>
+      <c r="X13" s="95"/>
+      <c r="Y13" s="99"/>
+      <c r="Z13" s="96"/>
+      <c r="AA13" s="96"/>
+      <c r="AB13" s="95"/>
     </row>
     <row r="14" spans="1:28">
-      <c r="A14" s="97"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="77"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="79"/>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="79"/>
-      <c r="U14" s="77"/>
-      <c r="V14" s="78"/>
-      <c r="W14" s="78"/>
-      <c r="X14" s="79"/>
-      <c r="Y14" s="77"/>
-      <c r="Z14" s="78"/>
-      <c r="AA14" s="78"/>
-      <c r="AB14" s="79"/>
+      <c r="A14" s="77"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="99"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="95"/>
+      <c r="Q14" s="99"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
+      <c r="T14" s="95"/>
+      <c r="U14" s="99"/>
+      <c r="V14" s="96"/>
+      <c r="W14" s="96"/>
+      <c r="X14" s="95"/>
+      <c r="Y14" s="99"/>
+      <c r="Z14" s="96"/>
+      <c r="AA14" s="96"/>
+      <c r="AB14" s="95"/>
     </row>
     <row r="15" spans="1:28">
-      <c r="A15" s="97"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="77"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="79"/>
-      <c r="Q15" s="77"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="79"/>
-      <c r="U15" s="77"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="79"/>
-      <c r="Y15" s="77"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="78"/>
-      <c r="AB15" s="79"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="95"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="96"/>
+      <c r="S15" s="96"/>
+      <c r="T15" s="95"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="96"/>
+      <c r="W15" s="96"/>
+      <c r="X15" s="95"/>
+      <c r="Y15" s="99"/>
+      <c r="Z15" s="96"/>
+      <c r="AA15" s="96"/>
+      <c r="AB15" s="95"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="97"/>
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="77"/>
-      <c r="N16" s="78"/>
-      <c r="O16" s="78"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="77"/>
-      <c r="R16" s="78"/>
-      <c r="S16" s="78"/>
-      <c r="T16" s="79"/>
-      <c r="U16" s="77"/>
-      <c r="V16" s="78"/>
-      <c r="W16" s="78"/>
-      <c r="X16" s="79"/>
-      <c r="Y16" s="77"/>
-      <c r="Z16" s="78"/>
-      <c r="AA16" s="78"/>
-      <c r="AB16" s="79"/>
+      <c r="A16" s="77"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="95"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="95"/>
+      <c r="U16" s="99"/>
+      <c r="V16" s="96"/>
+      <c r="W16" s="96"/>
+      <c r="X16" s="95"/>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="96"/>
+      <c r="AA16" s="96"/>
+      <c r="AB16" s="95"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="3" t="s">
@@ -3524,32 +3524,14 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="J1:AB1"/>
-    <mergeCell ref="E10:X10"/>
-    <mergeCell ref="Y10:AB11"/>
-    <mergeCell ref="A10:D11"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:P11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="Y12:AB12"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="Y13:AB13"/>
+    <mergeCell ref="U14:X14"/>
+    <mergeCell ref="Y14:AB14"/>
     <mergeCell ref="M15:P15"/>
     <mergeCell ref="Q15:T15"/>
     <mergeCell ref="M16:P16"/>
@@ -3562,14 +3544,32 @@
     <mergeCell ref="Q13:T13"/>
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="Y15:AB15"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="Y12:AB12"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="Y13:AB13"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="Y14:AB14"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="J1:AB1"/>
+    <mergeCell ref="E10:X10"/>
+    <mergeCell ref="Y10:AB11"/>
+    <mergeCell ref="A10:D11"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3610,32 +3610,32 @@
       <c r="J1" s="41"/>
       <c r="K1" s="41"/>
       <c r="L1" s="41"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="121"/>
-      <c r="AK1" s="121"/>
-      <c r="AL1" s="121"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
+      <c r="AC1" s="106"/>
+      <c r="AD1" s="106"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
+      <c r="AG1" s="106"/>
+      <c r="AH1" s="106"/>
+      <c r="AI1" s="106"/>
+      <c r="AJ1" s="106"/>
+      <c r="AK1" s="106"/>
+      <c r="AL1" s="106"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="42" t="s">
@@ -3671,17 +3671,17 @@
       <c r="AF2" s="39"/>
     </row>
     <row r="3" spans="1:38" ht="15.75" customHeight="1">
-      <c r="A3" s="122"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
+      <c r="A3" s="107"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
       <c r="L3" s="39"/>
       <c r="M3" s="39"/>
       <c r="N3" s="39"/>
@@ -3898,45 +3898,45 @@
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="115" t="s">
+      <c r="D10" s="108"/>
+      <c r="E10" s="109"/>
+      <c r="F10" s="100" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="116"/>
-      <c r="H10" s="116"/>
-      <c r="I10" s="116"/>
-      <c r="J10" s="116"/>
-      <c r="K10" s="116"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="116"/>
-      <c r="O10" s="117"/>
-      <c r="P10" s="115" t="s">
+      <c r="G10" s="101"/>
+      <c r="H10" s="101"/>
+      <c r="I10" s="101"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="101"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="100" t="s">
         <v>85</v>
       </c>
-      <c r="Q10" s="116"/>
-      <c r="R10" s="116"/>
-      <c r="S10" s="116"/>
-      <c r="T10" s="116"/>
-      <c r="U10" s="116"/>
-      <c r="V10" s="116"/>
-      <c r="W10" s="116"/>
-      <c r="X10" s="116"/>
-      <c r="Y10" s="116"/>
-      <c r="Z10" s="116"/>
-      <c r="AA10" s="116"/>
-      <c r="AB10" s="116"/>
-      <c r="AC10" s="116"/>
-      <c r="AD10" s="116"/>
-      <c r="AE10" s="116"/>
-      <c r="AF10" s="116"/>
-      <c r="AG10" s="116"/>
-      <c r="AH10" s="116"/>
-      <c r="AI10" s="116"/>
-      <c r="AJ10" s="116"/>
-      <c r="AK10" s="116"/>
-      <c r="AL10" s="117"/>
+      <c r="Q10" s="101"/>
+      <c r="R10" s="101"/>
+      <c r="S10" s="101"/>
+      <c r="T10" s="101"/>
+      <c r="U10" s="101"/>
+      <c r="V10" s="101"/>
+      <c r="W10" s="101"/>
+      <c r="X10" s="101"/>
+      <c r="Y10" s="101"/>
+      <c r="Z10" s="101"/>
+      <c r="AA10" s="101"/>
+      <c r="AB10" s="101"/>
+      <c r="AC10" s="101"/>
+      <c r="AD10" s="101"/>
+      <c r="AE10" s="101"/>
+      <c r="AF10" s="101"/>
+      <c r="AG10" s="101"/>
+      <c r="AH10" s="101"/>
+      <c r="AI10" s="101"/>
+      <c r="AJ10" s="101"/>
+      <c r="AK10" s="101"/>
+      <c r="AL10" s="102"/>
     </row>
     <row r="11" spans="1:38">
       <c r="A11" s="43" t="s">
@@ -3946,62 +3946,62 @@
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
       <c r="E11" s="46"/>
-      <c r="F11" s="115" t="s">
+      <c r="F11" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="117"/>
-      <c r="K11" s="115" t="s">
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="116"/>
-      <c r="M11" s="116"/>
-      <c r="N11" s="116"/>
-      <c r="O11" s="117"/>
-      <c r="P11" s="115" t="s">
+      <c r="L11" s="101"/>
+      <c r="M11" s="101"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="102"/>
+      <c r="P11" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" s="116"/>
-      <c r="R11" s="116"/>
-      <c r="S11" s="116"/>
-      <c r="T11" s="117"/>
-      <c r="U11" s="115" t="s">
+      <c r="Q11" s="101"/>
+      <c r="R11" s="101"/>
+      <c r="S11" s="101"/>
+      <c r="T11" s="102"/>
+      <c r="U11" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="V11" s="116"/>
-      <c r="W11" s="116"/>
-      <c r="X11" s="116"/>
-      <c r="Y11" s="117"/>
-      <c r="Z11" s="115" t="s">
+      <c r="V11" s="101"/>
+      <c r="W11" s="101"/>
+      <c r="X11" s="101"/>
+      <c r="Y11" s="102"/>
+      <c r="Z11" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="116"/>
-      <c r="AB11" s="116"/>
-      <c r="AC11" s="116"/>
-      <c r="AD11" s="117"/>
-      <c r="AE11" s="115" t="s">
+      <c r="AA11" s="101"/>
+      <c r="AB11" s="101"/>
+      <c r="AC11" s="101"/>
+      <c r="AD11" s="102"/>
+      <c r="AE11" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="AF11" s="116"/>
-      <c r="AG11" s="116"/>
-      <c r="AH11" s="116"/>
-      <c r="AI11" s="117"/>
-      <c r="AJ11" s="118" t="s">
+      <c r="AF11" s="101"/>
+      <c r="AG11" s="101"/>
+      <c r="AH11" s="101"/>
+      <c r="AI11" s="102"/>
+      <c r="AJ11" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="119"/>
-      <c r="AL11" s="120"/>
+      <c r="AK11" s="104"/>
+      <c r="AL11" s="105"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="110" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="112"/>
       <c r="F12" s="47"/>
       <c r="G12" s="48"/>
       <c r="H12" s="48"/>
@@ -4037,11 +4037,11 @@
       <c r="AL12" s="52"/>
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A13" s="103"/>
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="105"/>
+      <c r="A13" s="113"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
       <c r="F13" s="53"/>
       <c r="G13" s="54"/>
       <c r="H13" s="54"/>
@@ -4077,13 +4077,13 @@
       <c r="AL13" s="58"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="110" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="102"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="112"/>
       <c r="F14" s="47"/>
       <c r="G14" s="48"/>
       <c r="H14" s="48"/>
@@ -4119,11 +4119,11 @@
       <c r="AL14" s="52"/>
     </row>
     <row r="15" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A15" s="103"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="105"/>
+      <c r="A15" s="113"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="115"/>
       <c r="F15" s="53"/>
       <c r="G15" s="54"/>
       <c r="H15" s="54"/>
@@ -4159,13 +4159,13 @@
       <c r="AL15" s="58"/>
     </row>
     <row r="16" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="110" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="102"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
       <c r="F16" s="47"/>
       <c r="G16" s="48"/>
       <c r="H16" s="48"/>
@@ -4201,11 +4201,11 @@
       <c r="AL16" s="52"/>
     </row>
     <row r="17" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A17" s="103"/>
-      <c r="B17" s="104"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="105"/>
+      <c r="A17" s="113"/>
+      <c r="B17" s="114"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="115"/>
       <c r="F17" s="53"/>
       <c r="G17" s="54"/>
       <c r="H17" s="54"/>
@@ -4241,13 +4241,13 @@
       <c r="AL17" s="58"/>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A18" s="100" t="s">
+      <c r="A18" s="110" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="101"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="102"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
       <c r="F18" s="47"/>
       <c r="G18" s="48"/>
       <c r="H18" s="48"/>
@@ -4283,11 +4283,11 @@
       <c r="AL18" s="52"/>
     </row>
     <row r="19" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A19" s="103"/>
-      <c r="B19" s="104"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="105"/>
+      <c r="A19" s="113"/>
+      <c r="B19" s="114"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="115"/>
       <c r="F19" s="53"/>
       <c r="G19" s="54"/>
       <c r="H19" s="54"/>
@@ -4323,13 +4323,13 @@
       <c r="AL19" s="58"/>
     </row>
     <row r="20" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="110" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="101"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="102"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="112"/>
       <c r="F20" s="47"/>
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
@@ -4365,11 +4365,11 @@
       <c r="AL20" s="52"/>
     </row>
     <row r="21" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A21" s="103"/>
-      <c r="B21" s="104"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="105"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="115"/>
       <c r="F21" s="53"/>
       <c r="G21" s="54"/>
       <c r="H21" s="54"/>
@@ -4405,13 +4405,13 @@
       <c r="AL21" s="58"/>
     </row>
     <row r="22" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A22" s="100" t="s">
+      <c r="A22" s="110" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="101"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="102"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
       <c r="F22" s="47"/>
       <c r="G22" s="48"/>
       <c r="H22" s="48"/>
@@ -4447,11 +4447,11 @@
       <c r="AL22" s="52"/>
     </row>
     <row r="23" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A23" s="103"/>
-      <c r="B23" s="104"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="105"/>
+      <c r="A23" s="113"/>
+      <c r="B23" s="114"/>
+      <c r="C23" s="114"/>
+      <c r="D23" s="114"/>
+      <c r="E23" s="115"/>
       <c r="F23" s="53"/>
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
@@ -4487,13 +4487,13 @@
       <c r="AL23" s="58"/>
     </row>
     <row r="24" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A24" s="100" t="s">
+      <c r="A24" s="110" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="101"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="102"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="112"/>
       <c r="F24" s="47"/>
       <c r="G24" s="48"/>
       <c r="H24" s="48"/>
@@ -4529,11 +4529,11 @@
       <c r="AL24" s="52"/>
     </row>
     <row r="25" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A25" s="103"/>
-      <c r="B25" s="104"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="105"/>
+      <c r="A25" s="113"/>
+      <c r="B25" s="114"/>
+      <c r="C25" s="114"/>
+      <c r="D25" s="114"/>
+      <c r="E25" s="115"/>
       <c r="F25" s="53"/>
       <c r="G25" s="54"/>
       <c r="H25" s="54"/>
@@ -4569,13 +4569,13 @@
       <c r="AL25" s="58"/>
     </row>
     <row r="26" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A26" s="100" t="s">
+      <c r="A26" s="110" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="102"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="112"/>
       <c r="F26" s="47"/>
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
@@ -4611,11 +4611,11 @@
       <c r="AL26" s="52"/>
     </row>
     <row r="27" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A27" s="103"/>
-      <c r="B27" s="104"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="105"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="114"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="115"/>
       <c r="F27" s="53"/>
       <c r="G27" s="54"/>
       <c r="H27" s="54"/>
@@ -4651,13 +4651,13 @@
       <c r="AL27" s="58"/>
     </row>
     <row r="28" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="110" t="s">
         <v>100</v>
       </c>
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="102"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
       <c r="F28" s="47"/>
       <c r="G28" s="48"/>
       <c r="H28" s="48"/>
@@ -4693,11 +4693,11 @@
       <c r="AL28" s="52"/>
     </row>
     <row r="29" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A29" s="103"/>
-      <c r="B29" s="104"/>
-      <c r="C29" s="104"/>
-      <c r="D29" s="104"/>
-      <c r="E29" s="105"/>
+      <c r="A29" s="113"/>
+      <c r="B29" s="114"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="115"/>
       <c r="F29" s="53"/>
       <c r="G29" s="54"/>
       <c r="H29" s="54"/>
@@ -4733,13 +4733,13 @@
       <c r="AL29" s="58"/>
     </row>
     <row r="30" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A30" s="100" t="s">
+      <c r="A30" s="110" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="101"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="102"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="112"/>
       <c r="F30" s="47"/>
       <c r="G30" s="48"/>
       <c r="H30" s="48"/>
@@ -4775,11 +4775,11 @@
       <c r="AL30" s="52"/>
     </row>
     <row r="31" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A31" s="103"/>
-      <c r="B31" s="104"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="105"/>
+      <c r="A31" s="113"/>
+      <c r="B31" s="114"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="114"/>
+      <c r="E31" s="115"/>
       <c r="F31" s="53"/>
       <c r="G31" s="54"/>
       <c r="H31" s="54"/>
@@ -4815,13 +4815,13 @@
       <c r="AL31" s="58"/>
     </row>
     <row r="32" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A32" s="100" t="s">
+      <c r="A32" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="101"/>
-      <c r="C32" s="101"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="101"/>
+      <c r="B32" s="111"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
       <c r="F32" s="47"/>
       <c r="G32" s="48"/>
       <c r="H32" s="48"/>
@@ -4857,11 +4857,11 @@
       <c r="AL32" s="52"/>
     </row>
     <row r="33" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A33" s="103"/>
-      <c r="B33" s="104"/>
-      <c r="C33" s="104"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="104"/>
+      <c r="A33" s="113"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="114"/>
+      <c r="E33" s="114"/>
       <c r="F33" s="53"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
@@ -4897,13 +4897,13 @@
       <c r="AL33" s="58"/>
     </row>
     <row r="34" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A34" s="100" t="s">
+      <c r="A34" s="110" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="101"/>
-      <c r="C34" s="101"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
+      <c r="B34" s="111"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
       <c r="F34" s="47"/>
       <c r="G34" s="48"/>
       <c r="H34" s="48"/>
@@ -4939,11 +4939,11 @@
       <c r="AL34" s="52"/>
     </row>
     <row r="35" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A35" s="103"/>
-      <c r="B35" s="104"/>
-      <c r="C35" s="104"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="105"/>
+      <c r="A35" s="113"/>
+      <c r="B35" s="114"/>
+      <c r="C35" s="114"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="115"/>
       <c r="F35" s="53"/>
       <c r="G35" s="54"/>
       <c r="H35" s="54"/>
@@ -4979,13 +4979,13 @@
       <c r="AL35" s="58"/>
     </row>
     <row r="36" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="107"/>
-      <c r="C36" s="107"/>
-      <c r="D36" s="107"/>
-      <c r="E36" s="108"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="118"/>
       <c r="F36" s="47"/>
       <c r="G36" s="48"/>
       <c r="H36" s="48"/>
@@ -5021,11 +5021,11 @@
       <c r="AL36" s="52"/>
     </row>
     <row r="37" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A37" s="109"/>
-      <c r="B37" s="110"/>
-      <c r="C37" s="110"/>
-      <c r="D37" s="110"/>
-      <c r="E37" s="111"/>
+      <c r="A37" s="119"/>
+      <c r="B37" s="120"/>
+      <c r="C37" s="120"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="121"/>
       <c r="F37" s="53"/>
       <c r="G37" s="54"/>
       <c r="H37" s="54"/>
@@ -5094,21 +5094,21 @@
       <c r="AF38" s="39"/>
     </row>
     <row r="39" spans="1:38">
-      <c r="A39" s="112" t="s">
+      <c r="A39" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="112"/>
-      <c r="C39" s="112"/>
-      <c r="D39" s="113" t="s">
+      <c r="B39" s="122"/>
+      <c r="C39" s="122"/>
+      <c r="D39" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="113"/>
-      <c r="F39" s="113"/>
-      <c r="G39" s="113"/>
-      <c r="H39" s="113"/>
-      <c r="I39" s="113"/>
-      <c r="J39" s="113"/>
-      <c r="K39" s="113"/>
+      <c r="E39" s="123"/>
+      <c r="F39" s="123"/>
+      <c r="G39" s="123"/>
+      <c r="H39" s="123"/>
+      <c r="I39" s="123"/>
+      <c r="J39" s="123"/>
+      <c r="K39" s="123"/>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
       <c r="N39" s="39"/>
@@ -5132,19 +5132,19 @@
       <c r="AF39" s="39"/>
     </row>
     <row r="40" spans="1:38">
-      <c r="A40" s="112"/>
-      <c r="B40" s="112"/>
-      <c r="C40" s="112"/>
-      <c r="D40" s="114" t="s">
+      <c r="A40" s="122"/>
+      <c r="B40" s="122"/>
+      <c r="C40" s="122"/>
+      <c r="D40" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="E40" s="114"/>
-      <c r="F40" s="114"/>
-      <c r="G40" s="114"/>
-      <c r="H40" s="114"/>
-      <c r="I40" s="114"/>
-      <c r="J40" s="114"/>
-      <c r="K40" s="114"/>
+      <c r="E40" s="124"/>
+      <c r="F40" s="124"/>
+      <c r="G40" s="124"/>
+      <c r="H40" s="124"/>
+      <c r="I40" s="124"/>
+      <c r="J40" s="124"/>
+      <c r="K40" s="124"/>
       <c r="L40" s="39"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
@@ -5363,13 +5363,13 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="AE11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="P10:AL10"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="A32:E33"/>
+    <mergeCell ref="A34:E35"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:K39"/>
+    <mergeCell ref="D40:K40"/>
     <mergeCell ref="A12:E13"/>
     <mergeCell ref="A14:E15"/>
     <mergeCell ref="A16:E17"/>
@@ -5384,13 +5384,13 @@
     <mergeCell ref="K11:O11"/>
     <mergeCell ref="P11:T11"/>
     <mergeCell ref="U11:Y11"/>
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="A32:E33"/>
-    <mergeCell ref="A34:E35"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="AE11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="P10:AL10"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5597,238 +5597,238 @@
       <c r="AL5" s="1"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="132" t="s">
+      <c r="A6" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132"/>
-      <c r="G6" s="132"/>
-      <c r="H6" s="127" t="s">
+      <c r="B6" s="128"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="127"/>
-      <c r="J6" s="127"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="128" t="s">
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
+      <c r="L6" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="128"/>
-      <c r="N6" s="128"/>
-      <c r="O6" s="128"/>
-      <c r="P6" s="128"/>
-      <c r="Q6" s="128"/>
-      <c r="R6" s="128"/>
-      <c r="S6" s="128"/>
-      <c r="T6" s="128"/>
-      <c r="U6" s="128"/>
-      <c r="V6" s="128"/>
-      <c r="W6" s="128"/>
-      <c r="X6" s="127" t="s">
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
+      <c r="O6" s="133"/>
+      <c r="P6" s="133"/>
+      <c r="Q6" s="133"/>
+      <c r="R6" s="133"/>
+      <c r="S6" s="133"/>
+      <c r="T6" s="133"/>
+      <c r="U6" s="133"/>
+      <c r="V6" s="133"/>
+      <c r="W6" s="133"/>
+      <c r="X6" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="Y6" s="127"/>
-      <c r="Z6" s="127"/>
-      <c r="AA6" s="127"/>
-      <c r="AB6" s="128" t="s">
+      <c r="Y6" s="132"/>
+      <c r="Z6" s="132"/>
+      <c r="AA6" s="132"/>
+      <c r="AB6" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="AC6" s="128"/>
-      <c r="AD6" s="128"/>
-      <c r="AE6" s="128"/>
-      <c r="AF6" s="128"/>
-      <c r="AG6" s="128"/>
-      <c r="AH6" s="128"/>
-      <c r="AI6" s="128"/>
-      <c r="AJ6" s="128"/>
-      <c r="AK6" s="128"/>
-      <c r="AL6" s="128"/>
+      <c r="AC6" s="133"/>
+      <c r="AD6" s="133"/>
+      <c r="AE6" s="133"/>
+      <c r="AF6" s="133"/>
+      <c r="AG6" s="133"/>
+      <c r="AH6" s="133"/>
+      <c r="AI6" s="133"/>
+      <c r="AJ6" s="133"/>
+      <c r="AK6" s="133"/>
+      <c r="AL6" s="133"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
-      <c r="A7" s="132"/>
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="128" t="s">
+      <c r="A7" s="128"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="128"/>
-      <c r="N7" s="128"/>
-      <c r="O7" s="128"/>
-      <c r="P7" s="128" t="s">
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="Q7" s="128"/>
-      <c r="R7" s="128"/>
-      <c r="S7" s="128"/>
-      <c r="T7" s="128" t="s">
+      <c r="Q7" s="133"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="133"/>
+      <c r="T7" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="U7" s="128"/>
-      <c r="V7" s="128"/>
-      <c r="W7" s="128"/>
-      <c r="X7" s="127"/>
-      <c r="Y7" s="127"/>
-      <c r="Z7" s="127"/>
-      <c r="AA7" s="127"/>
-      <c r="AB7" s="128" t="s">
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="133"/>
+      <c r="X7" s="132"/>
+      <c r="Y7" s="132"/>
+      <c r="Z7" s="132"/>
+      <c r="AA7" s="132"/>
+      <c r="AB7" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="AC7" s="128"/>
-      <c r="AD7" s="128"/>
-      <c r="AE7" s="128"/>
-      <c r="AF7" s="128" t="s">
+      <c r="AC7" s="133"/>
+      <c r="AD7" s="133"/>
+      <c r="AE7" s="133"/>
+      <c r="AF7" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="AG7" s="128"/>
-      <c r="AH7" s="128"/>
-      <c r="AI7" s="128"/>
-      <c r="AJ7" s="128" t="s">
+      <c r="AG7" s="133"/>
+      <c r="AH7" s="133"/>
+      <c r="AI7" s="133"/>
+      <c r="AJ7" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="AK7" s="128"/>
-      <c r="AL7" s="128"/>
+      <c r="AK7" s="133"/>
+      <c r="AL7" s="133"/>
     </row>
     <row r="8" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A8" s="133"/>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
+      <c r="A8" s="125"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
       <c r="H8" s="126">
         <v>125</v>
       </c>
       <c r="I8" s="126"/>
       <c r="J8" s="126"/>
       <c r="K8" s="126"/>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
-      <c r="P8" s="125"/>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="125"/>
-      <c r="U8" s="125"/>
-      <c r="V8" s="125"/>
-      <c r="W8" s="125"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="127"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="127"/>
+      <c r="U8" s="127"/>
+      <c r="V8" s="127"/>
+      <c r="W8" s="127"/>
       <c r="X8" s="126">
         <v>2000</v>
       </c>
       <c r="Y8" s="126"/>
       <c r="Z8" s="126"/>
       <c r="AA8" s="126"/>
-      <c r="AB8" s="125"/>
-      <c r="AC8" s="125"/>
-      <c r="AD8" s="125"/>
-      <c r="AE8" s="125"/>
-      <c r="AF8" s="125"/>
-      <c r="AG8" s="125"/>
-      <c r="AH8" s="125"/>
-      <c r="AI8" s="125"/>
-      <c r="AJ8" s="125"/>
-      <c r="AK8" s="125"/>
-      <c r="AL8" s="125"/>
+      <c r="AB8" s="127"/>
+      <c r="AC8" s="127"/>
+      <c r="AD8" s="127"/>
+      <c r="AE8" s="127"/>
+      <c r="AF8" s="127"/>
+      <c r="AG8" s="127"/>
+      <c r="AH8" s="127"/>
+      <c r="AI8" s="127"/>
+      <c r="AJ8" s="127"/>
+      <c r="AK8" s="127"/>
+      <c r="AL8" s="127"/>
     </row>
     <row r="9" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A9" s="133"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
+      <c r="A9" s="125"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="126">
         <v>500</v>
       </c>
       <c r="I9" s="126"/>
       <c r="J9" s="126"/>
       <c r="K9" s="126"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="125"/>
-      <c r="N9" s="125"/>
-      <c r="O9" s="125"/>
-      <c r="P9" s="125"/>
-      <c r="Q9" s="125"/>
-      <c r="R9" s="125"/>
-      <c r="S9" s="125"/>
-      <c r="T9" s="125"/>
-      <c r="U9" s="125"/>
-      <c r="V9" s="125"/>
-      <c r="W9" s="125"/>
+      <c r="L9" s="127"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="127"/>
+      <c r="O9" s="127"/>
+      <c r="P9" s="127"/>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="127"/>
+      <c r="T9" s="127"/>
+      <c r="U9" s="127"/>
+      <c r="V9" s="127"/>
+      <c r="W9" s="127"/>
       <c r="X9" s="126">
         <v>5000</v>
       </c>
       <c r="Y9" s="126"/>
       <c r="Z9" s="126"/>
       <c r="AA9" s="126"/>
-      <c r="AB9" s="125"/>
-      <c r="AC9" s="125"/>
-      <c r="AD9" s="125"/>
-      <c r="AE9" s="125"/>
-      <c r="AF9" s="125"/>
-      <c r="AG9" s="125"/>
-      <c r="AH9" s="125"/>
-      <c r="AI9" s="125"/>
-      <c r="AJ9" s="125"/>
-      <c r="AK9" s="125"/>
-      <c r="AL9" s="125"/>
+      <c r="AB9" s="127"/>
+      <c r="AC9" s="127"/>
+      <c r="AD9" s="127"/>
+      <c r="AE9" s="127"/>
+      <c r="AF9" s="127"/>
+      <c r="AG9" s="127"/>
+      <c r="AH9" s="127"/>
+      <c r="AI9" s="127"/>
+      <c r="AJ9" s="127"/>
+      <c r="AK9" s="127"/>
+      <c r="AL9" s="127"/>
     </row>
     <row r="10" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A10" s="133"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
+      <c r="A10" s="125"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
       <c r="H10" s="126">
         <v>1000</v>
       </c>
       <c r="I10" s="126"/>
       <c r="J10" s="126"/>
       <c r="K10" s="126"/>
-      <c r="L10" s="125"/>
-      <c r="M10" s="125"/>
-      <c r="N10" s="125"/>
-      <c r="O10" s="125"/>
-      <c r="P10" s="125"/>
-      <c r="Q10" s="125"/>
-      <c r="R10" s="125"/>
-      <c r="S10" s="125"/>
-      <c r="T10" s="125"/>
-      <c r="U10" s="125"/>
-      <c r="V10" s="125"/>
-      <c r="W10" s="125"/>
+      <c r="L10" s="127"/>
+      <c r="M10" s="127"/>
+      <c r="N10" s="127"/>
+      <c r="O10" s="127"/>
+      <c r="P10" s="127"/>
+      <c r="Q10" s="127"/>
+      <c r="R10" s="127"/>
+      <c r="S10" s="127"/>
+      <c r="T10" s="127"/>
+      <c r="U10" s="127"/>
+      <c r="V10" s="127"/>
+      <c r="W10" s="127"/>
       <c r="X10" s="126">
         <v>7000</v>
       </c>
       <c r="Y10" s="126"/>
       <c r="Z10" s="126"/>
       <c r="AA10" s="126"/>
-      <c r="AB10" s="125"/>
-      <c r="AC10" s="125"/>
-      <c r="AD10" s="125"/>
-      <c r="AE10" s="125"/>
-      <c r="AF10" s="125"/>
-      <c r="AG10" s="125"/>
-      <c r="AH10" s="125"/>
-      <c r="AI10" s="125"/>
-      <c r="AJ10" s="125"/>
-      <c r="AK10" s="125"/>
-      <c r="AL10" s="125"/>
+      <c r="AB10" s="127"/>
+      <c r="AC10" s="127"/>
+      <c r="AD10" s="127"/>
+      <c r="AE10" s="127"/>
+      <c r="AF10" s="127"/>
+      <c r="AG10" s="127"/>
+      <c r="AH10" s="127"/>
+      <c r="AI10" s="127"/>
+      <c r="AJ10" s="127"/>
+      <c r="AK10" s="127"/>
+      <c r="AL10" s="127"/>
     </row>
     <row r="11" spans="1:38" ht="21.15" customHeight="1">
       <c r="A11" s="28"/>
@@ -5907,238 +5907,238 @@
       <c r="AL12" s="1"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1">
-      <c r="A13" s="132" t="s">
+      <c r="A13" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="127" t="s">
+      <c r="B13" s="128"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="128" t="s">
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="128"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="128"/>
-      <c r="S13" s="128"/>
-      <c r="T13" s="128"/>
-      <c r="U13" s="128"/>
-      <c r="V13" s="128"/>
-      <c r="W13" s="128"/>
-      <c r="X13" s="127" t="s">
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="133"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="133"/>
+      <c r="T13" s="133"/>
+      <c r="U13" s="133"/>
+      <c r="V13" s="133"/>
+      <c r="W13" s="133"/>
+      <c r="X13" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="Y13" s="127"/>
-      <c r="Z13" s="127"/>
-      <c r="AA13" s="127"/>
-      <c r="AB13" s="128" t="s">
+      <c r="Y13" s="132"/>
+      <c r="Z13" s="132"/>
+      <c r="AA13" s="132"/>
+      <c r="AB13" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="AC13" s="128"/>
-      <c r="AD13" s="128"/>
-      <c r="AE13" s="128"/>
-      <c r="AF13" s="128"/>
-      <c r="AG13" s="128"/>
-      <c r="AH13" s="128"/>
-      <c r="AI13" s="128"/>
-      <c r="AJ13" s="128"/>
-      <c r="AK13" s="128"/>
-      <c r="AL13" s="128"/>
+      <c r="AC13" s="133"/>
+      <c r="AD13" s="133"/>
+      <c r="AE13" s="133"/>
+      <c r="AF13" s="133"/>
+      <c r="AG13" s="133"/>
+      <c r="AH13" s="133"/>
+      <c r="AI13" s="133"/>
+      <c r="AJ13" s="133"/>
+      <c r="AK13" s="133"/>
+      <c r="AL13" s="133"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1">
-      <c r="A14" s="132"/>
-      <c r="B14" s="132"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="127"/>
-      <c r="L14" s="128" t="s">
+      <c r="A14" s="128"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="128"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="M14" s="128"/>
-      <c r="N14" s="128"/>
-      <c r="O14" s="128"/>
-      <c r="P14" s="128" t="s">
+      <c r="M14" s="133"/>
+      <c r="N14" s="133"/>
+      <c r="O14" s="133"/>
+      <c r="P14" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="Q14" s="128"/>
-      <c r="R14" s="128"/>
-      <c r="S14" s="128"/>
-      <c r="T14" s="128" t="s">
+      <c r="Q14" s="133"/>
+      <c r="R14" s="133"/>
+      <c r="S14" s="133"/>
+      <c r="T14" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="U14" s="128"/>
-      <c r="V14" s="128"/>
-      <c r="W14" s="128"/>
-      <c r="X14" s="127"/>
-      <c r="Y14" s="127"/>
-      <c r="Z14" s="127"/>
-      <c r="AA14" s="127"/>
-      <c r="AB14" s="128" t="s">
+      <c r="U14" s="133"/>
+      <c r="V14" s="133"/>
+      <c r="W14" s="133"/>
+      <c r="X14" s="132"/>
+      <c r="Y14" s="132"/>
+      <c r="Z14" s="132"/>
+      <c r="AA14" s="132"/>
+      <c r="AB14" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="AC14" s="128"/>
-      <c r="AD14" s="128"/>
-      <c r="AE14" s="128"/>
-      <c r="AF14" s="128" t="s">
+      <c r="AC14" s="133"/>
+      <c r="AD14" s="133"/>
+      <c r="AE14" s="133"/>
+      <c r="AF14" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="AG14" s="128"/>
-      <c r="AH14" s="128"/>
-      <c r="AI14" s="128"/>
-      <c r="AJ14" s="128" t="s">
+      <c r="AG14" s="133"/>
+      <c r="AH14" s="133"/>
+      <c r="AI14" s="133"/>
+      <c r="AJ14" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="AK14" s="128"/>
-      <c r="AL14" s="128"/>
+      <c r="AK14" s="133"/>
+      <c r="AL14" s="133"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1">
-      <c r="A15" s="133"/>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
+      <c r="A15" s="125"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
       <c r="H15" s="126">
         <v>125</v>
       </c>
       <c r="I15" s="126"/>
       <c r="J15" s="126"/>
       <c r="K15" s="126"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
-      <c r="U15" s="125"/>
-      <c r="V15" s="125"/>
-      <c r="W15" s="125"/>
+      <c r="L15" s="127"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="127"/>
+      <c r="O15" s="127"/>
+      <c r="P15" s="127"/>
+      <c r="Q15" s="127"/>
+      <c r="R15" s="127"/>
+      <c r="S15" s="127"/>
+      <c r="T15" s="127"/>
+      <c r="U15" s="127"/>
+      <c r="V15" s="127"/>
+      <c r="W15" s="127"/>
       <c r="X15" s="126">
         <v>2000</v>
       </c>
       <c r="Y15" s="126"/>
       <c r="Z15" s="126"/>
       <c r="AA15" s="126"/>
-      <c r="AB15" s="125"/>
-      <c r="AC15" s="125"/>
-      <c r="AD15" s="125"/>
-      <c r="AE15" s="125"/>
-      <c r="AF15" s="125"/>
-      <c r="AG15" s="125"/>
-      <c r="AH15" s="125"/>
-      <c r="AI15" s="125"/>
-      <c r="AJ15" s="125"/>
-      <c r="AK15" s="125"/>
-      <c r="AL15" s="125"/>
+      <c r="AB15" s="127"/>
+      <c r="AC15" s="127"/>
+      <c r="AD15" s="127"/>
+      <c r="AE15" s="127"/>
+      <c r="AF15" s="127"/>
+      <c r="AG15" s="127"/>
+      <c r="AH15" s="127"/>
+      <c r="AI15" s="127"/>
+      <c r="AJ15" s="127"/>
+      <c r="AK15" s="127"/>
+      <c r="AL15" s="127"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1">
-      <c r="A16" s="133"/>
-      <c r="B16" s="133"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
+      <c r="A16" s="125"/>
+      <c r="B16" s="125"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
       <c r="H16" s="126">
         <v>500</v>
       </c>
       <c r="I16" s="126"/>
       <c r="J16" s="126"/>
       <c r="K16" s="126"/>
-      <c r="L16" s="125"/>
-      <c r="M16" s="125"/>
-      <c r="N16" s="125"/>
-      <c r="O16" s="125"/>
-      <c r="P16" s="125"/>
-      <c r="Q16" s="125"/>
-      <c r="R16" s="125"/>
-      <c r="S16" s="125"/>
-      <c r="T16" s="125"/>
-      <c r="U16" s="125"/>
-      <c r="V16" s="125"/>
-      <c r="W16" s="125"/>
+      <c r="L16" s="127"/>
+      <c r="M16" s="127"/>
+      <c r="N16" s="127"/>
+      <c r="O16" s="127"/>
+      <c r="P16" s="127"/>
+      <c r="Q16" s="127"/>
+      <c r="R16" s="127"/>
+      <c r="S16" s="127"/>
+      <c r="T16" s="127"/>
+      <c r="U16" s="127"/>
+      <c r="V16" s="127"/>
+      <c r="W16" s="127"/>
       <c r="X16" s="126">
         <v>5000</v>
       </c>
       <c r="Y16" s="126"/>
       <c r="Z16" s="126"/>
       <c r="AA16" s="126"/>
-      <c r="AB16" s="125"/>
-      <c r="AC16" s="125"/>
-      <c r="AD16" s="125"/>
-      <c r="AE16" s="125"/>
-      <c r="AF16" s="125"/>
-      <c r="AG16" s="125"/>
-      <c r="AH16" s="125"/>
-      <c r="AI16" s="125"/>
-      <c r="AJ16" s="125"/>
-      <c r="AK16" s="125"/>
-      <c r="AL16" s="125"/>
+      <c r="AB16" s="127"/>
+      <c r="AC16" s="127"/>
+      <c r="AD16" s="127"/>
+      <c r="AE16" s="127"/>
+      <c r="AF16" s="127"/>
+      <c r="AG16" s="127"/>
+      <c r="AH16" s="127"/>
+      <c r="AI16" s="127"/>
+      <c r="AJ16" s="127"/>
+      <c r="AK16" s="127"/>
+      <c r="AL16" s="127"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
-      <c r="A17" s="133"/>
-      <c r="B17" s="133"/>
-      <c r="C17" s="133"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
+      <c r="A17" s="125"/>
+      <c r="B17" s="125"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
       <c r="H17" s="126">
         <v>1000</v>
       </c>
       <c r="I17" s="126"/>
       <c r="J17" s="126"/>
       <c r="K17" s="126"/>
-      <c r="L17" s="125"/>
-      <c r="M17" s="125"/>
-      <c r="N17" s="125"/>
-      <c r="O17" s="125"/>
-      <c r="P17" s="125"/>
-      <c r="Q17" s="125"/>
-      <c r="R17" s="125"/>
-      <c r="S17" s="125"/>
-      <c r="T17" s="125"/>
-      <c r="U17" s="125"/>
-      <c r="V17" s="125"/>
-      <c r="W17" s="125"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="127"/>
+      <c r="P17" s="127"/>
+      <c r="Q17" s="127"/>
+      <c r="R17" s="127"/>
+      <c r="S17" s="127"/>
+      <c r="T17" s="127"/>
+      <c r="U17" s="127"/>
+      <c r="V17" s="127"/>
+      <c r="W17" s="127"/>
       <c r="X17" s="126">
         <v>7000</v>
       </c>
       <c r="Y17" s="126"/>
       <c r="Z17" s="126"/>
       <c r="AA17" s="126"/>
-      <c r="AB17" s="125"/>
-      <c r="AC17" s="125"/>
-      <c r="AD17" s="125"/>
-      <c r="AE17" s="125"/>
-      <c r="AF17" s="125"/>
-      <c r="AG17" s="125"/>
-      <c r="AH17" s="125"/>
-      <c r="AI17" s="125"/>
-      <c r="AJ17" s="125"/>
-      <c r="AK17" s="125"/>
-      <c r="AL17" s="125"/>
+      <c r="AB17" s="127"/>
+      <c r="AC17" s="127"/>
+      <c r="AD17" s="127"/>
+      <c r="AE17" s="127"/>
+      <c r="AF17" s="127"/>
+      <c r="AG17" s="127"/>
+      <c r="AH17" s="127"/>
+      <c r="AI17" s="127"/>
+      <c r="AJ17" s="127"/>
+      <c r="AK17" s="127"/>
+      <c r="AL17" s="127"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1">
       <c r="A18" s="28"/>
@@ -7588,6 +7588,65 @@
     </row>
   </sheetData>
   <mergeCells count="75">
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AB15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="X16:AA16"/>
+    <mergeCell ref="AB16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="AJ16:AL16"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="L10:O10"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="X15:AA15"/>
+    <mergeCell ref="H13:K14"/>
+    <mergeCell ref="L13:W13"/>
+    <mergeCell ref="X13:AA14"/>
+    <mergeCell ref="AB13:AL13"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="AB14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="AB8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="AB10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="L9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="F3:S3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A6:G7"/>
+    <mergeCell ref="H6:K7"/>
+    <mergeCell ref="L6:W6"/>
+    <mergeCell ref="X6:AA7"/>
+    <mergeCell ref="AB6:AL6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="P7:S7"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="AB7:AE7"/>
+    <mergeCell ref="AF7:AI7"/>
+    <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="A8:G10"/>
     <mergeCell ref="A15:G17"/>
     <mergeCell ref="H15:K15"/>
@@ -7604,65 +7663,6 @@
     <mergeCell ref="L8:O8"/>
     <mergeCell ref="P8:S8"/>
     <mergeCell ref="A13:G14"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="F3:S3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A6:G7"/>
-    <mergeCell ref="H6:K7"/>
-    <mergeCell ref="L6:W6"/>
-    <mergeCell ref="X6:AA7"/>
-    <mergeCell ref="AB6:AL6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="P7:S7"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="AB7:AE7"/>
-    <mergeCell ref="AF7:AI7"/>
-    <mergeCell ref="AJ7:AL7"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="L9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AB10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="AB13:AL13"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="AB14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L10:O10"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X10:AA10"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="X15:AA15"/>
-    <mergeCell ref="H13:K14"/>
-    <mergeCell ref="L13:W13"/>
-    <mergeCell ref="X13:AA14"/>
-    <mergeCell ref="AB15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="AJ15:AL15"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="X16:AA16"/>
-    <mergeCell ref="AB16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7763,17 +7763,17 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
       <c r="L3" s="16"/>
       <c r="M3" s="16"/>
       <c r="N3" s="12" t="s">
@@ -10212,32 +10212,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
-      <c r="U1" s="144"/>
-      <c r="V1" s="144"/>
-      <c r="W1" s="144"/>
-      <c r="X1" s="144"/>
-      <c r="Y1" s="144"/>
-      <c r="Z1" s="144"/>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="144"/>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="144"/>
-      <c r="AF1" s="144"/>
-      <c r="AG1" s="144"/>
-      <c r="AH1" s="144"/>
-      <c r="AI1" s="144"/>
-      <c r="AJ1" s="144"/>
-      <c r="AK1" s="144"/>
-      <c r="AL1" s="144"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="135"/>
+      <c r="S1" s="135"/>
+      <c r="T1" s="135"/>
+      <c r="U1" s="135"/>
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="135"/>
+      <c r="Z1" s="135"/>
+      <c r="AA1" s="135"/>
+      <c r="AB1" s="135"/>
+      <c r="AC1" s="135"/>
+      <c r="AD1" s="135"/>
+      <c r="AE1" s="135"/>
+      <c r="AF1" s="135"/>
+      <c r="AG1" s="135"/>
+      <c r="AH1" s="135"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="135"/>
+      <c r="AL1" s="135"/>
       <c r="AM1" s="67"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -10281,17 +10281,17 @@
       <c r="AM2" s="67"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="141"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
+      <c r="A3" s="136"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -10311,11 +10311,11 @@
       <c r="Z3" s="38"/>
       <c r="AA3" s="76"/>
       <c r="AB3" s="34"/>
-      <c r="AC3" s="144"/>
-      <c r="AD3" s="144"/>
-      <c r="AE3" s="144"/>
-      <c r="AF3" s="144"/>
-      <c r="AG3" s="144"/>
+      <c r="AC3" s="135"/>
+      <c r="AD3" s="135"/>
+      <c r="AE3" s="135"/>
+      <c r="AF3" s="135"/>
+      <c r="AG3" s="135"/>
       <c r="AH3" s="34"/>
       <c r="AI3" s="34"/>
       <c r="AJ3" s="34"/>
@@ -10335,12 +10335,12 @@
       <c r="G4" s="69"/>
       <c r="H4" s="69"/>
       <c r="I4" s="69"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="145"/>
-      <c r="N4" s="145"/>
-      <c r="O4" s="145"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137"/>
       <c r="P4" s="34"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="34"/>
@@ -10373,51 +10373,51 @@
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
       <c r="D5" s="138"/>
-      <c r="E5" s="143" t="s">
+      <c r="E5" s="140" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143" t="s">
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140" t="s">
         <v>165</v>
       </c>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
-      <c r="Q5" s="143"/>
-      <c r="R5" s="143"/>
-      <c r="S5" s="143" t="s">
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="140" t="s">
         <v>164</v>
       </c>
-      <c r="T5" s="143"/>
-      <c r="U5" s="143"/>
-      <c r="V5" s="143"/>
-      <c r="W5" s="143"/>
-      <c r="X5" s="143"/>
-      <c r="Y5" s="143"/>
-      <c r="Z5" s="143" t="s">
+      <c r="T5" s="140"/>
+      <c r="U5" s="140"/>
+      <c r="V5" s="140"/>
+      <c r="W5" s="140"/>
+      <c r="X5" s="140"/>
+      <c r="Y5" s="140"/>
+      <c r="Z5" s="140" t="s">
         <v>163</v>
       </c>
-      <c r="AA5" s="143"/>
-      <c r="AB5" s="143"/>
-      <c r="AC5" s="143"/>
-      <c r="AD5" s="143"/>
-      <c r="AE5" s="143"/>
-      <c r="AF5" s="143"/>
-      <c r="AG5" s="143" t="s">
+      <c r="AA5" s="140"/>
+      <c r="AB5" s="140"/>
+      <c r="AC5" s="140"/>
+      <c r="AD5" s="140"/>
+      <c r="AE5" s="140"/>
+      <c r="AF5" s="140"/>
+      <c r="AG5" s="140" t="s">
         <v>162</v>
       </c>
-      <c r="AH5" s="143"/>
-      <c r="AI5" s="143"/>
-      <c r="AJ5" s="143"/>
-      <c r="AK5" s="143"/>
-      <c r="AL5" s="143"/>
-      <c r="AM5" s="143"/>
+      <c r="AH5" s="140"/>
+      <c r="AI5" s="140"/>
+      <c r="AJ5" s="140"/>
+      <c r="AK5" s="140"/>
+      <c r="AL5" s="140"/>
+      <c r="AM5" s="140"/>
     </row>
     <row r="6" spans="1:39" ht="15" customHeight="1">
       <c r="A6" s="138" t="s">
@@ -10426,41 +10426,41 @@
       <c r="B6" s="138"/>
       <c r="C6" s="138"/>
       <c r="D6" s="138"/>
-      <c r="E6" s="142"/>
-      <c r="F6" s="142"/>
-      <c r="G6" s="142"/>
-      <c r="H6" s="142"/>
-      <c r="I6" s="142"/>
-      <c r="J6" s="142"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-      <c r="M6" s="142"/>
-      <c r="N6" s="142"/>
-      <c r="O6" s="142"/>
-      <c r="P6" s="142"/>
-      <c r="Q6" s="142"/>
-      <c r="R6" s="142"/>
-      <c r="S6" s="142"/>
-      <c r="T6" s="142"/>
-      <c r="U6" s="142"/>
-      <c r="V6" s="142"/>
-      <c r="W6" s="142"/>
-      <c r="X6" s="142"/>
-      <c r="Y6" s="142"/>
-      <c r="Z6" s="142"/>
-      <c r="AA6" s="142"/>
-      <c r="AB6" s="142"/>
-      <c r="AC6" s="142"/>
-      <c r="AD6" s="142"/>
-      <c r="AE6" s="142"/>
-      <c r="AF6" s="142"/>
-      <c r="AG6" s="142"/>
-      <c r="AH6" s="142"/>
-      <c r="AI6" s="142"/>
-      <c r="AJ6" s="142"/>
-      <c r="AK6" s="142"/>
-      <c r="AL6" s="142"/>
-      <c r="AM6" s="142"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="139"/>
+      <c r="I6" s="139"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
+      <c r="M6" s="139"/>
+      <c r="N6" s="139"/>
+      <c r="O6" s="139"/>
+      <c r="P6" s="139"/>
+      <c r="Q6" s="139"/>
+      <c r="R6" s="139"/>
+      <c r="S6" s="139"/>
+      <c r="T6" s="139"/>
+      <c r="U6" s="139"/>
+      <c r="V6" s="139"/>
+      <c r="W6" s="139"/>
+      <c r="X6" s="139"/>
+      <c r="Y6" s="139"/>
+      <c r="Z6" s="139"/>
+      <c r="AA6" s="139"/>
+      <c r="AB6" s="139"/>
+      <c r="AC6" s="139"/>
+      <c r="AD6" s="139"/>
+      <c r="AE6" s="139"/>
+      <c r="AF6" s="139"/>
+      <c r="AG6" s="139"/>
+      <c r="AH6" s="139"/>
+      <c r="AI6" s="139"/>
+      <c r="AJ6" s="139"/>
+      <c r="AK6" s="139"/>
+      <c r="AL6" s="139"/>
+      <c r="AM6" s="139"/>
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
       <c r="A7" s="138" t="s">
@@ -10469,41 +10469,41 @@
       <c r="B7" s="138"/>
       <c r="C7" s="138"/>
       <c r="D7" s="138"/>
-      <c r="E7" s="142"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="142"/>
-      <c r="H7" s="142"/>
-      <c r="I7" s="142"/>
-      <c r="J7" s="142"/>
-      <c r="K7" s="142"/>
-      <c r="L7" s="142"/>
-      <c r="M7" s="142"/>
-      <c r="N7" s="142"/>
-      <c r="O7" s="142"/>
-      <c r="P7" s="142"/>
-      <c r="Q7" s="142"/>
-      <c r="R7" s="142"/>
-      <c r="S7" s="142"/>
-      <c r="T7" s="142"/>
-      <c r="U7" s="142"/>
-      <c r="V7" s="142"/>
-      <c r="W7" s="142"/>
-      <c r="X7" s="142"/>
-      <c r="Y7" s="142"/>
-      <c r="Z7" s="142"/>
-      <c r="AA7" s="142"/>
-      <c r="AB7" s="142"/>
-      <c r="AC7" s="142"/>
-      <c r="AD7" s="142"/>
-      <c r="AE7" s="142"/>
-      <c r="AF7" s="142"/>
-      <c r="AG7" s="142"/>
-      <c r="AH7" s="142"/>
-      <c r="AI7" s="142"/>
-      <c r="AJ7" s="142"/>
-      <c r="AK7" s="142"/>
-      <c r="AL7" s="142"/>
-      <c r="AM7" s="142"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
+      <c r="M7" s="139"/>
+      <c r="N7" s="139"/>
+      <c r="O7" s="139"/>
+      <c r="P7" s="139"/>
+      <c r="Q7" s="139"/>
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="139"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="139"/>
+      <c r="X7" s="139"/>
+      <c r="Y7" s="139"/>
+      <c r="Z7" s="139"/>
+      <c r="AA7" s="139"/>
+      <c r="AB7" s="139"/>
+      <c r="AC7" s="139"/>
+      <c r="AD7" s="139"/>
+      <c r="AE7" s="139"/>
+      <c r="AF7" s="139"/>
+      <c r="AG7" s="139"/>
+      <c r="AH7" s="139"/>
+      <c r="AI7" s="139"/>
+      <c r="AJ7" s="139"/>
+      <c r="AK7" s="139"/>
+      <c r="AL7" s="139"/>
+      <c r="AM7" s="139"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
       <c r="A8" s="138" t="s">
@@ -10512,51 +10512,51 @@
       <c r="B8" s="138"/>
       <c r="C8" s="138"/>
       <c r="D8" s="138"/>
-      <c r="E8" s="143" t="s">
+      <c r="E8" s="140" t="s">
         <v>166</v>
       </c>
-      <c r="F8" s="143"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="143"/>
-      <c r="J8" s="143"/>
-      <c r="K8" s="143"/>
-      <c r="L8" s="143" t="s">
+      <c r="F8" s="140"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140" t="s">
         <v>167</v>
       </c>
-      <c r="M8" s="143"/>
-      <c r="N8" s="143"/>
-      <c r="O8" s="143"/>
-      <c r="P8" s="143"/>
-      <c r="Q8" s="143"/>
-      <c r="R8" s="143"/>
-      <c r="S8" s="143" t="s">
+      <c r="M8" s="140"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="140"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="140" t="s">
         <v>168</v>
       </c>
-      <c r="T8" s="143"/>
-      <c r="U8" s="143"/>
-      <c r="V8" s="143"/>
-      <c r="W8" s="143"/>
-      <c r="X8" s="143"/>
-      <c r="Y8" s="143"/>
-      <c r="Z8" s="143" t="s">
+      <c r="T8" s="140"/>
+      <c r="U8" s="140"/>
+      <c r="V8" s="140"/>
+      <c r="W8" s="140"/>
+      <c r="X8" s="140"/>
+      <c r="Y8" s="140"/>
+      <c r="Z8" s="140" t="s">
         <v>169</v>
       </c>
-      <c r="AA8" s="143"/>
-      <c r="AB8" s="143"/>
-      <c r="AC8" s="143"/>
-      <c r="AD8" s="143"/>
-      <c r="AE8" s="143"/>
-      <c r="AF8" s="143"/>
-      <c r="AG8" s="143" t="s">
+      <c r="AA8" s="140"/>
+      <c r="AB8" s="140"/>
+      <c r="AC8" s="140"/>
+      <c r="AD8" s="140"/>
+      <c r="AE8" s="140"/>
+      <c r="AF8" s="140"/>
+      <c r="AG8" s="140" t="s">
         <v>170</v>
       </c>
-      <c r="AH8" s="143"/>
-      <c r="AI8" s="143"/>
-      <c r="AJ8" s="143"/>
-      <c r="AK8" s="143"/>
-      <c r="AL8" s="143"/>
-      <c r="AM8" s="143"/>
+      <c r="AH8" s="140"/>
+      <c r="AI8" s="140"/>
+      <c r="AJ8" s="140"/>
+      <c r="AK8" s="140"/>
+      <c r="AL8" s="140"/>
+      <c r="AM8" s="140"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
       <c r="A9" s="138" t="s">
@@ -10565,41 +10565,41 @@
       <c r="B9" s="138"/>
       <c r="C9" s="138"/>
       <c r="D9" s="138"/>
-      <c r="E9" s="142"/>
-      <c r="F9" s="142"/>
-      <c r="G9" s="142"/>
-      <c r="H9" s="142"/>
-      <c r="I9" s="142"/>
-      <c r="J9" s="142"/>
-      <c r="K9" s="142"/>
-      <c r="L9" s="142"/>
-      <c r="M9" s="142"/>
-      <c r="N9" s="142"/>
-      <c r="O9" s="142"/>
-      <c r="P9" s="142"/>
-      <c r="Q9" s="142"/>
-      <c r="R9" s="142"/>
-      <c r="S9" s="142"/>
-      <c r="T9" s="142"/>
-      <c r="U9" s="142"/>
-      <c r="V9" s="142"/>
-      <c r="W9" s="142"/>
-      <c r="X9" s="142"/>
-      <c r="Y9" s="142"/>
-      <c r="Z9" s="142"/>
-      <c r="AA9" s="142"/>
-      <c r="AB9" s="142"/>
-      <c r="AC9" s="142"/>
-      <c r="AD9" s="142"/>
-      <c r="AE9" s="142"/>
-      <c r="AF9" s="142"/>
-      <c r="AG9" s="142"/>
-      <c r="AH9" s="142"/>
-      <c r="AI9" s="142"/>
-      <c r="AJ9" s="142"/>
-      <c r="AK9" s="142"/>
-      <c r="AL9" s="142"/>
-      <c r="AM9" s="142"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="139"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="139"/>
+      <c r="K9" s="139"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="139"/>
+      <c r="N9" s="139"/>
+      <c r="O9" s="139"/>
+      <c r="P9" s="139"/>
+      <c r="Q9" s="139"/>
+      <c r="R9" s="139"/>
+      <c r="S9" s="139"/>
+      <c r="T9" s="139"/>
+      <c r="U9" s="139"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="139"/>
+      <c r="X9" s="139"/>
+      <c r="Y9" s="139"/>
+      <c r="Z9" s="139"/>
+      <c r="AA9" s="139"/>
+      <c r="AB9" s="139"/>
+      <c r="AC9" s="139"/>
+      <c r="AD9" s="139"/>
+      <c r="AE9" s="139"/>
+      <c r="AF9" s="139"/>
+      <c r="AG9" s="139"/>
+      <c r="AH9" s="139"/>
+      <c r="AI9" s="139"/>
+      <c r="AJ9" s="139"/>
+      <c r="AK9" s="139"/>
+      <c r="AL9" s="139"/>
+      <c r="AM9" s="139"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
       <c r="A10" s="138" t="s">
@@ -10608,41 +10608,41 @@
       <c r="B10" s="138"/>
       <c r="C10" s="138"/>
       <c r="D10" s="138"/>
-      <c r="E10" s="142"/>
-      <c r="F10" s="142"/>
-      <c r="G10" s="142"/>
-      <c r="H10" s="142"/>
-      <c r="I10" s="142"/>
-      <c r="J10" s="142"/>
-      <c r="K10" s="142"/>
-      <c r="L10" s="142"/>
-      <c r="M10" s="142"/>
-      <c r="N10" s="142"/>
-      <c r="O10" s="142"/>
-      <c r="P10" s="142"/>
-      <c r="Q10" s="142"/>
-      <c r="R10" s="142"/>
-      <c r="S10" s="142"/>
-      <c r="T10" s="142"/>
-      <c r="U10" s="142"/>
-      <c r="V10" s="142"/>
-      <c r="W10" s="142"/>
-      <c r="X10" s="142"/>
-      <c r="Y10" s="142"/>
-      <c r="Z10" s="142"/>
-      <c r="AA10" s="142"/>
-      <c r="AB10" s="142"/>
-      <c r="AC10" s="142"/>
-      <c r="AD10" s="142"/>
-      <c r="AE10" s="142"/>
-      <c r="AF10" s="142"/>
-      <c r="AG10" s="142"/>
-      <c r="AH10" s="142"/>
-      <c r="AI10" s="142"/>
-      <c r="AJ10" s="142"/>
-      <c r="AK10" s="142"/>
-      <c r="AL10" s="142"/>
-      <c r="AM10" s="142"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="139"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="139"/>
+      <c r="N10" s="139"/>
+      <c r="O10" s="139"/>
+      <c r="P10" s="139"/>
+      <c r="Q10" s="139"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="139"/>
+      <c r="T10" s="139"/>
+      <c r="U10" s="139"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="139"/>
+      <c r="X10" s="139"/>
+      <c r="Y10" s="139"/>
+      <c r="Z10" s="139"/>
+      <c r="AA10" s="139"/>
+      <c r="AB10" s="139"/>
+      <c r="AC10" s="139"/>
+      <c r="AD10" s="139"/>
+      <c r="AE10" s="139"/>
+      <c r="AF10" s="139"/>
+      <c r="AG10" s="139"/>
+      <c r="AH10" s="139"/>
+      <c r="AI10" s="139"/>
+      <c r="AJ10" s="139"/>
+      <c r="AK10" s="139"/>
+      <c r="AL10" s="139"/>
+      <c r="AM10" s="139"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
       <c r="A11" s="138" t="s">
@@ -10651,51 +10651,51 @@
       <c r="B11" s="138"/>
       <c r="C11" s="138"/>
       <c r="D11" s="138"/>
-      <c r="E11" s="143" t="s">
+      <c r="E11" s="140" t="s">
         <v>171</v>
       </c>
-      <c r="F11" s="143"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="143"/>
-      <c r="I11" s="143"/>
-      <c r="J11" s="143"/>
-      <c r="K11" s="143"/>
-      <c r="L11" s="143" t="s">
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="140" t="s">
         <v>172</v>
       </c>
-      <c r="M11" s="143"/>
-      <c r="N11" s="143"/>
-      <c r="O11" s="143"/>
-      <c r="P11" s="143"/>
-      <c r="Q11" s="143"/>
-      <c r="R11" s="143"/>
-      <c r="S11" s="143" t="s">
+      <c r="M11" s="140"/>
+      <c r="N11" s="140"/>
+      <c r="O11" s="140"/>
+      <c r="P11" s="140"/>
+      <c r="Q11" s="140"/>
+      <c r="R11" s="140"/>
+      <c r="S11" s="140" t="s">
         <v>173</v>
       </c>
-      <c r="T11" s="143"/>
-      <c r="U11" s="143"/>
-      <c r="V11" s="143"/>
-      <c r="W11" s="143"/>
-      <c r="X11" s="143"/>
-      <c r="Y11" s="143"/>
-      <c r="Z11" s="143" t="s">
+      <c r="T11" s="140"/>
+      <c r="U11" s="140"/>
+      <c r="V11" s="140"/>
+      <c r="W11" s="140"/>
+      <c r="X11" s="140"/>
+      <c r="Y11" s="140"/>
+      <c r="Z11" s="140" t="s">
         <v>174</v>
       </c>
-      <c r="AA11" s="143"/>
-      <c r="AB11" s="143"/>
-      <c r="AC11" s="143"/>
-      <c r="AD11" s="143"/>
-      <c r="AE11" s="143"/>
-      <c r="AF11" s="143"/>
-      <c r="AG11" s="143" t="s">
+      <c r="AA11" s="140"/>
+      <c r="AB11" s="140"/>
+      <c r="AC11" s="140"/>
+      <c r="AD11" s="140"/>
+      <c r="AE11" s="140"/>
+      <c r="AF11" s="140"/>
+      <c r="AG11" s="140" t="s">
         <v>175</v>
       </c>
-      <c r="AH11" s="143"/>
-      <c r="AI11" s="143"/>
-      <c r="AJ11" s="143"/>
-      <c r="AK11" s="143"/>
-      <c r="AL11" s="143"/>
-      <c r="AM11" s="143"/>
+      <c r="AH11" s="140"/>
+      <c r="AI11" s="140"/>
+      <c r="AJ11" s="140"/>
+      <c r="AK11" s="140"/>
+      <c r="AL11" s="140"/>
+      <c r="AM11" s="140"/>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1">
       <c r="A12" s="138" t="s">
@@ -10704,41 +10704,41 @@
       <c r="B12" s="138"/>
       <c r="C12" s="138"/>
       <c r="D12" s="138"/>
-      <c r="E12" s="142"/>
-      <c r="F12" s="142"/>
-      <c r="G12" s="142"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="142"/>
-      <c r="J12" s="142"/>
-      <c r="K12" s="142"/>
-      <c r="L12" s="142"/>
-      <c r="M12" s="142"/>
-      <c r="N12" s="142"/>
-      <c r="O12" s="142"/>
-      <c r="P12" s="142"/>
-      <c r="Q12" s="142"/>
-      <c r="R12" s="142"/>
-      <c r="S12" s="142"/>
-      <c r="T12" s="142"/>
-      <c r="U12" s="142"/>
-      <c r="V12" s="142"/>
-      <c r="W12" s="142"/>
-      <c r="X12" s="142"/>
-      <c r="Y12" s="142"/>
-      <c r="Z12" s="142"/>
-      <c r="AA12" s="142"/>
-      <c r="AB12" s="142"/>
-      <c r="AC12" s="142"/>
-      <c r="AD12" s="142"/>
-      <c r="AE12" s="142"/>
-      <c r="AF12" s="142"/>
-      <c r="AG12" s="142"/>
-      <c r="AH12" s="142"/>
-      <c r="AI12" s="142"/>
-      <c r="AJ12" s="142"/>
-      <c r="AK12" s="142"/>
-      <c r="AL12" s="142"/>
-      <c r="AM12" s="142"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="139"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="139"/>
+      <c r="K12" s="139"/>
+      <c r="L12" s="139"/>
+      <c r="M12" s="139"/>
+      <c r="N12" s="139"/>
+      <c r="O12" s="139"/>
+      <c r="P12" s="139"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="139"/>
+      <c r="T12" s="139"/>
+      <c r="U12" s="139"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="139"/>
+      <c r="X12" s="139"/>
+      <c r="Y12" s="139"/>
+      <c r="Z12" s="139"/>
+      <c r="AA12" s="139"/>
+      <c r="AB12" s="139"/>
+      <c r="AC12" s="139"/>
+      <c r="AD12" s="139"/>
+      <c r="AE12" s="139"/>
+      <c r="AF12" s="139"/>
+      <c r="AG12" s="139"/>
+      <c r="AH12" s="139"/>
+      <c r="AI12" s="139"/>
+      <c r="AJ12" s="139"/>
+      <c r="AK12" s="139"/>
+      <c r="AL12" s="139"/>
+      <c r="AM12" s="139"/>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1">
       <c r="A13" s="138" t="s">
@@ -10747,41 +10747,41 @@
       <c r="B13" s="138"/>
       <c r="C13" s="138"/>
       <c r="D13" s="138"/>
-      <c r="E13" s="142"/>
-      <c r="F13" s="142"/>
-      <c r="G13" s="142"/>
-      <c r="H13" s="142"/>
-      <c r="I13" s="142"/>
-      <c r="J13" s="142"/>
-      <c r="K13" s="142"/>
-      <c r="L13" s="142"/>
-      <c r="M13" s="142"/>
-      <c r="N13" s="142"/>
-      <c r="O13" s="142"/>
-      <c r="P13" s="142"/>
-      <c r="Q13" s="142"/>
-      <c r="R13" s="142"/>
-      <c r="S13" s="142"/>
-      <c r="T13" s="142"/>
-      <c r="U13" s="142"/>
-      <c r="V13" s="142"/>
-      <c r="W13" s="142"/>
-      <c r="X13" s="142"/>
-      <c r="Y13" s="142"/>
-      <c r="Z13" s="142"/>
-      <c r="AA13" s="142"/>
-      <c r="AB13" s="142"/>
-      <c r="AC13" s="142"/>
-      <c r="AD13" s="142"/>
-      <c r="AE13" s="142"/>
-      <c r="AF13" s="142"/>
-      <c r="AG13" s="142"/>
-      <c r="AH13" s="142"/>
-      <c r="AI13" s="142"/>
-      <c r="AJ13" s="142"/>
-      <c r="AK13" s="142"/>
-      <c r="AL13" s="142"/>
-      <c r="AM13" s="142"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="139"/>
+      <c r="K13" s="139"/>
+      <c r="L13" s="139"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="139"/>
+      <c r="O13" s="139"/>
+      <c r="P13" s="139"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139"/>
+      <c r="T13" s="139"/>
+      <c r="U13" s="139"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="139"/>
+      <c r="X13" s="139"/>
+      <c r="Y13" s="139"/>
+      <c r="Z13" s="139"/>
+      <c r="AA13" s="139"/>
+      <c r="AB13" s="139"/>
+      <c r="AC13" s="139"/>
+      <c r="AD13" s="139"/>
+      <c r="AE13" s="139"/>
+      <c r="AF13" s="139"/>
+      <c r="AG13" s="139"/>
+      <c r="AH13" s="139"/>
+      <c r="AI13" s="139"/>
+      <c r="AJ13" s="139"/>
+      <c r="AK13" s="139"/>
+      <c r="AL13" s="139"/>
+      <c r="AM13" s="139"/>
     </row>
     <row r="14" spans="1:39">
       <c r="A14" s="68" t="s">
@@ -10908,17 +10908,17 @@
       <c r="AM16" s="34"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="141"/>
-      <c r="B17" s="141"/>
-      <c r="C17" s="141"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="141"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="141"/>
-      <c r="K17" s="141"/>
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
       <c r="L17" s="34"/>
       <c r="M17" s="34"/>
       <c r="N17" s="34"/>
@@ -10990,118 +10990,118 @@
       <c r="AM18" s="34"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="140" t="s">
+      <c r="A19" s="145" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="140"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140"/>
-      <c r="E19" s="139" t="s">
+      <c r="B19" s="145"/>
+      <c r="C19" s="145"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="144" t="s">
         <v>184</v>
       </c>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="139"/>
-      <c r="I19" s="139"/>
-      <c r="J19" s="139"/>
-      <c r="K19" s="139"/>
-      <c r="L19" s="139" t="s">
+      <c r="F19" s="144"/>
+      <c r="G19" s="144"/>
+      <c r="H19" s="144"/>
+      <c r="I19" s="144"/>
+      <c r="J19" s="144"/>
+      <c r="K19" s="144"/>
+      <c r="L19" s="144" t="s">
         <v>185</v>
       </c>
-      <c r="M19" s="139"/>
-      <c r="N19" s="139"/>
-      <c r="O19" s="139"/>
-      <c r="P19" s="139"/>
-      <c r="Q19" s="139"/>
-      <c r="R19" s="139"/>
-      <c r="S19" s="139" t="s">
+      <c r="M19" s="144"/>
+      <c r="N19" s="144"/>
+      <c r="O19" s="144"/>
+      <c r="P19" s="144"/>
+      <c r="Q19" s="144"/>
+      <c r="R19" s="144"/>
+      <c r="S19" s="144" t="s">
         <v>186</v>
       </c>
-      <c r="T19" s="139"/>
-      <c r="U19" s="139"/>
-      <c r="V19" s="139"/>
-      <c r="W19" s="139"/>
-      <c r="X19" s="139"/>
-      <c r="Y19" s="139"/>
-      <c r="Z19" s="139" t="s">
+      <c r="T19" s="144"/>
+      <c r="U19" s="144"/>
+      <c r="V19" s="144"/>
+      <c r="W19" s="144"/>
+      <c r="X19" s="144"/>
+      <c r="Y19" s="144"/>
+      <c r="Z19" s="144" t="s">
         <v>187</v>
       </c>
-      <c r="AA19" s="139"/>
-      <c r="AB19" s="139"/>
-      <c r="AC19" s="139"/>
-      <c r="AD19" s="139"/>
-      <c r="AE19" s="139"/>
-      <c r="AF19" s="139"/>
-      <c r="AG19" s="139" t="s">
+      <c r="AA19" s="144"/>
+      <c r="AB19" s="144"/>
+      <c r="AC19" s="144"/>
+      <c r="AD19" s="144"/>
+      <c r="AE19" s="144"/>
+      <c r="AF19" s="144"/>
+      <c r="AG19" s="144" t="s">
         <v>188</v>
       </c>
-      <c r="AH19" s="139"/>
-      <c r="AI19" s="139"/>
-      <c r="AJ19" s="139"/>
-      <c r="AK19" s="139"/>
-      <c r="AL19" s="139"/>
-      <c r="AM19" s="139"/>
+      <c r="AH19" s="144"/>
+      <c r="AI19" s="144"/>
+      <c r="AJ19" s="144"/>
+      <c r="AK19" s="144"/>
+      <c r="AL19" s="144"/>
+      <c r="AM19" s="144"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="140"/>
-      <c r="B20" s="140"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="139" t="s">
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="145"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139" t="s">
+      <c r="F20" s="144"/>
+      <c r="G20" s="144"/>
+      <c r="H20" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="I20" s="139"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139" t="s">
+      <c r="I20" s="144"/>
+      <c r="J20" s="144"/>
+      <c r="K20" s="144"/>
+      <c r="L20" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="M20" s="139"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="139" t="s">
+      <c r="M20" s="144"/>
+      <c r="N20" s="144"/>
+      <c r="O20" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="P20" s="139"/>
-      <c r="Q20" s="139"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="139" t="s">
+      <c r="P20" s="144"/>
+      <c r="Q20" s="144"/>
+      <c r="R20" s="144"/>
+      <c r="S20" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="T20" s="139"/>
-      <c r="U20" s="139"/>
-      <c r="V20" s="139" t="s">
+      <c r="T20" s="144"/>
+      <c r="U20" s="144"/>
+      <c r="V20" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="W20" s="139"/>
-      <c r="X20" s="139"/>
-      <c r="Y20" s="139"/>
-      <c r="Z20" s="139" t="s">
+      <c r="W20" s="144"/>
+      <c r="X20" s="144"/>
+      <c r="Y20" s="144"/>
+      <c r="Z20" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="AA20" s="139"/>
-      <c r="AB20" s="139"/>
-      <c r="AC20" s="139" t="s">
+      <c r="AA20" s="144"/>
+      <c r="AB20" s="144"/>
+      <c r="AC20" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="AD20" s="139"/>
-      <c r="AE20" s="139"/>
-      <c r="AF20" s="139"/>
-      <c r="AG20" s="139" t="s">
+      <c r="AD20" s="144"/>
+      <c r="AE20" s="144"/>
+      <c r="AF20" s="144"/>
+      <c r="AG20" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="AH20" s="139"/>
-      <c r="AI20" s="139"/>
-      <c r="AJ20" s="139" t="s">
+      <c r="AH20" s="144"/>
+      <c r="AI20" s="144"/>
+      <c r="AJ20" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="AK20" s="139"/>
-      <c r="AL20" s="139"/>
-      <c r="AM20" s="139"/>
+      <c r="AK20" s="144"/>
+      <c r="AL20" s="144"/>
+      <c r="AM20" s="144"/>
     </row>
     <row r="21" spans="1:39">
       <c r="A21" s="138" t="s">
@@ -11110,41 +11110,41 @@
       <c r="B21" s="138"/>
       <c r="C21" s="138"/>
       <c r="D21" s="138"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="136"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="136"/>
-      <c r="J21" s="136"/>
-      <c r="K21" s="137"/>
-      <c r="L21" s="135"/>
-      <c r="M21" s="136"/>
-      <c r="N21" s="137"/>
-      <c r="O21" s="135"/>
-      <c r="P21" s="136"/>
-      <c r="Q21" s="136"/>
-      <c r="R21" s="137"/>
-      <c r="S21" s="135"/>
-      <c r="T21" s="136"/>
-      <c r="U21" s="137"/>
-      <c r="V21" s="135"/>
-      <c r="W21" s="136"/>
-      <c r="X21" s="136"/>
-      <c r="Y21" s="137"/>
-      <c r="Z21" s="135"/>
-      <c r="AA21" s="136"/>
-      <c r="AB21" s="137"/>
-      <c r="AC21" s="135"/>
-      <c r="AD21" s="136"/>
-      <c r="AE21" s="136"/>
-      <c r="AF21" s="137"/>
-      <c r="AG21" s="135"/>
-      <c r="AH21" s="136"/>
-      <c r="AI21" s="137"/>
-      <c r="AJ21" s="135"/>
-      <c r="AK21" s="136"/>
-      <c r="AL21" s="136"/>
-      <c r="AM21" s="137"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="142"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="141"/>
+      <c r="I21" s="142"/>
+      <c r="J21" s="142"/>
+      <c r="K21" s="143"/>
+      <c r="L21" s="141"/>
+      <c r="M21" s="142"/>
+      <c r="N21" s="143"/>
+      <c r="O21" s="141"/>
+      <c r="P21" s="142"/>
+      <c r="Q21" s="142"/>
+      <c r="R21" s="143"/>
+      <c r="S21" s="141"/>
+      <c r="T21" s="142"/>
+      <c r="U21" s="143"/>
+      <c r="V21" s="141"/>
+      <c r="W21" s="142"/>
+      <c r="X21" s="142"/>
+      <c r="Y21" s="143"/>
+      <c r="Z21" s="141"/>
+      <c r="AA21" s="142"/>
+      <c r="AB21" s="143"/>
+      <c r="AC21" s="141"/>
+      <c r="AD21" s="142"/>
+      <c r="AE21" s="142"/>
+      <c r="AF21" s="143"/>
+      <c r="AG21" s="141"/>
+      <c r="AH21" s="142"/>
+      <c r="AI21" s="143"/>
+      <c r="AJ21" s="141"/>
+      <c r="AK21" s="142"/>
+      <c r="AL21" s="142"/>
+      <c r="AM21" s="143"/>
     </row>
     <row r="22" spans="1:39">
       <c r="A22" s="138" t="s">
@@ -11153,155 +11153,155 @@
       <c r="B22" s="138"/>
       <c r="C22" s="138"/>
       <c r="D22" s="138"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="136"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="135"/>
-      <c r="M22" s="136"/>
-      <c r="N22" s="137"/>
-      <c r="O22" s="135"/>
-      <c r="P22" s="136"/>
-      <c r="Q22" s="136"/>
-      <c r="R22" s="137"/>
-      <c r="S22" s="135"/>
-      <c r="T22" s="136"/>
-      <c r="U22" s="137"/>
-      <c r="V22" s="135"/>
-      <c r="W22" s="136"/>
-      <c r="X22" s="136"/>
-      <c r="Y22" s="137"/>
-      <c r="Z22" s="135"/>
-      <c r="AA22" s="136"/>
-      <c r="AB22" s="137"/>
-      <c r="AC22" s="135"/>
-      <c r="AD22" s="136"/>
-      <c r="AE22" s="136"/>
-      <c r="AF22" s="137"/>
-      <c r="AG22" s="135"/>
-      <c r="AH22" s="136"/>
-      <c r="AI22" s="137"/>
-      <c r="AJ22" s="135"/>
-      <c r="AK22" s="136"/>
-      <c r="AL22" s="136"/>
-      <c r="AM22" s="137"/>
+      <c r="E22" s="141"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="141"/>
+      <c r="I22" s="142"/>
+      <c r="J22" s="142"/>
+      <c r="K22" s="143"/>
+      <c r="L22" s="141"/>
+      <c r="M22" s="142"/>
+      <c r="N22" s="143"/>
+      <c r="O22" s="141"/>
+      <c r="P22" s="142"/>
+      <c r="Q22" s="142"/>
+      <c r="R22" s="143"/>
+      <c r="S22" s="141"/>
+      <c r="T22" s="142"/>
+      <c r="U22" s="143"/>
+      <c r="V22" s="141"/>
+      <c r="W22" s="142"/>
+      <c r="X22" s="142"/>
+      <c r="Y22" s="143"/>
+      <c r="Z22" s="141"/>
+      <c r="AA22" s="142"/>
+      <c r="AB22" s="143"/>
+      <c r="AC22" s="141"/>
+      <c r="AD22" s="142"/>
+      <c r="AE22" s="142"/>
+      <c r="AF22" s="143"/>
+      <c r="AG22" s="141"/>
+      <c r="AH22" s="142"/>
+      <c r="AI22" s="143"/>
+      <c r="AJ22" s="141"/>
+      <c r="AK22" s="142"/>
+      <c r="AL22" s="142"/>
+      <c r="AM22" s="143"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="140" t="s">
+      <c r="A23" s="145" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="140"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="139" t="s">
+      <c r="B23" s="145"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="144" t="s">
         <v>189</v>
       </c>
-      <c r="F23" s="139"/>
-      <c r="G23" s="139"/>
-      <c r="H23" s="139"/>
-      <c r="I23" s="139"/>
-      <c r="J23" s="139"/>
-      <c r="K23" s="139"/>
-      <c r="L23" s="139" t="s">
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="144"/>
+      <c r="J23" s="144"/>
+      <c r="K23" s="144"/>
+      <c r="L23" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="M23" s="139"/>
-      <c r="N23" s="139"/>
-      <c r="O23" s="139"/>
-      <c r="P23" s="139"/>
-      <c r="Q23" s="139"/>
-      <c r="R23" s="139"/>
-      <c r="S23" s="139" t="s">
+      <c r="M23" s="144"/>
+      <c r="N23" s="144"/>
+      <c r="O23" s="144"/>
+      <c r="P23" s="144"/>
+      <c r="Q23" s="144"/>
+      <c r="R23" s="144"/>
+      <c r="S23" s="144" t="s">
         <v>191</v>
       </c>
-      <c r="T23" s="139"/>
-      <c r="U23" s="139"/>
-      <c r="V23" s="139"/>
-      <c r="W23" s="139"/>
-      <c r="X23" s="139"/>
-      <c r="Y23" s="139"/>
-      <c r="Z23" s="139" t="s">
+      <c r="T23" s="144"/>
+      <c r="U23" s="144"/>
+      <c r="V23" s="144"/>
+      <c r="W23" s="144"/>
+      <c r="X23" s="144"/>
+      <c r="Y23" s="144"/>
+      <c r="Z23" s="144" t="s">
         <v>192</v>
       </c>
-      <c r="AA23" s="139"/>
-      <c r="AB23" s="139"/>
-      <c r="AC23" s="139"/>
-      <c r="AD23" s="139"/>
-      <c r="AE23" s="139"/>
-      <c r="AF23" s="139"/>
-      <c r="AG23" s="139" t="s">
+      <c r="AA23" s="144"/>
+      <c r="AB23" s="144"/>
+      <c r="AC23" s="144"/>
+      <c r="AD23" s="144"/>
+      <c r="AE23" s="144"/>
+      <c r="AF23" s="144"/>
+      <c r="AG23" s="144" t="s">
         <v>193</v>
       </c>
-      <c r="AH23" s="139"/>
-      <c r="AI23" s="139"/>
-      <c r="AJ23" s="139"/>
-      <c r="AK23" s="139"/>
-      <c r="AL23" s="139"/>
-      <c r="AM23" s="139"/>
+      <c r="AH23" s="144"/>
+      <c r="AI23" s="144"/>
+      <c r="AJ23" s="144"/>
+      <c r="AK23" s="144"/>
+      <c r="AL23" s="144"/>
+      <c r="AM23" s="144"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="140"/>
-      <c r="B24" s="140"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="140"/>
-      <c r="E24" s="139" t="s">
+      <c r="A24" s="145"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="F24" s="139"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="139" t="s">
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="I24" s="139"/>
-      <c r="J24" s="139"/>
-      <c r="K24" s="139"/>
-      <c r="L24" s="139" t="s">
+      <c r="I24" s="144"/>
+      <c r="J24" s="144"/>
+      <c r="K24" s="144"/>
+      <c r="L24" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="M24" s="139"/>
-      <c r="N24" s="139"/>
-      <c r="O24" s="139" t="s">
+      <c r="M24" s="144"/>
+      <c r="N24" s="144"/>
+      <c r="O24" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="P24" s="139"/>
-      <c r="Q24" s="139"/>
-      <c r="R24" s="139"/>
-      <c r="S24" s="139" t="s">
+      <c r="P24" s="144"/>
+      <c r="Q24" s="144"/>
+      <c r="R24" s="144"/>
+      <c r="S24" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="T24" s="139"/>
-      <c r="U24" s="139"/>
-      <c r="V24" s="139" t="s">
+      <c r="T24" s="144"/>
+      <c r="U24" s="144"/>
+      <c r="V24" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="W24" s="139"/>
-      <c r="X24" s="139"/>
-      <c r="Y24" s="139"/>
-      <c r="Z24" s="139" t="s">
+      <c r="W24" s="144"/>
+      <c r="X24" s="144"/>
+      <c r="Y24" s="144"/>
+      <c r="Z24" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="AA24" s="139"/>
-      <c r="AB24" s="139"/>
-      <c r="AC24" s="139" t="s">
+      <c r="AA24" s="144"/>
+      <c r="AB24" s="144"/>
+      <c r="AC24" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="AD24" s="139"/>
-      <c r="AE24" s="139"/>
-      <c r="AF24" s="139"/>
-      <c r="AG24" s="139" t="s">
+      <c r="AD24" s="144"/>
+      <c r="AE24" s="144"/>
+      <c r="AF24" s="144"/>
+      <c r="AG24" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="AH24" s="139"/>
-      <c r="AI24" s="139"/>
-      <c r="AJ24" s="139" t="s">
+      <c r="AH24" s="144"/>
+      <c r="AI24" s="144"/>
+      <c r="AJ24" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="AK24" s="139"/>
-      <c r="AL24" s="139"/>
-      <c r="AM24" s="139"/>
+      <c r="AK24" s="144"/>
+      <c r="AL24" s="144"/>
+      <c r="AM24" s="144"/>
     </row>
     <row r="25" spans="1:39">
       <c r="A25" s="138" t="s">
@@ -11310,41 +11310,41 @@
       <c r="B25" s="138"/>
       <c r="C25" s="138"/>
       <c r="D25" s="138"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="137"/>
-      <c r="H25" s="135"/>
-      <c r="I25" s="136"/>
-      <c r="J25" s="136"/>
-      <c r="K25" s="137"/>
-      <c r="L25" s="135"/>
-      <c r="M25" s="136"/>
-      <c r="N25" s="137"/>
-      <c r="O25" s="135"/>
-      <c r="P25" s="136"/>
-      <c r="Q25" s="136"/>
-      <c r="R25" s="137"/>
-      <c r="S25" s="135"/>
-      <c r="T25" s="136"/>
-      <c r="U25" s="137"/>
-      <c r="V25" s="135"/>
-      <c r="W25" s="136"/>
-      <c r="X25" s="136"/>
-      <c r="Y25" s="137"/>
-      <c r="Z25" s="135"/>
-      <c r="AA25" s="136"/>
-      <c r="AB25" s="137"/>
-      <c r="AC25" s="135"/>
-      <c r="AD25" s="136"/>
-      <c r="AE25" s="136"/>
-      <c r="AF25" s="137"/>
-      <c r="AG25" s="135"/>
-      <c r="AH25" s="136"/>
-      <c r="AI25" s="137"/>
-      <c r="AJ25" s="135"/>
-      <c r="AK25" s="136"/>
-      <c r="AL25" s="136"/>
-      <c r="AM25" s="137"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="142"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="141"/>
+      <c r="I25" s="142"/>
+      <c r="J25" s="142"/>
+      <c r="K25" s="143"/>
+      <c r="L25" s="141"/>
+      <c r="M25" s="142"/>
+      <c r="N25" s="143"/>
+      <c r="O25" s="141"/>
+      <c r="P25" s="142"/>
+      <c r="Q25" s="142"/>
+      <c r="R25" s="143"/>
+      <c r="S25" s="141"/>
+      <c r="T25" s="142"/>
+      <c r="U25" s="143"/>
+      <c r="V25" s="141"/>
+      <c r="W25" s="142"/>
+      <c r="X25" s="142"/>
+      <c r="Y25" s="143"/>
+      <c r="Z25" s="141"/>
+      <c r="AA25" s="142"/>
+      <c r="AB25" s="143"/>
+      <c r="AC25" s="141"/>
+      <c r="AD25" s="142"/>
+      <c r="AE25" s="142"/>
+      <c r="AF25" s="143"/>
+      <c r="AG25" s="141"/>
+      <c r="AH25" s="142"/>
+      <c r="AI25" s="143"/>
+      <c r="AJ25" s="141"/>
+      <c r="AK25" s="142"/>
+      <c r="AL25" s="142"/>
+      <c r="AM25" s="143"/>
     </row>
     <row r="26" spans="1:39">
       <c r="A26" s="138" t="s">
@@ -11353,155 +11353,155 @@
       <c r="B26" s="138"/>
       <c r="C26" s="138"/>
       <c r="D26" s="138"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="136"/>
-      <c r="G26" s="137"/>
-      <c r="H26" s="135"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="136"/>
-      <c r="K26" s="137"/>
-      <c r="L26" s="135"/>
-      <c r="M26" s="136"/>
-      <c r="N26" s="137"/>
-      <c r="O26" s="135"/>
-      <c r="P26" s="136"/>
-      <c r="Q26" s="136"/>
-      <c r="R26" s="137"/>
-      <c r="S26" s="135"/>
-      <c r="T26" s="136"/>
-      <c r="U26" s="137"/>
-      <c r="V26" s="135"/>
-      <c r="W26" s="136"/>
-      <c r="X26" s="136"/>
-      <c r="Y26" s="137"/>
-      <c r="Z26" s="135"/>
-      <c r="AA26" s="136"/>
-      <c r="AB26" s="137"/>
-      <c r="AC26" s="135"/>
-      <c r="AD26" s="136"/>
-      <c r="AE26" s="136"/>
-      <c r="AF26" s="137"/>
-      <c r="AG26" s="135"/>
-      <c r="AH26" s="136"/>
-      <c r="AI26" s="137"/>
-      <c r="AJ26" s="135"/>
-      <c r="AK26" s="136"/>
-      <c r="AL26" s="136"/>
-      <c r="AM26" s="137"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="141"/>
+      <c r="I26" s="142"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="143"/>
+      <c r="L26" s="141"/>
+      <c r="M26" s="142"/>
+      <c r="N26" s="143"/>
+      <c r="O26" s="141"/>
+      <c r="P26" s="142"/>
+      <c r="Q26" s="142"/>
+      <c r="R26" s="143"/>
+      <c r="S26" s="141"/>
+      <c r="T26" s="142"/>
+      <c r="U26" s="143"/>
+      <c r="V26" s="141"/>
+      <c r="W26" s="142"/>
+      <c r="X26" s="142"/>
+      <c r="Y26" s="143"/>
+      <c r="Z26" s="141"/>
+      <c r="AA26" s="142"/>
+      <c r="AB26" s="143"/>
+      <c r="AC26" s="141"/>
+      <c r="AD26" s="142"/>
+      <c r="AE26" s="142"/>
+      <c r="AF26" s="143"/>
+      <c r="AG26" s="141"/>
+      <c r="AH26" s="142"/>
+      <c r="AI26" s="143"/>
+      <c r="AJ26" s="141"/>
+      <c r="AK26" s="142"/>
+      <c r="AL26" s="142"/>
+      <c r="AM26" s="143"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="140" t="s">
+      <c r="A27" s="145" t="s">
         <v>160</v>
       </c>
-      <c r="B27" s="140"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="140"/>
-      <c r="E27" s="139" t="s">
+      <c r="B27" s="145"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="145"/>
+      <c r="E27" s="144" t="s">
         <v>198</v>
       </c>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
-      <c r="H27" s="139"/>
-      <c r="I27" s="139"/>
-      <c r="J27" s="139"/>
-      <c r="K27" s="139"/>
-      <c r="L27" s="139" t="s">
+      <c r="F27" s="144"/>
+      <c r="G27" s="144"/>
+      <c r="H27" s="144"/>
+      <c r="I27" s="144"/>
+      <c r="J27" s="144"/>
+      <c r="K27" s="144"/>
+      <c r="L27" s="144" t="s">
         <v>197</v>
       </c>
-      <c r="M27" s="139"/>
-      <c r="N27" s="139"/>
-      <c r="O27" s="139"/>
-      <c r="P27" s="139"/>
-      <c r="Q27" s="139"/>
-      <c r="R27" s="139"/>
-      <c r="S27" s="139" t="s">
+      <c r="M27" s="144"/>
+      <c r="N27" s="144"/>
+      <c r="O27" s="144"/>
+      <c r="P27" s="144"/>
+      <c r="Q27" s="144"/>
+      <c r="R27" s="144"/>
+      <c r="S27" s="144" t="s">
         <v>196</v>
       </c>
-      <c r="T27" s="139"/>
-      <c r="U27" s="139"/>
-      <c r="V27" s="139"/>
-      <c r="W27" s="139"/>
-      <c r="X27" s="139"/>
-      <c r="Y27" s="139"/>
-      <c r="Z27" s="139" t="s">
+      <c r="T27" s="144"/>
+      <c r="U27" s="144"/>
+      <c r="V27" s="144"/>
+      <c r="W27" s="144"/>
+      <c r="X27" s="144"/>
+      <c r="Y27" s="144"/>
+      <c r="Z27" s="144" t="s">
         <v>195</v>
       </c>
-      <c r="AA27" s="139"/>
-      <c r="AB27" s="139"/>
-      <c r="AC27" s="139"/>
-      <c r="AD27" s="139"/>
-      <c r="AE27" s="139"/>
-      <c r="AF27" s="139"/>
-      <c r="AG27" s="139" t="s">
+      <c r="AA27" s="144"/>
+      <c r="AB27" s="144"/>
+      <c r="AC27" s="144"/>
+      <c r="AD27" s="144"/>
+      <c r="AE27" s="144"/>
+      <c r="AF27" s="144"/>
+      <c r="AG27" s="144" t="s">
         <v>194</v>
       </c>
-      <c r="AH27" s="139"/>
-      <c r="AI27" s="139"/>
-      <c r="AJ27" s="139"/>
-      <c r="AK27" s="139"/>
-      <c r="AL27" s="139"/>
-      <c r="AM27" s="139"/>
+      <c r="AH27" s="144"/>
+      <c r="AI27" s="144"/>
+      <c r="AJ27" s="144"/>
+      <c r="AK27" s="144"/>
+      <c r="AL27" s="144"/>
+      <c r="AM27" s="144"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="140"/>
-      <c r="B28" s="140"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="140"/>
-      <c r="E28" s="139" t="s">
+      <c r="A28" s="145"/>
+      <c r="B28" s="145"/>
+      <c r="C28" s="145"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139" t="s">
+      <c r="F28" s="144"/>
+      <c r="G28" s="144"/>
+      <c r="H28" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="I28" s="139"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="139"/>
-      <c r="L28" s="139" t="s">
+      <c r="I28" s="144"/>
+      <c r="J28" s="144"/>
+      <c r="K28" s="144"/>
+      <c r="L28" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="M28" s="139"/>
-      <c r="N28" s="139"/>
-      <c r="O28" s="139" t="s">
+      <c r="M28" s="144"/>
+      <c r="N28" s="144"/>
+      <c r="O28" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="P28" s="139"/>
-      <c r="Q28" s="139"/>
-      <c r="R28" s="139"/>
-      <c r="S28" s="139" t="s">
+      <c r="P28" s="144"/>
+      <c r="Q28" s="144"/>
+      <c r="R28" s="144"/>
+      <c r="S28" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="T28" s="139"/>
-      <c r="U28" s="139"/>
-      <c r="V28" s="139" t="s">
+      <c r="T28" s="144"/>
+      <c r="U28" s="144"/>
+      <c r="V28" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="W28" s="139"/>
-      <c r="X28" s="139"/>
-      <c r="Y28" s="139"/>
-      <c r="Z28" s="139" t="s">
+      <c r="W28" s="144"/>
+      <c r="X28" s="144"/>
+      <c r="Y28" s="144"/>
+      <c r="Z28" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="AA28" s="139"/>
-      <c r="AB28" s="139"/>
-      <c r="AC28" s="139" t="s">
+      <c r="AA28" s="144"/>
+      <c r="AB28" s="144"/>
+      <c r="AC28" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="AD28" s="139"/>
-      <c r="AE28" s="139"/>
-      <c r="AF28" s="139"/>
-      <c r="AG28" s="139" t="s">
+      <c r="AD28" s="144"/>
+      <c r="AE28" s="144"/>
+      <c r="AF28" s="144"/>
+      <c r="AG28" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="AH28" s="139"/>
-      <c r="AI28" s="139"/>
-      <c r="AJ28" s="139" t="s">
+      <c r="AH28" s="144"/>
+      <c r="AI28" s="144"/>
+      <c r="AJ28" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="AK28" s="139"/>
-      <c r="AL28" s="139"/>
-      <c r="AM28" s="139"/>
+      <c r="AK28" s="144"/>
+      <c r="AL28" s="144"/>
+      <c r="AM28" s="144"/>
     </row>
     <row r="29" spans="1:39">
       <c r="A29" s="138" t="s">
@@ -11510,41 +11510,41 @@
       <c r="B29" s="138"/>
       <c r="C29" s="138"/>
       <c r="D29" s="138"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="136"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="135"/>
-      <c r="I29" s="136"/>
-      <c r="J29" s="136"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="135"/>
-      <c r="M29" s="136"/>
-      <c r="N29" s="137"/>
-      <c r="O29" s="135"/>
-      <c r="P29" s="136"/>
-      <c r="Q29" s="136"/>
-      <c r="R29" s="137"/>
-      <c r="S29" s="135"/>
-      <c r="T29" s="136"/>
-      <c r="U29" s="137"/>
-      <c r="V29" s="135"/>
-      <c r="W29" s="136"/>
-      <c r="X29" s="136"/>
-      <c r="Y29" s="137"/>
-      <c r="Z29" s="135"/>
-      <c r="AA29" s="136"/>
-      <c r="AB29" s="137"/>
-      <c r="AC29" s="135"/>
-      <c r="AD29" s="136"/>
-      <c r="AE29" s="136"/>
-      <c r="AF29" s="137"/>
-      <c r="AG29" s="135"/>
-      <c r="AH29" s="136"/>
-      <c r="AI29" s="137"/>
-      <c r="AJ29" s="135"/>
-      <c r="AK29" s="136"/>
-      <c r="AL29" s="136"/>
-      <c r="AM29" s="137"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="142"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="143"/>
+      <c r="L29" s="141"/>
+      <c r="M29" s="142"/>
+      <c r="N29" s="143"/>
+      <c r="O29" s="141"/>
+      <c r="P29" s="142"/>
+      <c r="Q29" s="142"/>
+      <c r="R29" s="143"/>
+      <c r="S29" s="141"/>
+      <c r="T29" s="142"/>
+      <c r="U29" s="143"/>
+      <c r="V29" s="141"/>
+      <c r="W29" s="142"/>
+      <c r="X29" s="142"/>
+      <c r="Y29" s="143"/>
+      <c r="Z29" s="141"/>
+      <c r="AA29" s="142"/>
+      <c r="AB29" s="143"/>
+      <c r="AC29" s="141"/>
+      <c r="AD29" s="142"/>
+      <c r="AE29" s="142"/>
+      <c r="AF29" s="143"/>
+      <c r="AG29" s="141"/>
+      <c r="AH29" s="142"/>
+      <c r="AI29" s="143"/>
+      <c r="AJ29" s="141"/>
+      <c r="AK29" s="142"/>
+      <c r="AL29" s="142"/>
+      <c r="AM29" s="143"/>
     </row>
     <row r="30" spans="1:39">
       <c r="A30" s="138" t="s">
@@ -11553,41 +11553,41 @@
       <c r="B30" s="138"/>
       <c r="C30" s="138"/>
       <c r="D30" s="138"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="136"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="135"/>
-      <c r="I30" s="136"/>
-      <c r="J30" s="136"/>
-      <c r="K30" s="137"/>
-      <c r="L30" s="135"/>
-      <c r="M30" s="136"/>
-      <c r="N30" s="137"/>
-      <c r="O30" s="135"/>
-      <c r="P30" s="136"/>
-      <c r="Q30" s="136"/>
-      <c r="R30" s="137"/>
-      <c r="S30" s="135"/>
-      <c r="T30" s="136"/>
-      <c r="U30" s="137"/>
-      <c r="V30" s="135"/>
-      <c r="W30" s="136"/>
-      <c r="X30" s="136"/>
-      <c r="Y30" s="137"/>
-      <c r="Z30" s="135"/>
-      <c r="AA30" s="136"/>
-      <c r="AB30" s="137"/>
-      <c r="AC30" s="135"/>
-      <c r="AD30" s="136"/>
-      <c r="AE30" s="136"/>
-      <c r="AF30" s="137"/>
-      <c r="AG30" s="135"/>
-      <c r="AH30" s="136"/>
-      <c r="AI30" s="137"/>
-      <c r="AJ30" s="135"/>
-      <c r="AK30" s="136"/>
-      <c r="AL30" s="136"/>
-      <c r="AM30" s="137"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="141"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="142"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="141"/>
+      <c r="M30" s="142"/>
+      <c r="N30" s="143"/>
+      <c r="O30" s="141"/>
+      <c r="P30" s="142"/>
+      <c r="Q30" s="142"/>
+      <c r="R30" s="143"/>
+      <c r="S30" s="141"/>
+      <c r="T30" s="142"/>
+      <c r="U30" s="143"/>
+      <c r="V30" s="141"/>
+      <c r="W30" s="142"/>
+      <c r="X30" s="142"/>
+      <c r="Y30" s="143"/>
+      <c r="Z30" s="141"/>
+      <c r="AA30" s="142"/>
+      <c r="AB30" s="143"/>
+      <c r="AC30" s="141"/>
+      <c r="AD30" s="142"/>
+      <c r="AE30" s="142"/>
+      <c r="AF30" s="143"/>
+      <c r="AG30" s="141"/>
+      <c r="AH30" s="142"/>
+      <c r="AI30" s="143"/>
+      <c r="AJ30" s="141"/>
+      <c r="AK30" s="142"/>
+      <c r="AL30" s="142"/>
+      <c r="AM30" s="143"/>
     </row>
     <row r="31" spans="1:39">
       <c r="A31" s="68" t="s">
@@ -11708,6 +11708,155 @@
     </row>
   </sheetData>
   <mergeCells count="173">
+    <mergeCell ref="S30:U30"/>
+    <mergeCell ref="V30:Y30"/>
+    <mergeCell ref="Z30:AB30"/>
+    <mergeCell ref="AC30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AM30"/>
+    <mergeCell ref="V29:Y29"/>
+    <mergeCell ref="Z29:AB29"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AM29"/>
+    <mergeCell ref="S29:U29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="S28:U28"/>
+    <mergeCell ref="V28:Y28"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="AC28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AJ28:AM28"/>
+    <mergeCell ref="A27:D28"/>
+    <mergeCell ref="E27:K27"/>
+    <mergeCell ref="L27:R27"/>
+    <mergeCell ref="S27:Y27"/>
+    <mergeCell ref="Z27:AF27"/>
+    <mergeCell ref="AG27:AM27"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="S26:U26"/>
+    <mergeCell ref="V26:Y26"/>
+    <mergeCell ref="Z26:AB26"/>
+    <mergeCell ref="AC26:AF26"/>
+    <mergeCell ref="AG26:AI26"/>
+    <mergeCell ref="AJ26:AM26"/>
+    <mergeCell ref="V25:Y25"/>
+    <mergeCell ref="Z25:AB25"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AM25"/>
+    <mergeCell ref="S25:U25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="AC20:AF20"/>
+    <mergeCell ref="AG20:AI20"/>
+    <mergeCell ref="AJ20:AM20"/>
+    <mergeCell ref="A23:D24"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="L23:R23"/>
+    <mergeCell ref="S23:Y23"/>
+    <mergeCell ref="Z23:AF23"/>
+    <mergeCell ref="AG23:AM23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="V24:Y24"/>
+    <mergeCell ref="Z24:AB24"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AJ24:AM24"/>
+    <mergeCell ref="AG19:AM19"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="Z20:AB20"/>
+    <mergeCell ref="AG21:AI21"/>
+    <mergeCell ref="AJ21:AM21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="S22:U22"/>
+    <mergeCell ref="V22:Y22"/>
+    <mergeCell ref="Z22:AB22"/>
+    <mergeCell ref="AC22:AF22"/>
+    <mergeCell ref="AG22:AI22"/>
+    <mergeCell ref="AJ22:AM22"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="S21:U21"/>
+    <mergeCell ref="V21:Y21"/>
+    <mergeCell ref="Z21:AB21"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:K12"/>
+    <mergeCell ref="L12:R12"/>
+    <mergeCell ref="S12:Y12"/>
+    <mergeCell ref="Z12:AF12"/>
+    <mergeCell ref="L19:R19"/>
+    <mergeCell ref="S19:Y19"/>
+    <mergeCell ref="Z19:AF19"/>
+    <mergeCell ref="A19:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="AC21:AF21"/>
+    <mergeCell ref="AG12:AM12"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:K10"/>
+    <mergeCell ref="L10:R10"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="Z10:AF10"/>
+    <mergeCell ref="AG10:AM10"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:K9"/>
+    <mergeCell ref="L9:R9"/>
+    <mergeCell ref="S9:Y9"/>
+    <mergeCell ref="Z9:AF9"/>
+    <mergeCell ref="AG9:AM9"/>
+    <mergeCell ref="AG6:AM6"/>
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="L5:R5"/>
+    <mergeCell ref="S5:Y5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:K8"/>
+    <mergeCell ref="L8:R8"/>
+    <mergeCell ref="S8:Y8"/>
+    <mergeCell ref="Z8:AF8"/>
+    <mergeCell ref="AG8:AM8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:K7"/>
+    <mergeCell ref="L7:R7"/>
+    <mergeCell ref="S7:Y7"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AM7"/>
     <mergeCell ref="AC3:AG3"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A3:K3"/>
@@ -11732,155 +11881,6 @@
     <mergeCell ref="L6:R6"/>
     <mergeCell ref="S6:Y6"/>
     <mergeCell ref="Z6:AF6"/>
-    <mergeCell ref="AG6:AM6"/>
-    <mergeCell ref="E5:K5"/>
-    <mergeCell ref="L5:R5"/>
-    <mergeCell ref="S5:Y5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:K8"/>
-    <mergeCell ref="L8:R8"/>
-    <mergeCell ref="S8:Y8"/>
-    <mergeCell ref="Z8:AF8"/>
-    <mergeCell ref="AG8:AM8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:K7"/>
-    <mergeCell ref="L7:R7"/>
-    <mergeCell ref="S7:Y7"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AM7"/>
-    <mergeCell ref="AG12:AM12"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E10:K10"/>
-    <mergeCell ref="L10:R10"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="Z10:AF10"/>
-    <mergeCell ref="AG10:AM10"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:K9"/>
-    <mergeCell ref="L9:R9"/>
-    <mergeCell ref="S9:Y9"/>
-    <mergeCell ref="Z9:AF9"/>
-    <mergeCell ref="AG9:AM9"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="V21:Y21"/>
-    <mergeCell ref="Z21:AB21"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E12:K12"/>
-    <mergeCell ref="L12:R12"/>
-    <mergeCell ref="S12:Y12"/>
-    <mergeCell ref="Z12:AF12"/>
-    <mergeCell ref="L19:R19"/>
-    <mergeCell ref="S19:Y19"/>
-    <mergeCell ref="Z19:AF19"/>
-    <mergeCell ref="A19:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="E19:K19"/>
-    <mergeCell ref="AC21:AF21"/>
-    <mergeCell ref="AG19:AM19"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="S20:U20"/>
-    <mergeCell ref="V20:Y20"/>
-    <mergeCell ref="Z20:AB20"/>
-    <mergeCell ref="AG21:AI21"/>
-    <mergeCell ref="AJ21:AM21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="S22:U22"/>
-    <mergeCell ref="V22:Y22"/>
-    <mergeCell ref="Z22:AB22"/>
-    <mergeCell ref="AC22:AF22"/>
-    <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AJ22:AM22"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="AC20:AF20"/>
-    <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="AJ20:AM20"/>
-    <mergeCell ref="A23:D24"/>
-    <mergeCell ref="E23:K23"/>
-    <mergeCell ref="L23:R23"/>
-    <mergeCell ref="S23:Y23"/>
-    <mergeCell ref="Z23:AF23"/>
-    <mergeCell ref="AG23:AM23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="V24:Y24"/>
-    <mergeCell ref="Z24:AB24"/>
-    <mergeCell ref="AC24:AF24"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="AJ24:AM24"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="S26:U26"/>
-    <mergeCell ref="V26:Y26"/>
-    <mergeCell ref="Z26:AB26"/>
-    <mergeCell ref="AC26:AF26"/>
-    <mergeCell ref="AG26:AI26"/>
-    <mergeCell ref="AJ26:AM26"/>
-    <mergeCell ref="V25:Y25"/>
-    <mergeCell ref="Z25:AB25"/>
-    <mergeCell ref="AC25:AF25"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AM25"/>
-    <mergeCell ref="S25:U25"/>
-    <mergeCell ref="S28:U28"/>
-    <mergeCell ref="V28:Y28"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="AC28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ28:AM28"/>
-    <mergeCell ref="A27:D28"/>
-    <mergeCell ref="E27:K27"/>
-    <mergeCell ref="L27:R27"/>
-    <mergeCell ref="S27:Y27"/>
-    <mergeCell ref="Z27:AF27"/>
-    <mergeCell ref="AG27:AM27"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="S30:U30"/>
-    <mergeCell ref="V30:Y30"/>
-    <mergeCell ref="Z30:AB30"/>
-    <mergeCell ref="AC30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AM30"/>
-    <mergeCell ref="V29:Y29"/>
-    <mergeCell ref="Z29:AB29"/>
-    <mergeCell ref="AC29:AF29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AM29"/>
-    <mergeCell ref="S29:U29"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11921,32 +11921,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
-      <c r="U1" s="144"/>
-      <c r="V1" s="144"/>
-      <c r="W1" s="144"/>
-      <c r="X1" s="144"/>
-      <c r="Y1" s="144"/>
-      <c r="Z1" s="144"/>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="144"/>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="144"/>
-      <c r="AF1" s="144"/>
-      <c r="AG1" s="144"/>
-      <c r="AH1" s="144"/>
-      <c r="AI1" s="144"/>
-      <c r="AJ1" s="144"/>
-      <c r="AK1" s="144"/>
-      <c r="AL1" s="144"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="135"/>
+      <c r="S1" s="135"/>
+      <c r="T1" s="135"/>
+      <c r="U1" s="135"/>
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="135"/>
+      <c r="Z1" s="135"/>
+      <c r="AA1" s="135"/>
+      <c r="AB1" s="135"/>
+      <c r="AC1" s="135"/>
+      <c r="AD1" s="135"/>
+      <c r="AE1" s="135"/>
+      <c r="AF1" s="135"/>
+      <c r="AG1" s="135"/>
+      <c r="AH1" s="135"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="135"/>
+      <c r="AL1" s="135"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="33" t="s">
@@ -11988,17 +11988,17 @@
       <c r="AL2" s="34"/>
     </row>
     <row r="3" spans="1:38">
-      <c r="A3" s="141"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
+      <c r="A3" s="136"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -12075,12 +12075,12 @@
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="35"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
       <c r="L5" s="6" t="s">
         <v>129</v>
       </c>
@@ -12118,13 +12118,13 @@
       <c r="B6" s="6"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
-      <c r="I6" s="157"/>
-      <c r="J6" s="157"/>
-      <c r="K6" s="157"/>
+      <c r="E6" s="147"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="147"/>
+      <c r="H6" s="147"/>
+      <c r="I6" s="147"/>
+      <c r="J6" s="147"/>
+      <c r="K6" s="147"/>
       <c r="L6" s="6" t="s">
         <v>131</v>
       </c>
@@ -12166,13 +12166,13 @@
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="37"/>
-      <c r="I7" s="158"/>
-      <c r="J7" s="158"/>
-      <c r="K7" s="158"/>
-      <c r="L7" s="158"/>
-      <c r="M7" s="158"/>
-      <c r="N7" s="158"/>
-      <c r="O7" s="158"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="148"/>
+      <c r="L7" s="148"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="148"/>
+      <c r="O7" s="148"/>
       <c r="P7" s="37"/>
       <c r="Q7" s="37"/>
       <c r="R7" s="37"/>
@@ -12285,547 +12285,547 @@
       </c>
       <c r="B10" s="65"/>
       <c r="C10" s="66"/>
-      <c r="D10" s="151"/>
-      <c r="E10" s="151"/>
-      <c r="F10" s="151"/>
-      <c r="G10" s="155" t="s">
+      <c r="D10" s="150"/>
+      <c r="E10" s="150"/>
+      <c r="F10" s="150"/>
+      <c r="G10" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="H10" s="156"/>
-      <c r="I10" s="153"/>
-      <c r="J10" s="154"/>
-      <c r="K10" s="154"/>
-      <c r="L10" s="154"/>
-      <c r="M10" s="154"/>
-      <c r="N10" s="154"/>
-      <c r="O10" s="154"/>
-      <c r="P10" s="154"/>
-      <c r="Q10" s="154"/>
-      <c r="R10" s="154"/>
-      <c r="S10" s="154"/>
-      <c r="T10" s="154"/>
-      <c r="U10" s="154"/>
-      <c r="V10" s="154"/>
-      <c r="W10" s="154"/>
-      <c r="X10" s="154"/>
-      <c r="Y10" s="154"/>
-      <c r="Z10" s="154"/>
-      <c r="AA10" s="154"/>
-      <c r="AB10" s="154"/>
-      <c r="AC10" s="154"/>
-      <c r="AD10" s="154"/>
-      <c r="AE10" s="154"/>
-      <c r="AF10" s="154"/>
-      <c r="AG10" s="154"/>
-      <c r="AH10" s="154"/>
-      <c r="AI10" s="154"/>
-      <c r="AJ10" s="154"/>
-      <c r="AK10" s="154"/>
-      <c r="AL10" s="154"/>
+      <c r="H10" s="154"/>
+      <c r="I10" s="152"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="146"/>
+      <c r="L10" s="146"/>
+      <c r="M10" s="146"/>
+      <c r="N10" s="146"/>
+      <c r="O10" s="146"/>
+      <c r="P10" s="146"/>
+      <c r="Q10" s="146"/>
+      <c r="R10" s="146"/>
+      <c r="S10" s="146"/>
+      <c r="T10" s="146"/>
+      <c r="U10" s="146"/>
+      <c r="V10" s="146"/>
+      <c r="W10" s="146"/>
+      <c r="X10" s="146"/>
+      <c r="Y10" s="146"/>
+      <c r="Z10" s="146"/>
+      <c r="AA10" s="146"/>
+      <c r="AB10" s="146"/>
+      <c r="AC10" s="146"/>
+      <c r="AD10" s="146"/>
+      <c r="AE10" s="146"/>
+      <c r="AF10" s="146"/>
+      <c r="AG10" s="146"/>
+      <c r="AH10" s="146"/>
+      <c r="AI10" s="146"/>
+      <c r="AJ10" s="146"/>
+      <c r="AK10" s="146"/>
+      <c r="AL10" s="146"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1">
-      <c r="A11" s="150" t="s">
+      <c r="A11" s="149" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="150"/>
-      <c r="C11" s="152"/>
-      <c r="D11" s="152"/>
-      <c r="E11" s="152"/>
-      <c r="F11" s="152"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="150"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="150"/>
-      <c r="N11" s="150"/>
-      <c r="O11" s="150"/>
-      <c r="P11" s="150"/>
-      <c r="Q11" s="150"/>
-      <c r="R11" s="150"/>
-      <c r="S11" s="150"/>
-      <c r="T11" s="150"/>
-      <c r="U11" s="150"/>
-      <c r="V11" s="150"/>
-      <c r="W11" s="150"/>
-      <c r="X11" s="150"/>
-      <c r="Y11" s="150"/>
-      <c r="Z11" s="150"/>
-      <c r="AA11" s="150"/>
-      <c r="AB11" s="150"/>
-      <c r="AC11" s="150"/>
-      <c r="AD11" s="150"/>
-      <c r="AE11" s="150"/>
-      <c r="AF11" s="150"/>
-      <c r="AG11" s="150"/>
-      <c r="AH11" s="150"/>
-      <c r="AI11" s="150"/>
-      <c r="AJ11" s="150"/>
-      <c r="AK11" s="150"/>
-      <c r="AL11" s="150"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="151"/>
+      <c r="H11" s="151"/>
+      <c r="I11" s="149"/>
+      <c r="J11" s="149"/>
+      <c r="K11" s="149"/>
+      <c r="L11" s="149"/>
+      <c r="M11" s="149"/>
+      <c r="N11" s="149"/>
+      <c r="O11" s="149"/>
+      <c r="P11" s="149"/>
+      <c r="Q11" s="149"/>
+      <c r="R11" s="149"/>
+      <c r="S11" s="149"/>
+      <c r="T11" s="149"/>
+      <c r="U11" s="149"/>
+      <c r="V11" s="149"/>
+      <c r="W11" s="149"/>
+      <c r="X11" s="149"/>
+      <c r="Y11" s="149"/>
+      <c r="Z11" s="149"/>
+      <c r="AA11" s="149"/>
+      <c r="AB11" s="149"/>
+      <c r="AC11" s="149"/>
+      <c r="AD11" s="149"/>
+      <c r="AE11" s="149"/>
+      <c r="AF11" s="149"/>
+      <c r="AG11" s="149"/>
+      <c r="AH11" s="149"/>
+      <c r="AI11" s="149"/>
+      <c r="AJ11" s="149"/>
+      <c r="AK11" s="149"/>
+      <c r="AL11" s="149"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="150" t="s">
+      <c r="A12" s="149" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="150"/>
-      <c r="C12" s="150"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="150"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="150"/>
-      <c r="K12" s="150"/>
-      <c r="L12" s="150"/>
-      <c r="M12" s="150"/>
-      <c r="N12" s="150"/>
-      <c r="O12" s="150"/>
-      <c r="P12" s="150"/>
-      <c r="Q12" s="150"/>
-      <c r="R12" s="150"/>
-      <c r="S12" s="150"/>
-      <c r="T12" s="150"/>
-      <c r="U12" s="150"/>
-      <c r="V12" s="150"/>
-      <c r="W12" s="150"/>
-      <c r="X12" s="150"/>
-      <c r="Y12" s="150"/>
-      <c r="Z12" s="150"/>
-      <c r="AA12" s="150"/>
-      <c r="AB12" s="150"/>
-      <c r="AC12" s="150"/>
-      <c r="AD12" s="150"/>
-      <c r="AE12" s="150"/>
-      <c r="AF12" s="150"/>
-      <c r="AG12" s="150"/>
-      <c r="AH12" s="150"/>
-      <c r="AI12" s="150"/>
-      <c r="AJ12" s="150"/>
-      <c r="AK12" s="150"/>
-      <c r="AL12" s="150"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="149"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="149"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="149"/>
+      <c r="J12" s="149"/>
+      <c r="K12" s="149"/>
+      <c r="L12" s="149"/>
+      <c r="M12" s="149"/>
+      <c r="N12" s="149"/>
+      <c r="O12" s="149"/>
+      <c r="P12" s="149"/>
+      <c r="Q12" s="149"/>
+      <c r="R12" s="149"/>
+      <c r="S12" s="149"/>
+      <c r="T12" s="149"/>
+      <c r="U12" s="149"/>
+      <c r="V12" s="149"/>
+      <c r="W12" s="149"/>
+      <c r="X12" s="149"/>
+      <c r="Y12" s="149"/>
+      <c r="Z12" s="149"/>
+      <c r="AA12" s="149"/>
+      <c r="AB12" s="149"/>
+      <c r="AC12" s="149"/>
+      <c r="AD12" s="149"/>
+      <c r="AE12" s="149"/>
+      <c r="AF12" s="149"/>
+      <c r="AG12" s="149"/>
+      <c r="AH12" s="149"/>
+      <c r="AI12" s="149"/>
+      <c r="AJ12" s="149"/>
+      <c r="AK12" s="149"/>
+      <c r="AL12" s="149"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="150" t="s">
+      <c r="A13" s="149" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="150"/>
-      <c r="C13" s="150"/>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="150"/>
-      <c r="G13" s="150"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="150"/>
-      <c r="J13" s="150"/>
-      <c r="K13" s="150"/>
-      <c r="L13" s="150"/>
-      <c r="M13" s="150"/>
-      <c r="N13" s="150"/>
-      <c r="O13" s="150"/>
-      <c r="P13" s="150"/>
-      <c r="Q13" s="150"/>
-      <c r="R13" s="150"/>
-      <c r="S13" s="150"/>
-      <c r="T13" s="150"/>
-      <c r="U13" s="150"/>
-      <c r="V13" s="150"/>
-      <c r="W13" s="150"/>
-      <c r="X13" s="150"/>
-      <c r="Y13" s="150"/>
-      <c r="Z13" s="150"/>
-      <c r="AA13" s="150"/>
-      <c r="AB13" s="150"/>
-      <c r="AC13" s="150"/>
-      <c r="AD13" s="150"/>
-      <c r="AE13" s="150"/>
-      <c r="AF13" s="150"/>
-      <c r="AG13" s="150"/>
-      <c r="AH13" s="150"/>
-      <c r="AI13" s="150"/>
-      <c r="AJ13" s="150"/>
-      <c r="AK13" s="150"/>
-      <c r="AL13" s="150"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149"/>
+      <c r="F13" s="149"/>
+      <c r="G13" s="149"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="149"/>
+      <c r="J13" s="149"/>
+      <c r="K13" s="149"/>
+      <c r="L13" s="149"/>
+      <c r="M13" s="149"/>
+      <c r="N13" s="149"/>
+      <c r="O13" s="149"/>
+      <c r="P13" s="149"/>
+      <c r="Q13" s="149"/>
+      <c r="R13" s="149"/>
+      <c r="S13" s="149"/>
+      <c r="T13" s="149"/>
+      <c r="U13" s="149"/>
+      <c r="V13" s="149"/>
+      <c r="W13" s="149"/>
+      <c r="X13" s="149"/>
+      <c r="Y13" s="149"/>
+      <c r="Z13" s="149"/>
+      <c r="AA13" s="149"/>
+      <c r="AB13" s="149"/>
+      <c r="AC13" s="149"/>
+      <c r="AD13" s="149"/>
+      <c r="AE13" s="149"/>
+      <c r="AF13" s="149"/>
+      <c r="AG13" s="149"/>
+      <c r="AH13" s="149"/>
+      <c r="AI13" s="149"/>
+      <c r="AJ13" s="149"/>
+      <c r="AK13" s="149"/>
+      <c r="AL13" s="149"/>
     </row>
     <row r="14" spans="1:38" ht="18" customHeight="1">
-      <c r="A14" s="150" t="s">
+      <c r="A14" s="149" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="150"/>
-      <c r="C14" s="150"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="150"/>
-      <c r="M14" s="150"/>
-      <c r="N14" s="150"/>
-      <c r="O14" s="150"/>
-      <c r="P14" s="150"/>
-      <c r="Q14" s="150"/>
-      <c r="R14" s="150"/>
-      <c r="S14" s="150"/>
-      <c r="T14" s="150"/>
-      <c r="U14" s="150"/>
-      <c r="V14" s="150"/>
-      <c r="W14" s="150"/>
-      <c r="X14" s="150"/>
-      <c r="Y14" s="150"/>
-      <c r="Z14" s="150"/>
-      <c r="AA14" s="150"/>
-      <c r="AB14" s="150"/>
-      <c r="AC14" s="150"/>
-      <c r="AD14" s="150"/>
-      <c r="AE14" s="150"/>
-      <c r="AF14" s="150"/>
-      <c r="AG14" s="150"/>
-      <c r="AH14" s="150"/>
-      <c r="AI14" s="150"/>
-      <c r="AJ14" s="150"/>
-      <c r="AK14" s="150"/>
-      <c r="AL14" s="150"/>
+      <c r="B14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="149"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="149"/>
+      <c r="J14" s="149"/>
+      <c r="K14" s="149"/>
+      <c r="L14" s="149"/>
+      <c r="M14" s="149"/>
+      <c r="N14" s="149"/>
+      <c r="O14" s="149"/>
+      <c r="P14" s="149"/>
+      <c r="Q14" s="149"/>
+      <c r="R14" s="149"/>
+      <c r="S14" s="149"/>
+      <c r="T14" s="149"/>
+      <c r="U14" s="149"/>
+      <c r="V14" s="149"/>
+      <c r="W14" s="149"/>
+      <c r="X14" s="149"/>
+      <c r="Y14" s="149"/>
+      <c r="Z14" s="149"/>
+      <c r="AA14" s="149"/>
+      <c r="AB14" s="149"/>
+      <c r="AC14" s="149"/>
+      <c r="AD14" s="149"/>
+      <c r="AE14" s="149"/>
+      <c r="AF14" s="149"/>
+      <c r="AG14" s="149"/>
+      <c r="AH14" s="149"/>
+      <c r="AI14" s="149"/>
+      <c r="AJ14" s="149"/>
+      <c r="AK14" s="149"/>
+      <c r="AL14" s="149"/>
     </row>
     <row r="15" spans="1:38" ht="18" customHeight="1">
-      <c r="A15" s="150" t="s">
+      <c r="A15" s="149" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="150"/>
-      <c r="C15" s="150"/>
-      <c r="D15" s="150"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="150"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="150"/>
-      <c r="M15" s="150"/>
-      <c r="N15" s="150"/>
-      <c r="O15" s="150"/>
-      <c r="P15" s="150"/>
-      <c r="Q15" s="150"/>
-      <c r="R15" s="150"/>
-      <c r="S15" s="150"/>
-      <c r="T15" s="150"/>
-      <c r="U15" s="150"/>
-      <c r="V15" s="150"/>
-      <c r="W15" s="150"/>
-      <c r="X15" s="150"/>
-      <c r="Y15" s="150"/>
-      <c r="Z15" s="150"/>
-      <c r="AA15" s="150"/>
-      <c r="AB15" s="150"/>
-      <c r="AC15" s="150"/>
-      <c r="AD15" s="150"/>
-      <c r="AE15" s="150"/>
-      <c r="AF15" s="150"/>
-      <c r="AG15" s="150"/>
-      <c r="AH15" s="150"/>
-      <c r="AI15" s="150"/>
-      <c r="AJ15" s="150"/>
-      <c r="AK15" s="150"/>
-      <c r="AL15" s="150"/>
+      <c r="B15" s="149"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="149"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="149"/>
+      <c r="J15" s="149"/>
+      <c r="K15" s="149"/>
+      <c r="L15" s="149"/>
+      <c r="M15" s="149"/>
+      <c r="N15" s="149"/>
+      <c r="O15" s="149"/>
+      <c r="P15" s="149"/>
+      <c r="Q15" s="149"/>
+      <c r="R15" s="149"/>
+      <c r="S15" s="149"/>
+      <c r="T15" s="149"/>
+      <c r="U15" s="149"/>
+      <c r="V15" s="149"/>
+      <c r="W15" s="149"/>
+      <c r="X15" s="149"/>
+      <c r="Y15" s="149"/>
+      <c r="Z15" s="149"/>
+      <c r="AA15" s="149"/>
+      <c r="AB15" s="149"/>
+      <c r="AC15" s="149"/>
+      <c r="AD15" s="149"/>
+      <c r="AE15" s="149"/>
+      <c r="AF15" s="149"/>
+      <c r="AG15" s="149"/>
+      <c r="AH15" s="149"/>
+      <c r="AI15" s="149"/>
+      <c r="AJ15" s="149"/>
+      <c r="AK15" s="149"/>
+      <c r="AL15" s="149"/>
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
-      <c r="A16" s="150" t="s">
+      <c r="A16" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="150"/>
-      <c r="C16" s="150"/>
-      <c r="D16" s="150"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="150"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="150"/>
-      <c r="M16" s="150"/>
-      <c r="N16" s="150"/>
-      <c r="O16" s="150"/>
-      <c r="P16" s="150"/>
-      <c r="Q16" s="150"/>
-      <c r="R16" s="150"/>
-      <c r="S16" s="150"/>
-      <c r="T16" s="150"/>
-      <c r="U16" s="150"/>
-      <c r="V16" s="150"/>
-      <c r="W16" s="150"/>
-      <c r="X16" s="150"/>
-      <c r="Y16" s="150"/>
-      <c r="Z16" s="150"/>
-      <c r="AA16" s="150"/>
-      <c r="AB16" s="150"/>
-      <c r="AC16" s="150"/>
-      <c r="AD16" s="150"/>
-      <c r="AE16" s="150"/>
-      <c r="AF16" s="150"/>
-      <c r="AG16" s="150"/>
-      <c r="AH16" s="150"/>
-      <c r="AI16" s="150"/>
-      <c r="AJ16" s="150"/>
-      <c r="AK16" s="150"/>
-      <c r="AL16" s="150"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="149"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="149"/>
+      <c r="M16" s="149"/>
+      <c r="N16" s="149"/>
+      <c r="O16" s="149"/>
+      <c r="P16" s="149"/>
+      <c r="Q16" s="149"/>
+      <c r="R16" s="149"/>
+      <c r="S16" s="149"/>
+      <c r="T16" s="149"/>
+      <c r="U16" s="149"/>
+      <c r="V16" s="149"/>
+      <c r="W16" s="149"/>
+      <c r="X16" s="149"/>
+      <c r="Y16" s="149"/>
+      <c r="Z16" s="149"/>
+      <c r="AA16" s="149"/>
+      <c r="AB16" s="149"/>
+      <c r="AC16" s="149"/>
+      <c r="AD16" s="149"/>
+      <c r="AE16" s="149"/>
+      <c r="AF16" s="149"/>
+      <c r="AG16" s="149"/>
+      <c r="AH16" s="149"/>
+      <c r="AI16" s="149"/>
+      <c r="AJ16" s="149"/>
+      <c r="AK16" s="149"/>
+      <c r="AL16" s="149"/>
     </row>
     <row r="17" spans="1:38" ht="18" customHeight="1">
-      <c r="A17" s="150" t="s">
+      <c r="A17" s="149" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="150"/>
-      <c r="C17" s="150"/>
-      <c r="D17" s="150"/>
-      <c r="E17" s="150"/>
-      <c r="F17" s="150"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="150"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="150"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="150"/>
-      <c r="R17" s="150"/>
-      <c r="S17" s="150"/>
-      <c r="T17" s="150"/>
-      <c r="U17" s="150"/>
-      <c r="V17" s="150"/>
-      <c r="W17" s="150"/>
-      <c r="X17" s="150"/>
-      <c r="Y17" s="150"/>
-      <c r="Z17" s="150"/>
-      <c r="AA17" s="150"/>
-      <c r="AB17" s="150"/>
-      <c r="AC17" s="150"/>
-      <c r="AD17" s="150"/>
-      <c r="AE17" s="150"/>
-      <c r="AF17" s="150"/>
-      <c r="AG17" s="150"/>
-      <c r="AH17" s="150"/>
-      <c r="AI17" s="150"/>
-      <c r="AJ17" s="150"/>
-      <c r="AK17" s="150"/>
-      <c r="AL17" s="150"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
+      <c r="I17" s="149"/>
+      <c r="J17" s="149"/>
+      <c r="K17" s="149"/>
+      <c r="L17" s="149"/>
+      <c r="M17" s="149"/>
+      <c r="N17" s="149"/>
+      <c r="O17" s="149"/>
+      <c r="P17" s="149"/>
+      <c r="Q17" s="149"/>
+      <c r="R17" s="149"/>
+      <c r="S17" s="149"/>
+      <c r="T17" s="149"/>
+      <c r="U17" s="149"/>
+      <c r="V17" s="149"/>
+      <c r="W17" s="149"/>
+      <c r="X17" s="149"/>
+      <c r="Y17" s="149"/>
+      <c r="Z17" s="149"/>
+      <c r="AA17" s="149"/>
+      <c r="AB17" s="149"/>
+      <c r="AC17" s="149"/>
+      <c r="AD17" s="149"/>
+      <c r="AE17" s="149"/>
+      <c r="AF17" s="149"/>
+      <c r="AG17" s="149"/>
+      <c r="AH17" s="149"/>
+      <c r="AI17" s="149"/>
+      <c r="AJ17" s="149"/>
+      <c r="AK17" s="149"/>
+      <c r="AL17" s="149"/>
     </row>
     <row r="18" spans="1:38" ht="18" customHeight="1">
-      <c r="A18" s="150" t="s">
+      <c r="A18" s="149" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="150"/>
-      <c r="C18" s="150"/>
-      <c r="D18" s="150"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="150"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="150"/>
-      <c r="K18" s="150"/>
-      <c r="L18" s="150"/>
-      <c r="M18" s="150"/>
-      <c r="N18" s="150"/>
-      <c r="O18" s="150"/>
-      <c r="P18" s="150"/>
-      <c r="Q18" s="150"/>
-      <c r="R18" s="150"/>
-      <c r="S18" s="150"/>
-      <c r="T18" s="150"/>
-      <c r="U18" s="150"/>
-      <c r="V18" s="150"/>
-      <c r="W18" s="150"/>
-      <c r="X18" s="150"/>
-      <c r="Y18" s="150"/>
-      <c r="Z18" s="150"/>
-      <c r="AA18" s="150"/>
-      <c r="AB18" s="150"/>
-      <c r="AC18" s="150"/>
-      <c r="AD18" s="150"/>
-      <c r="AE18" s="150"/>
-      <c r="AF18" s="150"/>
-      <c r="AG18" s="150"/>
-      <c r="AH18" s="150"/>
-      <c r="AI18" s="150"/>
-      <c r="AJ18" s="150"/>
-      <c r="AK18" s="150"/>
-      <c r="AL18" s="150"/>
+      <c r="B18" s="149"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="149"/>
+      <c r="G18" s="149"/>
+      <c r="H18" s="149"/>
+      <c r="I18" s="149"/>
+      <c r="J18" s="149"/>
+      <c r="K18" s="149"/>
+      <c r="L18" s="149"/>
+      <c r="M18" s="149"/>
+      <c r="N18" s="149"/>
+      <c r="O18" s="149"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
+      <c r="S18" s="149"/>
+      <c r="T18" s="149"/>
+      <c r="U18" s="149"/>
+      <c r="V18" s="149"/>
+      <c r="W18" s="149"/>
+      <c r="X18" s="149"/>
+      <c r="Y18" s="149"/>
+      <c r="Z18" s="149"/>
+      <c r="AA18" s="149"/>
+      <c r="AB18" s="149"/>
+      <c r="AC18" s="149"/>
+      <c r="AD18" s="149"/>
+      <c r="AE18" s="149"/>
+      <c r="AF18" s="149"/>
+      <c r="AG18" s="149"/>
+      <c r="AH18" s="149"/>
+      <c r="AI18" s="149"/>
+      <c r="AJ18" s="149"/>
+      <c r="AK18" s="149"/>
+      <c r="AL18" s="149"/>
     </row>
     <row r="19" spans="1:38" ht="18" customHeight="1">
-      <c r="A19" s="150" t="s">
+      <c r="A19" s="149" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="150"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="150"/>
-      <c r="I19" s="150"/>
-      <c r="J19" s="150"/>
-      <c r="K19" s="150"/>
-      <c r="L19" s="150"/>
-      <c r="M19" s="150"/>
-      <c r="N19" s="150"/>
-      <c r="O19" s="150"/>
-      <c r="P19" s="150"/>
-      <c r="Q19" s="150"/>
-      <c r="R19" s="150"/>
-      <c r="S19" s="150"/>
-      <c r="T19" s="150"/>
-      <c r="U19" s="150"/>
-      <c r="V19" s="150"/>
-      <c r="W19" s="150"/>
-      <c r="X19" s="150"/>
-      <c r="Y19" s="150"/>
-      <c r="Z19" s="150"/>
-      <c r="AA19" s="150"/>
-      <c r="AB19" s="150"/>
-      <c r="AC19" s="150"/>
-      <c r="AD19" s="150"/>
-      <c r="AE19" s="150"/>
-      <c r="AF19" s="150"/>
-      <c r="AG19" s="150"/>
-      <c r="AH19" s="150"/>
-      <c r="AI19" s="150"/>
-      <c r="AJ19" s="150"/>
-      <c r="AK19" s="150"/>
-      <c r="AL19" s="150"/>
+      <c r="B19" s="149"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="149"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="149"/>
+      <c r="G19" s="149"/>
+      <c r="H19" s="149"/>
+      <c r="I19" s="149"/>
+      <c r="J19" s="149"/>
+      <c r="K19" s="149"/>
+      <c r="L19" s="149"/>
+      <c r="M19" s="149"/>
+      <c r="N19" s="149"/>
+      <c r="O19" s="149"/>
+      <c r="P19" s="149"/>
+      <c r="Q19" s="149"/>
+      <c r="R19" s="149"/>
+      <c r="S19" s="149"/>
+      <c r="T19" s="149"/>
+      <c r="U19" s="149"/>
+      <c r="V19" s="149"/>
+      <c r="W19" s="149"/>
+      <c r="X19" s="149"/>
+      <c r="Y19" s="149"/>
+      <c r="Z19" s="149"/>
+      <c r="AA19" s="149"/>
+      <c r="AB19" s="149"/>
+      <c r="AC19" s="149"/>
+      <c r="AD19" s="149"/>
+      <c r="AE19" s="149"/>
+      <c r="AF19" s="149"/>
+      <c r="AG19" s="149"/>
+      <c r="AH19" s="149"/>
+      <c r="AI19" s="149"/>
+      <c r="AJ19" s="149"/>
+      <c r="AK19" s="149"/>
+      <c r="AL19" s="149"/>
     </row>
     <row r="20" spans="1:38" ht="18" customHeight="1">
-      <c r="A20" s="150" t="s">
+      <c r="A20" s="149" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="150"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="150"/>
-      <c r="I20" s="150"/>
-      <c r="J20" s="150"/>
-      <c r="K20" s="150"/>
-      <c r="L20" s="150"/>
-      <c r="M20" s="150"/>
-      <c r="N20" s="150"/>
-      <c r="O20" s="150"/>
-      <c r="P20" s="150"/>
-      <c r="Q20" s="150"/>
-      <c r="R20" s="150"/>
-      <c r="S20" s="150"/>
-      <c r="T20" s="150"/>
-      <c r="U20" s="150"/>
-      <c r="V20" s="150"/>
-      <c r="W20" s="150"/>
-      <c r="X20" s="150"/>
-      <c r="Y20" s="150"/>
-      <c r="Z20" s="150"/>
-      <c r="AA20" s="150"/>
-      <c r="AB20" s="150"/>
-      <c r="AC20" s="150"/>
-      <c r="AD20" s="150"/>
-      <c r="AE20" s="150"/>
-      <c r="AF20" s="150"/>
-      <c r="AG20" s="150"/>
-      <c r="AH20" s="150"/>
-      <c r="AI20" s="150"/>
-      <c r="AJ20" s="150"/>
-      <c r="AK20" s="150"/>
-      <c r="AL20" s="150"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="149"/>
+      <c r="I20" s="149"/>
+      <c r="J20" s="149"/>
+      <c r="K20" s="149"/>
+      <c r="L20" s="149"/>
+      <c r="M20" s="149"/>
+      <c r="N20" s="149"/>
+      <c r="O20" s="149"/>
+      <c r="P20" s="149"/>
+      <c r="Q20" s="149"/>
+      <c r="R20" s="149"/>
+      <c r="S20" s="149"/>
+      <c r="T20" s="149"/>
+      <c r="U20" s="149"/>
+      <c r="V20" s="149"/>
+      <c r="W20" s="149"/>
+      <c r="X20" s="149"/>
+      <c r="Y20" s="149"/>
+      <c r="Z20" s="149"/>
+      <c r="AA20" s="149"/>
+      <c r="AB20" s="149"/>
+      <c r="AC20" s="149"/>
+      <c r="AD20" s="149"/>
+      <c r="AE20" s="149"/>
+      <c r="AF20" s="149"/>
+      <c r="AG20" s="149"/>
+      <c r="AH20" s="149"/>
+      <c r="AI20" s="149"/>
+      <c r="AJ20" s="149"/>
+      <c r="AK20" s="149"/>
+      <c r="AL20" s="149"/>
     </row>
     <row r="21" spans="1:38" ht="18" customHeight="1">
-      <c r="A21" s="150" t="s">
+      <c r="A21" s="149" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="150"/>
-      <c r="C21" s="150"/>
-      <c r="D21" s="150"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="150"/>
-      <c r="H21" s="150"/>
-      <c r="I21" s="150"/>
-      <c r="J21" s="150"/>
-      <c r="K21" s="150"/>
-      <c r="L21" s="150"/>
-      <c r="M21" s="150"/>
-      <c r="N21" s="150"/>
-      <c r="O21" s="150"/>
-      <c r="P21" s="150"/>
-      <c r="Q21" s="150"/>
-      <c r="R21" s="150"/>
-      <c r="S21" s="150"/>
-      <c r="T21" s="150"/>
-      <c r="U21" s="150"/>
-      <c r="V21" s="150"/>
-      <c r="W21" s="150"/>
-      <c r="X21" s="150"/>
-      <c r="Y21" s="150"/>
-      <c r="Z21" s="150"/>
-      <c r="AA21" s="150"/>
-      <c r="AB21" s="150"/>
-      <c r="AC21" s="150"/>
-      <c r="AD21" s="150"/>
-      <c r="AE21" s="150"/>
-      <c r="AF21" s="150"/>
-      <c r="AG21" s="150"/>
-      <c r="AH21" s="150"/>
-      <c r="AI21" s="150"/>
-      <c r="AJ21" s="150"/>
-      <c r="AK21" s="150"/>
-      <c r="AL21" s="150"/>
+      <c r="B21" s="149"/>
+      <c r="C21" s="149"/>
+      <c r="D21" s="149"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="149"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="149"/>
+      <c r="I21" s="149"/>
+      <c r="J21" s="149"/>
+      <c r="K21" s="149"/>
+      <c r="L21" s="149"/>
+      <c r="M21" s="149"/>
+      <c r="N21" s="149"/>
+      <c r="O21" s="149"/>
+      <c r="P21" s="149"/>
+      <c r="Q21" s="149"/>
+      <c r="R21" s="149"/>
+      <c r="S21" s="149"/>
+      <c r="T21" s="149"/>
+      <c r="U21" s="149"/>
+      <c r="V21" s="149"/>
+      <c r="W21" s="149"/>
+      <c r="X21" s="149"/>
+      <c r="Y21" s="149"/>
+      <c r="Z21" s="149"/>
+      <c r="AA21" s="149"/>
+      <c r="AB21" s="149"/>
+      <c r="AC21" s="149"/>
+      <c r="AD21" s="149"/>
+      <c r="AE21" s="149"/>
+      <c r="AF21" s="149"/>
+      <c r="AG21" s="149"/>
+      <c r="AH21" s="149"/>
+      <c r="AI21" s="149"/>
+      <c r="AJ21" s="149"/>
+      <c r="AK21" s="149"/>
+      <c r="AL21" s="149"/>
     </row>
     <row r="22" spans="1:38" ht="18" customHeight="1">
-      <c r="A22" s="150" t="s">
+      <c r="A22" s="149" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="150"/>
-      <c r="C22" s="150"/>
-      <c r="D22" s="150"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="150"/>
-      <c r="G22" s="150"/>
-      <c r="H22" s="150"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="150"/>
-      <c r="K22" s="150"/>
-      <c r="L22" s="150"/>
-      <c r="M22" s="150"/>
-      <c r="N22" s="150"/>
-      <c r="O22" s="150"/>
-      <c r="P22" s="150"/>
-      <c r="Q22" s="150"/>
-      <c r="R22" s="150"/>
-      <c r="S22" s="150"/>
-      <c r="T22" s="150"/>
-      <c r="U22" s="150"/>
-      <c r="V22" s="150"/>
-      <c r="W22" s="150"/>
-      <c r="X22" s="150"/>
-      <c r="Y22" s="150"/>
-      <c r="Z22" s="150"/>
-      <c r="AA22" s="150"/>
-      <c r="AB22" s="150"/>
-      <c r="AC22" s="150"/>
-      <c r="AD22" s="150"/>
-      <c r="AE22" s="150"/>
-      <c r="AF22" s="150"/>
-      <c r="AG22" s="150"/>
-      <c r="AH22" s="150"/>
-      <c r="AI22" s="150"/>
-      <c r="AJ22" s="150"/>
-      <c r="AK22" s="150"/>
-      <c r="AL22" s="150"/>
+      <c r="B22" s="149"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="149"/>
+      <c r="H22" s="149"/>
+      <c r="I22" s="149"/>
+      <c r="J22" s="149"/>
+      <c r="K22" s="149"/>
+      <c r="L22" s="149"/>
+      <c r="M22" s="149"/>
+      <c r="N22" s="149"/>
+      <c r="O22" s="149"/>
+      <c r="P22" s="149"/>
+      <c r="Q22" s="149"/>
+      <c r="R22" s="149"/>
+      <c r="S22" s="149"/>
+      <c r="T22" s="149"/>
+      <c r="U22" s="149"/>
+      <c r="V22" s="149"/>
+      <c r="W22" s="149"/>
+      <c r="X22" s="149"/>
+      <c r="Y22" s="149"/>
+      <c r="Z22" s="149"/>
+      <c r="AA22" s="149"/>
+      <c r="AB22" s="149"/>
+      <c r="AC22" s="149"/>
+      <c r="AD22" s="149"/>
+      <c r="AE22" s="149"/>
+      <c r="AF22" s="149"/>
+      <c r="AG22" s="149"/>
+      <c r="AH22" s="149"/>
+      <c r="AI22" s="149"/>
+      <c r="AJ22" s="149"/>
+      <c r="AK22" s="149"/>
+      <c r="AL22" s="149"/>
     </row>
     <row r="23" spans="1:38" ht="14.4">
       <c r="A23" s="6" t="s">
@@ -12833,146 +12833,146 @@
       </c>
     </row>
     <row r="24" spans="1:38">
-      <c r="A24" s="139" t="s">
+      <c r="A24" s="144" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="139"/>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="139"/>
-      <c r="I24" s="149" t="s">
+      <c r="B24" s="144"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="158" t="s">
         <v>149</v>
       </c>
-      <c r="J24" s="149"/>
-      <c r="K24" s="149"/>
-      <c r="L24" s="149"/>
-      <c r="M24" s="149"/>
-      <c r="N24" s="149"/>
-      <c r="O24" s="139" t="s">
+      <c r="J24" s="158"/>
+      <c r="K24" s="158"/>
+      <c r="L24" s="158"/>
+      <c r="M24" s="158"/>
+      <c r="N24" s="158"/>
+      <c r="O24" s="144" t="s">
         <v>150</v>
       </c>
-      <c r="P24" s="139"/>
-      <c r="Q24" s="139"/>
-      <c r="R24" s="139"/>
-      <c r="S24" s="139"/>
-      <c r="T24" s="139"/>
-      <c r="U24" s="139"/>
-      <c r="V24" s="139"/>
-      <c r="W24" s="139"/>
-      <c r="X24" s="139"/>
-      <c r="Y24" s="139"/>
-      <c r="Z24" s="139"/>
-      <c r="AA24" s="139"/>
-      <c r="AB24" s="139"/>
-      <c r="AC24" s="139" t="s">
+      <c r="P24" s="144"/>
+      <c r="Q24" s="144"/>
+      <c r="R24" s="144"/>
+      <c r="S24" s="144"/>
+      <c r="T24" s="144"/>
+      <c r="U24" s="144"/>
+      <c r="V24" s="144"/>
+      <c r="W24" s="144"/>
+      <c r="X24" s="144"/>
+      <c r="Y24" s="144"/>
+      <c r="Z24" s="144"/>
+      <c r="AA24" s="144"/>
+      <c r="AB24" s="144"/>
+      <c r="AC24" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="AD24" s="139"/>
-      <c r="AE24" s="139"/>
-      <c r="AF24" s="139"/>
-      <c r="AG24" s="139"/>
-      <c r="AH24" s="139"/>
-      <c r="AI24" s="139"/>
-      <c r="AJ24" s="139"/>
-      <c r="AK24" s="139"/>
-      <c r="AL24" s="139"/>
+      <c r="AD24" s="144"/>
+      <c r="AE24" s="144"/>
+      <c r="AF24" s="144"/>
+      <c r="AG24" s="144"/>
+      <c r="AH24" s="144"/>
+      <c r="AI24" s="144"/>
+      <c r="AJ24" s="144"/>
+      <c r="AK24" s="144"/>
+      <c r="AL24" s="144"/>
     </row>
     <row r="25" spans="1:38">
-      <c r="A25" s="139" t="s">
+      <c r="A25" s="144" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="139"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139">
+      <c r="B25" s="144"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="144"/>
+      <c r="E25" s="144"/>
+      <c r="F25" s="144"/>
+      <c r="G25" s="144"/>
+      <c r="H25" s="144"/>
+      <c r="I25" s="144">
         <v>20</v>
       </c>
-      <c r="J25" s="139"/>
-      <c r="K25" s="139"/>
-      <c r="L25" s="139"/>
-      <c r="M25" s="139"/>
-      <c r="N25" s="139"/>
-      <c r="O25" s="146" t="s">
+      <c r="J25" s="144"/>
+      <c r="K25" s="144"/>
+      <c r="L25" s="144"/>
+      <c r="M25" s="144"/>
+      <c r="N25" s="144"/>
+      <c r="O25" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="P25" s="147"/>
-      <c r="Q25" s="147"/>
-      <c r="R25" s="147"/>
-      <c r="S25" s="147"/>
-      <c r="T25" s="147"/>
-      <c r="U25" s="147"/>
-      <c r="V25" s="147"/>
-      <c r="W25" s="147"/>
-      <c r="X25" s="147"/>
-      <c r="Y25" s="148"/>
-      <c r="Z25" s="146">
+      <c r="P25" s="156"/>
+      <c r="Q25" s="156"/>
+      <c r="R25" s="156"/>
+      <c r="S25" s="156"/>
+      <c r="T25" s="156"/>
+      <c r="U25" s="156"/>
+      <c r="V25" s="156"/>
+      <c r="W25" s="156"/>
+      <c r="X25" s="156"/>
+      <c r="Y25" s="157"/>
+      <c r="Z25" s="155">
         <v>100</v>
       </c>
-      <c r="AA25" s="147"/>
-      <c r="AB25" s="148"/>
-      <c r="AC25" s="139" t="s">
+      <c r="AA25" s="156"/>
+      <c r="AB25" s="157"/>
+      <c r="AC25" s="144" t="s">
         <v>154</v>
       </c>
-      <c r="AD25" s="139"/>
-      <c r="AE25" s="139"/>
-      <c r="AF25" s="139"/>
-      <c r="AG25" s="139"/>
-      <c r="AH25" s="139"/>
-      <c r="AI25" s="139"/>
-      <c r="AJ25" s="139"/>
-      <c r="AK25" s="139"/>
-      <c r="AL25" s="139"/>
+      <c r="AD25" s="144"/>
+      <c r="AE25" s="144"/>
+      <c r="AF25" s="144"/>
+      <c r="AG25" s="144"/>
+      <c r="AH25" s="144"/>
+      <c r="AI25" s="144"/>
+      <c r="AJ25" s="144"/>
+      <c r="AK25" s="144"/>
+      <c r="AL25" s="144"/>
     </row>
     <row r="26" spans="1:38">
-      <c r="A26" s="139"/>
-      <c r="B26" s="139"/>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="139"/>
-      <c r="L26" s="139"/>
-      <c r="M26" s="139"/>
-      <c r="N26" s="139"/>
-      <c r="O26" s="146" t="s">
+      <c r="A26" s="144"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="144"/>
+      <c r="E26" s="144"/>
+      <c r="F26" s="144"/>
+      <c r="G26" s="144"/>
+      <c r="H26" s="144"/>
+      <c r="I26" s="144"/>
+      <c r="J26" s="144"/>
+      <c r="K26" s="144"/>
+      <c r="L26" s="144"/>
+      <c r="M26" s="144"/>
+      <c r="N26" s="144"/>
+      <c r="O26" s="155" t="s">
         <v>153</v>
       </c>
-      <c r="P26" s="147"/>
-      <c r="Q26" s="147"/>
-      <c r="R26" s="147"/>
-      <c r="S26" s="147"/>
-      <c r="T26" s="147"/>
-      <c r="U26" s="147"/>
-      <c r="V26" s="147"/>
-      <c r="W26" s="147"/>
-      <c r="X26" s="147"/>
-      <c r="Y26" s="148"/>
-      <c r="Z26" s="146">
+      <c r="P26" s="156"/>
+      <c r="Q26" s="156"/>
+      <c r="R26" s="156"/>
+      <c r="S26" s="156"/>
+      <c r="T26" s="156"/>
+      <c r="U26" s="156"/>
+      <c r="V26" s="156"/>
+      <c r="W26" s="156"/>
+      <c r="X26" s="156"/>
+      <c r="Y26" s="157"/>
+      <c r="Z26" s="155">
         <v>200</v>
       </c>
-      <c r="AA26" s="147"/>
-      <c r="AB26" s="148"/>
-      <c r="AC26" s="139"/>
-      <c r="AD26" s="139"/>
-      <c r="AE26" s="139"/>
-      <c r="AF26" s="139"/>
-      <c r="AG26" s="139"/>
-      <c r="AH26" s="139"/>
-      <c r="AI26" s="139"/>
-      <c r="AJ26" s="139"/>
-      <c r="AK26" s="139"/>
-      <c r="AL26" s="139"/>
+      <c r="AA26" s="156"/>
+      <c r="AB26" s="157"/>
+      <c r="AC26" s="144"/>
+      <c r="AD26" s="144"/>
+      <c r="AE26" s="144"/>
+      <c r="AF26" s="144"/>
+      <c r="AG26" s="144"/>
+      <c r="AH26" s="144"/>
+      <c r="AI26" s="144"/>
+      <c r="AJ26" s="144"/>
+      <c r="AK26" s="144"/>
+      <c r="AL26" s="144"/>
     </row>
     <row r="27" spans="1:38">
       <c r="A27" s="6" t="s">
@@ -12981,14 +12981,77 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="U10:Z10"/>
-    <mergeCell ref="AA10:AF10"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="I7:O7"/>
-    <mergeCell ref="AG10:AL10"/>
+    <mergeCell ref="AC24:AL24"/>
+    <mergeCell ref="A25:H26"/>
+    <mergeCell ref="I25:N26"/>
+    <mergeCell ref="AC25:AL26"/>
+    <mergeCell ref="Z25:AB25"/>
+    <mergeCell ref="Z26:AB26"/>
+    <mergeCell ref="O25:Y25"/>
+    <mergeCell ref="O26:Y26"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="O24:AB24"/>
+    <mergeCell ref="AG22:AL22"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="I21:N21"/>
+    <mergeCell ref="O21:T21"/>
+    <mergeCell ref="U21:Z21"/>
+    <mergeCell ref="AA21:AF21"/>
+    <mergeCell ref="AG21:AL21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="I22:N22"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="U22:Z22"/>
+    <mergeCell ref="AA22:AF22"/>
+    <mergeCell ref="AG20:AL20"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="U19:Z19"/>
+    <mergeCell ref="AA19:AF19"/>
+    <mergeCell ref="AG19:AL19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="I20:N20"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="U20:Z20"/>
+    <mergeCell ref="AA20:AF20"/>
+    <mergeCell ref="AG18:AL18"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="U17:Z17"/>
+    <mergeCell ref="AA17:AF17"/>
+    <mergeCell ref="AG17:AL17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="AA18:AF18"/>
+    <mergeCell ref="AG16:AL16"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:T15"/>
+    <mergeCell ref="U15:Z15"/>
+    <mergeCell ref="AA15:AF15"/>
+    <mergeCell ref="AG15:AL15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="AA16:AF16"/>
+    <mergeCell ref="AG13:AL13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="U14:Z14"/>
+    <mergeCell ref="AA14:AF14"/>
+    <mergeCell ref="AG14:AL14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="U13:Z13"/>
+    <mergeCell ref="AA13:AF13"/>
     <mergeCell ref="AG12:AL12"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="I11:N11"/>
@@ -13005,77 +13068,14 @@
     <mergeCell ref="U12:Z12"/>
     <mergeCell ref="AA12:AF12"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="AG13:AL13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="U14:Z14"/>
-    <mergeCell ref="AA14:AF14"/>
-    <mergeCell ref="AG14:AL14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="U13:Z13"/>
-    <mergeCell ref="AA13:AF13"/>
-    <mergeCell ref="AG16:AL16"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:T15"/>
-    <mergeCell ref="U15:Z15"/>
-    <mergeCell ref="AA15:AF15"/>
-    <mergeCell ref="AG15:AL15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="AA16:AF16"/>
-    <mergeCell ref="AG18:AL18"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="U17:Z17"/>
-    <mergeCell ref="AA17:AF17"/>
-    <mergeCell ref="AG17:AL17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="U18:Z18"/>
-    <mergeCell ref="AA18:AF18"/>
-    <mergeCell ref="AG20:AL20"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="U19:Z19"/>
-    <mergeCell ref="AA19:AF19"/>
-    <mergeCell ref="AG19:AL19"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="I20:N20"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="U20:Z20"/>
-    <mergeCell ref="AA20:AF20"/>
-    <mergeCell ref="AG22:AL22"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="I21:N21"/>
-    <mergeCell ref="O21:T21"/>
-    <mergeCell ref="U21:Z21"/>
-    <mergeCell ref="AA21:AF21"/>
-    <mergeCell ref="AG21:AL21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="I22:N22"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="U22:Z22"/>
-    <mergeCell ref="AA22:AF22"/>
-    <mergeCell ref="AC24:AL24"/>
-    <mergeCell ref="A25:H26"/>
-    <mergeCell ref="I25:N26"/>
-    <mergeCell ref="AC25:AL26"/>
-    <mergeCell ref="Z25:AB25"/>
-    <mergeCell ref="Z26:AB26"/>
-    <mergeCell ref="O25:Y25"/>
-    <mergeCell ref="O26:Y26"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="O24:AB24"/>
+    <mergeCell ref="U10:Z10"/>
+    <mergeCell ref="AA10:AF10"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="F5:K5"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="AG10:AL10"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13116,32 +13116,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
-      <c r="U1" s="144"/>
-      <c r="V1" s="144"/>
-      <c r="W1" s="144"/>
-      <c r="X1" s="144"/>
-      <c r="Y1" s="144"/>
-      <c r="Z1" s="144"/>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="144"/>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="144"/>
-      <c r="AF1" s="144"/>
-      <c r="AG1" s="144"/>
-      <c r="AH1" s="144"/>
-      <c r="AI1" s="144"/>
-      <c r="AJ1" s="144"/>
-      <c r="AK1" s="144"/>
-      <c r="AL1" s="144"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="135"/>
+      <c r="S1" s="135"/>
+      <c r="T1" s="135"/>
+      <c r="U1" s="135"/>
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="135"/>
+      <c r="Z1" s="135"/>
+      <c r="AA1" s="135"/>
+      <c r="AB1" s="135"/>
+      <c r="AC1" s="135"/>
+      <c r="AD1" s="135"/>
+      <c r="AE1" s="135"/>
+      <c r="AF1" s="135"/>
+      <c r="AG1" s="135"/>
+      <c r="AH1" s="135"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="135"/>
+      <c r="AL1" s="135"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="33" t="s">
@@ -13183,17 +13183,17 @@
       <c r="AL2" s="34"/>
     </row>
     <row r="3" spans="1:38">
-      <c r="A3" s="141"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
+      <c r="A3" s="136"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -13350,9 +13350,9 @@
       <c r="A7" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="144"/>
-      <c r="F7" s="144"/>
-      <c r="G7" s="144"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="135"/>
       <c r="H7" s="63" t="s">
         <v>113</v>
       </c>
@@ -13383,270 +13383,270 @@
       <c r="AL7" s="34"/>
     </row>
     <row r="8" spans="1:38">
-      <c r="A8" s="174" t="s">
+      <c r="A8" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="174"/>
-      <c r="C8" s="174"/>
-      <c r="D8" s="174"/>
-      <c r="E8" s="174"/>
-      <c r="F8" s="174" t="s">
+      <c r="B8" s="168"/>
+      <c r="C8" s="168"/>
+      <c r="D8" s="168"/>
+      <c r="E8" s="168"/>
+      <c r="F8" s="168" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="174"/>
-      <c r="H8" s="174"/>
-      <c r="I8" s="174"/>
-      <c r="J8" s="174" t="s">
+      <c r="G8" s="168"/>
+      <c r="H8" s="168"/>
+      <c r="I8" s="168"/>
+      <c r="J8" s="168" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="174"/>
-      <c r="L8" s="174"/>
-      <c r="M8" s="174"/>
-      <c r="N8" s="174"/>
-      <c r="O8" s="174"/>
-      <c r="P8" s="174"/>
-      <c r="Q8" s="174"/>
-      <c r="R8" s="174"/>
-      <c r="S8" s="174"/>
-      <c r="T8" s="174"/>
-      <c r="U8" s="174"/>
-      <c r="V8" s="174"/>
-      <c r="W8" s="174"/>
-      <c r="X8" s="174"/>
-      <c r="Y8" s="174"/>
-      <c r="Z8" s="174"/>
-      <c r="AA8" s="174"/>
-      <c r="AB8" s="174"/>
-      <c r="AC8" s="174"/>
-      <c r="AD8" s="174"/>
-      <c r="AE8" s="174"/>
-      <c r="AF8" s="174"/>
-      <c r="AG8" s="174"/>
-      <c r="AH8" s="174"/>
-      <c r="AI8" s="168" t="s">
+      <c r="K8" s="168"/>
+      <c r="L8" s="168"/>
+      <c r="M8" s="168"/>
+      <c r="N8" s="168"/>
+      <c r="O8" s="168"/>
+      <c r="P8" s="168"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="168"/>
+      <c r="S8" s="168"/>
+      <c r="T8" s="168"/>
+      <c r="U8" s="168"/>
+      <c r="V8" s="168"/>
+      <c r="W8" s="168"/>
+      <c r="X8" s="168"/>
+      <c r="Y8" s="168"/>
+      <c r="Z8" s="168"/>
+      <c r="AA8" s="168"/>
+      <c r="AB8" s="168"/>
+      <c r="AC8" s="168"/>
+      <c r="AD8" s="168"/>
+      <c r="AE8" s="168"/>
+      <c r="AF8" s="168"/>
+      <c r="AG8" s="168"/>
+      <c r="AH8" s="168"/>
+      <c r="AI8" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="AJ8" s="169"/>
-      <c r="AK8" s="169"/>
-      <c r="AL8" s="170"/>
+      <c r="AJ8" s="170"/>
+      <c r="AK8" s="170"/>
+      <c r="AL8" s="171"/>
     </row>
     <row r="9" spans="1:38">
-      <c r="A9" s="174"/>
-      <c r="B9" s="174"/>
-      <c r="C9" s="174"/>
-      <c r="D9" s="174"/>
-      <c r="E9" s="174"/>
-      <c r="F9" s="174"/>
-      <c r="G9" s="174"/>
-      <c r="H9" s="174"/>
-      <c r="I9" s="174"/>
-      <c r="J9" s="174" t="s">
+      <c r="A9" s="168"/>
+      <c r="B9" s="168"/>
+      <c r="C9" s="168"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="168"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="168"/>
+      <c r="H9" s="168"/>
+      <c r="I9" s="168"/>
+      <c r="J9" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="174"/>
-      <c r="L9" s="174"/>
-      <c r="M9" s="174"/>
-      <c r="N9" s="174"/>
-      <c r="O9" s="174" t="s">
+      <c r="K9" s="168"/>
+      <c r="L9" s="168"/>
+      <c r="M9" s="168"/>
+      <c r="N9" s="168"/>
+      <c r="O9" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="174"/>
-      <c r="Q9" s="174"/>
-      <c r="R9" s="174"/>
-      <c r="S9" s="174"/>
-      <c r="T9" s="174" t="s">
+      <c r="P9" s="168"/>
+      <c r="Q9" s="168"/>
+      <c r="R9" s="168"/>
+      <c r="S9" s="168"/>
+      <c r="T9" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="174"/>
-      <c r="V9" s="174"/>
-      <c r="W9" s="174"/>
-      <c r="X9" s="174"/>
-      <c r="Y9" s="174" t="s">
+      <c r="U9" s="168"/>
+      <c r="V9" s="168"/>
+      <c r="W9" s="168"/>
+      <c r="X9" s="168"/>
+      <c r="Y9" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="Z9" s="174"/>
-      <c r="AA9" s="174"/>
-      <c r="AB9" s="174"/>
-      <c r="AC9" s="174"/>
-      <c r="AD9" s="174" t="s">
+      <c r="Z9" s="168"/>
+      <c r="AA9" s="168"/>
+      <c r="AB9" s="168"/>
+      <c r="AC9" s="168"/>
+      <c r="AD9" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="AE9" s="174"/>
-      <c r="AF9" s="174"/>
-      <c r="AG9" s="174"/>
-      <c r="AH9" s="174"/>
-      <c r="AI9" s="171"/>
-      <c r="AJ9" s="172"/>
-      <c r="AK9" s="172"/>
-      <c r="AL9" s="173"/>
+      <c r="AE9" s="168"/>
+      <c r="AF9" s="168"/>
+      <c r="AG9" s="168"/>
+      <c r="AH9" s="168"/>
+      <c r="AI9" s="172"/>
+      <c r="AJ9" s="173"/>
+      <c r="AK9" s="173"/>
+      <c r="AL9" s="174"/>
     </row>
     <row r="10" spans="1:38">
-      <c r="A10" s="159"/>
-      <c r="B10" s="160"/>
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="161"/>
-      <c r="F10" s="166" t="s">
+      <c r="A10" s="162"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="164"/>
+      <c r="F10" s="160" t="s">
         <v>117</v>
       </c>
-      <c r="G10" s="166"/>
-      <c r="H10" s="166"/>
-      <c r="I10" s="166"/>
-      <c r="J10" s="165"/>
-      <c r="K10" s="166"/>
-      <c r="L10" s="166"/>
-      <c r="M10" s="166"/>
-      <c r="N10" s="166"/>
-      <c r="O10" s="165"/>
-      <c r="P10" s="166"/>
-      <c r="Q10" s="166"/>
-      <c r="R10" s="166"/>
-      <c r="S10" s="166"/>
-      <c r="T10" s="165"/>
-      <c r="U10" s="166"/>
-      <c r="V10" s="166"/>
-      <c r="W10" s="166"/>
-      <c r="X10" s="166"/>
-      <c r="Y10" s="165"/>
-      <c r="Z10" s="166"/>
-      <c r="AA10" s="166"/>
-      <c r="AB10" s="166"/>
-      <c r="AC10" s="166"/>
-      <c r="AD10" s="165"/>
-      <c r="AE10" s="166"/>
-      <c r="AF10" s="166"/>
-      <c r="AG10" s="166"/>
-      <c r="AH10" s="166"/>
-      <c r="AI10" s="165"/>
-      <c r="AJ10" s="166"/>
-      <c r="AK10" s="166"/>
-      <c r="AL10" s="167"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="159"/>
+      <c r="K10" s="160"/>
+      <c r="L10" s="160"/>
+      <c r="M10" s="160"/>
+      <c r="N10" s="160"/>
+      <c r="O10" s="159"/>
+      <c r="P10" s="160"/>
+      <c r="Q10" s="160"/>
+      <c r="R10" s="160"/>
+      <c r="S10" s="160"/>
+      <c r="T10" s="159"/>
+      <c r="U10" s="160"/>
+      <c r="V10" s="160"/>
+      <c r="W10" s="160"/>
+      <c r="X10" s="160"/>
+      <c r="Y10" s="159"/>
+      <c r="Z10" s="160"/>
+      <c r="AA10" s="160"/>
+      <c r="AB10" s="160"/>
+      <c r="AC10" s="160"/>
+      <c r="AD10" s="159"/>
+      <c r="AE10" s="160"/>
+      <c r="AF10" s="160"/>
+      <c r="AG10" s="160"/>
+      <c r="AH10" s="160"/>
+      <c r="AI10" s="159"/>
+      <c r="AJ10" s="160"/>
+      <c r="AK10" s="160"/>
+      <c r="AL10" s="161"/>
     </row>
     <row r="11" spans="1:38" ht="16.2">
-      <c r="A11" s="162"/>
-      <c r="B11" s="163"/>
-      <c r="C11" s="163"/>
-      <c r="D11" s="163"/>
-      <c r="E11" s="164"/>
-      <c r="F11" s="166" t="s">
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="G11" s="166"/>
-      <c r="H11" s="166"/>
-      <c r="I11" s="166"/>
-      <c r="J11" s="165"/>
-      <c r="K11" s="166"/>
-      <c r="L11" s="166"/>
-      <c r="M11" s="166"/>
-      <c r="N11" s="166"/>
-      <c r="O11" s="165"/>
-      <c r="P11" s="166"/>
-      <c r="Q11" s="166"/>
-      <c r="R11" s="166"/>
-      <c r="S11" s="166"/>
-      <c r="T11" s="165"/>
-      <c r="U11" s="166"/>
-      <c r="V11" s="166"/>
-      <c r="W11" s="166"/>
-      <c r="X11" s="166"/>
-      <c r="Y11" s="165"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="166"/>
-      <c r="AB11" s="166"/>
-      <c r="AC11" s="166"/>
-      <c r="AD11" s="165"/>
-      <c r="AE11" s="166"/>
-      <c r="AF11" s="166"/>
-      <c r="AG11" s="166"/>
-      <c r="AH11" s="166"/>
-      <c r="AI11" s="165"/>
-      <c r="AJ11" s="166"/>
-      <c r="AK11" s="166"/>
-      <c r="AL11" s="167"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="159"/>
+      <c r="K11" s="160"/>
+      <c r="L11" s="160"/>
+      <c r="M11" s="160"/>
+      <c r="N11" s="160"/>
+      <c r="O11" s="159"/>
+      <c r="P11" s="160"/>
+      <c r="Q11" s="160"/>
+      <c r="R11" s="160"/>
+      <c r="S11" s="160"/>
+      <c r="T11" s="159"/>
+      <c r="U11" s="160"/>
+      <c r="V11" s="160"/>
+      <c r="W11" s="160"/>
+      <c r="X11" s="160"/>
+      <c r="Y11" s="159"/>
+      <c r="Z11" s="160"/>
+      <c r="AA11" s="160"/>
+      <c r="AB11" s="160"/>
+      <c r="AC11" s="160"/>
+      <c r="AD11" s="159"/>
+      <c r="AE11" s="160"/>
+      <c r="AF11" s="160"/>
+      <c r="AG11" s="160"/>
+      <c r="AH11" s="160"/>
+      <c r="AI11" s="159"/>
+      <c r="AJ11" s="160"/>
+      <c r="AK11" s="160"/>
+      <c r="AL11" s="161"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="159"/>
-      <c r="B12" s="160"/>
-      <c r="C12" s="160"/>
-      <c r="D12" s="160"/>
-      <c r="E12" s="161"/>
-      <c r="F12" s="166" t="s">
+      <c r="A12" s="162"/>
+      <c r="B12" s="163"/>
+      <c r="C12" s="163"/>
+      <c r="D12" s="163"/>
+      <c r="E12" s="164"/>
+      <c r="F12" s="160" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="166"/>
-      <c r="H12" s="166"/>
-      <c r="I12" s="166"/>
-      <c r="J12" s="165"/>
-      <c r="K12" s="166"/>
-      <c r="L12" s="166"/>
-      <c r="M12" s="166"/>
-      <c r="N12" s="166"/>
-      <c r="O12" s="165"/>
-      <c r="P12" s="166"/>
-      <c r="Q12" s="166"/>
-      <c r="R12" s="166"/>
-      <c r="S12" s="166"/>
-      <c r="T12" s="165"/>
-      <c r="U12" s="166"/>
-      <c r="V12" s="166"/>
-      <c r="W12" s="166"/>
-      <c r="X12" s="166"/>
-      <c r="Y12" s="165"/>
-      <c r="Z12" s="166"/>
-      <c r="AA12" s="166"/>
-      <c r="AB12" s="166"/>
-      <c r="AC12" s="166"/>
-      <c r="AD12" s="165"/>
-      <c r="AE12" s="166"/>
-      <c r="AF12" s="166"/>
-      <c r="AG12" s="166"/>
-      <c r="AH12" s="166"/>
-      <c r="AI12" s="165"/>
-      <c r="AJ12" s="166"/>
-      <c r="AK12" s="166"/>
-      <c r="AL12" s="167"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="159"/>
+      <c r="K12" s="160"/>
+      <c r="L12" s="160"/>
+      <c r="M12" s="160"/>
+      <c r="N12" s="160"/>
+      <c r="O12" s="159"/>
+      <c r="P12" s="160"/>
+      <c r="Q12" s="160"/>
+      <c r="R12" s="160"/>
+      <c r="S12" s="160"/>
+      <c r="T12" s="159"/>
+      <c r="U12" s="160"/>
+      <c r="V12" s="160"/>
+      <c r="W12" s="160"/>
+      <c r="X12" s="160"/>
+      <c r="Y12" s="159"/>
+      <c r="Z12" s="160"/>
+      <c r="AA12" s="160"/>
+      <c r="AB12" s="160"/>
+      <c r="AC12" s="160"/>
+      <c r="AD12" s="159"/>
+      <c r="AE12" s="160"/>
+      <c r="AF12" s="160"/>
+      <c r="AG12" s="160"/>
+      <c r="AH12" s="160"/>
+      <c r="AI12" s="159"/>
+      <c r="AJ12" s="160"/>
+      <c r="AK12" s="160"/>
+      <c r="AL12" s="161"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="162"/>
-      <c r="B13" s="163"/>
-      <c r="C13" s="163"/>
-      <c r="D13" s="163"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="166" t="s">
+      <c r="A13" s="165"/>
+      <c r="B13" s="166"/>
+      <c r="C13" s="166"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="165"/>
-      <c r="K13" s="166"/>
-      <c r="L13" s="166"/>
-      <c r="M13" s="166"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="165"/>
-      <c r="P13" s="166"/>
-      <c r="Q13" s="166"/>
-      <c r="R13" s="166"/>
-      <c r="S13" s="166"/>
-      <c r="T13" s="165"/>
-      <c r="U13" s="166"/>
-      <c r="V13" s="166"/>
-      <c r="W13" s="166"/>
-      <c r="X13" s="166"/>
-      <c r="Y13" s="165"/>
-      <c r="Z13" s="166"/>
-      <c r="AA13" s="166"/>
-      <c r="AB13" s="166"/>
-      <c r="AC13" s="166"/>
-      <c r="AD13" s="165"/>
-      <c r="AE13" s="166"/>
-      <c r="AF13" s="166"/>
-      <c r="AG13" s="166"/>
-      <c r="AH13" s="166"/>
-      <c r="AI13" s="165"/>
-      <c r="AJ13" s="166"/>
-      <c r="AK13" s="166"/>
-      <c r="AL13" s="167"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="159"/>
+      <c r="K13" s="160"/>
+      <c r="L13" s="160"/>
+      <c r="M13" s="160"/>
+      <c r="N13" s="160"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="160"/>
+      <c r="Q13" s="160"/>
+      <c r="R13" s="160"/>
+      <c r="S13" s="160"/>
+      <c r="T13" s="159"/>
+      <c r="U13" s="160"/>
+      <c r="V13" s="160"/>
+      <c r="W13" s="160"/>
+      <c r="X13" s="160"/>
+      <c r="Y13" s="159"/>
+      <c r="Z13" s="160"/>
+      <c r="AA13" s="160"/>
+      <c r="AB13" s="160"/>
+      <c r="AC13" s="160"/>
+      <c r="AD13" s="159"/>
+      <c r="AE13" s="160"/>
+      <c r="AF13" s="160"/>
+      <c r="AG13" s="160"/>
+      <c r="AH13" s="160"/>
+      <c r="AI13" s="159"/>
+      <c r="AJ13" s="160"/>
+      <c r="AK13" s="160"/>
+      <c r="AL13" s="161"/>
     </row>
     <row r="14" spans="1:38" ht="10.8" customHeight="1">
       <c r="A14" s="35"/>
@@ -13692,9 +13692,9 @@
       <c r="A15" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
       <c r="H15" s="63" t="s">
         <v>113</v>
       </c>
@@ -13725,270 +13725,270 @@
       <c r="AL15" s="34"/>
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
-      <c r="A16" s="174" t="s">
+      <c r="A16" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="174"/>
-      <c r="C16" s="174"/>
-      <c r="D16" s="174"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="174" t="s">
+      <c r="B16" s="168"/>
+      <c r="C16" s="168"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="168"/>
+      <c r="F16" s="168" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="174"/>
-      <c r="H16" s="174"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="174" t="s">
+      <c r="G16" s="168"/>
+      <c r="H16" s="168"/>
+      <c r="I16" s="168"/>
+      <c r="J16" s="168" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="174"/>
-      <c r="L16" s="174"/>
-      <c r="M16" s="174"/>
-      <c r="N16" s="174"/>
-      <c r="O16" s="174"/>
-      <c r="P16" s="174"/>
-      <c r="Q16" s="174"/>
-      <c r="R16" s="174"/>
-      <c r="S16" s="174"/>
-      <c r="T16" s="174"/>
-      <c r="U16" s="174"/>
-      <c r="V16" s="174"/>
-      <c r="W16" s="174"/>
-      <c r="X16" s="174"/>
-      <c r="Y16" s="174"/>
-      <c r="Z16" s="174"/>
-      <c r="AA16" s="174"/>
-      <c r="AB16" s="174"/>
-      <c r="AC16" s="174"/>
-      <c r="AD16" s="174"/>
-      <c r="AE16" s="174"/>
-      <c r="AF16" s="174"/>
-      <c r="AG16" s="174"/>
-      <c r="AH16" s="174"/>
-      <c r="AI16" s="168" t="s">
+      <c r="K16" s="168"/>
+      <c r="L16" s="168"/>
+      <c r="M16" s="168"/>
+      <c r="N16" s="168"/>
+      <c r="O16" s="168"/>
+      <c r="P16" s="168"/>
+      <c r="Q16" s="168"/>
+      <c r="R16" s="168"/>
+      <c r="S16" s="168"/>
+      <c r="T16" s="168"/>
+      <c r="U16" s="168"/>
+      <c r="V16" s="168"/>
+      <c r="W16" s="168"/>
+      <c r="X16" s="168"/>
+      <c r="Y16" s="168"/>
+      <c r="Z16" s="168"/>
+      <c r="AA16" s="168"/>
+      <c r="AB16" s="168"/>
+      <c r="AC16" s="168"/>
+      <c r="AD16" s="168"/>
+      <c r="AE16" s="168"/>
+      <c r="AF16" s="168"/>
+      <c r="AG16" s="168"/>
+      <c r="AH16" s="168"/>
+      <c r="AI16" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="AJ16" s="169"/>
-      <c r="AK16" s="169"/>
-      <c r="AL16" s="170"/>
+      <c r="AJ16" s="170"/>
+      <c r="AK16" s="170"/>
+      <c r="AL16" s="171"/>
     </row>
     <row r="17" spans="1:38">
-      <c r="A17" s="174"/>
-      <c r="B17" s="174"/>
-      <c r="C17" s="174"/>
-      <c r="D17" s="174"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="174"/>
-      <c r="G17" s="174"/>
-      <c r="H17" s="174"/>
-      <c r="I17" s="174"/>
-      <c r="J17" s="174" t="s">
+      <c r="A17" s="168"/>
+      <c r="B17" s="168"/>
+      <c r="C17" s="168"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="168"/>
+      <c r="H17" s="168"/>
+      <c r="I17" s="168"/>
+      <c r="J17" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="K17" s="174"/>
-      <c r="L17" s="174"/>
-      <c r="M17" s="174"/>
-      <c r="N17" s="174"/>
-      <c r="O17" s="174" t="s">
+      <c r="K17" s="168"/>
+      <c r="L17" s="168"/>
+      <c r="M17" s="168"/>
+      <c r="N17" s="168"/>
+      <c r="O17" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="P17" s="174"/>
-      <c r="Q17" s="174"/>
-      <c r="R17" s="174"/>
-      <c r="S17" s="174"/>
-      <c r="T17" s="174" t="s">
+      <c r="P17" s="168"/>
+      <c r="Q17" s="168"/>
+      <c r="R17" s="168"/>
+      <c r="S17" s="168"/>
+      <c r="T17" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="U17" s="174"/>
-      <c r="V17" s="174"/>
-      <c r="W17" s="174"/>
-      <c r="X17" s="174"/>
-      <c r="Y17" s="174" t="s">
+      <c r="U17" s="168"/>
+      <c r="V17" s="168"/>
+      <c r="W17" s="168"/>
+      <c r="X17" s="168"/>
+      <c r="Y17" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="Z17" s="174"/>
-      <c r="AA17" s="174"/>
-      <c r="AB17" s="174"/>
-      <c r="AC17" s="174"/>
-      <c r="AD17" s="174" t="s">
+      <c r="Z17" s="168"/>
+      <c r="AA17" s="168"/>
+      <c r="AB17" s="168"/>
+      <c r="AC17" s="168"/>
+      <c r="AD17" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="AE17" s="174"/>
-      <c r="AF17" s="174"/>
-      <c r="AG17" s="174"/>
-      <c r="AH17" s="174"/>
-      <c r="AI17" s="171"/>
-      <c r="AJ17" s="172"/>
-      <c r="AK17" s="172"/>
-      <c r="AL17" s="173"/>
+      <c r="AE17" s="168"/>
+      <c r="AF17" s="168"/>
+      <c r="AG17" s="168"/>
+      <c r="AH17" s="168"/>
+      <c r="AI17" s="172"/>
+      <c r="AJ17" s="173"/>
+      <c r="AK17" s="173"/>
+      <c r="AL17" s="174"/>
     </row>
     <row r="18" spans="1:38">
-      <c r="A18" s="159"/>
-      <c r="B18" s="160"/>
-      <c r="C18" s="160"/>
-      <c r="D18" s="160"/>
-      <c r="E18" s="161"/>
-      <c r="F18" s="166" t="s">
+      <c r="A18" s="162"/>
+      <c r="B18" s="163"/>
+      <c r="C18" s="163"/>
+      <c r="D18" s="163"/>
+      <c r="E18" s="164"/>
+      <c r="F18" s="160" t="s">
         <v>117</v>
       </c>
-      <c r="G18" s="166"/>
-      <c r="H18" s="166"/>
-      <c r="I18" s="166"/>
-      <c r="J18" s="165"/>
-      <c r="K18" s="166"/>
-      <c r="L18" s="166"/>
-      <c r="M18" s="166"/>
-      <c r="N18" s="166"/>
-      <c r="O18" s="165"/>
-      <c r="P18" s="166"/>
-      <c r="Q18" s="166"/>
-      <c r="R18" s="166"/>
-      <c r="S18" s="166"/>
-      <c r="T18" s="165"/>
-      <c r="U18" s="166"/>
-      <c r="V18" s="166"/>
-      <c r="W18" s="166"/>
-      <c r="X18" s="166"/>
-      <c r="Y18" s="165"/>
-      <c r="Z18" s="166"/>
-      <c r="AA18" s="166"/>
-      <c r="AB18" s="166"/>
-      <c r="AC18" s="166"/>
-      <c r="AD18" s="165"/>
-      <c r="AE18" s="166"/>
-      <c r="AF18" s="166"/>
-      <c r="AG18" s="166"/>
-      <c r="AH18" s="166"/>
-      <c r="AI18" s="165"/>
-      <c r="AJ18" s="166"/>
-      <c r="AK18" s="166"/>
-      <c r="AL18" s="167"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="160"/>
+      <c r="J18" s="159"/>
+      <c r="K18" s="160"/>
+      <c r="L18" s="160"/>
+      <c r="M18" s="160"/>
+      <c r="N18" s="160"/>
+      <c r="O18" s="159"/>
+      <c r="P18" s="160"/>
+      <c r="Q18" s="160"/>
+      <c r="R18" s="160"/>
+      <c r="S18" s="160"/>
+      <c r="T18" s="159"/>
+      <c r="U18" s="160"/>
+      <c r="V18" s="160"/>
+      <c r="W18" s="160"/>
+      <c r="X18" s="160"/>
+      <c r="Y18" s="159"/>
+      <c r="Z18" s="160"/>
+      <c r="AA18" s="160"/>
+      <c r="AB18" s="160"/>
+      <c r="AC18" s="160"/>
+      <c r="AD18" s="159"/>
+      <c r="AE18" s="160"/>
+      <c r="AF18" s="160"/>
+      <c r="AG18" s="160"/>
+      <c r="AH18" s="160"/>
+      <c r="AI18" s="159"/>
+      <c r="AJ18" s="160"/>
+      <c r="AK18" s="160"/>
+      <c r="AL18" s="161"/>
     </row>
     <row r="19" spans="1:38" ht="16.2">
-      <c r="A19" s="162"/>
-      <c r="B19" s="163"/>
-      <c r="C19" s="163"/>
-      <c r="D19" s="163"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="166" t="s">
+      <c r="A19" s="165"/>
+      <c r="B19" s="166"/>
+      <c r="C19" s="166"/>
+      <c r="D19" s="166"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="G19" s="166"/>
-      <c r="H19" s="166"/>
-      <c r="I19" s="166"/>
-      <c r="J19" s="165"/>
-      <c r="K19" s="166"/>
-      <c r="L19" s="166"/>
-      <c r="M19" s="166"/>
-      <c r="N19" s="166"/>
-      <c r="O19" s="165"/>
-      <c r="P19" s="166"/>
-      <c r="Q19" s="166"/>
-      <c r="R19" s="166"/>
-      <c r="S19" s="166"/>
-      <c r="T19" s="165"/>
-      <c r="U19" s="166"/>
-      <c r="V19" s="166"/>
-      <c r="W19" s="166"/>
-      <c r="X19" s="166"/>
-      <c r="Y19" s="165"/>
-      <c r="Z19" s="166"/>
-      <c r="AA19" s="166"/>
-      <c r="AB19" s="166"/>
-      <c r="AC19" s="166"/>
-      <c r="AD19" s="165"/>
-      <c r="AE19" s="166"/>
-      <c r="AF19" s="166"/>
-      <c r="AG19" s="166"/>
-      <c r="AH19" s="166"/>
-      <c r="AI19" s="165"/>
-      <c r="AJ19" s="166"/>
-      <c r="AK19" s="166"/>
-      <c r="AL19" s="167"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="160"/>
+      <c r="I19" s="160"/>
+      <c r="J19" s="159"/>
+      <c r="K19" s="160"/>
+      <c r="L19" s="160"/>
+      <c r="M19" s="160"/>
+      <c r="N19" s="160"/>
+      <c r="O19" s="159"/>
+      <c r="P19" s="160"/>
+      <c r="Q19" s="160"/>
+      <c r="R19" s="160"/>
+      <c r="S19" s="160"/>
+      <c r="T19" s="159"/>
+      <c r="U19" s="160"/>
+      <c r="V19" s="160"/>
+      <c r="W19" s="160"/>
+      <c r="X19" s="160"/>
+      <c r="Y19" s="159"/>
+      <c r="Z19" s="160"/>
+      <c r="AA19" s="160"/>
+      <c r="AB19" s="160"/>
+      <c r="AC19" s="160"/>
+      <c r="AD19" s="159"/>
+      <c r="AE19" s="160"/>
+      <c r="AF19" s="160"/>
+      <c r="AG19" s="160"/>
+      <c r="AH19" s="160"/>
+      <c r="AI19" s="159"/>
+      <c r="AJ19" s="160"/>
+      <c r="AK19" s="160"/>
+      <c r="AL19" s="161"/>
     </row>
     <row r="20" spans="1:38">
-      <c r="A20" s="159"/>
-      <c r="B20" s="160"/>
-      <c r="C20" s="160"/>
-      <c r="D20" s="160"/>
-      <c r="E20" s="161"/>
-      <c r="F20" s="166" t="s">
+      <c r="A20" s="162"/>
+      <c r="B20" s="163"/>
+      <c r="C20" s="163"/>
+      <c r="D20" s="163"/>
+      <c r="E20" s="164"/>
+      <c r="F20" s="160" t="s">
         <v>117</v>
       </c>
-      <c r="G20" s="166"/>
-      <c r="H20" s="166"/>
-      <c r="I20" s="166"/>
-      <c r="J20" s="165"/>
-      <c r="K20" s="166"/>
-      <c r="L20" s="166"/>
-      <c r="M20" s="166"/>
-      <c r="N20" s="166"/>
-      <c r="O20" s="165"/>
-      <c r="P20" s="166"/>
-      <c r="Q20" s="166"/>
-      <c r="R20" s="166"/>
-      <c r="S20" s="166"/>
-      <c r="T20" s="165"/>
-      <c r="U20" s="166"/>
-      <c r="V20" s="166"/>
-      <c r="W20" s="166"/>
-      <c r="X20" s="166"/>
-      <c r="Y20" s="165"/>
-      <c r="Z20" s="166"/>
-      <c r="AA20" s="166"/>
-      <c r="AB20" s="166"/>
-      <c r="AC20" s="166"/>
-      <c r="AD20" s="165"/>
-      <c r="AE20" s="166"/>
-      <c r="AF20" s="166"/>
-      <c r="AG20" s="166"/>
-      <c r="AH20" s="166"/>
-      <c r="AI20" s="165"/>
-      <c r="AJ20" s="166"/>
-      <c r="AK20" s="166"/>
-      <c r="AL20" s="167"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="160"/>
+      <c r="I20" s="160"/>
+      <c r="J20" s="159"/>
+      <c r="K20" s="160"/>
+      <c r="L20" s="160"/>
+      <c r="M20" s="160"/>
+      <c r="N20" s="160"/>
+      <c r="O20" s="159"/>
+      <c r="P20" s="160"/>
+      <c r="Q20" s="160"/>
+      <c r="R20" s="160"/>
+      <c r="S20" s="160"/>
+      <c r="T20" s="159"/>
+      <c r="U20" s="160"/>
+      <c r="V20" s="160"/>
+      <c r="W20" s="160"/>
+      <c r="X20" s="160"/>
+      <c r="Y20" s="159"/>
+      <c r="Z20" s="160"/>
+      <c r="AA20" s="160"/>
+      <c r="AB20" s="160"/>
+      <c r="AC20" s="160"/>
+      <c r="AD20" s="159"/>
+      <c r="AE20" s="160"/>
+      <c r="AF20" s="160"/>
+      <c r="AG20" s="160"/>
+      <c r="AH20" s="160"/>
+      <c r="AI20" s="159"/>
+      <c r="AJ20" s="160"/>
+      <c r="AK20" s="160"/>
+      <c r="AL20" s="161"/>
     </row>
     <row r="21" spans="1:38" ht="16.2">
-      <c r="A21" s="162"/>
-      <c r="B21" s="163"/>
-      <c r="C21" s="163"/>
-      <c r="D21" s="163"/>
-      <c r="E21" s="164"/>
-      <c r="F21" s="166" t="s">
+      <c r="A21" s="165"/>
+      <c r="B21" s="166"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="G21" s="166"/>
-      <c r="H21" s="166"/>
-      <c r="I21" s="166"/>
-      <c r="J21" s="165"/>
-      <c r="K21" s="166"/>
-      <c r="L21" s="166"/>
-      <c r="M21" s="166"/>
-      <c r="N21" s="166"/>
-      <c r="O21" s="165"/>
-      <c r="P21" s="166"/>
-      <c r="Q21" s="166"/>
-      <c r="R21" s="166"/>
-      <c r="S21" s="166"/>
-      <c r="T21" s="165"/>
-      <c r="U21" s="166"/>
-      <c r="V21" s="166"/>
-      <c r="W21" s="166"/>
-      <c r="X21" s="166"/>
-      <c r="Y21" s="165"/>
-      <c r="Z21" s="166"/>
-      <c r="AA21" s="166"/>
-      <c r="AB21" s="166"/>
-      <c r="AC21" s="166"/>
-      <c r="AD21" s="165"/>
-      <c r="AE21" s="166"/>
-      <c r="AF21" s="166"/>
-      <c r="AG21" s="166"/>
-      <c r="AH21" s="166"/>
-      <c r="AI21" s="165"/>
-      <c r="AJ21" s="166"/>
-      <c r="AK21" s="166"/>
-      <c r="AL21" s="167"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="160"/>
+      <c r="I21" s="160"/>
+      <c r="J21" s="159"/>
+      <c r="K21" s="160"/>
+      <c r="L21" s="160"/>
+      <c r="M21" s="160"/>
+      <c r="N21" s="160"/>
+      <c r="O21" s="159"/>
+      <c r="P21" s="160"/>
+      <c r="Q21" s="160"/>
+      <c r="R21" s="160"/>
+      <c r="S21" s="160"/>
+      <c r="T21" s="159"/>
+      <c r="U21" s="160"/>
+      <c r="V21" s="160"/>
+      <c r="W21" s="160"/>
+      <c r="X21" s="160"/>
+      <c r="Y21" s="159"/>
+      <c r="Z21" s="160"/>
+      <c r="AA21" s="160"/>
+      <c r="AB21" s="160"/>
+      <c r="AC21" s="160"/>
+      <c r="AD21" s="159"/>
+      <c r="AE21" s="160"/>
+      <c r="AF21" s="160"/>
+      <c r="AG21" s="160"/>
+      <c r="AH21" s="160"/>
+      <c r="AI21" s="159"/>
+      <c r="AJ21" s="160"/>
+      <c r="AK21" s="160"/>
+      <c r="AL21" s="161"/>
     </row>
     <row r="22" spans="1:38">
       <c r="A22" s="74"/>
@@ -14313,72 +14313,6 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="Y13:AC13"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="AI13:AL13"/>
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="AI11:AL11"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="AI10:AL10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="A12:E13"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:I9"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="AI8:AL9"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:N20"/>
-    <mergeCell ref="O20:S20"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="AI21:AL21"/>
-    <mergeCell ref="J21:N21"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="Y21:AC21"/>
-    <mergeCell ref="AD21:AH21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A16:E17"/>
-    <mergeCell ref="F16:I17"/>
-    <mergeCell ref="J16:AH16"/>
-    <mergeCell ref="J17:N17"/>
-    <mergeCell ref="O17:S17"/>
-    <mergeCell ref="T17:X17"/>
-    <mergeCell ref="Y17:AC17"/>
-    <mergeCell ref="AD17:AH17"/>
-    <mergeCell ref="AI19:AL19"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="J18:N18"/>
-    <mergeCell ref="O18:S18"/>
-    <mergeCell ref="T18:X18"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="Y18:AC18"/>
     <mergeCell ref="M1:AL1"/>
@@ -14395,6 +14329,72 @@
     <mergeCell ref="T19:X19"/>
     <mergeCell ref="Y19:AC19"/>
     <mergeCell ref="AD19:AH19"/>
+    <mergeCell ref="AI19:AL19"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="J18:N18"/>
+    <mergeCell ref="O18:S18"/>
+    <mergeCell ref="T18:X18"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A16:E17"/>
+    <mergeCell ref="F16:I17"/>
+    <mergeCell ref="J16:AH16"/>
+    <mergeCell ref="J17:N17"/>
+    <mergeCell ref="O17:S17"/>
+    <mergeCell ref="T17:X17"/>
+    <mergeCell ref="Y17:AC17"/>
+    <mergeCell ref="AD17:AH17"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:N20"/>
+    <mergeCell ref="O20:S20"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="AI21:AL21"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="Y21:AC21"/>
+    <mergeCell ref="AD21:AH21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="F8:I9"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="AI8:AL9"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="A12:E13"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="AI11:AL11"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AI10:AL10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="J11:N11"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="AI12:AL12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="Y13:AC13"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="AI13:AL13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -14435,32 +14435,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
-      <c r="U1" s="144"/>
-      <c r="V1" s="144"/>
-      <c r="W1" s="144"/>
-      <c r="X1" s="144"/>
-      <c r="Y1" s="144"/>
-      <c r="Z1" s="144"/>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="144"/>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="144"/>
-      <c r="AF1" s="144"/>
-      <c r="AG1" s="144"/>
-      <c r="AH1" s="144"/>
-      <c r="AI1" s="144"/>
-      <c r="AJ1" s="144"/>
-      <c r="AK1" s="144"/>
-      <c r="AL1" s="144"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="135"/>
+      <c r="S1" s="135"/>
+      <c r="T1" s="135"/>
+      <c r="U1" s="135"/>
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="135"/>
+      <c r="Z1" s="135"/>
+      <c r="AA1" s="135"/>
+      <c r="AB1" s="135"/>
+      <c r="AC1" s="135"/>
+      <c r="AD1" s="135"/>
+      <c r="AE1" s="135"/>
+      <c r="AF1" s="135"/>
+      <c r="AG1" s="135"/>
+      <c r="AH1" s="135"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="135"/>
+      <c r="AL1" s="135"/>
       <c r="AM1" s="67"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -14504,25 +14504,25 @@
       <c r="AM2" s="67"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="141"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="141"/>
-      <c r="R3" s="141"/>
-      <c r="S3" s="141"/>
+      <c r="A3" s="136"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
+      <c r="S3" s="136"/>
       <c r="T3" s="34"/>
       <c r="U3" s="34"/>
       <c r="V3" s="34"/>
@@ -14561,442 +14561,442 @@
       <c r="A7" s="6"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="139" t="s">
+      <c r="A8" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="139"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="139" t="s">
+      <c r="B8" s="144"/>
+      <c r="C8" s="144"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="144"/>
+      <c r="J8" s="144" t="s">
         <v>160</v>
       </c>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="139"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="139"/>
-      <c r="R8" s="139"/>
-      <c r="S8" s="139"/>
-      <c r="T8" s="139"/>
-      <c r="U8" s="139"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="139"/>
-      <c r="X8" s="139"/>
-      <c r="Y8" s="139"/>
-      <c r="Z8" s="139"/>
-      <c r="AA8" s="139"/>
-      <c r="AB8" s="139"/>
-      <c r="AC8" s="139"/>
-      <c r="AD8" s="139"/>
-      <c r="AE8" s="139"/>
-      <c r="AF8" s="139"/>
-      <c r="AG8" s="139"/>
-      <c r="AH8" s="139"/>
-      <c r="AI8" s="139" t="s">
+      <c r="K8" s="144"/>
+      <c r="L8" s="144"/>
+      <c r="M8" s="144"/>
+      <c r="N8" s="144"/>
+      <c r="O8" s="144"/>
+      <c r="P8" s="144"/>
+      <c r="Q8" s="144"/>
+      <c r="R8" s="144"/>
+      <c r="S8" s="144"/>
+      <c r="T8" s="144"/>
+      <c r="U8" s="144"/>
+      <c r="V8" s="144"/>
+      <c r="W8" s="144"/>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="144"/>
+      <c r="Z8" s="144"/>
+      <c r="AA8" s="144"/>
+      <c r="AB8" s="144"/>
+      <c r="AC8" s="144"/>
+      <c r="AD8" s="144"/>
+      <c r="AE8" s="144"/>
+      <c r="AF8" s="144"/>
+      <c r="AG8" s="144"/>
+      <c r="AH8" s="144"/>
+      <c r="AI8" s="144" t="s">
         <v>203</v>
       </c>
-      <c r="AJ8" s="139"/>
-      <c r="AK8" s="139"/>
-      <c r="AL8" s="139"/>
-      <c r="AM8" s="139"/>
+      <c r="AJ8" s="144"/>
+      <c r="AK8" s="144"/>
+      <c r="AL8" s="144"/>
+      <c r="AM8" s="144"/>
     </row>
     <row r="9" spans="1:39">
-      <c r="A9" s="139"/>
-      <c r="B9" s="139"/>
-      <c r="C9" s="139"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="139"/>
-      <c r="G9" s="139"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139" t="s">
+      <c r="A9" s="144"/>
+      <c r="B9" s="144"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="144"/>
+      <c r="E9" s="144"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="144"/>
+      <c r="J9" s="144" t="s">
         <v>205</v>
       </c>
-      <c r="K9" s="139"/>
-      <c r="L9" s="139"/>
-      <c r="M9" s="139" t="s">
+      <c r="K9" s="144"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="144" t="s">
         <v>206</v>
       </c>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="139" t="s">
+      <c r="N9" s="144"/>
+      <c r="O9" s="144"/>
+      <c r="P9" s="144" t="s">
         <v>207</v>
       </c>
-      <c r="Q9" s="139"/>
-      <c r="R9" s="139"/>
-      <c r="S9" s="139" t="s">
+      <c r="Q9" s="144"/>
+      <c r="R9" s="144"/>
+      <c r="S9" s="144" t="s">
         <v>208</v>
       </c>
-      <c r="T9" s="139"/>
-      <c r="U9" s="139"/>
-      <c r="V9" s="139" t="s">
+      <c r="T9" s="144"/>
+      <c r="U9" s="144"/>
+      <c r="V9" s="144" t="s">
         <v>209</v>
       </c>
-      <c r="W9" s="139"/>
-      <c r="X9" s="139"/>
-      <c r="Y9" s="139" t="s">
+      <c r="W9" s="144"/>
+      <c r="X9" s="144"/>
+      <c r="Y9" s="144" t="s">
         <v>204</v>
       </c>
-      <c r="Z9" s="139"/>
-      <c r="AA9" s="139"/>
-      <c r="AB9" s="139"/>
-      <c r="AC9" s="139" t="s">
+      <c r="Z9" s="144"/>
+      <c r="AA9" s="144"/>
+      <c r="AB9" s="144"/>
+      <c r="AC9" s="144" t="s">
         <v>202</v>
       </c>
-      <c r="AD9" s="139"/>
-      <c r="AE9" s="139"/>
-      <c r="AF9" s="139"/>
-      <c r="AG9" s="139"/>
-      <c r="AH9" s="139"/>
-      <c r="AI9" s="139"/>
-      <c r="AJ9" s="139"/>
-      <c r="AK9" s="139"/>
-      <c r="AL9" s="139"/>
-      <c r="AM9" s="139"/>
+      <c r="AD9" s="144"/>
+      <c r="AE9" s="144"/>
+      <c r="AF9" s="144"/>
+      <c r="AG9" s="144"/>
+      <c r="AH9" s="144"/>
+      <c r="AI9" s="144"/>
+      <c r="AJ9" s="144"/>
+      <c r="AK9" s="144"/>
+      <c r="AL9" s="144"/>
+      <c r="AM9" s="144"/>
     </row>
     <row r="10" spans="1:39">
       <c r="A10" s="175"/>
       <c r="B10" s="175"/>
-      <c r="C10" s="139" t="s">
+      <c r="C10" s="144" t="s">
         <v>211</v>
       </c>
-      <c r="D10" s="139"/>
-      <c r="E10" s="139"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="139"/>
-      <c r="K10" s="139"/>
-      <c r="L10" s="139"/>
-      <c r="M10" s="139"/>
-      <c r="N10" s="139"/>
-      <c r="O10" s="139"/>
-      <c r="P10" s="139"/>
-      <c r="Q10" s="139"/>
-      <c r="R10" s="139"/>
-      <c r="S10" s="139"/>
-      <c r="T10" s="139"/>
-      <c r="U10" s="139"/>
-      <c r="V10" s="139"/>
-      <c r="W10" s="139"/>
-      <c r="X10" s="139"/>
-      <c r="Y10" s="139"/>
-      <c r="Z10" s="139"/>
-      <c r="AA10" s="139"/>
-      <c r="AB10" s="139"/>
-      <c r="AC10" s="139"/>
-      <c r="AD10" s="139"/>
-      <c r="AE10" s="139"/>
-      <c r="AF10" s="139"/>
-      <c r="AG10" s="139"/>
-      <c r="AH10" s="139"/>
-      <c r="AI10" s="139"/>
-      <c r="AJ10" s="139"/>
-      <c r="AK10" s="139"/>
-      <c r="AL10" s="139"/>
-      <c r="AM10" s="139"/>
+      <c r="D10" s="144"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="144"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="144"/>
+      <c r="L10" s="144"/>
+      <c r="M10" s="144"/>
+      <c r="N10" s="144"/>
+      <c r="O10" s="144"/>
+      <c r="P10" s="144"/>
+      <c r="Q10" s="144"/>
+      <c r="R10" s="144"/>
+      <c r="S10" s="144"/>
+      <c r="T10" s="144"/>
+      <c r="U10" s="144"/>
+      <c r="V10" s="144"/>
+      <c r="W10" s="144"/>
+      <c r="X10" s="144"/>
+      <c r="Y10" s="144"/>
+      <c r="Z10" s="144"/>
+      <c r="AA10" s="144"/>
+      <c r="AB10" s="144"/>
+      <c r="AC10" s="144"/>
+      <c r="AD10" s="144"/>
+      <c r="AE10" s="144"/>
+      <c r="AF10" s="144"/>
+      <c r="AG10" s="144"/>
+      <c r="AH10" s="144"/>
+      <c r="AI10" s="144"/>
+      <c r="AJ10" s="144"/>
+      <c r="AK10" s="144"/>
+      <c r="AL10" s="144"/>
+      <c r="AM10" s="144"/>
     </row>
     <row r="11" spans="1:39">
       <c r="A11" s="175"/>
       <c r="B11" s="175"/>
-      <c r="C11" s="139"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="139"/>
-      <c r="G11" s="139"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="139"/>
-      <c r="K11" s="139"/>
-      <c r="L11" s="139"/>
-      <c r="M11" s="139"/>
-      <c r="N11" s="139"/>
-      <c r="O11" s="139"/>
-      <c r="P11" s="139"/>
-      <c r="Q11" s="139"/>
-      <c r="R11" s="139"/>
-      <c r="S11" s="139"/>
-      <c r="T11" s="139"/>
-      <c r="U11" s="139"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="139"/>
-      <c r="X11" s="139"/>
-      <c r="Y11" s="139"/>
-      <c r="Z11" s="139"/>
-      <c r="AA11" s="139"/>
-      <c r="AB11" s="139"/>
-      <c r="AC11" s="139"/>
-      <c r="AD11" s="139"/>
-      <c r="AE11" s="139"/>
-      <c r="AF11" s="139"/>
-      <c r="AG11" s="139"/>
-      <c r="AH11" s="139"/>
-      <c r="AI11" s="139"/>
-      <c r="AJ11" s="139"/>
-      <c r="AK11" s="139"/>
-      <c r="AL11" s="139"/>
-      <c r="AM11" s="139"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="144"/>
+      <c r="M11" s="144"/>
+      <c r="N11" s="144"/>
+      <c r="O11" s="144"/>
+      <c r="P11" s="144"/>
+      <c r="Q11" s="144"/>
+      <c r="R11" s="144"/>
+      <c r="S11" s="144"/>
+      <c r="T11" s="144"/>
+      <c r="U11" s="144"/>
+      <c r="V11" s="144"/>
+      <c r="W11" s="144"/>
+      <c r="X11" s="144"/>
+      <c r="Y11" s="144"/>
+      <c r="Z11" s="144"/>
+      <c r="AA11" s="144"/>
+      <c r="AB11" s="144"/>
+      <c r="AC11" s="144"/>
+      <c r="AD11" s="144"/>
+      <c r="AE11" s="144"/>
+      <c r="AF11" s="144"/>
+      <c r="AG11" s="144"/>
+      <c r="AH11" s="144"/>
+      <c r="AI11" s="144"/>
+      <c r="AJ11" s="144"/>
+      <c r="AK11" s="144"/>
+      <c r="AL11" s="144"/>
+      <c r="AM11" s="144"/>
     </row>
     <row r="12" spans="1:39">
       <c r="A12" s="175"/>
       <c r="B12" s="175"/>
-      <c r="C12" s="139" t="s">
+      <c r="C12" s="144" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="139"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="139"/>
-      <c r="K12" s="139"/>
-      <c r="L12" s="139"/>
-      <c r="M12" s="139"/>
-      <c r="N12" s="139"/>
-      <c r="O12" s="139"/>
-      <c r="P12" s="139"/>
-      <c r="Q12" s="139"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="139"/>
-      <c r="T12" s="139"/>
-      <c r="U12" s="139"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="139"/>
-      <c r="X12" s="139"/>
-      <c r="Y12" s="139"/>
-      <c r="Z12" s="139"/>
-      <c r="AA12" s="139"/>
-      <c r="AB12" s="139"/>
-      <c r="AC12" s="139"/>
-      <c r="AD12" s="139"/>
-      <c r="AE12" s="139"/>
-      <c r="AF12" s="139"/>
-      <c r="AG12" s="139"/>
-      <c r="AH12" s="139"/>
-      <c r="AI12" s="139"/>
-      <c r="AJ12" s="139"/>
-      <c r="AK12" s="139"/>
-      <c r="AL12" s="139"/>
-      <c r="AM12" s="139"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="144"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="144"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="144"/>
+      <c r="P12" s="144"/>
+      <c r="Q12" s="144"/>
+      <c r="R12" s="144"/>
+      <c r="S12" s="144"/>
+      <c r="T12" s="144"/>
+      <c r="U12" s="144"/>
+      <c r="V12" s="144"/>
+      <c r="W12" s="144"/>
+      <c r="X12" s="144"/>
+      <c r="Y12" s="144"/>
+      <c r="Z12" s="144"/>
+      <c r="AA12" s="144"/>
+      <c r="AB12" s="144"/>
+      <c r="AC12" s="144"/>
+      <c r="AD12" s="144"/>
+      <c r="AE12" s="144"/>
+      <c r="AF12" s="144"/>
+      <c r="AG12" s="144"/>
+      <c r="AH12" s="144"/>
+      <c r="AI12" s="144"/>
+      <c r="AJ12" s="144"/>
+      <c r="AK12" s="144"/>
+      <c r="AL12" s="144"/>
+      <c r="AM12" s="144"/>
     </row>
     <row r="13" spans="1:39">
       <c r="A13" s="175"/>
       <c r="B13" s="175"/>
-      <c r="C13" s="139"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="139"/>
-      <c r="G13" s="139"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="139"/>
-      <c r="J13" s="139"/>
-      <c r="K13" s="139"/>
-      <c r="L13" s="139"/>
-      <c r="M13" s="139"/>
-      <c r="N13" s="139"/>
-      <c r="O13" s="139"/>
-      <c r="P13" s="139"/>
-      <c r="Q13" s="139"/>
-      <c r="R13" s="139"/>
-      <c r="S13" s="139"/>
-      <c r="T13" s="139"/>
-      <c r="U13" s="139"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="139"/>
-      <c r="X13" s="139"/>
-      <c r="Y13" s="139"/>
-      <c r="Z13" s="139"/>
-      <c r="AA13" s="139"/>
-      <c r="AB13" s="139"/>
-      <c r="AC13" s="139"/>
-      <c r="AD13" s="139"/>
-      <c r="AE13" s="139"/>
-      <c r="AF13" s="139"/>
-      <c r="AG13" s="139"/>
-      <c r="AH13" s="139"/>
-      <c r="AI13" s="139"/>
-      <c r="AJ13" s="139"/>
-      <c r="AK13" s="139"/>
-      <c r="AL13" s="139"/>
-      <c r="AM13" s="139"/>
+      <c r="C13" s="144"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="144"/>
+      <c r="N13" s="144"/>
+      <c r="O13" s="144"/>
+      <c r="P13" s="144"/>
+      <c r="Q13" s="144"/>
+      <c r="R13" s="144"/>
+      <c r="S13" s="144"/>
+      <c r="T13" s="144"/>
+      <c r="U13" s="144"/>
+      <c r="V13" s="144"/>
+      <c r="W13" s="144"/>
+      <c r="X13" s="144"/>
+      <c r="Y13" s="144"/>
+      <c r="Z13" s="144"/>
+      <c r="AA13" s="144"/>
+      <c r="AB13" s="144"/>
+      <c r="AC13" s="144"/>
+      <c r="AD13" s="144"/>
+      <c r="AE13" s="144"/>
+      <c r="AF13" s="144"/>
+      <c r="AG13" s="144"/>
+      <c r="AH13" s="144"/>
+      <c r="AI13" s="144"/>
+      <c r="AJ13" s="144"/>
+      <c r="AK13" s="144"/>
+      <c r="AL13" s="144"/>
+      <c r="AM13" s="144"/>
     </row>
     <row r="14" spans="1:39">
       <c r="A14" s="175"/>
       <c r="B14" s="175"/>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="144" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="139"/>
-      <c r="E14" s="139"/>
-      <c r="F14" s="139"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="139"/>
-      <c r="J14" s="139"/>
-      <c r="K14" s="139"/>
-      <c r="L14" s="139"/>
-      <c r="M14" s="139"/>
-      <c r="N14" s="139"/>
-      <c r="O14" s="139"/>
-      <c r="P14" s="139"/>
-      <c r="Q14" s="139"/>
-      <c r="R14" s="139"/>
-      <c r="S14" s="139"/>
-      <c r="T14" s="139"/>
-      <c r="U14" s="139"/>
-      <c r="V14" s="139"/>
-      <c r="W14" s="139"/>
-      <c r="X14" s="139"/>
-      <c r="Y14" s="139"/>
-      <c r="Z14" s="139"/>
-      <c r="AA14" s="139"/>
-      <c r="AB14" s="139"/>
-      <c r="AC14" s="139"/>
-      <c r="AD14" s="139"/>
-      <c r="AE14" s="139"/>
-      <c r="AF14" s="139"/>
-      <c r="AG14" s="139"/>
-      <c r="AH14" s="139"/>
-      <c r="AI14" s="139"/>
-      <c r="AJ14" s="139"/>
-      <c r="AK14" s="139"/>
-      <c r="AL14" s="139"/>
-      <c r="AM14" s="139"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="144"/>
+      <c r="P14" s="144"/>
+      <c r="Q14" s="144"/>
+      <c r="R14" s="144"/>
+      <c r="S14" s="144"/>
+      <c r="T14" s="144"/>
+      <c r="U14" s="144"/>
+      <c r="V14" s="144"/>
+      <c r="W14" s="144"/>
+      <c r="X14" s="144"/>
+      <c r="Y14" s="144"/>
+      <c r="Z14" s="144"/>
+      <c r="AA14" s="144"/>
+      <c r="AB14" s="144"/>
+      <c r="AC14" s="144"/>
+      <c r="AD14" s="144"/>
+      <c r="AE14" s="144"/>
+      <c r="AF14" s="144"/>
+      <c r="AG14" s="144"/>
+      <c r="AH14" s="144"/>
+      <c r="AI14" s="144"/>
+      <c r="AJ14" s="144"/>
+      <c r="AK14" s="144"/>
+      <c r="AL14" s="144"/>
+      <c r="AM14" s="144"/>
     </row>
     <row r="15" spans="1:39">
       <c r="A15" s="175"/>
       <c r="B15" s="175"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
-      <c r="M15" s="139"/>
-      <c r="N15" s="139"/>
-      <c r="O15" s="139"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
-      <c r="U15" s="139"/>
-      <c r="V15" s="139"/>
-      <c r="W15" s="139"/>
-      <c r="X15" s="139"/>
-      <c r="Y15" s="139"/>
-      <c r="Z15" s="139"/>
-      <c r="AA15" s="139"/>
-      <c r="AB15" s="139"/>
-      <c r="AC15" s="139"/>
-      <c r="AD15" s="139"/>
-      <c r="AE15" s="139"/>
-      <c r="AF15" s="139"/>
-      <c r="AG15" s="139"/>
-      <c r="AH15" s="139"/>
-      <c r="AI15" s="139"/>
-      <c r="AJ15" s="139"/>
-      <c r="AK15" s="139"/>
-      <c r="AL15" s="139"/>
-      <c r="AM15" s="139"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
+      <c r="S15" s="144"/>
+      <c r="T15" s="144"/>
+      <c r="U15" s="144"/>
+      <c r="V15" s="144"/>
+      <c r="W15" s="144"/>
+      <c r="X15" s="144"/>
+      <c r="Y15" s="144"/>
+      <c r="Z15" s="144"/>
+      <c r="AA15" s="144"/>
+      <c r="AB15" s="144"/>
+      <c r="AC15" s="144"/>
+      <c r="AD15" s="144"/>
+      <c r="AE15" s="144"/>
+      <c r="AF15" s="144"/>
+      <c r="AG15" s="144"/>
+      <c r="AH15" s="144"/>
+      <c r="AI15" s="144"/>
+      <c r="AJ15" s="144"/>
+      <c r="AK15" s="144"/>
+      <c r="AL15" s="144"/>
+      <c r="AM15" s="144"/>
     </row>
     <row r="16" spans="1:39">
       <c r="A16" s="175"/>
       <c r="B16" s="175"/>
-      <c r="C16" s="139" t="s">
+      <c r="C16" s="144" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="139"/>
-      <c r="J16" s="139"/>
-      <c r="K16" s="139"/>
-      <c r="L16" s="139"/>
-      <c r="M16" s="139"/>
-      <c r="N16" s="139"/>
-      <c r="O16" s="139"/>
-      <c r="P16" s="139"/>
-      <c r="Q16" s="139"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="139"/>
-      <c r="T16" s="139"/>
-      <c r="U16" s="139"/>
-      <c r="V16" s="139"/>
-      <c r="W16" s="139"/>
-      <c r="X16" s="139"/>
-      <c r="Y16" s="139"/>
-      <c r="Z16" s="139"/>
-      <c r="AA16" s="139"/>
-      <c r="AB16" s="139"/>
-      <c r="AC16" s="139"/>
-      <c r="AD16" s="139"/>
-      <c r="AE16" s="139"/>
-      <c r="AF16" s="139"/>
-      <c r="AG16" s="139"/>
-      <c r="AH16" s="139"/>
-      <c r="AI16" s="139"/>
-      <c r="AJ16" s="139"/>
-      <c r="AK16" s="139"/>
-      <c r="AL16" s="139"/>
-      <c r="AM16" s="139"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="144"/>
+      <c r="Q16" s="144"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="144"/>
+      <c r="T16" s="144"/>
+      <c r="U16" s="144"/>
+      <c r="V16" s="144"/>
+      <c r="W16" s="144"/>
+      <c r="X16" s="144"/>
+      <c r="Y16" s="144"/>
+      <c r="Z16" s="144"/>
+      <c r="AA16" s="144"/>
+      <c r="AB16" s="144"/>
+      <c r="AC16" s="144"/>
+      <c r="AD16" s="144"/>
+      <c r="AE16" s="144"/>
+      <c r="AF16" s="144"/>
+      <c r="AG16" s="144"/>
+      <c r="AH16" s="144"/>
+      <c r="AI16" s="144"/>
+      <c r="AJ16" s="144"/>
+      <c r="AK16" s="144"/>
+      <c r="AL16" s="144"/>
+      <c r="AM16" s="144"/>
     </row>
     <row r="17" spans="1:39">
       <c r="A17" s="175"/>
       <c r="B17" s="175"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="139"/>
-      <c r="E17" s="139"/>
-      <c r="F17" s="139"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="139"/>
-      <c r="I17" s="139"/>
-      <c r="J17" s="139"/>
-      <c r="K17" s="139"/>
-      <c r="L17" s="139"/>
-      <c r="M17" s="139"/>
-      <c r="N17" s="139"/>
-      <c r="O17" s="139"/>
-      <c r="P17" s="139"/>
-      <c r="Q17" s="139"/>
-      <c r="R17" s="139"/>
-      <c r="S17" s="139"/>
-      <c r="T17" s="139"/>
-      <c r="U17" s="139"/>
-      <c r="V17" s="139"/>
-      <c r="W17" s="139"/>
-      <c r="X17" s="139"/>
-      <c r="Y17" s="139"/>
-      <c r="Z17" s="139"/>
-      <c r="AA17" s="139"/>
-      <c r="AB17" s="139"/>
-      <c r="AC17" s="139"/>
-      <c r="AD17" s="139"/>
-      <c r="AE17" s="139"/>
-      <c r="AF17" s="139"/>
-      <c r="AG17" s="139"/>
-      <c r="AH17" s="139"/>
-      <c r="AI17" s="139"/>
-      <c r="AJ17" s="139"/>
-      <c r="AK17" s="139"/>
-      <c r="AL17" s="139"/>
-      <c r="AM17" s="139"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="144"/>
+      <c r="J17" s="144"/>
+      <c r="K17" s="144"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="144"/>
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
+      <c r="U17" s="144"/>
+      <c r="V17" s="144"/>
+      <c r="W17" s="144"/>
+      <c r="X17" s="144"/>
+      <c r="Y17" s="144"/>
+      <c r="Z17" s="144"/>
+      <c r="AA17" s="144"/>
+      <c r="AB17" s="144"/>
+      <c r="AC17" s="144"/>
+      <c r="AD17" s="144"/>
+      <c r="AE17" s="144"/>
+      <c r="AF17" s="144"/>
+      <c r="AG17" s="144"/>
+      <c r="AH17" s="144"/>
+      <c r="AI17" s="144"/>
+      <c r="AJ17" s="144"/>
+      <c r="AK17" s="144"/>
+      <c r="AL17" s="144"/>
+      <c r="AM17" s="144"/>
     </row>
     <row r="19" spans="1:39">
       <c r="A19" s="68" t="s">
@@ -15005,6 +15005,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="Y16:AB17"/>
+    <mergeCell ref="AC16:AH17"/>
+    <mergeCell ref="AI16:AM17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="J16:L17"/>
+    <mergeCell ref="M16:O17"/>
+    <mergeCell ref="P16:R17"/>
+    <mergeCell ref="S16:U17"/>
+    <mergeCell ref="V16:X17"/>
+    <mergeCell ref="AI14:AM15"/>
+    <mergeCell ref="J10:L11"/>
+    <mergeCell ref="P10:R11"/>
+    <mergeCell ref="M10:O11"/>
+    <mergeCell ref="S10:U11"/>
+    <mergeCell ref="V10:X11"/>
+    <mergeCell ref="Y10:AB11"/>
+    <mergeCell ref="AC10:AH11"/>
+    <mergeCell ref="AI12:AM13"/>
+    <mergeCell ref="AI10:AM11"/>
+    <mergeCell ref="P14:R15"/>
+    <mergeCell ref="S14:U15"/>
+    <mergeCell ref="V14:X15"/>
+    <mergeCell ref="Y14:AB15"/>
+    <mergeCell ref="AC14:AH15"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="Y9:AB9"/>
+    <mergeCell ref="AC9:AH9"/>
+    <mergeCell ref="P12:R13"/>
+    <mergeCell ref="S12:U13"/>
+    <mergeCell ref="V12:X13"/>
+    <mergeCell ref="Y12:AB13"/>
+    <mergeCell ref="AC12:AH13"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="S9:U9"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="AI8:AM9"/>
     <mergeCell ref="M1:AL1"/>
@@ -15021,40 +15055,6 @@
     <mergeCell ref="C10:I11"/>
     <mergeCell ref="C12:I13"/>
     <mergeCell ref="A8:I9"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="AC9:AH9"/>
-    <mergeCell ref="P12:R13"/>
-    <mergeCell ref="S12:U13"/>
-    <mergeCell ref="V12:X13"/>
-    <mergeCell ref="Y12:AB13"/>
-    <mergeCell ref="AC12:AH13"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="AI14:AM15"/>
-    <mergeCell ref="J10:L11"/>
-    <mergeCell ref="P10:R11"/>
-    <mergeCell ref="M10:O11"/>
-    <mergeCell ref="S10:U11"/>
-    <mergeCell ref="V10:X11"/>
-    <mergeCell ref="Y10:AB11"/>
-    <mergeCell ref="AC10:AH11"/>
-    <mergeCell ref="AI12:AM13"/>
-    <mergeCell ref="AI10:AM11"/>
-    <mergeCell ref="P14:R15"/>
-    <mergeCell ref="S14:U15"/>
-    <mergeCell ref="V14:X15"/>
-    <mergeCell ref="Y14:AB15"/>
-    <mergeCell ref="AC14:AH15"/>
-    <mergeCell ref="Y16:AB17"/>
-    <mergeCell ref="AC16:AH17"/>
-    <mergeCell ref="AI16:AM17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="J16:L17"/>
-    <mergeCell ref="M16:O17"/>
-    <mergeCell ref="P16:R17"/>
-    <mergeCell ref="S16:U17"/>
-    <mergeCell ref="V16:X17"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/wwwroot/ExcelModel/Kik_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Kik_PHY_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8F7AEE-16F9-4FE0-8B9E-9E11CC81F335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627743DF-A83D-41E0-A24A-33161B2F5EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,7 +244,7 @@
   </si>
   <si>
     <t>Pilling Resistance</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -269,7 +269,7 @@
       </rPr>
       <t>: Not applicable</t>
     </r>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Zipper Strength</t>
@@ -835,102 +835,102 @@
   </si>
   <si>
     <t>Cycle：</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Original</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Sample</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Cycle</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Rating</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Pilling</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Fuzzing</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Matting</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Pilling grading scheme</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Fuzzing grading scheme</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Matting grading scheme</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>5 No change</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>4 partially formed pills</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>4 Slight surface fuzzing</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">3 Moderate pilling- pills of varying  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>3Moderate surface fuzzing</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">size and density partially covering </t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>the specimen surface</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>2 Distinct pilling- pills of varying</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>2 Distinct surface fuzzing</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">size and density covering a large </t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>proportion of the specimen surface</t>
   </si>
   <si>
     <t xml:space="preserve">1 Severe pilling- pills of varying size </t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>1 Dense surface fuzzing</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>and density covering the whole of the</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> specimen surface</t>
@@ -1015,11 +1015,11 @@
   </si>
   <si>
     <t xml:space="preserve">Hydrostatic Head; Rate of increase of water pressure: 10 cm/min &amp; 60cm/min, temp of distilled </t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>water: 20ºC, face side facing water.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Original: </t>
@@ -1134,7 +1134,7 @@
   </si>
   <si>
     <t>Air Permeability</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1165,11 +1165,11 @@
       </rPr>
       <t>：</t>
     </r>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Pa</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1185,70 +1185,70 @@
       </rPr>
       <t>：</t>
     </r>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>sq. cm.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>CV(%):</t>
   </si>
   <si>
     <t xml:space="preserve">(Unit: </t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 5</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 6</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 7</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 8</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 9</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimen 10</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Average</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>CV%</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1264,119 +1264,119 @@
       </rPr>
       <t>：</t>
     </r>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Standards</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Test area (cm2)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Test Pressure (Pa)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Unit of measure</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Apparel fabrics</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Industrial fabrics</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>mm/s</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>DIN EN ISO 9237</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Attachment Strength of Button</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Attachment Strength：</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Result(kg)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Result(N)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Specimens</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button5</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button6</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button7</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button8</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button9</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button10</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button11</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button12</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button13</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button14</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Button15</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Remarks: Apply a force of </t>
@@ -1431,75 +1431,75 @@
   </si>
   <si>
     <t>Attachment Strength of Snap</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Male</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Female</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap5</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap6</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap7</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap8</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap9</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap10</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap15</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap14</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap13</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap12</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Snap11</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1514,75 +1514,75 @@
       </rPr>
       <t>: S.B.D—Snap Break Down    S.T.B—Sewing Thread Break   F.B—Fabric Break</t>
     </r>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Warp end count/Warp end/Lengthwise/ Wales                            /  cm                                               /   inch</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Filling pick count/Weft pick/Widthwise/ courses                       /  cm                                               /   inch</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Distance(cm)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Ave./cm</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Ave.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>#1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>#2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>#3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>#4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>#5</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Weft / Courses</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Warp / Wales</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Threads/Stitches Per Inch/cm</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Sample：</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Clockwise</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Anticlockwise</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Sample Size:</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1675,12 +1675,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2153,13 +2160,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2168,482 +2175,482 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2938,25 +2945,25 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
-      <c r="Z1" s="79"/>
-      <c r="AA1" s="79"/>
-      <c r="AB1" s="79"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="5" t="s">
@@ -2988,25 +2995,25 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="95"/>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="95"/>
-      <c r="S3" s="95"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -3192,230 +3199,230 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" ht="16.2">
-      <c r="A10" s="88" t="s">
+      <c r="A10" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="89"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="80" t="s">
+      <c r="B10" s="95"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="81"/>
-      <c r="U10" s="81"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="82" t="s">
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="87"/>
+      <c r="L10" s="87"/>
+      <c r="M10" s="87"/>
+      <c r="N10" s="87"/>
+      <c r="O10" s="87"/>
+      <c r="P10" s="87"/>
+      <c r="Q10" s="87"/>
+      <c r="R10" s="87"/>
+      <c r="S10" s="87"/>
+      <c r="T10" s="87"/>
+      <c r="U10" s="87"/>
+      <c r="V10" s="87"/>
+      <c r="W10" s="87"/>
+      <c r="X10" s="87"/>
+      <c r="Y10" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="83"/>
-      <c r="AA10" s="83"/>
-      <c r="AB10" s="84"/>
+      <c r="Z10" s="89"/>
+      <c r="AA10" s="89"/>
+      <c r="AB10" s="90"/>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="91"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="80" t="s">
+      <c r="A11" s="97"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="80" t="s">
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="80" t="s">
+      <c r="J11" s="87"/>
+      <c r="K11" s="87"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="78"/>
-      <c r="Q11" s="80" t="s">
+      <c r="N11" s="87"/>
+      <c r="O11" s="87"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="80" t="s">
+      <c r="R11" s="87"/>
+      <c r="S11" s="87"/>
+      <c r="T11" s="100"/>
+      <c r="U11" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="77"/>
-      <c r="Y11" s="85"/>
-      <c r="Z11" s="86"/>
-      <c r="AA11" s="86"/>
-      <c r="AB11" s="87"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="87"/>
+      <c r="X11" s="101"/>
+      <c r="Y11" s="91"/>
+      <c r="Z11" s="92"/>
+      <c r="AA11" s="92"/>
+      <c r="AB11" s="93"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="96"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="78"/>
-      <c r="Q12" s="76"/>
-      <c r="R12" s="77"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="78"/>
-      <c r="U12" s="76"/>
-      <c r="V12" s="77"/>
-      <c r="W12" s="77"/>
-      <c r="X12" s="78"/>
-      <c r="Y12" s="76"/>
-      <c r="Z12" s="77"/>
-      <c r="AA12" s="77"/>
-      <c r="AB12" s="78"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="104"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="100"/>
+      <c r="Q12" s="104"/>
+      <c r="R12" s="101"/>
+      <c r="S12" s="101"/>
+      <c r="T12" s="100"/>
+      <c r="U12" s="104"/>
+      <c r="V12" s="101"/>
+      <c r="W12" s="101"/>
+      <c r="X12" s="100"/>
+      <c r="Y12" s="104"/>
+      <c r="Z12" s="101"/>
+      <c r="AA12" s="101"/>
+      <c r="AB12" s="100"/>
     </row>
     <row r="13" spans="1:28">
-      <c r="A13" s="96"/>
-      <c r="B13" s="97"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="77"/>
-      <c r="O13" s="77"/>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="76"/>
-      <c r="R13" s="77"/>
-      <c r="S13" s="77"/>
-      <c r="T13" s="78"/>
-      <c r="U13" s="76"/>
-      <c r="V13" s="77"/>
-      <c r="W13" s="77"/>
-      <c r="X13" s="78"/>
-      <c r="Y13" s="76"/>
-      <c r="Z13" s="77"/>
-      <c r="AA13" s="77"/>
-      <c r="AB13" s="78"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="101"/>
+      <c r="K13" s="101"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="101"/>
+      <c r="P13" s="100"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="101"/>
+      <c r="S13" s="101"/>
+      <c r="T13" s="100"/>
+      <c r="U13" s="104"/>
+      <c r="V13" s="101"/>
+      <c r="W13" s="101"/>
+      <c r="X13" s="100"/>
+      <c r="Y13" s="104"/>
+      <c r="Z13" s="101"/>
+      <c r="AA13" s="101"/>
+      <c r="AB13" s="100"/>
     </row>
     <row r="14" spans="1:28">
-      <c r="A14" s="96"/>
-      <c r="B14" s="97"/>
-      <c r="C14" s="97"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="77"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="76"/>
-      <c r="R14" s="77"/>
-      <c r="S14" s="77"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="76"/>
-      <c r="V14" s="77"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="78"/>
-      <c r="Y14" s="76"/>
-      <c r="Z14" s="77"/>
-      <c r="AA14" s="77"/>
-      <c r="AB14" s="78"/>
+      <c r="A14" s="82"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="101"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="100"/>
+      <c r="Q14" s="104"/>
+      <c r="R14" s="101"/>
+      <c r="S14" s="101"/>
+      <c r="T14" s="100"/>
+      <c r="U14" s="104"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="101"/>
+      <c r="X14" s="100"/>
+      <c r="Y14" s="104"/>
+      <c r="Z14" s="101"/>
+      <c r="AA14" s="101"/>
+      <c r="AB14" s="100"/>
     </row>
     <row r="15" spans="1:28">
-      <c r="A15" s="96"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="76"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="77"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="76"/>
-      <c r="R15" s="77"/>
-      <c r="S15" s="77"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="76"/>
-      <c r="V15" s="77"/>
-      <c r="W15" s="77"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="76"/>
-      <c r="Z15" s="77"/>
-      <c r="AA15" s="77"/>
-      <c r="AB15" s="78"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="101"/>
+      <c r="L15" s="100"/>
+      <c r="M15" s="104"/>
+      <c r="N15" s="101"/>
+      <c r="O15" s="101"/>
+      <c r="P15" s="100"/>
+      <c r="Q15" s="104"/>
+      <c r="R15" s="101"/>
+      <c r="S15" s="101"/>
+      <c r="T15" s="100"/>
+      <c r="U15" s="104"/>
+      <c r="V15" s="101"/>
+      <c r="W15" s="101"/>
+      <c r="X15" s="100"/>
+      <c r="Y15" s="104"/>
+      <c r="Z15" s="101"/>
+      <c r="AA15" s="101"/>
+      <c r="AB15" s="100"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="96"/>
-      <c r="B16" s="97"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="76"/>
-      <c r="N16" s="77"/>
-      <c r="O16" s="77"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="76"/>
-      <c r="R16" s="77"/>
-      <c r="S16" s="77"/>
-      <c r="T16" s="78"/>
-      <c r="U16" s="76"/>
-      <c r="V16" s="77"/>
-      <c r="W16" s="77"/>
-      <c r="X16" s="78"/>
-      <c r="Y16" s="76"/>
-      <c r="Z16" s="77"/>
-      <c r="AA16" s="77"/>
-      <c r="AB16" s="78"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="101"/>
+      <c r="K16" s="101"/>
+      <c r="L16" s="100"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="101"/>
+      <c r="O16" s="101"/>
+      <c r="P16" s="100"/>
+      <c r="Q16" s="104"/>
+      <c r="R16" s="101"/>
+      <c r="S16" s="101"/>
+      <c r="T16" s="100"/>
+      <c r="U16" s="104"/>
+      <c r="V16" s="101"/>
+      <c r="W16" s="101"/>
+      <c r="X16" s="100"/>
+      <c r="Y16" s="104"/>
+      <c r="Z16" s="101"/>
+      <c r="AA16" s="101"/>
+      <c r="AB16" s="100"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="3" t="s">
@@ -3558,32 +3565,14 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="J1:AB1"/>
-    <mergeCell ref="E10:X10"/>
-    <mergeCell ref="Y10:AB11"/>
-    <mergeCell ref="A10:D11"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:P11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="Y12:AB12"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="Y13:AB13"/>
+    <mergeCell ref="U14:X14"/>
+    <mergeCell ref="Y14:AB14"/>
     <mergeCell ref="M15:P15"/>
     <mergeCell ref="Q15:T15"/>
     <mergeCell ref="M16:P16"/>
@@ -3596,16 +3585,34 @@
     <mergeCell ref="Q13:T13"/>
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="Y15:AB15"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="Y12:AB12"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="Y13:AB13"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="Y14:AB14"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="J1:AB1"/>
+    <mergeCell ref="E10:X10"/>
+    <mergeCell ref="Y10:AB11"/>
+    <mergeCell ref="A10:D11"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -3644,32 +3651,32 @@
       <c r="J1" s="41"/>
       <c r="K1" s="41"/>
       <c r="L1" s="41"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
-      <c r="AL1" s="120"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+      <c r="V1" s="111"/>
+      <c r="W1" s="111"/>
+      <c r="X1" s="111"/>
+      <c r="Y1" s="111"/>
+      <c r="Z1" s="111"/>
+      <c r="AA1" s="111"/>
+      <c r="AB1" s="111"/>
+      <c r="AC1" s="111"/>
+      <c r="AD1" s="111"/>
+      <c r="AE1" s="111"/>
+      <c r="AF1" s="111"/>
+      <c r="AG1" s="111"/>
+      <c r="AH1" s="111"/>
+      <c r="AI1" s="111"/>
+      <c r="AJ1" s="111"/>
+      <c r="AK1" s="111"/>
+      <c r="AL1" s="111"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="42" t="s">
@@ -3705,17 +3712,17 @@
       <c r="AF2" s="39"/>
     </row>
     <row r="3" spans="1:38" ht="15.75" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
+      <c r="A3" s="112"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
       <c r="L3" s="39"/>
       <c r="M3" s="39"/>
       <c r="N3" s="39"/>
@@ -3932,45 +3939,45 @@
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="114" t="s">
+      <c r="D10" s="113"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="116"/>
-      <c r="P10" s="114" t="s">
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="106"/>
+      <c r="O10" s="107"/>
+      <c r="P10" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="Q10" s="115"/>
-      <c r="R10" s="115"/>
-      <c r="S10" s="115"/>
-      <c r="T10" s="115"/>
-      <c r="U10" s="115"/>
-      <c r="V10" s="115"/>
-      <c r="W10" s="115"/>
-      <c r="X10" s="115"/>
-      <c r="Y10" s="115"/>
-      <c r="Z10" s="115"/>
-      <c r="AA10" s="115"/>
-      <c r="AB10" s="115"/>
-      <c r="AC10" s="115"/>
-      <c r="AD10" s="115"/>
-      <c r="AE10" s="115"/>
-      <c r="AF10" s="115"/>
-      <c r="AG10" s="115"/>
-      <c r="AH10" s="115"/>
-      <c r="AI10" s="115"/>
-      <c r="AJ10" s="115"/>
-      <c r="AK10" s="115"/>
-      <c r="AL10" s="116"/>
+      <c r="Q10" s="106"/>
+      <c r="R10" s="106"/>
+      <c r="S10" s="106"/>
+      <c r="T10" s="106"/>
+      <c r="U10" s="106"/>
+      <c r="V10" s="106"/>
+      <c r="W10" s="106"/>
+      <c r="X10" s="106"/>
+      <c r="Y10" s="106"/>
+      <c r="Z10" s="106"/>
+      <c r="AA10" s="106"/>
+      <c r="AB10" s="106"/>
+      <c r="AC10" s="106"/>
+      <c r="AD10" s="106"/>
+      <c r="AE10" s="106"/>
+      <c r="AF10" s="106"/>
+      <c r="AG10" s="106"/>
+      <c r="AH10" s="106"/>
+      <c r="AI10" s="106"/>
+      <c r="AJ10" s="106"/>
+      <c r="AK10" s="106"/>
+      <c r="AL10" s="107"/>
     </row>
     <row r="11" spans="1:38">
       <c r="A11" s="43" t="s">
@@ -3980,62 +3987,62 @@
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
       <c r="E11" s="46"/>
-      <c r="F11" s="114" t="s">
+      <c r="F11" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="115"/>
-      <c r="H11" s="115"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="114" t="s">
+      <c r="G11" s="106"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="115"/>
-      <c r="M11" s="115"/>
-      <c r="N11" s="115"/>
-      <c r="O11" s="116"/>
-      <c r="P11" s="114" t="s">
+      <c r="L11" s="106"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="106"/>
+      <c r="O11" s="107"/>
+      <c r="P11" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" s="115"/>
-      <c r="R11" s="115"/>
-      <c r="S11" s="115"/>
-      <c r="T11" s="116"/>
-      <c r="U11" s="114" t="s">
+      <c r="Q11" s="106"/>
+      <c r="R11" s="106"/>
+      <c r="S11" s="106"/>
+      <c r="T11" s="107"/>
+      <c r="U11" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="V11" s="115"/>
-      <c r="W11" s="115"/>
-      <c r="X11" s="115"/>
-      <c r="Y11" s="116"/>
-      <c r="Z11" s="114" t="s">
+      <c r="V11" s="106"/>
+      <c r="W11" s="106"/>
+      <c r="X11" s="106"/>
+      <c r="Y11" s="107"/>
+      <c r="Z11" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="115"/>
-      <c r="AB11" s="115"/>
-      <c r="AC11" s="115"/>
-      <c r="AD11" s="116"/>
-      <c r="AE11" s="114" t="s">
+      <c r="AA11" s="106"/>
+      <c r="AB11" s="106"/>
+      <c r="AC11" s="106"/>
+      <c r="AD11" s="107"/>
+      <c r="AE11" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AF11" s="115"/>
-      <c r="AG11" s="115"/>
-      <c r="AH11" s="115"/>
-      <c r="AI11" s="116"/>
-      <c r="AJ11" s="117" t="s">
+      <c r="AF11" s="106"/>
+      <c r="AG11" s="106"/>
+      <c r="AH11" s="106"/>
+      <c r="AI11" s="107"/>
+      <c r="AJ11" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="118"/>
-      <c r="AL11" s="119"/>
+      <c r="AK11" s="109"/>
+      <c r="AL11" s="110"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="101"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="117"/>
       <c r="F12" s="47"/>
       <c r="G12" s="48"/>
       <c r="H12" s="48"/>
@@ -4071,11 +4078,11 @@
       <c r="AL12" s="52"/>
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A13" s="102"/>
-      <c r="B13" s="103"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
+      <c r="A13" s="118"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="120"/>
       <c r="F13" s="53"/>
       <c r="G13" s="54"/>
       <c r="H13" s="54"/>
@@ -4111,13 +4118,13 @@
       <c r="AL13" s="58"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A14" s="99" t="s">
+      <c r="A14" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="100"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="101"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="117"/>
       <c r="F14" s="47"/>
       <c r="G14" s="48"/>
       <c r="H14" s="48"/>
@@ -4153,11 +4160,11 @@
       <c r="AL14" s="52"/>
     </row>
     <row r="15" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A15" s="102"/>
-      <c r="B15" s="103"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="104"/>
+      <c r="A15" s="118"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="120"/>
       <c r="F15" s="53"/>
       <c r="G15" s="54"/>
       <c r="H15" s="54"/>
@@ -4193,13 +4200,13 @@
       <c r="AL15" s="58"/>
     </row>
     <row r="16" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="100"/>
-      <c r="C16" s="100"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="101"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="117"/>
       <c r="F16" s="47"/>
       <c r="G16" s="48"/>
       <c r="H16" s="48"/>
@@ -4235,11 +4242,11 @@
       <c r="AL16" s="52"/>
     </row>
     <row r="17" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="104"/>
+      <c r="A17" s="118"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="120"/>
       <c r="F17" s="53"/>
       <c r="G17" s="54"/>
       <c r="H17" s="54"/>
@@ -4275,13 +4282,13 @@
       <c r="AL17" s="58"/>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="115" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="100"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="101"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="117"/>
       <c r="F18" s="47"/>
       <c r="G18" s="48"/>
       <c r="H18" s="48"/>
@@ -4317,11 +4324,11 @@
       <c r="AL18" s="52"/>
     </row>
     <row r="19" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="104"/>
+      <c r="A19" s="118"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="120"/>
       <c r="F19" s="53"/>
       <c r="G19" s="54"/>
       <c r="H19" s="54"/>
@@ -4357,13 +4364,13 @@
       <c r="AL19" s="58"/>
     </row>
     <row r="20" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A20" s="99" t="s">
+      <c r="A20" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="100"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="101"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="117"/>
       <c r="F20" s="47"/>
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
@@ -4399,11 +4406,11 @@
       <c r="AL20" s="52"/>
     </row>
     <row r="21" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="104"/>
+      <c r="A21" s="118"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="120"/>
       <c r="F21" s="53"/>
       <c r="G21" s="54"/>
       <c r="H21" s="54"/>
@@ -4439,13 +4446,13 @@
       <c r="AL21" s="58"/>
     </row>
     <row r="22" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A22" s="99" t="s">
+      <c r="A22" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="100"/>
-      <c r="C22" s="100"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="101"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="117"/>
       <c r="F22" s="47"/>
       <c r="G22" s="48"/>
       <c r="H22" s="48"/>
@@ -4481,11 +4488,11 @@
       <c r="AL22" s="52"/>
     </row>
     <row r="23" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="104"/>
+      <c r="A23" s="118"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="120"/>
       <c r="F23" s="53"/>
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
@@ -4521,13 +4528,13 @@
       <c r="AL23" s="58"/>
     </row>
     <row r="24" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="115" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="101"/>
+      <c r="B24" s="116"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="117"/>
       <c r="F24" s="47"/>
       <c r="G24" s="48"/>
       <c r="H24" s="48"/>
@@ -4563,11 +4570,11 @@
       <c r="AL24" s="52"/>
     </row>
     <row r="25" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="104"/>
+      <c r="A25" s="118"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="120"/>
       <c r="F25" s="53"/>
       <c r="G25" s="54"/>
       <c r="H25" s="54"/>
@@ -4603,13 +4610,13 @@
       <c r="AL25" s="58"/>
     </row>
     <row r="26" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A26" s="99" t="s">
+      <c r="A26" s="115" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="101"/>
+      <c r="B26" s="116"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="117"/>
       <c r="F26" s="47"/>
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
@@ -4645,11 +4652,11 @@
       <c r="AL26" s="52"/>
     </row>
     <row r="27" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="104"/>
+      <c r="A27" s="118"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="120"/>
       <c r="F27" s="53"/>
       <c r="G27" s="54"/>
       <c r="H27" s="54"/>
@@ -4685,13 +4692,13 @@
       <c r="AL27" s="58"/>
     </row>
     <row r="28" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="B28" s="100"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="101"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="117"/>
       <c r="F28" s="47"/>
       <c r="G28" s="48"/>
       <c r="H28" s="48"/>
@@ -4727,11 +4734,11 @@
       <c r="AL28" s="52"/>
     </row>
     <row r="29" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="103"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="104"/>
+      <c r="A29" s="118"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="120"/>
       <c r="F29" s="53"/>
       <c r="G29" s="54"/>
       <c r="H29" s="54"/>
@@ -4767,13 +4774,13 @@
       <c r="AL29" s="58"/>
     </row>
     <row r="30" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A30" s="99" t="s">
+      <c r="A30" s="115" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="100"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="101"/>
+      <c r="B30" s="116"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="117"/>
       <c r="F30" s="47"/>
       <c r="G30" s="48"/>
       <c r="H30" s="48"/>
@@ -4809,11 +4816,11 @@
       <c r="AL30" s="52"/>
     </row>
     <row r="31" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="103"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="104"/>
+      <c r="A31" s="118"/>
+      <c r="B31" s="119"/>
+      <c r="C31" s="119"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="120"/>
       <c r="F31" s="53"/>
       <c r="G31" s="54"/>
       <c r="H31" s="54"/>
@@ -4849,13 +4856,13 @@
       <c r="AL31" s="58"/>
     </row>
     <row r="32" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A32" s="99" t="s">
+      <c r="A32" s="115" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="100"/>
-      <c r="C32" s="100"/>
-      <c r="D32" s="100"/>
-      <c r="E32" s="100"/>
+      <c r="B32" s="116"/>
+      <c r="C32" s="116"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="116"/>
       <c r="F32" s="47"/>
       <c r="G32" s="48"/>
       <c r="H32" s="48"/>
@@ -4891,11 +4898,11 @@
       <c r="AL32" s="52"/>
     </row>
     <row r="33" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A33" s="102"/>
-      <c r="B33" s="103"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
+      <c r="A33" s="118"/>
+      <c r="B33" s="119"/>
+      <c r="C33" s="119"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
       <c r="F33" s="53"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
@@ -4931,13 +4938,13 @@
       <c r="AL33" s="58"/>
     </row>
     <row r="34" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A34" s="99" t="s">
+      <c r="A34" s="115" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
+      <c r="B34" s="116"/>
+      <c r="C34" s="116"/>
+      <c r="D34" s="116"/>
+      <c r="E34" s="116"/>
       <c r="F34" s="47"/>
       <c r="G34" s="48"/>
       <c r="H34" s="48"/>
@@ -4973,11 +4980,11 @@
       <c r="AL34" s="52"/>
     </row>
     <row r="35" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A35" s="102"/>
-      <c r="B35" s="103"/>
-      <c r="C35" s="103"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="104"/>
+      <c r="A35" s="118"/>
+      <c r="B35" s="119"/>
+      <c r="C35" s="119"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="120"/>
       <c r="F35" s="53"/>
       <c r="G35" s="54"/>
       <c r="H35" s="54"/>
@@ -5013,13 +5020,13 @@
       <c r="AL35" s="58"/>
     </row>
     <row r="36" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A36" s="105" t="s">
+      <c r="A36" s="121" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="106"/>
-      <c r="C36" s="106"/>
-      <c r="D36" s="106"/>
-      <c r="E36" s="107"/>
+      <c r="B36" s="122"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="123"/>
       <c r="F36" s="47"/>
       <c r="G36" s="48"/>
       <c r="H36" s="48"/>
@@ -5055,11 +5062,11 @@
       <c r="AL36" s="52"/>
     </row>
     <row r="37" spans="1:38" ht="9.75" customHeight="1">
-      <c r="A37" s="108"/>
-      <c r="B37" s="109"/>
-      <c r="C37" s="109"/>
-      <c r="D37" s="109"/>
-      <c r="E37" s="110"/>
+      <c r="A37" s="124"/>
+      <c r="B37" s="125"/>
+      <c r="C37" s="125"/>
+      <c r="D37" s="125"/>
+      <c r="E37" s="126"/>
       <c r="F37" s="53"/>
       <c r="G37" s="54"/>
       <c r="H37" s="54"/>
@@ -5128,21 +5135,21 @@
       <c r="AF38" s="39"/>
     </row>
     <row r="39" spans="1:38">
-      <c r="A39" s="111" t="s">
+      <c r="A39" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="111"/>
-      <c r="C39" s="111"/>
-      <c r="D39" s="112" t="s">
+      <c r="B39" s="127"/>
+      <c r="C39" s="127"/>
+      <c r="D39" s="128" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="112"/>
-      <c r="F39" s="112"/>
-      <c r="G39" s="112"/>
-      <c r="H39" s="112"/>
-      <c r="I39" s="112"/>
-      <c r="J39" s="112"/>
-      <c r="K39" s="112"/>
+      <c r="E39" s="128"/>
+      <c r="F39" s="128"/>
+      <c r="G39" s="128"/>
+      <c r="H39" s="128"/>
+      <c r="I39" s="128"/>
+      <c r="J39" s="128"/>
+      <c r="K39" s="128"/>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
       <c r="N39" s="39"/>
@@ -5166,19 +5173,19 @@
       <c r="AF39" s="39"/>
     </row>
     <row r="40" spans="1:38">
-      <c r="A40" s="111"/>
-      <c r="B40" s="111"/>
-      <c r="C40" s="111"/>
-      <c r="D40" s="113" t="s">
+      <c r="A40" s="127"/>
+      <c r="B40" s="127"/>
+      <c r="C40" s="127"/>
+      <c r="D40" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="E40" s="113"/>
-      <c r="F40" s="113"/>
-      <c r="G40" s="113"/>
-      <c r="H40" s="113"/>
-      <c r="I40" s="113"/>
-      <c r="J40" s="113"/>
-      <c r="K40" s="113"/>
+      <c r="E40" s="129"/>
+      <c r="F40" s="129"/>
+      <c r="G40" s="129"/>
+      <c r="H40" s="129"/>
+      <c r="I40" s="129"/>
+      <c r="J40" s="129"/>
+      <c r="K40" s="129"/>
       <c r="L40" s="39"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
@@ -5397,13 +5404,13 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="AE11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="P10:AL10"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="A32:E33"/>
+    <mergeCell ref="A34:E35"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:K39"/>
+    <mergeCell ref="D40:K40"/>
     <mergeCell ref="A12:E13"/>
     <mergeCell ref="A14:E15"/>
     <mergeCell ref="A16:E17"/>
@@ -5418,15 +5425,15 @@
     <mergeCell ref="K11:O11"/>
     <mergeCell ref="P11:T11"/>
     <mergeCell ref="U11:Y11"/>
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="A32:E33"/>
-    <mergeCell ref="A34:E35"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="AE11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="P10:AL10"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -5464,32 +5471,32 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="128"/>
-      <c r="T1" s="128"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="128"/>
-      <c r="W1" s="128"/>
-      <c r="X1" s="128"/>
-      <c r="Y1" s="128"/>
-      <c r="Z1" s="128"/>
-      <c r="AA1" s="128"/>
-      <c r="AB1" s="128"/>
-      <c r="AC1" s="128"/>
-      <c r="AD1" s="128"/>
-      <c r="AE1" s="128"/>
-      <c r="AF1" s="128"/>
-      <c r="AG1" s="128"/>
-      <c r="AH1" s="128"/>
-      <c r="AI1" s="128"/>
-      <c r="AJ1" s="128"/>
-      <c r="AK1" s="128"/>
-      <c r="AL1" s="128"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="134"/>
+      <c r="AD1" s="134"/>
+      <c r="AE1" s="134"/>
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="134"/>
+      <c r="AJ1" s="134"/>
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5528,20 +5535,20 @@
       <c r="A3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-      <c r="R3" s="129"/>
-      <c r="S3" s="129"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="135"/>
+      <c r="O3" s="135"/>
+      <c r="P3" s="135"/>
+      <c r="Q3" s="135"/>
+      <c r="R3" s="135"/>
+      <c r="S3" s="135"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -5559,13 +5566,13 @@
       <c r="A4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -5631,238 +5638,238 @@
       <c r="AL5" s="1"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="131" t="s">
+      <c r="A6" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="131"/>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="126" t="s">
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="126"/>
-      <c r="L6" s="127" t="s">
+      <c r="I6" s="137"/>
+      <c r="J6" s="137"/>
+      <c r="K6" s="137"/>
+      <c r="L6" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="127"/>
-      <c r="N6" s="127"/>
-      <c r="O6" s="127"/>
-      <c r="P6" s="127"/>
-      <c r="Q6" s="127"/>
-      <c r="R6" s="127"/>
-      <c r="S6" s="127"/>
-      <c r="T6" s="127"/>
-      <c r="U6" s="127"/>
-      <c r="V6" s="127"/>
-      <c r="W6" s="127"/>
-      <c r="X6" s="126" t="s">
+      <c r="M6" s="138"/>
+      <c r="N6" s="138"/>
+      <c r="O6" s="138"/>
+      <c r="P6" s="138"/>
+      <c r="Q6" s="138"/>
+      <c r="R6" s="138"/>
+      <c r="S6" s="138"/>
+      <c r="T6" s="138"/>
+      <c r="U6" s="138"/>
+      <c r="V6" s="138"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="Y6" s="126"/>
-      <c r="Z6" s="126"/>
-      <c r="AA6" s="126"/>
-      <c r="AB6" s="127" t="s">
+      <c r="Y6" s="137"/>
+      <c r="Z6" s="137"/>
+      <c r="AA6" s="137"/>
+      <c r="AB6" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="AC6" s="127"/>
-      <c r="AD6" s="127"/>
-      <c r="AE6" s="127"/>
-      <c r="AF6" s="127"/>
-      <c r="AG6" s="127"/>
-      <c r="AH6" s="127"/>
-      <c r="AI6" s="127"/>
-      <c r="AJ6" s="127"/>
-      <c r="AK6" s="127"/>
-      <c r="AL6" s="127"/>
+      <c r="AC6" s="138"/>
+      <c r="AD6" s="138"/>
+      <c r="AE6" s="138"/>
+      <c r="AF6" s="138"/>
+      <c r="AG6" s="138"/>
+      <c r="AH6" s="138"/>
+      <c r="AI6" s="138"/>
+      <c r="AJ6" s="138"/>
+      <c r="AK6" s="138"/>
+      <c r="AL6" s="138"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
-      <c r="A7" s="131"/>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126"/>
-      <c r="K7" s="126"/>
-      <c r="L7" s="127" t="s">
+      <c r="A7" s="133"/>
+      <c r="B7" s="133"/>
+      <c r="C7" s="133"/>
+      <c r="D7" s="133"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="137"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="127"/>
-      <c r="N7" s="127"/>
-      <c r="O7" s="127"/>
-      <c r="P7" s="127" t="s">
+      <c r="M7" s="138"/>
+      <c r="N7" s="138"/>
+      <c r="O7" s="138"/>
+      <c r="P7" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="127"/>
-      <c r="S7" s="127"/>
-      <c r="T7" s="127" t="s">
+      <c r="Q7" s="138"/>
+      <c r="R7" s="138"/>
+      <c r="S7" s="138"/>
+      <c r="T7" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="U7" s="127"/>
-      <c r="V7" s="127"/>
-      <c r="W7" s="127"/>
-      <c r="X7" s="126"/>
-      <c r="Y7" s="126"/>
-      <c r="Z7" s="126"/>
-      <c r="AA7" s="126"/>
-      <c r="AB7" s="127" t="s">
+      <c r="U7" s="138"/>
+      <c r="V7" s="138"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="137"/>
+      <c r="Y7" s="137"/>
+      <c r="Z7" s="137"/>
+      <c r="AA7" s="137"/>
+      <c r="AB7" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="AC7" s="127"/>
-      <c r="AD7" s="127"/>
-      <c r="AE7" s="127"/>
-      <c r="AF7" s="127" t="s">
+      <c r="AC7" s="138"/>
+      <c r="AD7" s="138"/>
+      <c r="AE7" s="138"/>
+      <c r="AF7" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="AG7" s="127"/>
-      <c r="AH7" s="127"/>
-      <c r="AI7" s="127"/>
-      <c r="AJ7" s="127" t="s">
+      <c r="AG7" s="138"/>
+      <c r="AH7" s="138"/>
+      <c r="AI7" s="138"/>
+      <c r="AJ7" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="AK7" s="127"/>
-      <c r="AL7" s="127"/>
+      <c r="AK7" s="138"/>
+      <c r="AL7" s="138"/>
     </row>
     <row r="8" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A8" s="132"/>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="125">
+      <c r="A8" s="130"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="131">
         <v>125</v>
       </c>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="125"/>
-      <c r="L8" s="124"/>
-      <c r="M8" s="124"/>
-      <c r="N8" s="124"/>
-      <c r="O8" s="124"/>
-      <c r="P8" s="124"/>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="124"/>
-      <c r="T8" s="124"/>
-      <c r="U8" s="124"/>
-      <c r="V8" s="124"/>
-      <c r="W8" s="124"/>
-      <c r="X8" s="125">
+      <c r="I8" s="131"/>
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="132"/>
+      <c r="M8" s="132"/>
+      <c r="N8" s="132"/>
+      <c r="O8" s="132"/>
+      <c r="P8" s="132"/>
+      <c r="Q8" s="132"/>
+      <c r="R8" s="132"/>
+      <c r="S8" s="132"/>
+      <c r="T8" s="132"/>
+      <c r="U8" s="132"/>
+      <c r="V8" s="132"/>
+      <c r="W8" s="132"/>
+      <c r="X8" s="131">
         <v>2000</v>
       </c>
-      <c r="Y8" s="125"/>
-      <c r="Z8" s="125"/>
-      <c r="AA8" s="125"/>
-      <c r="AB8" s="124"/>
-      <c r="AC8" s="124"/>
-      <c r="AD8" s="124"/>
-      <c r="AE8" s="124"/>
-      <c r="AF8" s="124"/>
-      <c r="AG8" s="124"/>
-      <c r="AH8" s="124"/>
-      <c r="AI8" s="124"/>
-      <c r="AJ8" s="124"/>
-      <c r="AK8" s="124"/>
-      <c r="AL8" s="124"/>
+      <c r="Y8" s="131"/>
+      <c r="Z8" s="131"/>
+      <c r="AA8" s="131"/>
+      <c r="AB8" s="132"/>
+      <c r="AC8" s="132"/>
+      <c r="AD8" s="132"/>
+      <c r="AE8" s="132"/>
+      <c r="AF8" s="132"/>
+      <c r="AG8" s="132"/>
+      <c r="AH8" s="132"/>
+      <c r="AI8" s="132"/>
+      <c r="AJ8" s="132"/>
+      <c r="AK8" s="132"/>
+      <c r="AL8" s="132"/>
     </row>
     <row r="9" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A9" s="132"/>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="125">
+      <c r="A9" s="130"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="131">
         <v>500</v>
       </c>
-      <c r="I9" s="125"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="125"/>
-      <c r="L9" s="124"/>
-      <c r="M9" s="124"/>
-      <c r="N9" s="124"/>
-      <c r="O9" s="124"/>
-      <c r="P9" s="124"/>
-      <c r="Q9" s="124"/>
-      <c r="R9" s="124"/>
-      <c r="S9" s="124"/>
-      <c r="T9" s="124"/>
-      <c r="U9" s="124"/>
-      <c r="V9" s="124"/>
-      <c r="W9" s="124"/>
-      <c r="X9" s="125">
+      <c r="I9" s="131"/>
+      <c r="J9" s="131"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="132"/>
+      <c r="N9" s="132"/>
+      <c r="O9" s="132"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="132"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="132"/>
+      <c r="T9" s="132"/>
+      <c r="U9" s="132"/>
+      <c r="V9" s="132"/>
+      <c r="W9" s="132"/>
+      <c r="X9" s="131">
         <v>5000</v>
       </c>
-      <c r="Y9" s="125"/>
-      <c r="Z9" s="125"/>
-      <c r="AA9" s="125"/>
-      <c r="AB9" s="124"/>
-      <c r="AC9" s="124"/>
-      <c r="AD9" s="124"/>
-      <c r="AE9" s="124"/>
-      <c r="AF9" s="124"/>
-      <c r="AG9" s="124"/>
-      <c r="AH9" s="124"/>
-      <c r="AI9" s="124"/>
-      <c r="AJ9" s="124"/>
-      <c r="AK9" s="124"/>
-      <c r="AL9" s="124"/>
+      <c r="Y9" s="131"/>
+      <c r="Z9" s="131"/>
+      <c r="AA9" s="131"/>
+      <c r="AB9" s="132"/>
+      <c r="AC9" s="132"/>
+      <c r="AD9" s="132"/>
+      <c r="AE9" s="132"/>
+      <c r="AF9" s="132"/>
+      <c r="AG9" s="132"/>
+      <c r="AH9" s="132"/>
+      <c r="AI9" s="132"/>
+      <c r="AJ9" s="132"/>
+      <c r="AK9" s="132"/>
+      <c r="AL9" s="132"/>
     </row>
     <row r="10" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A10" s="132"/>
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="125">
+      <c r="A10" s="130"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="130"/>
+      <c r="H10" s="131">
         <v>1000</v>
       </c>
-      <c r="I10" s="125"/>
-      <c r="J10" s="125"/>
-      <c r="K10" s="125"/>
-      <c r="L10" s="124"/>
-      <c r="M10" s="124"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="124"/>
-      <c r="P10" s="124"/>
-      <c r="Q10" s="124"/>
-      <c r="R10" s="124"/>
-      <c r="S10" s="124"/>
-      <c r="T10" s="124"/>
-      <c r="U10" s="124"/>
-      <c r="V10" s="124"/>
-      <c r="W10" s="124"/>
-      <c r="X10" s="125">
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="132"/>
+      <c r="M10" s="132"/>
+      <c r="N10" s="132"/>
+      <c r="O10" s="132"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
+      <c r="R10" s="132"/>
+      <c r="S10" s="132"/>
+      <c r="T10" s="132"/>
+      <c r="U10" s="132"/>
+      <c r="V10" s="132"/>
+      <c r="W10" s="132"/>
+      <c r="X10" s="131">
         <v>7000</v>
       </c>
-      <c r="Y10" s="125"/>
-      <c r="Z10" s="125"/>
-      <c r="AA10" s="125"/>
-      <c r="AB10" s="124"/>
-      <c r="AC10" s="124"/>
-      <c r="AD10" s="124"/>
-      <c r="AE10" s="124"/>
-      <c r="AF10" s="124"/>
-      <c r="AG10" s="124"/>
-      <c r="AH10" s="124"/>
-      <c r="AI10" s="124"/>
-      <c r="AJ10" s="124"/>
-      <c r="AK10" s="124"/>
-      <c r="AL10" s="124"/>
+      <c r="Y10" s="131"/>
+      <c r="Z10" s="131"/>
+      <c r="AA10" s="131"/>
+      <c r="AB10" s="132"/>
+      <c r="AC10" s="132"/>
+      <c r="AD10" s="132"/>
+      <c r="AE10" s="132"/>
+      <c r="AF10" s="132"/>
+      <c r="AG10" s="132"/>
+      <c r="AH10" s="132"/>
+      <c r="AI10" s="132"/>
+      <c r="AJ10" s="132"/>
+      <c r="AK10" s="132"/>
+      <c r="AL10" s="132"/>
     </row>
     <row r="11" spans="1:38" ht="21.15" customHeight="1">
       <c r="A11" s="28"/>
@@ -5941,238 +5948,238 @@
       <c r="AL12" s="1"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1">
-      <c r="A13" s="131" t="s">
+      <c r="A13" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="131"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="126" t="s">
+      <c r="B13" s="133"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="126"/>
-      <c r="L13" s="127" t="s">
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="137"/>
+      <c r="L13" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="127"/>
-      <c r="N13" s="127"/>
-      <c r="O13" s="127"/>
-      <c r="P13" s="127"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="127"/>
-      <c r="S13" s="127"/>
-      <c r="T13" s="127"/>
-      <c r="U13" s="127"/>
-      <c r="V13" s="127"/>
-      <c r="W13" s="127"/>
-      <c r="X13" s="126" t="s">
+      <c r="M13" s="138"/>
+      <c r="N13" s="138"/>
+      <c r="O13" s="138"/>
+      <c r="P13" s="138"/>
+      <c r="Q13" s="138"/>
+      <c r="R13" s="138"/>
+      <c r="S13" s="138"/>
+      <c r="T13" s="138"/>
+      <c r="U13" s="138"/>
+      <c r="V13" s="138"/>
+      <c r="W13" s="138"/>
+      <c r="X13" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="Y13" s="126"/>
-      <c r="Z13" s="126"/>
-      <c r="AA13" s="126"/>
-      <c r="AB13" s="127" t="s">
+      <c r="Y13" s="137"/>
+      <c r="Z13" s="137"/>
+      <c r="AA13" s="137"/>
+      <c r="AB13" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="AC13" s="127"/>
-      <c r="AD13" s="127"/>
-      <c r="AE13" s="127"/>
-      <c r="AF13" s="127"/>
-      <c r="AG13" s="127"/>
-      <c r="AH13" s="127"/>
-      <c r="AI13" s="127"/>
-      <c r="AJ13" s="127"/>
-      <c r="AK13" s="127"/>
-      <c r="AL13" s="127"/>
+      <c r="AC13" s="138"/>
+      <c r="AD13" s="138"/>
+      <c r="AE13" s="138"/>
+      <c r="AF13" s="138"/>
+      <c r="AG13" s="138"/>
+      <c r="AH13" s="138"/>
+      <c r="AI13" s="138"/>
+      <c r="AJ13" s="138"/>
+      <c r="AK13" s="138"/>
+      <c r="AL13" s="138"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1">
-      <c r="A14" s="131"/>
-      <c r="B14" s="131"/>
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
-      <c r="F14" s="131"/>
-      <c r="G14" s="131"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
-      <c r="K14" s="126"/>
-      <c r="L14" s="127" t="s">
+      <c r="A14" s="133"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="137"/>
+      <c r="K14" s="137"/>
+      <c r="L14" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="M14" s="127"/>
-      <c r="N14" s="127"/>
-      <c r="O14" s="127"/>
-      <c r="P14" s="127" t="s">
+      <c r="M14" s="138"/>
+      <c r="N14" s="138"/>
+      <c r="O14" s="138"/>
+      <c r="P14" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="Q14" s="127"/>
-      <c r="R14" s="127"/>
-      <c r="S14" s="127"/>
-      <c r="T14" s="127" t="s">
+      <c r="Q14" s="138"/>
+      <c r="R14" s="138"/>
+      <c r="S14" s="138"/>
+      <c r="T14" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="U14" s="127"/>
-      <c r="V14" s="127"/>
-      <c r="W14" s="127"/>
-      <c r="X14" s="126"/>
-      <c r="Y14" s="126"/>
-      <c r="Z14" s="126"/>
-      <c r="AA14" s="126"/>
-      <c r="AB14" s="127" t="s">
+      <c r="U14" s="138"/>
+      <c r="V14" s="138"/>
+      <c r="W14" s="138"/>
+      <c r="X14" s="137"/>
+      <c r="Y14" s="137"/>
+      <c r="Z14" s="137"/>
+      <c r="AA14" s="137"/>
+      <c r="AB14" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="AC14" s="127"/>
-      <c r="AD14" s="127"/>
-      <c r="AE14" s="127"/>
-      <c r="AF14" s="127" t="s">
+      <c r="AC14" s="138"/>
+      <c r="AD14" s="138"/>
+      <c r="AE14" s="138"/>
+      <c r="AF14" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="AG14" s="127"/>
-      <c r="AH14" s="127"/>
-      <c r="AI14" s="127"/>
-      <c r="AJ14" s="127" t="s">
+      <c r="AG14" s="138"/>
+      <c r="AH14" s="138"/>
+      <c r="AI14" s="138"/>
+      <c r="AJ14" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="AK14" s="127"/>
-      <c r="AL14" s="127"/>
+      <c r="AK14" s="138"/>
+      <c r="AL14" s="138"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1">
-      <c r="A15" s="132"/>
-      <c r="B15" s="132"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="125">
+      <c r="A15" s="130"/>
+      <c r="B15" s="130"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="131">
         <v>125</v>
       </c>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="124"/>
-      <c r="O15" s="124"/>
-      <c r="P15" s="124"/>
-      <c r="Q15" s="124"/>
-      <c r="R15" s="124"/>
-      <c r="S15" s="124"/>
-      <c r="T15" s="124"/>
-      <c r="U15" s="124"/>
-      <c r="V15" s="124"/>
-      <c r="W15" s="124"/>
-      <c r="X15" s="125">
+      <c r="I15" s="131"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="132"/>
+      <c r="N15" s="132"/>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="132"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="132"/>
+      <c r="T15" s="132"/>
+      <c r="U15" s="132"/>
+      <c r="V15" s="132"/>
+      <c r="W15" s="132"/>
+      <c r="X15" s="131">
         <v>2000</v>
       </c>
-      <c r="Y15" s="125"/>
-      <c r="Z15" s="125"/>
-      <c r="AA15" s="125"/>
-      <c r="AB15" s="124"/>
-      <c r="AC15" s="124"/>
-      <c r="AD15" s="124"/>
-      <c r="AE15" s="124"/>
-      <c r="AF15" s="124"/>
-      <c r="AG15" s="124"/>
-      <c r="AH15" s="124"/>
-      <c r="AI15" s="124"/>
-      <c r="AJ15" s="124"/>
-      <c r="AK15" s="124"/>
-      <c r="AL15" s="124"/>
+      <c r="Y15" s="131"/>
+      <c r="Z15" s="131"/>
+      <c r="AA15" s="131"/>
+      <c r="AB15" s="132"/>
+      <c r="AC15" s="132"/>
+      <c r="AD15" s="132"/>
+      <c r="AE15" s="132"/>
+      <c r="AF15" s="132"/>
+      <c r="AG15" s="132"/>
+      <c r="AH15" s="132"/>
+      <c r="AI15" s="132"/>
+      <c r="AJ15" s="132"/>
+      <c r="AK15" s="132"/>
+      <c r="AL15" s="132"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1">
-      <c r="A16" s="132"/>
-      <c r="B16" s="132"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="125">
+      <c r="A16" s="130"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="130"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="131">
         <v>500</v>
       </c>
-      <c r="I16" s="125"/>
-      <c r="J16" s="125"/>
-      <c r="K16" s="125"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="124"/>
-      <c r="P16" s="124"/>
-      <c r="Q16" s="124"/>
-      <c r="R16" s="124"/>
-      <c r="S16" s="124"/>
-      <c r="T16" s="124"/>
-      <c r="U16" s="124"/>
-      <c r="V16" s="124"/>
-      <c r="W16" s="124"/>
-      <c r="X16" s="125">
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="132"/>
+      <c r="M16" s="132"/>
+      <c r="N16" s="132"/>
+      <c r="O16" s="132"/>
+      <c r="P16" s="132"/>
+      <c r="Q16" s="132"/>
+      <c r="R16" s="132"/>
+      <c r="S16" s="132"/>
+      <c r="T16" s="132"/>
+      <c r="U16" s="132"/>
+      <c r="V16" s="132"/>
+      <c r="W16" s="132"/>
+      <c r="X16" s="131">
         <v>5000</v>
       </c>
-      <c r="Y16" s="125"/>
-      <c r="Z16" s="125"/>
-      <c r="AA16" s="125"/>
-      <c r="AB16" s="124"/>
-      <c r="AC16" s="124"/>
-      <c r="AD16" s="124"/>
-      <c r="AE16" s="124"/>
-      <c r="AF16" s="124"/>
-      <c r="AG16" s="124"/>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="124"/>
-      <c r="AJ16" s="124"/>
-      <c r="AK16" s="124"/>
-      <c r="AL16" s="124"/>
+      <c r="Y16" s="131"/>
+      <c r="Z16" s="131"/>
+      <c r="AA16" s="131"/>
+      <c r="AB16" s="132"/>
+      <c r="AC16" s="132"/>
+      <c r="AD16" s="132"/>
+      <c r="AE16" s="132"/>
+      <c r="AF16" s="132"/>
+      <c r="AG16" s="132"/>
+      <c r="AH16" s="132"/>
+      <c r="AI16" s="132"/>
+      <c r="AJ16" s="132"/>
+      <c r="AK16" s="132"/>
+      <c r="AL16" s="132"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
-      <c r="A17" s="132"/>
-      <c r="B17" s="132"/>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
-      <c r="H17" s="125">
+      <c r="A17" s="130"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="131">
         <v>1000</v>
       </c>
-      <c r="I17" s="125"/>
-      <c r="J17" s="125"/>
-      <c r="K17" s="125"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
-      <c r="U17" s="124"/>
-      <c r="V17" s="124"/>
-      <c r="W17" s="124"/>
-      <c r="X17" s="125">
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
+      <c r="L17" s="132"/>
+      <c r="M17" s="132"/>
+      <c r="N17" s="132"/>
+      <c r="O17" s="132"/>
+      <c r="P17" s="132"/>
+      <c r="Q17" s="132"/>
+      <c r="R17" s="132"/>
+      <c r="S17" s="132"/>
+      <c r="T17" s="132"/>
+      <c r="U17" s="132"/>
+      <c r="V17" s="132"/>
+      <c r="W17" s="132"/>
+      <c r="X17" s="131">
         <v>7000</v>
       </c>
-      <c r="Y17" s="125"/>
-      <c r="Z17" s="125"/>
-      <c r="AA17" s="125"/>
-      <c r="AB17" s="124"/>
-      <c r="AC17" s="124"/>
-      <c r="AD17" s="124"/>
-      <c r="AE17" s="124"/>
-      <c r="AF17" s="124"/>
-      <c r="AG17" s="124"/>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="124"/>
-      <c r="AJ17" s="124"/>
-      <c r="AK17" s="124"/>
-      <c r="AL17" s="124"/>
+      <c r="Y17" s="131"/>
+      <c r="Z17" s="131"/>
+      <c r="AA17" s="131"/>
+      <c r="AB17" s="132"/>
+      <c r="AC17" s="132"/>
+      <c r="AD17" s="132"/>
+      <c r="AE17" s="132"/>
+      <c r="AF17" s="132"/>
+      <c r="AG17" s="132"/>
+      <c r="AH17" s="132"/>
+      <c r="AI17" s="132"/>
+      <c r="AJ17" s="132"/>
+      <c r="AK17" s="132"/>
+      <c r="AL17" s="132"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1">
       <c r="A18" s="28"/>
@@ -7622,6 +7629,65 @@
     </row>
   </sheetData>
   <mergeCells count="75">
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AB15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="X16:AA16"/>
+    <mergeCell ref="AB16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="AJ16:AL16"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="L10:O10"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="X15:AA15"/>
+    <mergeCell ref="H13:K14"/>
+    <mergeCell ref="L13:W13"/>
+    <mergeCell ref="X13:AA14"/>
+    <mergeCell ref="AB13:AL13"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="AB14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="AB8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="AB10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="L9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="F3:S3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A6:G7"/>
+    <mergeCell ref="H6:K7"/>
+    <mergeCell ref="L6:W6"/>
+    <mergeCell ref="X6:AA7"/>
+    <mergeCell ref="AB6:AL6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="P7:S7"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="AB7:AE7"/>
+    <mergeCell ref="AF7:AI7"/>
+    <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="A8:G10"/>
     <mergeCell ref="A15:G17"/>
     <mergeCell ref="H15:K15"/>
@@ -7638,67 +7704,8 @@
     <mergeCell ref="L8:O8"/>
     <mergeCell ref="P8:S8"/>
     <mergeCell ref="A13:G14"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="F3:S3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A6:G7"/>
-    <mergeCell ref="H6:K7"/>
-    <mergeCell ref="L6:W6"/>
-    <mergeCell ref="X6:AA7"/>
-    <mergeCell ref="AB6:AL6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="P7:S7"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="AB7:AE7"/>
-    <mergeCell ref="AF7:AI7"/>
-    <mergeCell ref="AJ7:AL7"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="L9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AB10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="AB13:AL13"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="AB14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L10:O10"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X10:AA10"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="X15:AA15"/>
-    <mergeCell ref="H13:K14"/>
-    <mergeCell ref="L13:W13"/>
-    <mergeCell ref="X13:AA14"/>
-    <mergeCell ref="AB15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="AJ15:AL15"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="X16:AA16"/>
-    <mergeCell ref="AB16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -7736,32 +7743,32 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="128"/>
-      <c r="T1" s="128"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="128"/>
-      <c r="W1" s="128"/>
-      <c r="X1" s="128"/>
-      <c r="Y1" s="128"/>
-      <c r="Z1" s="128"/>
-      <c r="AA1" s="128"/>
-      <c r="AB1" s="128"/>
-      <c r="AC1" s="128"/>
-      <c r="AD1" s="128"/>
-      <c r="AE1" s="128"/>
-      <c r="AF1" s="128"/>
-      <c r="AG1" s="128"/>
-      <c r="AH1" s="128"/>
-      <c r="AI1" s="128"/>
-      <c r="AJ1" s="128"/>
-      <c r="AK1" s="128"/>
-      <c r="AL1" s="128"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="134"/>
+      <c r="AD1" s="134"/>
+      <c r="AE1" s="134"/>
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="134"/>
+      <c r="AJ1" s="134"/>
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
       <c r="AM1" s="20"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -7797,17 +7804,17 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
       <c r="L3" s="16"/>
       <c r="M3" s="16"/>
       <c r="N3" s="12" t="s">
@@ -7864,16 +7871,16 @@
       <c r="AF4" s="1"/>
     </row>
     <row r="5" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="133"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -10207,7 +10214,7 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:H5"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -10264,32 +10271,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="142"/>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="142"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="142"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="142"/>
-      <c r="AF1" s="142"/>
-      <c r="AG1" s="142"/>
-      <c r="AH1" s="142"/>
-      <c r="AI1" s="142"/>
-      <c r="AJ1" s="142"/>
-      <c r="AK1" s="142"/>
-      <c r="AL1" s="142"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="149"/>
+      <c r="Y1" s="149"/>
+      <c r="Z1" s="149"/>
+      <c r="AA1" s="149"/>
+      <c r="AB1" s="149"/>
+      <c r="AC1" s="149"/>
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="149"/>
+      <c r="AJ1" s="149"/>
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
       <c r="AM1" s="67"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -10333,17 +10340,17 @@
       <c r="AM2" s="67"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
+      <c r="A3" s="146"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -10363,11 +10370,11 @@
       <c r="Z3" s="38"/>
       <c r="AA3" s="74"/>
       <c r="AB3" s="34"/>
-      <c r="AC3" s="142"/>
-      <c r="AD3" s="142"/>
-      <c r="AE3" s="142"/>
-      <c r="AF3" s="142"/>
-      <c r="AG3" s="142"/>
+      <c r="AC3" s="149"/>
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="149"/>
+      <c r="AG3" s="149"/>
       <c r="AH3" s="34"/>
       <c r="AI3" s="34"/>
       <c r="AJ3" s="34"/>
@@ -10456,427 +10463,427 @@
       <c r="AM5" s="67"/>
     </row>
     <row r="6" spans="1:39" ht="15" customHeight="1">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="143" t="s">
         <v>160</v>
       </c>
-      <c r="B6" s="137"/>
-      <c r="C6" s="137"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="141" t="s">
+      <c r="B6" s="143"/>
+      <c r="C6" s="143"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="148" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="141"/>
-      <c r="G6" s="141"/>
-      <c r="H6" s="141"/>
-      <c r="I6" s="141"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="141"/>
-      <c r="L6" s="141" t="s">
+      <c r="F6" s="148"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="148"/>
+      <c r="L6" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="M6" s="141"/>
-      <c r="N6" s="141"/>
-      <c r="O6" s="141"/>
-      <c r="P6" s="141"/>
-      <c r="Q6" s="141"/>
-      <c r="R6" s="141"/>
-      <c r="S6" s="141" t="s">
+      <c r="M6" s="148"/>
+      <c r="N6" s="148"/>
+      <c r="O6" s="148"/>
+      <c r="P6" s="148"/>
+      <c r="Q6" s="148"/>
+      <c r="R6" s="148"/>
+      <c r="S6" s="148" t="s">
         <v>164</v>
       </c>
-      <c r="T6" s="141"/>
-      <c r="U6" s="141"/>
-      <c r="V6" s="141"/>
-      <c r="W6" s="141"/>
-      <c r="X6" s="141"/>
-      <c r="Y6" s="141"/>
-      <c r="Z6" s="141" t="s">
+      <c r="T6" s="148"/>
+      <c r="U6" s="148"/>
+      <c r="V6" s="148"/>
+      <c r="W6" s="148"/>
+      <c r="X6" s="148"/>
+      <c r="Y6" s="148"/>
+      <c r="Z6" s="148" t="s">
         <v>163</v>
       </c>
-      <c r="AA6" s="141"/>
-      <c r="AB6" s="141"/>
-      <c r="AC6" s="141"/>
-      <c r="AD6" s="141"/>
-      <c r="AE6" s="141"/>
-      <c r="AF6" s="141"/>
-      <c r="AG6" s="141" t="s">
+      <c r="AA6" s="148"/>
+      <c r="AB6" s="148"/>
+      <c r="AC6" s="148"/>
+      <c r="AD6" s="148"/>
+      <c r="AE6" s="148"/>
+      <c r="AF6" s="148"/>
+      <c r="AG6" s="148" t="s">
         <v>162</v>
       </c>
-      <c r="AH6" s="141"/>
-      <c r="AI6" s="141"/>
-      <c r="AJ6" s="141"/>
-      <c r="AK6" s="141"/>
-      <c r="AL6" s="141"/>
-      <c r="AM6" s="141"/>
+      <c r="AH6" s="148"/>
+      <c r="AI6" s="148"/>
+      <c r="AJ6" s="148"/>
+      <c r="AK6" s="148"/>
+      <c r="AL6" s="148"/>
+      <c r="AM6" s="148"/>
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="143" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="140"/>
-      <c r="N7" s="140"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="140"/>
-      <c r="S7" s="140"/>
-      <c r="T7" s="140"/>
-      <c r="U7" s="140"/>
-      <c r="V7" s="140"/>
-      <c r="W7" s="140"/>
-      <c r="X7" s="140"/>
-      <c r="Y7" s="140"/>
-      <c r="Z7" s="140"/>
-      <c r="AA7" s="140"/>
-      <c r="AB7" s="140"/>
-      <c r="AC7" s="140"/>
-      <c r="AD7" s="140"/>
-      <c r="AE7" s="140"/>
-      <c r="AF7" s="140"/>
-      <c r="AG7" s="140"/>
-      <c r="AH7" s="140"/>
-      <c r="AI7" s="140"/>
-      <c r="AJ7" s="140"/>
-      <c r="AK7" s="140"/>
-      <c r="AL7" s="140"/>
-      <c r="AM7" s="140"/>
+      <c r="B7" s="143"/>
+      <c r="C7" s="143"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="147"/>
+      <c r="U7" s="147"/>
+      <c r="V7" s="147"/>
+      <c r="W7" s="147"/>
+      <c r="X7" s="147"/>
+      <c r="Y7" s="147"/>
+      <c r="Z7" s="147"/>
+      <c r="AA7" s="147"/>
+      <c r="AB7" s="147"/>
+      <c r="AC7" s="147"/>
+      <c r="AD7" s="147"/>
+      <c r="AE7" s="147"/>
+      <c r="AF7" s="147"/>
+      <c r="AG7" s="147"/>
+      <c r="AH7" s="147"/>
+      <c r="AI7" s="147"/>
+      <c r="AJ7" s="147"/>
+      <c r="AK7" s="147"/>
+      <c r="AL7" s="147"/>
+      <c r="AM7" s="147"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="143" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="137"/>
-      <c r="C8" s="137"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="140"/>
-      <c r="S8" s="140"/>
-      <c r="T8" s="140"/>
-      <c r="U8" s="140"/>
-      <c r="V8" s="140"/>
-      <c r="W8" s="140"/>
-      <c r="X8" s="140"/>
-      <c r="Y8" s="140"/>
-      <c r="Z8" s="140"/>
-      <c r="AA8" s="140"/>
-      <c r="AB8" s="140"/>
-      <c r="AC8" s="140"/>
-      <c r="AD8" s="140"/>
-      <c r="AE8" s="140"/>
-      <c r="AF8" s="140"/>
-      <c r="AG8" s="140"/>
-      <c r="AH8" s="140"/>
-      <c r="AI8" s="140"/>
-      <c r="AJ8" s="140"/>
-      <c r="AK8" s="140"/>
-      <c r="AL8" s="140"/>
-      <c r="AM8" s="140"/>
+      <c r="B8" s="143"/>
+      <c r="C8" s="143"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="147"/>
+      <c r="H8" s="147"/>
+      <c r="I8" s="147"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="147"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="147"/>
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="147"/>
+      <c r="U8" s="147"/>
+      <c r="V8" s="147"/>
+      <c r="W8" s="147"/>
+      <c r="X8" s="147"/>
+      <c r="Y8" s="147"/>
+      <c r="Z8" s="147"/>
+      <c r="AA8" s="147"/>
+      <c r="AB8" s="147"/>
+      <c r="AC8" s="147"/>
+      <c r="AD8" s="147"/>
+      <c r="AE8" s="147"/>
+      <c r="AF8" s="147"/>
+      <c r="AG8" s="147"/>
+      <c r="AH8" s="147"/>
+      <c r="AI8" s="147"/>
+      <c r="AJ8" s="147"/>
+      <c r="AK8" s="147"/>
+      <c r="AL8" s="147"/>
+      <c r="AM8" s="147"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
-      <c r="A9" s="137" t="s">
+      <c r="A9" s="143" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="137"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="141" t="s">
+      <c r="B9" s="143"/>
+      <c r="C9" s="143"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="148" t="s">
         <v>166</v>
       </c>
-      <c r="F9" s="141"/>
-      <c r="G9" s="141"/>
-      <c r="H9" s="141"/>
-      <c r="I9" s="141"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="141"/>
-      <c r="L9" s="141" t="s">
+      <c r="F9" s="148"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="148"/>
+      <c r="I9" s="148"/>
+      <c r="J9" s="148"/>
+      <c r="K9" s="148"/>
+      <c r="L9" s="148" t="s">
         <v>167</v>
       </c>
-      <c r="M9" s="141"/>
-      <c r="N9" s="141"/>
-      <c r="O9" s="141"/>
-      <c r="P9" s="141"/>
-      <c r="Q9" s="141"/>
-      <c r="R9" s="141"/>
-      <c r="S9" s="141" t="s">
+      <c r="M9" s="148"/>
+      <c r="N9" s="148"/>
+      <c r="O9" s="148"/>
+      <c r="P9" s="148"/>
+      <c r="Q9" s="148"/>
+      <c r="R9" s="148"/>
+      <c r="S9" s="148" t="s">
         <v>168</v>
       </c>
-      <c r="T9" s="141"/>
-      <c r="U9" s="141"/>
-      <c r="V9" s="141"/>
-      <c r="W9" s="141"/>
-      <c r="X9" s="141"/>
-      <c r="Y9" s="141"/>
-      <c r="Z9" s="141" t="s">
+      <c r="T9" s="148"/>
+      <c r="U9" s="148"/>
+      <c r="V9" s="148"/>
+      <c r="W9" s="148"/>
+      <c r="X9" s="148"/>
+      <c r="Y9" s="148"/>
+      <c r="Z9" s="148" t="s">
         <v>169</v>
       </c>
-      <c r="AA9" s="141"/>
-      <c r="AB9" s="141"/>
-      <c r="AC9" s="141"/>
-      <c r="AD9" s="141"/>
-      <c r="AE9" s="141"/>
-      <c r="AF9" s="141"/>
-      <c r="AG9" s="141" t="s">
+      <c r="AA9" s="148"/>
+      <c r="AB9" s="148"/>
+      <c r="AC9" s="148"/>
+      <c r="AD9" s="148"/>
+      <c r="AE9" s="148"/>
+      <c r="AF9" s="148"/>
+      <c r="AG9" s="148" t="s">
         <v>170</v>
       </c>
-      <c r="AH9" s="141"/>
-      <c r="AI9" s="141"/>
-      <c r="AJ9" s="141"/>
-      <c r="AK9" s="141"/>
-      <c r="AL9" s="141"/>
-      <c r="AM9" s="141"/>
+      <c r="AH9" s="148"/>
+      <c r="AI9" s="148"/>
+      <c r="AJ9" s="148"/>
+      <c r="AK9" s="148"/>
+      <c r="AL9" s="148"/>
+      <c r="AM9" s="148"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="143" t="s">
         <v>158</v>
       </c>
-      <c r="B10" s="137"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="137"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="140"/>
-      <c r="T10" s="140"/>
-      <c r="U10" s="140"/>
-      <c r="V10" s="140"/>
-      <c r="W10" s="140"/>
-      <c r="X10" s="140"/>
-      <c r="Y10" s="140"/>
-      <c r="Z10" s="140"/>
-      <c r="AA10" s="140"/>
-      <c r="AB10" s="140"/>
-      <c r="AC10" s="140"/>
-      <c r="AD10" s="140"/>
-      <c r="AE10" s="140"/>
-      <c r="AF10" s="140"/>
-      <c r="AG10" s="140"/>
-      <c r="AH10" s="140"/>
-      <c r="AI10" s="140"/>
-      <c r="AJ10" s="140"/>
-      <c r="AK10" s="140"/>
-      <c r="AL10" s="140"/>
-      <c r="AM10" s="140"/>
+      <c r="B10" s="143"/>
+      <c r="C10" s="143"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="147"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="147"/>
+      <c r="H10" s="147"/>
+      <c r="I10" s="147"/>
+      <c r="J10" s="147"/>
+      <c r="K10" s="147"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="147"/>
+      <c r="N10" s="147"/>
+      <c r="O10" s="147"/>
+      <c r="P10" s="147"/>
+      <c r="Q10" s="147"/>
+      <c r="R10" s="147"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="147"/>
+      <c r="U10" s="147"/>
+      <c r="V10" s="147"/>
+      <c r="W10" s="147"/>
+      <c r="X10" s="147"/>
+      <c r="Y10" s="147"/>
+      <c r="Z10" s="147"/>
+      <c r="AA10" s="147"/>
+      <c r="AB10" s="147"/>
+      <c r="AC10" s="147"/>
+      <c r="AD10" s="147"/>
+      <c r="AE10" s="147"/>
+      <c r="AF10" s="147"/>
+      <c r="AG10" s="147"/>
+      <c r="AH10" s="147"/>
+      <c r="AI10" s="147"/>
+      <c r="AJ10" s="147"/>
+      <c r="AK10" s="147"/>
+      <c r="AL10" s="147"/>
+      <c r="AM10" s="147"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="143" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="140"/>
-      <c r="N11" s="140"/>
-      <c r="O11" s="140"/>
-      <c r="P11" s="140"/>
-      <c r="Q11" s="140"/>
-      <c r="R11" s="140"/>
-      <c r="S11" s="140"/>
-      <c r="T11" s="140"/>
-      <c r="U11" s="140"/>
-      <c r="V11" s="140"/>
-      <c r="W11" s="140"/>
-      <c r="X11" s="140"/>
-      <c r="Y11" s="140"/>
-      <c r="Z11" s="140"/>
-      <c r="AA11" s="140"/>
-      <c r="AB11" s="140"/>
-      <c r="AC11" s="140"/>
-      <c r="AD11" s="140"/>
-      <c r="AE11" s="140"/>
-      <c r="AF11" s="140"/>
-      <c r="AG11" s="140"/>
-      <c r="AH11" s="140"/>
-      <c r="AI11" s="140"/>
-      <c r="AJ11" s="140"/>
-      <c r="AK11" s="140"/>
-      <c r="AL11" s="140"/>
-      <c r="AM11" s="140"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="147"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="147"/>
+      <c r="O11" s="147"/>
+      <c r="P11" s="147"/>
+      <c r="Q11" s="147"/>
+      <c r="R11" s="147"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="147"/>
+      <c r="U11" s="147"/>
+      <c r="V11" s="147"/>
+      <c r="W11" s="147"/>
+      <c r="X11" s="147"/>
+      <c r="Y11" s="147"/>
+      <c r="Z11" s="147"/>
+      <c r="AA11" s="147"/>
+      <c r="AB11" s="147"/>
+      <c r="AC11" s="147"/>
+      <c r="AD11" s="147"/>
+      <c r="AE11" s="147"/>
+      <c r="AF11" s="147"/>
+      <c r="AG11" s="147"/>
+      <c r="AH11" s="147"/>
+      <c r="AI11" s="147"/>
+      <c r="AJ11" s="147"/>
+      <c r="AK11" s="147"/>
+      <c r="AL11" s="147"/>
+      <c r="AM11" s="147"/>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1">
-      <c r="A12" s="137" t="s">
+      <c r="A12" s="143" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="137"/>
-      <c r="C12" s="137"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="141" t="s">
+      <c r="B12" s="143"/>
+      <c r="C12" s="143"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="148" t="s">
         <v>171</v>
       </c>
-      <c r="F12" s="141"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="141"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="141"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="141" t="s">
+      <c r="F12" s="148"/>
+      <c r="G12" s="148"/>
+      <c r="H12" s="148"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="148"/>
+      <c r="K12" s="148"/>
+      <c r="L12" s="148" t="s">
         <v>172</v>
       </c>
-      <c r="M12" s="141"/>
-      <c r="N12" s="141"/>
-      <c r="O12" s="141"/>
-      <c r="P12" s="141"/>
-      <c r="Q12" s="141"/>
-      <c r="R12" s="141"/>
-      <c r="S12" s="141" t="s">
+      <c r="M12" s="148"/>
+      <c r="N12" s="148"/>
+      <c r="O12" s="148"/>
+      <c r="P12" s="148"/>
+      <c r="Q12" s="148"/>
+      <c r="R12" s="148"/>
+      <c r="S12" s="148" t="s">
         <v>173</v>
       </c>
-      <c r="T12" s="141"/>
-      <c r="U12" s="141"/>
-      <c r="V12" s="141"/>
-      <c r="W12" s="141"/>
-      <c r="X12" s="141"/>
-      <c r="Y12" s="141"/>
-      <c r="Z12" s="141" t="s">
+      <c r="T12" s="148"/>
+      <c r="U12" s="148"/>
+      <c r="V12" s="148"/>
+      <c r="W12" s="148"/>
+      <c r="X12" s="148"/>
+      <c r="Y12" s="148"/>
+      <c r="Z12" s="148" t="s">
         <v>174</v>
       </c>
-      <c r="AA12" s="141"/>
-      <c r="AB12" s="141"/>
-      <c r="AC12" s="141"/>
-      <c r="AD12" s="141"/>
-      <c r="AE12" s="141"/>
-      <c r="AF12" s="141"/>
-      <c r="AG12" s="141" t="s">
+      <c r="AA12" s="148"/>
+      <c r="AB12" s="148"/>
+      <c r="AC12" s="148"/>
+      <c r="AD12" s="148"/>
+      <c r="AE12" s="148"/>
+      <c r="AF12" s="148"/>
+      <c r="AG12" s="148" t="s">
         <v>175</v>
       </c>
-      <c r="AH12" s="141"/>
-      <c r="AI12" s="141"/>
-      <c r="AJ12" s="141"/>
-      <c r="AK12" s="141"/>
-      <c r="AL12" s="141"/>
-      <c r="AM12" s="141"/>
+      <c r="AH12" s="148"/>
+      <c r="AI12" s="148"/>
+      <c r="AJ12" s="148"/>
+      <c r="AK12" s="148"/>
+      <c r="AL12" s="148"/>
+      <c r="AM12" s="148"/>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="143" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="140"/>
-      <c r="F13" s="140"/>
-      <c r="G13" s="140"/>
-      <c r="H13" s="140"/>
-      <c r="I13" s="140"/>
-      <c r="J13" s="140"/>
-      <c r="K13" s="140"/>
-      <c r="L13" s="140"/>
-      <c r="M13" s="140"/>
-      <c r="N13" s="140"/>
-      <c r="O13" s="140"/>
-      <c r="P13" s="140"/>
-      <c r="Q13" s="140"/>
-      <c r="R13" s="140"/>
-      <c r="S13" s="140"/>
-      <c r="T13" s="140"/>
-      <c r="U13" s="140"/>
-      <c r="V13" s="140"/>
-      <c r="W13" s="140"/>
-      <c r="X13" s="140"/>
-      <c r="Y13" s="140"/>
-      <c r="Z13" s="140"/>
-      <c r="AA13" s="140"/>
-      <c r="AB13" s="140"/>
-      <c r="AC13" s="140"/>
-      <c r="AD13" s="140"/>
-      <c r="AE13" s="140"/>
-      <c r="AF13" s="140"/>
-      <c r="AG13" s="140"/>
-      <c r="AH13" s="140"/>
-      <c r="AI13" s="140"/>
-      <c r="AJ13" s="140"/>
-      <c r="AK13" s="140"/>
-      <c r="AL13" s="140"/>
-      <c r="AM13" s="140"/>
+      <c r="B13" s="143"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="147"/>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="147"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="147"/>
+      <c r="Q13" s="147"/>
+      <c r="R13" s="147"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="147"/>
+      <c r="U13" s="147"/>
+      <c r="V13" s="147"/>
+      <c r="W13" s="147"/>
+      <c r="X13" s="147"/>
+      <c r="Y13" s="147"/>
+      <c r="Z13" s="147"/>
+      <c r="AA13" s="147"/>
+      <c r="AB13" s="147"/>
+      <c r="AC13" s="147"/>
+      <c r="AD13" s="147"/>
+      <c r="AE13" s="147"/>
+      <c r="AF13" s="147"/>
+      <c r="AG13" s="147"/>
+      <c r="AH13" s="147"/>
+      <c r="AI13" s="147"/>
+      <c r="AJ13" s="147"/>
+      <c r="AK13" s="147"/>
+      <c r="AL13" s="147"/>
+      <c r="AM13" s="147"/>
     </row>
     <row r="14" spans="1:39" ht="15" customHeight="1">
-      <c r="A14" s="137" t="s">
+      <c r="A14" s="143" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="137"/>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="140"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="140"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="140"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="140"/>
-      <c r="N14" s="140"/>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="140"/>
-      <c r="R14" s="140"/>
-      <c r="S14" s="140"/>
-      <c r="T14" s="140"/>
-      <c r="U14" s="140"/>
-      <c r="V14" s="140"/>
-      <c r="W14" s="140"/>
-      <c r="X14" s="140"/>
-      <c r="Y14" s="140"/>
-      <c r="Z14" s="140"/>
-      <c r="AA14" s="140"/>
-      <c r="AB14" s="140"/>
-      <c r="AC14" s="140"/>
-      <c r="AD14" s="140"/>
-      <c r="AE14" s="140"/>
-      <c r="AF14" s="140"/>
-      <c r="AG14" s="140"/>
-      <c r="AH14" s="140"/>
-      <c r="AI14" s="140"/>
-      <c r="AJ14" s="140"/>
-      <c r="AK14" s="140"/>
-      <c r="AL14" s="140"/>
-      <c r="AM14" s="140"/>
+      <c r="B14" s="143"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="147"/>
+      <c r="H14" s="147"/>
+      <c r="I14" s="147"/>
+      <c r="J14" s="147"/>
+      <c r="K14" s="147"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="147"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="147"/>
+      <c r="Q14" s="147"/>
+      <c r="R14" s="147"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="147"/>
+      <c r="U14" s="147"/>
+      <c r="V14" s="147"/>
+      <c r="W14" s="147"/>
+      <c r="X14" s="147"/>
+      <c r="Y14" s="147"/>
+      <c r="Z14" s="147"/>
+      <c r="AA14" s="147"/>
+      <c r="AB14" s="147"/>
+      <c r="AC14" s="147"/>
+      <c r="AD14" s="147"/>
+      <c r="AE14" s="147"/>
+      <c r="AF14" s="147"/>
+      <c r="AG14" s="147"/>
+      <c r="AH14" s="147"/>
+      <c r="AI14" s="147"/>
+      <c r="AJ14" s="147"/>
+      <c r="AK14" s="147"/>
+      <c r="AL14" s="147"/>
+      <c r="AM14" s="147"/>
     </row>
     <row r="15" spans="1:39">
-      <c r="A15" s="173" t="s">
+      <c r="A15" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="174"/>
+      <c r="B15" s="77"/>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
@@ -10915,7 +10922,7 @@
       <c r="AL15" s="34"/>
       <c r="AM15" s="34"/>
     </row>
-    <row r="16" spans="1:39" ht="27.6" customHeight="1">
+    <row r="16" spans="1:39" ht="102.75" customHeight="1">
       <c r="A16" s="34"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
@@ -10997,17 +11004,17 @@
       <c r="AM17" s="34"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="139"/>
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="139"/>
-      <c r="I18" s="139"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="139"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="146"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="146"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="146"/>
       <c r="L18" s="34"/>
       <c r="M18" s="34"/>
       <c r="N18" s="34"/>
@@ -11038,17 +11045,17 @@
       <c r="AM18" s="34"/>
     </row>
     <row r="19" spans="1:39" ht="9" customHeight="1">
-      <c r="A19" s="175"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="175"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="175"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="175"/>
-      <c r="I19" s="175"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="175"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
       <c r="L19" s="34"/>
       <c r="M19" s="34"/>
       <c r="N19" s="34"/>
@@ -11163,607 +11170,607 @@
       <c r="AM21" s="34"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="146" t="s">
+      <c r="A22" s="145" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="146"/>
-      <c r="C22" s="146"/>
-      <c r="D22" s="146"/>
-      <c r="E22" s="138" t="s">
+      <c r="B22" s="145"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="145"/>
+      <c r="E22" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="F22" s="138"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="138"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="138" t="s">
+      <c r="F22" s="144"/>
+      <c r="G22" s="144"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="144"/>
+      <c r="J22" s="144"/>
+      <c r="K22" s="144"/>
+      <c r="L22" s="144" t="s">
         <v>183</v>
       </c>
-      <c r="M22" s="138"/>
-      <c r="N22" s="138"/>
-      <c r="O22" s="138"/>
-      <c r="P22" s="138"/>
-      <c r="Q22" s="138"/>
-      <c r="R22" s="138"/>
-      <c r="S22" s="138" t="s">
+      <c r="M22" s="144"/>
+      <c r="N22" s="144"/>
+      <c r="O22" s="144"/>
+      <c r="P22" s="144"/>
+      <c r="Q22" s="144"/>
+      <c r="R22" s="144"/>
+      <c r="S22" s="144" t="s">
         <v>184</v>
       </c>
-      <c r="T22" s="138"/>
-      <c r="U22" s="138"/>
-      <c r="V22" s="138"/>
-      <c r="W22" s="138"/>
-      <c r="X22" s="138"/>
-      <c r="Y22" s="138"/>
-      <c r="Z22" s="138" t="s">
+      <c r="T22" s="144"/>
+      <c r="U22" s="144"/>
+      <c r="V22" s="144"/>
+      <c r="W22" s="144"/>
+      <c r="X22" s="144"/>
+      <c r="Y22" s="144"/>
+      <c r="Z22" s="144" t="s">
         <v>185</v>
       </c>
-      <c r="AA22" s="138"/>
-      <c r="AB22" s="138"/>
-      <c r="AC22" s="138"/>
-      <c r="AD22" s="138"/>
-      <c r="AE22" s="138"/>
-      <c r="AF22" s="138"/>
-      <c r="AG22" s="138" t="s">
+      <c r="AA22" s="144"/>
+      <c r="AB22" s="144"/>
+      <c r="AC22" s="144"/>
+      <c r="AD22" s="144"/>
+      <c r="AE22" s="144"/>
+      <c r="AF22" s="144"/>
+      <c r="AG22" s="144" t="s">
         <v>186</v>
       </c>
-      <c r="AH22" s="138"/>
-      <c r="AI22" s="138"/>
-      <c r="AJ22" s="138"/>
-      <c r="AK22" s="138"/>
-      <c r="AL22" s="138"/>
-      <c r="AM22" s="138"/>
+      <c r="AH22" s="144"/>
+      <c r="AI22" s="144"/>
+      <c r="AJ22" s="144"/>
+      <c r="AK22" s="144"/>
+      <c r="AL22" s="144"/>
+      <c r="AM22" s="144"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="146"/>
-      <c r="B23" s="146"/>
-      <c r="C23" s="146"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="138" t="s">
+      <c r="A23" s="145"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="F23" s="138"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="138" t="s">
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="I23" s="138"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="138"/>
-      <c r="L23" s="138" t="s">
+      <c r="I23" s="144"/>
+      <c r="J23" s="144"/>
+      <c r="K23" s="144"/>
+      <c r="L23" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="M23" s="138"/>
-      <c r="N23" s="138"/>
-      <c r="O23" s="138" t="s">
+      <c r="M23" s="144"/>
+      <c r="N23" s="144"/>
+      <c r="O23" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="P23" s="138"/>
-      <c r="Q23" s="138"/>
-      <c r="R23" s="138"/>
-      <c r="S23" s="138" t="s">
+      <c r="P23" s="144"/>
+      <c r="Q23" s="144"/>
+      <c r="R23" s="144"/>
+      <c r="S23" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="T23" s="138"/>
-      <c r="U23" s="138"/>
-      <c r="V23" s="138" t="s">
+      <c r="T23" s="144"/>
+      <c r="U23" s="144"/>
+      <c r="V23" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="W23" s="138"/>
-      <c r="X23" s="138"/>
-      <c r="Y23" s="138"/>
-      <c r="Z23" s="138" t="s">
+      <c r="W23" s="144"/>
+      <c r="X23" s="144"/>
+      <c r="Y23" s="144"/>
+      <c r="Z23" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="AA23" s="138"/>
-      <c r="AB23" s="138"/>
-      <c r="AC23" s="138" t="s">
+      <c r="AA23" s="144"/>
+      <c r="AB23" s="144"/>
+      <c r="AC23" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="AD23" s="138"/>
-      <c r="AE23" s="138"/>
-      <c r="AF23" s="138"/>
-      <c r="AG23" s="138" t="s">
+      <c r="AD23" s="144"/>
+      <c r="AE23" s="144"/>
+      <c r="AF23" s="144"/>
+      <c r="AG23" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="AH23" s="138"/>
-      <c r="AI23" s="138"/>
-      <c r="AJ23" s="138" t="s">
+      <c r="AH23" s="144"/>
+      <c r="AI23" s="144"/>
+      <c r="AJ23" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="AK23" s="138"/>
-      <c r="AL23" s="138"/>
-      <c r="AM23" s="138"/>
+      <c r="AK23" s="144"/>
+      <c r="AL23" s="144"/>
+      <c r="AM23" s="144"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="137" t="s">
+      <c r="A24" s="143" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="137"/>
-      <c r="C24" s="137"/>
-      <c r="D24" s="137"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="136"/>
-      <c r="H24" s="134"/>
-      <c r="I24" s="135"/>
-      <c r="J24" s="135"/>
-      <c r="K24" s="136"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="135"/>
-      <c r="N24" s="136"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="135"/>
-      <c r="Q24" s="135"/>
-      <c r="R24" s="136"/>
-      <c r="S24" s="134"/>
-      <c r="T24" s="135"/>
-      <c r="U24" s="136"/>
-      <c r="V24" s="134"/>
-      <c r="W24" s="135"/>
-      <c r="X24" s="135"/>
-      <c r="Y24" s="136"/>
-      <c r="Z24" s="134"/>
-      <c r="AA24" s="135"/>
-      <c r="AB24" s="136"/>
-      <c r="AC24" s="134"/>
-      <c r="AD24" s="135"/>
-      <c r="AE24" s="135"/>
-      <c r="AF24" s="136"/>
-      <c r="AG24" s="134"/>
-      <c r="AH24" s="135"/>
-      <c r="AI24" s="136"/>
-      <c r="AJ24" s="134"/>
-      <c r="AK24" s="135"/>
-      <c r="AL24" s="135"/>
-      <c r="AM24" s="136"/>
+      <c r="B24" s="143"/>
+      <c r="C24" s="143"/>
+      <c r="D24" s="143"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="142"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="141"/>
+      <c r="J24" s="141"/>
+      <c r="K24" s="142"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="141"/>
+      <c r="N24" s="142"/>
+      <c r="O24" s="140"/>
+      <c r="P24" s="141"/>
+      <c r="Q24" s="141"/>
+      <c r="R24" s="142"/>
+      <c r="S24" s="140"/>
+      <c r="T24" s="141"/>
+      <c r="U24" s="142"/>
+      <c r="V24" s="140"/>
+      <c r="W24" s="141"/>
+      <c r="X24" s="141"/>
+      <c r="Y24" s="142"/>
+      <c r="Z24" s="140"/>
+      <c r="AA24" s="141"/>
+      <c r="AB24" s="142"/>
+      <c r="AC24" s="140"/>
+      <c r="AD24" s="141"/>
+      <c r="AE24" s="141"/>
+      <c r="AF24" s="142"/>
+      <c r="AG24" s="140"/>
+      <c r="AH24" s="141"/>
+      <c r="AI24" s="142"/>
+      <c r="AJ24" s="140"/>
+      <c r="AK24" s="141"/>
+      <c r="AL24" s="141"/>
+      <c r="AM24" s="142"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="137" t="s">
+      <c r="A25" s="143" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="137"/>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="134"/>
-      <c r="F25" s="135"/>
-      <c r="G25" s="136"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="135"/>
-      <c r="J25" s="135"/>
-      <c r="K25" s="136"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="135"/>
-      <c r="N25" s="136"/>
-      <c r="O25" s="134"/>
-      <c r="P25" s="135"/>
-      <c r="Q25" s="135"/>
-      <c r="R25" s="136"/>
-      <c r="S25" s="134"/>
-      <c r="T25" s="135"/>
-      <c r="U25" s="136"/>
-      <c r="V25" s="134"/>
-      <c r="W25" s="135"/>
-      <c r="X25" s="135"/>
-      <c r="Y25" s="136"/>
-      <c r="Z25" s="134"/>
-      <c r="AA25" s="135"/>
-      <c r="AB25" s="136"/>
-      <c r="AC25" s="134"/>
-      <c r="AD25" s="135"/>
-      <c r="AE25" s="135"/>
-      <c r="AF25" s="136"/>
-      <c r="AG25" s="134"/>
-      <c r="AH25" s="135"/>
-      <c r="AI25" s="136"/>
-      <c r="AJ25" s="134"/>
-      <c r="AK25" s="135"/>
-      <c r="AL25" s="135"/>
-      <c r="AM25" s="136"/>
+      <c r="B25" s="143"/>
+      <c r="C25" s="143"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="142"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="141"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="142"/>
+      <c r="L25" s="140"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="142"/>
+      <c r="O25" s="140"/>
+      <c r="P25" s="141"/>
+      <c r="Q25" s="141"/>
+      <c r="R25" s="142"/>
+      <c r="S25" s="140"/>
+      <c r="T25" s="141"/>
+      <c r="U25" s="142"/>
+      <c r="V25" s="140"/>
+      <c r="W25" s="141"/>
+      <c r="X25" s="141"/>
+      <c r="Y25" s="142"/>
+      <c r="Z25" s="140"/>
+      <c r="AA25" s="141"/>
+      <c r="AB25" s="142"/>
+      <c r="AC25" s="140"/>
+      <c r="AD25" s="141"/>
+      <c r="AE25" s="141"/>
+      <c r="AF25" s="142"/>
+      <c r="AG25" s="140"/>
+      <c r="AH25" s="141"/>
+      <c r="AI25" s="142"/>
+      <c r="AJ25" s="140"/>
+      <c r="AK25" s="141"/>
+      <c r="AL25" s="141"/>
+      <c r="AM25" s="142"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="146" t="s">
+      <c r="A26" s="145" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="146"/>
-      <c r="C26" s="146"/>
-      <c r="D26" s="146"/>
-      <c r="E26" s="138" t="s">
+      <c r="B26" s="145"/>
+      <c r="C26" s="145"/>
+      <c r="D26" s="145"/>
+      <c r="E26" s="144" t="s">
         <v>187</v>
       </c>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="138"/>
-      <c r="I26" s="138"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="138"/>
-      <c r="L26" s="138" t="s">
+      <c r="F26" s="144"/>
+      <c r="G26" s="144"/>
+      <c r="H26" s="144"/>
+      <c r="I26" s="144"/>
+      <c r="J26" s="144"/>
+      <c r="K26" s="144"/>
+      <c r="L26" s="144" t="s">
         <v>188</v>
       </c>
-      <c r="M26" s="138"/>
-      <c r="N26" s="138"/>
-      <c r="O26" s="138"/>
-      <c r="P26" s="138"/>
-      <c r="Q26" s="138"/>
-      <c r="R26" s="138"/>
-      <c r="S26" s="138" t="s">
+      <c r="M26" s="144"/>
+      <c r="N26" s="144"/>
+      <c r="O26" s="144"/>
+      <c r="P26" s="144"/>
+      <c r="Q26" s="144"/>
+      <c r="R26" s="144"/>
+      <c r="S26" s="144" t="s">
         <v>189</v>
       </c>
-      <c r="T26" s="138"/>
-      <c r="U26" s="138"/>
-      <c r="V26" s="138"/>
-      <c r="W26" s="138"/>
-      <c r="X26" s="138"/>
-      <c r="Y26" s="138"/>
-      <c r="Z26" s="138" t="s">
+      <c r="T26" s="144"/>
+      <c r="U26" s="144"/>
+      <c r="V26" s="144"/>
+      <c r="W26" s="144"/>
+      <c r="X26" s="144"/>
+      <c r="Y26" s="144"/>
+      <c r="Z26" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AA26" s="138"/>
-      <c r="AB26" s="138"/>
-      <c r="AC26" s="138"/>
-      <c r="AD26" s="138"/>
-      <c r="AE26" s="138"/>
-      <c r="AF26" s="138"/>
-      <c r="AG26" s="138" t="s">
+      <c r="AA26" s="144"/>
+      <c r="AB26" s="144"/>
+      <c r="AC26" s="144"/>
+      <c r="AD26" s="144"/>
+      <c r="AE26" s="144"/>
+      <c r="AF26" s="144"/>
+      <c r="AG26" s="144" t="s">
         <v>191</v>
       </c>
-      <c r="AH26" s="138"/>
-      <c r="AI26" s="138"/>
-      <c r="AJ26" s="138"/>
-      <c r="AK26" s="138"/>
-      <c r="AL26" s="138"/>
-      <c r="AM26" s="138"/>
+      <c r="AH26" s="144"/>
+      <c r="AI26" s="144"/>
+      <c r="AJ26" s="144"/>
+      <c r="AK26" s="144"/>
+      <c r="AL26" s="144"/>
+      <c r="AM26" s="144"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="146"/>
-      <c r="B27" s="146"/>
-      <c r="C27" s="146"/>
-      <c r="D27" s="146"/>
-      <c r="E27" s="138" t="s">
+      <c r="A27" s="145"/>
+      <c r="B27" s="145"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="145"/>
+      <c r="E27" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="F27" s="138"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="138" t="s">
+      <c r="F27" s="144"/>
+      <c r="G27" s="144"/>
+      <c r="H27" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="I27" s="138"/>
-      <c r="J27" s="138"/>
-      <c r="K27" s="138"/>
-      <c r="L27" s="138" t="s">
+      <c r="I27" s="144"/>
+      <c r="J27" s="144"/>
+      <c r="K27" s="144"/>
+      <c r="L27" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="M27" s="138"/>
-      <c r="N27" s="138"/>
-      <c r="O27" s="138" t="s">
+      <c r="M27" s="144"/>
+      <c r="N27" s="144"/>
+      <c r="O27" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="P27" s="138"/>
-      <c r="Q27" s="138"/>
-      <c r="R27" s="138"/>
-      <c r="S27" s="138" t="s">
+      <c r="P27" s="144"/>
+      <c r="Q27" s="144"/>
+      <c r="R27" s="144"/>
+      <c r="S27" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="T27" s="138"/>
-      <c r="U27" s="138"/>
-      <c r="V27" s="138" t="s">
+      <c r="T27" s="144"/>
+      <c r="U27" s="144"/>
+      <c r="V27" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="W27" s="138"/>
-      <c r="X27" s="138"/>
-      <c r="Y27" s="138"/>
-      <c r="Z27" s="138" t="s">
+      <c r="W27" s="144"/>
+      <c r="X27" s="144"/>
+      <c r="Y27" s="144"/>
+      <c r="Z27" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="AA27" s="138"/>
-      <c r="AB27" s="138"/>
-      <c r="AC27" s="138" t="s">
+      <c r="AA27" s="144"/>
+      <c r="AB27" s="144"/>
+      <c r="AC27" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="AD27" s="138"/>
-      <c r="AE27" s="138"/>
-      <c r="AF27" s="138"/>
-      <c r="AG27" s="138" t="s">
+      <c r="AD27" s="144"/>
+      <c r="AE27" s="144"/>
+      <c r="AF27" s="144"/>
+      <c r="AG27" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="AH27" s="138"/>
-      <c r="AI27" s="138"/>
-      <c r="AJ27" s="138" t="s">
+      <c r="AH27" s="144"/>
+      <c r="AI27" s="144"/>
+      <c r="AJ27" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="AK27" s="138"/>
-      <c r="AL27" s="138"/>
-      <c r="AM27" s="138"/>
+      <c r="AK27" s="144"/>
+      <c r="AL27" s="144"/>
+      <c r="AM27" s="144"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="137" t="s">
+      <c r="A28" s="143" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="137"/>
-      <c r="C28" s="137"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="136"/>
-      <c r="H28" s="134"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="135"/>
-      <c r="K28" s="136"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="135"/>
-      <c r="N28" s="136"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="135"/>
-      <c r="Q28" s="135"/>
-      <c r="R28" s="136"/>
-      <c r="S28" s="134"/>
-      <c r="T28" s="135"/>
-      <c r="U28" s="136"/>
-      <c r="V28" s="134"/>
-      <c r="W28" s="135"/>
-      <c r="X28" s="135"/>
-      <c r="Y28" s="136"/>
-      <c r="Z28" s="134"/>
-      <c r="AA28" s="135"/>
-      <c r="AB28" s="136"/>
-      <c r="AC28" s="134"/>
-      <c r="AD28" s="135"/>
-      <c r="AE28" s="135"/>
-      <c r="AF28" s="136"/>
-      <c r="AG28" s="134"/>
-      <c r="AH28" s="135"/>
-      <c r="AI28" s="136"/>
-      <c r="AJ28" s="134"/>
-      <c r="AK28" s="135"/>
-      <c r="AL28" s="135"/>
-      <c r="AM28" s="136"/>
+      <c r="B28" s="143"/>
+      <c r="C28" s="143"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="141"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="142"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="141"/>
+      <c r="N28" s="142"/>
+      <c r="O28" s="140"/>
+      <c r="P28" s="141"/>
+      <c r="Q28" s="141"/>
+      <c r="R28" s="142"/>
+      <c r="S28" s="140"/>
+      <c r="T28" s="141"/>
+      <c r="U28" s="142"/>
+      <c r="V28" s="140"/>
+      <c r="W28" s="141"/>
+      <c r="X28" s="141"/>
+      <c r="Y28" s="142"/>
+      <c r="Z28" s="140"/>
+      <c r="AA28" s="141"/>
+      <c r="AB28" s="142"/>
+      <c r="AC28" s="140"/>
+      <c r="AD28" s="141"/>
+      <c r="AE28" s="141"/>
+      <c r="AF28" s="142"/>
+      <c r="AG28" s="140"/>
+      <c r="AH28" s="141"/>
+      <c r="AI28" s="142"/>
+      <c r="AJ28" s="140"/>
+      <c r="AK28" s="141"/>
+      <c r="AL28" s="141"/>
+      <c r="AM28" s="142"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="137" t="s">
+      <c r="A29" s="143" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="137"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="134"/>
-      <c r="F29" s="135"/>
-      <c r="G29" s="136"/>
-      <c r="H29" s="134"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="135"/>
-      <c r="K29" s="136"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="135"/>
-      <c r="N29" s="136"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="135"/>
-      <c r="Q29" s="135"/>
-      <c r="R29" s="136"/>
-      <c r="S29" s="134"/>
-      <c r="T29" s="135"/>
-      <c r="U29" s="136"/>
-      <c r="V29" s="134"/>
-      <c r="W29" s="135"/>
-      <c r="X29" s="135"/>
-      <c r="Y29" s="136"/>
-      <c r="Z29" s="134"/>
-      <c r="AA29" s="135"/>
-      <c r="AB29" s="136"/>
-      <c r="AC29" s="134"/>
-      <c r="AD29" s="135"/>
-      <c r="AE29" s="135"/>
-      <c r="AF29" s="136"/>
-      <c r="AG29" s="134"/>
-      <c r="AH29" s="135"/>
-      <c r="AI29" s="136"/>
-      <c r="AJ29" s="134"/>
-      <c r="AK29" s="135"/>
-      <c r="AL29" s="135"/>
-      <c r="AM29" s="136"/>
+      <c r="B29" s="143"/>
+      <c r="C29" s="143"/>
+      <c r="D29" s="143"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="140"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="142"/>
+      <c r="O29" s="140"/>
+      <c r="P29" s="141"/>
+      <c r="Q29" s="141"/>
+      <c r="R29" s="142"/>
+      <c r="S29" s="140"/>
+      <c r="T29" s="141"/>
+      <c r="U29" s="142"/>
+      <c r="V29" s="140"/>
+      <c r="W29" s="141"/>
+      <c r="X29" s="141"/>
+      <c r="Y29" s="142"/>
+      <c r="Z29" s="140"/>
+      <c r="AA29" s="141"/>
+      <c r="AB29" s="142"/>
+      <c r="AC29" s="140"/>
+      <c r="AD29" s="141"/>
+      <c r="AE29" s="141"/>
+      <c r="AF29" s="142"/>
+      <c r="AG29" s="140"/>
+      <c r="AH29" s="141"/>
+      <c r="AI29" s="142"/>
+      <c r="AJ29" s="140"/>
+      <c r="AK29" s="141"/>
+      <c r="AL29" s="141"/>
+      <c r="AM29" s="142"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="146" t="s">
+      <c r="A30" s="145" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="146"/>
-      <c r="C30" s="146"/>
-      <c r="D30" s="146"/>
-      <c r="E30" s="138" t="s">
+      <c r="B30" s="145"/>
+      <c r="C30" s="145"/>
+      <c r="D30" s="145"/>
+      <c r="E30" s="144" t="s">
         <v>196</v>
       </c>
-      <c r="F30" s="138"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="138"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="138"/>
-      <c r="L30" s="138" t="s">
+      <c r="F30" s="144"/>
+      <c r="G30" s="144"/>
+      <c r="H30" s="144"/>
+      <c r="I30" s="144"/>
+      <c r="J30" s="144"/>
+      <c r="K30" s="144"/>
+      <c r="L30" s="144" t="s">
         <v>195</v>
       </c>
-      <c r="M30" s="138"/>
-      <c r="N30" s="138"/>
-      <c r="O30" s="138"/>
-      <c r="P30" s="138"/>
-      <c r="Q30" s="138"/>
-      <c r="R30" s="138"/>
-      <c r="S30" s="138" t="s">
+      <c r="M30" s="144"/>
+      <c r="N30" s="144"/>
+      <c r="O30" s="144"/>
+      <c r="P30" s="144"/>
+      <c r="Q30" s="144"/>
+      <c r="R30" s="144"/>
+      <c r="S30" s="144" t="s">
         <v>194</v>
       </c>
-      <c r="T30" s="138"/>
-      <c r="U30" s="138"/>
-      <c r="V30" s="138"/>
-      <c r="W30" s="138"/>
-      <c r="X30" s="138"/>
-      <c r="Y30" s="138"/>
-      <c r="Z30" s="138" t="s">
+      <c r="T30" s="144"/>
+      <c r="U30" s="144"/>
+      <c r="V30" s="144"/>
+      <c r="W30" s="144"/>
+      <c r="X30" s="144"/>
+      <c r="Y30" s="144"/>
+      <c r="Z30" s="144" t="s">
         <v>193</v>
       </c>
-      <c r="AA30" s="138"/>
-      <c r="AB30" s="138"/>
-      <c r="AC30" s="138"/>
-      <c r="AD30" s="138"/>
-      <c r="AE30" s="138"/>
-      <c r="AF30" s="138"/>
-      <c r="AG30" s="138" t="s">
+      <c r="AA30" s="144"/>
+      <c r="AB30" s="144"/>
+      <c r="AC30" s="144"/>
+      <c r="AD30" s="144"/>
+      <c r="AE30" s="144"/>
+      <c r="AF30" s="144"/>
+      <c r="AG30" s="144" t="s">
         <v>192</v>
       </c>
-      <c r="AH30" s="138"/>
-      <c r="AI30" s="138"/>
-      <c r="AJ30" s="138"/>
-      <c r="AK30" s="138"/>
-      <c r="AL30" s="138"/>
-      <c r="AM30" s="138"/>
+      <c r="AH30" s="144"/>
+      <c r="AI30" s="144"/>
+      <c r="AJ30" s="144"/>
+      <c r="AK30" s="144"/>
+      <c r="AL30" s="144"/>
+      <c r="AM30" s="144"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="146"/>
-      <c r="B31" s="146"/>
-      <c r="C31" s="146"/>
-      <c r="D31" s="146"/>
-      <c r="E31" s="138" t="s">
+      <c r="A31" s="145"/>
+      <c r="B31" s="145"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="F31" s="138"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="138" t="s">
+      <c r="F31" s="144"/>
+      <c r="G31" s="144"/>
+      <c r="H31" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="I31" s="138"/>
-      <c r="J31" s="138"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="138" t="s">
+      <c r="I31" s="144"/>
+      <c r="J31" s="144"/>
+      <c r="K31" s="144"/>
+      <c r="L31" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="M31" s="138"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="138" t="s">
+      <c r="M31" s="144"/>
+      <c r="N31" s="144"/>
+      <c r="O31" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="P31" s="138"/>
-      <c r="Q31" s="138"/>
-      <c r="R31" s="138"/>
-      <c r="S31" s="138" t="s">
+      <c r="P31" s="144"/>
+      <c r="Q31" s="144"/>
+      <c r="R31" s="144"/>
+      <c r="S31" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="T31" s="138"/>
-      <c r="U31" s="138"/>
-      <c r="V31" s="138" t="s">
+      <c r="T31" s="144"/>
+      <c r="U31" s="144"/>
+      <c r="V31" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="W31" s="138"/>
-      <c r="X31" s="138"/>
-      <c r="Y31" s="138"/>
-      <c r="Z31" s="138" t="s">
+      <c r="W31" s="144"/>
+      <c r="X31" s="144"/>
+      <c r="Y31" s="144"/>
+      <c r="Z31" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="AA31" s="138"/>
-      <c r="AB31" s="138"/>
-      <c r="AC31" s="138" t="s">
+      <c r="AA31" s="144"/>
+      <c r="AB31" s="144"/>
+      <c r="AC31" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="AD31" s="138"/>
-      <c r="AE31" s="138"/>
-      <c r="AF31" s="138"/>
-      <c r="AG31" s="138" t="s">
+      <c r="AD31" s="144"/>
+      <c r="AE31" s="144"/>
+      <c r="AF31" s="144"/>
+      <c r="AG31" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="AH31" s="138"/>
-      <c r="AI31" s="138"/>
-      <c r="AJ31" s="138" t="s">
+      <c r="AH31" s="144"/>
+      <c r="AI31" s="144"/>
+      <c r="AJ31" s="144" t="s">
         <v>181</v>
       </c>
-      <c r="AK31" s="138"/>
-      <c r="AL31" s="138"/>
-      <c r="AM31" s="138"/>
+      <c r="AK31" s="144"/>
+      <c r="AL31" s="144"/>
+      <c r="AM31" s="144"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="137" t="s">
+      <c r="A32" s="143" t="s">
         <v>158</v>
       </c>
-      <c r="B32" s="137"/>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="134"/>
-      <c r="F32" s="135"/>
-      <c r="G32" s="136"/>
-      <c r="H32" s="134"/>
-      <c r="I32" s="135"/>
-      <c r="J32" s="135"/>
-      <c r="K32" s="136"/>
-      <c r="L32" s="134"/>
-      <c r="M32" s="135"/>
-      <c r="N32" s="136"/>
-      <c r="O32" s="134"/>
-      <c r="P32" s="135"/>
-      <c r="Q32" s="135"/>
-      <c r="R32" s="136"/>
-      <c r="S32" s="134"/>
-      <c r="T32" s="135"/>
-      <c r="U32" s="136"/>
-      <c r="V32" s="134"/>
-      <c r="W32" s="135"/>
-      <c r="X32" s="135"/>
-      <c r="Y32" s="136"/>
-      <c r="Z32" s="134"/>
-      <c r="AA32" s="135"/>
-      <c r="AB32" s="136"/>
-      <c r="AC32" s="134"/>
-      <c r="AD32" s="135"/>
-      <c r="AE32" s="135"/>
-      <c r="AF32" s="136"/>
-      <c r="AG32" s="134"/>
-      <c r="AH32" s="135"/>
-      <c r="AI32" s="136"/>
-      <c r="AJ32" s="134"/>
-      <c r="AK32" s="135"/>
-      <c r="AL32" s="135"/>
-      <c r="AM32" s="136"/>
+      <c r="B32" s="143"/>
+      <c r="C32" s="143"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="140"/>
+      <c r="I32" s="141"/>
+      <c r="J32" s="141"/>
+      <c r="K32" s="142"/>
+      <c r="L32" s="140"/>
+      <c r="M32" s="141"/>
+      <c r="N32" s="142"/>
+      <c r="O32" s="140"/>
+      <c r="P32" s="141"/>
+      <c r="Q32" s="141"/>
+      <c r="R32" s="142"/>
+      <c r="S32" s="140"/>
+      <c r="T32" s="141"/>
+      <c r="U32" s="142"/>
+      <c r="V32" s="140"/>
+      <c r="W32" s="141"/>
+      <c r="X32" s="141"/>
+      <c r="Y32" s="142"/>
+      <c r="Z32" s="140"/>
+      <c r="AA32" s="141"/>
+      <c r="AB32" s="142"/>
+      <c r="AC32" s="140"/>
+      <c r="AD32" s="141"/>
+      <c r="AE32" s="141"/>
+      <c r="AF32" s="142"/>
+      <c r="AG32" s="140"/>
+      <c r="AH32" s="141"/>
+      <c r="AI32" s="142"/>
+      <c r="AJ32" s="140"/>
+      <c r="AK32" s="141"/>
+      <c r="AL32" s="141"/>
+      <c r="AM32" s="142"/>
     </row>
     <row r="33" spans="1:39">
-      <c r="A33" s="137" t="s">
+      <c r="A33" s="143" t="s">
         <v>159</v>
       </c>
-      <c r="B33" s="137"/>
-      <c r="C33" s="137"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="134"/>
-      <c r="F33" s="135"/>
-      <c r="G33" s="136"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="135"/>
-      <c r="J33" s="135"/>
-      <c r="K33" s="136"/>
-      <c r="L33" s="134"/>
-      <c r="M33" s="135"/>
-      <c r="N33" s="136"/>
-      <c r="O33" s="134"/>
-      <c r="P33" s="135"/>
-      <c r="Q33" s="135"/>
-      <c r="R33" s="136"/>
-      <c r="S33" s="134"/>
-      <c r="T33" s="135"/>
-      <c r="U33" s="136"/>
-      <c r="V33" s="134"/>
-      <c r="W33" s="135"/>
-      <c r="X33" s="135"/>
-      <c r="Y33" s="136"/>
-      <c r="Z33" s="134"/>
-      <c r="AA33" s="135"/>
-      <c r="AB33" s="136"/>
-      <c r="AC33" s="134"/>
-      <c r="AD33" s="135"/>
-      <c r="AE33" s="135"/>
-      <c r="AF33" s="136"/>
-      <c r="AG33" s="134"/>
-      <c r="AH33" s="135"/>
-      <c r="AI33" s="136"/>
-      <c r="AJ33" s="134"/>
-      <c r="AK33" s="135"/>
-      <c r="AL33" s="135"/>
-      <c r="AM33" s="136"/>
+      <c r="B33" s="143"/>
+      <c r="C33" s="143"/>
+      <c r="D33" s="143"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="142"/>
+      <c r="H33" s="140"/>
+      <c r="I33" s="141"/>
+      <c r="J33" s="141"/>
+      <c r="K33" s="142"/>
+      <c r="L33" s="140"/>
+      <c r="M33" s="141"/>
+      <c r="N33" s="142"/>
+      <c r="O33" s="140"/>
+      <c r="P33" s="141"/>
+      <c r="Q33" s="141"/>
+      <c r="R33" s="142"/>
+      <c r="S33" s="140"/>
+      <c r="T33" s="141"/>
+      <c r="U33" s="142"/>
+      <c r="V33" s="140"/>
+      <c r="W33" s="141"/>
+      <c r="X33" s="141"/>
+      <c r="Y33" s="142"/>
+      <c r="Z33" s="140"/>
+      <c r="AA33" s="141"/>
+      <c r="AB33" s="142"/>
+      <c r="AC33" s="140"/>
+      <c r="AD33" s="141"/>
+      <c r="AE33" s="141"/>
+      <c r="AF33" s="142"/>
+      <c r="AG33" s="140"/>
+      <c r="AH33" s="141"/>
+      <c r="AI33" s="142"/>
+      <c r="AJ33" s="140"/>
+      <c r="AK33" s="141"/>
+      <c r="AL33" s="141"/>
+      <c r="AM33" s="142"/>
     </row>
     <row r="34" spans="1:39">
-      <c r="A34" s="173" t="s">
+      <c r="A34" s="76" t="s">
         <v>86</v>
       </c>
       <c r="B34" s="70"/>
@@ -11806,7 +11813,7 @@
       <c r="AM34" s="71"/>
     </row>
     <row r="35" spans="1:39" ht="6" customHeight="1">
-      <c r="A35" s="173"/>
+      <c r="A35" s="76"/>
       <c r="B35" s="70"/>
       <c r="C35" s="70"/>
       <c r="D35" s="70"/>
@@ -11847,108 +11854,108 @@
       <c r="AM35" s="71"/>
     </row>
     <row r="36" spans="1:39">
-      <c r="A36" s="176" t="s">
+      <c r="A36" s="79" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:39">
-      <c r="A37" s="177" t="s">
+      <c r="A37" s="80" t="s">
         <v>215</v>
       </c>
-      <c r="B37" s="178"/>
-      <c r="C37" s="178"/>
-      <c r="D37" s="178"/>
-      <c r="E37" s="178"/>
-      <c r="F37" s="178"/>
-      <c r="G37" s="178"/>
-      <c r="H37" s="178"/>
-      <c r="I37" s="178"/>
-      <c r="J37" s="178"/>
-      <c r="K37" s="178"/>
-      <c r="L37" s="178"/>
-      <c r="M37" s="178"/>
-      <c r="N37" s="178"/>
-      <c r="O37" s="178"/>
-      <c r="P37" s="178"/>
-      <c r="Q37" s="178"/>
-      <c r="R37" s="178"/>
-      <c r="S37" s="178"/>
-      <c r="T37" s="178"/>
-      <c r="U37" s="178"/>
-      <c r="V37" s="178"/>
-      <c r="W37" s="178"/>
-      <c r="X37" s="178"/>
-      <c r="Y37" s="178"/>
-      <c r="Z37" s="178"/>
-      <c r="AA37" s="178"/>
-      <c r="AB37" s="178"/>
-      <c r="AC37" s="178"/>
-      <c r="AD37" s="178"/>
-      <c r="AE37" s="178"/>
-      <c r="AF37" s="178"/>
-      <c r="AG37" s="178"/>
-      <c r="AH37" s="178"/>
-      <c r="AI37" s="178"/>
-      <c r="AJ37" s="178"/>
-      <c r="AK37" s="178"/>
-      <c r="AL37" s="178"/>
-      <c r="AM37" s="178"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
+      <c r="M37" s="81"/>
+      <c r="N37" s="81"/>
+      <c r="O37" s="81"/>
+      <c r="P37" s="81"/>
+      <c r="Q37" s="81"/>
+      <c r="R37" s="81"/>
+      <c r="S37" s="81"/>
+      <c r="T37" s="81"/>
+      <c r="U37" s="81"/>
+      <c r="V37" s="81"/>
+      <c r="W37" s="81"/>
+      <c r="X37" s="81"/>
+      <c r="Y37" s="81"/>
+      <c r="Z37" s="81"/>
+      <c r="AA37" s="81"/>
+      <c r="AB37" s="81"/>
+      <c r="AC37" s="81"/>
+      <c r="AD37" s="81"/>
+      <c r="AE37" s="81"/>
+      <c r="AF37" s="81"/>
+      <c r="AG37" s="81"/>
+      <c r="AH37" s="81"/>
+      <c r="AI37" s="81"/>
+      <c r="AJ37" s="81"/>
+      <c r="AK37" s="81"/>
+      <c r="AL37" s="81"/>
+      <c r="AM37" s="81"/>
     </row>
     <row r="38" spans="1:39">
-      <c r="A38" s="177" t="s">
+      <c r="A38" s="80" t="s">
         <v>216</v>
       </c>
-      <c r="B38" s="178"/>
-      <c r="C38" s="178"/>
-      <c r="D38" s="178"/>
-      <c r="E38" s="178"/>
-      <c r="F38" s="178"/>
-      <c r="G38" s="178"/>
-      <c r="H38" s="178"/>
-      <c r="I38" s="178"/>
-      <c r="J38" s="178"/>
-      <c r="K38" s="178"/>
-      <c r="L38" s="178"/>
-      <c r="M38" s="178"/>
-      <c r="N38" s="178"/>
-      <c r="O38" s="178"/>
-      <c r="P38" s="178"/>
-      <c r="Q38" s="178"/>
-      <c r="R38" s="178"/>
-      <c r="S38" s="178"/>
-      <c r="T38" s="178"/>
-      <c r="U38" s="178"/>
-      <c r="V38" s="178"/>
-      <c r="W38" s="178"/>
-      <c r="X38" s="178"/>
-      <c r="Y38" s="178"/>
-      <c r="Z38" s="178"/>
-      <c r="AA38" s="178"/>
-      <c r="AB38" s="178"/>
-      <c r="AC38" s="178"/>
-      <c r="AD38" s="178"/>
-      <c r="AE38" s="178"/>
-      <c r="AF38" s="178"/>
-      <c r="AG38" s="178"/>
-      <c r="AH38" s="178"/>
-      <c r="AI38" s="178"/>
-      <c r="AJ38" s="178"/>
-      <c r="AK38" s="178"/>
-      <c r="AL38" s="178"/>
-      <c r="AM38" s="178"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
+      <c r="M38" s="81"/>
+      <c r="N38" s="81"/>
+      <c r="O38" s="81"/>
+      <c r="P38" s="81"/>
+      <c r="Q38" s="81"/>
+      <c r="R38" s="81"/>
+      <c r="S38" s="81"/>
+      <c r="T38" s="81"/>
+      <c r="U38" s="81"/>
+      <c r="V38" s="81"/>
+      <c r="W38" s="81"/>
+      <c r="X38" s="81"/>
+      <c r="Y38" s="81"/>
+      <c r="Z38" s="81"/>
+      <c r="AA38" s="81"/>
+      <c r="AB38" s="81"/>
+      <c r="AC38" s="81"/>
+      <c r="AD38" s="81"/>
+      <c r="AE38" s="81"/>
+      <c r="AF38" s="81"/>
+      <c r="AG38" s="81"/>
+      <c r="AH38" s="81"/>
+      <c r="AI38" s="81"/>
+      <c r="AJ38" s="81"/>
+      <c r="AK38" s="81"/>
+      <c r="AL38" s="81"/>
+      <c r="AM38" s="81"/>
     </row>
     <row r="39" spans="1:39">
-      <c r="A39" s="176" t="s">
+      <c r="A39" s="79" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:39">
-      <c r="A40" s="176" t="s">
+      <c r="A40" s="79" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:39">
-      <c r="A41" s="176" t="s">
+      <c r="A41" s="79" t="s">
         <v>178</v>
       </c>
     </row>
@@ -11958,59 +11965,109 @@
     <row r="62" hidden="1"/>
   </sheetData>
   <mergeCells count="172">
-    <mergeCell ref="AC33:AF33"/>
-    <mergeCell ref="AG33:AI33"/>
-    <mergeCell ref="AJ33:AM33"/>
-    <mergeCell ref="AG32:AI32"/>
-    <mergeCell ref="AJ32:AM32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="S33:U33"/>
-    <mergeCell ref="V33:Y33"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AJ31:AM31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="S32:U32"/>
-    <mergeCell ref="V32:Y32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="AC32:AF32"/>
-    <mergeCell ref="AG30:AM30"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="S31:U31"/>
-    <mergeCell ref="V31:Y31"/>
-    <mergeCell ref="Z31:AB31"/>
-    <mergeCell ref="AC31:AF31"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="V29:Y29"/>
-    <mergeCell ref="Z29:AB29"/>
-    <mergeCell ref="AC29:AF29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AM29"/>
-    <mergeCell ref="A30:D31"/>
-    <mergeCell ref="E30:K30"/>
-    <mergeCell ref="L30:R30"/>
-    <mergeCell ref="S30:Y30"/>
-    <mergeCell ref="Z30:AF30"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="AC28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ28:AM28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="S29:U29"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:K7"/>
+    <mergeCell ref="L7:R7"/>
+    <mergeCell ref="S7:Y7"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AM7"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="L6:R6"/>
+    <mergeCell ref="S6:Y6"/>
+    <mergeCell ref="Z6:AF6"/>
+    <mergeCell ref="AG6:AM6"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:K9"/>
+    <mergeCell ref="L9:R9"/>
+    <mergeCell ref="S9:Y9"/>
+    <mergeCell ref="Z9:AF9"/>
+    <mergeCell ref="AG9:AM9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:K8"/>
+    <mergeCell ref="L8:R8"/>
+    <mergeCell ref="S8:Y8"/>
+    <mergeCell ref="Z8:AF8"/>
+    <mergeCell ref="AG8:AM8"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:K11"/>
+    <mergeCell ref="L11:R11"/>
+    <mergeCell ref="S11:Y11"/>
+    <mergeCell ref="Z11:AF11"/>
+    <mergeCell ref="AG11:AM11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:K10"/>
+    <mergeCell ref="L10:R10"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="Z10:AF10"/>
+    <mergeCell ref="AG10:AM10"/>
+    <mergeCell ref="AG14:AM14"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:K13"/>
+    <mergeCell ref="L13:R13"/>
+    <mergeCell ref="S13:Y13"/>
+    <mergeCell ref="Z13:AF13"/>
+    <mergeCell ref="AG13:AM13"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:K12"/>
+    <mergeCell ref="L12:R12"/>
+    <mergeCell ref="S12:Y12"/>
+    <mergeCell ref="Z12:AF12"/>
+    <mergeCell ref="AG12:AM12"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A22:D23"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="L22:R22"/>
+    <mergeCell ref="S22:Y22"/>
+    <mergeCell ref="Z22:AF22"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:K14"/>
+    <mergeCell ref="L14:R14"/>
+    <mergeCell ref="S14:Y14"/>
+    <mergeCell ref="Z14:AF14"/>
+    <mergeCell ref="AG22:AM22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S23:U23"/>
+    <mergeCell ref="V23:Y23"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="AC23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AM23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="V24:Y24"/>
+    <mergeCell ref="Z24:AB24"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AJ24:AM24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="S25:U25"/>
+    <mergeCell ref="V25:Y25"/>
+    <mergeCell ref="Z25:AB25"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AM25"/>
+    <mergeCell ref="A26:D27"/>
+    <mergeCell ref="E26:K26"/>
+    <mergeCell ref="L26:R26"/>
+    <mergeCell ref="S26:Y26"/>
+    <mergeCell ref="Z26:AF26"/>
+    <mergeCell ref="AG26:AM26"/>
+    <mergeCell ref="E27:G27"/>
     <mergeCell ref="AC27:AF27"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="AJ27:AM27"/>
@@ -12027,111 +12084,61 @@
     <mergeCell ref="S27:U27"/>
     <mergeCell ref="V27:Y27"/>
     <mergeCell ref="Z27:AB27"/>
-    <mergeCell ref="AC25:AF25"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AM25"/>
-    <mergeCell ref="A26:D27"/>
-    <mergeCell ref="E26:K26"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="S26:Y26"/>
-    <mergeCell ref="Z26:AF26"/>
-    <mergeCell ref="AG26:AM26"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="AJ24:AM24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="S25:U25"/>
-    <mergeCell ref="V25:Y25"/>
-    <mergeCell ref="Z25:AB25"/>
-    <mergeCell ref="AJ23:AM23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="V24:Y24"/>
-    <mergeCell ref="Z24:AB24"/>
-    <mergeCell ref="AC24:AF24"/>
-    <mergeCell ref="AG22:AM22"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="V23:Y23"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="AC23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A22:D23"/>
-    <mergeCell ref="E22:K22"/>
-    <mergeCell ref="L22:R22"/>
-    <mergeCell ref="S22:Y22"/>
-    <mergeCell ref="Z22:AF22"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:K14"/>
-    <mergeCell ref="L14:R14"/>
-    <mergeCell ref="S14:Y14"/>
-    <mergeCell ref="Z14:AF14"/>
-    <mergeCell ref="AG14:AM14"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:K13"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="S13:Y13"/>
-    <mergeCell ref="Z13:AF13"/>
-    <mergeCell ref="AG13:AM13"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E12:K12"/>
-    <mergeCell ref="L12:R12"/>
-    <mergeCell ref="S12:Y12"/>
-    <mergeCell ref="Z12:AF12"/>
-    <mergeCell ref="AG12:AM12"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E11:K11"/>
-    <mergeCell ref="L11:R11"/>
-    <mergeCell ref="S11:Y11"/>
-    <mergeCell ref="Z11:AF11"/>
-    <mergeCell ref="AG11:AM11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E10:K10"/>
-    <mergeCell ref="L10:R10"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="Z10:AF10"/>
-    <mergeCell ref="AG10:AM10"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:K9"/>
-    <mergeCell ref="L9:R9"/>
-    <mergeCell ref="S9:Y9"/>
-    <mergeCell ref="Z9:AF9"/>
-    <mergeCell ref="AG9:AM9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:K8"/>
-    <mergeCell ref="L8:R8"/>
-    <mergeCell ref="S8:Y8"/>
-    <mergeCell ref="Z8:AF8"/>
-    <mergeCell ref="AG8:AM8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:K7"/>
-    <mergeCell ref="L7:R7"/>
-    <mergeCell ref="S7:Y7"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AM7"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="L6:R6"/>
-    <mergeCell ref="S6:Y6"/>
-    <mergeCell ref="Z6:AF6"/>
-    <mergeCell ref="AG6:AM6"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="AC28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AJ28:AM28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="S29:U29"/>
+    <mergeCell ref="V29:Y29"/>
+    <mergeCell ref="Z29:AB29"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AM29"/>
+    <mergeCell ref="A30:D31"/>
+    <mergeCell ref="E30:K30"/>
+    <mergeCell ref="L30:R30"/>
+    <mergeCell ref="S30:Y30"/>
+    <mergeCell ref="Z30:AF30"/>
+    <mergeCell ref="AG30:AM30"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="S31:U31"/>
+    <mergeCell ref="V31:Y31"/>
+    <mergeCell ref="Z31:AB31"/>
+    <mergeCell ref="AC31:AF31"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="AJ31:AM31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="S32:U32"/>
+    <mergeCell ref="V32:Y32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="AC32:AF32"/>
+    <mergeCell ref="AC33:AF33"/>
+    <mergeCell ref="AG33:AI33"/>
+    <mergeCell ref="AJ33:AM33"/>
+    <mergeCell ref="AG32:AI32"/>
+    <mergeCell ref="AJ32:AM32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="S33:U33"/>
+    <mergeCell ref="V33:Y33"/>
+    <mergeCell ref="Z33:AB33"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.47244094488188981" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -12170,32 +12177,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="142"/>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="142"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="142"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="142"/>
-      <c r="AF1" s="142"/>
-      <c r="AG1" s="142"/>
-      <c r="AH1" s="142"/>
-      <c r="AI1" s="142"/>
-      <c r="AJ1" s="142"/>
-      <c r="AK1" s="142"/>
-      <c r="AL1" s="142"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="149"/>
+      <c r="Y1" s="149"/>
+      <c r="Z1" s="149"/>
+      <c r="AA1" s="149"/>
+      <c r="AB1" s="149"/>
+      <c r="AC1" s="149"/>
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="149"/>
+      <c r="AJ1" s="149"/>
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="33" t="s">
@@ -12237,17 +12244,17 @@
       <c r="AL2" s="34"/>
     </row>
     <row r="3" spans="1:38">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
+      <c r="A3" s="146"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -12324,12 +12331,12 @@
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="35"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="154"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="151"/>
       <c r="L5" s="6" t="s">
         <v>129</v>
       </c>
@@ -12367,13 +12374,13 @@
       <c r="B6" s="6"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
-      <c r="E6" s="154"/>
-      <c r="F6" s="154"/>
-      <c r="G6" s="154"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="154"/>
-      <c r="J6" s="154"/>
-      <c r="K6" s="154"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="151"/>
+      <c r="H6" s="151"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="151"/>
+      <c r="K6" s="151"/>
       <c r="L6" s="6" t="s">
         <v>131</v>
       </c>
@@ -12415,13 +12422,13 @@
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="37"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="155"/>
-      <c r="K7" s="155"/>
-      <c r="L7" s="155"/>
-      <c r="M7" s="155"/>
-      <c r="N7" s="155"/>
-      <c r="O7" s="155"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="152"/>
+      <c r="K7" s="152"/>
+      <c r="L7" s="152"/>
+      <c r="M7" s="152"/>
+      <c r="N7" s="152"/>
+      <c r="O7" s="152"/>
       <c r="P7" s="37"/>
       <c r="Q7" s="37"/>
       <c r="R7" s="37"/>
@@ -12534,547 +12541,547 @@
       </c>
       <c r="B10" s="65"/>
       <c r="C10" s="66"/>
-      <c r="D10" s="148"/>
-      <c r="E10" s="148"/>
-      <c r="F10" s="148"/>
-      <c r="G10" s="152" t="s">
+      <c r="D10" s="154"/>
+      <c r="E10" s="154"/>
+      <c r="F10" s="154"/>
+      <c r="G10" s="157" t="s">
         <v>134</v>
       </c>
-      <c r="H10" s="153"/>
-      <c r="I10" s="150"/>
-      <c r="J10" s="151"/>
-      <c r="K10" s="151"/>
-      <c r="L10" s="151"/>
-      <c r="M10" s="151"/>
-      <c r="N10" s="151"/>
-      <c r="O10" s="151"/>
-      <c r="P10" s="151"/>
-      <c r="Q10" s="151"/>
-      <c r="R10" s="151"/>
-      <c r="S10" s="151"/>
-      <c r="T10" s="151"/>
-      <c r="U10" s="151"/>
-      <c r="V10" s="151"/>
-      <c r="W10" s="151"/>
-      <c r="X10" s="151"/>
-      <c r="Y10" s="151"/>
-      <c r="Z10" s="151"/>
-      <c r="AA10" s="151"/>
-      <c r="AB10" s="151"/>
-      <c r="AC10" s="151"/>
-      <c r="AD10" s="151"/>
-      <c r="AE10" s="151"/>
-      <c r="AF10" s="151"/>
-      <c r="AG10" s="151"/>
-      <c r="AH10" s="151"/>
-      <c r="AI10" s="151"/>
-      <c r="AJ10" s="151"/>
-      <c r="AK10" s="151"/>
-      <c r="AL10" s="151"/>
+      <c r="H10" s="158"/>
+      <c r="I10" s="156"/>
+      <c r="J10" s="150"/>
+      <c r="K10" s="150"/>
+      <c r="L10" s="150"/>
+      <c r="M10" s="150"/>
+      <c r="N10" s="150"/>
+      <c r="O10" s="150"/>
+      <c r="P10" s="150"/>
+      <c r="Q10" s="150"/>
+      <c r="R10" s="150"/>
+      <c r="S10" s="150"/>
+      <c r="T10" s="150"/>
+      <c r="U10" s="150"/>
+      <c r="V10" s="150"/>
+      <c r="W10" s="150"/>
+      <c r="X10" s="150"/>
+      <c r="Y10" s="150"/>
+      <c r="Z10" s="150"/>
+      <c r="AA10" s="150"/>
+      <c r="AB10" s="150"/>
+      <c r="AC10" s="150"/>
+      <c r="AD10" s="150"/>
+      <c r="AE10" s="150"/>
+      <c r="AF10" s="150"/>
+      <c r="AG10" s="150"/>
+      <c r="AH10" s="150"/>
+      <c r="AI10" s="150"/>
+      <c r="AJ10" s="150"/>
+      <c r="AK10" s="150"/>
+      <c r="AL10" s="150"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1">
-      <c r="A11" s="147" t="s">
+      <c r="A11" s="153" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="147"/>
-      <c r="C11" s="149"/>
-      <c r="D11" s="149"/>
-      <c r="E11" s="149"/>
-      <c r="F11" s="149"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="147"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="147"/>
-      <c r="O11" s="147"/>
-      <c r="P11" s="147"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="147"/>
-      <c r="S11" s="147"/>
-      <c r="T11" s="147"/>
-      <c r="U11" s="147"/>
-      <c r="V11" s="147"/>
-      <c r="W11" s="147"/>
-      <c r="X11" s="147"/>
-      <c r="Y11" s="147"/>
-      <c r="Z11" s="147"/>
-      <c r="AA11" s="147"/>
-      <c r="AB11" s="147"/>
-      <c r="AC11" s="147"/>
-      <c r="AD11" s="147"/>
-      <c r="AE11" s="147"/>
-      <c r="AF11" s="147"/>
-      <c r="AG11" s="147"/>
-      <c r="AH11" s="147"/>
-      <c r="AI11" s="147"/>
-      <c r="AJ11" s="147"/>
-      <c r="AK11" s="147"/>
-      <c r="AL11" s="147"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="155"/>
+      <c r="G11" s="155"/>
+      <c r="H11" s="155"/>
+      <c r="I11" s="153"/>
+      <c r="J11" s="153"/>
+      <c r="K11" s="153"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="153"/>
+      <c r="N11" s="153"/>
+      <c r="O11" s="153"/>
+      <c r="P11" s="153"/>
+      <c r="Q11" s="153"/>
+      <c r="R11" s="153"/>
+      <c r="S11" s="153"/>
+      <c r="T11" s="153"/>
+      <c r="U11" s="153"/>
+      <c r="V11" s="153"/>
+      <c r="W11" s="153"/>
+      <c r="X11" s="153"/>
+      <c r="Y11" s="153"/>
+      <c r="Z11" s="153"/>
+      <c r="AA11" s="153"/>
+      <c r="AB11" s="153"/>
+      <c r="AC11" s="153"/>
+      <c r="AD11" s="153"/>
+      <c r="AE11" s="153"/>
+      <c r="AF11" s="153"/>
+      <c r="AG11" s="153"/>
+      <c r="AH11" s="153"/>
+      <c r="AI11" s="153"/>
+      <c r="AJ11" s="153"/>
+      <c r="AK11" s="153"/>
+      <c r="AL11" s="153"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="147" t="s">
+      <c r="A12" s="153" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="147"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="147"/>
-      <c r="O12" s="147"/>
-      <c r="P12" s="147"/>
-      <c r="Q12" s="147"/>
-      <c r="R12" s="147"/>
-      <c r="S12" s="147"/>
-      <c r="T12" s="147"/>
-      <c r="U12" s="147"/>
-      <c r="V12" s="147"/>
-      <c r="W12" s="147"/>
-      <c r="X12" s="147"/>
-      <c r="Y12" s="147"/>
-      <c r="Z12" s="147"/>
-      <c r="AA12" s="147"/>
-      <c r="AB12" s="147"/>
-      <c r="AC12" s="147"/>
-      <c r="AD12" s="147"/>
-      <c r="AE12" s="147"/>
-      <c r="AF12" s="147"/>
-      <c r="AG12" s="147"/>
-      <c r="AH12" s="147"/>
-      <c r="AI12" s="147"/>
-      <c r="AJ12" s="147"/>
-      <c r="AK12" s="147"/>
-      <c r="AL12" s="147"/>
+      <c r="B12" s="153"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="153"/>
+      <c r="O12" s="153"/>
+      <c r="P12" s="153"/>
+      <c r="Q12" s="153"/>
+      <c r="R12" s="153"/>
+      <c r="S12" s="153"/>
+      <c r="T12" s="153"/>
+      <c r="U12" s="153"/>
+      <c r="V12" s="153"/>
+      <c r="W12" s="153"/>
+      <c r="X12" s="153"/>
+      <c r="Y12" s="153"/>
+      <c r="Z12" s="153"/>
+      <c r="AA12" s="153"/>
+      <c r="AB12" s="153"/>
+      <c r="AC12" s="153"/>
+      <c r="AD12" s="153"/>
+      <c r="AE12" s="153"/>
+      <c r="AF12" s="153"/>
+      <c r="AG12" s="153"/>
+      <c r="AH12" s="153"/>
+      <c r="AI12" s="153"/>
+      <c r="AJ12" s="153"/>
+      <c r="AK12" s="153"/>
+      <c r="AL12" s="153"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="147" t="s">
+      <c r="A13" s="153" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="147"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="147"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="147"/>
-      <c r="R13" s="147"/>
-      <c r="S13" s="147"/>
-      <c r="T13" s="147"/>
-      <c r="U13" s="147"/>
-      <c r="V13" s="147"/>
-      <c r="W13" s="147"/>
-      <c r="X13" s="147"/>
-      <c r="Y13" s="147"/>
-      <c r="Z13" s="147"/>
-      <c r="AA13" s="147"/>
-      <c r="AB13" s="147"/>
-      <c r="AC13" s="147"/>
-      <c r="AD13" s="147"/>
-      <c r="AE13" s="147"/>
-      <c r="AF13" s="147"/>
-      <c r="AG13" s="147"/>
-      <c r="AH13" s="147"/>
-      <c r="AI13" s="147"/>
-      <c r="AJ13" s="147"/>
-      <c r="AK13" s="147"/>
-      <c r="AL13" s="147"/>
+      <c r="B13" s="153"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="153"/>
+      <c r="H13" s="153"/>
+      <c r="I13" s="153"/>
+      <c r="J13" s="153"/>
+      <c r="K13" s="153"/>
+      <c r="L13" s="153"/>
+      <c r="M13" s="153"/>
+      <c r="N13" s="153"/>
+      <c r="O13" s="153"/>
+      <c r="P13" s="153"/>
+      <c r="Q13" s="153"/>
+      <c r="R13" s="153"/>
+      <c r="S13" s="153"/>
+      <c r="T13" s="153"/>
+      <c r="U13" s="153"/>
+      <c r="V13" s="153"/>
+      <c r="W13" s="153"/>
+      <c r="X13" s="153"/>
+      <c r="Y13" s="153"/>
+      <c r="Z13" s="153"/>
+      <c r="AA13" s="153"/>
+      <c r="AB13" s="153"/>
+      <c r="AC13" s="153"/>
+      <c r="AD13" s="153"/>
+      <c r="AE13" s="153"/>
+      <c r="AF13" s="153"/>
+      <c r="AG13" s="153"/>
+      <c r="AH13" s="153"/>
+      <c r="AI13" s="153"/>
+      <c r="AJ13" s="153"/>
+      <c r="AK13" s="153"/>
+      <c r="AL13" s="153"/>
     </row>
     <row r="14" spans="1:38" ht="18" customHeight="1">
-      <c r="A14" s="147" t="s">
+      <c r="A14" s="153" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="147"/>
-      <c r="C14" s="147"/>
-      <c r="D14" s="147"/>
-      <c r="E14" s="147"/>
-      <c r="F14" s="147"/>
-      <c r="G14" s="147"/>
-      <c r="H14" s="147"/>
-      <c r="I14" s="147"/>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="147"/>
-      <c r="N14" s="147"/>
-      <c r="O14" s="147"/>
-      <c r="P14" s="147"/>
-      <c r="Q14" s="147"/>
-      <c r="R14" s="147"/>
-      <c r="S14" s="147"/>
-      <c r="T14" s="147"/>
-      <c r="U14" s="147"/>
-      <c r="V14" s="147"/>
-      <c r="W14" s="147"/>
-      <c r="X14" s="147"/>
-      <c r="Y14" s="147"/>
-      <c r="Z14" s="147"/>
-      <c r="AA14" s="147"/>
-      <c r="AB14" s="147"/>
-      <c r="AC14" s="147"/>
-      <c r="AD14" s="147"/>
-      <c r="AE14" s="147"/>
-      <c r="AF14" s="147"/>
-      <c r="AG14" s="147"/>
-      <c r="AH14" s="147"/>
-      <c r="AI14" s="147"/>
-      <c r="AJ14" s="147"/>
-      <c r="AK14" s="147"/>
-      <c r="AL14" s="147"/>
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="153"/>
+      <c r="F14" s="153"/>
+      <c r="G14" s="153"/>
+      <c r="H14" s="153"/>
+      <c r="I14" s="153"/>
+      <c r="J14" s="153"/>
+      <c r="K14" s="153"/>
+      <c r="L14" s="153"/>
+      <c r="M14" s="153"/>
+      <c r="N14" s="153"/>
+      <c r="O14" s="153"/>
+      <c r="P14" s="153"/>
+      <c r="Q14" s="153"/>
+      <c r="R14" s="153"/>
+      <c r="S14" s="153"/>
+      <c r="T14" s="153"/>
+      <c r="U14" s="153"/>
+      <c r="V14" s="153"/>
+      <c r="W14" s="153"/>
+      <c r="X14" s="153"/>
+      <c r="Y14" s="153"/>
+      <c r="Z14" s="153"/>
+      <c r="AA14" s="153"/>
+      <c r="AB14" s="153"/>
+      <c r="AC14" s="153"/>
+      <c r="AD14" s="153"/>
+      <c r="AE14" s="153"/>
+      <c r="AF14" s="153"/>
+      <c r="AG14" s="153"/>
+      <c r="AH14" s="153"/>
+      <c r="AI14" s="153"/>
+      <c r="AJ14" s="153"/>
+      <c r="AK14" s="153"/>
+      <c r="AL14" s="153"/>
     </row>
     <row r="15" spans="1:38" ht="18" customHeight="1">
-      <c r="A15" s="147" t="s">
+      <c r="A15" s="153" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="147"/>
-      <c r="G15" s="147"/>
-      <c r="H15" s="147"/>
-      <c r="I15" s="147"/>
-      <c r="J15" s="147"/>
-      <c r="K15" s="147"/>
-      <c r="L15" s="147"/>
-      <c r="M15" s="147"/>
-      <c r="N15" s="147"/>
-      <c r="O15" s="147"/>
-      <c r="P15" s="147"/>
-      <c r="Q15" s="147"/>
-      <c r="R15" s="147"/>
-      <c r="S15" s="147"/>
-      <c r="T15" s="147"/>
-      <c r="U15" s="147"/>
-      <c r="V15" s="147"/>
-      <c r="W15" s="147"/>
-      <c r="X15" s="147"/>
-      <c r="Y15" s="147"/>
-      <c r="Z15" s="147"/>
-      <c r="AA15" s="147"/>
-      <c r="AB15" s="147"/>
-      <c r="AC15" s="147"/>
-      <c r="AD15" s="147"/>
-      <c r="AE15" s="147"/>
-      <c r="AF15" s="147"/>
-      <c r="AG15" s="147"/>
-      <c r="AH15" s="147"/>
-      <c r="AI15" s="147"/>
-      <c r="AJ15" s="147"/>
-      <c r="AK15" s="147"/>
-      <c r="AL15" s="147"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
+      <c r="F15" s="153"/>
+      <c r="G15" s="153"/>
+      <c r="H15" s="153"/>
+      <c r="I15" s="153"/>
+      <c r="J15" s="153"/>
+      <c r="K15" s="153"/>
+      <c r="L15" s="153"/>
+      <c r="M15" s="153"/>
+      <c r="N15" s="153"/>
+      <c r="O15" s="153"/>
+      <c r="P15" s="153"/>
+      <c r="Q15" s="153"/>
+      <c r="R15" s="153"/>
+      <c r="S15" s="153"/>
+      <c r="T15" s="153"/>
+      <c r="U15" s="153"/>
+      <c r="V15" s="153"/>
+      <c r="W15" s="153"/>
+      <c r="X15" s="153"/>
+      <c r="Y15" s="153"/>
+      <c r="Z15" s="153"/>
+      <c r="AA15" s="153"/>
+      <c r="AB15" s="153"/>
+      <c r="AC15" s="153"/>
+      <c r="AD15" s="153"/>
+      <c r="AE15" s="153"/>
+      <c r="AF15" s="153"/>
+      <c r="AG15" s="153"/>
+      <c r="AH15" s="153"/>
+      <c r="AI15" s="153"/>
+      <c r="AJ15" s="153"/>
+      <c r="AK15" s="153"/>
+      <c r="AL15" s="153"/>
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
-      <c r="A16" s="147" t="s">
+      <c r="A16" s="153" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="147"/>
-      <c r="C16" s="147"/>
-      <c r="D16" s="147"/>
-      <c r="E16" s="147"/>
-      <c r="F16" s="147"/>
-      <c r="G16" s="147"/>
-      <c r="H16" s="147"/>
-      <c r="I16" s="147"/>
-      <c r="J16" s="147"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="147"/>
-      <c r="M16" s="147"/>
-      <c r="N16" s="147"/>
-      <c r="O16" s="147"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="147"/>
-      <c r="R16" s="147"/>
-      <c r="S16" s="147"/>
-      <c r="T16" s="147"/>
-      <c r="U16" s="147"/>
-      <c r="V16" s="147"/>
-      <c r="W16" s="147"/>
-      <c r="X16" s="147"/>
-      <c r="Y16" s="147"/>
-      <c r="Z16" s="147"/>
-      <c r="AA16" s="147"/>
-      <c r="AB16" s="147"/>
-      <c r="AC16" s="147"/>
-      <c r="AD16" s="147"/>
-      <c r="AE16" s="147"/>
-      <c r="AF16" s="147"/>
-      <c r="AG16" s="147"/>
-      <c r="AH16" s="147"/>
-      <c r="AI16" s="147"/>
-      <c r="AJ16" s="147"/>
-      <c r="AK16" s="147"/>
-      <c r="AL16" s="147"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="153"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="153"/>
+      <c r="K16" s="153"/>
+      <c r="L16" s="153"/>
+      <c r="M16" s="153"/>
+      <c r="N16" s="153"/>
+      <c r="O16" s="153"/>
+      <c r="P16" s="153"/>
+      <c r="Q16" s="153"/>
+      <c r="R16" s="153"/>
+      <c r="S16" s="153"/>
+      <c r="T16" s="153"/>
+      <c r="U16" s="153"/>
+      <c r="V16" s="153"/>
+      <c r="W16" s="153"/>
+      <c r="X16" s="153"/>
+      <c r="Y16" s="153"/>
+      <c r="Z16" s="153"/>
+      <c r="AA16" s="153"/>
+      <c r="AB16" s="153"/>
+      <c r="AC16" s="153"/>
+      <c r="AD16" s="153"/>
+      <c r="AE16" s="153"/>
+      <c r="AF16" s="153"/>
+      <c r="AG16" s="153"/>
+      <c r="AH16" s="153"/>
+      <c r="AI16" s="153"/>
+      <c r="AJ16" s="153"/>
+      <c r="AK16" s="153"/>
+      <c r="AL16" s="153"/>
     </row>
     <row r="17" spans="1:38" ht="18" customHeight="1">
-      <c r="A17" s="147" t="s">
+      <c r="A17" s="153" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="147"/>
-      <c r="D17" s="147"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="147"/>
-      <c r="H17" s="147"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="147"/>
-      <c r="K17" s="147"/>
-      <c r="L17" s="147"/>
-      <c r="M17" s="147"/>
-      <c r="N17" s="147"/>
-      <c r="O17" s="147"/>
-      <c r="P17" s="147"/>
-      <c r="Q17" s="147"/>
-      <c r="R17" s="147"/>
-      <c r="S17" s="147"/>
-      <c r="T17" s="147"/>
-      <c r="U17" s="147"/>
-      <c r="V17" s="147"/>
-      <c r="W17" s="147"/>
-      <c r="X17" s="147"/>
-      <c r="Y17" s="147"/>
-      <c r="Z17" s="147"/>
-      <c r="AA17" s="147"/>
-      <c r="AB17" s="147"/>
-      <c r="AC17" s="147"/>
-      <c r="AD17" s="147"/>
-      <c r="AE17" s="147"/>
-      <c r="AF17" s="147"/>
-      <c r="AG17" s="147"/>
-      <c r="AH17" s="147"/>
-      <c r="AI17" s="147"/>
-      <c r="AJ17" s="147"/>
-      <c r="AK17" s="147"/>
-      <c r="AL17" s="147"/>
+      <c r="B17" s="153"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="153"/>
+      <c r="K17" s="153"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="153"/>
+      <c r="N17" s="153"/>
+      <c r="O17" s="153"/>
+      <c r="P17" s="153"/>
+      <c r="Q17" s="153"/>
+      <c r="R17" s="153"/>
+      <c r="S17" s="153"/>
+      <c r="T17" s="153"/>
+      <c r="U17" s="153"/>
+      <c r="V17" s="153"/>
+      <c r="W17" s="153"/>
+      <c r="X17" s="153"/>
+      <c r="Y17" s="153"/>
+      <c r="Z17" s="153"/>
+      <c r="AA17" s="153"/>
+      <c r="AB17" s="153"/>
+      <c r="AC17" s="153"/>
+      <c r="AD17" s="153"/>
+      <c r="AE17" s="153"/>
+      <c r="AF17" s="153"/>
+      <c r="AG17" s="153"/>
+      <c r="AH17" s="153"/>
+      <c r="AI17" s="153"/>
+      <c r="AJ17" s="153"/>
+      <c r="AK17" s="153"/>
+      <c r="AL17" s="153"/>
     </row>
     <row r="18" spans="1:38" ht="18" customHeight="1">
-      <c r="A18" s="147" t="s">
+      <c r="A18" s="153" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="147"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="147"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="147"/>
-      <c r="L18" s="147"/>
-      <c r="M18" s="147"/>
-      <c r="N18" s="147"/>
-      <c r="O18" s="147"/>
-      <c r="P18" s="147"/>
-      <c r="Q18" s="147"/>
-      <c r="R18" s="147"/>
-      <c r="S18" s="147"/>
-      <c r="T18" s="147"/>
-      <c r="U18" s="147"/>
-      <c r="V18" s="147"/>
-      <c r="W18" s="147"/>
-      <c r="X18" s="147"/>
-      <c r="Y18" s="147"/>
-      <c r="Z18" s="147"/>
-      <c r="AA18" s="147"/>
-      <c r="AB18" s="147"/>
-      <c r="AC18" s="147"/>
-      <c r="AD18" s="147"/>
-      <c r="AE18" s="147"/>
-      <c r="AF18" s="147"/>
-      <c r="AG18" s="147"/>
-      <c r="AH18" s="147"/>
-      <c r="AI18" s="147"/>
-      <c r="AJ18" s="147"/>
-      <c r="AK18" s="147"/>
-      <c r="AL18" s="147"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="153"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="153"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="153"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="153"/>
+      <c r="K18" s="153"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="153"/>
+      <c r="N18" s="153"/>
+      <c r="O18" s="153"/>
+      <c r="P18" s="153"/>
+      <c r="Q18" s="153"/>
+      <c r="R18" s="153"/>
+      <c r="S18" s="153"/>
+      <c r="T18" s="153"/>
+      <c r="U18" s="153"/>
+      <c r="V18" s="153"/>
+      <c r="W18" s="153"/>
+      <c r="X18" s="153"/>
+      <c r="Y18" s="153"/>
+      <c r="Z18" s="153"/>
+      <c r="AA18" s="153"/>
+      <c r="AB18" s="153"/>
+      <c r="AC18" s="153"/>
+      <c r="AD18" s="153"/>
+      <c r="AE18" s="153"/>
+      <c r="AF18" s="153"/>
+      <c r="AG18" s="153"/>
+      <c r="AH18" s="153"/>
+      <c r="AI18" s="153"/>
+      <c r="AJ18" s="153"/>
+      <c r="AK18" s="153"/>
+      <c r="AL18" s="153"/>
     </row>
     <row r="19" spans="1:38" ht="18" customHeight="1">
-      <c r="A19" s="147" t="s">
+      <c r="A19" s="153" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="147"/>
-      <c r="C19" s="147"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="147"/>
-      <c r="F19" s="147"/>
-      <c r="G19" s="147"/>
-      <c r="H19" s="147"/>
-      <c r="I19" s="147"/>
-      <c r="J19" s="147"/>
-      <c r="K19" s="147"/>
-      <c r="L19" s="147"/>
-      <c r="M19" s="147"/>
-      <c r="N19" s="147"/>
-      <c r="O19" s="147"/>
-      <c r="P19" s="147"/>
-      <c r="Q19" s="147"/>
-      <c r="R19" s="147"/>
-      <c r="S19" s="147"/>
-      <c r="T19" s="147"/>
-      <c r="U19" s="147"/>
-      <c r="V19" s="147"/>
-      <c r="W19" s="147"/>
-      <c r="X19" s="147"/>
-      <c r="Y19" s="147"/>
-      <c r="Z19" s="147"/>
-      <c r="AA19" s="147"/>
-      <c r="AB19" s="147"/>
-      <c r="AC19" s="147"/>
-      <c r="AD19" s="147"/>
-      <c r="AE19" s="147"/>
-      <c r="AF19" s="147"/>
-      <c r="AG19" s="147"/>
-      <c r="AH19" s="147"/>
-      <c r="AI19" s="147"/>
-      <c r="AJ19" s="147"/>
-      <c r="AK19" s="147"/>
-      <c r="AL19" s="147"/>
+      <c r="B19" s="153"/>
+      <c r="C19" s="153"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="153"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="153"/>
+      <c r="K19" s="153"/>
+      <c r="L19" s="153"/>
+      <c r="M19" s="153"/>
+      <c r="N19" s="153"/>
+      <c r="O19" s="153"/>
+      <c r="P19" s="153"/>
+      <c r="Q19" s="153"/>
+      <c r="R19" s="153"/>
+      <c r="S19" s="153"/>
+      <c r="T19" s="153"/>
+      <c r="U19" s="153"/>
+      <c r="V19" s="153"/>
+      <c r="W19" s="153"/>
+      <c r="X19" s="153"/>
+      <c r="Y19" s="153"/>
+      <c r="Z19" s="153"/>
+      <c r="AA19" s="153"/>
+      <c r="AB19" s="153"/>
+      <c r="AC19" s="153"/>
+      <c r="AD19" s="153"/>
+      <c r="AE19" s="153"/>
+      <c r="AF19" s="153"/>
+      <c r="AG19" s="153"/>
+      <c r="AH19" s="153"/>
+      <c r="AI19" s="153"/>
+      <c r="AJ19" s="153"/>
+      <c r="AK19" s="153"/>
+      <c r="AL19" s="153"/>
     </row>
     <row r="20" spans="1:38" ht="18" customHeight="1">
-      <c r="A20" s="147" t="s">
+      <c r="A20" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="147"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="147"/>
-      <c r="F20" s="147"/>
-      <c r="G20" s="147"/>
-      <c r="H20" s="147"/>
-      <c r="I20" s="147"/>
-      <c r="J20" s="147"/>
-      <c r="K20" s="147"/>
-      <c r="L20" s="147"/>
-      <c r="M20" s="147"/>
-      <c r="N20" s="147"/>
-      <c r="O20" s="147"/>
-      <c r="P20" s="147"/>
-      <c r="Q20" s="147"/>
-      <c r="R20" s="147"/>
-      <c r="S20" s="147"/>
-      <c r="T20" s="147"/>
-      <c r="U20" s="147"/>
-      <c r="V20" s="147"/>
-      <c r="W20" s="147"/>
-      <c r="X20" s="147"/>
-      <c r="Y20" s="147"/>
-      <c r="Z20" s="147"/>
-      <c r="AA20" s="147"/>
-      <c r="AB20" s="147"/>
-      <c r="AC20" s="147"/>
-      <c r="AD20" s="147"/>
-      <c r="AE20" s="147"/>
-      <c r="AF20" s="147"/>
-      <c r="AG20" s="147"/>
-      <c r="AH20" s="147"/>
-      <c r="AI20" s="147"/>
-      <c r="AJ20" s="147"/>
-      <c r="AK20" s="147"/>
-      <c r="AL20" s="147"/>
+      <c r="B20" s="153"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="153"/>
+      <c r="J20" s="153"/>
+      <c r="K20" s="153"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="153"/>
+      <c r="N20" s="153"/>
+      <c r="O20" s="153"/>
+      <c r="P20" s="153"/>
+      <c r="Q20" s="153"/>
+      <c r="R20" s="153"/>
+      <c r="S20" s="153"/>
+      <c r="T20" s="153"/>
+      <c r="U20" s="153"/>
+      <c r="V20" s="153"/>
+      <c r="W20" s="153"/>
+      <c r="X20" s="153"/>
+      <c r="Y20" s="153"/>
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="153"/>
+      <c r="AB20" s="153"/>
+      <c r="AC20" s="153"/>
+      <c r="AD20" s="153"/>
+      <c r="AE20" s="153"/>
+      <c r="AF20" s="153"/>
+      <c r="AG20" s="153"/>
+      <c r="AH20" s="153"/>
+      <c r="AI20" s="153"/>
+      <c r="AJ20" s="153"/>
+      <c r="AK20" s="153"/>
+      <c r="AL20" s="153"/>
     </row>
     <row r="21" spans="1:38" ht="18" customHeight="1">
-      <c r="A21" s="147" t="s">
+      <c r="A21" s="153" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="147"/>
-      <c r="C21" s="147"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="147"/>
-      <c r="F21" s="147"/>
-      <c r="G21" s="147"/>
-      <c r="H21" s="147"/>
-      <c r="I21" s="147"/>
-      <c r="J21" s="147"/>
-      <c r="K21" s="147"/>
-      <c r="L21" s="147"/>
-      <c r="M21" s="147"/>
-      <c r="N21" s="147"/>
-      <c r="O21" s="147"/>
-      <c r="P21" s="147"/>
-      <c r="Q21" s="147"/>
-      <c r="R21" s="147"/>
-      <c r="S21" s="147"/>
-      <c r="T21" s="147"/>
-      <c r="U21" s="147"/>
-      <c r="V21" s="147"/>
-      <c r="W21" s="147"/>
-      <c r="X21" s="147"/>
-      <c r="Y21" s="147"/>
-      <c r="Z21" s="147"/>
-      <c r="AA21" s="147"/>
-      <c r="AB21" s="147"/>
-      <c r="AC21" s="147"/>
-      <c r="AD21" s="147"/>
-      <c r="AE21" s="147"/>
-      <c r="AF21" s="147"/>
-      <c r="AG21" s="147"/>
-      <c r="AH21" s="147"/>
-      <c r="AI21" s="147"/>
-      <c r="AJ21" s="147"/>
-      <c r="AK21" s="147"/>
-      <c r="AL21" s="147"/>
+      <c r="B21" s="153"/>
+      <c r="C21" s="153"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="153"/>
+      <c r="H21" s="153"/>
+      <c r="I21" s="153"/>
+      <c r="J21" s="153"/>
+      <c r="K21" s="153"/>
+      <c r="L21" s="153"/>
+      <c r="M21" s="153"/>
+      <c r="N21" s="153"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="153"/>
+      <c r="Q21" s="153"/>
+      <c r="R21" s="153"/>
+      <c r="S21" s="153"/>
+      <c r="T21" s="153"/>
+      <c r="U21" s="153"/>
+      <c r="V21" s="153"/>
+      <c r="W21" s="153"/>
+      <c r="X21" s="153"/>
+      <c r="Y21" s="153"/>
+      <c r="Z21" s="153"/>
+      <c r="AA21" s="153"/>
+      <c r="AB21" s="153"/>
+      <c r="AC21" s="153"/>
+      <c r="AD21" s="153"/>
+      <c r="AE21" s="153"/>
+      <c r="AF21" s="153"/>
+      <c r="AG21" s="153"/>
+      <c r="AH21" s="153"/>
+      <c r="AI21" s="153"/>
+      <c r="AJ21" s="153"/>
+      <c r="AK21" s="153"/>
+      <c r="AL21" s="153"/>
     </row>
     <row r="22" spans="1:38" ht="18" customHeight="1">
-      <c r="A22" s="147" t="s">
+      <c r="A22" s="153" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="147"/>
-      <c r="C22" s="147"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="147"/>
-      <c r="F22" s="147"/>
-      <c r="G22" s="147"/>
-      <c r="H22" s="147"/>
-      <c r="I22" s="147"/>
-      <c r="J22" s="147"/>
-      <c r="K22" s="147"/>
-      <c r="L22" s="147"/>
-      <c r="M22" s="147"/>
-      <c r="N22" s="147"/>
-      <c r="O22" s="147"/>
-      <c r="P22" s="147"/>
-      <c r="Q22" s="147"/>
-      <c r="R22" s="147"/>
-      <c r="S22" s="147"/>
-      <c r="T22" s="147"/>
-      <c r="U22" s="147"/>
-      <c r="V22" s="147"/>
-      <c r="W22" s="147"/>
-      <c r="X22" s="147"/>
-      <c r="Y22" s="147"/>
-      <c r="Z22" s="147"/>
-      <c r="AA22" s="147"/>
-      <c r="AB22" s="147"/>
-      <c r="AC22" s="147"/>
-      <c r="AD22" s="147"/>
-      <c r="AE22" s="147"/>
-      <c r="AF22" s="147"/>
-      <c r="AG22" s="147"/>
-      <c r="AH22" s="147"/>
-      <c r="AI22" s="147"/>
-      <c r="AJ22" s="147"/>
-      <c r="AK22" s="147"/>
-      <c r="AL22" s="147"/>
+      <c r="B22" s="153"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="153"/>
+      <c r="H22" s="153"/>
+      <c r="I22" s="153"/>
+      <c r="J22" s="153"/>
+      <c r="K22" s="153"/>
+      <c r="L22" s="153"/>
+      <c r="M22" s="153"/>
+      <c r="N22" s="153"/>
+      <c r="O22" s="153"/>
+      <c r="P22" s="153"/>
+      <c r="Q22" s="153"/>
+      <c r="R22" s="153"/>
+      <c r="S22" s="153"/>
+      <c r="T22" s="153"/>
+      <c r="U22" s="153"/>
+      <c r="V22" s="153"/>
+      <c r="W22" s="153"/>
+      <c r="X22" s="153"/>
+      <c r="Y22" s="153"/>
+      <c r="Z22" s="153"/>
+      <c r="AA22" s="153"/>
+      <c r="AB22" s="153"/>
+      <c r="AC22" s="153"/>
+      <c r="AD22" s="153"/>
+      <c r="AE22" s="153"/>
+      <c r="AF22" s="153"/>
+      <c r="AG22" s="153"/>
+      <c r="AH22" s="153"/>
+      <c r="AI22" s="153"/>
+      <c r="AJ22" s="153"/>
+      <c r="AK22" s="153"/>
+      <c r="AL22" s="153"/>
     </row>
     <row r="23" spans="1:38" ht="14.4">
       <c r="A23" s="6" t="s">
@@ -13082,146 +13089,146 @@
       </c>
     </row>
     <row r="24" spans="1:38">
-      <c r="A24" s="138" t="s">
+      <c r="A24" s="144" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="138"/>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="138"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="146" t="s">
+      <c r="B24" s="144"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="145" t="s">
         <v>149</v>
       </c>
-      <c r="J24" s="146"/>
-      <c r="K24" s="146"/>
-      <c r="L24" s="146"/>
-      <c r="M24" s="146"/>
-      <c r="N24" s="146"/>
-      <c r="O24" s="138" t="s">
+      <c r="J24" s="145"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="145"/>
+      <c r="N24" s="145"/>
+      <c r="O24" s="144" t="s">
         <v>150</v>
       </c>
-      <c r="P24" s="138"/>
-      <c r="Q24" s="138"/>
-      <c r="R24" s="138"/>
-      <c r="S24" s="138"/>
-      <c r="T24" s="138"/>
-      <c r="U24" s="138"/>
-      <c r="V24" s="138"/>
-      <c r="W24" s="138"/>
-      <c r="X24" s="138"/>
-      <c r="Y24" s="138"/>
-      <c r="Z24" s="138"/>
-      <c r="AA24" s="138"/>
-      <c r="AB24" s="138"/>
-      <c r="AC24" s="138" t="s">
+      <c r="P24" s="144"/>
+      <c r="Q24" s="144"/>
+      <c r="R24" s="144"/>
+      <c r="S24" s="144"/>
+      <c r="T24" s="144"/>
+      <c r="U24" s="144"/>
+      <c r="V24" s="144"/>
+      <c r="W24" s="144"/>
+      <c r="X24" s="144"/>
+      <c r="Y24" s="144"/>
+      <c r="Z24" s="144"/>
+      <c r="AA24" s="144"/>
+      <c r="AB24" s="144"/>
+      <c r="AC24" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="AD24" s="138"/>
-      <c r="AE24" s="138"/>
-      <c r="AF24" s="138"/>
-      <c r="AG24" s="138"/>
-      <c r="AH24" s="138"/>
-      <c r="AI24" s="138"/>
-      <c r="AJ24" s="138"/>
-      <c r="AK24" s="138"/>
-      <c r="AL24" s="138"/>
+      <c r="AD24" s="144"/>
+      <c r="AE24" s="144"/>
+      <c r="AF24" s="144"/>
+      <c r="AG24" s="144"/>
+      <c r="AH24" s="144"/>
+      <c r="AI24" s="144"/>
+      <c r="AJ24" s="144"/>
+      <c r="AK24" s="144"/>
+      <c r="AL24" s="144"/>
     </row>
     <row r="25" spans="1:38">
-      <c r="A25" s="138" t="s">
+      <c r="A25" s="144" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="138"/>
-      <c r="C25" s="138"/>
-      <c r="D25" s="138"/>
-      <c r="E25" s="138"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="138"/>
-      <c r="I25" s="138">
+      <c r="B25" s="144"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="144"/>
+      <c r="E25" s="144"/>
+      <c r="F25" s="144"/>
+      <c r="G25" s="144"/>
+      <c r="H25" s="144"/>
+      <c r="I25" s="144">
         <v>20</v>
       </c>
-      <c r="J25" s="138"/>
-      <c r="K25" s="138"/>
-      <c r="L25" s="138"/>
-      <c r="M25" s="138"/>
-      <c r="N25" s="138"/>
-      <c r="O25" s="143" t="s">
+      <c r="J25" s="144"/>
+      <c r="K25" s="144"/>
+      <c r="L25" s="144"/>
+      <c r="M25" s="144"/>
+      <c r="N25" s="144"/>
+      <c r="O25" s="159" t="s">
         <v>152</v>
       </c>
-      <c r="P25" s="144"/>
-      <c r="Q25" s="144"/>
-      <c r="R25" s="144"/>
-      <c r="S25" s="144"/>
-      <c r="T25" s="144"/>
-      <c r="U25" s="144"/>
-      <c r="V25" s="144"/>
-      <c r="W25" s="144"/>
-      <c r="X25" s="144"/>
-      <c r="Y25" s="145"/>
-      <c r="Z25" s="143">
+      <c r="P25" s="160"/>
+      <c r="Q25" s="160"/>
+      <c r="R25" s="160"/>
+      <c r="S25" s="160"/>
+      <c r="T25" s="160"/>
+      <c r="U25" s="160"/>
+      <c r="V25" s="160"/>
+      <c r="W25" s="160"/>
+      <c r="X25" s="160"/>
+      <c r="Y25" s="161"/>
+      <c r="Z25" s="159">
         <v>100</v>
       </c>
-      <c r="AA25" s="144"/>
-      <c r="AB25" s="145"/>
-      <c r="AC25" s="138" t="s">
+      <c r="AA25" s="160"/>
+      <c r="AB25" s="161"/>
+      <c r="AC25" s="144" t="s">
         <v>154</v>
       </c>
-      <c r="AD25" s="138"/>
-      <c r="AE25" s="138"/>
-      <c r="AF25" s="138"/>
-      <c r="AG25" s="138"/>
-      <c r="AH25" s="138"/>
-      <c r="AI25" s="138"/>
-      <c r="AJ25" s="138"/>
-      <c r="AK25" s="138"/>
-      <c r="AL25" s="138"/>
+      <c r="AD25" s="144"/>
+      <c r="AE25" s="144"/>
+      <c r="AF25" s="144"/>
+      <c r="AG25" s="144"/>
+      <c r="AH25" s="144"/>
+      <c r="AI25" s="144"/>
+      <c r="AJ25" s="144"/>
+      <c r="AK25" s="144"/>
+      <c r="AL25" s="144"/>
     </row>
     <row r="26" spans="1:38">
-      <c r="A26" s="138"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="138"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="138"/>
-      <c r="I26" s="138"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="138"/>
-      <c r="L26" s="138"/>
-      <c r="M26" s="138"/>
-      <c r="N26" s="138"/>
-      <c r="O26" s="143" t="s">
+      <c r="A26" s="144"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="144"/>
+      <c r="E26" s="144"/>
+      <c r="F26" s="144"/>
+      <c r="G26" s="144"/>
+      <c r="H26" s="144"/>
+      <c r="I26" s="144"/>
+      <c r="J26" s="144"/>
+      <c r="K26" s="144"/>
+      <c r="L26" s="144"/>
+      <c r="M26" s="144"/>
+      <c r="N26" s="144"/>
+      <c r="O26" s="159" t="s">
         <v>153</v>
       </c>
-      <c r="P26" s="144"/>
-      <c r="Q26" s="144"/>
-      <c r="R26" s="144"/>
-      <c r="S26" s="144"/>
-      <c r="T26" s="144"/>
-      <c r="U26" s="144"/>
-      <c r="V26" s="144"/>
-      <c r="W26" s="144"/>
-      <c r="X26" s="144"/>
-      <c r="Y26" s="145"/>
-      <c r="Z26" s="143">
+      <c r="P26" s="160"/>
+      <c r="Q26" s="160"/>
+      <c r="R26" s="160"/>
+      <c r="S26" s="160"/>
+      <c r="T26" s="160"/>
+      <c r="U26" s="160"/>
+      <c r="V26" s="160"/>
+      <c r="W26" s="160"/>
+      <c r="X26" s="160"/>
+      <c r="Y26" s="161"/>
+      <c r="Z26" s="159">
         <v>200</v>
       </c>
-      <c r="AA26" s="144"/>
-      <c r="AB26" s="145"/>
-      <c r="AC26" s="138"/>
-      <c r="AD26" s="138"/>
-      <c r="AE26" s="138"/>
-      <c r="AF26" s="138"/>
-      <c r="AG26" s="138"/>
-      <c r="AH26" s="138"/>
-      <c r="AI26" s="138"/>
-      <c r="AJ26" s="138"/>
-      <c r="AK26" s="138"/>
-      <c r="AL26" s="138"/>
+      <c r="AA26" s="160"/>
+      <c r="AB26" s="161"/>
+      <c r="AC26" s="144"/>
+      <c r="AD26" s="144"/>
+      <c r="AE26" s="144"/>
+      <c r="AF26" s="144"/>
+      <c r="AG26" s="144"/>
+      <c r="AH26" s="144"/>
+      <c r="AI26" s="144"/>
+      <c r="AJ26" s="144"/>
+      <c r="AK26" s="144"/>
+      <c r="AL26" s="144"/>
     </row>
     <row r="27" spans="1:38">
       <c r="A27" s="6" t="s">
@@ -13230,14 +13237,77 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="U10:Z10"/>
-    <mergeCell ref="AA10:AF10"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="I7:O7"/>
-    <mergeCell ref="AG10:AL10"/>
+    <mergeCell ref="AC24:AL24"/>
+    <mergeCell ref="A25:H26"/>
+    <mergeCell ref="I25:N26"/>
+    <mergeCell ref="AC25:AL26"/>
+    <mergeCell ref="Z25:AB25"/>
+    <mergeCell ref="Z26:AB26"/>
+    <mergeCell ref="O25:Y25"/>
+    <mergeCell ref="O26:Y26"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="O24:AB24"/>
+    <mergeCell ref="AG22:AL22"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="I21:N21"/>
+    <mergeCell ref="O21:T21"/>
+    <mergeCell ref="U21:Z21"/>
+    <mergeCell ref="AA21:AF21"/>
+    <mergeCell ref="AG21:AL21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="I22:N22"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="U22:Z22"/>
+    <mergeCell ref="AA22:AF22"/>
+    <mergeCell ref="AG20:AL20"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="U19:Z19"/>
+    <mergeCell ref="AA19:AF19"/>
+    <mergeCell ref="AG19:AL19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="I20:N20"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="U20:Z20"/>
+    <mergeCell ref="AA20:AF20"/>
+    <mergeCell ref="AG18:AL18"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="U17:Z17"/>
+    <mergeCell ref="AA17:AF17"/>
+    <mergeCell ref="AG17:AL17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="AA18:AF18"/>
+    <mergeCell ref="AG16:AL16"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:T15"/>
+    <mergeCell ref="U15:Z15"/>
+    <mergeCell ref="AA15:AF15"/>
+    <mergeCell ref="AG15:AL15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="AA16:AF16"/>
+    <mergeCell ref="AG13:AL13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="U14:Z14"/>
+    <mergeCell ref="AA14:AF14"/>
+    <mergeCell ref="AG14:AL14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="U13:Z13"/>
+    <mergeCell ref="AA13:AF13"/>
     <mergeCell ref="AG12:AL12"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="I11:N11"/>
@@ -13254,79 +13324,16 @@
     <mergeCell ref="U12:Z12"/>
     <mergeCell ref="AA12:AF12"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="AG13:AL13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="U14:Z14"/>
-    <mergeCell ref="AA14:AF14"/>
-    <mergeCell ref="AG14:AL14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="U13:Z13"/>
-    <mergeCell ref="AA13:AF13"/>
-    <mergeCell ref="AG16:AL16"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:T15"/>
-    <mergeCell ref="U15:Z15"/>
-    <mergeCell ref="AA15:AF15"/>
-    <mergeCell ref="AG15:AL15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="AA16:AF16"/>
-    <mergeCell ref="AG18:AL18"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="U17:Z17"/>
-    <mergeCell ref="AA17:AF17"/>
-    <mergeCell ref="AG17:AL17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="U18:Z18"/>
-    <mergeCell ref="AA18:AF18"/>
-    <mergeCell ref="AG20:AL20"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="U19:Z19"/>
-    <mergeCell ref="AA19:AF19"/>
-    <mergeCell ref="AG19:AL19"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="I20:N20"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="U20:Z20"/>
-    <mergeCell ref="AA20:AF20"/>
-    <mergeCell ref="AG22:AL22"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="I21:N21"/>
-    <mergeCell ref="O21:T21"/>
-    <mergeCell ref="U21:Z21"/>
-    <mergeCell ref="AA21:AF21"/>
-    <mergeCell ref="AG21:AL21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="I22:N22"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="U22:Z22"/>
-    <mergeCell ref="AA22:AF22"/>
-    <mergeCell ref="AC24:AL24"/>
-    <mergeCell ref="A25:H26"/>
-    <mergeCell ref="I25:N26"/>
-    <mergeCell ref="AC25:AL26"/>
-    <mergeCell ref="Z25:AB25"/>
-    <mergeCell ref="Z26:AB26"/>
-    <mergeCell ref="O25:Y25"/>
-    <mergeCell ref="O26:Y26"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="O24:AB24"/>
+    <mergeCell ref="U10:Z10"/>
+    <mergeCell ref="AA10:AF10"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="F5:K5"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="AG10:AL10"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -13365,32 +13372,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="142"/>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="142"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="142"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="142"/>
-      <c r="AF1" s="142"/>
-      <c r="AG1" s="142"/>
-      <c r="AH1" s="142"/>
-      <c r="AI1" s="142"/>
-      <c r="AJ1" s="142"/>
-      <c r="AK1" s="142"/>
-      <c r="AL1" s="142"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="149"/>
+      <c r="Y1" s="149"/>
+      <c r="Z1" s="149"/>
+      <c r="AA1" s="149"/>
+      <c r="AB1" s="149"/>
+      <c r="AC1" s="149"/>
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="149"/>
+      <c r="AJ1" s="149"/>
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="33" t="s">
@@ -13432,17 +13439,17 @@
       <c r="AL2" s="34"/>
     </row>
     <row r="3" spans="1:38">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
+      <c r="A3" s="146"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -13599,9 +13606,9 @@
       <c r="A7" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="142"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="142"/>
+      <c r="E7" s="149"/>
+      <c r="F7" s="149"/>
+      <c r="G7" s="149"/>
       <c r="H7" s="63" t="s">
         <v>113</v>
       </c>
@@ -13672,12 +13679,12 @@
       <c r="AF8" s="171"/>
       <c r="AG8" s="171"/>
       <c r="AH8" s="171"/>
-      <c r="AI8" s="165" t="s">
+      <c r="AI8" s="172" t="s">
         <v>116</v>
       </c>
-      <c r="AJ8" s="166"/>
-      <c r="AK8" s="166"/>
-      <c r="AL8" s="167"/>
+      <c r="AJ8" s="173"/>
+      <c r="AK8" s="173"/>
+      <c r="AL8" s="174"/>
     </row>
     <row r="9" spans="1:38">
       <c r="A9" s="171"/>
@@ -13724,17 +13731,17 @@
       <c r="AF9" s="171"/>
       <c r="AG9" s="171"/>
       <c r="AH9" s="171"/>
-      <c r="AI9" s="168"/>
-      <c r="AJ9" s="169"/>
-      <c r="AK9" s="169"/>
-      <c r="AL9" s="170"/>
+      <c r="AI9" s="175"/>
+      <c r="AJ9" s="176"/>
+      <c r="AK9" s="176"/>
+      <c r="AL9" s="177"/>
     </row>
     <row r="10" spans="1:38">
-      <c r="A10" s="156"/>
-      <c r="B10" s="157"/>
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="158"/>
+      <c r="A10" s="165"/>
+      <c r="B10" s="166"/>
+      <c r="C10" s="166"/>
+      <c r="D10" s="166"/>
+      <c r="E10" s="167"/>
       <c r="F10" s="163" t="s">
         <v>117</v>
       </c>
@@ -13772,11 +13779,11 @@
       <c r="AL10" s="164"/>
     </row>
     <row r="11" spans="1:38" ht="16.2">
-      <c r="A11" s="159"/>
-      <c r="B11" s="160"/>
-      <c r="C11" s="160"/>
-      <c r="D11" s="160"/>
-      <c r="E11" s="161"/>
+      <c r="A11" s="168"/>
+      <c r="B11" s="169"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="170"/>
       <c r="F11" s="163" t="s">
         <v>118</v>
       </c>
@@ -13814,11 +13821,11 @@
       <c r="AL11" s="164"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="156"/>
-      <c r="B12" s="157"/>
-      <c r="C12" s="157"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="158"/>
+      <c r="A12" s="165"/>
+      <c r="B12" s="166"/>
+      <c r="C12" s="166"/>
+      <c r="D12" s="166"/>
+      <c r="E12" s="167"/>
       <c r="F12" s="163" t="s">
         <v>117</v>
       </c>
@@ -13856,11 +13863,11 @@
       <c r="AL12" s="164"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="159"/>
-      <c r="B13" s="160"/>
-      <c r="C13" s="160"/>
-      <c r="D13" s="160"/>
-      <c r="E13" s="161"/>
+      <c r="A13" s="168"/>
+      <c r="B13" s="169"/>
+      <c r="C13" s="169"/>
+      <c r="D13" s="169"/>
+      <c r="E13" s="170"/>
       <c r="F13" s="163" t="s">
         <v>118</v>
       </c>
@@ -13941,9 +13948,9 @@
       <c r="A15" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
-      <c r="G15" s="142"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="149"/>
       <c r="H15" s="63" t="s">
         <v>113</v>
       </c>
@@ -14014,12 +14021,12 @@
       <c r="AF16" s="171"/>
       <c r="AG16" s="171"/>
       <c r="AH16" s="171"/>
-      <c r="AI16" s="165" t="s">
+      <c r="AI16" s="172" t="s">
         <v>116</v>
       </c>
-      <c r="AJ16" s="166"/>
-      <c r="AK16" s="166"/>
-      <c r="AL16" s="167"/>
+      <c r="AJ16" s="173"/>
+      <c r="AK16" s="173"/>
+      <c r="AL16" s="174"/>
     </row>
     <row r="17" spans="1:38">
       <c r="A17" s="171"/>
@@ -14066,17 +14073,17 @@
       <c r="AF17" s="171"/>
       <c r="AG17" s="171"/>
       <c r="AH17" s="171"/>
-      <c r="AI17" s="168"/>
-      <c r="AJ17" s="169"/>
-      <c r="AK17" s="169"/>
-      <c r="AL17" s="170"/>
+      <c r="AI17" s="175"/>
+      <c r="AJ17" s="176"/>
+      <c r="AK17" s="176"/>
+      <c r="AL17" s="177"/>
     </row>
     <row r="18" spans="1:38">
-      <c r="A18" s="156"/>
-      <c r="B18" s="157"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
-      <c r="E18" s="158"/>
+      <c r="A18" s="165"/>
+      <c r="B18" s="166"/>
+      <c r="C18" s="166"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="167"/>
       <c r="F18" s="163" t="s">
         <v>117</v>
       </c>
@@ -14114,11 +14121,11 @@
       <c r="AL18" s="164"/>
     </row>
     <row r="19" spans="1:38" ht="16.2">
-      <c r="A19" s="159"/>
-      <c r="B19" s="160"/>
-      <c r="C19" s="160"/>
-      <c r="D19" s="160"/>
-      <c r="E19" s="161"/>
+      <c r="A19" s="168"/>
+      <c r="B19" s="169"/>
+      <c r="C19" s="169"/>
+      <c r="D19" s="169"/>
+      <c r="E19" s="170"/>
       <c r="F19" s="163" t="s">
         <v>118</v>
       </c>
@@ -14156,11 +14163,11 @@
       <c r="AL19" s="164"/>
     </row>
     <row r="20" spans="1:38">
-      <c r="A20" s="156"/>
-      <c r="B20" s="157"/>
-      <c r="C20" s="157"/>
-      <c r="D20" s="157"/>
-      <c r="E20" s="158"/>
+      <c r="A20" s="165"/>
+      <c r="B20" s="166"/>
+      <c r="C20" s="166"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="167"/>
       <c r="F20" s="163" t="s">
         <v>117</v>
       </c>
@@ -14198,11 +14205,11 @@
       <c r="AL20" s="164"/>
     </row>
     <row r="21" spans="1:38" ht="16.2">
-      <c r="A21" s="159"/>
-      <c r="B21" s="160"/>
-      <c r="C21" s="160"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="161"/>
+      <c r="A21" s="168"/>
+      <c r="B21" s="169"/>
+      <c r="C21" s="169"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="170"/>
       <c r="F21" s="163" t="s">
         <v>118</v>
       </c>
@@ -14562,72 +14569,6 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="Y13:AC13"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="AI13:AL13"/>
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="AI11:AL11"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="AI10:AL10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="A12:E13"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:I9"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="AI8:AL9"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:N20"/>
-    <mergeCell ref="O20:S20"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="AI21:AL21"/>
-    <mergeCell ref="J21:N21"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="Y21:AC21"/>
-    <mergeCell ref="AD21:AH21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A16:E17"/>
-    <mergeCell ref="F16:I17"/>
-    <mergeCell ref="J16:AH16"/>
-    <mergeCell ref="J17:N17"/>
-    <mergeCell ref="O17:S17"/>
-    <mergeCell ref="T17:X17"/>
-    <mergeCell ref="Y17:AC17"/>
-    <mergeCell ref="AD17:AH17"/>
-    <mergeCell ref="AI19:AL19"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="J18:N18"/>
-    <mergeCell ref="O18:S18"/>
-    <mergeCell ref="T18:X18"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="Y18:AC18"/>
     <mergeCell ref="M1:AL1"/>
@@ -14644,8 +14585,74 @@
     <mergeCell ref="T19:X19"/>
     <mergeCell ref="Y19:AC19"/>
     <mergeCell ref="AD19:AH19"/>
+    <mergeCell ref="AI19:AL19"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="J18:N18"/>
+    <mergeCell ref="O18:S18"/>
+    <mergeCell ref="T18:X18"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A16:E17"/>
+    <mergeCell ref="F16:I17"/>
+    <mergeCell ref="J16:AH16"/>
+    <mergeCell ref="J17:N17"/>
+    <mergeCell ref="O17:S17"/>
+    <mergeCell ref="T17:X17"/>
+    <mergeCell ref="Y17:AC17"/>
+    <mergeCell ref="AD17:AH17"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:N20"/>
+    <mergeCell ref="O20:S20"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="AI21:AL21"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="Y21:AC21"/>
+    <mergeCell ref="AD21:AH21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="F8:I9"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="AI8:AL9"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="A12:E13"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="AI11:AL11"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AI10:AL10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="J11:N11"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="AI12:AL12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="Y13:AC13"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="AI13:AL13"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -14684,32 +14691,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="142"/>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="142"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="142"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="142"/>
-      <c r="AF1" s="142"/>
-      <c r="AG1" s="142"/>
-      <c r="AH1" s="142"/>
-      <c r="AI1" s="142"/>
-      <c r="AJ1" s="142"/>
-      <c r="AK1" s="142"/>
-      <c r="AL1" s="142"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="149"/>
+      <c r="Y1" s="149"/>
+      <c r="Z1" s="149"/>
+      <c r="AA1" s="149"/>
+      <c r="AB1" s="149"/>
+      <c r="AC1" s="149"/>
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="149"/>
+      <c r="AJ1" s="149"/>
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
       <c r="AM1" s="67"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -14753,25 +14760,25 @@
       <c r="AM2" s="67"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="139"/>
-      <c r="O3" s="139"/>
-      <c r="P3" s="139"/>
-      <c r="Q3" s="139"/>
-      <c r="R3" s="139"/>
-      <c r="S3" s="139"/>
+      <c r="A3" s="146"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="146"/>
+      <c r="M3" s="146"/>
+      <c r="N3" s="146"/>
+      <c r="O3" s="146"/>
+      <c r="P3" s="146"/>
+      <c r="Q3" s="146"/>
+      <c r="R3" s="146"/>
+      <c r="S3" s="146"/>
       <c r="T3" s="34"/>
       <c r="U3" s="34"/>
       <c r="V3" s="34"/>
@@ -14810,442 +14817,442 @@
       <c r="A7" s="6"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="138"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="138"/>
-      <c r="E8" s="138"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="138"/>
-      <c r="J8" s="138" t="s">
+      <c r="B8" s="144"/>
+      <c r="C8" s="144"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="144"/>
+      <c r="J8" s="144" t="s">
         <v>160</v>
       </c>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="138"/>
-      <c r="N8" s="138"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="138"/>
-      <c r="R8" s="138"/>
-      <c r="S8" s="138"/>
-      <c r="T8" s="138"/>
-      <c r="U8" s="138"/>
-      <c r="V8" s="138"/>
-      <c r="W8" s="138"/>
-      <c r="X8" s="138"/>
-      <c r="Y8" s="138"/>
-      <c r="Z8" s="138"/>
-      <c r="AA8" s="138"/>
-      <c r="AB8" s="138"/>
-      <c r="AC8" s="138"/>
-      <c r="AD8" s="138"/>
-      <c r="AE8" s="138"/>
-      <c r="AF8" s="138"/>
-      <c r="AG8" s="138"/>
-      <c r="AH8" s="138"/>
-      <c r="AI8" s="138" t="s">
+      <c r="K8" s="144"/>
+      <c r="L8" s="144"/>
+      <c r="M8" s="144"/>
+      <c r="N8" s="144"/>
+      <c r="O8" s="144"/>
+      <c r="P8" s="144"/>
+      <c r="Q8" s="144"/>
+      <c r="R8" s="144"/>
+      <c r="S8" s="144"/>
+      <c r="T8" s="144"/>
+      <c r="U8" s="144"/>
+      <c r="V8" s="144"/>
+      <c r="W8" s="144"/>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="144"/>
+      <c r="Z8" s="144"/>
+      <c r="AA8" s="144"/>
+      <c r="AB8" s="144"/>
+      <c r="AC8" s="144"/>
+      <c r="AD8" s="144"/>
+      <c r="AE8" s="144"/>
+      <c r="AF8" s="144"/>
+      <c r="AG8" s="144"/>
+      <c r="AH8" s="144"/>
+      <c r="AI8" s="144" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="138"/>
-      <c r="AK8" s="138"/>
-      <c r="AL8" s="138"/>
-      <c r="AM8" s="138"/>
+      <c r="AJ8" s="144"/>
+      <c r="AK8" s="144"/>
+      <c r="AL8" s="144"/>
+      <c r="AM8" s="144"/>
     </row>
     <row r="9" spans="1:39">
-      <c r="A9" s="138"/>
-      <c r="B9" s="138"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-      <c r="J9" s="138" t="s">
+      <c r="A9" s="144"/>
+      <c r="B9" s="144"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="144"/>
+      <c r="E9" s="144"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="144"/>
+      <c r="J9" s="144" t="s">
         <v>203</v>
       </c>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138"/>
-      <c r="M9" s="138" t="s">
+      <c r="K9" s="144"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="144" t="s">
         <v>204</v>
       </c>
-      <c r="N9" s="138"/>
-      <c r="O9" s="138"/>
-      <c r="P9" s="138" t="s">
+      <c r="N9" s="144"/>
+      <c r="O9" s="144"/>
+      <c r="P9" s="144" t="s">
         <v>205</v>
       </c>
-      <c r="Q9" s="138"/>
-      <c r="R9" s="138"/>
-      <c r="S9" s="138" t="s">
+      <c r="Q9" s="144"/>
+      <c r="R9" s="144"/>
+      <c r="S9" s="144" t="s">
         <v>206</v>
       </c>
-      <c r="T9" s="138"/>
-      <c r="U9" s="138"/>
-      <c r="V9" s="138" t="s">
+      <c r="T9" s="144"/>
+      <c r="U9" s="144"/>
+      <c r="V9" s="144" t="s">
         <v>207</v>
       </c>
-      <c r="W9" s="138"/>
-      <c r="X9" s="138"/>
-      <c r="Y9" s="138" t="s">
+      <c r="W9" s="144"/>
+      <c r="X9" s="144"/>
+      <c r="Y9" s="144" t="s">
         <v>202</v>
       </c>
-      <c r="Z9" s="138"/>
-      <c r="AA9" s="138"/>
-      <c r="AB9" s="138"/>
-      <c r="AC9" s="138" t="s">
+      <c r="Z9" s="144"/>
+      <c r="AA9" s="144"/>
+      <c r="AB9" s="144"/>
+      <c r="AC9" s="144" t="s">
         <v>200</v>
       </c>
-      <c r="AD9" s="138"/>
-      <c r="AE9" s="138"/>
-      <c r="AF9" s="138"/>
-      <c r="AG9" s="138"/>
-      <c r="AH9" s="138"/>
-      <c r="AI9" s="138"/>
-      <c r="AJ9" s="138"/>
-      <c r="AK9" s="138"/>
-      <c r="AL9" s="138"/>
-      <c r="AM9" s="138"/>
+      <c r="AD9" s="144"/>
+      <c r="AE9" s="144"/>
+      <c r="AF9" s="144"/>
+      <c r="AG9" s="144"/>
+      <c r="AH9" s="144"/>
+      <c r="AI9" s="144"/>
+      <c r="AJ9" s="144"/>
+      <c r="AK9" s="144"/>
+      <c r="AL9" s="144"/>
+      <c r="AM9" s="144"/>
     </row>
     <row r="10" spans="1:39">
-      <c r="A10" s="172"/>
-      <c r="B10" s="172"/>
-      <c r="C10" s="138" t="s">
+      <c r="A10" s="178"/>
+      <c r="B10" s="178"/>
+      <c r="C10" s="144" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="138"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="138"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="138"/>
-      <c r="I10" s="138"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="138"/>
-      <c r="L10" s="138"/>
-      <c r="M10" s="138"/>
-      <c r="N10" s="138"/>
-      <c r="O10" s="138"/>
-      <c r="P10" s="138"/>
-      <c r="Q10" s="138"/>
-      <c r="R10" s="138"/>
-      <c r="S10" s="138"/>
-      <c r="T10" s="138"/>
-      <c r="U10" s="138"/>
-      <c r="V10" s="138"/>
-      <c r="W10" s="138"/>
-      <c r="X10" s="138"/>
-      <c r="Y10" s="138"/>
-      <c r="Z10" s="138"/>
-      <c r="AA10" s="138"/>
-      <c r="AB10" s="138"/>
-      <c r="AC10" s="138"/>
-      <c r="AD10" s="138"/>
-      <c r="AE10" s="138"/>
-      <c r="AF10" s="138"/>
-      <c r="AG10" s="138"/>
-      <c r="AH10" s="138"/>
-      <c r="AI10" s="138"/>
-      <c r="AJ10" s="138"/>
-      <c r="AK10" s="138"/>
-      <c r="AL10" s="138"/>
-      <c r="AM10" s="138"/>
+      <c r="D10" s="144"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="144"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="144"/>
+      <c r="L10" s="144"/>
+      <c r="M10" s="144"/>
+      <c r="N10" s="144"/>
+      <c r="O10" s="144"/>
+      <c r="P10" s="144"/>
+      <c r="Q10" s="144"/>
+      <c r="R10" s="144"/>
+      <c r="S10" s="144"/>
+      <c r="T10" s="144"/>
+      <c r="U10" s="144"/>
+      <c r="V10" s="144"/>
+      <c r="W10" s="144"/>
+      <c r="X10" s="144"/>
+      <c r="Y10" s="144"/>
+      <c r="Z10" s="144"/>
+      <c r="AA10" s="144"/>
+      <c r="AB10" s="144"/>
+      <c r="AC10" s="144"/>
+      <c r="AD10" s="144"/>
+      <c r="AE10" s="144"/>
+      <c r="AF10" s="144"/>
+      <c r="AG10" s="144"/>
+      <c r="AH10" s="144"/>
+      <c r="AI10" s="144"/>
+      <c r="AJ10" s="144"/>
+      <c r="AK10" s="144"/>
+      <c r="AL10" s="144"/>
+      <c r="AM10" s="144"/>
     </row>
     <row r="11" spans="1:39">
-      <c r="A11" s="172"/>
-      <c r="B11" s="172"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="138"/>
-      <c r="L11" s="138"/>
-      <c r="M11" s="138"/>
-      <c r="N11" s="138"/>
-      <c r="O11" s="138"/>
-      <c r="P11" s="138"/>
-      <c r="Q11" s="138"/>
-      <c r="R11" s="138"/>
-      <c r="S11" s="138"/>
-      <c r="T11" s="138"/>
-      <c r="U11" s="138"/>
-      <c r="V11" s="138"/>
-      <c r="W11" s="138"/>
-      <c r="X11" s="138"/>
-      <c r="Y11" s="138"/>
-      <c r="Z11" s="138"/>
-      <c r="AA11" s="138"/>
-      <c r="AB11" s="138"/>
-      <c r="AC11" s="138"/>
-      <c r="AD11" s="138"/>
-      <c r="AE11" s="138"/>
-      <c r="AF11" s="138"/>
-      <c r="AG11" s="138"/>
-      <c r="AH11" s="138"/>
-      <c r="AI11" s="138"/>
-      <c r="AJ11" s="138"/>
-      <c r="AK11" s="138"/>
-      <c r="AL11" s="138"/>
-      <c r="AM11" s="138"/>
+      <c r="A11" s="178"/>
+      <c r="B11" s="178"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="144"/>
+      <c r="M11" s="144"/>
+      <c r="N11" s="144"/>
+      <c r="O11" s="144"/>
+      <c r="P11" s="144"/>
+      <c r="Q11" s="144"/>
+      <c r="R11" s="144"/>
+      <c r="S11" s="144"/>
+      <c r="T11" s="144"/>
+      <c r="U11" s="144"/>
+      <c r="V11" s="144"/>
+      <c r="W11" s="144"/>
+      <c r="X11" s="144"/>
+      <c r="Y11" s="144"/>
+      <c r="Z11" s="144"/>
+      <c r="AA11" s="144"/>
+      <c r="AB11" s="144"/>
+      <c r="AC11" s="144"/>
+      <c r="AD11" s="144"/>
+      <c r="AE11" s="144"/>
+      <c r="AF11" s="144"/>
+      <c r="AG11" s="144"/>
+      <c r="AH11" s="144"/>
+      <c r="AI11" s="144"/>
+      <c r="AJ11" s="144"/>
+      <c r="AK11" s="144"/>
+      <c r="AL11" s="144"/>
+      <c r="AM11" s="144"/>
     </row>
     <row r="12" spans="1:39">
-      <c r="A12" s="172"/>
-      <c r="B12" s="172"/>
-      <c r="C12" s="138" t="s">
+      <c r="A12" s="178"/>
+      <c r="B12" s="178"/>
+      <c r="C12" s="144" t="s">
         <v>208</v>
       </c>
-      <c r="D12" s="138"/>
-      <c r="E12" s="138"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="138"/>
-      <c r="J12" s="138"/>
-      <c r="K12" s="138"/>
-      <c r="L12" s="138"/>
-      <c r="M12" s="138"/>
-      <c r="N12" s="138"/>
-      <c r="O12" s="138"/>
-      <c r="P12" s="138"/>
-      <c r="Q12" s="138"/>
-      <c r="R12" s="138"/>
-      <c r="S12" s="138"/>
-      <c r="T12" s="138"/>
-      <c r="U12" s="138"/>
-      <c r="V12" s="138"/>
-      <c r="W12" s="138"/>
-      <c r="X12" s="138"/>
-      <c r="Y12" s="138"/>
-      <c r="Z12" s="138"/>
-      <c r="AA12" s="138"/>
-      <c r="AB12" s="138"/>
-      <c r="AC12" s="138"/>
-      <c r="AD12" s="138"/>
-      <c r="AE12" s="138"/>
-      <c r="AF12" s="138"/>
-      <c r="AG12" s="138"/>
-      <c r="AH12" s="138"/>
-      <c r="AI12" s="138"/>
-      <c r="AJ12" s="138"/>
-      <c r="AK12" s="138"/>
-      <c r="AL12" s="138"/>
-      <c r="AM12" s="138"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="144"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="144"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="144"/>
+      <c r="P12" s="144"/>
+      <c r="Q12" s="144"/>
+      <c r="R12" s="144"/>
+      <c r="S12" s="144"/>
+      <c r="T12" s="144"/>
+      <c r="U12" s="144"/>
+      <c r="V12" s="144"/>
+      <c r="W12" s="144"/>
+      <c r="X12" s="144"/>
+      <c r="Y12" s="144"/>
+      <c r="Z12" s="144"/>
+      <c r="AA12" s="144"/>
+      <c r="AB12" s="144"/>
+      <c r="AC12" s="144"/>
+      <c r="AD12" s="144"/>
+      <c r="AE12" s="144"/>
+      <c r="AF12" s="144"/>
+      <c r="AG12" s="144"/>
+      <c r="AH12" s="144"/>
+      <c r="AI12" s="144"/>
+      <c r="AJ12" s="144"/>
+      <c r="AK12" s="144"/>
+      <c r="AL12" s="144"/>
+      <c r="AM12" s="144"/>
     </row>
     <row r="13" spans="1:39">
-      <c r="A13" s="172"/>
-      <c r="B13" s="172"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="138"/>
-      <c r="I13" s="138"/>
-      <c r="J13" s="138"/>
-      <c r="K13" s="138"/>
-      <c r="L13" s="138"/>
-      <c r="M13" s="138"/>
-      <c r="N13" s="138"/>
-      <c r="O13" s="138"/>
-      <c r="P13" s="138"/>
-      <c r="Q13" s="138"/>
-      <c r="R13" s="138"/>
-      <c r="S13" s="138"/>
-      <c r="T13" s="138"/>
-      <c r="U13" s="138"/>
-      <c r="V13" s="138"/>
-      <c r="W13" s="138"/>
-      <c r="X13" s="138"/>
-      <c r="Y13" s="138"/>
-      <c r="Z13" s="138"/>
-      <c r="AA13" s="138"/>
-      <c r="AB13" s="138"/>
-      <c r="AC13" s="138"/>
-      <c r="AD13" s="138"/>
-      <c r="AE13" s="138"/>
-      <c r="AF13" s="138"/>
-      <c r="AG13" s="138"/>
-      <c r="AH13" s="138"/>
-      <c r="AI13" s="138"/>
-      <c r="AJ13" s="138"/>
-      <c r="AK13" s="138"/>
-      <c r="AL13" s="138"/>
-      <c r="AM13" s="138"/>
+      <c r="A13" s="178"/>
+      <c r="B13" s="178"/>
+      <c r="C13" s="144"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="144"/>
+      <c r="N13" s="144"/>
+      <c r="O13" s="144"/>
+      <c r="P13" s="144"/>
+      <c r="Q13" s="144"/>
+      <c r="R13" s="144"/>
+      <c r="S13" s="144"/>
+      <c r="T13" s="144"/>
+      <c r="U13" s="144"/>
+      <c r="V13" s="144"/>
+      <c r="W13" s="144"/>
+      <c r="X13" s="144"/>
+      <c r="Y13" s="144"/>
+      <c r="Z13" s="144"/>
+      <c r="AA13" s="144"/>
+      <c r="AB13" s="144"/>
+      <c r="AC13" s="144"/>
+      <c r="AD13" s="144"/>
+      <c r="AE13" s="144"/>
+      <c r="AF13" s="144"/>
+      <c r="AG13" s="144"/>
+      <c r="AH13" s="144"/>
+      <c r="AI13" s="144"/>
+      <c r="AJ13" s="144"/>
+      <c r="AK13" s="144"/>
+      <c r="AL13" s="144"/>
+      <c r="AM13" s="144"/>
     </row>
     <row r="14" spans="1:39">
-      <c r="A14" s="172"/>
-      <c r="B14" s="172"/>
-      <c r="C14" s="138" t="s">
+      <c r="A14" s="178"/>
+      <c r="B14" s="178"/>
+      <c r="C14" s="144" t="s">
         <v>209</v>
       </c>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="138"/>
-      <c r="L14" s="138"/>
-      <c r="M14" s="138"/>
-      <c r="N14" s="138"/>
-      <c r="O14" s="138"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138"/>
-      <c r="R14" s="138"/>
-      <c r="S14" s="138"/>
-      <c r="T14" s="138"/>
-      <c r="U14" s="138"/>
-      <c r="V14" s="138"/>
-      <c r="W14" s="138"/>
-      <c r="X14" s="138"/>
-      <c r="Y14" s="138"/>
-      <c r="Z14" s="138"/>
-      <c r="AA14" s="138"/>
-      <c r="AB14" s="138"/>
-      <c r="AC14" s="138"/>
-      <c r="AD14" s="138"/>
-      <c r="AE14" s="138"/>
-      <c r="AF14" s="138"/>
-      <c r="AG14" s="138"/>
-      <c r="AH14" s="138"/>
-      <c r="AI14" s="138"/>
-      <c r="AJ14" s="138"/>
-      <c r="AK14" s="138"/>
-      <c r="AL14" s="138"/>
-      <c r="AM14" s="138"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="144"/>
+      <c r="P14" s="144"/>
+      <c r="Q14" s="144"/>
+      <c r="R14" s="144"/>
+      <c r="S14" s="144"/>
+      <c r="T14" s="144"/>
+      <c r="U14" s="144"/>
+      <c r="V14" s="144"/>
+      <c r="W14" s="144"/>
+      <c r="X14" s="144"/>
+      <c r="Y14" s="144"/>
+      <c r="Z14" s="144"/>
+      <c r="AA14" s="144"/>
+      <c r="AB14" s="144"/>
+      <c r="AC14" s="144"/>
+      <c r="AD14" s="144"/>
+      <c r="AE14" s="144"/>
+      <c r="AF14" s="144"/>
+      <c r="AG14" s="144"/>
+      <c r="AH14" s="144"/>
+      <c r="AI14" s="144"/>
+      <c r="AJ14" s="144"/>
+      <c r="AK14" s="144"/>
+      <c r="AL14" s="144"/>
+      <c r="AM14" s="144"/>
     </row>
     <row r="15" spans="1:39">
-      <c r="A15" s="172"/>
-      <c r="B15" s="172"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="138"/>
-      <c r="P15" s="138"/>
-      <c r="Q15" s="138"/>
-      <c r="R15" s="138"/>
-      <c r="S15" s="138"/>
-      <c r="T15" s="138"/>
-      <c r="U15" s="138"/>
-      <c r="V15" s="138"/>
-      <c r="W15" s="138"/>
-      <c r="X15" s="138"/>
-      <c r="Y15" s="138"/>
-      <c r="Z15" s="138"/>
-      <c r="AA15" s="138"/>
-      <c r="AB15" s="138"/>
-      <c r="AC15" s="138"/>
-      <c r="AD15" s="138"/>
-      <c r="AE15" s="138"/>
-      <c r="AF15" s="138"/>
-      <c r="AG15" s="138"/>
-      <c r="AH15" s="138"/>
-      <c r="AI15" s="138"/>
-      <c r="AJ15" s="138"/>
-      <c r="AK15" s="138"/>
-      <c r="AL15" s="138"/>
-      <c r="AM15" s="138"/>
+      <c r="A15" s="178"/>
+      <c r="B15" s="178"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
+      <c r="S15" s="144"/>
+      <c r="T15" s="144"/>
+      <c r="U15" s="144"/>
+      <c r="V15" s="144"/>
+      <c r="W15" s="144"/>
+      <c r="X15" s="144"/>
+      <c r="Y15" s="144"/>
+      <c r="Z15" s="144"/>
+      <c r="AA15" s="144"/>
+      <c r="AB15" s="144"/>
+      <c r="AC15" s="144"/>
+      <c r="AD15" s="144"/>
+      <c r="AE15" s="144"/>
+      <c r="AF15" s="144"/>
+      <c r="AG15" s="144"/>
+      <c r="AH15" s="144"/>
+      <c r="AI15" s="144"/>
+      <c r="AJ15" s="144"/>
+      <c r="AK15" s="144"/>
+      <c r="AL15" s="144"/>
+      <c r="AM15" s="144"/>
     </row>
     <row r="16" spans="1:39">
-      <c r="A16" s="172"/>
-      <c r="B16" s="172"/>
-      <c r="C16" s="138" t="s">
+      <c r="A16" s="178"/>
+      <c r="B16" s="178"/>
+      <c r="C16" s="144" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="138"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="138"/>
-      <c r="M16" s="138"/>
-      <c r="N16" s="138"/>
-      <c r="O16" s="138"/>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="138"/>
-      <c r="R16" s="138"/>
-      <c r="S16" s="138"/>
-      <c r="T16" s="138"/>
-      <c r="U16" s="138"/>
-      <c r="V16" s="138"/>
-      <c r="W16" s="138"/>
-      <c r="X16" s="138"/>
-      <c r="Y16" s="138"/>
-      <c r="Z16" s="138"/>
-      <c r="AA16" s="138"/>
-      <c r="AB16" s="138"/>
-      <c r="AC16" s="138"/>
-      <c r="AD16" s="138"/>
-      <c r="AE16" s="138"/>
-      <c r="AF16" s="138"/>
-      <c r="AG16" s="138"/>
-      <c r="AH16" s="138"/>
-      <c r="AI16" s="138"/>
-      <c r="AJ16" s="138"/>
-      <c r="AK16" s="138"/>
-      <c r="AL16" s="138"/>
-      <c r="AM16" s="138"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="144"/>
+      <c r="Q16" s="144"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="144"/>
+      <c r="T16" s="144"/>
+      <c r="U16" s="144"/>
+      <c r="V16" s="144"/>
+      <c r="W16" s="144"/>
+      <c r="X16" s="144"/>
+      <c r="Y16" s="144"/>
+      <c r="Z16" s="144"/>
+      <c r="AA16" s="144"/>
+      <c r="AB16" s="144"/>
+      <c r="AC16" s="144"/>
+      <c r="AD16" s="144"/>
+      <c r="AE16" s="144"/>
+      <c r="AF16" s="144"/>
+      <c r="AG16" s="144"/>
+      <c r="AH16" s="144"/>
+      <c r="AI16" s="144"/>
+      <c r="AJ16" s="144"/>
+      <c r="AK16" s="144"/>
+      <c r="AL16" s="144"/>
+      <c r="AM16" s="144"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="172"/>
-      <c r="B17" s="172"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="138"/>
-      <c r="K17" s="138"/>
-      <c r="L17" s="138"/>
-      <c r="M17" s="138"/>
-      <c r="N17" s="138"/>
-      <c r="O17" s="138"/>
-      <c r="P17" s="138"/>
-      <c r="Q17" s="138"/>
-      <c r="R17" s="138"/>
-      <c r="S17" s="138"/>
-      <c r="T17" s="138"/>
-      <c r="U17" s="138"/>
-      <c r="V17" s="138"/>
-      <c r="W17" s="138"/>
-      <c r="X17" s="138"/>
-      <c r="Y17" s="138"/>
-      <c r="Z17" s="138"/>
-      <c r="AA17" s="138"/>
-      <c r="AB17" s="138"/>
-      <c r="AC17" s="138"/>
-      <c r="AD17" s="138"/>
-      <c r="AE17" s="138"/>
-      <c r="AF17" s="138"/>
-      <c r="AG17" s="138"/>
-      <c r="AH17" s="138"/>
-      <c r="AI17" s="138"/>
-      <c r="AJ17" s="138"/>
-      <c r="AK17" s="138"/>
-      <c r="AL17" s="138"/>
-      <c r="AM17" s="138"/>
+      <c r="A17" s="178"/>
+      <c r="B17" s="178"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="144"/>
+      <c r="J17" s="144"/>
+      <c r="K17" s="144"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="144"/>
+      <c r="P17" s="144"/>
+      <c r="Q17" s="144"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
+      <c r="U17" s="144"/>
+      <c r="V17" s="144"/>
+      <c r="W17" s="144"/>
+      <c r="X17" s="144"/>
+      <c r="Y17" s="144"/>
+      <c r="Z17" s="144"/>
+      <c r="AA17" s="144"/>
+      <c r="AB17" s="144"/>
+      <c r="AC17" s="144"/>
+      <c r="AD17" s="144"/>
+      <c r="AE17" s="144"/>
+      <c r="AF17" s="144"/>
+      <c r="AG17" s="144"/>
+      <c r="AH17" s="144"/>
+      <c r="AI17" s="144"/>
+      <c r="AJ17" s="144"/>
+      <c r="AK17" s="144"/>
+      <c r="AL17" s="144"/>
+      <c r="AM17" s="144"/>
     </row>
     <row r="19" spans="1:39">
       <c r="A19" s="68" t="s">
@@ -15254,6 +15261,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="Y16:AB17"/>
+    <mergeCell ref="AC16:AH17"/>
+    <mergeCell ref="AI16:AM17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="J16:L17"/>
+    <mergeCell ref="M16:O17"/>
+    <mergeCell ref="P16:R17"/>
+    <mergeCell ref="S16:U17"/>
+    <mergeCell ref="V16:X17"/>
+    <mergeCell ref="AI14:AM15"/>
+    <mergeCell ref="J10:L11"/>
+    <mergeCell ref="P10:R11"/>
+    <mergeCell ref="M10:O11"/>
+    <mergeCell ref="S10:U11"/>
+    <mergeCell ref="V10:X11"/>
+    <mergeCell ref="Y10:AB11"/>
+    <mergeCell ref="AC10:AH11"/>
+    <mergeCell ref="AI12:AM13"/>
+    <mergeCell ref="AI10:AM11"/>
+    <mergeCell ref="P14:R15"/>
+    <mergeCell ref="S14:U15"/>
+    <mergeCell ref="V14:X15"/>
+    <mergeCell ref="Y14:AB15"/>
+    <mergeCell ref="AC14:AH15"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="Y9:AB9"/>
+    <mergeCell ref="AC9:AH9"/>
+    <mergeCell ref="P12:R13"/>
+    <mergeCell ref="S12:U13"/>
+    <mergeCell ref="V12:X13"/>
+    <mergeCell ref="Y12:AB13"/>
+    <mergeCell ref="AC12:AH13"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="S9:U9"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="AI8:AM9"/>
     <mergeCell ref="M1:AL1"/>
@@ -15270,42 +15311,8 @@
     <mergeCell ref="C10:I11"/>
     <mergeCell ref="C12:I13"/>
     <mergeCell ref="A8:I9"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="AC9:AH9"/>
-    <mergeCell ref="P12:R13"/>
-    <mergeCell ref="S12:U13"/>
-    <mergeCell ref="V12:X13"/>
-    <mergeCell ref="Y12:AB13"/>
-    <mergeCell ref="AC12:AH13"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="AI14:AM15"/>
-    <mergeCell ref="J10:L11"/>
-    <mergeCell ref="P10:R11"/>
-    <mergeCell ref="M10:O11"/>
-    <mergeCell ref="S10:U11"/>
-    <mergeCell ref="V10:X11"/>
-    <mergeCell ref="Y10:AB11"/>
-    <mergeCell ref="AC10:AH11"/>
-    <mergeCell ref="AI12:AM13"/>
-    <mergeCell ref="AI10:AM11"/>
-    <mergeCell ref="P14:R15"/>
-    <mergeCell ref="S14:U15"/>
-    <mergeCell ref="V14:X15"/>
-    <mergeCell ref="Y14:AB15"/>
-    <mergeCell ref="AC14:AH15"/>
-    <mergeCell ref="Y16:AB17"/>
-    <mergeCell ref="AC16:AH17"/>
-    <mergeCell ref="AI16:AM17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="J16:L17"/>
-    <mergeCell ref="M16:O17"/>
-    <mergeCell ref="P16:R17"/>
-    <mergeCell ref="S16:U17"/>
-    <mergeCell ref="V16:X17"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
   <headerFooter>

--- a/wwwroot/ExcelModel/Kik_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Kik_PHY_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627743DF-A83D-41E0-A24A-33161B2F5EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE07A83-B19D-4ABD-B7B0-4E1F0418CAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Air Permeability" sheetId="30" r:id="rId6"/>
     <sheet name="Hydroatatic" sheetId="29" r:id="rId7"/>
     <sheet name="Density" sheetId="33" r:id="rId8"/>
+    <sheet name="WaterRepellency" sheetId="35" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="ReportNumber" localSheetId="5">'Air Permeability'!$M$1</definedName>
@@ -28,6 +29,7 @@
     <definedName name="ReportNumber" localSheetId="7">Density!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="6">Hydroatatic!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="2">'Pilling Resistance'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="8">WaterRepellency!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="0">Weight!$J$1</definedName>
     <definedName name="ReportNumber" localSheetId="1">'Yarn count'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="3">'Zipper Strength'!$M$1</definedName>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="249">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -1670,12 +1672,124 @@
       <t xml:space="preserve"> does not comply with the requested test requirements.</t>
     </r>
   </si>
+  <si>
+    <t>Water Repellency</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Original</t>
+  </si>
+  <si>
+    <t>Specimen</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Washing  procedures:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedure No: </t>
+  </si>
+  <si>
+    <t>Using horizontal axis, front-loading type machine: Machine wash at</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>degree C with _2.0_  kg  total dry mass(</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">+ specimen) and </t>
+  </si>
+  <si>
+    <t>"77%" ECE(A)+3%TAED+20% sodium perborate,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">, </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remark：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>AATCC 22  Spray Rating</t>
+  </si>
+  <si>
+    <t>Other Standard Spray Rating</t>
+  </si>
+  <si>
+    <t>100 No sticking or wetting of upper surface</t>
+  </si>
+  <si>
+    <t>100/ISO 5No sticking or wetting of the specimen</t>
+  </si>
+  <si>
+    <t>90 Slight random sticking or wetting of specimen surface</t>
+  </si>
+  <si>
+    <t>90/ISO 4Slight random sticking or wetting the</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>80 Wetting of specimen face at spray points</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>specimen face</t>
+  </si>
+  <si>
+    <t>70 Partial wetting of specimen face beyond the spray points</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>80/ISO 3Wetting of specimen face at spray</t>
+  </si>
+  <si>
+    <t>50 Complete wetting of the entire specimen face</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70/ISO 2Partial wetting of the specimen face </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>beyond the spray points</t>
+  </si>
+  <si>
+    <t>beyond the points</t>
+  </si>
+  <si>
+    <t>0 Complete wetting of the entire face of the specimen</t>
+  </si>
+  <si>
+    <t>50/ISO 1Complete wetting of the entire specimen</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>face beyond the spray points</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">0/ISO0 Complete wetting of the entire </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>face of specimen</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment No: SFL-NGB-EQP-</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44">
+  <fonts count="45">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2011,6 +2125,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2156,7 +2278,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2169,8 +2291,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2363,6 +2491,96 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2372,65 +2590,50 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2462,143 +2665,86 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2610,54 +2756,131 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="4" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="6">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{B926554C-D793-41B2-A366-631BCC55C3AD}"/>
     <cellStyle name="常规 2 2" xfId="3" xr:uid="{405C80A6-CCE2-4CBA-93F1-C2B0ABC79892}"/>
     <cellStyle name="常规 3" xfId="2" xr:uid="{28C94EE5-F9AC-470C-A4F5-B8BACA1FC4BE}"/>
+    <cellStyle name="常规 3 2" xfId="5" xr:uid="{587F29AD-1796-44FB-A970-4DDD50AFBA96}"/>
+    <cellStyle name="常规 4" xfId="4" xr:uid="{1E217DC7-C878-4C54-8E4D-B1C493B19CCE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2945,25 +3168,25 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
-      <c r="Z1" s="85"/>
-      <c r="AA1" s="85"/>
-      <c r="AB1" s="85"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="95"/>
+      <c r="X1" s="95"/>
+      <c r="Y1" s="95"/>
+      <c r="Z1" s="95"/>
+      <c r="AA1" s="95"/>
+      <c r="AB1" s="95"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="5" t="s">
@@ -2995,25 +3218,25 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="102"/>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="110"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="103"/>
+      <c r="P3" s="111"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -3199,230 +3422,230 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" ht="16.2">
-      <c r="A10" s="94" t="s">
+      <c r="A10" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="86" t="s">
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="87"/>
-      <c r="K10" s="87"/>
-      <c r="L10" s="87"/>
-      <c r="M10" s="87"/>
-      <c r="N10" s="87"/>
-      <c r="O10" s="87"/>
-      <c r="P10" s="87"/>
-      <c r="Q10" s="87"/>
-      <c r="R10" s="87"/>
-      <c r="S10" s="87"/>
-      <c r="T10" s="87"/>
-      <c r="U10" s="87"/>
-      <c r="V10" s="87"/>
-      <c r="W10" s="87"/>
-      <c r="X10" s="87"/>
-      <c r="Y10" s="88" t="s">
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="97"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
+      <c r="M10" s="97"/>
+      <c r="N10" s="97"/>
+      <c r="O10" s="97"/>
+      <c r="P10" s="97"/>
+      <c r="Q10" s="97"/>
+      <c r="R10" s="97"/>
+      <c r="S10" s="97"/>
+      <c r="T10" s="97"/>
+      <c r="U10" s="97"/>
+      <c r="V10" s="97"/>
+      <c r="W10" s="97"/>
+      <c r="X10" s="97"/>
+      <c r="Y10" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="89"/>
-      <c r="AA10" s="89"/>
-      <c r="AB10" s="90"/>
+      <c r="Z10" s="99"/>
+      <c r="AA10" s="99"/>
+      <c r="AB10" s="100"/>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="97"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="86" t="s">
+      <c r="A11" s="107"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="86" t="s">
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="87"/>
-      <c r="K11" s="87"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="86" t="s">
+      <c r="J11" s="97"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="87"/>
-      <c r="O11" s="87"/>
-      <c r="P11" s="100"/>
-      <c r="Q11" s="86" t="s">
+      <c r="N11" s="97"/>
+      <c r="O11" s="97"/>
+      <c r="P11" s="94"/>
+      <c r="Q11" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="87"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="100"/>
-      <c r="U11" s="86" t="s">
+      <c r="R11" s="97"/>
+      <c r="S11" s="97"/>
+      <c r="T11" s="94"/>
+      <c r="U11" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="87"/>
-      <c r="W11" s="87"/>
-      <c r="X11" s="101"/>
-      <c r="Y11" s="91"/>
-      <c r="Z11" s="92"/>
-      <c r="AA11" s="92"/>
-      <c r="AB11" s="93"/>
+      <c r="V11" s="97"/>
+      <c r="W11" s="97"/>
+      <c r="X11" s="93"/>
+      <c r="Y11" s="101"/>
+      <c r="Z11" s="102"/>
+      <c r="AA11" s="102"/>
+      <c r="AB11" s="103"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="82"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="104"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="100"/>
-      <c r="Q12" s="104"/>
-      <c r="R12" s="101"/>
-      <c r="S12" s="101"/>
-      <c r="T12" s="100"/>
-      <c r="U12" s="104"/>
-      <c r="V12" s="101"/>
-      <c r="W12" s="101"/>
-      <c r="X12" s="100"/>
-      <c r="Y12" s="104"/>
-      <c r="Z12" s="101"/>
-      <c r="AA12" s="101"/>
-      <c r="AB12" s="100"/>
+      <c r="A12" s="112"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="114"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="94"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="92"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="93"/>
+      <c r="T12" s="94"/>
+      <c r="U12" s="92"/>
+      <c r="V12" s="93"/>
+      <c r="W12" s="93"/>
+      <c r="X12" s="94"/>
+      <c r="Y12" s="92"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="93"/>
+      <c r="AB12" s="94"/>
     </row>
     <row r="13" spans="1:28">
-      <c r="A13" s="82"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="101"/>
-      <c r="K13" s="101"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="101"/>
-      <c r="O13" s="101"/>
-      <c r="P13" s="100"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="101"/>
-      <c r="S13" s="101"/>
-      <c r="T13" s="100"/>
-      <c r="U13" s="104"/>
-      <c r="V13" s="101"/>
-      <c r="W13" s="101"/>
-      <c r="X13" s="100"/>
-      <c r="Y13" s="104"/>
-      <c r="Z13" s="101"/>
-      <c r="AA13" s="101"/>
-      <c r="AB13" s="100"/>
+      <c r="A13" s="112"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="93"/>
+      <c r="O13" s="93"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="92"/>
+      <c r="R13" s="93"/>
+      <c r="S13" s="93"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="92"/>
+      <c r="V13" s="93"/>
+      <c r="W13" s="93"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="92"/>
+      <c r="Z13" s="93"/>
+      <c r="AA13" s="93"/>
+      <c r="AB13" s="94"/>
     </row>
     <row r="14" spans="1:28">
-      <c r="A14" s="82"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="101"/>
-      <c r="K14" s="101"/>
-      <c r="L14" s="100"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="101"/>
-      <c r="O14" s="101"/>
-      <c r="P14" s="100"/>
-      <c r="Q14" s="104"/>
-      <c r="R14" s="101"/>
-      <c r="S14" s="101"/>
-      <c r="T14" s="100"/>
-      <c r="U14" s="104"/>
-      <c r="V14" s="101"/>
-      <c r="W14" s="101"/>
-      <c r="X14" s="100"/>
-      <c r="Y14" s="104"/>
-      <c r="Z14" s="101"/>
-      <c r="AA14" s="101"/>
-      <c r="AB14" s="100"/>
+      <c r="A14" s="112"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="93"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="93"/>
+      <c r="O14" s="93"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="92"/>
+      <c r="R14" s="93"/>
+      <c r="S14" s="93"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="92"/>
+      <c r="V14" s="93"/>
+      <c r="W14" s="93"/>
+      <c r="X14" s="94"/>
+      <c r="Y14" s="92"/>
+      <c r="Z14" s="93"/>
+      <c r="AA14" s="93"/>
+      <c r="AB14" s="94"/>
     </row>
     <row r="15" spans="1:28">
-      <c r="A15" s="82"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="100"/>
-      <c r="M15" s="104"/>
-      <c r="N15" s="101"/>
-      <c r="O15" s="101"/>
-      <c r="P15" s="100"/>
-      <c r="Q15" s="104"/>
-      <c r="R15" s="101"/>
-      <c r="S15" s="101"/>
-      <c r="T15" s="100"/>
-      <c r="U15" s="104"/>
-      <c r="V15" s="101"/>
-      <c r="W15" s="101"/>
-      <c r="X15" s="100"/>
-      <c r="Y15" s="104"/>
-      <c r="Z15" s="101"/>
-      <c r="AA15" s="101"/>
-      <c r="AB15" s="100"/>
+      <c r="A15" s="112"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="93"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="93"/>
+      <c r="O15" s="93"/>
+      <c r="P15" s="94"/>
+      <c r="Q15" s="92"/>
+      <c r="R15" s="93"/>
+      <c r="S15" s="93"/>
+      <c r="T15" s="94"/>
+      <c r="U15" s="92"/>
+      <c r="V15" s="93"/>
+      <c r="W15" s="93"/>
+      <c r="X15" s="94"/>
+      <c r="Y15" s="92"/>
+      <c r="Z15" s="93"/>
+      <c r="AA15" s="93"/>
+      <c r="AB15" s="94"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="82"/>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="101"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="101"/>
-      <c r="K16" s="101"/>
-      <c r="L16" s="100"/>
-      <c r="M16" s="104"/>
-      <c r="N16" s="101"/>
-      <c r="O16" s="101"/>
-      <c r="P16" s="100"/>
-      <c r="Q16" s="104"/>
-      <c r="R16" s="101"/>
-      <c r="S16" s="101"/>
-      <c r="T16" s="100"/>
-      <c r="U16" s="104"/>
-      <c r="V16" s="101"/>
-      <c r="W16" s="101"/>
-      <c r="X16" s="100"/>
-      <c r="Y16" s="104"/>
-      <c r="Z16" s="101"/>
-      <c r="AA16" s="101"/>
-      <c r="AB16" s="100"/>
+      <c r="A16" s="112"/>
+      <c r="B16" s="113"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="93"/>
+      <c r="P16" s="94"/>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="93"/>
+      <c r="S16" s="93"/>
+      <c r="T16" s="94"/>
+      <c r="U16" s="92"/>
+      <c r="V16" s="93"/>
+      <c r="W16" s="93"/>
+      <c r="X16" s="94"/>
+      <c r="Y16" s="92"/>
+      <c r="Z16" s="93"/>
+      <c r="AA16" s="93"/>
+      <c r="AB16" s="94"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="3" t="s">
@@ -3565,14 +3788,32 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="Y15:AB15"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="Y12:AB12"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="Y13:AB13"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="Y14:AB14"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="J1:AB1"/>
+    <mergeCell ref="E10:X10"/>
+    <mergeCell ref="Y10:AB11"/>
+    <mergeCell ref="A10:D11"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
     <mergeCell ref="M15:P15"/>
     <mergeCell ref="Q15:T15"/>
     <mergeCell ref="M16:P16"/>
@@ -3585,32 +3826,14 @@
     <mergeCell ref="Q13:T13"/>
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="J1:AB1"/>
-    <mergeCell ref="E10:X10"/>
-    <mergeCell ref="Y10:AB11"/>
-    <mergeCell ref="A10:D11"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:P11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="Y12:AB12"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="Y13:AB13"/>
+    <mergeCell ref="U14:X14"/>
+    <mergeCell ref="Y14:AB14"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3651,32 +3874,32 @@
       <c r="J1" s="41"/>
       <c r="K1" s="41"/>
       <c r="L1" s="41"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="111"/>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="111"/>
-      <c r="AG1" s="111"/>
-      <c r="AH1" s="111"/>
-      <c r="AI1" s="111"/>
-      <c r="AJ1" s="111"/>
-      <c r="AK1" s="111"/>
-      <c r="AL1" s="111"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
+      <c r="U1" s="136"/>
+      <c r="V1" s="136"/>
+      <c r="W1" s="136"/>
+      <c r="X1" s="136"/>
+      <c r="Y1" s="136"/>
+      <c r="Z1" s="136"/>
+      <c r="AA1" s="136"/>
+      <c r="AB1" s="136"/>
+      <c r="AC1" s="136"/>
+      <c r="AD1" s="136"/>
+      <c r="AE1" s="136"/>
+      <c r="AF1" s="136"/>
+      <c r="AG1" s="136"/>
+      <c r="AH1" s="136"/>
+      <c r="AI1" s="136"/>
+      <c r="AJ1" s="136"/>
+      <c r="AK1" s="136"/>
+      <c r="AL1" s="136"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="42" t="s">
@@ -3712,17 +3935,17 @@
       <c r="AF2" s="39"/>
     </row>
     <row r="3" spans="1:38" ht="15.75" customHeight="1">
-      <c r="A3" s="112"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
-      <c r="K3" s="112"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
       <c r="L3" s="39"/>
       <c r="M3" s="39"/>
       <c r="N3" s="39"/>
@@ -3939,45 +4162,45 @@
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="105" t="s">
+      <c r="D10" s="138"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="130" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="107"/>
-      <c r="P10" s="105" t="s">
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="132"/>
+      <c r="P10" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="Q10" s="106"/>
-      <c r="R10" s="106"/>
-      <c r="S10" s="106"/>
-      <c r="T10" s="106"/>
-      <c r="U10" s="106"/>
-      <c r="V10" s="106"/>
-      <c r="W10" s="106"/>
-      <c r="X10" s="106"/>
-      <c r="Y10" s="106"/>
-      <c r="Z10" s="106"/>
-      <c r="AA10" s="106"/>
-      <c r="AB10" s="106"/>
-      <c r="AC10" s="106"/>
-      <c r="AD10" s="106"/>
-      <c r="AE10" s="106"/>
-      <c r="AF10" s="106"/>
-      <c r="AG10" s="106"/>
-      <c r="AH10" s="106"/>
-      <c r="AI10" s="106"/>
-      <c r="AJ10" s="106"/>
-      <c r="AK10" s="106"/>
-      <c r="AL10" s="107"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="131"/>
+      <c r="T10" s="131"/>
+      <c r="U10" s="131"/>
+      <c r="V10" s="131"/>
+      <c r="W10" s="131"/>
+      <c r="X10" s="131"/>
+      <c r="Y10" s="131"/>
+      <c r="Z10" s="131"/>
+      <c r="AA10" s="131"/>
+      <c r="AB10" s="131"/>
+      <c r="AC10" s="131"/>
+      <c r="AD10" s="131"/>
+      <c r="AE10" s="131"/>
+      <c r="AF10" s="131"/>
+      <c r="AG10" s="131"/>
+      <c r="AH10" s="131"/>
+      <c r="AI10" s="131"/>
+      <c r="AJ10" s="131"/>
+      <c r="AK10" s="131"/>
+      <c r="AL10" s="132"/>
     </row>
     <row r="11" spans="1:38">
       <c r="A11" s="43" t="s">
@@ -3987,53 +4210,53 @@
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
       <c r="E11" s="46"/>
-      <c r="F11" s="105" t="s">
+      <c r="F11" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="107"/>
-      <c r="K11" s="105" t="s">
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="106"/>
-      <c r="O11" s="107"/>
-      <c r="P11" s="105" t="s">
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="132"/>
+      <c r="P11" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" s="106"/>
-      <c r="R11" s="106"/>
-      <c r="S11" s="106"/>
-      <c r="T11" s="107"/>
-      <c r="U11" s="105" t="s">
+      <c r="Q11" s="131"/>
+      <c r="R11" s="131"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="132"/>
+      <c r="U11" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="V11" s="106"/>
-      <c r="W11" s="106"/>
-      <c r="X11" s="106"/>
-      <c r="Y11" s="107"/>
-      <c r="Z11" s="105" t="s">
+      <c r="V11" s="131"/>
+      <c r="W11" s="131"/>
+      <c r="X11" s="131"/>
+      <c r="Y11" s="132"/>
+      <c r="Z11" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="106"/>
-      <c r="AB11" s="106"/>
-      <c r="AC11" s="106"/>
-      <c r="AD11" s="107"/>
-      <c r="AE11" s="105" t="s">
+      <c r="AA11" s="131"/>
+      <c r="AB11" s="131"/>
+      <c r="AC11" s="131"/>
+      <c r="AD11" s="132"/>
+      <c r="AE11" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="AF11" s="106"/>
-      <c r="AG11" s="106"/>
-      <c r="AH11" s="106"/>
-      <c r="AI11" s="107"/>
-      <c r="AJ11" s="108" t="s">
+      <c r="AF11" s="131"/>
+      <c r="AG11" s="131"/>
+      <c r="AH11" s="131"/>
+      <c r="AI11" s="132"/>
+      <c r="AJ11" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="109"/>
-      <c r="AL11" s="110"/>
+      <c r="AK11" s="134"/>
+      <c r="AL11" s="135"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1">
       <c r="A12" s="115" t="s">
@@ -5404,13 +5627,13 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="A32:E33"/>
-    <mergeCell ref="A34:E35"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="AE11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="P10:AL10"/>
     <mergeCell ref="A12:E13"/>
     <mergeCell ref="A14:E15"/>
     <mergeCell ref="A16:E17"/>
@@ -5425,13 +5648,13 @@
     <mergeCell ref="K11:O11"/>
     <mergeCell ref="P11:T11"/>
     <mergeCell ref="U11:Y11"/>
-    <mergeCell ref="AE11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="P10:AL10"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="A32:E33"/>
+    <mergeCell ref="A34:E35"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:K39"/>
+    <mergeCell ref="D40:K40"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5471,32 +5694,32 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
-      <c r="X1" s="134"/>
-      <c r="Y1" s="134"/>
-      <c r="Z1" s="134"/>
-      <c r="AA1" s="134"/>
-      <c r="AB1" s="134"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="134"/>
-      <c r="AE1" s="134"/>
-      <c r="AF1" s="134"/>
-      <c r="AG1" s="134"/>
-      <c r="AH1" s="134"/>
-      <c r="AI1" s="134"/>
-      <c r="AJ1" s="134"/>
-      <c r="AK1" s="134"/>
-      <c r="AL1" s="134"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="144"/>
+      <c r="Z1" s="144"/>
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="144"/>
+      <c r="AF1" s="144"/>
+      <c r="AG1" s="144"/>
+      <c r="AH1" s="144"/>
+      <c r="AI1" s="144"/>
+      <c r="AJ1" s="144"/>
+      <c r="AK1" s="144"/>
+      <c r="AL1" s="144"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5535,20 +5758,20 @@
       <c r="A3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="135"/>
-      <c r="O3" s="135"/>
-      <c r="P3" s="135"/>
-      <c r="Q3" s="135"/>
-      <c r="R3" s="135"/>
-      <c r="S3" s="135"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="145"/>
+      <c r="O3" s="145"/>
+      <c r="P3" s="145"/>
+      <c r="Q3" s="145"/>
+      <c r="R3" s="145"/>
+      <c r="S3" s="145"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -5566,13 +5789,13 @@
       <c r="A4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -5638,238 +5861,238 @@
       <c r="AL5" s="1"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="137" t="s">
+      <c r="B6" s="147"/>
+      <c r="C6" s="147"/>
+      <c r="D6" s="147"/>
+      <c r="E6" s="147"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="147"/>
+      <c r="H6" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="137"/>
-      <c r="J6" s="137"/>
-      <c r="K6" s="137"/>
-      <c r="L6" s="138" t="s">
+      <c r="I6" s="142"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="138"/>
-      <c r="N6" s="138"/>
-      <c r="O6" s="138"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="138"/>
-      <c r="R6" s="138"/>
-      <c r="S6" s="138"/>
-      <c r="T6" s="138"/>
-      <c r="U6" s="138"/>
-      <c r="V6" s="138"/>
-      <c r="W6" s="138"/>
-      <c r="X6" s="137" t="s">
+      <c r="M6" s="143"/>
+      <c r="N6" s="143"/>
+      <c r="O6" s="143"/>
+      <c r="P6" s="143"/>
+      <c r="Q6" s="143"/>
+      <c r="R6" s="143"/>
+      <c r="S6" s="143"/>
+      <c r="T6" s="143"/>
+      <c r="U6" s="143"/>
+      <c r="V6" s="143"/>
+      <c r="W6" s="143"/>
+      <c r="X6" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="Y6" s="137"/>
-      <c r="Z6" s="137"/>
-      <c r="AA6" s="137"/>
-      <c r="AB6" s="138" t="s">
+      <c r="Y6" s="142"/>
+      <c r="Z6" s="142"/>
+      <c r="AA6" s="142"/>
+      <c r="AB6" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="AC6" s="138"/>
-      <c r="AD6" s="138"/>
-      <c r="AE6" s="138"/>
-      <c r="AF6" s="138"/>
-      <c r="AG6" s="138"/>
-      <c r="AH6" s="138"/>
-      <c r="AI6" s="138"/>
-      <c r="AJ6" s="138"/>
-      <c r="AK6" s="138"/>
-      <c r="AL6" s="138"/>
+      <c r="AC6" s="143"/>
+      <c r="AD6" s="143"/>
+      <c r="AE6" s="143"/>
+      <c r="AF6" s="143"/>
+      <c r="AG6" s="143"/>
+      <c r="AH6" s="143"/>
+      <c r="AI6" s="143"/>
+      <c r="AJ6" s="143"/>
+      <c r="AK6" s="143"/>
+      <c r="AL6" s="143"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
-      <c r="A7" s="133"/>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="137"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="137"/>
-      <c r="K7" s="137"/>
-      <c r="L7" s="138" t="s">
+      <c r="A7" s="147"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="142"/>
+      <c r="I7" s="142"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="138"/>
-      <c r="N7" s="138"/>
-      <c r="O7" s="138"/>
-      <c r="P7" s="138" t="s">
+      <c r="M7" s="143"/>
+      <c r="N7" s="143"/>
+      <c r="O7" s="143"/>
+      <c r="P7" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="Q7" s="138"/>
-      <c r="R7" s="138"/>
-      <c r="S7" s="138"/>
-      <c r="T7" s="138" t="s">
+      <c r="Q7" s="143"/>
+      <c r="R7" s="143"/>
+      <c r="S7" s="143"/>
+      <c r="T7" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="U7" s="138"/>
-      <c r="V7" s="138"/>
-      <c r="W7" s="138"/>
-      <c r="X7" s="137"/>
-      <c r="Y7" s="137"/>
-      <c r="Z7" s="137"/>
-      <c r="AA7" s="137"/>
-      <c r="AB7" s="138" t="s">
+      <c r="U7" s="143"/>
+      <c r="V7" s="143"/>
+      <c r="W7" s="143"/>
+      <c r="X7" s="142"/>
+      <c r="Y7" s="142"/>
+      <c r="Z7" s="142"/>
+      <c r="AA7" s="142"/>
+      <c r="AB7" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="AC7" s="138"/>
-      <c r="AD7" s="138"/>
-      <c r="AE7" s="138"/>
-      <c r="AF7" s="138" t="s">
+      <c r="AC7" s="143"/>
+      <c r="AD7" s="143"/>
+      <c r="AE7" s="143"/>
+      <c r="AF7" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="AG7" s="138"/>
-      <c r="AH7" s="138"/>
-      <c r="AI7" s="138"/>
-      <c r="AJ7" s="138" t="s">
+      <c r="AG7" s="143"/>
+      <c r="AH7" s="143"/>
+      <c r="AI7" s="143"/>
+      <c r="AJ7" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="AK7" s="138"/>
-      <c r="AL7" s="138"/>
+      <c r="AK7" s="143"/>
+      <c r="AL7" s="143"/>
     </row>
     <row r="8" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A8" s="130"/>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="131">
+      <c r="A8" s="148"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="141">
         <v>125</v>
       </c>
-      <c r="I8" s="131"/>
-      <c r="J8" s="131"/>
-      <c r="K8" s="131"/>
-      <c r="L8" s="132"/>
-      <c r="M8" s="132"/>
-      <c r="N8" s="132"/>
-      <c r="O8" s="132"/>
-      <c r="P8" s="132"/>
-      <c r="Q8" s="132"/>
-      <c r="R8" s="132"/>
-      <c r="S8" s="132"/>
-      <c r="T8" s="132"/>
-      <c r="U8" s="132"/>
-      <c r="V8" s="132"/>
-      <c r="W8" s="132"/>
-      <c r="X8" s="131">
+      <c r="I8" s="141"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="140"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="140"/>
+      <c r="T8" s="140"/>
+      <c r="U8" s="140"/>
+      <c r="V8" s="140"/>
+      <c r="W8" s="140"/>
+      <c r="X8" s="141">
         <v>2000</v>
       </c>
-      <c r="Y8" s="131"/>
-      <c r="Z8" s="131"/>
-      <c r="AA8" s="131"/>
-      <c r="AB8" s="132"/>
-      <c r="AC8" s="132"/>
-      <c r="AD8" s="132"/>
-      <c r="AE8" s="132"/>
-      <c r="AF8" s="132"/>
-      <c r="AG8" s="132"/>
-      <c r="AH8" s="132"/>
-      <c r="AI8" s="132"/>
-      <c r="AJ8" s="132"/>
-      <c r="AK8" s="132"/>
-      <c r="AL8" s="132"/>
+      <c r="Y8" s="141"/>
+      <c r="Z8" s="141"/>
+      <c r="AA8" s="141"/>
+      <c r="AB8" s="140"/>
+      <c r="AC8" s="140"/>
+      <c r="AD8" s="140"/>
+      <c r="AE8" s="140"/>
+      <c r="AF8" s="140"/>
+      <c r="AG8" s="140"/>
+      <c r="AH8" s="140"/>
+      <c r="AI8" s="140"/>
+      <c r="AJ8" s="140"/>
+      <c r="AK8" s="140"/>
+      <c r="AL8" s="140"/>
     </row>
     <row r="9" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A9" s="130"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="131">
+      <c r="A9" s="148"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="148"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="148"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="141">
         <v>500</v>
       </c>
-      <c r="I9" s="131"/>
-      <c r="J9" s="131"/>
-      <c r="K9" s="131"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="132"/>
-      <c r="N9" s="132"/>
-      <c r="O9" s="132"/>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="132"/>
-      <c r="R9" s="132"/>
-      <c r="S9" s="132"/>
-      <c r="T9" s="132"/>
-      <c r="U9" s="132"/>
-      <c r="V9" s="132"/>
-      <c r="W9" s="132"/>
-      <c r="X9" s="131">
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="140"/>
+      <c r="N9" s="140"/>
+      <c r="O9" s="140"/>
+      <c r="P9" s="140"/>
+      <c r="Q9" s="140"/>
+      <c r="R9" s="140"/>
+      <c r="S9" s="140"/>
+      <c r="T9" s="140"/>
+      <c r="U9" s="140"/>
+      <c r="V9" s="140"/>
+      <c r="W9" s="140"/>
+      <c r="X9" s="141">
         <v>5000</v>
       </c>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="131"/>
-      <c r="AA9" s="131"/>
-      <c r="AB9" s="132"/>
-      <c r="AC9" s="132"/>
-      <c r="AD9" s="132"/>
-      <c r="AE9" s="132"/>
-      <c r="AF9" s="132"/>
-      <c r="AG9" s="132"/>
-      <c r="AH9" s="132"/>
-      <c r="AI9" s="132"/>
-      <c r="AJ9" s="132"/>
-      <c r="AK9" s="132"/>
-      <c r="AL9" s="132"/>
+      <c r="Y9" s="141"/>
+      <c r="Z9" s="141"/>
+      <c r="AA9" s="141"/>
+      <c r="AB9" s="140"/>
+      <c r="AC9" s="140"/>
+      <c r="AD9" s="140"/>
+      <c r="AE9" s="140"/>
+      <c r="AF9" s="140"/>
+      <c r="AG9" s="140"/>
+      <c r="AH9" s="140"/>
+      <c r="AI9" s="140"/>
+      <c r="AJ9" s="140"/>
+      <c r="AK9" s="140"/>
+      <c r="AL9" s="140"/>
     </row>
     <row r="10" spans="1:38" ht="21.15" customHeight="1">
-      <c r="A10" s="130"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="131">
+      <c r="A10" s="148"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
+      <c r="F10" s="148"/>
+      <c r="G10" s="148"/>
+      <c r="H10" s="141">
         <v>1000</v>
       </c>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="132"/>
-      <c r="M10" s="132"/>
-      <c r="N10" s="132"/>
-      <c r="O10" s="132"/>
-      <c r="P10" s="132"/>
-      <c r="Q10" s="132"/>
-      <c r="R10" s="132"/>
-      <c r="S10" s="132"/>
-      <c r="T10" s="132"/>
-      <c r="U10" s="132"/>
-      <c r="V10" s="132"/>
-      <c r="W10" s="132"/>
-      <c r="X10" s="131">
+      <c r="I10" s="141"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="140"/>
+      <c r="T10" s="140"/>
+      <c r="U10" s="140"/>
+      <c r="V10" s="140"/>
+      <c r="W10" s="140"/>
+      <c r="X10" s="141">
         <v>7000</v>
       </c>
-      <c r="Y10" s="131"/>
-      <c r="Z10" s="131"/>
-      <c r="AA10" s="131"/>
-      <c r="AB10" s="132"/>
-      <c r="AC10" s="132"/>
-      <c r="AD10" s="132"/>
-      <c r="AE10" s="132"/>
-      <c r="AF10" s="132"/>
-      <c r="AG10" s="132"/>
-      <c r="AH10" s="132"/>
-      <c r="AI10" s="132"/>
-      <c r="AJ10" s="132"/>
-      <c r="AK10" s="132"/>
-      <c r="AL10" s="132"/>
+      <c r="Y10" s="141"/>
+      <c r="Z10" s="141"/>
+      <c r="AA10" s="141"/>
+      <c r="AB10" s="140"/>
+      <c r="AC10" s="140"/>
+      <c r="AD10" s="140"/>
+      <c r="AE10" s="140"/>
+      <c r="AF10" s="140"/>
+      <c r="AG10" s="140"/>
+      <c r="AH10" s="140"/>
+      <c r="AI10" s="140"/>
+      <c r="AJ10" s="140"/>
+      <c r="AK10" s="140"/>
+      <c r="AL10" s="140"/>
     </row>
     <row r="11" spans="1:38" ht="21.15" customHeight="1">
       <c r="A11" s="28"/>
@@ -5948,238 +6171,238 @@
       <c r="AL12" s="1"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1">
-      <c r="A13" s="133" t="s">
+      <c r="A13" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="137" t="s">
+      <c r="B13" s="147"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
+      <c r="H13" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="137"/>
-      <c r="L13" s="138" t="s">
+      <c r="I13" s="142"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="138"/>
-      <c r="N13" s="138"/>
-      <c r="O13" s="138"/>
-      <c r="P13" s="138"/>
-      <c r="Q13" s="138"/>
-      <c r="R13" s="138"/>
-      <c r="S13" s="138"/>
-      <c r="T13" s="138"/>
-      <c r="U13" s="138"/>
-      <c r="V13" s="138"/>
-      <c r="W13" s="138"/>
-      <c r="X13" s="137" t="s">
+      <c r="M13" s="143"/>
+      <c r="N13" s="143"/>
+      <c r="O13" s="143"/>
+      <c r="P13" s="143"/>
+      <c r="Q13" s="143"/>
+      <c r="R13" s="143"/>
+      <c r="S13" s="143"/>
+      <c r="T13" s="143"/>
+      <c r="U13" s="143"/>
+      <c r="V13" s="143"/>
+      <c r="W13" s="143"/>
+      <c r="X13" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="Y13" s="137"/>
-      <c r="Z13" s="137"/>
-      <c r="AA13" s="137"/>
-      <c r="AB13" s="138" t="s">
+      <c r="Y13" s="142"/>
+      <c r="Z13" s="142"/>
+      <c r="AA13" s="142"/>
+      <c r="AB13" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="AC13" s="138"/>
-      <c r="AD13" s="138"/>
-      <c r="AE13" s="138"/>
-      <c r="AF13" s="138"/>
-      <c r="AG13" s="138"/>
-      <c r="AH13" s="138"/>
-      <c r="AI13" s="138"/>
-      <c r="AJ13" s="138"/>
-      <c r="AK13" s="138"/>
-      <c r="AL13" s="138"/>
+      <c r="AC13" s="143"/>
+      <c r="AD13" s="143"/>
+      <c r="AE13" s="143"/>
+      <c r="AF13" s="143"/>
+      <c r="AG13" s="143"/>
+      <c r="AH13" s="143"/>
+      <c r="AI13" s="143"/>
+      <c r="AJ13" s="143"/>
+      <c r="AK13" s="143"/>
+      <c r="AL13" s="143"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1">
-      <c r="A14" s="133"/>
-      <c r="B14" s="133"/>
-      <c r="C14" s="133"/>
-      <c r="D14" s="133"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="137"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="138" t="s">
+      <c r="A14" s="147"/>
+      <c r="B14" s="147"/>
+      <c r="C14" s="147"/>
+      <c r="D14" s="147"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="147"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="M14" s="138"/>
-      <c r="N14" s="138"/>
-      <c r="O14" s="138"/>
-      <c r="P14" s="138" t="s">
+      <c r="M14" s="143"/>
+      <c r="N14" s="143"/>
+      <c r="O14" s="143"/>
+      <c r="P14" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="Q14" s="138"/>
-      <c r="R14" s="138"/>
-      <c r="S14" s="138"/>
-      <c r="T14" s="138" t="s">
+      <c r="Q14" s="143"/>
+      <c r="R14" s="143"/>
+      <c r="S14" s="143"/>
+      <c r="T14" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="U14" s="138"/>
-      <c r="V14" s="138"/>
-      <c r="W14" s="138"/>
-      <c r="X14" s="137"/>
-      <c r="Y14" s="137"/>
-      <c r="Z14" s="137"/>
-      <c r="AA14" s="137"/>
-      <c r="AB14" s="138" t="s">
+      <c r="U14" s="143"/>
+      <c r="V14" s="143"/>
+      <c r="W14" s="143"/>
+      <c r="X14" s="142"/>
+      <c r="Y14" s="142"/>
+      <c r="Z14" s="142"/>
+      <c r="AA14" s="142"/>
+      <c r="AB14" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="AC14" s="138"/>
-      <c r="AD14" s="138"/>
-      <c r="AE14" s="138"/>
-      <c r="AF14" s="138" t="s">
+      <c r="AC14" s="143"/>
+      <c r="AD14" s="143"/>
+      <c r="AE14" s="143"/>
+      <c r="AF14" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="AG14" s="138"/>
-      <c r="AH14" s="138"/>
-      <c r="AI14" s="138"/>
-      <c r="AJ14" s="138" t="s">
+      <c r="AG14" s="143"/>
+      <c r="AH14" s="143"/>
+      <c r="AI14" s="143"/>
+      <c r="AJ14" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="AK14" s="138"/>
-      <c r="AL14" s="138"/>
+      <c r="AK14" s="143"/>
+      <c r="AL14" s="143"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1">
-      <c r="A15" s="130"/>
-      <c r="B15" s="130"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="131">
+      <c r="A15" s="148"/>
+      <c r="B15" s="148"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="141">
         <v>125</v>
       </c>
-      <c r="I15" s="131"/>
-      <c r="J15" s="131"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="132"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="132"/>
-      <c r="R15" s="132"/>
-      <c r="S15" s="132"/>
-      <c r="T15" s="132"/>
-      <c r="U15" s="132"/>
-      <c r="V15" s="132"/>
-      <c r="W15" s="132"/>
-      <c r="X15" s="131">
+      <c r="I15" s="141"/>
+      <c r="J15" s="141"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="140"/>
+      <c r="M15" s="140"/>
+      <c r="N15" s="140"/>
+      <c r="O15" s="140"/>
+      <c r="P15" s="140"/>
+      <c r="Q15" s="140"/>
+      <c r="R15" s="140"/>
+      <c r="S15" s="140"/>
+      <c r="T15" s="140"/>
+      <c r="U15" s="140"/>
+      <c r="V15" s="140"/>
+      <c r="W15" s="140"/>
+      <c r="X15" s="141">
         <v>2000</v>
       </c>
-      <c r="Y15" s="131"/>
-      <c r="Z15" s="131"/>
-      <c r="AA15" s="131"/>
-      <c r="AB15" s="132"/>
-      <c r="AC15" s="132"/>
-      <c r="AD15" s="132"/>
-      <c r="AE15" s="132"/>
-      <c r="AF15" s="132"/>
-      <c r="AG15" s="132"/>
-      <c r="AH15" s="132"/>
-      <c r="AI15" s="132"/>
-      <c r="AJ15" s="132"/>
-      <c r="AK15" s="132"/>
-      <c r="AL15" s="132"/>
+      <c r="Y15" s="141"/>
+      <c r="Z15" s="141"/>
+      <c r="AA15" s="141"/>
+      <c r="AB15" s="140"/>
+      <c r="AC15" s="140"/>
+      <c r="AD15" s="140"/>
+      <c r="AE15" s="140"/>
+      <c r="AF15" s="140"/>
+      <c r="AG15" s="140"/>
+      <c r="AH15" s="140"/>
+      <c r="AI15" s="140"/>
+      <c r="AJ15" s="140"/>
+      <c r="AK15" s="140"/>
+      <c r="AL15" s="140"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1">
-      <c r="A16" s="130"/>
-      <c r="B16" s="130"/>
-      <c r="C16" s="130"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="131">
+      <c r="A16" s="148"/>
+      <c r="B16" s="148"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="141">
         <v>500</v>
       </c>
-      <c r="I16" s="131"/>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="132"/>
-      <c r="M16" s="132"/>
-      <c r="N16" s="132"/>
-      <c r="O16" s="132"/>
-      <c r="P16" s="132"/>
-      <c r="Q16" s="132"/>
-      <c r="R16" s="132"/>
-      <c r="S16" s="132"/>
-      <c r="T16" s="132"/>
-      <c r="U16" s="132"/>
-      <c r="V16" s="132"/>
-      <c r="W16" s="132"/>
-      <c r="X16" s="131">
+      <c r="I16" s="141"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="140"/>
+      <c r="N16" s="140"/>
+      <c r="O16" s="140"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="140"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="140"/>
+      <c r="T16" s="140"/>
+      <c r="U16" s="140"/>
+      <c r="V16" s="140"/>
+      <c r="W16" s="140"/>
+      <c r="X16" s="141">
         <v>5000</v>
       </c>
-      <c r="Y16" s="131"/>
-      <c r="Z16" s="131"/>
-      <c r="AA16" s="131"/>
-      <c r="AB16" s="132"/>
-      <c r="AC16" s="132"/>
-      <c r="AD16" s="132"/>
-      <c r="AE16" s="132"/>
-      <c r="AF16" s="132"/>
-      <c r="AG16" s="132"/>
-      <c r="AH16" s="132"/>
-      <c r="AI16" s="132"/>
-      <c r="AJ16" s="132"/>
-      <c r="AK16" s="132"/>
-      <c r="AL16" s="132"/>
+      <c r="Y16" s="141"/>
+      <c r="Z16" s="141"/>
+      <c r="AA16" s="141"/>
+      <c r="AB16" s="140"/>
+      <c r="AC16" s="140"/>
+      <c r="AD16" s="140"/>
+      <c r="AE16" s="140"/>
+      <c r="AF16" s="140"/>
+      <c r="AG16" s="140"/>
+      <c r="AH16" s="140"/>
+      <c r="AI16" s="140"/>
+      <c r="AJ16" s="140"/>
+      <c r="AK16" s="140"/>
+      <c r="AL16" s="140"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
-      <c r="A17" s="130"/>
-      <c r="B17" s="130"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="131">
+      <c r="A17" s="148"/>
+      <c r="B17" s="148"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="148"/>
+      <c r="E17" s="148"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="141">
         <v>1000</v>
       </c>
-      <c r="I17" s="131"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
-      <c r="L17" s="132"/>
-      <c r="M17" s="132"/>
-      <c r="N17" s="132"/>
-      <c r="O17" s="132"/>
-      <c r="P17" s="132"/>
-      <c r="Q17" s="132"/>
-      <c r="R17" s="132"/>
-      <c r="S17" s="132"/>
-      <c r="T17" s="132"/>
-      <c r="U17" s="132"/>
-      <c r="V17" s="132"/>
-      <c r="W17" s="132"/>
-      <c r="X17" s="131">
+      <c r="I17" s="141"/>
+      <c r="J17" s="141"/>
+      <c r="K17" s="141"/>
+      <c r="L17" s="140"/>
+      <c r="M17" s="140"/>
+      <c r="N17" s="140"/>
+      <c r="O17" s="140"/>
+      <c r="P17" s="140"/>
+      <c r="Q17" s="140"/>
+      <c r="R17" s="140"/>
+      <c r="S17" s="140"/>
+      <c r="T17" s="140"/>
+      <c r="U17" s="140"/>
+      <c r="V17" s="140"/>
+      <c r="W17" s="140"/>
+      <c r="X17" s="141">
         <v>7000</v>
       </c>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="131"/>
-      <c r="AA17" s="131"/>
-      <c r="AB17" s="132"/>
-      <c r="AC17" s="132"/>
-      <c r="AD17" s="132"/>
-      <c r="AE17" s="132"/>
-      <c r="AF17" s="132"/>
-      <c r="AG17" s="132"/>
-      <c r="AH17" s="132"/>
-      <c r="AI17" s="132"/>
-      <c r="AJ17" s="132"/>
-      <c r="AK17" s="132"/>
-      <c r="AL17" s="132"/>
+      <c r="Y17" s="141"/>
+      <c r="Z17" s="141"/>
+      <c r="AA17" s="141"/>
+      <c r="AB17" s="140"/>
+      <c r="AC17" s="140"/>
+      <c r="AD17" s="140"/>
+      <c r="AE17" s="140"/>
+      <c r="AF17" s="140"/>
+      <c r="AG17" s="140"/>
+      <c r="AH17" s="140"/>
+      <c r="AI17" s="140"/>
+      <c r="AJ17" s="140"/>
+      <c r="AK17" s="140"/>
+      <c r="AL17" s="140"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1">
       <c r="A18" s="28"/>
@@ -7629,65 +7852,6 @@
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AB15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="AJ15:AL15"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="X16:AA16"/>
-    <mergeCell ref="AB16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L10:O10"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X10:AA10"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="X15:AA15"/>
-    <mergeCell ref="H13:K14"/>
-    <mergeCell ref="L13:W13"/>
-    <mergeCell ref="X13:AA14"/>
-    <mergeCell ref="AB13:AL13"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="AB14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AB10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="L9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="F3:S3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A6:G7"/>
-    <mergeCell ref="H6:K7"/>
-    <mergeCell ref="L6:W6"/>
-    <mergeCell ref="X6:AA7"/>
-    <mergeCell ref="AB6:AL6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="P7:S7"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="AB7:AE7"/>
-    <mergeCell ref="AF7:AI7"/>
-    <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="A8:G10"/>
     <mergeCell ref="A15:G17"/>
     <mergeCell ref="H15:K15"/>
@@ -7704,6 +7868,65 @@
     <mergeCell ref="L8:O8"/>
     <mergeCell ref="P8:S8"/>
     <mergeCell ref="A13:G14"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="F3:S3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A6:G7"/>
+    <mergeCell ref="H6:K7"/>
+    <mergeCell ref="L6:W6"/>
+    <mergeCell ref="X6:AA7"/>
+    <mergeCell ref="AB6:AL6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="P7:S7"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="AB7:AE7"/>
+    <mergeCell ref="AF7:AI7"/>
+    <mergeCell ref="AJ7:AL7"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="L9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="AB8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="AB10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AB13:AL13"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="AB14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="L10:O10"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="X15:AA15"/>
+    <mergeCell ref="H13:K14"/>
+    <mergeCell ref="L13:W13"/>
+    <mergeCell ref="X13:AA14"/>
+    <mergeCell ref="AB15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="X16:AA16"/>
+    <mergeCell ref="AB16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="AJ16:AL16"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7743,32 +7966,32 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
-      <c r="X1" s="134"/>
-      <c r="Y1" s="134"/>
-      <c r="Z1" s="134"/>
-      <c r="AA1" s="134"/>
-      <c r="AB1" s="134"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="134"/>
-      <c r="AE1" s="134"/>
-      <c r="AF1" s="134"/>
-      <c r="AG1" s="134"/>
-      <c r="AH1" s="134"/>
-      <c r="AI1" s="134"/>
-      <c r="AJ1" s="134"/>
-      <c r="AK1" s="134"/>
-      <c r="AL1" s="134"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="144"/>
+      <c r="Z1" s="144"/>
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="144"/>
+      <c r="AF1" s="144"/>
+      <c r="AG1" s="144"/>
+      <c r="AH1" s="144"/>
+      <c r="AI1" s="144"/>
+      <c r="AJ1" s="144"/>
+      <c r="AK1" s="144"/>
+      <c r="AL1" s="144"/>
       <c r="AM1" s="20"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -7804,17 +8027,17 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="102"/>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
       <c r="L3" s="16"/>
       <c r="M3" s="16"/>
       <c r="N3" s="12" t="s">
@@ -7871,16 +8094,16 @@
       <c r="AF4" s="1"/>
     </row>
     <row r="5" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="149" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -10271,32 +10494,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
-      <c r="Z1" s="149"/>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
-      <c r="AC1" s="149"/>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="149"/>
-      <c r="AJ1" s="149"/>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="84"/>
+      <c r="AD1" s="84"/>
+      <c r="AE1" s="84"/>
+      <c r="AF1" s="84"/>
+      <c r="AG1" s="84"/>
+      <c r="AH1" s="84"/>
+      <c r="AI1" s="84"/>
+      <c r="AJ1" s="84"/>
+      <c r="AK1" s="84"/>
+      <c r="AL1" s="84"/>
       <c r="AM1" s="67"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -10340,17 +10563,17 @@
       <c r="AM2" s="67"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="146"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="146"/>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -10370,11 +10593,11 @@
       <c r="Z3" s="38"/>
       <c r="AA3" s="74"/>
       <c r="AB3" s="34"/>
-      <c r="AC3" s="149"/>
-      <c r="AD3" s="149"/>
-      <c r="AE3" s="149"/>
-      <c r="AF3" s="149"/>
-      <c r="AG3" s="149"/>
+      <c r="AC3" s="84"/>
+      <c r="AD3" s="84"/>
+      <c r="AE3" s="84"/>
+      <c r="AF3" s="84"/>
+      <c r="AG3" s="84"/>
       <c r="AH3" s="34"/>
       <c r="AI3" s="34"/>
       <c r="AJ3" s="34"/>
@@ -10463,421 +10686,421 @@
       <c r="AM5" s="67"/>
     </row>
     <row r="6" spans="1:39" ht="15" customHeight="1">
-      <c r="A6" s="143" t="s">
+      <c r="A6" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="B6" s="143"/>
-      <c r="C6" s="143"/>
-      <c r="D6" s="143"/>
-      <c r="E6" s="148" t="s">
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="148" t="s">
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="86"/>
+      <c r="L6" s="86" t="s">
         <v>165</v>
       </c>
-      <c r="M6" s="148"/>
-      <c r="N6" s="148"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="148"/>
-      <c r="R6" s="148"/>
-      <c r="S6" s="148" t="s">
+      <c r="M6" s="86"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="86"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="86"/>
+      <c r="R6" s="86"/>
+      <c r="S6" s="86" t="s">
         <v>164</v>
       </c>
-      <c r="T6" s="148"/>
-      <c r="U6" s="148"/>
-      <c r="V6" s="148"/>
-      <c r="W6" s="148"/>
-      <c r="X6" s="148"/>
-      <c r="Y6" s="148"/>
-      <c r="Z6" s="148" t="s">
+      <c r="T6" s="86"/>
+      <c r="U6" s="86"/>
+      <c r="V6" s="86"/>
+      <c r="W6" s="86"/>
+      <c r="X6" s="86"/>
+      <c r="Y6" s="86"/>
+      <c r="Z6" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="AA6" s="148"/>
-      <c r="AB6" s="148"/>
-      <c r="AC6" s="148"/>
-      <c r="AD6" s="148"/>
-      <c r="AE6" s="148"/>
-      <c r="AF6" s="148"/>
-      <c r="AG6" s="148" t="s">
+      <c r="AA6" s="86"/>
+      <c r="AB6" s="86"/>
+      <c r="AC6" s="86"/>
+      <c r="AD6" s="86"/>
+      <c r="AE6" s="86"/>
+      <c r="AF6" s="86"/>
+      <c r="AG6" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="AH6" s="148"/>
-      <c r="AI6" s="148"/>
-      <c r="AJ6" s="148"/>
-      <c r="AK6" s="148"/>
-      <c r="AL6" s="148"/>
-      <c r="AM6" s="148"/>
+      <c r="AH6" s="86"/>
+      <c r="AI6" s="86"/>
+      <c r="AJ6" s="86"/>
+      <c r="AK6" s="86"/>
+      <c r="AL6" s="86"/>
+      <c r="AM6" s="86"/>
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
-      <c r="A7" s="143" t="s">
+      <c r="A7" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="143"/>
-      <c r="C7" s="143"/>
-      <c r="D7" s="143"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="147"/>
-      <c r="K7" s="147"/>
-      <c r="L7" s="147"/>
-      <c r="M7" s="147"/>
-      <c r="N7" s="147"/>
-      <c r="O7" s="147"/>
-      <c r="P7" s="147"/>
-      <c r="Q7" s="147"/>
-      <c r="R7" s="147"/>
-      <c r="S7" s="147"/>
-      <c r="T7" s="147"/>
-      <c r="U7" s="147"/>
-      <c r="V7" s="147"/>
-      <c r="W7" s="147"/>
-      <c r="X7" s="147"/>
-      <c r="Y7" s="147"/>
-      <c r="Z7" s="147"/>
-      <c r="AA7" s="147"/>
-      <c r="AB7" s="147"/>
-      <c r="AC7" s="147"/>
-      <c r="AD7" s="147"/>
-      <c r="AE7" s="147"/>
-      <c r="AF7" s="147"/>
-      <c r="AG7" s="147"/>
-      <c r="AH7" s="147"/>
-      <c r="AI7" s="147"/>
-      <c r="AJ7" s="147"/>
-      <c r="AK7" s="147"/>
-      <c r="AL7" s="147"/>
-      <c r="AM7" s="147"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="83"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="83"/>
+      <c r="U7" s="83"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="83"/>
+      <c r="X7" s="83"/>
+      <c r="Y7" s="83"/>
+      <c r="Z7" s="83"/>
+      <c r="AA7" s="83"/>
+      <c r="AB7" s="83"/>
+      <c r="AC7" s="83"/>
+      <c r="AD7" s="83"/>
+      <c r="AE7" s="83"/>
+      <c r="AF7" s="83"/>
+      <c r="AG7" s="83"/>
+      <c r="AH7" s="83"/>
+      <c r="AI7" s="83"/>
+      <c r="AJ7" s="83"/>
+      <c r="AK7" s="83"/>
+      <c r="AL7" s="83"/>
+      <c r="AM7" s="83"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
-      <c r="A8" s="143" t="s">
+      <c r="A8" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="143"/>
-      <c r="C8" s="143"/>
-      <c r="D8" s="143"/>
-      <c r="E8" s="147"/>
-      <c r="F8" s="147"/>
-      <c r="G8" s="147"/>
-      <c r="H8" s="147"/>
-      <c r="I8" s="147"/>
-      <c r="J8" s="147"/>
-      <c r="K8" s="147"/>
-      <c r="L8" s="147"/>
-      <c r="M8" s="147"/>
-      <c r="N8" s="147"/>
-      <c r="O8" s="147"/>
-      <c r="P8" s="147"/>
-      <c r="Q8" s="147"/>
-      <c r="R8" s="147"/>
-      <c r="S8" s="147"/>
-      <c r="T8" s="147"/>
-      <c r="U8" s="147"/>
-      <c r="V8" s="147"/>
-      <c r="W8" s="147"/>
-      <c r="X8" s="147"/>
-      <c r="Y8" s="147"/>
-      <c r="Z8" s="147"/>
-      <c r="AA8" s="147"/>
-      <c r="AB8" s="147"/>
-      <c r="AC8" s="147"/>
-      <c r="AD8" s="147"/>
-      <c r="AE8" s="147"/>
-      <c r="AF8" s="147"/>
-      <c r="AG8" s="147"/>
-      <c r="AH8" s="147"/>
-      <c r="AI8" s="147"/>
-      <c r="AJ8" s="147"/>
-      <c r="AK8" s="147"/>
-      <c r="AL8" s="147"/>
-      <c r="AM8" s="147"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="83"/>
+      <c r="U8" s="83"/>
+      <c r="V8" s="83"/>
+      <c r="W8" s="83"/>
+      <c r="X8" s="83"/>
+      <c r="Y8" s="83"/>
+      <c r="Z8" s="83"/>
+      <c r="AA8" s="83"/>
+      <c r="AB8" s="83"/>
+      <c r="AC8" s="83"/>
+      <c r="AD8" s="83"/>
+      <c r="AE8" s="83"/>
+      <c r="AF8" s="83"/>
+      <c r="AG8" s="83"/>
+      <c r="AH8" s="83"/>
+      <c r="AI8" s="83"/>
+      <c r="AJ8" s="83"/>
+      <c r="AK8" s="83"/>
+      <c r="AL8" s="83"/>
+      <c r="AM8" s="83"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
-      <c r="A9" s="143" t="s">
+      <c r="A9" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="143"/>
-      <c r="C9" s="143"/>
-      <c r="D9" s="143"/>
-      <c r="E9" s="148" t="s">
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="F9" s="148"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="148"/>
-      <c r="I9" s="148"/>
-      <c r="J9" s="148"/>
-      <c r="K9" s="148"/>
-      <c r="L9" s="148" t="s">
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="M9" s="148"/>
-      <c r="N9" s="148"/>
-      <c r="O9" s="148"/>
-      <c r="P9" s="148"/>
-      <c r="Q9" s="148"/>
-      <c r="R9" s="148"/>
-      <c r="S9" s="148" t="s">
+      <c r="M9" s="86"/>
+      <c r="N9" s="86"/>
+      <c r="O9" s="86"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="86"/>
+      <c r="S9" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="T9" s="148"/>
-      <c r="U9" s="148"/>
-      <c r="V9" s="148"/>
-      <c r="W9" s="148"/>
-      <c r="X9" s="148"/>
-      <c r="Y9" s="148"/>
-      <c r="Z9" s="148" t="s">
+      <c r="T9" s="86"/>
+      <c r="U9" s="86"/>
+      <c r="V9" s="86"/>
+      <c r="W9" s="86"/>
+      <c r="X9" s="86"/>
+      <c r="Y9" s="86"/>
+      <c r="Z9" s="86" t="s">
         <v>169</v>
       </c>
-      <c r="AA9" s="148"/>
-      <c r="AB9" s="148"/>
-      <c r="AC9" s="148"/>
-      <c r="AD9" s="148"/>
-      <c r="AE9" s="148"/>
-      <c r="AF9" s="148"/>
-      <c r="AG9" s="148" t="s">
+      <c r="AA9" s="86"/>
+      <c r="AB9" s="86"/>
+      <c r="AC9" s="86"/>
+      <c r="AD9" s="86"/>
+      <c r="AE9" s="86"/>
+      <c r="AF9" s="86"/>
+      <c r="AG9" s="86" t="s">
         <v>170</v>
       </c>
-      <c r="AH9" s="148"/>
-      <c r="AI9" s="148"/>
-      <c r="AJ9" s="148"/>
-      <c r="AK9" s="148"/>
-      <c r="AL9" s="148"/>
-      <c r="AM9" s="148"/>
+      <c r="AH9" s="86"/>
+      <c r="AI9" s="86"/>
+      <c r="AJ9" s="86"/>
+      <c r="AK9" s="86"/>
+      <c r="AL9" s="86"/>
+      <c r="AM9" s="86"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
-      <c r="A10" s="143" t="s">
+      <c r="A10" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="B10" s="143"/>
-      <c r="C10" s="143"/>
-      <c r="D10" s="143"/>
-      <c r="E10" s="147"/>
-      <c r="F10" s="147"/>
-      <c r="G10" s="147"/>
-      <c r="H10" s="147"/>
-      <c r="I10" s="147"/>
-      <c r="J10" s="147"/>
-      <c r="K10" s="147"/>
-      <c r="L10" s="147"/>
-      <c r="M10" s="147"/>
-      <c r="N10" s="147"/>
-      <c r="O10" s="147"/>
-      <c r="P10" s="147"/>
-      <c r="Q10" s="147"/>
-      <c r="R10" s="147"/>
-      <c r="S10" s="147"/>
-      <c r="T10" s="147"/>
-      <c r="U10" s="147"/>
-      <c r="V10" s="147"/>
-      <c r="W10" s="147"/>
-      <c r="X10" s="147"/>
-      <c r="Y10" s="147"/>
-      <c r="Z10" s="147"/>
-      <c r="AA10" s="147"/>
-      <c r="AB10" s="147"/>
-      <c r="AC10" s="147"/>
-      <c r="AD10" s="147"/>
-      <c r="AE10" s="147"/>
-      <c r="AF10" s="147"/>
-      <c r="AG10" s="147"/>
-      <c r="AH10" s="147"/>
-      <c r="AI10" s="147"/>
-      <c r="AJ10" s="147"/>
-      <c r="AK10" s="147"/>
-      <c r="AL10" s="147"/>
-      <c r="AM10" s="147"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="83"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="83"/>
+      <c r="T10" s="83"/>
+      <c r="U10" s="83"/>
+      <c r="V10" s="83"/>
+      <c r="W10" s="83"/>
+      <c r="X10" s="83"/>
+      <c r="Y10" s="83"/>
+      <c r="Z10" s="83"/>
+      <c r="AA10" s="83"/>
+      <c r="AB10" s="83"/>
+      <c r="AC10" s="83"/>
+      <c r="AD10" s="83"/>
+      <c r="AE10" s="83"/>
+      <c r="AF10" s="83"/>
+      <c r="AG10" s="83"/>
+      <c r="AH10" s="83"/>
+      <c r="AI10" s="83"/>
+      <c r="AJ10" s="83"/>
+      <c r="AK10" s="83"/>
+      <c r="AL10" s="83"/>
+      <c r="AM10" s="83"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
-      <c r="A11" s="143" t="s">
+      <c r="A11" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="143"/>
-      <c r="C11" s="143"/>
-      <c r="D11" s="143"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="147"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="147"/>
-      <c r="O11" s="147"/>
-      <c r="P11" s="147"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="147"/>
-      <c r="S11" s="147"/>
-      <c r="T11" s="147"/>
-      <c r="U11" s="147"/>
-      <c r="V11" s="147"/>
-      <c r="W11" s="147"/>
-      <c r="X11" s="147"/>
-      <c r="Y11" s="147"/>
-      <c r="Z11" s="147"/>
-      <c r="AA11" s="147"/>
-      <c r="AB11" s="147"/>
-      <c r="AC11" s="147"/>
-      <c r="AD11" s="147"/>
-      <c r="AE11" s="147"/>
-      <c r="AF11" s="147"/>
-      <c r="AG11" s="147"/>
-      <c r="AH11" s="147"/>
-      <c r="AI11" s="147"/>
-      <c r="AJ11" s="147"/>
-      <c r="AK11" s="147"/>
-      <c r="AL11" s="147"/>
-      <c r="AM11" s="147"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="83"/>
+      <c r="P11" s="83"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="83"/>
+      <c r="S11" s="83"/>
+      <c r="T11" s="83"/>
+      <c r="U11" s="83"/>
+      <c r="V11" s="83"/>
+      <c r="W11" s="83"/>
+      <c r="X11" s="83"/>
+      <c r="Y11" s="83"/>
+      <c r="Z11" s="83"/>
+      <c r="AA11" s="83"/>
+      <c r="AB11" s="83"/>
+      <c r="AC11" s="83"/>
+      <c r="AD11" s="83"/>
+      <c r="AE11" s="83"/>
+      <c r="AF11" s="83"/>
+      <c r="AG11" s="83"/>
+      <c r="AH11" s="83"/>
+      <c r="AI11" s="83"/>
+      <c r="AJ11" s="83"/>
+      <c r="AK11" s="83"/>
+      <c r="AL11" s="83"/>
+      <c r="AM11" s="83"/>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1">
-      <c r="A12" s="143" t="s">
+      <c r="A12" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="143"/>
-      <c r="C12" s="143"/>
-      <c r="D12" s="143"/>
-      <c r="E12" s="148" t="s">
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="86" t="s">
         <v>171</v>
       </c>
-      <c r="F12" s="148"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="148"/>
-      <c r="I12" s="148"/>
-      <c r="J12" s="148"/>
-      <c r="K12" s="148"/>
-      <c r="L12" s="148" t="s">
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86" t="s">
         <v>172</v>
       </c>
-      <c r="M12" s="148"/>
-      <c r="N12" s="148"/>
-      <c r="O12" s="148"/>
-      <c r="P12" s="148"/>
-      <c r="Q12" s="148"/>
-      <c r="R12" s="148"/>
-      <c r="S12" s="148" t="s">
+      <c r="M12" s="86"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="86"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="86"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="86" t="s">
         <v>173</v>
       </c>
-      <c r="T12" s="148"/>
-      <c r="U12" s="148"/>
-      <c r="V12" s="148"/>
-      <c r="W12" s="148"/>
-      <c r="X12" s="148"/>
-      <c r="Y12" s="148"/>
-      <c r="Z12" s="148" t="s">
+      <c r="T12" s="86"/>
+      <c r="U12" s="86"/>
+      <c r="V12" s="86"/>
+      <c r="W12" s="86"/>
+      <c r="X12" s="86"/>
+      <c r="Y12" s="86"/>
+      <c r="Z12" s="86" t="s">
         <v>174</v>
       </c>
-      <c r="AA12" s="148"/>
-      <c r="AB12" s="148"/>
-      <c r="AC12" s="148"/>
-      <c r="AD12" s="148"/>
-      <c r="AE12" s="148"/>
-      <c r="AF12" s="148"/>
-      <c r="AG12" s="148" t="s">
+      <c r="AA12" s="86"/>
+      <c r="AB12" s="86"/>
+      <c r="AC12" s="86"/>
+      <c r="AD12" s="86"/>
+      <c r="AE12" s="86"/>
+      <c r="AF12" s="86"/>
+      <c r="AG12" s="86" t="s">
         <v>175</v>
       </c>
-      <c r="AH12" s="148"/>
-      <c r="AI12" s="148"/>
-      <c r="AJ12" s="148"/>
-      <c r="AK12" s="148"/>
-      <c r="AL12" s="148"/>
-      <c r="AM12" s="148"/>
+      <c r="AH12" s="86"/>
+      <c r="AI12" s="86"/>
+      <c r="AJ12" s="86"/>
+      <c r="AK12" s="86"/>
+      <c r="AL12" s="86"/>
+      <c r="AM12" s="86"/>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1">
-      <c r="A13" s="143" t="s">
+      <c r="A13" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="143"/>
-      <c r="C13" s="143"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="147"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="147"/>
-      <c r="R13" s="147"/>
-      <c r="S13" s="147"/>
-      <c r="T13" s="147"/>
-      <c r="U13" s="147"/>
-      <c r="V13" s="147"/>
-      <c r="W13" s="147"/>
-      <c r="X13" s="147"/>
-      <c r="Y13" s="147"/>
-      <c r="Z13" s="147"/>
-      <c r="AA13" s="147"/>
-      <c r="AB13" s="147"/>
-      <c r="AC13" s="147"/>
-      <c r="AD13" s="147"/>
-      <c r="AE13" s="147"/>
-      <c r="AF13" s="147"/>
-      <c r="AG13" s="147"/>
-      <c r="AH13" s="147"/>
-      <c r="AI13" s="147"/>
-      <c r="AJ13" s="147"/>
-      <c r="AK13" s="147"/>
-      <c r="AL13" s="147"/>
-      <c r="AM13" s="147"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="83"/>
+      <c r="T13" s="83"/>
+      <c r="U13" s="83"/>
+      <c r="V13" s="83"/>
+      <c r="W13" s="83"/>
+      <c r="X13" s="83"/>
+      <c r="Y13" s="83"/>
+      <c r="Z13" s="83"/>
+      <c r="AA13" s="83"/>
+      <c r="AB13" s="83"/>
+      <c r="AC13" s="83"/>
+      <c r="AD13" s="83"/>
+      <c r="AE13" s="83"/>
+      <c r="AF13" s="83"/>
+      <c r="AG13" s="83"/>
+      <c r="AH13" s="83"/>
+      <c r="AI13" s="83"/>
+      <c r="AJ13" s="83"/>
+      <c r="AK13" s="83"/>
+      <c r="AL13" s="83"/>
+      <c r="AM13" s="83"/>
     </row>
     <row r="14" spans="1:39" ht="15" customHeight="1">
-      <c r="A14" s="143" t="s">
+      <c r="A14" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="143"/>
-      <c r="C14" s="143"/>
-      <c r="D14" s="143"/>
-      <c r="E14" s="147"/>
-      <c r="F14" s="147"/>
-      <c r="G14" s="147"/>
-      <c r="H14" s="147"/>
-      <c r="I14" s="147"/>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="147"/>
-      <c r="N14" s="147"/>
-      <c r="O14" s="147"/>
-      <c r="P14" s="147"/>
-      <c r="Q14" s="147"/>
-      <c r="R14" s="147"/>
-      <c r="S14" s="147"/>
-      <c r="T14" s="147"/>
-      <c r="U14" s="147"/>
-      <c r="V14" s="147"/>
-      <c r="W14" s="147"/>
-      <c r="X14" s="147"/>
-      <c r="Y14" s="147"/>
-      <c r="Z14" s="147"/>
-      <c r="AA14" s="147"/>
-      <c r="AB14" s="147"/>
-      <c r="AC14" s="147"/>
-      <c r="AD14" s="147"/>
-      <c r="AE14" s="147"/>
-      <c r="AF14" s="147"/>
-      <c r="AG14" s="147"/>
-      <c r="AH14" s="147"/>
-      <c r="AI14" s="147"/>
-      <c r="AJ14" s="147"/>
-      <c r="AK14" s="147"/>
-      <c r="AL14" s="147"/>
-      <c r="AM14" s="147"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="83"/>
+      <c r="N14" s="83"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="83"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="83"/>
+      <c r="U14" s="83"/>
+      <c r="V14" s="83"/>
+      <c r="W14" s="83"/>
+      <c r="X14" s="83"/>
+      <c r="Y14" s="83"/>
+      <c r="Z14" s="83"/>
+      <c r="AA14" s="83"/>
+      <c r="AB14" s="83"/>
+      <c r="AC14" s="83"/>
+      <c r="AD14" s="83"/>
+      <c r="AE14" s="83"/>
+      <c r="AF14" s="83"/>
+      <c r="AG14" s="83"/>
+      <c r="AH14" s="83"/>
+      <c r="AI14" s="83"/>
+      <c r="AJ14" s="83"/>
+      <c r="AK14" s="83"/>
+      <c r="AL14" s="83"/>
+      <c r="AM14" s="83"/>
     </row>
     <row r="15" spans="1:39">
       <c r="A15" s="76" t="s">
@@ -11004,17 +11227,17 @@
       <c r="AM17" s="34"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="146"/>
-      <c r="D18" s="146"/>
-      <c r="E18" s="146"/>
-      <c r="F18" s="146"/>
-      <c r="G18" s="146"/>
-      <c r="H18" s="146"/>
-      <c r="I18" s="146"/>
-      <c r="J18" s="146"/>
-      <c r="K18" s="146"/>
+      <c r="A18" s="85"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
       <c r="L18" s="34"/>
       <c r="M18" s="34"/>
       <c r="N18" s="34"/>
@@ -11170,604 +11393,604 @@
       <c r="AM21" s="34"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="145" t="s">
+      <c r="A22" s="87" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="145"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="145"/>
-      <c r="E22" s="144" t="s">
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="88" t="s">
         <v>182</v>
       </c>
-      <c r="F22" s="144"/>
-      <c r="G22" s="144"/>
-      <c r="H22" s="144"/>
-      <c r="I22" s="144"/>
-      <c r="J22" s="144"/>
-      <c r="K22" s="144"/>
-      <c r="L22" s="144" t="s">
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="M22" s="144"/>
-      <c r="N22" s="144"/>
-      <c r="O22" s="144"/>
-      <c r="P22" s="144"/>
-      <c r="Q22" s="144"/>
-      <c r="R22" s="144"/>
-      <c r="S22" s="144" t="s">
+      <c r="M22" s="88"/>
+      <c r="N22" s="88"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="88" t="s">
         <v>184</v>
       </c>
-      <c r="T22" s="144"/>
-      <c r="U22" s="144"/>
-      <c r="V22" s="144"/>
-      <c r="W22" s="144"/>
-      <c r="X22" s="144"/>
-      <c r="Y22" s="144"/>
-      <c r="Z22" s="144" t="s">
+      <c r="T22" s="88"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88" t="s">
         <v>185</v>
       </c>
-      <c r="AA22" s="144"/>
-      <c r="AB22" s="144"/>
-      <c r="AC22" s="144"/>
-      <c r="AD22" s="144"/>
-      <c r="AE22" s="144"/>
-      <c r="AF22" s="144"/>
-      <c r="AG22" s="144" t="s">
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="88"/>
+      <c r="AF22" s="88"/>
+      <c r="AG22" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="AH22" s="144"/>
-      <c r="AI22" s="144"/>
-      <c r="AJ22" s="144"/>
-      <c r="AK22" s="144"/>
-      <c r="AL22" s="144"/>
-      <c r="AM22" s="144"/>
+      <c r="AH22" s="88"/>
+      <c r="AI22" s="88"/>
+      <c r="AJ22" s="88"/>
+      <c r="AK22" s="88"/>
+      <c r="AL22" s="88"/>
+      <c r="AM22" s="88"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="145"/>
-      <c r="B23" s="145"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="144" t="s">
+      <c r="A23" s="87"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144" t="s">
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
-      <c r="K23" s="144"/>
-      <c r="L23" s="144" t="s">
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="M23" s="144"/>
-      <c r="N23" s="144"/>
-      <c r="O23" s="144" t="s">
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="P23" s="144"/>
-      <c r="Q23" s="144"/>
-      <c r="R23" s="144"/>
-      <c r="S23" s="144" t="s">
+      <c r="P23" s="88"/>
+      <c r="Q23" s="88"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="T23" s="144"/>
-      <c r="U23" s="144"/>
-      <c r="V23" s="144" t="s">
+      <c r="T23" s="88"/>
+      <c r="U23" s="88"/>
+      <c r="V23" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="W23" s="144"/>
-      <c r="X23" s="144"/>
-      <c r="Y23" s="144"/>
-      <c r="Z23" s="144" t="s">
+      <c r="W23" s="88"/>
+      <c r="X23" s="88"/>
+      <c r="Y23" s="88"/>
+      <c r="Z23" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="AA23" s="144"/>
-      <c r="AB23" s="144"/>
-      <c r="AC23" s="144" t="s">
+      <c r="AA23" s="88"/>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="AD23" s="144"/>
-      <c r="AE23" s="144"/>
-      <c r="AF23" s="144"/>
-      <c r="AG23" s="144" t="s">
+      <c r="AD23" s="88"/>
+      <c r="AE23" s="88"/>
+      <c r="AF23" s="88"/>
+      <c r="AG23" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="AH23" s="144"/>
-      <c r="AI23" s="144"/>
-      <c r="AJ23" s="144" t="s">
+      <c r="AH23" s="88"/>
+      <c r="AI23" s="88"/>
+      <c r="AJ23" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="AK23" s="144"/>
-      <c r="AL23" s="144"/>
-      <c r="AM23" s="144"/>
+      <c r="AK23" s="88"/>
+      <c r="AL23" s="88"/>
+      <c r="AM23" s="88"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="143" t="s">
+      <c r="A24" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="143"/>
-      <c r="C24" s="143"/>
-      <c r="D24" s="143"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="142"/>
-      <c r="H24" s="140"/>
-      <c r="I24" s="141"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="142"/>
-      <c r="L24" s="140"/>
-      <c r="M24" s="141"/>
-      <c r="N24" s="142"/>
-      <c r="O24" s="140"/>
-      <c r="P24" s="141"/>
-      <c r="Q24" s="141"/>
-      <c r="R24" s="142"/>
-      <c r="S24" s="140"/>
-      <c r="T24" s="141"/>
-      <c r="U24" s="142"/>
-      <c r="V24" s="140"/>
-      <c r="W24" s="141"/>
-      <c r="X24" s="141"/>
-      <c r="Y24" s="142"/>
-      <c r="Z24" s="140"/>
-      <c r="AA24" s="141"/>
-      <c r="AB24" s="142"/>
-      <c r="AC24" s="140"/>
-      <c r="AD24" s="141"/>
-      <c r="AE24" s="141"/>
-      <c r="AF24" s="142"/>
-      <c r="AG24" s="140"/>
-      <c r="AH24" s="141"/>
-      <c r="AI24" s="142"/>
-      <c r="AJ24" s="140"/>
-      <c r="AK24" s="141"/>
-      <c r="AL24" s="141"/>
-      <c r="AM24" s="142"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="89"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="90"/>
+      <c r="R24" s="91"/>
+      <c r="S24" s="89"/>
+      <c r="T24" s="90"/>
+      <c r="U24" s="91"/>
+      <c r="V24" s="89"/>
+      <c r="W24" s="90"/>
+      <c r="X24" s="90"/>
+      <c r="Y24" s="91"/>
+      <c r="Z24" s="89"/>
+      <c r="AA24" s="90"/>
+      <c r="AB24" s="91"/>
+      <c r="AC24" s="89"/>
+      <c r="AD24" s="90"/>
+      <c r="AE24" s="90"/>
+      <c r="AF24" s="91"/>
+      <c r="AG24" s="89"/>
+      <c r="AH24" s="90"/>
+      <c r="AI24" s="91"/>
+      <c r="AJ24" s="89"/>
+      <c r="AK24" s="90"/>
+      <c r="AL24" s="90"/>
+      <c r="AM24" s="91"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="143" t="s">
+      <c r="A25" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="143"/>
-      <c r="C25" s="143"/>
-      <c r="D25" s="143"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="142"/>
-      <c r="H25" s="140"/>
-      <c r="I25" s="141"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="142"/>
-      <c r="L25" s="140"/>
-      <c r="M25" s="141"/>
-      <c r="N25" s="142"/>
-      <c r="O25" s="140"/>
-      <c r="P25" s="141"/>
-      <c r="Q25" s="141"/>
-      <c r="R25" s="142"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="141"/>
-      <c r="U25" s="142"/>
-      <c r="V25" s="140"/>
-      <c r="W25" s="141"/>
-      <c r="X25" s="141"/>
-      <c r="Y25" s="142"/>
-      <c r="Z25" s="140"/>
-      <c r="AA25" s="141"/>
-      <c r="AB25" s="142"/>
-      <c r="AC25" s="140"/>
-      <c r="AD25" s="141"/>
-      <c r="AE25" s="141"/>
-      <c r="AF25" s="142"/>
-      <c r="AG25" s="140"/>
-      <c r="AH25" s="141"/>
-      <c r="AI25" s="142"/>
-      <c r="AJ25" s="140"/>
-      <c r="AK25" s="141"/>
-      <c r="AL25" s="141"/>
-      <c r="AM25" s="142"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="89"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="90"/>
+      <c r="R25" s="91"/>
+      <c r="S25" s="89"/>
+      <c r="T25" s="90"/>
+      <c r="U25" s="91"/>
+      <c r="V25" s="89"/>
+      <c r="W25" s="90"/>
+      <c r="X25" s="90"/>
+      <c r="Y25" s="91"/>
+      <c r="Z25" s="89"/>
+      <c r="AA25" s="90"/>
+      <c r="AB25" s="91"/>
+      <c r="AC25" s="89"/>
+      <c r="AD25" s="90"/>
+      <c r="AE25" s="90"/>
+      <c r="AF25" s="91"/>
+      <c r="AG25" s="89"/>
+      <c r="AH25" s="90"/>
+      <c r="AI25" s="91"/>
+      <c r="AJ25" s="89"/>
+      <c r="AK25" s="90"/>
+      <c r="AL25" s="90"/>
+      <c r="AM25" s="91"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="145" t="s">
+      <c r="A26" s="87" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="145"/>
-      <c r="C26" s="145"/>
-      <c r="D26" s="145"/>
-      <c r="E26" s="144" t="s">
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="88" t="s">
         <v>187</v>
       </c>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="144"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="144"/>
-      <c r="L26" s="144" t="s">
+      <c r="F26" s="88"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="88"/>
+      <c r="K26" s="88"/>
+      <c r="L26" s="88" t="s">
         <v>188</v>
       </c>
-      <c r="M26" s="144"/>
-      <c r="N26" s="144"/>
-      <c r="O26" s="144"/>
-      <c r="P26" s="144"/>
-      <c r="Q26" s="144"/>
-      <c r="R26" s="144"/>
-      <c r="S26" s="144" t="s">
+      <c r="M26" s="88"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="88"/>
+      <c r="P26" s="88"/>
+      <c r="Q26" s="88"/>
+      <c r="R26" s="88"/>
+      <c r="S26" s="88" t="s">
         <v>189</v>
       </c>
-      <c r="T26" s="144"/>
-      <c r="U26" s="144"/>
-      <c r="V26" s="144"/>
-      <c r="W26" s="144"/>
-      <c r="X26" s="144"/>
-      <c r="Y26" s="144"/>
-      <c r="Z26" s="144" t="s">
+      <c r="T26" s="88"/>
+      <c r="U26" s="88"/>
+      <c r="V26" s="88"/>
+      <c r="W26" s="88"/>
+      <c r="X26" s="88"/>
+      <c r="Y26" s="88"/>
+      <c r="Z26" s="88" t="s">
         <v>190</v>
       </c>
-      <c r="AA26" s="144"/>
-      <c r="AB26" s="144"/>
-      <c r="AC26" s="144"/>
-      <c r="AD26" s="144"/>
-      <c r="AE26" s="144"/>
-      <c r="AF26" s="144"/>
-      <c r="AG26" s="144" t="s">
+      <c r="AA26" s="88"/>
+      <c r="AB26" s="88"/>
+      <c r="AC26" s="88"/>
+      <c r="AD26" s="88"/>
+      <c r="AE26" s="88"/>
+      <c r="AF26" s="88"/>
+      <c r="AG26" s="88" t="s">
         <v>191</v>
       </c>
-      <c r="AH26" s="144"/>
-      <c r="AI26" s="144"/>
-      <c r="AJ26" s="144"/>
-      <c r="AK26" s="144"/>
-      <c r="AL26" s="144"/>
-      <c r="AM26" s="144"/>
+      <c r="AH26" s="88"/>
+      <c r="AI26" s="88"/>
+      <c r="AJ26" s="88"/>
+      <c r="AK26" s="88"/>
+      <c r="AL26" s="88"/>
+      <c r="AM26" s="88"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="145"/>
-      <c r="B27" s="145"/>
-      <c r="C27" s="145"/>
-      <c r="D27" s="145"/>
-      <c r="E27" s="144" t="s">
+      <c r="A27" s="87"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="F27" s="144"/>
-      <c r="G27" s="144"/>
-      <c r="H27" s="144" t="s">
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="I27" s="144"/>
-      <c r="J27" s="144"/>
-      <c r="K27" s="144"/>
-      <c r="L27" s="144" t="s">
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
+      <c r="L27" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="M27" s="144"/>
-      <c r="N27" s="144"/>
-      <c r="O27" s="144" t="s">
+      <c r="M27" s="88"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="P27" s="144"/>
-      <c r="Q27" s="144"/>
-      <c r="R27" s="144"/>
-      <c r="S27" s="144" t="s">
+      <c r="P27" s="88"/>
+      <c r="Q27" s="88"/>
+      <c r="R27" s="88"/>
+      <c r="S27" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="T27" s="144"/>
-      <c r="U27" s="144"/>
-      <c r="V27" s="144" t="s">
+      <c r="T27" s="88"/>
+      <c r="U27" s="88"/>
+      <c r="V27" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="W27" s="144"/>
-      <c r="X27" s="144"/>
-      <c r="Y27" s="144"/>
-      <c r="Z27" s="144" t="s">
+      <c r="W27" s="88"/>
+      <c r="X27" s="88"/>
+      <c r="Y27" s="88"/>
+      <c r="Z27" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="AA27" s="144"/>
-      <c r="AB27" s="144"/>
-      <c r="AC27" s="144" t="s">
+      <c r="AA27" s="88"/>
+      <c r="AB27" s="88"/>
+      <c r="AC27" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="AD27" s="144"/>
-      <c r="AE27" s="144"/>
-      <c r="AF27" s="144"/>
-      <c r="AG27" s="144" t="s">
+      <c r="AD27" s="88"/>
+      <c r="AE27" s="88"/>
+      <c r="AF27" s="88"/>
+      <c r="AG27" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="AH27" s="144"/>
-      <c r="AI27" s="144"/>
-      <c r="AJ27" s="144" t="s">
+      <c r="AH27" s="88"/>
+      <c r="AI27" s="88"/>
+      <c r="AJ27" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="AK27" s="144"/>
-      <c r="AL27" s="144"/>
-      <c r="AM27" s="144"/>
+      <c r="AK27" s="88"/>
+      <c r="AL27" s="88"/>
+      <c r="AM27" s="88"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="143" t="s">
+      <c r="A28" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="143"/>
-      <c r="C28" s="143"/>
-      <c r="D28" s="143"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="142"/>
-      <c r="H28" s="140"/>
-      <c r="I28" s="141"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="142"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="141"/>
-      <c r="N28" s="142"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="141"/>
-      <c r="Q28" s="141"/>
-      <c r="R28" s="142"/>
-      <c r="S28" s="140"/>
-      <c r="T28" s="141"/>
-      <c r="U28" s="142"/>
-      <c r="V28" s="140"/>
-      <c r="W28" s="141"/>
-      <c r="X28" s="141"/>
-      <c r="Y28" s="142"/>
-      <c r="Z28" s="140"/>
-      <c r="AA28" s="141"/>
-      <c r="AB28" s="142"/>
-      <c r="AC28" s="140"/>
-      <c r="AD28" s="141"/>
-      <c r="AE28" s="141"/>
-      <c r="AF28" s="142"/>
-      <c r="AG28" s="140"/>
-      <c r="AH28" s="141"/>
-      <c r="AI28" s="142"/>
-      <c r="AJ28" s="140"/>
-      <c r="AK28" s="141"/>
-      <c r="AL28" s="141"/>
-      <c r="AM28" s="142"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="89"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="89"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="90"/>
+      <c r="R28" s="91"/>
+      <c r="S28" s="89"/>
+      <c r="T28" s="90"/>
+      <c r="U28" s="91"/>
+      <c r="V28" s="89"/>
+      <c r="W28" s="90"/>
+      <c r="X28" s="90"/>
+      <c r="Y28" s="91"/>
+      <c r="Z28" s="89"/>
+      <c r="AA28" s="90"/>
+      <c r="AB28" s="91"/>
+      <c r="AC28" s="89"/>
+      <c r="AD28" s="90"/>
+      <c r="AE28" s="90"/>
+      <c r="AF28" s="91"/>
+      <c r="AG28" s="89"/>
+      <c r="AH28" s="90"/>
+      <c r="AI28" s="91"/>
+      <c r="AJ28" s="89"/>
+      <c r="AK28" s="90"/>
+      <c r="AL28" s="90"/>
+      <c r="AM28" s="91"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="143" t="s">
+      <c r="A29" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="143"/>
-      <c r="C29" s="143"/>
-      <c r="D29" s="143"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="140"/>
-      <c r="I29" s="141"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="140"/>
-      <c r="M29" s="141"/>
-      <c r="N29" s="142"/>
-      <c r="O29" s="140"/>
-      <c r="P29" s="141"/>
-      <c r="Q29" s="141"/>
-      <c r="R29" s="142"/>
-      <c r="S29" s="140"/>
-      <c r="T29" s="141"/>
-      <c r="U29" s="142"/>
-      <c r="V29" s="140"/>
-      <c r="W29" s="141"/>
-      <c r="X29" s="141"/>
-      <c r="Y29" s="142"/>
-      <c r="Z29" s="140"/>
-      <c r="AA29" s="141"/>
-      <c r="AB29" s="142"/>
-      <c r="AC29" s="140"/>
-      <c r="AD29" s="141"/>
-      <c r="AE29" s="141"/>
-      <c r="AF29" s="142"/>
-      <c r="AG29" s="140"/>
-      <c r="AH29" s="141"/>
-      <c r="AI29" s="142"/>
-      <c r="AJ29" s="140"/>
-      <c r="AK29" s="141"/>
-      <c r="AL29" s="141"/>
-      <c r="AM29" s="142"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="91"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="91"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="89"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="90"/>
+      <c r="R29" s="91"/>
+      <c r="S29" s="89"/>
+      <c r="T29" s="90"/>
+      <c r="U29" s="91"/>
+      <c r="V29" s="89"/>
+      <c r="W29" s="90"/>
+      <c r="X29" s="90"/>
+      <c r="Y29" s="91"/>
+      <c r="Z29" s="89"/>
+      <c r="AA29" s="90"/>
+      <c r="AB29" s="91"/>
+      <c r="AC29" s="89"/>
+      <c r="AD29" s="90"/>
+      <c r="AE29" s="90"/>
+      <c r="AF29" s="91"/>
+      <c r="AG29" s="89"/>
+      <c r="AH29" s="90"/>
+      <c r="AI29" s="91"/>
+      <c r="AJ29" s="89"/>
+      <c r="AK29" s="90"/>
+      <c r="AL29" s="90"/>
+      <c r="AM29" s="91"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="145" t="s">
+      <c r="A30" s="87" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="145"/>
-      <c r="C30" s="145"/>
-      <c r="D30" s="145"/>
-      <c r="E30" s="144" t="s">
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="88" t="s">
         <v>196</v>
       </c>
-      <c r="F30" s="144"/>
-      <c r="G30" s="144"/>
-      <c r="H30" s="144"/>
-      <c r="I30" s="144"/>
-      <c r="J30" s="144"/>
-      <c r="K30" s="144"/>
-      <c r="L30" s="144" t="s">
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="88"/>
+      <c r="L30" s="88" t="s">
         <v>195</v>
       </c>
-      <c r="M30" s="144"/>
-      <c r="N30" s="144"/>
-      <c r="O30" s="144"/>
-      <c r="P30" s="144"/>
-      <c r="Q30" s="144"/>
-      <c r="R30" s="144"/>
-      <c r="S30" s="144" t="s">
+      <c r="M30" s="88"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="88"/>
+      <c r="P30" s="88"/>
+      <c r="Q30" s="88"/>
+      <c r="R30" s="88"/>
+      <c r="S30" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="T30" s="144"/>
-      <c r="U30" s="144"/>
-      <c r="V30" s="144"/>
-      <c r="W30" s="144"/>
-      <c r="X30" s="144"/>
-      <c r="Y30" s="144"/>
-      <c r="Z30" s="144" t="s">
+      <c r="T30" s="88"/>
+      <c r="U30" s="88"/>
+      <c r="V30" s="88"/>
+      <c r="W30" s="88"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="88"/>
+      <c r="Z30" s="88" t="s">
         <v>193</v>
       </c>
-      <c r="AA30" s="144"/>
-      <c r="AB30" s="144"/>
-      <c r="AC30" s="144"/>
-      <c r="AD30" s="144"/>
-      <c r="AE30" s="144"/>
-      <c r="AF30" s="144"/>
-      <c r="AG30" s="144" t="s">
+      <c r="AA30" s="88"/>
+      <c r="AB30" s="88"/>
+      <c r="AC30" s="88"/>
+      <c r="AD30" s="88"/>
+      <c r="AE30" s="88"/>
+      <c r="AF30" s="88"/>
+      <c r="AG30" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="AH30" s="144"/>
-      <c r="AI30" s="144"/>
-      <c r="AJ30" s="144"/>
-      <c r="AK30" s="144"/>
-      <c r="AL30" s="144"/>
-      <c r="AM30" s="144"/>
+      <c r="AH30" s="88"/>
+      <c r="AI30" s="88"/>
+      <c r="AJ30" s="88"/>
+      <c r="AK30" s="88"/>
+      <c r="AL30" s="88"/>
+      <c r="AM30" s="88"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="145"/>
-      <c r="B31" s="145"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="145"/>
-      <c r="E31" s="144" t="s">
+      <c r="A31" s="87"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="F31" s="144"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="144" t="s">
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="I31" s="144"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="144"/>
-      <c r="L31" s="144" t="s">
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
+      <c r="L31" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="M31" s="144"/>
-      <c r="N31" s="144"/>
-      <c r="O31" s="144" t="s">
+      <c r="M31" s="88"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="P31" s="144"/>
-      <c r="Q31" s="144"/>
-      <c r="R31" s="144"/>
-      <c r="S31" s="144" t="s">
+      <c r="P31" s="88"/>
+      <c r="Q31" s="88"/>
+      <c r="R31" s="88"/>
+      <c r="S31" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="T31" s="144"/>
-      <c r="U31" s="144"/>
-      <c r="V31" s="144" t="s">
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="W31" s="144"/>
-      <c r="X31" s="144"/>
-      <c r="Y31" s="144"/>
-      <c r="Z31" s="144" t="s">
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+      <c r="Y31" s="88"/>
+      <c r="Z31" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="AA31" s="144"/>
-      <c r="AB31" s="144"/>
-      <c r="AC31" s="144" t="s">
+      <c r="AA31" s="88"/>
+      <c r="AB31" s="88"/>
+      <c r="AC31" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="AD31" s="144"/>
-      <c r="AE31" s="144"/>
-      <c r="AF31" s="144"/>
-      <c r="AG31" s="144" t="s">
+      <c r="AD31" s="88"/>
+      <c r="AE31" s="88"/>
+      <c r="AF31" s="88"/>
+      <c r="AG31" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="AH31" s="144"/>
-      <c r="AI31" s="144"/>
-      <c r="AJ31" s="144" t="s">
+      <c r="AH31" s="88"/>
+      <c r="AI31" s="88"/>
+      <c r="AJ31" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="AK31" s="144"/>
-      <c r="AL31" s="144"/>
-      <c r="AM31" s="144"/>
+      <c r="AK31" s="88"/>
+      <c r="AL31" s="88"/>
+      <c r="AM31" s="88"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="143" t="s">
+      <c r="A32" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="B32" s="143"/>
-      <c r="C32" s="143"/>
-      <c r="D32" s="143"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="141"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="140"/>
-      <c r="I32" s="141"/>
-      <c r="J32" s="141"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="140"/>
-      <c r="M32" s="141"/>
-      <c r="N32" s="142"/>
-      <c r="O32" s="140"/>
-      <c r="P32" s="141"/>
-      <c r="Q32" s="141"/>
-      <c r="R32" s="142"/>
-      <c r="S32" s="140"/>
-      <c r="T32" s="141"/>
-      <c r="U32" s="142"/>
-      <c r="V32" s="140"/>
-      <c r="W32" s="141"/>
-      <c r="X32" s="141"/>
-      <c r="Y32" s="142"/>
-      <c r="Z32" s="140"/>
-      <c r="AA32" s="141"/>
-      <c r="AB32" s="142"/>
-      <c r="AC32" s="140"/>
-      <c r="AD32" s="141"/>
-      <c r="AE32" s="141"/>
-      <c r="AF32" s="142"/>
-      <c r="AG32" s="140"/>
-      <c r="AH32" s="141"/>
-      <c r="AI32" s="142"/>
-      <c r="AJ32" s="140"/>
-      <c r="AK32" s="141"/>
-      <c r="AL32" s="141"/>
-      <c r="AM32" s="142"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="90"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="91"/>
+      <c r="L32" s="89"/>
+      <c r="M32" s="90"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="89"/>
+      <c r="P32" s="90"/>
+      <c r="Q32" s="90"/>
+      <c r="R32" s="91"/>
+      <c r="S32" s="89"/>
+      <c r="T32" s="90"/>
+      <c r="U32" s="91"/>
+      <c r="V32" s="89"/>
+      <c r="W32" s="90"/>
+      <c r="X32" s="90"/>
+      <c r="Y32" s="91"/>
+      <c r="Z32" s="89"/>
+      <c r="AA32" s="90"/>
+      <c r="AB32" s="91"/>
+      <c r="AC32" s="89"/>
+      <c r="AD32" s="90"/>
+      <c r="AE32" s="90"/>
+      <c r="AF32" s="91"/>
+      <c r="AG32" s="89"/>
+      <c r="AH32" s="90"/>
+      <c r="AI32" s="91"/>
+      <c r="AJ32" s="89"/>
+      <c r="AK32" s="90"/>
+      <c r="AL32" s="90"/>
+      <c r="AM32" s="91"/>
     </row>
     <row r="33" spans="1:39">
-      <c r="A33" s="143" t="s">
+      <c r="A33" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="B33" s="143"/>
-      <c r="C33" s="143"/>
-      <c r="D33" s="143"/>
-      <c r="E33" s="140"/>
-      <c r="F33" s="141"/>
-      <c r="G33" s="142"/>
-      <c r="H33" s="140"/>
-      <c r="I33" s="141"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="142"/>
-      <c r="L33" s="140"/>
-      <c r="M33" s="141"/>
-      <c r="N33" s="142"/>
-      <c r="O33" s="140"/>
-      <c r="P33" s="141"/>
-      <c r="Q33" s="141"/>
-      <c r="R33" s="142"/>
-      <c r="S33" s="140"/>
-      <c r="T33" s="141"/>
-      <c r="U33" s="142"/>
-      <c r="V33" s="140"/>
-      <c r="W33" s="141"/>
-      <c r="X33" s="141"/>
-      <c r="Y33" s="142"/>
-      <c r="Z33" s="140"/>
-      <c r="AA33" s="141"/>
-      <c r="AB33" s="142"/>
-      <c r="AC33" s="140"/>
-      <c r="AD33" s="141"/>
-      <c r="AE33" s="141"/>
-      <c r="AF33" s="142"/>
-      <c r="AG33" s="140"/>
-      <c r="AH33" s="141"/>
-      <c r="AI33" s="142"/>
-      <c r="AJ33" s="140"/>
-      <c r="AK33" s="141"/>
-      <c r="AL33" s="141"/>
-      <c r="AM33" s="142"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="89"/>
+      <c r="M33" s="90"/>
+      <c r="N33" s="91"/>
+      <c r="O33" s="89"/>
+      <c r="P33" s="90"/>
+      <c r="Q33" s="90"/>
+      <c r="R33" s="91"/>
+      <c r="S33" s="89"/>
+      <c r="T33" s="90"/>
+      <c r="U33" s="91"/>
+      <c r="V33" s="89"/>
+      <c r="W33" s="90"/>
+      <c r="X33" s="90"/>
+      <c r="Y33" s="91"/>
+      <c r="Z33" s="89"/>
+      <c r="AA33" s="90"/>
+      <c r="AB33" s="91"/>
+      <c r="AC33" s="89"/>
+      <c r="AD33" s="90"/>
+      <c r="AE33" s="90"/>
+      <c r="AF33" s="91"/>
+      <c r="AG33" s="89"/>
+      <c r="AH33" s="90"/>
+      <c r="AI33" s="91"/>
+      <c r="AJ33" s="89"/>
+      <c r="AK33" s="90"/>
+      <c r="AL33" s="90"/>
+      <c r="AM33" s="91"/>
     </row>
     <row r="34" spans="1:39">
       <c r="A34" s="76" t="s">
@@ -11965,140 +12188,28 @@
     <row r="62" hidden="1"/>
   </sheetData>
   <mergeCells count="172">
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:K7"/>
-    <mergeCell ref="L7:R7"/>
-    <mergeCell ref="S7:Y7"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AM7"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="L6:R6"/>
-    <mergeCell ref="S6:Y6"/>
-    <mergeCell ref="Z6:AF6"/>
-    <mergeCell ref="AG6:AM6"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:K9"/>
-    <mergeCell ref="L9:R9"/>
-    <mergeCell ref="S9:Y9"/>
-    <mergeCell ref="Z9:AF9"/>
-    <mergeCell ref="AG9:AM9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:K8"/>
-    <mergeCell ref="L8:R8"/>
-    <mergeCell ref="S8:Y8"/>
-    <mergeCell ref="Z8:AF8"/>
-    <mergeCell ref="AG8:AM8"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E11:K11"/>
-    <mergeCell ref="L11:R11"/>
-    <mergeCell ref="S11:Y11"/>
-    <mergeCell ref="Z11:AF11"/>
-    <mergeCell ref="AG11:AM11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E10:K10"/>
-    <mergeCell ref="L10:R10"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="Z10:AF10"/>
-    <mergeCell ref="AG10:AM10"/>
-    <mergeCell ref="AG14:AM14"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:K13"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="S13:Y13"/>
-    <mergeCell ref="Z13:AF13"/>
-    <mergeCell ref="AG13:AM13"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E12:K12"/>
-    <mergeCell ref="L12:R12"/>
-    <mergeCell ref="S12:Y12"/>
-    <mergeCell ref="Z12:AF12"/>
-    <mergeCell ref="AG12:AM12"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A22:D23"/>
-    <mergeCell ref="E22:K22"/>
-    <mergeCell ref="L22:R22"/>
-    <mergeCell ref="S22:Y22"/>
-    <mergeCell ref="Z22:AF22"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:K14"/>
-    <mergeCell ref="L14:R14"/>
-    <mergeCell ref="S14:Y14"/>
-    <mergeCell ref="Z14:AF14"/>
-    <mergeCell ref="AG22:AM22"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="V23:Y23"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="AC23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="AJ23:AM23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="V24:Y24"/>
-    <mergeCell ref="Z24:AB24"/>
-    <mergeCell ref="AC24:AF24"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="AJ24:AM24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="S25:U25"/>
-    <mergeCell ref="V25:Y25"/>
-    <mergeCell ref="Z25:AB25"/>
-    <mergeCell ref="AC25:AF25"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AM25"/>
-    <mergeCell ref="A26:D27"/>
-    <mergeCell ref="E26:K26"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="S26:Y26"/>
-    <mergeCell ref="Z26:AF26"/>
-    <mergeCell ref="AG26:AM26"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="AC27:AF27"/>
-    <mergeCell ref="AG27:AI27"/>
-    <mergeCell ref="AJ27:AM27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="S28:U28"/>
-    <mergeCell ref="V28:Y28"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="S27:U27"/>
-    <mergeCell ref="V27:Y27"/>
-    <mergeCell ref="Z27:AB27"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="AC28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ28:AM28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="S29:U29"/>
-    <mergeCell ref="V29:Y29"/>
-    <mergeCell ref="Z29:AB29"/>
-    <mergeCell ref="AC29:AF29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AM29"/>
+    <mergeCell ref="AC33:AF33"/>
+    <mergeCell ref="AG33:AI33"/>
+    <mergeCell ref="AJ33:AM33"/>
+    <mergeCell ref="AG32:AI32"/>
+    <mergeCell ref="AJ32:AM32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="S33:U33"/>
+    <mergeCell ref="V33:Y33"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="S32:U32"/>
+    <mergeCell ref="V32:Y32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="AC32:AF32"/>
     <mergeCell ref="A30:D31"/>
     <mergeCell ref="E30:K30"/>
     <mergeCell ref="L30:R30"/>
@@ -12115,28 +12226,140 @@
     <mergeCell ref="AC31:AF31"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="AJ31:AM31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="S32:U32"/>
-    <mergeCell ref="V32:Y32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="AC32:AF32"/>
-    <mergeCell ref="AC33:AF33"/>
-    <mergeCell ref="AG33:AI33"/>
-    <mergeCell ref="AJ33:AM33"/>
-    <mergeCell ref="AG32:AI32"/>
-    <mergeCell ref="AJ32:AM32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="S33:U33"/>
-    <mergeCell ref="V33:Y33"/>
-    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="AC28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AJ28:AM28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="S29:U29"/>
+    <mergeCell ref="V29:Y29"/>
+    <mergeCell ref="Z29:AB29"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AM29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="S28:U28"/>
+    <mergeCell ref="V28:Y28"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="S27:U27"/>
+    <mergeCell ref="V27:Y27"/>
+    <mergeCell ref="A26:D27"/>
+    <mergeCell ref="E26:K26"/>
+    <mergeCell ref="L26:R26"/>
+    <mergeCell ref="S26:Y26"/>
+    <mergeCell ref="Z26:AF26"/>
+    <mergeCell ref="AG26:AM26"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="AC27:AF27"/>
+    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ27:AM27"/>
+    <mergeCell ref="Z27:AB27"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AJ24:AM24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="S25:U25"/>
+    <mergeCell ref="V25:Y25"/>
+    <mergeCell ref="Z25:AB25"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AM25"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="V24:Y24"/>
+    <mergeCell ref="Z24:AB24"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="AG22:AM22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S23:U23"/>
+    <mergeCell ref="V23:Y23"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="AC23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AM23"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A22:D23"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="L22:R22"/>
+    <mergeCell ref="S22:Y22"/>
+    <mergeCell ref="Z22:AF22"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:K14"/>
+    <mergeCell ref="L14:R14"/>
+    <mergeCell ref="S14:Y14"/>
+    <mergeCell ref="Z14:AF14"/>
+    <mergeCell ref="AG14:AM14"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:K13"/>
+    <mergeCell ref="L13:R13"/>
+    <mergeCell ref="S13:Y13"/>
+    <mergeCell ref="Z13:AF13"/>
+    <mergeCell ref="AG13:AM13"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:K12"/>
+    <mergeCell ref="L12:R12"/>
+    <mergeCell ref="S12:Y12"/>
+    <mergeCell ref="Z12:AF12"/>
+    <mergeCell ref="AG12:AM12"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:K11"/>
+    <mergeCell ref="L11:R11"/>
+    <mergeCell ref="S11:Y11"/>
+    <mergeCell ref="Z11:AF11"/>
+    <mergeCell ref="AG11:AM11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:K10"/>
+    <mergeCell ref="L10:R10"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="Z10:AF10"/>
+    <mergeCell ref="AG10:AM10"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:K9"/>
+    <mergeCell ref="L9:R9"/>
+    <mergeCell ref="S9:Y9"/>
+    <mergeCell ref="Z9:AF9"/>
+    <mergeCell ref="AG9:AM9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:K8"/>
+    <mergeCell ref="L8:R8"/>
+    <mergeCell ref="S8:Y8"/>
+    <mergeCell ref="Z8:AF8"/>
+    <mergeCell ref="AG8:AM8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:K7"/>
+    <mergeCell ref="L7:R7"/>
+    <mergeCell ref="S7:Y7"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AM7"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="L6:R6"/>
+    <mergeCell ref="S6:Y6"/>
+    <mergeCell ref="Z6:AF6"/>
+    <mergeCell ref="AG6:AM6"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.47244094488188981" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12177,32 +12400,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
-      <c r="Z1" s="149"/>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
-      <c r="AC1" s="149"/>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="149"/>
-      <c r="AJ1" s="149"/>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="84"/>
+      <c r="AD1" s="84"/>
+      <c r="AE1" s="84"/>
+      <c r="AF1" s="84"/>
+      <c r="AG1" s="84"/>
+      <c r="AH1" s="84"/>
+      <c r="AI1" s="84"/>
+      <c r="AJ1" s="84"/>
+      <c r="AK1" s="84"/>
+      <c r="AL1" s="84"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="33" t="s">
@@ -12244,17 +12467,17 @@
       <c r="AL2" s="34"/>
     </row>
     <row r="3" spans="1:38">
-      <c r="A3" s="146"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="146"/>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -12331,12 +12554,12 @@
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="35"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="151"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
       <c r="L5" s="6" t="s">
         <v>129</v>
       </c>
@@ -12374,13 +12597,13 @@
       <c r="B6" s="6"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
-      <c r="E6" s="151"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="151"/>
-      <c r="H6" s="151"/>
-      <c r="I6" s="151"/>
-      <c r="J6" s="151"/>
-      <c r="K6" s="151"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160"/>
       <c r="L6" s="6" t="s">
         <v>131</v>
       </c>
@@ -12422,13 +12645,13 @@
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="37"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="152"/>
-      <c r="O7" s="152"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="161"/>
       <c r="P7" s="37"/>
       <c r="Q7" s="37"/>
       <c r="R7" s="37"/>
@@ -12544,40 +12767,40 @@
       <c r="D10" s="154"/>
       <c r="E10" s="154"/>
       <c r="F10" s="154"/>
-      <c r="G10" s="157" t="s">
+      <c r="G10" s="158" t="s">
         <v>134</v>
       </c>
-      <c r="H10" s="158"/>
+      <c r="H10" s="159"/>
       <c r="I10" s="156"/>
-      <c r="J10" s="150"/>
-      <c r="K10" s="150"/>
-      <c r="L10" s="150"/>
-      <c r="M10" s="150"/>
-      <c r="N10" s="150"/>
-      <c r="O10" s="150"/>
-      <c r="P10" s="150"/>
-      <c r="Q10" s="150"/>
-      <c r="R10" s="150"/>
-      <c r="S10" s="150"/>
-      <c r="T10" s="150"/>
-      <c r="U10" s="150"/>
-      <c r="V10" s="150"/>
-      <c r="W10" s="150"/>
-      <c r="X10" s="150"/>
-      <c r="Y10" s="150"/>
-      <c r="Z10" s="150"/>
-      <c r="AA10" s="150"/>
-      <c r="AB10" s="150"/>
-      <c r="AC10" s="150"/>
-      <c r="AD10" s="150"/>
-      <c r="AE10" s="150"/>
-      <c r="AF10" s="150"/>
-      <c r="AG10" s="150"/>
-      <c r="AH10" s="150"/>
-      <c r="AI10" s="150"/>
-      <c r="AJ10" s="150"/>
-      <c r="AK10" s="150"/>
-      <c r="AL10" s="150"/>
+      <c r="J10" s="157"/>
+      <c r="K10" s="157"/>
+      <c r="L10" s="157"/>
+      <c r="M10" s="157"/>
+      <c r="N10" s="157"/>
+      <c r="O10" s="157"/>
+      <c r="P10" s="157"/>
+      <c r="Q10" s="157"/>
+      <c r="R10" s="157"/>
+      <c r="S10" s="157"/>
+      <c r="T10" s="157"/>
+      <c r="U10" s="157"/>
+      <c r="V10" s="157"/>
+      <c r="W10" s="157"/>
+      <c r="X10" s="157"/>
+      <c r="Y10" s="157"/>
+      <c r="Z10" s="157"/>
+      <c r="AA10" s="157"/>
+      <c r="AB10" s="157"/>
+      <c r="AC10" s="157"/>
+      <c r="AD10" s="157"/>
+      <c r="AE10" s="157"/>
+      <c r="AF10" s="157"/>
+      <c r="AG10" s="157"/>
+      <c r="AH10" s="157"/>
+      <c r="AI10" s="157"/>
+      <c r="AJ10" s="157"/>
+      <c r="AK10" s="157"/>
+      <c r="AL10" s="157"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1">
       <c r="A11" s="153" t="s">
@@ -13089,146 +13312,146 @@
       </c>
     </row>
     <row r="24" spans="1:38">
-      <c r="A24" s="144" t="s">
+      <c r="A24" s="88" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="144"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="145" t="s">
+      <c r="B24" s="88"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="J24" s="145"/>
-      <c r="K24" s="145"/>
-      <c r="L24" s="145"/>
-      <c r="M24" s="145"/>
-      <c r="N24" s="145"/>
-      <c r="O24" s="144" t="s">
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="87"/>
+      <c r="M24" s="87"/>
+      <c r="N24" s="87"/>
+      <c r="O24" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="P24" s="144"/>
-      <c r="Q24" s="144"/>
-      <c r="R24" s="144"/>
-      <c r="S24" s="144"/>
-      <c r="T24" s="144"/>
-      <c r="U24" s="144"/>
-      <c r="V24" s="144"/>
-      <c r="W24" s="144"/>
-      <c r="X24" s="144"/>
-      <c r="Y24" s="144"/>
-      <c r="Z24" s="144"/>
-      <c r="AA24" s="144"/>
-      <c r="AB24" s="144"/>
-      <c r="AC24" s="144" t="s">
+      <c r="P24" s="88"/>
+      <c r="Q24" s="88"/>
+      <c r="R24" s="88"/>
+      <c r="S24" s="88"/>
+      <c r="T24" s="88"/>
+      <c r="U24" s="88"/>
+      <c r="V24" s="88"/>
+      <c r="W24" s="88"/>
+      <c r="X24" s="88"/>
+      <c r="Y24" s="88"/>
+      <c r="Z24" s="88"/>
+      <c r="AA24" s="88"/>
+      <c r="AB24" s="88"/>
+      <c r="AC24" s="88" t="s">
         <v>151</v>
       </c>
-      <c r="AD24" s="144"/>
-      <c r="AE24" s="144"/>
-      <c r="AF24" s="144"/>
-      <c r="AG24" s="144"/>
-      <c r="AH24" s="144"/>
-      <c r="AI24" s="144"/>
-      <c r="AJ24" s="144"/>
-      <c r="AK24" s="144"/>
-      <c r="AL24" s="144"/>
+      <c r="AD24" s="88"/>
+      <c r="AE24" s="88"/>
+      <c r="AF24" s="88"/>
+      <c r="AG24" s="88"/>
+      <c r="AH24" s="88"/>
+      <c r="AI24" s="88"/>
+      <c r="AJ24" s="88"/>
+      <c r="AK24" s="88"/>
+      <c r="AL24" s="88"/>
     </row>
     <row r="25" spans="1:38">
-      <c r="A25" s="144" t="s">
+      <c r="A25" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="144"/>
-      <c r="C25" s="144"/>
-      <c r="D25" s="144"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="144"/>
-      <c r="I25" s="144">
+      <c r="B25" s="88"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88"/>
+      <c r="I25" s="88">
         <v>20</v>
       </c>
-      <c r="J25" s="144"/>
-      <c r="K25" s="144"/>
-      <c r="L25" s="144"/>
-      <c r="M25" s="144"/>
-      <c r="N25" s="144"/>
-      <c r="O25" s="159" t="s">
+      <c r="J25" s="88"/>
+      <c r="K25" s="88"/>
+      <c r="L25" s="88"/>
+      <c r="M25" s="88"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="150" t="s">
         <v>152</v>
       </c>
-      <c r="P25" s="160"/>
-      <c r="Q25" s="160"/>
-      <c r="R25" s="160"/>
-      <c r="S25" s="160"/>
-      <c r="T25" s="160"/>
-      <c r="U25" s="160"/>
-      <c r="V25" s="160"/>
-      <c r="W25" s="160"/>
-      <c r="X25" s="160"/>
-      <c r="Y25" s="161"/>
-      <c r="Z25" s="159">
+      <c r="P25" s="151"/>
+      <c r="Q25" s="151"/>
+      <c r="R25" s="151"/>
+      <c r="S25" s="151"/>
+      <c r="T25" s="151"/>
+      <c r="U25" s="151"/>
+      <c r="V25" s="151"/>
+      <c r="W25" s="151"/>
+      <c r="X25" s="151"/>
+      <c r="Y25" s="152"/>
+      <c r="Z25" s="150">
         <v>100</v>
       </c>
-      <c r="AA25" s="160"/>
-      <c r="AB25" s="161"/>
-      <c r="AC25" s="144" t="s">
+      <c r="AA25" s="151"/>
+      <c r="AB25" s="152"/>
+      <c r="AC25" s="88" t="s">
         <v>154</v>
       </c>
-      <c r="AD25" s="144"/>
-      <c r="AE25" s="144"/>
-      <c r="AF25" s="144"/>
-      <c r="AG25" s="144"/>
-      <c r="AH25" s="144"/>
-      <c r="AI25" s="144"/>
-      <c r="AJ25" s="144"/>
-      <c r="AK25" s="144"/>
-      <c r="AL25" s="144"/>
+      <c r="AD25" s="88"/>
+      <c r="AE25" s="88"/>
+      <c r="AF25" s="88"/>
+      <c r="AG25" s="88"/>
+      <c r="AH25" s="88"/>
+      <c r="AI25" s="88"/>
+      <c r="AJ25" s="88"/>
+      <c r="AK25" s="88"/>
+      <c r="AL25" s="88"/>
     </row>
     <row r="26" spans="1:38">
-      <c r="A26" s="144"/>
-      <c r="B26" s="144"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="144"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="144"/>
-      <c r="L26" s="144"/>
-      <c r="M26" s="144"/>
-      <c r="N26" s="144"/>
-      <c r="O26" s="159" t="s">
+      <c r="A26" s="88"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="88"/>
+      <c r="K26" s="88"/>
+      <c r="L26" s="88"/>
+      <c r="M26" s="88"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="150" t="s">
         <v>153</v>
       </c>
-      <c r="P26" s="160"/>
-      <c r="Q26" s="160"/>
-      <c r="R26" s="160"/>
-      <c r="S26" s="160"/>
-      <c r="T26" s="160"/>
-      <c r="U26" s="160"/>
-      <c r="V26" s="160"/>
-      <c r="W26" s="160"/>
-      <c r="X26" s="160"/>
-      <c r="Y26" s="161"/>
-      <c r="Z26" s="159">
+      <c r="P26" s="151"/>
+      <c r="Q26" s="151"/>
+      <c r="R26" s="151"/>
+      <c r="S26" s="151"/>
+      <c r="T26" s="151"/>
+      <c r="U26" s="151"/>
+      <c r="V26" s="151"/>
+      <c r="W26" s="151"/>
+      <c r="X26" s="151"/>
+      <c r="Y26" s="152"/>
+      <c r="Z26" s="150">
         <v>200</v>
       </c>
-      <c r="AA26" s="160"/>
-      <c r="AB26" s="161"/>
-      <c r="AC26" s="144"/>
-      <c r="AD26" s="144"/>
-      <c r="AE26" s="144"/>
-      <c r="AF26" s="144"/>
-      <c r="AG26" s="144"/>
-      <c r="AH26" s="144"/>
-      <c r="AI26" s="144"/>
-      <c r="AJ26" s="144"/>
-      <c r="AK26" s="144"/>
-      <c r="AL26" s="144"/>
+      <c r="AA26" s="151"/>
+      <c r="AB26" s="152"/>
+      <c r="AC26" s="88"/>
+      <c r="AD26" s="88"/>
+      <c r="AE26" s="88"/>
+      <c r="AF26" s="88"/>
+      <c r="AG26" s="88"/>
+      <c r="AH26" s="88"/>
+      <c r="AI26" s="88"/>
+      <c r="AJ26" s="88"/>
+      <c r="AK26" s="88"/>
+      <c r="AL26" s="88"/>
     </row>
     <row r="27" spans="1:38">
       <c r="A27" s="6" t="s">
@@ -13237,77 +13460,14 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="AC24:AL24"/>
-    <mergeCell ref="A25:H26"/>
-    <mergeCell ref="I25:N26"/>
-    <mergeCell ref="AC25:AL26"/>
-    <mergeCell ref="Z25:AB25"/>
-    <mergeCell ref="Z26:AB26"/>
-    <mergeCell ref="O25:Y25"/>
-    <mergeCell ref="O26:Y26"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="O24:AB24"/>
-    <mergeCell ref="AG22:AL22"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="I21:N21"/>
-    <mergeCell ref="O21:T21"/>
-    <mergeCell ref="U21:Z21"/>
-    <mergeCell ref="AA21:AF21"/>
-    <mergeCell ref="AG21:AL21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="I22:N22"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="U22:Z22"/>
-    <mergeCell ref="AA22:AF22"/>
-    <mergeCell ref="AG20:AL20"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="U19:Z19"/>
-    <mergeCell ref="AA19:AF19"/>
-    <mergeCell ref="AG19:AL19"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="I20:N20"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="U20:Z20"/>
-    <mergeCell ref="AA20:AF20"/>
-    <mergeCell ref="AG18:AL18"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="U17:Z17"/>
-    <mergeCell ref="AA17:AF17"/>
-    <mergeCell ref="AG17:AL17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="U18:Z18"/>
-    <mergeCell ref="AA18:AF18"/>
-    <mergeCell ref="AG16:AL16"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:T15"/>
-    <mergeCell ref="U15:Z15"/>
-    <mergeCell ref="AA15:AF15"/>
-    <mergeCell ref="AG15:AL15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="AA16:AF16"/>
-    <mergeCell ref="AG13:AL13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="U14:Z14"/>
-    <mergeCell ref="AA14:AF14"/>
-    <mergeCell ref="AG14:AL14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="U13:Z13"/>
-    <mergeCell ref="AA13:AF13"/>
+    <mergeCell ref="U10:Z10"/>
+    <mergeCell ref="AA10:AF10"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="F5:K5"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="AG10:AL10"/>
     <mergeCell ref="AG12:AL12"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="I11:N11"/>
@@ -13324,14 +13484,77 @@
     <mergeCell ref="U12:Z12"/>
     <mergeCell ref="AA12:AF12"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="U10:Z10"/>
-    <mergeCell ref="AA10:AF10"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="F5:K5"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="I7:O7"/>
-    <mergeCell ref="AG10:AL10"/>
+    <mergeCell ref="AG13:AL13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="U14:Z14"/>
+    <mergeCell ref="AA14:AF14"/>
+    <mergeCell ref="AG14:AL14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="U13:Z13"/>
+    <mergeCell ref="AA13:AF13"/>
+    <mergeCell ref="AG16:AL16"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:T15"/>
+    <mergeCell ref="U15:Z15"/>
+    <mergeCell ref="AA15:AF15"/>
+    <mergeCell ref="AG15:AL15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="AA16:AF16"/>
+    <mergeCell ref="AG18:AL18"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="U17:Z17"/>
+    <mergeCell ref="AA17:AF17"/>
+    <mergeCell ref="AG17:AL17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="AA18:AF18"/>
+    <mergeCell ref="AG20:AL20"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="U19:Z19"/>
+    <mergeCell ref="AA19:AF19"/>
+    <mergeCell ref="AG19:AL19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="I20:N20"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="U20:Z20"/>
+    <mergeCell ref="AA20:AF20"/>
+    <mergeCell ref="AG22:AL22"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="I21:N21"/>
+    <mergeCell ref="O21:T21"/>
+    <mergeCell ref="U21:Z21"/>
+    <mergeCell ref="AA21:AF21"/>
+    <mergeCell ref="AG21:AL21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="I22:N22"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="U22:Z22"/>
+    <mergeCell ref="AA22:AF22"/>
+    <mergeCell ref="AC24:AL24"/>
+    <mergeCell ref="A25:H26"/>
+    <mergeCell ref="I25:N26"/>
+    <mergeCell ref="AC25:AL26"/>
+    <mergeCell ref="Z25:AB25"/>
+    <mergeCell ref="Z26:AB26"/>
+    <mergeCell ref="O25:Y25"/>
+    <mergeCell ref="O26:Y26"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="O24:AB24"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13372,32 +13595,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
-      <c r="Z1" s="149"/>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
-      <c r="AC1" s="149"/>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="149"/>
-      <c r="AJ1" s="149"/>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="84"/>
+      <c r="AD1" s="84"/>
+      <c r="AE1" s="84"/>
+      <c r="AF1" s="84"/>
+      <c r="AG1" s="84"/>
+      <c r="AH1" s="84"/>
+      <c r="AI1" s="84"/>
+      <c r="AJ1" s="84"/>
+      <c r="AK1" s="84"/>
+      <c r="AL1" s="84"/>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="33" t="s">
@@ -13439,17 +13662,17 @@
       <c r="AL2" s="34"/>
     </row>
     <row r="3" spans="1:38">
-      <c r="A3" s="146"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="146"/>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
@@ -13606,9 +13829,9 @@
       <c r="A7" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="149"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="149"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
       <c r="H7" s="63" t="s">
         <v>113</v>
       </c>
@@ -13639,270 +13862,270 @@
       <c r="AL7" s="34"/>
     </row>
     <row r="8" spans="1:38">
-      <c r="A8" s="171" t="s">
+      <c r="A8" s="177" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="171"/>
-      <c r="C8" s="171"/>
-      <c r="D8" s="171"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="171" t="s">
+      <c r="B8" s="177"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="171"/>
-      <c r="H8" s="171"/>
-      <c r="I8" s="171"/>
-      <c r="J8" s="171" t="s">
+      <c r="G8" s="177"/>
+      <c r="H8" s="177"/>
+      <c r="I8" s="177"/>
+      <c r="J8" s="177" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="171"/>
-      <c r="L8" s="171"/>
-      <c r="M8" s="171"/>
-      <c r="N8" s="171"/>
-      <c r="O8" s="171"/>
-      <c r="P8" s="171"/>
-      <c r="Q8" s="171"/>
-      <c r="R8" s="171"/>
-      <c r="S8" s="171"/>
-      <c r="T8" s="171"/>
-      <c r="U8" s="171"/>
-      <c r="V8" s="171"/>
-      <c r="W8" s="171"/>
-      <c r="X8" s="171"/>
-      <c r="Y8" s="171"/>
-      <c r="Z8" s="171"/>
-      <c r="AA8" s="171"/>
-      <c r="AB8" s="171"/>
-      <c r="AC8" s="171"/>
-      <c r="AD8" s="171"/>
-      <c r="AE8" s="171"/>
-      <c r="AF8" s="171"/>
-      <c r="AG8" s="171"/>
-      <c r="AH8" s="171"/>
-      <c r="AI8" s="172" t="s">
+      <c r="K8" s="177"/>
+      <c r="L8" s="177"/>
+      <c r="M8" s="177"/>
+      <c r="N8" s="177"/>
+      <c r="O8" s="177"/>
+      <c r="P8" s="177"/>
+      <c r="Q8" s="177"/>
+      <c r="R8" s="177"/>
+      <c r="S8" s="177"/>
+      <c r="T8" s="177"/>
+      <c r="U8" s="177"/>
+      <c r="V8" s="177"/>
+      <c r="W8" s="177"/>
+      <c r="X8" s="177"/>
+      <c r="Y8" s="177"/>
+      <c r="Z8" s="177"/>
+      <c r="AA8" s="177"/>
+      <c r="AB8" s="177"/>
+      <c r="AC8" s="177"/>
+      <c r="AD8" s="177"/>
+      <c r="AE8" s="177"/>
+      <c r="AF8" s="177"/>
+      <c r="AG8" s="177"/>
+      <c r="AH8" s="177"/>
+      <c r="AI8" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="AJ8" s="173"/>
-      <c r="AK8" s="173"/>
-      <c r="AL8" s="174"/>
+      <c r="AJ8" s="172"/>
+      <c r="AK8" s="172"/>
+      <c r="AL8" s="173"/>
     </row>
     <row r="9" spans="1:38">
-      <c r="A9" s="171"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="171"/>
-      <c r="G9" s="171"/>
-      <c r="H9" s="171"/>
-      <c r="I9" s="171"/>
-      <c r="J9" s="171" t="s">
+      <c r="A9" s="177"/>
+      <c r="B9" s="177"/>
+      <c r="C9" s="177"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="177"/>
+      <c r="F9" s="177"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="177"/>
+      <c r="I9" s="177"/>
+      <c r="J9" s="177" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="171"/>
-      <c r="L9" s="171"/>
-      <c r="M9" s="171"/>
-      <c r="N9" s="171"/>
-      <c r="O9" s="171" t="s">
+      <c r="K9" s="177"/>
+      <c r="L9" s="177"/>
+      <c r="M9" s="177"/>
+      <c r="N9" s="177"/>
+      <c r="O9" s="177" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="171"/>
-      <c r="Q9" s="171"/>
-      <c r="R9" s="171"/>
-      <c r="S9" s="171"/>
-      <c r="T9" s="171" t="s">
+      <c r="P9" s="177"/>
+      <c r="Q9" s="177"/>
+      <c r="R9" s="177"/>
+      <c r="S9" s="177"/>
+      <c r="T9" s="177" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="171"/>
-      <c r="V9" s="171"/>
-      <c r="W9" s="171"/>
-      <c r="X9" s="171"/>
-      <c r="Y9" s="171" t="s">
+      <c r="U9" s="177"/>
+      <c r="V9" s="177"/>
+      <c r="W9" s="177"/>
+      <c r="X9" s="177"/>
+      <c r="Y9" s="177" t="s">
         <v>12</v>
       </c>
-      <c r="Z9" s="171"/>
-      <c r="AA9" s="171"/>
-      <c r="AB9" s="171"/>
-      <c r="AC9" s="171"/>
-      <c r="AD9" s="171" t="s">
+      <c r="Z9" s="177"/>
+      <c r="AA9" s="177"/>
+      <c r="AB9" s="177"/>
+      <c r="AC9" s="177"/>
+      <c r="AD9" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="AE9" s="171"/>
-      <c r="AF9" s="171"/>
-      <c r="AG9" s="171"/>
-      <c r="AH9" s="171"/>
-      <c r="AI9" s="175"/>
-      <c r="AJ9" s="176"/>
-      <c r="AK9" s="176"/>
-      <c r="AL9" s="177"/>
+      <c r="AE9" s="177"/>
+      <c r="AF9" s="177"/>
+      <c r="AG9" s="177"/>
+      <c r="AH9" s="177"/>
+      <c r="AI9" s="174"/>
+      <c r="AJ9" s="175"/>
+      <c r="AK9" s="175"/>
+      <c r="AL9" s="176"/>
     </row>
     <row r="10" spans="1:38">
-      <c r="A10" s="165"/>
-      <c r="B10" s="166"/>
-      <c r="C10" s="166"/>
-      <c r="D10" s="166"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="163" t="s">
+      <c r="A10" s="162"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="164"/>
+      <c r="F10" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="G10" s="163"/>
-      <c r="H10" s="163"/>
-      <c r="I10" s="163"/>
-      <c r="J10" s="162"/>
-      <c r="K10" s="163"/>
-      <c r="L10" s="163"/>
-      <c r="M10" s="163"/>
-      <c r="N10" s="163"/>
-      <c r="O10" s="162"/>
-      <c r="P10" s="163"/>
-      <c r="Q10" s="163"/>
-      <c r="R10" s="163"/>
-      <c r="S10" s="163"/>
-      <c r="T10" s="162"/>
-      <c r="U10" s="163"/>
-      <c r="V10" s="163"/>
-      <c r="W10" s="163"/>
-      <c r="X10" s="163"/>
-      <c r="Y10" s="162"/>
-      <c r="Z10" s="163"/>
-      <c r="AA10" s="163"/>
-      <c r="AB10" s="163"/>
-      <c r="AC10" s="163"/>
-      <c r="AD10" s="162"/>
-      <c r="AE10" s="163"/>
-      <c r="AF10" s="163"/>
-      <c r="AG10" s="163"/>
-      <c r="AH10" s="163"/>
-      <c r="AI10" s="162"/>
-      <c r="AJ10" s="163"/>
-      <c r="AK10" s="163"/>
-      <c r="AL10" s="164"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="169"/>
+      <c r="J10" s="168"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="169"/>
+      <c r="M10" s="169"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="168"/>
+      <c r="P10" s="169"/>
+      <c r="Q10" s="169"/>
+      <c r="R10" s="169"/>
+      <c r="S10" s="169"/>
+      <c r="T10" s="168"/>
+      <c r="U10" s="169"/>
+      <c r="V10" s="169"/>
+      <c r="W10" s="169"/>
+      <c r="X10" s="169"/>
+      <c r="Y10" s="168"/>
+      <c r="Z10" s="169"/>
+      <c r="AA10" s="169"/>
+      <c r="AB10" s="169"/>
+      <c r="AC10" s="169"/>
+      <c r="AD10" s="168"/>
+      <c r="AE10" s="169"/>
+      <c r="AF10" s="169"/>
+      <c r="AG10" s="169"/>
+      <c r="AH10" s="169"/>
+      <c r="AI10" s="168"/>
+      <c r="AJ10" s="169"/>
+      <c r="AK10" s="169"/>
+      <c r="AL10" s="170"/>
     </row>
     <row r="11" spans="1:38" ht="16.2">
-      <c r="A11" s="168"/>
-      <c r="B11" s="169"/>
-      <c r="C11" s="169"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="170"/>
-      <c r="F11" s="163" t="s">
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="169" t="s">
         <v>118</v>
       </c>
-      <c r="G11" s="163"/>
-      <c r="H11" s="163"/>
-      <c r="I11" s="163"/>
-      <c r="J11" s="162"/>
-      <c r="K11" s="163"/>
-      <c r="L11" s="163"/>
-      <c r="M11" s="163"/>
-      <c r="N11" s="163"/>
-      <c r="O11" s="162"/>
-      <c r="P11" s="163"/>
-      <c r="Q11" s="163"/>
-      <c r="R11" s="163"/>
-      <c r="S11" s="163"/>
-      <c r="T11" s="162"/>
-      <c r="U11" s="163"/>
-      <c r="V11" s="163"/>
-      <c r="W11" s="163"/>
-      <c r="X11" s="163"/>
-      <c r="Y11" s="162"/>
-      <c r="Z11" s="163"/>
-      <c r="AA11" s="163"/>
-      <c r="AB11" s="163"/>
-      <c r="AC11" s="163"/>
-      <c r="AD11" s="162"/>
-      <c r="AE11" s="163"/>
-      <c r="AF11" s="163"/>
-      <c r="AG11" s="163"/>
-      <c r="AH11" s="163"/>
-      <c r="AI11" s="162"/>
-      <c r="AJ11" s="163"/>
-      <c r="AK11" s="163"/>
-      <c r="AL11" s="164"/>
+      <c r="G11" s="169"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="169"/>
+      <c r="J11" s="168"/>
+      <c r="K11" s="169"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="169"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="168"/>
+      <c r="P11" s="169"/>
+      <c r="Q11" s="169"/>
+      <c r="R11" s="169"/>
+      <c r="S11" s="169"/>
+      <c r="T11" s="168"/>
+      <c r="U11" s="169"/>
+      <c r="V11" s="169"/>
+      <c r="W11" s="169"/>
+      <c r="X11" s="169"/>
+      <c r="Y11" s="168"/>
+      <c r="Z11" s="169"/>
+      <c r="AA11" s="169"/>
+      <c r="AB11" s="169"/>
+      <c r="AC11" s="169"/>
+      <c r="AD11" s="168"/>
+      <c r="AE11" s="169"/>
+      <c r="AF11" s="169"/>
+      <c r="AG11" s="169"/>
+      <c r="AH11" s="169"/>
+      <c r="AI11" s="168"/>
+      <c r="AJ11" s="169"/>
+      <c r="AK11" s="169"/>
+      <c r="AL11" s="170"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="165"/>
-      <c r="B12" s="166"/>
-      <c r="C12" s="166"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="163" t="s">
+      <c r="A12" s="162"/>
+      <c r="B12" s="163"/>
+      <c r="C12" s="163"/>
+      <c r="D12" s="163"/>
+      <c r="E12" s="164"/>
+      <c r="F12" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="163"/>
-      <c r="H12" s="163"/>
-      <c r="I12" s="163"/>
-      <c r="J12" s="162"/>
-      <c r="K12" s="163"/>
-      <c r="L12" s="163"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="163"/>
-      <c r="O12" s="162"/>
-      <c r="P12" s="163"/>
-      <c r="Q12" s="163"/>
-      <c r="R12" s="163"/>
-      <c r="S12" s="163"/>
-      <c r="T12" s="162"/>
-      <c r="U12" s="163"/>
-      <c r="V12" s="163"/>
-      <c r="W12" s="163"/>
-      <c r="X12" s="163"/>
-      <c r="Y12" s="162"/>
-      <c r="Z12" s="163"/>
-      <c r="AA12" s="163"/>
-      <c r="AB12" s="163"/>
-      <c r="AC12" s="163"/>
-      <c r="AD12" s="162"/>
-      <c r="AE12" s="163"/>
-      <c r="AF12" s="163"/>
-      <c r="AG12" s="163"/>
-      <c r="AH12" s="163"/>
-      <c r="AI12" s="162"/>
-      <c r="AJ12" s="163"/>
-      <c r="AK12" s="163"/>
-      <c r="AL12" s="164"/>
+      <c r="G12" s="169"/>
+      <c r="H12" s="169"/>
+      <c r="I12" s="169"/>
+      <c r="J12" s="168"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="168"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="169"/>
+      <c r="R12" s="169"/>
+      <c r="S12" s="169"/>
+      <c r="T12" s="168"/>
+      <c r="U12" s="169"/>
+      <c r="V12" s="169"/>
+      <c r="W12" s="169"/>
+      <c r="X12" s="169"/>
+      <c r="Y12" s="168"/>
+      <c r="Z12" s="169"/>
+      <c r="AA12" s="169"/>
+      <c r="AB12" s="169"/>
+      <c r="AC12" s="169"/>
+      <c r="AD12" s="168"/>
+      <c r="AE12" s="169"/>
+      <c r="AF12" s="169"/>
+      <c r="AG12" s="169"/>
+      <c r="AH12" s="169"/>
+      <c r="AI12" s="168"/>
+      <c r="AJ12" s="169"/>
+      <c r="AK12" s="169"/>
+      <c r="AL12" s="170"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="168"/>
-      <c r="B13" s="169"/>
-      <c r="C13" s="169"/>
-      <c r="D13" s="169"/>
-      <c r="E13" s="170"/>
-      <c r="F13" s="163" t="s">
+      <c r="A13" s="165"/>
+      <c r="B13" s="166"/>
+      <c r="C13" s="166"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="169" t="s">
         <v>118</v>
       </c>
-      <c r="G13" s="163"/>
-      <c r="H13" s="163"/>
-      <c r="I13" s="163"/>
-      <c r="J13" s="162"/>
-      <c r="K13" s="163"/>
-      <c r="L13" s="163"/>
-      <c r="M13" s="163"/>
-      <c r="N13" s="163"/>
-      <c r="O13" s="162"/>
-      <c r="P13" s="163"/>
-      <c r="Q13" s="163"/>
-      <c r="R13" s="163"/>
-      <c r="S13" s="163"/>
-      <c r="T13" s="162"/>
-      <c r="U13" s="163"/>
-      <c r="V13" s="163"/>
-      <c r="W13" s="163"/>
-      <c r="X13" s="163"/>
-      <c r="Y13" s="162"/>
-      <c r="Z13" s="163"/>
-      <c r="AA13" s="163"/>
-      <c r="AB13" s="163"/>
-      <c r="AC13" s="163"/>
-      <c r="AD13" s="162"/>
-      <c r="AE13" s="163"/>
-      <c r="AF13" s="163"/>
-      <c r="AG13" s="163"/>
-      <c r="AH13" s="163"/>
-      <c r="AI13" s="162"/>
-      <c r="AJ13" s="163"/>
-      <c r="AK13" s="163"/>
-      <c r="AL13" s="164"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="169"/>
+      <c r="I13" s="169"/>
+      <c r="J13" s="168"/>
+      <c r="K13" s="169"/>
+      <c r="L13" s="169"/>
+      <c r="M13" s="169"/>
+      <c r="N13" s="169"/>
+      <c r="O13" s="168"/>
+      <c r="P13" s="169"/>
+      <c r="Q13" s="169"/>
+      <c r="R13" s="169"/>
+      <c r="S13" s="169"/>
+      <c r="T13" s="168"/>
+      <c r="U13" s="169"/>
+      <c r="V13" s="169"/>
+      <c r="W13" s="169"/>
+      <c r="X13" s="169"/>
+      <c r="Y13" s="168"/>
+      <c r="Z13" s="169"/>
+      <c r="AA13" s="169"/>
+      <c r="AB13" s="169"/>
+      <c r="AC13" s="169"/>
+      <c r="AD13" s="168"/>
+      <c r="AE13" s="169"/>
+      <c r="AF13" s="169"/>
+      <c r="AG13" s="169"/>
+      <c r="AH13" s="169"/>
+      <c r="AI13" s="168"/>
+      <c r="AJ13" s="169"/>
+      <c r="AK13" s="169"/>
+      <c r="AL13" s="170"/>
     </row>
     <row r="14" spans="1:38" ht="10.8" customHeight="1">
       <c r="A14" s="35"/>
@@ -13948,9 +14171,9 @@
       <c r="A15" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="149"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
       <c r="H15" s="63" t="s">
         <v>113</v>
       </c>
@@ -13981,270 +14204,270 @@
       <c r="AL15" s="34"/>
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
-      <c r="A16" s="171" t="s">
+      <c r="A16" s="177" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="171"/>
-      <c r="C16" s="171"/>
-      <c r="D16" s="171"/>
-      <c r="E16" s="171"/>
-      <c r="F16" s="171" t="s">
+      <c r="B16" s="177"/>
+      <c r="C16" s="177"/>
+      <c r="D16" s="177"/>
+      <c r="E16" s="177"/>
+      <c r="F16" s="177" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="171"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="171"/>
-      <c r="J16" s="171" t="s">
+      <c r="G16" s="177"/>
+      <c r="H16" s="177"/>
+      <c r="I16" s="177"/>
+      <c r="J16" s="177" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="171"/>
-      <c r="L16" s="171"/>
-      <c r="M16" s="171"/>
-      <c r="N16" s="171"/>
-      <c r="O16" s="171"/>
-      <c r="P16" s="171"/>
-      <c r="Q16" s="171"/>
-      <c r="R16" s="171"/>
-      <c r="S16" s="171"/>
-      <c r="T16" s="171"/>
-      <c r="U16" s="171"/>
-      <c r="V16" s="171"/>
-      <c r="W16" s="171"/>
-      <c r="X16" s="171"/>
-      <c r="Y16" s="171"/>
-      <c r="Z16" s="171"/>
-      <c r="AA16" s="171"/>
-      <c r="AB16" s="171"/>
-      <c r="AC16" s="171"/>
-      <c r="AD16" s="171"/>
-      <c r="AE16" s="171"/>
-      <c r="AF16" s="171"/>
-      <c r="AG16" s="171"/>
-      <c r="AH16" s="171"/>
-      <c r="AI16" s="172" t="s">
+      <c r="K16" s="177"/>
+      <c r="L16" s="177"/>
+      <c r="M16" s="177"/>
+      <c r="N16" s="177"/>
+      <c r="O16" s="177"/>
+      <c r="P16" s="177"/>
+      <c r="Q16" s="177"/>
+      <c r="R16" s="177"/>
+      <c r="S16" s="177"/>
+      <c r="T16" s="177"/>
+      <c r="U16" s="177"/>
+      <c r="V16" s="177"/>
+      <c r="W16" s="177"/>
+      <c r="X16" s="177"/>
+      <c r="Y16" s="177"/>
+      <c r="Z16" s="177"/>
+      <c r="AA16" s="177"/>
+      <c r="AB16" s="177"/>
+      <c r="AC16" s="177"/>
+      <c r="AD16" s="177"/>
+      <c r="AE16" s="177"/>
+      <c r="AF16" s="177"/>
+      <c r="AG16" s="177"/>
+      <c r="AH16" s="177"/>
+      <c r="AI16" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="AJ16" s="173"/>
-      <c r="AK16" s="173"/>
-      <c r="AL16" s="174"/>
+      <c r="AJ16" s="172"/>
+      <c r="AK16" s="172"/>
+      <c r="AL16" s="173"/>
     </row>
     <row r="17" spans="1:38">
-      <c r="A17" s="171"/>
-      <c r="B17" s="171"/>
-      <c r="C17" s="171"/>
-      <c r="D17" s="171"/>
-      <c r="E17" s="171"/>
-      <c r="F17" s="171"/>
-      <c r="G17" s="171"/>
-      <c r="H17" s="171"/>
-      <c r="I17" s="171"/>
-      <c r="J17" s="171" t="s">
+      <c r="A17" s="177"/>
+      <c r="B17" s="177"/>
+      <c r="C17" s="177"/>
+      <c r="D17" s="177"/>
+      <c r="E17" s="177"/>
+      <c r="F17" s="177"/>
+      <c r="G17" s="177"/>
+      <c r="H17" s="177"/>
+      <c r="I17" s="177"/>
+      <c r="J17" s="177" t="s">
         <v>9</v>
       </c>
-      <c r="K17" s="171"/>
-      <c r="L17" s="171"/>
-      <c r="M17" s="171"/>
-      <c r="N17" s="171"/>
-      <c r="O17" s="171" t="s">
+      <c r="K17" s="177"/>
+      <c r="L17" s="177"/>
+      <c r="M17" s="177"/>
+      <c r="N17" s="177"/>
+      <c r="O17" s="177" t="s">
         <v>10</v>
       </c>
-      <c r="P17" s="171"/>
-      <c r="Q17" s="171"/>
-      <c r="R17" s="171"/>
-      <c r="S17" s="171"/>
-      <c r="T17" s="171" t="s">
+      <c r="P17" s="177"/>
+      <c r="Q17" s="177"/>
+      <c r="R17" s="177"/>
+      <c r="S17" s="177"/>
+      <c r="T17" s="177" t="s">
         <v>11</v>
       </c>
-      <c r="U17" s="171"/>
-      <c r="V17" s="171"/>
-      <c r="W17" s="171"/>
-      <c r="X17" s="171"/>
-      <c r="Y17" s="171" t="s">
+      <c r="U17" s="177"/>
+      <c r="V17" s="177"/>
+      <c r="W17" s="177"/>
+      <c r="X17" s="177"/>
+      <c r="Y17" s="177" t="s">
         <v>12</v>
       </c>
-      <c r="Z17" s="171"/>
-      <c r="AA17" s="171"/>
-      <c r="AB17" s="171"/>
-      <c r="AC17" s="171"/>
-      <c r="AD17" s="171" t="s">
+      <c r="Z17" s="177"/>
+      <c r="AA17" s="177"/>
+      <c r="AB17" s="177"/>
+      <c r="AC17" s="177"/>
+      <c r="AD17" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="AE17" s="171"/>
-      <c r="AF17" s="171"/>
-      <c r="AG17" s="171"/>
-      <c r="AH17" s="171"/>
-      <c r="AI17" s="175"/>
-      <c r="AJ17" s="176"/>
-      <c r="AK17" s="176"/>
-      <c r="AL17" s="177"/>
+      <c r="AE17" s="177"/>
+      <c r="AF17" s="177"/>
+      <c r="AG17" s="177"/>
+      <c r="AH17" s="177"/>
+      <c r="AI17" s="174"/>
+      <c r="AJ17" s="175"/>
+      <c r="AK17" s="175"/>
+      <c r="AL17" s="176"/>
     </row>
     <row r="18" spans="1:38">
-      <c r="A18" s="165"/>
-      <c r="B18" s="166"/>
-      <c r="C18" s="166"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="163" t="s">
+      <c r="A18" s="162"/>
+      <c r="B18" s="163"/>
+      <c r="C18" s="163"/>
+      <c r="D18" s="163"/>
+      <c r="E18" s="164"/>
+      <c r="F18" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="G18" s="163"/>
-      <c r="H18" s="163"/>
-      <c r="I18" s="163"/>
-      <c r="J18" s="162"/>
-      <c r="K18" s="163"/>
-      <c r="L18" s="163"/>
-      <c r="M18" s="163"/>
-      <c r="N18" s="163"/>
-      <c r="O18" s="162"/>
-      <c r="P18" s="163"/>
-      <c r="Q18" s="163"/>
-      <c r="R18" s="163"/>
-      <c r="S18" s="163"/>
-      <c r="T18" s="162"/>
-      <c r="U18" s="163"/>
-      <c r="V18" s="163"/>
-      <c r="W18" s="163"/>
-      <c r="X18" s="163"/>
-      <c r="Y18" s="162"/>
-      <c r="Z18" s="163"/>
-      <c r="AA18" s="163"/>
-      <c r="AB18" s="163"/>
-      <c r="AC18" s="163"/>
-      <c r="AD18" s="162"/>
-      <c r="AE18" s="163"/>
-      <c r="AF18" s="163"/>
-      <c r="AG18" s="163"/>
-      <c r="AH18" s="163"/>
-      <c r="AI18" s="162"/>
-      <c r="AJ18" s="163"/>
-      <c r="AK18" s="163"/>
-      <c r="AL18" s="164"/>
+      <c r="G18" s="169"/>
+      <c r="H18" s="169"/>
+      <c r="I18" s="169"/>
+      <c r="J18" s="168"/>
+      <c r="K18" s="169"/>
+      <c r="L18" s="169"/>
+      <c r="M18" s="169"/>
+      <c r="N18" s="169"/>
+      <c r="O18" s="168"/>
+      <c r="P18" s="169"/>
+      <c r="Q18" s="169"/>
+      <c r="R18" s="169"/>
+      <c r="S18" s="169"/>
+      <c r="T18" s="168"/>
+      <c r="U18" s="169"/>
+      <c r="V18" s="169"/>
+      <c r="W18" s="169"/>
+      <c r="X18" s="169"/>
+      <c r="Y18" s="168"/>
+      <c r="Z18" s="169"/>
+      <c r="AA18" s="169"/>
+      <c r="AB18" s="169"/>
+      <c r="AC18" s="169"/>
+      <c r="AD18" s="168"/>
+      <c r="AE18" s="169"/>
+      <c r="AF18" s="169"/>
+      <c r="AG18" s="169"/>
+      <c r="AH18" s="169"/>
+      <c r="AI18" s="168"/>
+      <c r="AJ18" s="169"/>
+      <c r="AK18" s="169"/>
+      <c r="AL18" s="170"/>
     </row>
     <row r="19" spans="1:38" ht="16.2">
-      <c r="A19" s="168"/>
-      <c r="B19" s="169"/>
-      <c r="C19" s="169"/>
-      <c r="D19" s="169"/>
-      <c r="E19" s="170"/>
-      <c r="F19" s="163" t="s">
+      <c r="A19" s="165"/>
+      <c r="B19" s="166"/>
+      <c r="C19" s="166"/>
+      <c r="D19" s="166"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="169" t="s">
         <v>118</v>
       </c>
-      <c r="G19" s="163"/>
-      <c r="H19" s="163"/>
-      <c r="I19" s="163"/>
-      <c r="J19" s="162"/>
-      <c r="K19" s="163"/>
-      <c r="L19" s="163"/>
-      <c r="M19" s="163"/>
-      <c r="N19" s="163"/>
-      <c r="O19" s="162"/>
-      <c r="P19" s="163"/>
-      <c r="Q19" s="163"/>
-      <c r="R19" s="163"/>
-      <c r="S19" s="163"/>
-      <c r="T19" s="162"/>
-      <c r="U19" s="163"/>
-      <c r="V19" s="163"/>
-      <c r="W19" s="163"/>
-      <c r="X19" s="163"/>
-      <c r="Y19" s="162"/>
-      <c r="Z19" s="163"/>
-      <c r="AA19" s="163"/>
-      <c r="AB19" s="163"/>
-      <c r="AC19" s="163"/>
-      <c r="AD19" s="162"/>
-      <c r="AE19" s="163"/>
-      <c r="AF19" s="163"/>
-      <c r="AG19" s="163"/>
-      <c r="AH19" s="163"/>
-      <c r="AI19" s="162"/>
-      <c r="AJ19" s="163"/>
-      <c r="AK19" s="163"/>
-      <c r="AL19" s="164"/>
+      <c r="G19" s="169"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="169"/>
+      <c r="J19" s="168"/>
+      <c r="K19" s="169"/>
+      <c r="L19" s="169"/>
+      <c r="M19" s="169"/>
+      <c r="N19" s="169"/>
+      <c r="O19" s="168"/>
+      <c r="P19" s="169"/>
+      <c r="Q19" s="169"/>
+      <c r="R19" s="169"/>
+      <c r="S19" s="169"/>
+      <c r="T19" s="168"/>
+      <c r="U19" s="169"/>
+      <c r="V19" s="169"/>
+      <c r="W19" s="169"/>
+      <c r="X19" s="169"/>
+      <c r="Y19" s="168"/>
+      <c r="Z19" s="169"/>
+      <c r="AA19" s="169"/>
+      <c r="AB19" s="169"/>
+      <c r="AC19" s="169"/>
+      <c r="AD19" s="168"/>
+      <c r="AE19" s="169"/>
+      <c r="AF19" s="169"/>
+      <c r="AG19" s="169"/>
+      <c r="AH19" s="169"/>
+      <c r="AI19" s="168"/>
+      <c r="AJ19" s="169"/>
+      <c r="AK19" s="169"/>
+      <c r="AL19" s="170"/>
     </row>
     <row r="20" spans="1:38">
-      <c r="A20" s="165"/>
-      <c r="B20" s="166"/>
-      <c r="C20" s="166"/>
-      <c r="D20" s="166"/>
-      <c r="E20" s="167"/>
-      <c r="F20" s="163" t="s">
+      <c r="A20" s="162"/>
+      <c r="B20" s="163"/>
+      <c r="C20" s="163"/>
+      <c r="D20" s="163"/>
+      <c r="E20" s="164"/>
+      <c r="F20" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="G20" s="163"/>
-      <c r="H20" s="163"/>
-      <c r="I20" s="163"/>
-      <c r="J20" s="162"/>
-      <c r="K20" s="163"/>
-      <c r="L20" s="163"/>
-      <c r="M20" s="163"/>
-      <c r="N20" s="163"/>
-      <c r="O20" s="162"/>
-      <c r="P20" s="163"/>
-      <c r="Q20" s="163"/>
-      <c r="R20" s="163"/>
-      <c r="S20" s="163"/>
-      <c r="T20" s="162"/>
-      <c r="U20" s="163"/>
-      <c r="V20" s="163"/>
-      <c r="W20" s="163"/>
-      <c r="X20" s="163"/>
-      <c r="Y20" s="162"/>
-      <c r="Z20" s="163"/>
-      <c r="AA20" s="163"/>
-      <c r="AB20" s="163"/>
-      <c r="AC20" s="163"/>
-      <c r="AD20" s="162"/>
-      <c r="AE20" s="163"/>
-      <c r="AF20" s="163"/>
-      <c r="AG20" s="163"/>
-      <c r="AH20" s="163"/>
-      <c r="AI20" s="162"/>
-      <c r="AJ20" s="163"/>
-      <c r="AK20" s="163"/>
-      <c r="AL20" s="164"/>
+      <c r="G20" s="169"/>
+      <c r="H20" s="169"/>
+      <c r="I20" s="169"/>
+      <c r="J20" s="168"/>
+      <c r="K20" s="169"/>
+      <c r="L20" s="169"/>
+      <c r="M20" s="169"/>
+      <c r="N20" s="169"/>
+      <c r="O20" s="168"/>
+      <c r="P20" s="169"/>
+      <c r="Q20" s="169"/>
+      <c r="R20" s="169"/>
+      <c r="S20" s="169"/>
+      <c r="T20" s="168"/>
+      <c r="U20" s="169"/>
+      <c r="V20" s="169"/>
+      <c r="W20" s="169"/>
+      <c r="X20" s="169"/>
+      <c r="Y20" s="168"/>
+      <c r="Z20" s="169"/>
+      <c r="AA20" s="169"/>
+      <c r="AB20" s="169"/>
+      <c r="AC20" s="169"/>
+      <c r="AD20" s="168"/>
+      <c r="AE20" s="169"/>
+      <c r="AF20" s="169"/>
+      <c r="AG20" s="169"/>
+      <c r="AH20" s="169"/>
+      <c r="AI20" s="168"/>
+      <c r="AJ20" s="169"/>
+      <c r="AK20" s="169"/>
+      <c r="AL20" s="170"/>
     </row>
     <row r="21" spans="1:38" ht="16.2">
-      <c r="A21" s="168"/>
-      <c r="B21" s="169"/>
-      <c r="C21" s="169"/>
-      <c r="D21" s="169"/>
-      <c r="E21" s="170"/>
-      <c r="F21" s="163" t="s">
+      <c r="A21" s="165"/>
+      <c r="B21" s="166"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="169" t="s">
         <v>118</v>
       </c>
-      <c r="G21" s="163"/>
-      <c r="H21" s="163"/>
-      <c r="I21" s="163"/>
-      <c r="J21" s="162"/>
-      <c r="K21" s="163"/>
-      <c r="L21" s="163"/>
-      <c r="M21" s="163"/>
-      <c r="N21" s="163"/>
-      <c r="O21" s="162"/>
-      <c r="P21" s="163"/>
-      <c r="Q21" s="163"/>
-      <c r="R21" s="163"/>
-      <c r="S21" s="163"/>
-      <c r="T21" s="162"/>
-      <c r="U21" s="163"/>
-      <c r="V21" s="163"/>
-      <c r="W21" s="163"/>
-      <c r="X21" s="163"/>
-      <c r="Y21" s="162"/>
-      <c r="Z21" s="163"/>
-      <c r="AA21" s="163"/>
-      <c r="AB21" s="163"/>
-      <c r="AC21" s="163"/>
-      <c r="AD21" s="162"/>
-      <c r="AE21" s="163"/>
-      <c r="AF21" s="163"/>
-      <c r="AG21" s="163"/>
-      <c r="AH21" s="163"/>
-      <c r="AI21" s="162"/>
-      <c r="AJ21" s="163"/>
-      <c r="AK21" s="163"/>
-      <c r="AL21" s="164"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="169"/>
+      <c r="J21" s="168"/>
+      <c r="K21" s="169"/>
+      <c r="L21" s="169"/>
+      <c r="M21" s="169"/>
+      <c r="N21" s="169"/>
+      <c r="O21" s="168"/>
+      <c r="P21" s="169"/>
+      <c r="Q21" s="169"/>
+      <c r="R21" s="169"/>
+      <c r="S21" s="169"/>
+      <c r="T21" s="168"/>
+      <c r="U21" s="169"/>
+      <c r="V21" s="169"/>
+      <c r="W21" s="169"/>
+      <c r="X21" s="169"/>
+      <c r="Y21" s="168"/>
+      <c r="Z21" s="169"/>
+      <c r="AA21" s="169"/>
+      <c r="AB21" s="169"/>
+      <c r="AC21" s="169"/>
+      <c r="AD21" s="168"/>
+      <c r="AE21" s="169"/>
+      <c r="AF21" s="169"/>
+      <c r="AG21" s="169"/>
+      <c r="AH21" s="169"/>
+      <c r="AI21" s="168"/>
+      <c r="AJ21" s="169"/>
+      <c r="AK21" s="169"/>
+      <c r="AL21" s="170"/>
     </row>
     <row r="22" spans="1:38">
       <c r="A22" s="72"/>
@@ -14569,6 +14792,72 @@
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="AI12:AL12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="Y13:AC13"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="AI13:AL13"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="AI11:AL11"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AI10:AL10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="J11:N11"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="A12:E13"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="F8:I9"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="AI8:AL9"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:N20"/>
+    <mergeCell ref="O20:S20"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="AI21:AL21"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="Y21:AC21"/>
+    <mergeCell ref="AD21:AH21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A16:E17"/>
+    <mergeCell ref="F16:I17"/>
+    <mergeCell ref="J16:AH16"/>
+    <mergeCell ref="J17:N17"/>
+    <mergeCell ref="O17:S17"/>
+    <mergeCell ref="T17:X17"/>
+    <mergeCell ref="Y17:AC17"/>
+    <mergeCell ref="AD17:AH17"/>
+    <mergeCell ref="AI19:AL19"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="J18:N18"/>
+    <mergeCell ref="O18:S18"/>
+    <mergeCell ref="T18:X18"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="Y18:AC18"/>
     <mergeCell ref="M1:AL1"/>
@@ -14585,72 +14874,6 @@
     <mergeCell ref="T19:X19"/>
     <mergeCell ref="Y19:AC19"/>
     <mergeCell ref="AD19:AH19"/>
-    <mergeCell ref="AI19:AL19"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="J18:N18"/>
-    <mergeCell ref="O18:S18"/>
-    <mergeCell ref="T18:X18"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A16:E17"/>
-    <mergeCell ref="F16:I17"/>
-    <mergeCell ref="J16:AH16"/>
-    <mergeCell ref="J17:N17"/>
-    <mergeCell ref="O17:S17"/>
-    <mergeCell ref="T17:X17"/>
-    <mergeCell ref="Y17:AC17"/>
-    <mergeCell ref="AD17:AH17"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:N20"/>
-    <mergeCell ref="O20:S20"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="AI21:AL21"/>
-    <mergeCell ref="J21:N21"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="Y21:AC21"/>
-    <mergeCell ref="AD21:AH21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:I9"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="AI8:AL9"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="A12:E13"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="AI11:AL11"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="AI10:AL10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="Y13:AC13"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="AI13:AL13"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -14691,32 +14914,32 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
-      <c r="Z1" s="149"/>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
-      <c r="AC1" s="149"/>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="149"/>
-      <c r="AJ1" s="149"/>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="84"/>
+      <c r="AD1" s="84"/>
+      <c r="AE1" s="84"/>
+      <c r="AF1" s="84"/>
+      <c r="AG1" s="84"/>
+      <c r="AH1" s="84"/>
+      <c r="AI1" s="84"/>
+      <c r="AJ1" s="84"/>
+      <c r="AK1" s="84"/>
+      <c r="AL1" s="84"/>
       <c r="AM1" s="67"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -14760,25 +14983,25 @@
       <c r="AM2" s="67"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="146"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="146"/>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
-      <c r="L3" s="146"/>
-      <c r="M3" s="146"/>
-      <c r="N3" s="146"/>
-      <c r="O3" s="146"/>
-      <c r="P3" s="146"/>
-      <c r="Q3" s="146"/>
-      <c r="R3" s="146"/>
-      <c r="S3" s="146"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
       <c r="T3" s="34"/>
       <c r="U3" s="34"/>
       <c r="V3" s="34"/>
@@ -14817,442 +15040,442 @@
       <c r="A7" s="6"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="144" t="s">
+      <c r="A8" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="144"/>
-      <c r="J8" s="144" t="s">
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="K8" s="144"/>
-      <c r="L8" s="144"/>
-      <c r="M8" s="144"/>
-      <c r="N8" s="144"/>
-      <c r="O8" s="144"/>
-      <c r="P8" s="144"/>
-      <c r="Q8" s="144"/>
-      <c r="R8" s="144"/>
-      <c r="S8" s="144"/>
-      <c r="T8" s="144"/>
-      <c r="U8" s="144"/>
-      <c r="V8" s="144"/>
-      <c r="W8" s="144"/>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="144"/>
-      <c r="Z8" s="144"/>
-      <c r="AA8" s="144"/>
-      <c r="AB8" s="144"/>
-      <c r="AC8" s="144"/>
-      <c r="AD8" s="144"/>
-      <c r="AE8" s="144"/>
-      <c r="AF8" s="144"/>
-      <c r="AG8" s="144"/>
-      <c r="AH8" s="144"/>
-      <c r="AI8" s="144" t="s">
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="88"/>
+      <c r="T8" s="88"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="88"/>
+      <c r="Y8" s="88"/>
+      <c r="Z8" s="88"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="88"/>
+      <c r="AC8" s="88"/>
+      <c r="AD8" s="88"/>
+      <c r="AE8" s="88"/>
+      <c r="AF8" s="88"/>
+      <c r="AG8" s="88"/>
+      <c r="AH8" s="88"/>
+      <c r="AI8" s="88" t="s">
         <v>201</v>
       </c>
-      <c r="AJ8" s="144"/>
-      <c r="AK8" s="144"/>
-      <c r="AL8" s="144"/>
-      <c r="AM8" s="144"/>
+      <c r="AJ8" s="88"/>
+      <c r="AK8" s="88"/>
+      <c r="AL8" s="88"/>
+      <c r="AM8" s="88"/>
     </row>
     <row r="9" spans="1:39">
-      <c r="A9" s="144"/>
-      <c r="B9" s="144"/>
-      <c r="C9" s="144"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="144"/>
-      <c r="I9" s="144"/>
-      <c r="J9" s="144" t="s">
+      <c r="A9" s="88"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="88" t="s">
         <v>203</v>
       </c>
-      <c r="K9" s="144"/>
-      <c r="L9" s="144"/>
-      <c r="M9" s="144" t="s">
+      <c r="K9" s="88"/>
+      <c r="L9" s="88"/>
+      <c r="M9" s="88" t="s">
         <v>204</v>
       </c>
-      <c r="N9" s="144"/>
-      <c r="O9" s="144"/>
-      <c r="P9" s="144" t="s">
+      <c r="N9" s="88"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="Q9" s="144"/>
-      <c r="R9" s="144"/>
-      <c r="S9" s="144" t="s">
+      <c r="Q9" s="88"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="88" t="s">
         <v>206</v>
       </c>
-      <c r="T9" s="144"/>
-      <c r="U9" s="144"/>
-      <c r="V9" s="144" t="s">
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88" t="s">
         <v>207</v>
       </c>
-      <c r="W9" s="144"/>
-      <c r="X9" s="144"/>
-      <c r="Y9" s="144" t="s">
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88" t="s">
         <v>202</v>
       </c>
-      <c r="Z9" s="144"/>
-      <c r="AA9" s="144"/>
-      <c r="AB9" s="144"/>
-      <c r="AC9" s="144" t="s">
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88" t="s">
         <v>200</v>
       </c>
-      <c r="AD9" s="144"/>
-      <c r="AE9" s="144"/>
-      <c r="AF9" s="144"/>
-      <c r="AG9" s="144"/>
-      <c r="AH9" s="144"/>
-      <c r="AI9" s="144"/>
-      <c r="AJ9" s="144"/>
-      <c r="AK9" s="144"/>
-      <c r="AL9" s="144"/>
-      <c r="AM9" s="144"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="88"/>
+      <c r="AF9" s="88"/>
+      <c r="AG9" s="88"/>
+      <c r="AH9" s="88"/>
+      <c r="AI9" s="88"/>
+      <c r="AJ9" s="88"/>
+      <c r="AK9" s="88"/>
+      <c r="AL9" s="88"/>
+      <c r="AM9" s="88"/>
     </row>
     <row r="10" spans="1:39">
       <c r="A10" s="178"/>
       <c r="B10" s="178"/>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="144"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="144"/>
-      <c r="L10" s="144"/>
-      <c r="M10" s="144"/>
-      <c r="N10" s="144"/>
-      <c r="O10" s="144"/>
-      <c r="P10" s="144"/>
-      <c r="Q10" s="144"/>
-      <c r="R10" s="144"/>
-      <c r="S10" s="144"/>
-      <c r="T10" s="144"/>
-      <c r="U10" s="144"/>
-      <c r="V10" s="144"/>
-      <c r="W10" s="144"/>
-      <c r="X10" s="144"/>
-      <c r="Y10" s="144"/>
-      <c r="Z10" s="144"/>
-      <c r="AA10" s="144"/>
-      <c r="AB10" s="144"/>
-      <c r="AC10" s="144"/>
-      <c r="AD10" s="144"/>
-      <c r="AE10" s="144"/>
-      <c r="AF10" s="144"/>
-      <c r="AG10" s="144"/>
-      <c r="AH10" s="144"/>
-      <c r="AI10" s="144"/>
-      <c r="AJ10" s="144"/>
-      <c r="AK10" s="144"/>
-      <c r="AL10" s="144"/>
-      <c r="AM10" s="144"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="88"/>
+      <c r="L10" s="88"/>
+      <c r="M10" s="88"/>
+      <c r="N10" s="88"/>
+      <c r="O10" s="88"/>
+      <c r="P10" s="88"/>
+      <c r="Q10" s="88"/>
+      <c r="R10" s="88"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="88"/>
+      <c r="W10" s="88"/>
+      <c r="X10" s="88"/>
+      <c r="Y10" s="88"/>
+      <c r="Z10" s="88"/>
+      <c r="AA10" s="88"/>
+      <c r="AB10" s="88"/>
+      <c r="AC10" s="88"/>
+      <c r="AD10" s="88"/>
+      <c r="AE10" s="88"/>
+      <c r="AF10" s="88"/>
+      <c r="AG10" s="88"/>
+      <c r="AH10" s="88"/>
+      <c r="AI10" s="88"/>
+      <c r="AJ10" s="88"/>
+      <c r="AK10" s="88"/>
+      <c r="AL10" s="88"/>
+      <c r="AM10" s="88"/>
     </row>
     <row r="11" spans="1:39">
       <c r="A11" s="178"/>
       <c r="B11" s="178"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="144"/>
-      <c r="N11" s="144"/>
-      <c r="O11" s="144"/>
-      <c r="P11" s="144"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="144"/>
-      <c r="S11" s="144"/>
-      <c r="T11" s="144"/>
-      <c r="U11" s="144"/>
-      <c r="V11" s="144"/>
-      <c r="W11" s="144"/>
-      <c r="X11" s="144"/>
-      <c r="Y11" s="144"/>
-      <c r="Z11" s="144"/>
-      <c r="AA11" s="144"/>
-      <c r="AB11" s="144"/>
-      <c r="AC11" s="144"/>
-      <c r="AD11" s="144"/>
-      <c r="AE11" s="144"/>
-      <c r="AF11" s="144"/>
-      <c r="AG11" s="144"/>
-      <c r="AH11" s="144"/>
-      <c r="AI11" s="144"/>
-      <c r="AJ11" s="144"/>
-      <c r="AK11" s="144"/>
-      <c r="AL11" s="144"/>
-      <c r="AM11" s="144"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="88"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="88"/>
+      <c r="AF11" s="88"/>
+      <c r="AG11" s="88"/>
+      <c r="AH11" s="88"/>
+      <c r="AI11" s="88"/>
+      <c r="AJ11" s="88"/>
+      <c r="AK11" s="88"/>
+      <c r="AL11" s="88"/>
+      <c r="AM11" s="88"/>
     </row>
     <row r="12" spans="1:39">
       <c r="A12" s="178"/>
       <c r="B12" s="178"/>
-      <c r="C12" s="144" t="s">
+      <c r="C12" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="144"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="144"/>
-      <c r="L12" s="144"/>
-      <c r="M12" s="144"/>
-      <c r="N12" s="144"/>
-      <c r="O12" s="144"/>
-      <c r="P12" s="144"/>
-      <c r="Q12" s="144"/>
-      <c r="R12" s="144"/>
-      <c r="S12" s="144"/>
-      <c r="T12" s="144"/>
-      <c r="U12" s="144"/>
-      <c r="V12" s="144"/>
-      <c r="W12" s="144"/>
-      <c r="X12" s="144"/>
-      <c r="Y12" s="144"/>
-      <c r="Z12" s="144"/>
-      <c r="AA12" s="144"/>
-      <c r="AB12" s="144"/>
-      <c r="AC12" s="144"/>
-      <c r="AD12" s="144"/>
-      <c r="AE12" s="144"/>
-      <c r="AF12" s="144"/>
-      <c r="AG12" s="144"/>
-      <c r="AH12" s="144"/>
-      <c r="AI12" s="144"/>
-      <c r="AJ12" s="144"/>
-      <c r="AK12" s="144"/>
-      <c r="AL12" s="144"/>
-      <c r="AM12" s="144"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="88"/>
+      <c r="L12" s="88"/>
+      <c r="M12" s="88"/>
+      <c r="N12" s="88"/>
+      <c r="O12" s="88"/>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="88"/>
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="88"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12" s="88"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="88"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="88"/>
+      <c r="AF12" s="88"/>
+      <c r="AG12" s="88"/>
+      <c r="AH12" s="88"/>
+      <c r="AI12" s="88"/>
+      <c r="AJ12" s="88"/>
+      <c r="AK12" s="88"/>
+      <c r="AL12" s="88"/>
+      <c r="AM12" s="88"/>
     </row>
     <row r="13" spans="1:39">
       <c r="A13" s="178"/>
       <c r="B13" s="178"/>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
-      <c r="O13" s="144"/>
-      <c r="P13" s="144"/>
-      <c r="Q13" s="144"/>
-      <c r="R13" s="144"/>
-      <c r="S13" s="144"/>
-      <c r="T13" s="144"/>
-      <c r="U13" s="144"/>
-      <c r="V13" s="144"/>
-      <c r="W13" s="144"/>
-      <c r="X13" s="144"/>
-      <c r="Y13" s="144"/>
-      <c r="Z13" s="144"/>
-      <c r="AA13" s="144"/>
-      <c r="AB13" s="144"/>
-      <c r="AC13" s="144"/>
-      <c r="AD13" s="144"/>
-      <c r="AE13" s="144"/>
-      <c r="AF13" s="144"/>
-      <c r="AG13" s="144"/>
-      <c r="AH13" s="144"/>
-      <c r="AI13" s="144"/>
-      <c r="AJ13" s="144"/>
-      <c r="AK13" s="144"/>
-      <c r="AL13" s="144"/>
-      <c r="AM13" s="144"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88"/>
+      <c r="K13" s="88"/>
+      <c r="L13" s="88"/>
+      <c r="M13" s="88"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="88"/>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="88"/>
+      <c r="Z13" s="88"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="88"/>
+      <c r="AD13" s="88"/>
+      <c r="AE13" s="88"/>
+      <c r="AF13" s="88"/>
+      <c r="AG13" s="88"/>
+      <c r="AH13" s="88"/>
+      <c r="AI13" s="88"/>
+      <c r="AJ13" s="88"/>
+      <c r="AK13" s="88"/>
+      <c r="AL13" s="88"/>
+      <c r="AM13" s="88"/>
     </row>
     <row r="14" spans="1:39">
       <c r="A14" s="178"/>
       <c r="B14" s="178"/>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144"/>
-      <c r="Q14" s="144"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="144"/>
-      <c r="T14" s="144"/>
-      <c r="U14" s="144"/>
-      <c r="V14" s="144"/>
-      <c r="W14" s="144"/>
-      <c r="X14" s="144"/>
-      <c r="Y14" s="144"/>
-      <c r="Z14" s="144"/>
-      <c r="AA14" s="144"/>
-      <c r="AB14" s="144"/>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="144"/>
-      <c r="AG14" s="144"/>
-      <c r="AH14" s="144"/>
-      <c r="AI14" s="144"/>
-      <c r="AJ14" s="144"/>
-      <c r="AK14" s="144"/>
-      <c r="AL14" s="144"/>
-      <c r="AM14" s="144"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="88"/>
+      <c r="M14" s="88"/>
+      <c r="N14" s="88"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="88"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="88"/>
+      <c r="U14" s="88"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="88"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="88"/>
+      <c r="AC14" s="88"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="88"/>
+      <c r="AF14" s="88"/>
+      <c r="AG14" s="88"/>
+      <c r="AH14" s="88"/>
+      <c r="AI14" s="88"/>
+      <c r="AJ14" s="88"/>
+      <c r="AK14" s="88"/>
+      <c r="AL14" s="88"/>
+      <c r="AM14" s="88"/>
     </row>
     <row r="15" spans="1:39">
       <c r="A15" s="178"/>
       <c r="B15" s="178"/>
-      <c r="C15" s="144"/>
-      <c r="D15" s="144"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="144"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="144"/>
-      <c r="L15" s="144"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="144"/>
-      <c r="Q15" s="144"/>
-      <c r="R15" s="144"/>
-      <c r="S15" s="144"/>
-      <c r="T15" s="144"/>
-      <c r="U15" s="144"/>
-      <c r="V15" s="144"/>
-      <c r="W15" s="144"/>
-      <c r="X15" s="144"/>
-      <c r="Y15" s="144"/>
-      <c r="Z15" s="144"/>
-      <c r="AA15" s="144"/>
-      <c r="AB15" s="144"/>
-      <c r="AC15" s="144"/>
-      <c r="AD15" s="144"/>
-      <c r="AE15" s="144"/>
-      <c r="AF15" s="144"/>
-      <c r="AG15" s="144"/>
-      <c r="AH15" s="144"/>
-      <c r="AI15" s="144"/>
-      <c r="AJ15" s="144"/>
-      <c r="AK15" s="144"/>
-      <c r="AL15" s="144"/>
-      <c r="AM15" s="144"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="88"/>
+      <c r="AC15" s="88"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="88"/>
+      <c r="AF15" s="88"/>
+      <c r="AG15" s="88"/>
+      <c r="AH15" s="88"/>
+      <c r="AI15" s="88"/>
+      <c r="AJ15" s="88"/>
+      <c r="AK15" s="88"/>
+      <c r="AL15" s="88"/>
+      <c r="AM15" s="88"/>
     </row>
     <row r="16" spans="1:39">
       <c r="A16" s="178"/>
       <c r="B16" s="178"/>
-      <c r="C16" s="144" t="s">
+      <c r="C16" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="144"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="144"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="144"/>
-      <c r="P16" s="144"/>
-      <c r="Q16" s="144"/>
-      <c r="R16" s="144"/>
-      <c r="S16" s="144"/>
-      <c r="T16" s="144"/>
-      <c r="U16" s="144"/>
-      <c r="V16" s="144"/>
-      <c r="W16" s="144"/>
-      <c r="X16" s="144"/>
-      <c r="Y16" s="144"/>
-      <c r="Z16" s="144"/>
-      <c r="AA16" s="144"/>
-      <c r="AB16" s="144"/>
-      <c r="AC16" s="144"/>
-      <c r="AD16" s="144"/>
-      <c r="AE16" s="144"/>
-      <c r="AF16" s="144"/>
-      <c r="AG16" s="144"/>
-      <c r="AH16" s="144"/>
-      <c r="AI16" s="144"/>
-      <c r="AJ16" s="144"/>
-      <c r="AK16" s="144"/>
-      <c r="AL16" s="144"/>
-      <c r="AM16" s="144"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="88"/>
+      <c r="K16" s="88"/>
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="88"/>
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="88"/>
+      <c r="Y16" s="88"/>
+      <c r="Z16" s="88"/>
+      <c r="AA16" s="88"/>
+      <c r="AB16" s="88"/>
+      <c r="AC16" s="88"/>
+      <c r="AD16" s="88"/>
+      <c r="AE16" s="88"/>
+      <c r="AF16" s="88"/>
+      <c r="AG16" s="88"/>
+      <c r="AH16" s="88"/>
+      <c r="AI16" s="88"/>
+      <c r="AJ16" s="88"/>
+      <c r="AK16" s="88"/>
+      <c r="AL16" s="88"/>
+      <c r="AM16" s="88"/>
     </row>
     <row r="17" spans="1:39">
       <c r="A17" s="178"/>
       <c r="B17" s="178"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="144"/>
-      <c r="J17" s="144"/>
-      <c r="K17" s="144"/>
-      <c r="L17" s="144"/>
-      <c r="M17" s="144"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="144"/>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="144"/>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="144"/>
-      <c r="U17" s="144"/>
-      <c r="V17" s="144"/>
-      <c r="W17" s="144"/>
-      <c r="X17" s="144"/>
-      <c r="Y17" s="144"/>
-      <c r="Z17" s="144"/>
-      <c r="AA17" s="144"/>
-      <c r="AB17" s="144"/>
-      <c r="AC17" s="144"/>
-      <c r="AD17" s="144"/>
-      <c r="AE17" s="144"/>
-      <c r="AF17" s="144"/>
-      <c r="AG17" s="144"/>
-      <c r="AH17" s="144"/>
-      <c r="AI17" s="144"/>
-      <c r="AJ17" s="144"/>
-      <c r="AK17" s="144"/>
-      <c r="AL17" s="144"/>
-      <c r="AM17" s="144"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="88"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="88"/>
+      <c r="K17" s="88"/>
+      <c r="L17" s="88"/>
+      <c r="M17" s="88"/>
+      <c r="N17" s="88"/>
+      <c r="O17" s="88"/>
+      <c r="P17" s="88"/>
+      <c r="Q17" s="88"/>
+      <c r="R17" s="88"/>
+      <c r="S17" s="88"/>
+      <c r="T17" s="88"/>
+      <c r="U17" s="88"/>
+      <c r="V17" s="88"/>
+      <c r="W17" s="88"/>
+      <c r="X17" s="88"/>
+      <c r="Y17" s="88"/>
+      <c r="Z17" s="88"/>
+      <c r="AA17" s="88"/>
+      <c r="AB17" s="88"/>
+      <c r="AC17" s="88"/>
+      <c r="AD17" s="88"/>
+      <c r="AE17" s="88"/>
+      <c r="AF17" s="88"/>
+      <c r="AG17" s="88"/>
+      <c r="AH17" s="88"/>
+      <c r="AI17" s="88"/>
+      <c r="AJ17" s="88"/>
+      <c r="AK17" s="88"/>
+      <c r="AL17" s="88"/>
+      <c r="AM17" s="88"/>
     </row>
     <row r="19" spans="1:39">
       <c r="A19" s="68" t="s">
@@ -15261,40 +15484,6 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="Y16:AB17"/>
-    <mergeCell ref="AC16:AH17"/>
-    <mergeCell ref="AI16:AM17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="J16:L17"/>
-    <mergeCell ref="M16:O17"/>
-    <mergeCell ref="P16:R17"/>
-    <mergeCell ref="S16:U17"/>
-    <mergeCell ref="V16:X17"/>
-    <mergeCell ref="AI14:AM15"/>
-    <mergeCell ref="J10:L11"/>
-    <mergeCell ref="P10:R11"/>
-    <mergeCell ref="M10:O11"/>
-    <mergeCell ref="S10:U11"/>
-    <mergeCell ref="V10:X11"/>
-    <mergeCell ref="Y10:AB11"/>
-    <mergeCell ref="AC10:AH11"/>
-    <mergeCell ref="AI12:AM13"/>
-    <mergeCell ref="AI10:AM11"/>
-    <mergeCell ref="P14:R15"/>
-    <mergeCell ref="S14:U15"/>
-    <mergeCell ref="V14:X15"/>
-    <mergeCell ref="Y14:AB15"/>
-    <mergeCell ref="AC14:AH15"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="AC9:AH9"/>
-    <mergeCell ref="P12:R13"/>
-    <mergeCell ref="S12:U13"/>
-    <mergeCell ref="V12:X13"/>
-    <mergeCell ref="Y12:AB13"/>
-    <mergeCell ref="AC12:AH13"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="S9:U9"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="AI8:AM9"/>
     <mergeCell ref="M1:AL1"/>
@@ -15311,6 +15500,40 @@
     <mergeCell ref="C10:I11"/>
     <mergeCell ref="C12:I13"/>
     <mergeCell ref="A8:I9"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="Y9:AB9"/>
+    <mergeCell ref="AC9:AH9"/>
+    <mergeCell ref="P12:R13"/>
+    <mergeCell ref="S12:U13"/>
+    <mergeCell ref="V12:X13"/>
+    <mergeCell ref="Y12:AB13"/>
+    <mergeCell ref="AC12:AH13"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="AI14:AM15"/>
+    <mergeCell ref="J10:L11"/>
+    <mergeCell ref="P10:R11"/>
+    <mergeCell ref="M10:O11"/>
+    <mergeCell ref="S10:U11"/>
+    <mergeCell ref="V10:X11"/>
+    <mergeCell ref="Y10:AB11"/>
+    <mergeCell ref="AC10:AH11"/>
+    <mergeCell ref="AI12:AM13"/>
+    <mergeCell ref="AI10:AM11"/>
+    <mergeCell ref="P14:R15"/>
+    <mergeCell ref="S14:U15"/>
+    <mergeCell ref="V14:X15"/>
+    <mergeCell ref="Y14:AB15"/>
+    <mergeCell ref="AC14:AH15"/>
+    <mergeCell ref="Y16:AB17"/>
+    <mergeCell ref="AC16:AH17"/>
+    <mergeCell ref="AI16:AM17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="J16:L17"/>
+    <mergeCell ref="M16:O17"/>
+    <mergeCell ref="P16:R17"/>
+    <mergeCell ref="S16:U17"/>
+    <mergeCell ref="V16:X17"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -15327,6 +15550,647 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43CBB79E-0A7F-491A-AA58-F8602FC3AA4C}">
+  <dimension ref="A1:AM55"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.33203125" style="180" customWidth="1"/>
+    <col min="8" max="8" width="2" style="180" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" style="180" customWidth="1"/>
+    <col min="32" max="38" width="2.33203125" style="180" customWidth="1"/>
+    <col min="39" max="16384" width="8.88671875" style="180"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="15" customHeight="1">
+      <c r="A1" s="179" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="181"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
+      <c r="Q1" s="182"/>
+      <c r="R1" s="182"/>
+      <c r="S1" s="182"/>
+      <c r="T1" s="182"/>
+      <c r="U1" s="182"/>
+      <c r="V1" s="182"/>
+      <c r="W1" s="182"/>
+      <c r="X1" s="182"/>
+      <c r="Y1" s="182"/>
+      <c r="Z1" s="182"/>
+      <c r="AA1" s="182"/>
+      <c r="AB1" s="182"/>
+      <c r="AC1" s="182"/>
+      <c r="AD1" s="182"/>
+      <c r="AE1" s="182"/>
+      <c r="AF1" s="182"/>
+      <c r="AG1" s="182"/>
+      <c r="AH1" s="182"/>
+      <c r="AI1" s="182"/>
+      <c r="AJ1" s="182"/>
+      <c r="AK1" s="182"/>
+      <c r="AL1" s="182"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1">
+      <c r="A2" s="183" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+    </row>
+    <row r="3" spans="1:38" ht="15" customHeight="1">
+      <c r="A3" s="185"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="185"/>
+      <c r="P3" s="185"/>
+      <c r="Q3" s="185"/>
+      <c r="R3" s="185"/>
+      <c r="S3" s="185"/>
+      <c r="T3" s="185"/>
+    </row>
+    <row r="4" spans="1:38" ht="15" customHeight="1">
+      <c r="A4" s="186"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
+      <c r="M4" s="186"/>
+      <c r="N4" s="186"/>
+      <c r="O4" s="186"/>
+      <c r="P4" s="186"/>
+      <c r="Q4" s="186"/>
+      <c r="R4" s="186"/>
+      <c r="S4" s="186"/>
+      <c r="T4" s="186"/>
+    </row>
+    <row r="5" spans="1:38" ht="15" customHeight="1">
+      <c r="A5" s="187" t="s">
+        <v>218</v>
+      </c>
+      <c r="R5" s="187"/>
+    </row>
+    <row r="6" spans="1:38" ht="15" customHeight="1">
+      <c r="A6" s="188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="189"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="190"/>
+      <c r="G6" s="191" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="192"/>
+      <c r="I6" s="192"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="192"/>
+      <c r="L6" s="192"/>
+      <c r="M6" s="192"/>
+      <c r="N6" s="192"/>
+      <c r="O6" s="192"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="192"/>
+      <c r="T6" s="192"/>
+      <c r="U6" s="192"/>
+      <c r="V6" s="192"/>
+      <c r="W6" s="192"/>
+      <c r="X6" s="192"/>
+      <c r="Y6" s="192"/>
+      <c r="Z6" s="192"/>
+      <c r="AA6" s="192"/>
+      <c r="AB6" s="192"/>
+      <c r="AC6" s="192"/>
+      <c r="AD6" s="192"/>
+      <c r="AE6" s="192"/>
+      <c r="AF6" s="192"/>
+      <c r="AG6" s="192"/>
+      <c r="AH6" s="192"/>
+      <c r="AI6" s="192"/>
+      <c r="AJ6" s="192"/>
+      <c r="AK6" s="192"/>
+      <c r="AL6" s="193"/>
+    </row>
+    <row r="7" spans="1:38" ht="15" customHeight="1">
+      <c r="A7" s="194"/>
+      <c r="B7" s="195"/>
+      <c r="C7" s="195"/>
+      <c r="D7" s="195"/>
+      <c r="E7" s="195"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="197" t="s">
+        <v>203</v>
+      </c>
+      <c r="H7" s="197"/>
+      <c r="I7" s="197"/>
+      <c r="J7" s="197"/>
+      <c r="K7" s="197"/>
+      <c r="L7" s="197"/>
+      <c r="M7" s="197"/>
+      <c r="N7" s="197"/>
+      <c r="O7" s="197"/>
+      <c r="P7" s="197"/>
+      <c r="Q7" s="197"/>
+      <c r="R7" s="197" t="s">
+        <v>204</v>
+      </c>
+      <c r="S7" s="197"/>
+      <c r="T7" s="197"/>
+      <c r="U7" s="197"/>
+      <c r="V7" s="197"/>
+      <c r="W7" s="197"/>
+      <c r="X7" s="197"/>
+      <c r="Y7" s="197"/>
+      <c r="Z7" s="197"/>
+      <c r="AA7" s="197"/>
+      <c r="AB7" s="197"/>
+      <c r="AC7" s="197" t="s">
+        <v>205</v>
+      </c>
+      <c r="AD7" s="197"/>
+      <c r="AE7" s="197"/>
+      <c r="AF7" s="197"/>
+      <c r="AG7" s="197"/>
+      <c r="AH7" s="197"/>
+      <c r="AI7" s="197"/>
+      <c r="AJ7" s="197"/>
+      <c r="AK7" s="197"/>
+      <c r="AL7" s="197"/>
+    </row>
+    <row r="8" spans="1:38" ht="15" customHeight="1">
+      <c r="A8" s="198"/>
+      <c r="B8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="197"/>
+      <c r="H8" s="197"/>
+      <c r="I8" s="197"/>
+      <c r="J8" s="197"/>
+      <c r="K8" s="197"/>
+      <c r="L8" s="197"/>
+      <c r="M8" s="197"/>
+      <c r="N8" s="197"/>
+      <c r="O8" s="197"/>
+      <c r="P8" s="197"/>
+      <c r="Q8" s="197"/>
+      <c r="R8" s="197"/>
+      <c r="S8" s="197"/>
+      <c r="T8" s="197"/>
+      <c r="U8" s="197"/>
+      <c r="V8" s="197"/>
+      <c r="W8" s="197"/>
+      <c r="X8" s="197"/>
+      <c r="Y8" s="197"/>
+      <c r="Z8" s="197"/>
+      <c r="AA8" s="197"/>
+      <c r="AB8" s="197"/>
+      <c r="AC8" s="197"/>
+      <c r="AD8" s="197"/>
+      <c r="AE8" s="197"/>
+      <c r="AF8" s="197"/>
+      <c r="AG8" s="197"/>
+      <c r="AH8" s="197"/>
+      <c r="AI8" s="197"/>
+      <c r="AJ8" s="197"/>
+      <c r="AK8" s="197"/>
+      <c r="AL8" s="197"/>
+    </row>
+    <row r="9" spans="1:38" ht="15" customHeight="1">
+      <c r="A9" s="198"/>
+      <c r="B9" s="198"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="198"/>
+      <c r="E9" s="198"/>
+      <c r="F9" s="198"/>
+      <c r="G9" s="197"/>
+      <c r="H9" s="197"/>
+      <c r="I9" s="197"/>
+      <c r="J9" s="197"/>
+      <c r="K9" s="197"/>
+      <c r="L9" s="197"/>
+      <c r="M9" s="197"/>
+      <c r="N9" s="197"/>
+      <c r="O9" s="197"/>
+      <c r="P9" s="197"/>
+      <c r="Q9" s="197"/>
+      <c r="R9" s="197"/>
+      <c r="S9" s="197"/>
+      <c r="T9" s="197"/>
+      <c r="U9" s="197"/>
+      <c r="V9" s="197"/>
+      <c r="W9" s="197"/>
+      <c r="X9" s="197"/>
+      <c r="Y9" s="197"/>
+      <c r="Z9" s="197"/>
+      <c r="AA9" s="197"/>
+      <c r="AB9" s="197"/>
+      <c r="AC9" s="197"/>
+      <c r="AD9" s="197"/>
+      <c r="AE9" s="197"/>
+      <c r="AF9" s="197"/>
+      <c r="AG9" s="197"/>
+      <c r="AH9" s="197"/>
+      <c r="AI9" s="197"/>
+      <c r="AJ9" s="197"/>
+      <c r="AK9" s="197"/>
+      <c r="AL9" s="197"/>
+    </row>
+    <row r="10" spans="1:38" ht="15" customHeight="1">
+      <c r="A10" s="198"/>
+      <c r="B10" s="198"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="198"/>
+      <c r="E10" s="198"/>
+      <c r="F10" s="198"/>
+      <c r="G10" s="197"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="197"/>
+      <c r="L10" s="197"/>
+      <c r="M10" s="197"/>
+      <c r="N10" s="197"/>
+      <c r="O10" s="197"/>
+      <c r="P10" s="197"/>
+      <c r="Q10" s="197"/>
+      <c r="R10" s="197"/>
+      <c r="S10" s="197"/>
+      <c r="T10" s="197"/>
+      <c r="U10" s="197"/>
+      <c r="V10" s="197"/>
+      <c r="W10" s="197"/>
+      <c r="X10" s="197"/>
+      <c r="Y10" s="197"/>
+      <c r="Z10" s="197"/>
+      <c r="AA10" s="197"/>
+      <c r="AB10" s="197"/>
+      <c r="AC10" s="197"/>
+      <c r="AD10" s="197"/>
+      <c r="AE10" s="197"/>
+      <c r="AF10" s="197"/>
+      <c r="AG10" s="197"/>
+      <c r="AH10" s="197"/>
+      <c r="AI10" s="197"/>
+      <c r="AJ10" s="197"/>
+      <c r="AK10" s="197"/>
+      <c r="AL10" s="197"/>
+    </row>
+    <row r="11" spans="1:38" ht="15" customHeight="1">
+      <c r="A11" s="199"/>
+      <c r="B11" s="199"/>
+      <c r="C11" s="199"/>
+      <c r="D11" s="199"/>
+      <c r="E11" s="199"/>
+      <c r="F11" s="199"/>
+      <c r="G11" s="199"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="199"/>
+      <c r="K11" s="199"/>
+      <c r="L11" s="199"/>
+      <c r="M11" s="199"/>
+      <c r="N11" s="199"/>
+      <c r="O11" s="199"/>
+      <c r="P11" s="199"/>
+      <c r="Q11" s="199"/>
+      <c r="R11" s="199"/>
+      <c r="S11" s="199"/>
+      <c r="T11" s="199"/>
+      <c r="U11" s="199"/>
+      <c r="V11" s="199"/>
+      <c r="W11" s="199"/>
+      <c r="X11" s="199"/>
+      <c r="Y11" s="199"/>
+      <c r="Z11" s="199"/>
+      <c r="AA11" s="199"/>
+      <c r="AB11" s="199"/>
+      <c r="AC11" s="199"/>
+      <c r="AD11" s="199"/>
+      <c r="AE11" s="199"/>
+      <c r="AF11" s="199"/>
+      <c r="AG11" s="199"/>
+      <c r="AH11" s="199"/>
+      <c r="AI11" s="199"/>
+      <c r="AJ11" s="199"/>
+      <c r="AK11" s="199"/>
+      <c r="AL11" s="199"/>
+    </row>
+    <row r="12" spans="1:38" s="201" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A12" s="200" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" s="201" customFormat="1">
+      <c r="A13" s="201" t="s">
+        <v>221</v>
+      </c>
+      <c r="G13" s="202"/>
+      <c r="H13" s="202"/>
+      <c r="I13" s="203" t="s">
+        <v>222</v>
+      </c>
+      <c r="AJ13" s="204"/>
+      <c r="AK13" s="204"/>
+      <c r="AL13" s="204"/>
+    </row>
+    <row r="14" spans="1:38" s="201" customFormat="1">
+      <c r="A14" s="201" t="s">
+        <v>223</v>
+      </c>
+      <c r="P14" s="204"/>
+      <c r="Q14" s="204"/>
+      <c r="R14" s="204"/>
+      <c r="S14" s="204"/>
+      <c r="T14" s="204"/>
+      <c r="U14" s="204"/>
+      <c r="V14" s="204"/>
+      <c r="W14" s="204"/>
+      <c r="X14" s="204"/>
+      <c r="Y14" s="204"/>
+      <c r="Z14" s="204"/>
+      <c r="AA14" s="205" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" s="201" customFormat="1">
+      <c r="A15" s="203" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="203"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="203"/>
+      <c r="H15" s="203"/>
+      <c r="I15" s="203"/>
+      <c r="J15" s="203"/>
+      <c r="K15" s="203"/>
+      <c r="L15" s="203"/>
+      <c r="M15" s="203"/>
+      <c r="N15" s="203"/>
+      <c r="O15" s="203"/>
+      <c r="P15" s="203"/>
+      <c r="Q15" s="203"/>
+      <c r="S15" s="206"/>
+      <c r="T15" s="206"/>
+      <c r="U15" s="206"/>
+      <c r="V15" s="206"/>
+      <c r="W15" s="206"/>
+      <c r="X15" s="206"/>
+      <c r="Y15" s="206"/>
+      <c r="Z15" s="206"/>
+      <c r="AA15" s="201" t="s">
+        <v>226</v>
+      </c>
+      <c r="AB15" s="202"/>
+      <c r="AC15" s="202"/>
+      <c r="AD15" s="202"/>
+      <c r="AE15" s="202"/>
+      <c r="AF15" s="202"/>
+      <c r="AG15" s="202"/>
+      <c r="AH15" s="201" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" s="201" customFormat="1">
+      <c r="A16" s="203"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="203"/>
+      <c r="H16" s="203"/>
+      <c r="I16" s="203"/>
+      <c r="J16" s="203"/>
+      <c r="K16" s="203"/>
+      <c r="L16" s="203"/>
+      <c r="M16" s="203"/>
+      <c r="N16" s="203"/>
+      <c r="O16" s="203"/>
+      <c r="P16" s="203"/>
+      <c r="Q16" s="203"/>
+      <c r="S16" s="207"/>
+      <c r="T16" s="207"/>
+      <c r="U16" s="207"/>
+      <c r="V16" s="207"/>
+      <c r="W16" s="207"/>
+      <c r="X16" s="207"/>
+      <c r="Y16" s="207"/>
+      <c r="Z16" s="207"/>
+    </row>
+    <row r="17" spans="1:39" ht="15" customHeight="1">
+      <c r="A17" s="180" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" ht="15" customHeight="1">
+      <c r="A18" s="208" t="s">
+        <v>229</v>
+      </c>
+      <c r="U18" s="208" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" ht="15" customHeight="1">
+      <c r="B19" s="208" t="s">
+        <v>231</v>
+      </c>
+      <c r="W19" s="208" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" ht="15" customHeight="1">
+      <c r="B20" s="208" t="s">
+        <v>233</v>
+      </c>
+      <c r="W20" s="208" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" ht="15" customHeight="1">
+      <c r="B21" s="208" t="s">
+        <v>235</v>
+      </c>
+      <c r="X21" s="208" t="s">
+        <v>236</v>
+      </c>
+      <c r="AM21" s="209"/>
+    </row>
+    <row r="22" spans="1:39" ht="15" customHeight="1">
+      <c r="B22" s="208" t="s">
+        <v>237</v>
+      </c>
+      <c r="W22" s="208" t="s">
+        <v>238</v>
+      </c>
+      <c r="AM22" s="209"/>
+    </row>
+    <row r="23" spans="1:39" ht="15" customHeight="1">
+      <c r="B23" s="208" t="s">
+        <v>239</v>
+      </c>
+      <c r="W23" s="208" t="s">
+        <v>240</v>
+      </c>
+      <c r="AM23" s="209"/>
+    </row>
+    <row r="24" spans="1:39" ht="15" customHeight="1">
+      <c r="C24" s="208" t="s">
+        <v>241</v>
+      </c>
+      <c r="X24" s="208" t="s">
+        <v>242</v>
+      </c>
+      <c r="AM24" s="209"/>
+    </row>
+    <row r="25" spans="1:39" ht="15" customHeight="1">
+      <c r="B25" s="208" t="s">
+        <v>243</v>
+      </c>
+      <c r="W25" s="208" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" ht="15" customHeight="1">
+      <c r="X26" s="208" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" ht="15" customHeight="1">
+      <c r="A27" s="210"/>
+      <c r="W27" s="208" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" ht="15" customHeight="1">
+      <c r="X28" s="208" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" ht="15" customHeight="1">
+      <c r="A29" s="210" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" ht="15" customHeight="1"/>
+    <row r="31" spans="1:39" ht="13.95" customHeight="1">
+      <c r="U31" s="208"/>
+    </row>
+    <row r="32" spans="1:39" ht="13.95" customHeight="1">
+      <c r="W32" s="208"/>
+    </row>
+    <row r="33" spans="23:24" ht="13.95" customHeight="1">
+      <c r="W33" s="208"/>
+    </row>
+    <row r="34" spans="23:24">
+      <c r="X34" s="208"/>
+    </row>
+    <row r="35" spans="23:24">
+      <c r="W35" s="208"/>
+    </row>
+    <row r="36" spans="23:24">
+      <c r="W36" s="208"/>
+    </row>
+    <row r="37" spans="23:24">
+      <c r="X37" s="208"/>
+    </row>
+    <row r="38" spans="23:24">
+      <c r="W38" s="208"/>
+    </row>
+    <row r="39" spans="23:24">
+      <c r="X39" s="208"/>
+    </row>
+    <row r="40" spans="23:24">
+      <c r="W40" s="208"/>
+    </row>
+    <row r="41" spans="23:24">
+      <c r="X41" s="208"/>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="211"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="P14:Z14"/>
+    <mergeCell ref="S15:Z15"/>
+    <mergeCell ref="AB15:AG15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:Q10"/>
+    <mergeCell ref="R10:AB10"/>
+    <mergeCell ref="AC10:AL10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="G8:Q8"/>
+    <mergeCell ref="R8:AB8"/>
+    <mergeCell ref="AC8:AL8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G9:Q9"/>
+    <mergeCell ref="R9:AB9"/>
+    <mergeCell ref="AC9:AL9"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A6:F7"/>
+    <mergeCell ref="G6:AL6"/>
+    <mergeCell ref="G7:Q7"/>
+    <mergeCell ref="R7:AB7"/>
+    <mergeCell ref="AC7:AL7"/>
+  </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L
+Form Code表格编号: NGB_SFL_F_7.8_Kik-PHY_0009_CS_A.0&amp;R&amp;G</oddHeader>
+    <oddFooter>&amp;L测试/日期Conducted by/Date:
+&amp;U                                                   &amp;U.&amp;C复核/日期Checked by/Date:
+&amp;U                                            &amp;U.&amp;R测试环境Test Condition:
+&amp;U                &amp;U ℃,&amp;U                 &amp;U%RH</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{948094c8-480e-400b-91c4-c984b7e20814}" enabled="1" method="Standard" siteId="{a1109567-0815-4e1f-88af-e23555482aaa}" contentBits="0" removed="0"/>
